--- a/Mstar-Property-Task-Tracker.xlsx
+++ b/Mstar-Property-Task-Tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R257da747b9b0469a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R8e699934dc034eab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R51d779ea1f6944fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="R6aefc2579bcc4eec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="Rc296b3c00bbf44fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="R0be3e7a7d1244657"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R40fd5b7816544953"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R50be22aacf4c462e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R8a01334b2115450d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="Rbf35a2d2342b4ba7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R60459019ad5a44ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="R56058d6d2a254686"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5546,7 +5546,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a2543aef12142d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R304e6b669a70445c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6657,13 +6657,14 @@
         <x:v>PASS: source inventory, prototype JS syntax, immutable-source hashes, six-sheet IDs and synchronized views. NOT RUN: real-app browser/DB tests; application absent.</x:v>
       </x:c>
       <x:c r="K39" s="44" t="str">
-        <x:v>Local main connected to empty origin. Commit/push recorded in progress.md and final report.</x:v>
+        <x:v>cd897da pushed to origin/main successfully on 2026-10-09. This records the preceding preparation commit; final report identifies the latest verification commit.</x:v>
       </x:c>
       <x:c r="L39" s="44" t="str">
-        <x:v>Preparation files mirrored to live/. SHA-256 verification recorded in testing.md. No deployable application exists.</x:v>
+        <x:v>17 allowlisted preparation files match live by SHA-256. No deployable app exists. No secrets, .git, dependencies or caches copied.</x:v>
       </x:c>
       <x:c r="M39" s="44" t="str">
-        <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.</x:v>
+        <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
+2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="150" customHeight="1">
@@ -10408,7 +10409,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3153e067c4b549a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6726c2883a704b4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14681,7 +14682,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbca62864724a4ddf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44035d5ab3434e21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19211,13 +19212,14 @@
         <x:v>PASS: source inventory, prototype JS syntax, immutable-source hashes, six-sheet IDs and synchronized views. NOT RUN: real-app browser/DB tests; application absent.</x:v>
       </x:c>
       <x:c r="K16" s="44" t="str">
-        <x:v>Local main connected to empty origin. Commit/push recorded in progress.md and final report.</x:v>
+        <x:v>cd897da pushed to origin/main successfully on 2026-10-09. This records the preceding preparation commit; final report identifies the latest verification commit.</x:v>
       </x:c>
       <x:c r="L16" s="44" t="str">
-        <x:v>Preparation files mirrored to live/. SHA-256 verification recorded in testing.md. No deployable application exists.</x:v>
+        <x:v>17 allowlisted preparation files match live by SHA-256. No deployable app exists. No secrets, .git, dependencies or caches copied.</x:v>
       </x:c>
       <x:c r="M16" s="44" t="str">
-        <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.</x:v>
+        <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
+2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -23115,7 +23117,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d820f6c8e1846aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79ad2f6503194b1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28700,7 +28702,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e67604f301a47f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bebc63bbbba49e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Mstar-Property-Task-Tracker.xlsx
+++ b/Mstar-Property-Task-Tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R40fd5b7816544953"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R50be22aacf4c462e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R8a01334b2115450d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="Rbf35a2d2342b4ba7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R60459019ad5a44ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="R56058d6d2a254686"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R9c82dfab0b064f86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R94fc5426d11e4030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R868c1daef7894273"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="Rdce67be8736a42d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R4b1504229c424cc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="R641e1a803ce443d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -100,7 +100,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="47">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -191,6 +191,9 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -765,63 +768,85 @@
         <x:v>History</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="34" t="str">
+    <x:row r="6" ht="200" customHeight="1">
+      <x:c r="A6" s="46" t="str">
         <x:v>F02</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="44" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="32" t="str">
+      <x:c r="C6" s="44" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent</x:v>
       </x:c>
-      <x:c r="D6" s="32" t="str">
+      <x:c r="D6" s="44" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="32" t="str">
+      <x:c r="E6" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #1: accent not finalized</x:v>
-      </x:c>
-      <x:c r="G6" s="32" t="str">
-        <x:v>Owner: approve accent</x:v>
-      </x:c>
-      <x:c r="H6" s="41"/>
-      <x:c r="I6" s="41"/>
-      <x:c r="J6" s="42"/>
-      <x:c r="K6" s="42"/>
-      <x:c r="L6" s="42"/>
-      <x:c r="M6" s="42"/>
-    </x:row>
-    <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="F6" s="44" t="str">
+        <x:v>Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.</x:v>
+      </x:c>
+      <x:c r="G6" s="44" t="str">
+        <x:v>Codex: use exact wireframe tokens when building the foundation.</x:v>
+      </x:c>
+      <x:c r="H6" s="45"/>
+      <x:c r="I6" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J6" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K6" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L6" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M6" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
+2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="200" customHeight="1">
+      <x:c r="A7" s="46" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B7" s="32" t="str">
+      <x:c r="B7" s="44" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C7" s="32" t="str">
+      <x:c r="C7" s="44" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D7" s="32" t="str">
+      <x:c r="D7" s="44" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="32" t="str">
+      <x:c r="E7" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #2 and §11: logo source needed</x:v>
-      </x:c>
-      <x:c r="G7" s="32" t="str">
-        <x:v>Owner/designer: supply approved logo asset</x:v>
-      </x:c>
-      <x:c r="H7" s="41"/>
-      <x:c r="I7" s="41"/>
-      <x:c r="J7" s="42"/>
-      <x:c r="K7" s="42"/>
-      <x:c r="L7" s="42"/>
-      <x:c r="M7" s="42"/>
+      <x:c r="F7" s="44" t="str">
+        <x:v>Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.</x:v>
+      </x:c>
+      <x:c r="G7" s="44" t="str">
+        <x:v>Owner/designer: supply final header logo later.</x:v>
+      </x:c>
+      <x:c r="H7" s="45"/>
+      <x:c r="I7" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J7" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K7" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L7" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M7" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
+2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
       <x:c r="A8" s="34" t="str">
@@ -5546,7 +5571,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R304e6b669a70445c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a77b8b9ce154b76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5668,34 +5693,45 @@
         <x:v>History</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="34" t="str">
+    <x:row r="6" ht="200" customHeight="1">
+      <x:c r="A6" s="46" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="44" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C6" s="32" t="str">
+      <x:c r="C6" s="44" t="str">
         <x:v>Approve Google Maps Platform or Longdo Map</x:v>
       </x:c>
-      <x:c r="D6" s="32" t="str">
+      <x:c r="D6" s="44" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E6" s="32" t="str">
+      <x:c r="E6" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #8: map provider not selected</x:v>
-      </x:c>
-      <x:c r="G6" s="32" t="str">
-        <x:v>Owner: select map provider and API account</x:v>
-      </x:c>
-      <x:c r="H6" s="41"/>
-      <x:c r="I6" s="41"/>
-      <x:c r="J6" s="42"/>
-      <x:c r="K6" s="42"/>
-      <x:c r="L6" s="42"/>
-      <x:c r="M6" s="42"/>
+      <x:c r="F6" s="44" t="str">
+        <x:v>Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.</x:v>
+      </x:c>
+      <x:c r="G6" s="44" t="str">
+        <x:v>Codex: evaluate free open-source mapping before map step; confirm provider and usage policy.</x:v>
+      </x:c>
+      <x:c r="H6" s="45"/>
+      <x:c r="I6" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J6" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K6" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L6" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M6" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
+2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
       <x:c r="A7" s="34" t="str">
@@ -5726,34 +5762,45 @@
       <x:c r="L7" s="42"/>
       <x:c r="M7" s="42"/>
     </x:row>
-    <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="34" t="str">
+    <x:row r="8" ht="200" customHeight="1">
+      <x:c r="A8" s="46" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B8" s="32" t="str">
+      <x:c r="B8" s="44" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="str">
+      <x:c r="C8" s="44" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D8" s="32" t="str">
+      <x:c r="D8" s="44" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="32" t="str">
+      <x:c r="E8" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #4 unresolved</x:v>
-      </x:c>
-      <x:c r="G8" s="32" t="str">
-        <x:v>Owner: confirm IDs/numbers</x:v>
-      </x:c>
-      <x:c r="H8" s="41"/>
-      <x:c r="I8" s="41"/>
-      <x:c r="J8" s="42"/>
-      <x:c r="K8" s="42"/>
-      <x:c r="L8" s="42"/>
-      <x:c r="M8" s="42"/>
+      <x:c r="F8" s="44" t="str">
+        <x:v>Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.</x:v>
+      </x:c>
+      <x:c r="G8" s="44" t="str">
+        <x:v>Codex: create approved buttons first in foundation; owner: provide contacts before integration.</x:v>
+      </x:c>
+      <x:c r="H8" s="45"/>
+      <x:c r="I8" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J8" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K8" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L8" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M8" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #4 unresolved
+2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
       <x:c r="A9" s="34" t="str">
@@ -5784,63 +5831,85 @@
       <x:c r="L9" s="42"/>
       <x:c r="M9" s="42"/>
     </x:row>
-    <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="34" t="str">
+    <x:row r="10" ht="200" customHeight="1">
+      <x:c r="A10" s="46" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B10" s="32" t="str">
+      <x:c r="B10" s="44" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C10" s="32" t="str">
+      <x:c r="C10" s="44" t="str">
         <x:v>Approve THB only versus optional approximate FX display</x:v>
       </x:c>
-      <x:c r="D10" s="32" t="str">
+      <x:c r="D10" s="44" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="32" t="str">
+      <x:c r="E10" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #6 unresolved</x:v>
-      </x:c>
-      <x:c r="G10" s="32" t="str">
-        <x:v>Owner: approve currency policy</x:v>
-      </x:c>
-      <x:c r="H10" s="41"/>
-      <x:c r="I10" s="41"/>
-      <x:c r="J10" s="42"/>
-      <x:c r="K10" s="42"/>
-      <x:c r="L10" s="42"/>
-      <x:c r="M10" s="42"/>
-    </x:row>
-    <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="34" t="str">
+      <x:c r="F10" s="44" t="str">
+        <x:v>Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
+      </x:c>
+      <x:c r="G10" s="44" t="str">
+        <x:v>Codex: implement USD/THB during authorized currency work; confirm rate source.</x:v>
+      </x:c>
+      <x:c r="H10" s="45"/>
+      <x:c r="I10" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J10" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K10" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L10" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M10" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #6 unresolved
+2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="200" customHeight="1">
+      <x:c r="A11" s="46" t="str">
         <x:v>B29</x:v>
       </x:c>
-      <x:c r="B11" s="32" t="str">
+      <x:c r="B11" s="44" t="str">
         <x:v>Decision · Projects</x:v>
       </x:c>
-      <x:c r="C11" s="32" t="str">
+      <x:c r="C11" s="44" t="str">
         <x:v>Approve public project prices versus enquiry-only price list</x:v>
       </x:c>
-      <x:c r="D11" s="32" t="str">
+      <x:c r="D11" s="44" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E11" s="32" t="str">
+      <x:c r="E11" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #7 unresolved</x:v>
-      </x:c>
-      <x:c r="G11" s="32" t="str">
-        <x:v>Owner: approve project price visibility</x:v>
-      </x:c>
-      <x:c r="H11" s="41"/>
-      <x:c r="I11" s="41"/>
-      <x:c r="J11" s="42"/>
-      <x:c r="K11" s="42"/>
-      <x:c r="L11" s="42"/>
-      <x:c r="M11" s="42"/>
+      <x:c r="F11" s="44" t="str">
+        <x:v>Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
+      </x:c>
+      <x:c r="G11" s="44" t="str">
+        <x:v>Codex: add per-record price visibility in authorized backend/admin work after admin wireframe approval.</x:v>
+      </x:c>
+      <x:c r="H11" s="45"/>
+      <x:c r="I11" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J11" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K11" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L11" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M11" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #7 unresolved
+2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
       <x:c r="A12" s="34" t="str">
@@ -6625,7 +6694,7 @@
       <x:c r="L38" s="42"/>
       <x:c r="M38" s="42"/>
     </x:row>
-    <x:row r="39" ht="150" customHeight="1">
+    <x:row r="39" ht="200" customHeight="1">
       <x:c r="A39" s="44" t="str">
         <x:v>R01</x:v>
       </x:c>
@@ -6642,10 +6711,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F39" s="44" t="str">
-        <x:v>Documentation and tracker prepared. Git/live hashes checked. No application, health API, admin or project PostgreSQL configuration exists. Browser file navigation is blocked. G4/G5 remain pending.</x:v>
+        <x:v>Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.</x:v>
       </x:c>
       <x:c r="G39" s="44" t="str">
-        <x:v>Owner: provide Step 1 start prompt and branding choices. Codex: build only authorized foundation, then test real app.</x:v>
+        <x:v>Owner: start foundation build. Codex: prioritize approved LINE/WhatsApp buttons, then finish authorized foundation and test.</x:v>
       </x:c>
       <x:c r="H39" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -6654,17 +6723,18 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J39" s="44" t="str">
-        <x:v>PASS: source inventory, prototype JS syntax, immutable-source hashes, six-sheet IDs and synchronized views. NOT RUN: real-app browser/DB tests; application absent.</x:v>
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
       <x:c r="K39" s="44" t="str">
-        <x:v>cd897da pushed to origin/main successfully on 2026-10-09. This records the preceding preparation commit; final report identifies the latest verification commit.</x:v>
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
       <x:c r="L39" s="44" t="str">
-        <x:v>17 allowlisted preparation files match live by SHA-256. No deployable app exists. No secrets, .git, dependencies or caches copied.</x:v>
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
       <x:c r="M39" s="44" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
-2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.</x:v>
+2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
+2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="150" customHeight="1">
@@ -10409,7 +10479,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6726c2883a704b4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc85086fc0e704f3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14682,7 +14752,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44035d5ab3434e21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7eccad8d34364033"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18890,63 +18960,85 @@
         <x:v>History</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="34" t="str">
+    <x:row r="6" ht="200" customHeight="1">
+      <x:c r="A6" s="46" t="str">
         <x:v>F02</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="44" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="32" t="str">
+      <x:c r="C6" s="44" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent</x:v>
       </x:c>
-      <x:c r="D6" s="32" t="str">
+      <x:c r="D6" s="44" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="32" t="str">
+      <x:c r="E6" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #1: accent not finalized</x:v>
-      </x:c>
-      <x:c r="G6" s="32" t="str">
-        <x:v>Owner: approve accent</x:v>
-      </x:c>
-      <x:c r="H6" s="41"/>
-      <x:c r="I6" s="41"/>
-      <x:c r="J6" s="42"/>
-      <x:c r="K6" s="42"/>
-      <x:c r="L6" s="42"/>
-      <x:c r="M6" s="42"/>
-    </x:row>
-    <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="F6" s="44" t="str">
+        <x:v>Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.</x:v>
+      </x:c>
+      <x:c r="G6" s="44" t="str">
+        <x:v>Codex: use exact wireframe tokens when building the foundation.</x:v>
+      </x:c>
+      <x:c r="H6" s="45"/>
+      <x:c r="I6" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J6" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K6" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L6" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M6" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
+2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="200" customHeight="1">
+      <x:c r="A7" s="46" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B7" s="32" t="str">
+      <x:c r="B7" s="44" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C7" s="32" t="str">
+      <x:c r="C7" s="44" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D7" s="32" t="str">
+      <x:c r="D7" s="44" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="32" t="str">
+      <x:c r="E7" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #2 and §11: logo source needed</x:v>
-      </x:c>
-      <x:c r="G7" s="32" t="str">
-        <x:v>Owner/designer: supply approved logo asset</x:v>
-      </x:c>
-      <x:c r="H7" s="41"/>
-      <x:c r="I7" s="41"/>
-      <x:c r="J7" s="42"/>
-      <x:c r="K7" s="42"/>
-      <x:c r="L7" s="42"/>
-      <x:c r="M7" s="42"/>
+      <x:c r="F7" s="44" t="str">
+        <x:v>Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.</x:v>
+      </x:c>
+      <x:c r="G7" s="44" t="str">
+        <x:v>Owner/designer: supply final header logo later.</x:v>
+      </x:c>
+      <x:c r="H7" s="45"/>
+      <x:c r="I7" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J7" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K7" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L7" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M7" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
+2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
       <x:c r="A8" s="34" t="str">
@@ -19006,34 +19098,45 @@
       <x:c r="L9" s="42"/>
       <x:c r="M9" s="42"/>
     </x:row>
-    <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="34" t="str">
+    <x:row r="10" ht="200" customHeight="1">
+      <x:c r="A10" s="46" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B10" s="32" t="str">
+      <x:c r="B10" s="44" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C10" s="32" t="str">
+      <x:c r="C10" s="44" t="str">
         <x:v>Approve Google Maps Platform or Longdo Map</x:v>
       </x:c>
-      <x:c r="D10" s="32" t="str">
+      <x:c r="D10" s="44" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="32" t="str">
+      <x:c r="E10" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #8: map provider not selected</x:v>
-      </x:c>
-      <x:c r="G10" s="32" t="str">
-        <x:v>Owner: select map provider and API account</x:v>
-      </x:c>
-      <x:c r="H10" s="41"/>
-      <x:c r="I10" s="41"/>
-      <x:c r="J10" s="42"/>
-      <x:c r="K10" s="42"/>
-      <x:c r="L10" s="42"/>
-      <x:c r="M10" s="42"/>
+      <x:c r="F10" s="44" t="str">
+        <x:v>Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.</x:v>
+      </x:c>
+      <x:c r="G10" s="44" t="str">
+        <x:v>Codex: evaluate free open-source mapping before map step; confirm provider and usage policy.</x:v>
+      </x:c>
+      <x:c r="H10" s="45"/>
+      <x:c r="I10" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J10" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K10" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L10" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M10" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
+2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
       <x:c r="A11" s="34" t="str">
@@ -19064,34 +19167,45 @@
       <x:c r="L11" s="42"/>
       <x:c r="M11" s="42"/>
     </x:row>
-    <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="34" t="str">
+    <x:row r="12" ht="200" customHeight="1">
+      <x:c r="A12" s="46" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B12" s="32" t="str">
+      <x:c r="B12" s="44" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C12" s="32" t="str">
+      <x:c r="C12" s="44" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D12" s="32" t="str">
+      <x:c r="D12" s="44" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E12" s="32" t="str">
+      <x:c r="E12" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #4 unresolved</x:v>
-      </x:c>
-      <x:c r="G12" s="32" t="str">
-        <x:v>Owner: confirm IDs/numbers</x:v>
-      </x:c>
-      <x:c r="H12" s="41"/>
-      <x:c r="I12" s="41"/>
-      <x:c r="J12" s="42"/>
-      <x:c r="K12" s="42"/>
-      <x:c r="L12" s="42"/>
-      <x:c r="M12" s="42"/>
+      <x:c r="F12" s="44" t="str">
+        <x:v>Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.</x:v>
+      </x:c>
+      <x:c r="G12" s="44" t="str">
+        <x:v>Codex: create approved buttons first in foundation; owner: provide contacts before integration.</x:v>
+      </x:c>
+      <x:c r="H12" s="45"/>
+      <x:c r="I12" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J12" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K12" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L12" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M12" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #4 unresolved
+2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
       <x:c r="A13" s="34" t="str">
@@ -19122,65 +19236,87 @@
       <x:c r="L13" s="42"/>
       <x:c r="M13" s="42"/>
     </x:row>
-    <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="34" t="str">
+    <x:row r="14" ht="200" customHeight="1">
+      <x:c r="A14" s="46" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B14" s="32" t="str">
+      <x:c r="B14" s="44" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C14" s="32" t="str">
+      <x:c r="C14" s="44" t="str">
         <x:v>Approve THB only versus optional approximate FX display</x:v>
       </x:c>
-      <x:c r="D14" s="32" t="str">
+      <x:c r="D14" s="44" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E14" s="32" t="str">
+      <x:c r="E14" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #6 unresolved</x:v>
-      </x:c>
-      <x:c r="G14" s="32" t="str">
-        <x:v>Owner: approve currency policy</x:v>
-      </x:c>
-      <x:c r="H14" s="41"/>
-      <x:c r="I14" s="41"/>
-      <x:c r="J14" s="42"/>
-      <x:c r="K14" s="42"/>
-      <x:c r="L14" s="42"/>
-      <x:c r="M14" s="42"/>
-    </x:row>
-    <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="34" t="str">
+      <x:c r="F14" s="44" t="str">
+        <x:v>Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
+      </x:c>
+      <x:c r="G14" s="44" t="str">
+        <x:v>Codex: implement USD/THB during authorized currency work; confirm rate source.</x:v>
+      </x:c>
+      <x:c r="H14" s="45"/>
+      <x:c r="I14" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J14" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K14" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L14" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M14" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #6 unresolved
+2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="200" customHeight="1">
+      <x:c r="A15" s="46" t="str">
         <x:v>B29</x:v>
       </x:c>
-      <x:c r="B15" s="32" t="str">
+      <x:c r="B15" s="44" t="str">
         <x:v>Decision · Projects</x:v>
       </x:c>
-      <x:c r="C15" s="32" t="str">
+      <x:c r="C15" s="44" t="str">
         <x:v>Approve public project prices versus enquiry-only price list</x:v>
       </x:c>
-      <x:c r="D15" s="32" t="str">
+      <x:c r="D15" s="44" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E15" s="32" t="str">
+      <x:c r="E15" s="44" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F15" s="32" t="str">
-        <x:v>BUILD-SPEC §12 #7 unresolved</x:v>
-      </x:c>
-      <x:c r="G15" s="32" t="str">
-        <x:v>Owner: approve project price visibility</x:v>
-      </x:c>
-      <x:c r="H15" s="41"/>
-      <x:c r="I15" s="41"/>
-      <x:c r="J15" s="42"/>
-      <x:c r="K15" s="42"/>
-      <x:c r="L15" s="42"/>
-      <x:c r="M15" s="42"/>
-    </x:row>
-    <x:row r="16" ht="150" customHeight="1">
+      <x:c r="F15" s="44" t="str">
+        <x:v>Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
+      </x:c>
+      <x:c r="G15" s="44" t="str">
+        <x:v>Codex: add per-record price visibility in authorized backend/admin work after admin wireframe approval.</x:v>
+      </x:c>
+      <x:c r="H15" s="45"/>
+      <x:c r="I15" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J15" s="44" t="str">
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+      </x:c>
+      <x:c r="K15" s="44" t="str">
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+      </x:c>
+      <x:c r="L15" s="44" t="str">
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+      </x:c>
+      <x:c r="M15" s="44" t="str">
+        <x:v>Original planning evidence: BUILD-SPEC §12 #7 unresolved
+2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="200" customHeight="1">
       <x:c r="A16" s="44" t="str">
         <x:v>R01</x:v>
       </x:c>
@@ -19197,10 +19333,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F16" s="44" t="str">
-        <x:v>Documentation and tracker prepared. Git/live hashes checked. No application, health API, admin or project PostgreSQL configuration exists. Browser file navigation is blocked. G4/G5 remain pending.</x:v>
+        <x:v>Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.</x:v>
       </x:c>
       <x:c r="G16" s="44" t="str">
-        <x:v>Owner: provide Step 1 start prompt and branding choices. Codex: build only authorized foundation, then test real app.</x:v>
+        <x:v>Owner: start foundation build. Codex: prioritize approved LINE/WhatsApp buttons, then finish authorized foundation and test.</x:v>
       </x:c>
       <x:c r="H16" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -19209,17 +19345,18 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J16" s="44" t="str">
-        <x:v>PASS: source inventory, prototype JS syntax, immutable-source hashes, six-sheet IDs and synchronized views. NOT RUN: real-app browser/DB tests; application absent.</x:v>
+        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
       <x:c r="K16" s="44" t="str">
-        <x:v>cd897da pushed to origin/main successfully on 2026-10-09. This records the preceding preparation commit; final report identifies the latest verification commit.</x:v>
+        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
       <x:c r="L16" s="44" t="str">
-        <x:v>17 allowlisted preparation files match live by SHA-256. No deployable app exists. No secrets, .git, dependencies or caches copied.</x:v>
+        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
       <x:c r="M16" s="44" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
-2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.</x:v>
+2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
+2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -23117,7 +23254,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79ad2f6503194b1d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f0001341ca4694"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28702,7 +28839,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bebc63bbbba49e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb27453f98bb54861"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Mstar-Property-Task-Tracker.xlsx
+++ b/Mstar-Property-Task-Tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R7b765efbff6245ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R7334d51d33cd4af8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="Rc7825516e6a24465"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="R918bc54d48a54859"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="Re3b9a372d07f4f19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="Rc9aa087cd88842ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R4a40b80151914e17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R649c040592ee4b5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="Ra0cb1649582144db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="R351d6b6b298b4723"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R4e7644ae36de49bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="Rd670fa657f854d60"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -683,7 +683,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Foundation implemented, Pending runtime gates. 81 permanent IDs; append history. Port 3000 closed on owner request. Category tabs mirror open tasks; status tabs canonical.</x:v>
+        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -1122,7 +1122,7 @@
 2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="26" customHeight="1">
+    <x:row r="15" ht="250" customHeight="1">
       <x:c r="A15" s="46" t="str">
         <x:v>F08</x:v>
       </x:c>
@@ -1130,7 +1130,7 @@
         <x:v>Step 3 · Cards</x:v>
       </x:c>
       <x:c r="C15" s="44" t="str">
-        <x:v>4:3 cards, photo galleries, save heart, badges and type-specific facts</x:v>
+        <x:v>Realtor-style 3:2 listing cards, photo controls, bottom-right save heart, facts/address and Contact agent dialog trigger</x:v>
       </x:c>
       <x:c r="D15" s="44" t="str">
         <x:v>Frontend</x:v>
@@ -1139,17 +1139,28 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="F15" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+        <x:v>V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
       </x:c>
       <x:c r="G15" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
+        <x:v>Codex: build revised card only under Step 3 authorization, after the real database step.</x:v>
       </x:c>
       <x:c r="H15" s="45"/>
-      <x:c r="I15" s="45"/>
-      <x:c r="J15" s="44"/>
-      <x:c r="K15" s="44"/>
-      <x:c r="L15" s="44"/>
-      <x:c r="M15" s="44"/>
+      <x:c r="I15" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J15" s="44" t="str">
+        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
+      </x:c>
+      <x:c r="K15" s="44" t="str">
+        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
+      </x:c>
+      <x:c r="L15" s="44" t="str">
+        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
+      </x:c>
+      <x:c r="M15" s="44" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 V5 adoption: V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
       <x:c r="A16" s="46" t="str">
@@ -1499,7 +1510,7 @@
       <x:c r="L27" s="44"/>
       <x:c r="M27" s="44"/>
     </x:row>
-    <x:row r="28" ht="26" customHeight="1">
+    <x:row r="28" ht="250" customHeight="1">
       <x:c r="A28" s="46" t="str">
         <x:v>F21</x:v>
       </x:c>
@@ -1507,7 +1518,7 @@
         <x:v>Step 6 · Contact</x:v>
       </x:c>
       <x:c r="C28" s="44" t="str">
-        <x:v>Desktop sticky enquiry box and phone sticky action bar</x:v>
+        <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
       </x:c>
       <x:c r="D28" s="44" t="str">
         <x:v>Frontend</x:v>
@@ -1516,17 +1527,28 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="F28" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+        <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
       <x:c r="G28" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
+        <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
       </x:c>
       <x:c r="H28" s="45"/>
-      <x:c r="I28" s="45"/>
-      <x:c r="J28" s="44"/>
-      <x:c r="K28" s="44"/>
-      <x:c r="L28" s="44"/>
-      <x:c r="M28" s="44"/>
+      <x:c r="I28" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J28" s="44" t="str">
+        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
+      </x:c>
+      <x:c r="K28" s="44" t="str">
+        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
+      </x:c>
+      <x:c r="L28" s="44" t="str">
+        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
+      </x:c>
+      <x:c r="M28" s="44" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="26" customHeight="1">
       <x:c r="A29" s="46" t="str">
@@ -1615,7 +1637,7 @@
       <x:c r="L31" s="44"/>
       <x:c r="M31" s="44"/>
     </x:row>
-    <x:row r="32" ht="26" customHeight="1">
+    <x:row r="32" ht="250" customHeight="1">
       <x:c r="A32" s="46" t="str">
         <x:v>F25</x:v>
       </x:c>
@@ -1623,7 +1645,7 @@
         <x:v>Step 7 · Home</x:v>
       </x:c>
       <x:c r="C32" s="44" t="str">
-        <x:v>Featured homes, regions with accurate listing counts</x:v>
+        <x:v>Homes for you carousel directly below search; regions with real listing counts</x:v>
       </x:c>
       <x:c r="D32" s="44" t="str">
         <x:v>Frontend</x:v>
@@ -1632,17 +1654,28 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="F32" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+        <x:v>V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
       <x:c r="G32" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
+        <x:v>Codex: implement approved home-page.html only under Step 7 authorization.</x:v>
       </x:c>
       <x:c r="H32" s="45"/>
-      <x:c r="I32" s="45"/>
-      <x:c r="J32" s="44"/>
-      <x:c r="K32" s="44"/>
-      <x:c r="L32" s="44"/>
-      <x:c r="M32" s="44"/>
+      <x:c r="I32" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J32" s="44" t="str">
+        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
+      </x:c>
+      <x:c r="K32" s="44" t="str">
+        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
+      </x:c>
+      <x:c r="L32" s="44" t="str">
+        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
+      </x:c>
+      <x:c r="M32" s="44" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="26" customHeight="1">
       <x:c r="A33" s="46" t="str">
@@ -8841,7 +8874,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17602caa8f8b42fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R009d4f61af814f26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8878,7 +8911,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Foundation implemented, Pending runtime gates. 81 permanent IDs; append history. Port 3000 closed on owner request. Category tabs mirror open tasks; status tabs canonical.</x:v>
+        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -9201,10 +9234,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F12" s="44" t="str">
-        <x:v>Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed.</x:v>
+        <x:v>V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.</x:v>
       </x:c>
       <x:c r="G12" s="44" t="str">
-        <x:v>Codex: stop before Step 2. Retest only when owner opens localhost; verify real PostgreSQL.</x:v>
+        <x:v>Owner: supply the next stage prompt or authorize deferred tests. Codex: follow V5 one stage at a time; do not automatically advance.</x:v>
       </x:c>
       <x:c r="H12" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -9213,19 +9246,20 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J12" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
       <x:c r="K12" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
       <x:c r="L12" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
       <x:c r="M12" s="44" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
-2026-10-09 foundation: Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed. Owner requested localhost closure; do not reopen automatically.</x:v>
+2026-10-09 foundation: Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
@@ -16976,7 +17010,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R189ad101049e4bae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fa981a2a59a45ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17013,7 +17047,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Foundation implemented, Pending runtime gates. 81 permanent IDs; append history. Port 3000 closed on owner request. Category tabs mirror open tasks; status tabs canonical.</x:v>
+        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -24658,7 +24692,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recece073434e4a04"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc946a6e83e84fa8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24695,7 +24729,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Foundation implemented, Pending runtime gates. 81 permanent IDs; append history. Port 3000 closed on owner request. Category tabs mirror open tasks; status tabs canonical.</x:v>
+        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -32246,7 +32280,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Foundation implemented, Pending runtime gates. 81 permanent IDs; append history. Port 3000 closed on owner request. Category tabs mirror open tasks; status tabs canonical.</x:v>
+        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -32713,10 +32747,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F16" s="44" t="str">
-        <x:v>Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed.</x:v>
+        <x:v>V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.</x:v>
       </x:c>
       <x:c r="G16" s="44" t="str">
-        <x:v>Codex: stop before Step 2. Retest only when owner opens localhost; verify real PostgreSQL.</x:v>
+        <x:v>Owner: supply the next stage prompt or authorize deferred tests. Codex: follow V5 one stage at a time; do not automatically advance.</x:v>
       </x:c>
       <x:c r="H16" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -32725,19 +32759,20 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J16" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
       <x:c r="K16" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
       <x:c r="L16" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
       <x:c r="M16" s="44" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
-2026-10-09 foundation: Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed. Owner requested localhost closure; do not reopen automatically.</x:v>
+2026-10-09 foundation: Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="250" customHeight="1">
@@ -40185,7 +40220,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R193e42a6cff2492e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dcf99137e75432f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40222,7 +40257,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Foundation implemented, Pending runtime gates. 81 permanent IDs; append history. Port 3000 closed on owner request. Category tabs mirror open tasks; status tabs canonical.</x:v>
+        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -40307,7 +40342,7 @@
         <x:v>History</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="26" customHeight="1">
+    <x:row r="6" ht="250" customHeight="1">
       <x:c r="A6" s="46" t="str">
         <x:v>F08</x:v>
       </x:c>
@@ -40315,7 +40350,7 @@
         <x:v>Step 3 · Cards</x:v>
       </x:c>
       <x:c r="C6" s="44" t="str">
-        <x:v>4:3 cards, photo galleries, save heart, badges and type-specific facts</x:v>
+        <x:v>Realtor-style 3:2 listing cards, photo controls, bottom-right save heart, facts/address and Contact agent dialog trigger</x:v>
       </x:c>
       <x:c r="D6" s="44" t="str">
         <x:v>Frontend</x:v>
@@ -40324,17 +40359,28 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="F6" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+        <x:v>V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
       </x:c>
       <x:c r="G6" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
+        <x:v>Codex: build revised card only under Step 3 authorization, after the real database step.</x:v>
       </x:c>
       <x:c r="H6" s="45"/>
-      <x:c r="I6" s="45"/>
-      <x:c r="J6" s="44"/>
-      <x:c r="K6" s="44"/>
-      <x:c r="L6" s="44"/>
-      <x:c r="M6" s="44"/>
+      <x:c r="I6" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J6" s="44" t="str">
+        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
+      </x:c>
+      <x:c r="K6" s="44" t="str">
+        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
+      </x:c>
+      <x:c r="L6" s="44" t="str">
+        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
+      </x:c>
+      <x:c r="M6" s="44" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 V5 adoption: V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
       <x:c r="A7" s="46" t="str">
@@ -40684,7 +40730,7 @@
       <x:c r="L18" s="44"/>
       <x:c r="M18" s="44"/>
     </x:row>
-    <x:row r="19" ht="26" customHeight="1">
+    <x:row r="19" ht="250" customHeight="1">
       <x:c r="A19" s="46" t="str">
         <x:v>F21</x:v>
       </x:c>
@@ -40692,7 +40738,7 @@
         <x:v>Step 6 · Contact</x:v>
       </x:c>
       <x:c r="C19" s="44" t="str">
-        <x:v>Desktop sticky enquiry box and phone sticky action bar</x:v>
+        <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
       </x:c>
       <x:c r="D19" s="44" t="str">
         <x:v>Frontend</x:v>
@@ -40701,17 +40747,28 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="F19" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+        <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
       <x:c r="G19" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
+        <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
       </x:c>
       <x:c r="H19" s="45"/>
-      <x:c r="I19" s="45"/>
-      <x:c r="J19" s="44"/>
-      <x:c r="K19" s="44"/>
-      <x:c r="L19" s="44"/>
-      <x:c r="M19" s="44"/>
+      <x:c r="I19" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J19" s="44" t="str">
+        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
+      </x:c>
+      <x:c r="K19" s="44" t="str">
+        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
+      </x:c>
+      <x:c r="L19" s="44" t="str">
+        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
+      </x:c>
+      <x:c r="M19" s="44" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
       <x:c r="A20" s="46" t="str">
@@ -40800,7 +40857,7 @@
       <x:c r="L22" s="44"/>
       <x:c r="M22" s="44"/>
     </x:row>
-    <x:row r="23" ht="26" customHeight="1">
+    <x:row r="23" ht="250" customHeight="1">
       <x:c r="A23" s="46" t="str">
         <x:v>F25</x:v>
       </x:c>
@@ -40808,7 +40865,7 @@
         <x:v>Step 7 · Home</x:v>
       </x:c>
       <x:c r="C23" s="44" t="str">
-        <x:v>Featured homes, regions with accurate listing counts</x:v>
+        <x:v>Homes for you carousel directly below search; regions with real listing counts</x:v>
       </x:c>
       <x:c r="D23" s="44" t="str">
         <x:v>Frontend</x:v>
@@ -40817,17 +40874,28 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="F23" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+        <x:v>V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
       <x:c r="G23" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
+        <x:v>Codex: implement approved home-page.html only under Step 7 authorization.</x:v>
       </x:c>
       <x:c r="H23" s="45"/>
-      <x:c r="I23" s="45"/>
-      <x:c r="J23" s="44"/>
-      <x:c r="K23" s="44"/>
-      <x:c r="L23" s="44"/>
-      <x:c r="M23" s="44"/>
+      <x:c r="I23" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J23" s="44" t="str">
+        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
+      </x:c>
+      <x:c r="K23" s="44" t="str">
+        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
+      </x:c>
+      <x:c r="L23" s="44" t="str">
+        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
+      </x:c>
+      <x:c r="M23" s="44" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
       <x:c r="A24" s="46" t="str">
@@ -48654,7 +48722,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e60dd5e858d4191"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd923c45a72a64d84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Mstar-Property-Task-Tracker.xlsx
+++ b/Mstar-Property-Task-Tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R4a40b80151914e17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R649c040592ee4b5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="Ra0cb1649582144db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="R351d6b6b298b4723"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R4e7644ae36de49bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="Rd670fa657f854d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R15871fd3ebf54e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R1362a8b864124b5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="Rc2942399b44044d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="Rcd0af78f991b47a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R4056639bf4294f1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="Rf51eb27c7f0246b7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -356,7 +356,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -377,7 +377,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -398,7 +398,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -419,7 +419,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="MstarDoneTasks" displayName="MstarDoneTasks" ref="A5:M10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -440,7 +440,28 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M69" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
+    <x:tableColumn id="1" name="ID"/>
+    <x:tableColumn id="2" name="Area"/>
+    <x:tableColumn id="3" name="Task"/>
+    <x:tableColumn id="4" name="Side"/>
+    <x:tableColumn id="5" name="Status"/>
+    <x:tableColumn id="6" name="Why / waiting for / evidence"/>
+    <x:tableColumn id="7" name="Next step (who)"/>
+    <x:tableColumn id="8" name="Created date"/>
+    <x:tableColumn id="9" name="Updated date"/>
+    <x:tableColumn id="10" name="Test results"/>
+    <x:tableColumn id="11" name="Git / push"/>
+    <x:tableColumn id="12" name="Live synchronization"/>
+    <x:tableColumn id="13" name="History"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M65" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -683,7 +704,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
+        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -705,14 +726,14 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -724,7 +745,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -768,7 +789,7 @@
         <x:v>History</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="250" customHeight="1">
+    <x:row r="6" ht="310" customHeight="1">
       <x:c r="A6" s="46" t="str">
         <x:v>F02</x:v>
       </x:c>
@@ -785,10 +806,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F6" s="44" t="str">
-        <x:v>Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending.</x:v>
+        <x:v>Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G6" s="44" t="str">
-        <x:v>Codex: preserve approved colours; complete remaining runtime gates.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H6" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -797,18 +818,20 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J6" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K6" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L6" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M6" s="44" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
 2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.
-2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
+2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="250" customHeight="1">
@@ -912,7 +935,7 @@
       <x:c r="L9" s="44"/>
       <x:c r="M9" s="44"/>
     </x:row>
-    <x:row r="10" ht="250" customHeight="1">
+    <x:row r="10" ht="310" customHeight="1">
       <x:c r="A10" s="46" t="str">
         <x:v>F01</x:v>
       </x:c>
@@ -929,10 +952,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F10" s="44" t="str">
-        <x:v>Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending.</x:v>
+        <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G10" s="44" t="str">
-        <x:v>Codex: retest compiled final fixes when owner opens localhost; verify database gate.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H10" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -941,20 +964,22 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J10" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K10" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L10" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M10" s="44" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="250" customHeight="1">
+2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="310" customHeight="1">
       <x:c r="A11" s="46" t="str">
         <x:v>F04</x:v>
       </x:c>
@@ -971,10 +996,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F11" s="44" t="str">
-        <x:v>Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting.</x:v>
+        <x:v>Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G11" s="44" t="str">
-        <x:v>Codex: retest preference flow when owner explicitly opens localhost.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H11" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -983,20 +1008,22 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J11" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K11" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L11" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M11" s="44" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="250" customHeight="1">
+2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="310" customHeight="1">
       <x:c r="A12" s="46" t="str">
         <x:v>F05</x:v>
       </x:c>
@@ -1013,10 +1040,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F12" s="44" t="str">
-        <x:v>Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting.</x:v>
+        <x:v>Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G12" s="44" t="str">
-        <x:v>Codex: retest final phone search containment when localhost is opened.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H12" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -1025,20 +1052,22 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J12" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K12" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L12" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M12" s="44" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="250" customHeight="1">
+2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="310" customHeight="1">
       <x:c r="A13" s="46" t="str">
         <x:v>F06</x:v>
       </x:c>
@@ -1055,10 +1084,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F13" s="44" t="str">
-        <x:v>Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed.</x:v>
+        <x:v>Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G13" s="44" t="str">
-        <x:v>Owner: supply contact details; Codex: complete runtime gates.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H13" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -1067,20 +1096,22 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J13" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K13" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L13" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M13" s="44" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="250" customHeight="1">
+2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="310" customHeight="1">
       <x:c r="A14" s="46" t="str">
         <x:v>F07</x:v>
       </x:c>
@@ -1097,10 +1128,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F14" s="44" t="str">
-        <x:v>Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser.</x:v>
+        <x:v>Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G14" s="44" t="str">
-        <x:v>Codex: rerun preference persistence and search tests when owner opens localhost.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H14" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -1109,17 +1140,19 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J14" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K14" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L14" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M14" s="44" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.</x:v>
+2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="250" customHeight="1">
@@ -8874,7 +8907,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R009d4f61af814f26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13bbbb35cb3e4ec6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8911,7 +8944,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
+        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -8933,14 +8966,14 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -8952,7 +8985,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -8996,7 +9029,7 @@
         <x:v>History</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="200" customHeight="1">
+    <x:row r="6" ht="310" customHeight="1">
       <x:c r="A6" s="46" t="str">
         <x:v>B09</x:v>
       </x:c>
@@ -9004,7 +9037,7 @@
         <x:v>Decision · Map</x:v>
       </x:c>
       <x:c r="C6" s="44" t="str">
-        <x:v>Approve Google Maps Platform or Longdo Map</x:v>
+        <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
       <x:c r="D6" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9013,27 +9046,30 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F6" s="44" t="str">
-        <x:v>Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.</x:v>
+        <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
       <x:c r="G6" s="44" t="str">
-        <x:v>Codex: evaluate free open-source mapping before map step; confirm provider and usage policy.</x:v>
-      </x:c>
-      <x:c r="H6" s="45"/>
+        <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
+      </x:c>
+      <x:c r="H6" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
       <x:c r="I6" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J6" s="44" t="str">
-        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K6" s="44" t="str">
-        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L6" s="44" t="str">
-        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M6" s="44" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
-2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.</x:v>
+2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
+2026-10-09 Step 2: Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
@@ -9217,7 +9253,7 @@
 2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="250" customHeight="1">
+    <x:row r="12" ht="310" customHeight="1">
       <x:c r="A12" s="46" t="str">
         <x:v>R01</x:v>
       </x:c>
@@ -9234,10 +9270,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F12" s="44" t="str">
-        <x:v>V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.</x:v>
+        <x:v>Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request.</x:v>
       </x:c>
       <x:c r="G12" s="44" t="str">
-        <x:v>Owner: supply the next stage prompt or authorize deferred tests. Codex: follow V5 one stage at a time; do not automatically advance.</x:v>
+        <x:v>Codex: close the separate Step 0 utility/reference-review requirements only when authorized; stop before Step 3.</x:v>
       </x:c>
       <x:c r="H12" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -9246,31 +9282,32 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J12" s="44" t="str">
-        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K12" s="44" t="str">
-        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L12" s="44" t="str">
-        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M12" s="44" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
 2026-10-09 foundation: Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed. Owner requested localhost closure; do not reopen automatically.
-2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.</x:v>
+2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.
+2026-10-09 Step 2: Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
       <x:c r="A13" s="46" t="str">
-        <x:v>B01</x:v>
+        <x:v>B05</x:v>
       </x:c>
       <x:c r="B13" s="44" t="str">
-        <x:v>Step 2 · Database</x:v>
+        <x:v>Step 2 · Filters</x:v>
       </x:c>
       <x:c r="C13" s="44" t="str">
-        <x:v>PostgreSQL/Drizzle schema for listings, projects, agents and users</x:v>
+        <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
       </x:c>
       <x:c r="D13" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9293,13 +9330,13 @@
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
       <x:c r="A14" s="46" t="str">
-        <x:v>B02</x:v>
+        <x:v>B06</x:v>
       </x:c>
       <x:c r="B14" s="44" t="str">
-        <x:v>Step 2 · Database</x:v>
+        <x:v>Step 3 · Search</x:v>
       </x:c>
       <x:c r="C14" s="44" t="str">
-        <x:v>Migrations, foreign keys, constraints and rollback procedure</x:v>
+        <x:v>Typed validated listing/search data access and pagination</x:v>
       </x:c>
       <x:c r="D14" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9322,13 +9359,13 @@
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
       <x:c r="A15" s="46" t="str">
-        <x:v>B03</x:v>
+        <x:v>B07</x:v>
       </x:c>
       <x:c r="B15" s="44" t="str">
-        <x:v>Step 2 · Demo</x:v>
+        <x:v>Step 3 · Search</x:v>
       </x:c>
       <x:c r="C15" s="44" t="str">
-        <x:v>Clearly fictional seed listings, projects and agents</x:v>
+        <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
       </x:c>
       <x:c r="D15" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9351,13 +9388,13 @@
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
       <x:c r="A16" s="46" t="str">
-        <x:v>B04</x:v>
+        <x:v>B08</x:v>
       </x:c>
       <x:c r="B16" s="44" t="str">
-        <x:v>Step 2 · Search</x:v>
+        <x:v>Step 4 · Map</x:v>
       </x:c>
       <x:c r="C16" s="44" t="str">
-        <x:v>Indexes for status, intent, type, price, location and title</x:v>
+        <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
       </x:c>
       <x:c r="D16" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9380,13 +9417,13 @@
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
       <x:c r="A17" s="46" t="str">
-        <x:v>B05</x:v>
+        <x:v>B10</x:v>
       </x:c>
       <x:c r="B17" s="44" t="str">
-        <x:v>Step 2 · Filters</x:v>
+        <x:v>Step 4 · Nearby</x:v>
       </x:c>
       <x:c r="C17" s="44" t="str">
-        <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
+        <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
       </x:c>
       <x:c r="D17" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9409,13 +9446,13 @@
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
       <x:c r="A18" s="46" t="str">
-        <x:v>B06</x:v>
+        <x:v>B11</x:v>
       </x:c>
       <x:c r="B18" s="44" t="str">
-        <x:v>Step 3 · Search</x:v>
+        <x:v>Step 5 · Media</x:v>
       </x:c>
       <x:c r="C18" s="44" t="str">
-        <x:v>Typed validated listing/search data access and pagination</x:v>
+        <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
       </x:c>
       <x:c r="D18" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9438,13 +9475,13 @@
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
       <x:c r="A19" s="46" t="str">
-        <x:v>B07</x:v>
+        <x:v>B12</x:v>
       </x:c>
       <x:c r="B19" s="44" t="str">
-        <x:v>Step 3 · Search</x:v>
+        <x:v>Step 5 · Similar</x:v>
       </x:c>
       <x:c r="C19" s="44" t="str">
-        <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
+        <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
       </x:c>
       <x:c r="D19" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9467,13 +9504,13 @@
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
       <x:c r="A20" s="46" t="str">
-        <x:v>B08</x:v>
+        <x:v>B13</x:v>
       </x:c>
       <x:c r="B20" s="44" t="str">
-        <x:v>Step 4 · Map</x:v>
+        <x:v>Step 5 · Metrics</x:v>
       </x:c>
       <x:c r="C20" s="44" t="str">
-        <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
+        <x:v>Comparable pricing/yield gated by verified sample size</x:v>
       </x:c>
       <x:c r="D20" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9496,13 +9533,13 @@
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
       <x:c r="A21" s="46" t="str">
-        <x:v>B10</x:v>
+        <x:v>B14</x:v>
       </x:c>
       <x:c r="B21" s="44" t="str">
-        <x:v>Step 4 · Nearby</x:v>
+        <x:v>Step 6 · Leads</x:v>
       </x:c>
       <x:c r="C21" s="44" t="str">
-        <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
+        <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
       </x:c>
       <x:c r="D21" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9525,13 +9562,13 @@
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
       <x:c r="A22" s="46" t="str">
-        <x:v>B11</x:v>
+        <x:v>B15</x:v>
       </x:c>
       <x:c r="B22" s="44" t="str">
-        <x:v>Step 5 · Media</x:v>
+        <x:v>Step 6 · Leads</x:v>
       </x:c>
       <x:c r="C22" s="44" t="str">
-        <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
+        <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
       </x:c>
       <x:c r="D22" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9554,13 +9591,13 @@
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
       <x:c r="A23" s="46" t="str">
-        <x:v>B12</x:v>
+        <x:v>B16</x:v>
       </x:c>
       <x:c r="B23" s="44" t="str">
-        <x:v>Step 5 · Similar</x:v>
+        <x:v>Step 6 · Security</x:v>
       </x:c>
       <x:c r="C23" s="44" t="str">
-        <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
+        <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
       </x:c>
       <x:c r="D23" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9583,13 +9620,13 @@
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
       <x:c r="A24" s="46" t="str">
-        <x:v>B13</x:v>
+        <x:v>B19</x:v>
       </x:c>
       <x:c r="B24" s="44" t="str">
-        <x:v>Step 5 · Metrics</x:v>
+        <x:v>Step 6 · Chat</x:v>
       </x:c>
       <x:c r="C24" s="44" t="str">
-        <x:v>Comparable pricing/yield gated by verified sample size</x:v>
+        <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
       </x:c>
       <x:c r="D24" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9612,13 +9649,13 @@
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
       <x:c r="A25" s="46" t="str">
-        <x:v>B14</x:v>
+        <x:v>B20</x:v>
       </x:c>
       <x:c r="B25" s="44" t="str">
-        <x:v>Step 6 · Leads</x:v>
+        <x:v>Step 8 · Projects</x:v>
       </x:c>
       <x:c r="C25" s="44" t="str">
-        <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
+        <x:v>Project/unit/plot status logic and validation</x:v>
       </x:c>
       <x:c r="D25" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9641,13 +9678,13 @@
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
       <x:c r="A26" s="46" t="str">
-        <x:v>B15</x:v>
+        <x:v>B21</x:v>
       </x:c>
       <x:c r="B26" s="44" t="str">
-        <x:v>Step 6 · Leads</x:v>
+        <x:v>Step 8 · Booking</x:v>
       </x:c>
       <x:c r="C26" s="44" t="str">
-        <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
+        <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
       </x:c>
       <x:c r="D26" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9670,13 +9707,13 @@
     </x:row>
     <x:row r="27" ht="26" customHeight="1">
       <x:c r="A27" s="46" t="str">
-        <x:v>B16</x:v>
+        <x:v>B22</x:v>
       </x:c>
       <x:c r="B27" s="44" t="str">
-        <x:v>Step 6 · Security</x:v>
+        <x:v>Step 9 · Saved</x:v>
       </x:c>
       <x:c r="C27" s="44" t="str">
-        <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
+        <x:v>Saved listings/searches persistence, new-match calculations</x:v>
       </x:c>
       <x:c r="D27" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9699,13 +9736,13 @@
     </x:row>
     <x:row r="28" ht="26" customHeight="1">
       <x:c r="A28" s="46" t="str">
-        <x:v>B19</x:v>
+        <x:v>B24</x:v>
       </x:c>
       <x:c r="B28" s="44" t="str">
-        <x:v>Step 6 · Chat</x:v>
+        <x:v>Step 10B · Auth</x:v>
       </x:c>
       <x:c r="C28" s="44" t="str">
-        <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
+        <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
       </x:c>
       <x:c r="D28" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9728,13 +9765,13 @@
     </x:row>
     <x:row r="29" ht="26" customHeight="1">
       <x:c r="A29" s="46" t="str">
-        <x:v>B20</x:v>
+        <x:v>B25</x:v>
       </x:c>
       <x:c r="B29" s="44" t="str">
-        <x:v>Step 8 · Projects</x:v>
+        <x:v>Step 10B · Auth</x:v>
       </x:c>
       <x:c r="C29" s="44" t="str">
-        <x:v>Project/unit/plot status logic and validation</x:v>
+        <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
       </x:c>
       <x:c r="D29" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9757,13 +9794,13 @@
     </x:row>
     <x:row r="30" ht="26" customHeight="1">
       <x:c r="A30" s="46" t="str">
-        <x:v>B21</x:v>
+        <x:v>B26</x:v>
       </x:c>
       <x:c r="B30" s="44" t="str">
-        <x:v>Step 8 · Booking</x:v>
+        <x:v>Step 11B · Admin</x:v>
       </x:c>
       <x:c r="C30" s="44" t="str">
-        <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
+        <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
       </x:c>
       <x:c r="D30" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9786,13 +9823,13 @@
     </x:row>
     <x:row r="31" ht="26" customHeight="1">
       <x:c r="A31" s="46" t="str">
-        <x:v>B22</x:v>
+        <x:v>B27</x:v>
       </x:c>
       <x:c r="B31" s="44" t="str">
-        <x:v>Step 9 · Saved</x:v>
+        <x:v>Step 11B · Admin</x:v>
       </x:c>
       <x:c r="C31" s="44" t="str">
-        <x:v>Saved listings/searches persistence, new-match calculations</x:v>
+        <x:v>Admin user management, audit log and sensitive action authorization</x:v>
       </x:c>
       <x:c r="D31" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9815,13 +9852,13 @@
     </x:row>
     <x:row r="32" ht="26" customHeight="1">
       <x:c r="A32" s="46" t="str">
-        <x:v>B24</x:v>
+        <x:v>B30</x:v>
       </x:c>
       <x:c r="B32" s="44" t="str">
-        <x:v>Step 10B · Auth</x:v>
+        <x:v>Step 12 · Deploy</x:v>
       </x:c>
       <x:c r="C32" s="44" t="str">
-        <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
+        <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
       </x:c>
       <x:c r="D32" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9844,13 +9881,13 @@
     </x:row>
     <x:row r="33" ht="26" customHeight="1">
       <x:c r="A33" s="46" t="str">
-        <x:v>B25</x:v>
+        <x:v>B31</x:v>
       </x:c>
       <x:c r="B33" s="44" t="str">
-        <x:v>Step 10B · Auth</x:v>
+        <x:v>Step 12 · Quality</x:v>
       </x:c>
       <x:c r="C33" s="44" t="str">
-        <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
+        <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
       </x:c>
       <x:c r="D33" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9873,13 +9910,13 @@
     </x:row>
     <x:row r="34" ht="26" customHeight="1">
       <x:c r="A34" s="46" t="str">
-        <x:v>B26</x:v>
+        <x:v>B32</x:v>
       </x:c>
       <x:c r="B34" s="44" t="str">
-        <x:v>Step 11B · Admin</x:v>
+        <x:v>Step 12 · Security</x:v>
       </x:c>
       <x:c r="C34" s="44" t="str">
-        <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
+        <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
       </x:c>
       <x:c r="D34" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9902,13 +9939,13 @@
     </x:row>
     <x:row r="35" ht="26" customHeight="1">
       <x:c r="A35" s="46" t="str">
-        <x:v>B27</x:v>
+        <x:v>B33</x:v>
       </x:c>
       <x:c r="B35" s="44" t="str">
-        <x:v>Step 11B · Admin</x:v>
+        <x:v>Step 7 · Owners</x:v>
       </x:c>
       <x:c r="C35" s="44" t="str">
-        <x:v>Admin user management, audit log and sensitive action authorization</x:v>
+        <x:v>Home-value and service enquiry data handling</x:v>
       </x:c>
       <x:c r="D35" s="44" t="str">
         <x:v>Backend</x:v>
@@ -9930,27 +9967,13 @@
       <x:c r="M35" s="44"/>
     </x:row>
     <x:row r="36" ht="26" customHeight="1">
-      <x:c r="A36" s="46" t="str">
-        <x:v>B30</x:v>
-      </x:c>
-      <x:c r="B36" s="44" t="str">
-        <x:v>Step 12 · Deploy</x:v>
-      </x:c>
-      <x:c r="C36" s="44" t="str">
-        <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
-      </x:c>
-      <x:c r="D36" s="44" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E36" s="44" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F36" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G36" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A36" s="46"/>
+      <x:c r="B36" s="44"/>
+      <x:c r="C36" s="44"/>
+      <x:c r="D36" s="44"/>
+      <x:c r="E36" s="44"/>
+      <x:c r="F36" s="44"/>
+      <x:c r="G36" s="44"/>
       <x:c r="H36" s="45"/>
       <x:c r="I36" s="45"/>
       <x:c r="J36" s="44"/>
@@ -9959,27 +9982,13 @@
       <x:c r="M36" s="44"/>
     </x:row>
     <x:row r="37" ht="26" customHeight="1">
-      <x:c r="A37" s="46" t="str">
-        <x:v>B31</x:v>
-      </x:c>
-      <x:c r="B37" s="44" t="str">
-        <x:v>Step 12 · Quality</x:v>
-      </x:c>
-      <x:c r="C37" s="44" t="str">
-        <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
-      </x:c>
-      <x:c r="D37" s="44" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E37" s="44" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F37" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G37" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A37" s="46"/>
+      <x:c r="B37" s="44"/>
+      <x:c r="C37" s="44"/>
+      <x:c r="D37" s="44"/>
+      <x:c r="E37" s="44"/>
+      <x:c r="F37" s="44"/>
+      <x:c r="G37" s="44"/>
       <x:c r="H37" s="45"/>
       <x:c r="I37" s="45"/>
       <x:c r="J37" s="44"/>
@@ -9988,27 +9997,13 @@
       <x:c r="M37" s="44"/>
     </x:row>
     <x:row r="38" ht="26" customHeight="1">
-      <x:c r="A38" s="46" t="str">
-        <x:v>B32</x:v>
-      </x:c>
-      <x:c r="B38" s="44" t="str">
-        <x:v>Step 12 · Security</x:v>
-      </x:c>
-      <x:c r="C38" s="44" t="str">
-        <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
-      </x:c>
-      <x:c r="D38" s="44" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E38" s="44" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F38" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G38" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A38" s="46"/>
+      <x:c r="B38" s="44"/>
+      <x:c r="C38" s="44"/>
+      <x:c r="D38" s="44"/>
+      <x:c r="E38" s="44"/>
+      <x:c r="F38" s="44"/>
+      <x:c r="G38" s="44"/>
       <x:c r="H38" s="45"/>
       <x:c r="I38" s="45"/>
       <x:c r="J38" s="44"/>
@@ -10017,27 +10012,13 @@
       <x:c r="M38" s="44"/>
     </x:row>
     <x:row r="39" ht="200" customHeight="1">
-      <x:c r="A39" s="44" t="str">
-        <x:v>B33</x:v>
-      </x:c>
-      <x:c r="B39" s="44" t="str">
-        <x:v>Step 7 · Owners</x:v>
-      </x:c>
-      <x:c r="C39" s="44" t="str">
-        <x:v>Home-value and service enquiry data handling</x:v>
-      </x:c>
-      <x:c r="D39" s="44" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E39" s="44" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F39" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G39" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A39" s="44"/>
+      <x:c r="B39" s="44"/>
+      <x:c r="C39" s="44"/>
+      <x:c r="D39" s="44"/>
+      <x:c r="E39" s="44"/>
+      <x:c r="F39" s="44"/>
+      <x:c r="G39" s="44"/>
       <x:c r="H39" s="45"/>
       <x:c r="I39" s="45"/>
       <x:c r="J39" s="44"/>
@@ -10046,46 +10027,19 @@
       <x:c r="M39" s="44"/>
     </x:row>
     <x:row r="40" ht="250" customHeight="1">
-      <x:c r="A40" s="44" t="str">
-        <x:v>B34</x:v>
-      </x:c>
-      <x:c r="B40" s="44" t="str">
-        <x:v>Step 1 · Health</x:v>
-      </x:c>
-      <x:c r="C40" s="44" t="str">
-        <x:v>Basic /api/health endpoint with accurate application and database status</x:v>
-      </x:c>
-      <x:c r="D40" s="44" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E40" s="44" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="F40" s="44" t="str">
-        <x:v>Real health API implemented: HTTP 200 app ok, database not_configured, ready false before closure. Configured PostgreSQL is probed with Drizzle select 1; failure returns 503. No real database configuration exists.</x:v>
-      </x:c>
-      <x:c r="G40" s="44" t="str">
-        <x:v>Codex: verify against real PostgreSQL when configured and localhost opening is authorized.</x:v>
-      </x:c>
-      <x:c r="H40" s="45" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="I40" s="45" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="J40" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
-      </x:c>
-      <x:c r="K40" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
-      </x:c>
-      <x:c r="L40" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
-      </x:c>
-      <x:c r="M40" s="44" t="str">
-        <x:v>2026-10-09: Health API planned. No implementation in Step 0.
-2026-10-09 foundation: Real health API implemented: HTTP 200 app ok, database not_configured, ready false before closure. Configured PostgreSQL is probed with Drizzle select 1; failure returns 503. No real database configuration exists. Owner requested localhost closure; do not reopen automatically.</x:v>
-      </x:c>
+      <x:c r="A40" s="44"/>
+      <x:c r="B40" s="44"/>
+      <x:c r="C40" s="44"/>
+      <x:c r="D40" s="44"/>
+      <x:c r="E40" s="44"/>
+      <x:c r="F40" s="44"/>
+      <x:c r="G40" s="44"/>
+      <x:c r="H40" s="45"/>
+      <x:c r="I40" s="45"/>
+      <x:c r="J40" s="44"/>
+      <x:c r="K40" s="44"/>
+      <x:c r="L40" s="44"/>
+      <x:c r="M40" s="44"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="44"/>
@@ -17003,14 +16957,17 @@
       <x:formula>E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E40">
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="E36:E40">
+      <x:formula1>"Done,Pending,Not started"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E6:E35">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fa981a2a59a45ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf97900a44a464015"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17047,7 +17004,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
+        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -17069,14 +17026,14 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -17088,7 +17045,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -24692,7 +24649,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc946a6e83e84fa8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a3d0235b3e94810"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24729,7 +24686,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
+        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -24751,14 +24708,14 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -24770,7 +24727,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -24814,80 +24771,216 @@
         <x:v>History</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="44"/>
-      <x:c r="B6" s="44"/>
-      <x:c r="C6" s="44"/>
-      <x:c r="D6" s="44"/>
-      <x:c r="E6" s="44"/>
-      <x:c r="F6" s="44"/>
-      <x:c r="G6" s="44"/>
-      <x:c r="H6" s="45"/>
-      <x:c r="I6" s="45"/>
-      <x:c r="J6" s="44"/>
-      <x:c r="K6" s="44"/>
-      <x:c r="L6" s="44"/>
-      <x:c r="M6" s="44"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="44"/>
-      <x:c r="B7" s="44"/>
-      <x:c r="C7" s="44"/>
-      <x:c r="D7" s="44"/>
-      <x:c r="E7" s="44"/>
-      <x:c r="F7" s="44"/>
-      <x:c r="G7" s="44"/>
-      <x:c r="H7" s="45"/>
-      <x:c r="I7" s="45"/>
-      <x:c r="J7" s="44"/>
-      <x:c r="K7" s="44"/>
-      <x:c r="L7" s="44"/>
-      <x:c r="M7" s="44"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="44"/>
-      <x:c r="B8" s="44"/>
-      <x:c r="C8" s="44"/>
-      <x:c r="D8" s="44"/>
-      <x:c r="E8" s="44"/>
-      <x:c r="F8" s="44"/>
-      <x:c r="G8" s="44"/>
-      <x:c r="H8" s="45"/>
-      <x:c r="I8" s="45"/>
-      <x:c r="J8" s="44"/>
-      <x:c r="K8" s="44"/>
-      <x:c r="L8" s="44"/>
-      <x:c r="M8" s="44"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="44"/>
-      <x:c r="B9" s="44"/>
-      <x:c r="C9" s="44"/>
-      <x:c r="D9" s="44"/>
-      <x:c r="E9" s="44"/>
-      <x:c r="F9" s="44"/>
-      <x:c r="G9" s="44"/>
-      <x:c r="H9" s="45"/>
-      <x:c r="I9" s="45"/>
-      <x:c r="J9" s="44"/>
-      <x:c r="K9" s="44"/>
-      <x:c r="L9" s="44"/>
-      <x:c r="M9" s="44"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="44"/>
-      <x:c r="B10" s="44"/>
-      <x:c r="C10" s="44"/>
-      <x:c r="D10" s="44"/>
-      <x:c r="E10" s="44"/>
-      <x:c r="F10" s="44"/>
-      <x:c r="G10" s="44"/>
-      <x:c r="H10" s="45"/>
-      <x:c r="I10" s="45"/>
-      <x:c r="J10" s="44"/>
-      <x:c r="K10" s="44"/>
-      <x:c r="L10" s="44"/>
-      <x:c r="M10" s="44"/>
+    <x:row r="6" ht="310" customHeight="1">
+      <x:c r="A6" s="44" t="str">
+        <x:v>B34</x:v>
+      </x:c>
+      <x:c r="B6" s="44" t="str">
+        <x:v>Step 1 · Health</x:v>
+      </x:c>
+      <x:c r="C6" s="44" t="str">
+        <x:v>Basic /api/health endpoint with accurate application and database status</x:v>
+      </x:c>
+      <x:c r="D6" s="44" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E6" s="44" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F6" s="44" t="str">
+        <x:v>Real /api/health now probes the migrated public view rather than an empty database select 1. Actual 200/ready true, stopped-DB 503/unavailable/ready false and recovery to 200 verified.</x:v>
+      </x:c>
+      <x:c r="G6" s="44" t="str">
+        <x:v>Codex: retain truthful readiness and generic errors; start localhost only under owner/test authorization.</x:v>
+      </x:c>
+      <x:c r="H6" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I6" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J6" s="44" t="str">
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+      <x:c r="K6" s="44" t="str">
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
+      </x:c>
+      <x:c r="L6" s="44" t="str">
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M6" s="44" t="str">
+        <x:v>2026-10-09: Health API planned. No implementation in Step 0.
+2026-10-09 foundation: Real health API implemented: HTTP 200 app ok, database not_configured, ready false before closure. Configured PostgreSQL is probed with Drizzle select 1; failure returns 503. No real database configuration exists. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Real /api/health now probes the migrated public view rather than an empty database select 1. Actual 200/ready true, stopped-DB 503/unavailable/ready false and recovery to 200 verified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="310" customHeight="1">
+      <x:c r="A7" s="44" t="str">
+        <x:v>B01</x:v>
+      </x:c>
+      <x:c r="B7" s="44" t="str">
+        <x:v>Step 2 · Database</x:v>
+      </x:c>
+      <x:c r="C7" s="44" t="str">
+        <x:v>PostgreSQL/Drizzle schema for listings, projects, agents and users</x:v>
+      </x:c>
+      <x:c r="D7" s="44" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E7" s="44" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F7" s="44" t="str">
+        <x:v>18-table Drizzle schema implemented with bilingual fields, seven property types, sale/rent rules, explicit price visibility and separate non-superuser migration/read-only app roles. Isolated local development/test PostgreSQL configured; no shared service modified.</x:v>
+      </x:c>
+      <x:c r="G7" s="44" t="str">
+        <x:v>Codex: preserve schema/security contracts in later explicitly authorized stages.</x:v>
+      </x:c>
+      <x:c r="H7" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I7" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J7" s="44" t="str">
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+      <x:c r="K7" s="44" t="str">
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
+      </x:c>
+      <x:c r="L7" s="44" t="str">
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M7" s="44" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 2: 18-table Drizzle schema implemented with bilingual fields, seven property types, sale/rent rules, explicit price visibility and separate non-superuser migration/read-only app roles. Isolated local development/test PostgreSQL configured; no shared service modified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="310" customHeight="1">
+      <x:c r="A8" s="44" t="str">
+        <x:v>B02</x:v>
+      </x:c>
+      <x:c r="B8" s="44" t="str">
+        <x:v>Step 2 · Database</x:v>
+      </x:c>
+      <x:c r="C8" s="44" t="str">
+        <x:v>Migrations, foreign keys, constraints and rollback procedure</x:v>
+      </x:c>
+      <x:c r="D8" s="44" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E8" s="44" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F8" s="44" t="str">
+        <x:v>Generated foundation and custom relational migrations, journal/snapshots, constraints/FKs/triggers and guarded test-only initial rollback implemented. Real pg_dump/committed rollback/pg_restore/rerun pass. No production migration performed.</x:v>
+      </x:c>
+      <x:c r="G8" s="44" t="str">
+        <x:v>Codex: generate reviewed additive migrations for later changes; production migration requires authorization and verified backup.</x:v>
+      </x:c>
+      <x:c r="H8" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I8" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J8" s="44" t="str">
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+      <x:c r="K8" s="44" t="str">
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
+      </x:c>
+      <x:c r="L8" s="44" t="str">
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M8" s="44" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 2: Generated foundation and custom relational migrations, journal/snapshots, constraints/FKs/triggers and guarded test-only initial rollback implemented. Real pg_dump/committed rollback/pg_restore/rerun pass. No production migration performed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="310" customHeight="1">
+      <x:c r="A9" s="44" t="str">
+        <x:v>B03</x:v>
+      </x:c>
+      <x:c r="B9" s="44" t="str">
+        <x:v>Step 2 · Demo</x:v>
+      </x:c>
+      <x:c r="C9" s="44" t="str">
+        <x:v>Clearly fictional seed listings, projects and agents</x:v>
+      </x:c>
+      <x:c r="D9" s="44" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E9" s="44" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F9" s="44" t="str">
+        <x:v>Repeatable local-only seed: 14 explicitly fictional listings, seven types/both intents and related demo records. Invalid domains, disabled users/agents, closed enquiries and off alerts. Public projection excludes demo inventory; no real prices/agents advertised.</x:v>
+      </x:c>
+      <x:c r="G9" s="44" t="str">
+        <x:v>Codex: keep demo data labelled and excluded from genuine inventory; seed only named local dev/test databases.</x:v>
+      </x:c>
+      <x:c r="H9" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I9" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J9" s="44" t="str">
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+      <x:c r="K9" s="44" t="str">
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
+      </x:c>
+      <x:c r="L9" s="44" t="str">
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M9" s="44" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 2: Repeatable local-only seed: 14 explicitly fictional listings, seven types/both intents and related demo records. Invalid domains, disabled users/agents, closed enquiries and off alerts. Public projection excludes demo inventory; no real prices/agents advertised. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="310" customHeight="1">
+      <x:c r="A10" s="44" t="str">
+        <x:v>B04</x:v>
+      </x:c>
+      <x:c r="B10" s="44" t="str">
+        <x:v>Step 2 · Search</x:v>
+      </x:c>
+      <x:c r="C10" s="44" t="str">
+        <x:v>Indexes for status, intent, type, price, location and title</x:v>
+      </x:c>
+      <x:c r="D10" s="44" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E10" s="44" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F10" s="44" t="str">
+        <x:v>Intent/type/status/price, location/status, bounding coordinates, publication/feed and bilingual simple-text indexes implemented. Catalog and EXPLAIN use checks pass. Tiny-seed plans prove indexes are usable, not production speed.</x:v>
+      </x:c>
+      <x:c r="G10" s="44" t="str">
+        <x:v>Codex: use parameterized typed queries in Step 3; profile against realistic volume during later QA.</x:v>
+      </x:c>
+      <x:c r="H10" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I10" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J10" s="44" t="str">
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+      <x:c r="K10" s="44" t="str">
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
+      </x:c>
+      <x:c r="L10" s="44" t="str">
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M10" s="44" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 2: Intent/type/status/price, location/status, bounding coordinates, publication/feed and bilingual simple-text indexes implemented. Catalog and EXPLAIN use checks pass. Tiny-seed plans prove indexes are usable, not production speed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="44"/>
@@ -32244,7 +32337,15 @@
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="E6:E10">
+      <x:formula1>"Done,Pending,Not started"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58e460fd3323412f"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -32280,7 +32381,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
+        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -32302,14 +32403,14 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -32321,7 +32422,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -32365,7 +32466,7 @@
         <x:v>History</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="250" customHeight="1">
+    <x:row r="6" ht="310" customHeight="1">
       <x:c r="A6" s="46" t="str">
         <x:v>F02</x:v>
       </x:c>
@@ -32382,10 +32483,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F6" s="44" t="str">
-        <x:v>Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending.</x:v>
+        <x:v>Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G6" s="44" t="str">
-        <x:v>Codex: preserve approved colours; complete remaining runtime gates.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H6" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -32394,18 +32495,20 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J6" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K6" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L6" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M6" s="44" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
 2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.
-2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
+2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="250" customHeight="1">
@@ -32509,7 +32612,7 @@
       <x:c r="L9" s="44"/>
       <x:c r="M9" s="44"/>
     </x:row>
-    <x:row r="10" ht="200" customHeight="1">
+    <x:row r="10" ht="310" customHeight="1">
       <x:c r="A10" s="46" t="str">
         <x:v>B09</x:v>
       </x:c>
@@ -32517,7 +32620,7 @@
         <x:v>Decision · Map</x:v>
       </x:c>
       <x:c r="C10" s="44" t="str">
-        <x:v>Approve Google Maps Platform or Longdo Map</x:v>
+        <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
       <x:c r="D10" s="44" t="str">
         <x:v>Backend</x:v>
@@ -32526,27 +32629,30 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F10" s="44" t="str">
-        <x:v>Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.</x:v>
+        <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
       <x:c r="G10" s="44" t="str">
-        <x:v>Codex: evaluate free open-source mapping before map step; confirm provider and usage policy.</x:v>
-      </x:c>
-      <x:c r="H10" s="45"/>
+        <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
+      </x:c>
+      <x:c r="H10" s="45" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
       <x:c r="I10" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J10" s="44" t="str">
-        <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K10" s="44" t="str">
-        <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L10" s="44" t="str">
-        <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M10" s="44" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
-2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.</x:v>
+2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
+2026-10-09 Step 2: Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
@@ -32730,7 +32836,7 @@
 2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="250" customHeight="1">
+    <x:row r="16" ht="310" customHeight="1">
       <x:c r="A16" s="44" t="str">
         <x:v>R01</x:v>
       </x:c>
@@ -32747,10 +32853,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F16" s="44" t="str">
-        <x:v>V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.</x:v>
+        <x:v>Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request.</x:v>
       </x:c>
       <x:c r="G16" s="44" t="str">
-        <x:v>Owner: supply the next stage prompt or authorize deferred tests. Codex: follow V5 one stage at a time; do not automatically advance.</x:v>
+        <x:v>Codex: close the separate Step 0 utility/reference-review requirements only when authorized; stop before Step 3.</x:v>
       </x:c>
       <x:c r="H16" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -32759,23 +32865,24 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J16" s="44" t="str">
-        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K16" s="44" t="str">
-        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L16" s="44" t="str">
-        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M16" s="44" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
 2026-10-09 foundation: Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed. Owner requested localhost closure; do not reopen automatically.
-2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="250" customHeight="1">
+2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.
+2026-10-09 Step 2: Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="310" customHeight="1">
       <x:c r="A17" s="44" t="str">
         <x:v>F01</x:v>
       </x:c>
@@ -32792,10 +32899,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F17" s="44" t="str">
-        <x:v>Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending.</x:v>
+        <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G17" s="44" t="str">
-        <x:v>Codex: retest compiled final fixes when owner opens localhost; verify database gate.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H17" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -32804,20 +32911,22 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J17" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K17" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L17" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M17" s="44" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="250" customHeight="1">
+2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="310" customHeight="1">
       <x:c r="A18" s="44" t="str">
         <x:v>F04</x:v>
       </x:c>
@@ -32834,10 +32943,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F18" s="44" t="str">
-        <x:v>Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting.</x:v>
+        <x:v>Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G18" s="44" t="str">
-        <x:v>Codex: retest preference flow when owner explicitly opens localhost.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H18" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -32846,20 +32955,22 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J18" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K18" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L18" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M18" s="44" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="250" customHeight="1">
+2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="310" customHeight="1">
       <x:c r="A19" s="44" t="str">
         <x:v>F05</x:v>
       </x:c>
@@ -32876,10 +32987,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F19" s="44" t="str">
-        <x:v>Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting.</x:v>
+        <x:v>Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G19" s="44" t="str">
-        <x:v>Codex: retest final phone search containment when localhost is opened.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H19" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -32888,20 +32999,22 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J19" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K19" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L19" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M19" s="44" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="250" customHeight="1">
+2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="310" customHeight="1">
       <x:c r="A20" s="44" t="str">
         <x:v>F06</x:v>
       </x:c>
@@ -32918,10 +33031,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F20" s="44" t="str">
-        <x:v>Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed.</x:v>
+        <x:v>Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G20" s="44" t="str">
-        <x:v>Owner: supply contact details; Codex: complete runtime gates.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H20" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -32930,20 +33043,22 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J20" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K20" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L20" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M20" s="44" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="250" customHeight="1">
+2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="310" customHeight="1">
       <x:c r="A21" s="44" t="str">
         <x:v>F07</x:v>
       </x:c>
@@ -32960,10 +33075,10 @@
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F21" s="44" t="str">
-        <x:v>Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser.</x:v>
+        <x:v>Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
       <x:c r="G21" s="44" t="str">
-        <x:v>Codex: rerun preference persistence and search tests when owner opens localhost.</x:v>
+        <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
       <x:c r="H21" s="45" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
@@ -32972,60 +33087,35 @@
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J21" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
+        <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
       <x:c r="K21" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
+        <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
       <x:c r="L21" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
+        <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
       <x:c r="M21" s="44" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.</x:v>
+2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
+2026-10-09 Step 2: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 Step 2: Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="250" customHeight="1">
-      <x:c r="A22" s="44" t="str">
-        <x:v>B34</x:v>
-      </x:c>
-      <x:c r="B22" s="44" t="str">
-        <x:v>Step 1 · Health</x:v>
-      </x:c>
-      <x:c r="C22" s="44" t="str">
-        <x:v>Basic /api/health endpoint with accurate application and database status</x:v>
-      </x:c>
-      <x:c r="D22" s="44" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E22" s="44" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="F22" s="44" t="str">
-        <x:v>Real health API implemented: HTTP 200 app ok, database not_configured, ready false before closure. Configured PostgreSQL is probed with Drizzle select 1; failure returns 503. No real database configuration exists.</x:v>
-      </x:c>
-      <x:c r="G22" s="44" t="str">
-        <x:v>Codex: verify against real PostgreSQL when configured and localhost opening is authorized.</x:v>
-      </x:c>
-      <x:c r="H22" s="45" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="I22" s="45" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="J22" s="44" t="str">
-        <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
-      </x:c>
-      <x:c r="K22" s="44" t="str">
-        <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
-      </x:c>
-      <x:c r="L22" s="44" t="str">
-        <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
-      </x:c>
-      <x:c r="M22" s="44" t="str">
-        <x:v>2026-10-09: Health API planned. No implementation in Step 0.
-2026-10-09 foundation: Real health API implemented: HTTP 200 app ok, database not_configured, ready false before closure. Configured PostgreSQL is probed with Drizzle select 1; failure returns 503. No real database configuration exists. Owner requested localhost closure; do not reopen automatically.</x:v>
-      </x:c>
+      <x:c r="A22" s="44"/>
+      <x:c r="B22" s="44"/>
+      <x:c r="C22" s="44"/>
+      <x:c r="D22" s="44"/>
+      <x:c r="E22" s="44"/>
+      <x:c r="F22" s="44"/>
+      <x:c r="G22" s="44"/>
+      <x:c r="H22" s="45"/>
+      <x:c r="I22" s="45"/>
+      <x:c r="J22" s="44"/>
+      <x:c r="K22" s="44"/>
+      <x:c r="L22" s="44"/>
+      <x:c r="M22" s="44"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="44"/>
@@ -40213,14 +40303,17 @@
       <x:formula>E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E22">
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="E22">
+      <x:formula1>"Done,Pending,Not started"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E6:E21">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dcf99137e75432f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25f240809d04414e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40257,7 +40350,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Active V5 stage guide; owner-approved revised V3 references. No new build step or tests. 81 stable IDs; statuses unchanged. Preview open at owner request. Preserve append-only history.</x:v>
+        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -40279,14 +40372,14 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -40298,7 +40391,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -41218,13 +41311,13 @@
     </x:row>
     <x:row r="35" ht="26" customHeight="1">
       <x:c r="A35" s="46" t="str">
-        <x:v>B01</x:v>
+        <x:v>B05</x:v>
       </x:c>
       <x:c r="B35" s="44" t="str">
-        <x:v>Step 2 · Database</x:v>
+        <x:v>Step 2 · Filters</x:v>
       </x:c>
       <x:c r="C35" s="44" t="str">
-        <x:v>PostgreSQL/Drizzle schema for listings, projects, agents and users</x:v>
+        <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
       </x:c>
       <x:c r="D35" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41247,13 +41340,13 @@
     </x:row>
     <x:row r="36" ht="26" customHeight="1">
       <x:c r="A36" s="46" t="str">
-        <x:v>B02</x:v>
+        <x:v>B06</x:v>
       </x:c>
       <x:c r="B36" s="44" t="str">
-        <x:v>Step 2 · Database</x:v>
+        <x:v>Step 3 · Search</x:v>
       </x:c>
       <x:c r="C36" s="44" t="str">
-        <x:v>Migrations, foreign keys, constraints and rollback procedure</x:v>
+        <x:v>Typed validated listing/search data access and pagination</x:v>
       </x:c>
       <x:c r="D36" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41276,13 +41369,13 @@
     </x:row>
     <x:row r="37" ht="26" customHeight="1">
       <x:c r="A37" s="46" t="str">
-        <x:v>B03</x:v>
+        <x:v>B07</x:v>
       </x:c>
       <x:c r="B37" s="44" t="str">
-        <x:v>Step 2 · Demo</x:v>
+        <x:v>Step 3 · Search</x:v>
       </x:c>
       <x:c r="C37" s="44" t="str">
-        <x:v>Clearly fictional seed listings, projects and agents</x:v>
+        <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
       </x:c>
       <x:c r="D37" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41305,13 +41398,13 @@
     </x:row>
     <x:row r="38" ht="26" customHeight="1">
       <x:c r="A38" s="46" t="str">
-        <x:v>B04</x:v>
+        <x:v>B08</x:v>
       </x:c>
       <x:c r="B38" s="44" t="str">
-        <x:v>Step 2 · Search</x:v>
+        <x:v>Step 4 · Map</x:v>
       </x:c>
       <x:c r="C38" s="44" t="str">
-        <x:v>Indexes for status, intent, type, price, location and title</x:v>
+        <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
       </x:c>
       <x:c r="D38" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41334,13 +41427,13 @@
     </x:row>
     <x:row r="39" ht="26" customHeight="1">
       <x:c r="A39" s="46" t="str">
-        <x:v>B05</x:v>
+        <x:v>B10</x:v>
       </x:c>
       <x:c r="B39" s="44" t="str">
-        <x:v>Step 2 · Filters</x:v>
+        <x:v>Step 4 · Nearby</x:v>
       </x:c>
       <x:c r="C39" s="44" t="str">
-        <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
+        <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
       </x:c>
       <x:c r="D39" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41363,13 +41456,13 @@
     </x:row>
     <x:row r="40" ht="26" customHeight="1">
       <x:c r="A40" s="46" t="str">
-        <x:v>B06</x:v>
+        <x:v>B11</x:v>
       </x:c>
       <x:c r="B40" s="44" t="str">
-        <x:v>Step 3 · Search</x:v>
+        <x:v>Step 5 · Media</x:v>
       </x:c>
       <x:c r="C40" s="44" t="str">
-        <x:v>Typed validated listing/search data access and pagination</x:v>
+        <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
       </x:c>
       <x:c r="D40" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41392,13 +41485,13 @@
     </x:row>
     <x:row r="41" ht="26" customHeight="1">
       <x:c r="A41" s="46" t="str">
-        <x:v>B07</x:v>
+        <x:v>B12</x:v>
       </x:c>
       <x:c r="B41" s="44" t="str">
-        <x:v>Step 3 · Search</x:v>
+        <x:v>Step 5 · Similar</x:v>
       </x:c>
       <x:c r="C41" s="44" t="str">
-        <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
+        <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
       </x:c>
       <x:c r="D41" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41421,13 +41514,13 @@
     </x:row>
     <x:row r="42" ht="26" customHeight="1">
       <x:c r="A42" s="46" t="str">
-        <x:v>B08</x:v>
+        <x:v>B13</x:v>
       </x:c>
       <x:c r="B42" s="44" t="str">
-        <x:v>Step 4 · Map</x:v>
+        <x:v>Step 5 · Metrics</x:v>
       </x:c>
       <x:c r="C42" s="44" t="str">
-        <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
+        <x:v>Comparable pricing/yield gated by verified sample size</x:v>
       </x:c>
       <x:c r="D42" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41450,13 +41543,13 @@
     </x:row>
     <x:row r="43" ht="26" customHeight="1">
       <x:c r="A43" s="46" t="str">
-        <x:v>B10</x:v>
+        <x:v>B14</x:v>
       </x:c>
       <x:c r="B43" s="44" t="str">
-        <x:v>Step 4 · Nearby</x:v>
+        <x:v>Step 6 · Leads</x:v>
       </x:c>
       <x:c r="C43" s="44" t="str">
-        <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
+        <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
       </x:c>
       <x:c r="D43" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41479,13 +41572,13 @@
     </x:row>
     <x:row r="44" ht="26" customHeight="1">
       <x:c r="A44" s="46" t="str">
-        <x:v>B11</x:v>
+        <x:v>B15</x:v>
       </x:c>
       <x:c r="B44" s="44" t="str">
-        <x:v>Step 5 · Media</x:v>
+        <x:v>Step 6 · Leads</x:v>
       </x:c>
       <x:c r="C44" s="44" t="str">
-        <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
+        <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
       </x:c>
       <x:c r="D44" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41508,13 +41601,13 @@
     </x:row>
     <x:row r="45" ht="26" customHeight="1">
       <x:c r="A45" s="46" t="str">
-        <x:v>B12</x:v>
+        <x:v>B16</x:v>
       </x:c>
       <x:c r="B45" s="44" t="str">
-        <x:v>Step 5 · Similar</x:v>
+        <x:v>Step 6 · Security</x:v>
       </x:c>
       <x:c r="C45" s="44" t="str">
-        <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
+        <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
       </x:c>
       <x:c r="D45" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41537,13 +41630,13 @@
     </x:row>
     <x:row r="46" ht="26" customHeight="1">
       <x:c r="A46" s="46" t="str">
-        <x:v>B13</x:v>
+        <x:v>B19</x:v>
       </x:c>
       <x:c r="B46" s="44" t="str">
-        <x:v>Step 5 · Metrics</x:v>
+        <x:v>Step 6 · Chat</x:v>
       </x:c>
       <x:c r="C46" s="44" t="str">
-        <x:v>Comparable pricing/yield gated by verified sample size</x:v>
+        <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
       </x:c>
       <x:c r="D46" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41566,13 +41659,13 @@
     </x:row>
     <x:row r="47" ht="26" customHeight="1">
       <x:c r="A47" s="46" t="str">
-        <x:v>B14</x:v>
+        <x:v>B20</x:v>
       </x:c>
       <x:c r="B47" s="44" t="str">
-        <x:v>Step 6 · Leads</x:v>
+        <x:v>Step 8 · Projects</x:v>
       </x:c>
       <x:c r="C47" s="44" t="str">
-        <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
+        <x:v>Project/unit/plot status logic and validation</x:v>
       </x:c>
       <x:c r="D47" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41595,13 +41688,13 @@
     </x:row>
     <x:row r="48" ht="26" customHeight="1">
       <x:c r="A48" s="46" t="str">
-        <x:v>B15</x:v>
+        <x:v>B21</x:v>
       </x:c>
       <x:c r="B48" s="44" t="str">
-        <x:v>Step 6 · Leads</x:v>
+        <x:v>Step 8 · Booking</x:v>
       </x:c>
       <x:c r="C48" s="44" t="str">
-        <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
+        <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
       </x:c>
       <x:c r="D48" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41624,13 +41717,13 @@
     </x:row>
     <x:row r="49" ht="26" customHeight="1">
       <x:c r="A49" s="46" t="str">
-        <x:v>B16</x:v>
+        <x:v>B22</x:v>
       </x:c>
       <x:c r="B49" s="44" t="str">
-        <x:v>Step 6 · Security</x:v>
+        <x:v>Step 9 · Saved</x:v>
       </x:c>
       <x:c r="C49" s="44" t="str">
-        <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
+        <x:v>Saved listings/searches persistence, new-match calculations</x:v>
       </x:c>
       <x:c r="D49" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41653,13 +41746,13 @@
     </x:row>
     <x:row r="50" ht="26" customHeight="1">
       <x:c r="A50" s="46" t="str">
-        <x:v>B19</x:v>
+        <x:v>B24</x:v>
       </x:c>
       <x:c r="B50" s="44" t="str">
-        <x:v>Step 6 · Chat</x:v>
+        <x:v>Step 10B · Auth</x:v>
       </x:c>
       <x:c r="C50" s="44" t="str">
-        <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
+        <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
       </x:c>
       <x:c r="D50" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41682,13 +41775,13 @@
     </x:row>
     <x:row r="51" ht="26" customHeight="1">
       <x:c r="A51" s="46" t="str">
-        <x:v>B20</x:v>
+        <x:v>B25</x:v>
       </x:c>
       <x:c r="B51" s="44" t="str">
-        <x:v>Step 8 · Projects</x:v>
+        <x:v>Step 10B · Auth</x:v>
       </x:c>
       <x:c r="C51" s="44" t="str">
-        <x:v>Project/unit/plot status logic and validation</x:v>
+        <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
       </x:c>
       <x:c r="D51" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41711,13 +41804,13 @@
     </x:row>
     <x:row r="52" ht="26" customHeight="1">
       <x:c r="A52" s="46" t="str">
-        <x:v>B21</x:v>
+        <x:v>B26</x:v>
       </x:c>
       <x:c r="B52" s="44" t="str">
-        <x:v>Step 8 · Booking</x:v>
+        <x:v>Step 11B · Admin</x:v>
       </x:c>
       <x:c r="C52" s="44" t="str">
-        <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
+        <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
       </x:c>
       <x:c r="D52" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41740,13 +41833,13 @@
     </x:row>
     <x:row r="53" ht="26" customHeight="1">
       <x:c r="A53" s="46" t="str">
-        <x:v>B22</x:v>
+        <x:v>B27</x:v>
       </x:c>
       <x:c r="B53" s="44" t="str">
-        <x:v>Step 9 · Saved</x:v>
+        <x:v>Step 11B · Admin</x:v>
       </x:c>
       <x:c r="C53" s="44" t="str">
-        <x:v>Saved listings/searches persistence, new-match calculations</x:v>
+        <x:v>Admin user management, audit log and sensitive action authorization</x:v>
       </x:c>
       <x:c r="D53" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41769,13 +41862,13 @@
     </x:row>
     <x:row r="54" ht="26" customHeight="1">
       <x:c r="A54" s="46" t="str">
-        <x:v>B24</x:v>
+        <x:v>B30</x:v>
       </x:c>
       <x:c r="B54" s="44" t="str">
-        <x:v>Step 10B · Auth</x:v>
+        <x:v>Step 12 · Deploy</x:v>
       </x:c>
       <x:c r="C54" s="44" t="str">
-        <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
+        <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
       </x:c>
       <x:c r="D54" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41798,13 +41891,13 @@
     </x:row>
     <x:row r="55" ht="26" customHeight="1">
       <x:c r="A55" s="46" t="str">
-        <x:v>B25</x:v>
+        <x:v>B31</x:v>
       </x:c>
       <x:c r="B55" s="44" t="str">
-        <x:v>Step 10B · Auth</x:v>
+        <x:v>Step 12 · Quality</x:v>
       </x:c>
       <x:c r="C55" s="44" t="str">
-        <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
+        <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
       </x:c>
       <x:c r="D55" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41827,13 +41920,13 @@
     </x:row>
     <x:row r="56" ht="26" customHeight="1">
       <x:c r="A56" s="46" t="str">
-        <x:v>B26</x:v>
+        <x:v>B32</x:v>
       </x:c>
       <x:c r="B56" s="44" t="str">
-        <x:v>Step 11B · Admin</x:v>
+        <x:v>Step 12 · Security</x:v>
       </x:c>
       <x:c r="C56" s="44" t="str">
-        <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
+        <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
       </x:c>
       <x:c r="D56" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41856,13 +41949,13 @@
     </x:row>
     <x:row r="57" ht="26" customHeight="1">
       <x:c r="A57" s="46" t="str">
-        <x:v>B27</x:v>
+        <x:v>B33</x:v>
       </x:c>
       <x:c r="B57" s="44" t="str">
-        <x:v>Step 11B · Admin</x:v>
+        <x:v>Step 7 · Owners</x:v>
       </x:c>
       <x:c r="C57" s="44" t="str">
-        <x:v>Admin user management, audit log and sensitive action authorization</x:v>
+        <x:v>Home-value and service enquiry data handling</x:v>
       </x:c>
       <x:c r="D57" s="44" t="str">
         <x:v>Backend</x:v>
@@ -41885,16 +41978,16 @@
     </x:row>
     <x:row r="58" ht="26" customHeight="1">
       <x:c r="A58" s="46" t="str">
-        <x:v>B30</x:v>
+        <x:v>E01</x:v>
       </x:c>
       <x:c r="B58" s="44" t="str">
-        <x:v>Step 12 · Deploy</x:v>
+        <x:v>Step 6 · Email</x:v>
       </x:c>
       <x:c r="C58" s="44" t="str">
-        <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
+        <x:v>Enquiry notification with retryable queue/outbox</x:v>
       </x:c>
       <x:c r="D58" s="44" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Email</x:v>
       </x:c>
       <x:c r="E58" s="44" t="str">
         <x:v>Not started</x:v>
@@ -41914,16 +42007,16 @@
     </x:row>
     <x:row r="59" ht="26" customHeight="1">
       <x:c r="A59" s="46" t="str">
-        <x:v>B31</x:v>
+        <x:v>E02</x:v>
       </x:c>
       <x:c r="B59" s="44" t="str">
-        <x:v>Step 12 · Quality</x:v>
+        <x:v>Step 6 · Email</x:v>
       </x:c>
       <x:c r="C59" s="44" t="str">
-        <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
+        <x:v>Thai and English buyer enquiry acknowledgments</x:v>
       </x:c>
       <x:c r="D59" s="44" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Email</x:v>
       </x:c>
       <x:c r="E59" s="44" t="str">
         <x:v>Not started</x:v>
@@ -41943,16 +42036,16 @@
     </x:row>
     <x:row r="60" ht="26" customHeight="1">
       <x:c r="A60" s="46" t="str">
-        <x:v>B32</x:v>
+        <x:v>E03</x:v>
       </x:c>
       <x:c r="B60" s="44" t="str">
-        <x:v>Step 12 · Security</x:v>
+        <x:v>Step 8 · Email</x:v>
       </x:c>
       <x:c r="C60" s="44" t="str">
-        <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
+        <x:v>Project brochure/price list email delivery</x:v>
       </x:c>
       <x:c r="D60" s="44" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Email</x:v>
       </x:c>
       <x:c r="E60" s="44" t="str">
         <x:v>Not started</x:v>
@@ -41972,16 +42065,16 @@
     </x:row>
     <x:row r="61" ht="26" customHeight="1">
       <x:c r="A61" s="46" t="str">
-        <x:v>B33</x:v>
+        <x:v>E04</x:v>
       </x:c>
       <x:c r="B61" s="44" t="str">
-        <x:v>Step 7 · Owners</x:v>
+        <x:v>Step 8 · Email</x:v>
       </x:c>
       <x:c r="C61" s="44" t="str">
-        <x:v>Home-value and service enquiry data handling</x:v>
+        <x:v>Site visit request and confirmation notifications</x:v>
       </x:c>
       <x:c r="D61" s="44" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Email</x:v>
       </x:c>
       <x:c r="E61" s="44" t="str">
         <x:v>Not started</x:v>
@@ -42001,13 +42094,13 @@
     </x:row>
     <x:row r="62" ht="26" customHeight="1">
       <x:c r="A62" s="46" t="str">
-        <x:v>E01</x:v>
+        <x:v>E05</x:v>
       </x:c>
       <x:c r="B62" s="44" t="str">
-        <x:v>Step 6 · Email</x:v>
+        <x:v>Step 9 · Alerts</x:v>
       </x:c>
       <x:c r="C62" s="44" t="str">
-        <x:v>Enquiry notification with retryable queue/outbox</x:v>
+        <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
       </x:c>
       <x:c r="D62" s="44" t="str">
         <x:v>Email</x:v>
@@ -42030,13 +42123,13 @@
     </x:row>
     <x:row r="63" ht="26" customHeight="1">
       <x:c r="A63" s="46" t="str">
-        <x:v>E02</x:v>
+        <x:v>E06</x:v>
       </x:c>
       <x:c r="B63" s="44" t="str">
-        <x:v>Step 6 · Email</x:v>
+        <x:v>Step 10B · Email</x:v>
       </x:c>
       <x:c r="C63" s="44" t="str">
-        <x:v>Thai and English buyer enquiry acknowledgments</x:v>
+        <x:v>Account verification and recovery messages if email auth approved</x:v>
       </x:c>
       <x:c r="D63" s="44" t="str">
         <x:v>Email</x:v>
@@ -42059,13 +42152,13 @@
     </x:row>
     <x:row r="64" ht="26" customHeight="1">
       <x:c r="A64" s="46" t="str">
-        <x:v>E03</x:v>
+        <x:v>E07</x:v>
       </x:c>
       <x:c r="B64" s="44" t="str">
-        <x:v>Step 8 · Email</x:v>
+        <x:v>Step 11B · Email</x:v>
       </x:c>
       <x:c r="C64" s="44" t="str">
-        <x:v>Project brochure/price list email delivery</x:v>
+        <x:v>Agent notification/routing administration</x:v>
       </x:c>
       <x:c r="D64" s="44" t="str">
         <x:v>Email</x:v>
@@ -42088,13 +42181,13 @@
     </x:row>
     <x:row r="65" ht="26" customHeight="1">
       <x:c r="A65" s="46" t="str">
-        <x:v>E04</x:v>
+        <x:v>E08</x:v>
       </x:c>
       <x:c r="B65" s="44" t="str">
-        <x:v>Step 8 · Email</x:v>
+        <x:v>Step 7 · Email</x:v>
       </x:c>
       <x:c r="C65" s="44" t="str">
-        <x:v>Site visit request and confirmation notifications</x:v>
+        <x:v>Home valuation and service enquiry replies</x:v>
       </x:c>
       <x:c r="D65" s="44" t="str">
         <x:v>Email</x:v>
@@ -42116,27 +42209,13 @@
       <x:c r="M65" s="44"/>
     </x:row>
     <x:row r="66" ht="26" customHeight="1">
-      <x:c r="A66" s="46" t="str">
-        <x:v>E05</x:v>
-      </x:c>
-      <x:c r="B66" s="44" t="str">
-        <x:v>Step 9 · Alerts</x:v>
-      </x:c>
-      <x:c r="C66" s="44" t="str">
-        <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
-      </x:c>
-      <x:c r="D66" s="44" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E66" s="44" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F66" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G66" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A66" s="46"/>
+      <x:c r="B66" s="44"/>
+      <x:c r="C66" s="44"/>
+      <x:c r="D66" s="44"/>
+      <x:c r="E66" s="44"/>
+      <x:c r="F66" s="44"/>
+      <x:c r="G66" s="44"/>
       <x:c r="H66" s="45"/>
       <x:c r="I66" s="45"/>
       <x:c r="J66" s="44"/>
@@ -42145,27 +42224,13 @@
       <x:c r="M66" s="44"/>
     </x:row>
     <x:row r="67" ht="26" customHeight="1">
-      <x:c r="A67" s="46" t="str">
-        <x:v>E06</x:v>
-      </x:c>
-      <x:c r="B67" s="44" t="str">
-        <x:v>Step 10B · Email</x:v>
-      </x:c>
-      <x:c r="C67" s="44" t="str">
-        <x:v>Account verification and recovery messages if email auth approved</x:v>
-      </x:c>
-      <x:c r="D67" s="44" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E67" s="44" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F67" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G67" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A67" s="46"/>
+      <x:c r="B67" s="44"/>
+      <x:c r="C67" s="44"/>
+      <x:c r="D67" s="44"/>
+      <x:c r="E67" s="44"/>
+      <x:c r="F67" s="44"/>
+      <x:c r="G67" s="44"/>
       <x:c r="H67" s="45"/>
       <x:c r="I67" s="45"/>
       <x:c r="J67" s="44"/>
@@ -42174,27 +42239,13 @@
       <x:c r="M67" s="44"/>
     </x:row>
     <x:row r="68" ht="26" customHeight="1">
-      <x:c r="A68" s="46" t="str">
-        <x:v>E07</x:v>
-      </x:c>
-      <x:c r="B68" s="44" t="str">
-        <x:v>Step 11B · Email</x:v>
-      </x:c>
-      <x:c r="C68" s="44" t="str">
-        <x:v>Agent notification/routing administration</x:v>
-      </x:c>
-      <x:c r="D68" s="44" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E68" s="44" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F68" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G68" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A68" s="46"/>
+      <x:c r="B68" s="44"/>
+      <x:c r="C68" s="44"/>
+      <x:c r="D68" s="44"/>
+      <x:c r="E68" s="44"/>
+      <x:c r="F68" s="44"/>
+      <x:c r="G68" s="44"/>
       <x:c r="H68" s="45"/>
       <x:c r="I68" s="45"/>
       <x:c r="J68" s="44"/>
@@ -42203,27 +42254,13 @@
       <x:c r="M68" s="44"/>
     </x:row>
     <x:row r="69" ht="26" customHeight="1">
-      <x:c r="A69" s="46" t="str">
-        <x:v>E08</x:v>
-      </x:c>
-      <x:c r="B69" s="44" t="str">
-        <x:v>Step 7 · Email</x:v>
-      </x:c>
-      <x:c r="C69" s="44" t="str">
-        <x:v>Home valuation and service enquiry replies</x:v>
-      </x:c>
-      <x:c r="D69" s="44" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E69" s="44" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F69" s="44" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G69" s="44" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A69" s="46"/>
+      <x:c r="B69" s="44"/>
+      <x:c r="C69" s="44"/>
+      <x:c r="D69" s="44"/>
+      <x:c r="E69" s="44"/>
+      <x:c r="F69" s="44"/>
+      <x:c r="G69" s="44"/>
       <x:c r="H69" s="45"/>
       <x:c r="I69" s="45"/>
       <x:c r="J69" s="44"/>
@@ -48712,17 +48749,20 @@
       <x:formula>E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="E70:E75">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="E6:E69">
+    <x:dataValidation type="list" sqref="E66:E69">
+      <x:formula1>"Done,Pending,Not started"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E6:E65">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd923c45a72a64d84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22c0e574be984312"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Mstar-Property-Task-Tracker.xlsx
+++ b/Mstar-Property-Task-Tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R15871fd3ebf54e99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R1362a8b864124b5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="Rc2942399b44044d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="Rcd0af78f991b47a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R4056639bf4294f1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="Rf51eb27c7f0246b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R27626f1841ef4132"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R1b22002ff2cb479e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R0989bca6f4704ce0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="Rbffd9243c811433b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="Re71fca11b8984ef5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="R19c5979771d742c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +21,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -59,8 +59,19 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -92,6 +103,21 @@
         <x:fgColor rgb="FF1F2633"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFF6666"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC6EFCE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -100,7 +126,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="47">
+  <x:cellXfs count="63">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -196,11 +222,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="15">
+  <x:dxfs count="33">
     <x:dxf>
       <x:font>
         <x:color rgb="FF92400E"/>
@@ -351,12 +425,192 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -372,12 +626,12 @@
     <x:tableColumn id="12" name="Live synchronization"/>
     <x:tableColumn id="13" name="History"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -393,12 +647,12 @@
     <x:tableColumn id="12" name="Live synchronization"/>
     <x:tableColumn id="13" name="History"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -414,12 +668,12 @@
     <x:tableColumn id="12" name="Live synchronization"/>
     <x:tableColumn id="13" name="History"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="MstarDoneTasks" displayName="MstarDoneTasks" ref="A5:M10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="MstarDoneTasks" displayName="MstarDoneTasks" ref="A5:M10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -435,12 +689,12 @@
     <x:tableColumn id="12" name="Live synchronization"/>
     <x:tableColumn id="13" name="History"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -456,12 +710,12 @@
     <x:tableColumn id="12" name="Live synchronization"/>
     <x:tableColumn id="13" name="History"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M65" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="33" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M65" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -477,7 +731,7 @@
     <x:tableColumn id="12" name="Live synchronization"/>
     <x:tableColumn id="13" name="History"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -674,6 +928,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF202733"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
@@ -704,7 +961,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
+        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -790,43 +1047,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="46" t="str">
+      <x:c r="A6" s="50" t="str">
         <x:v>F02</x:v>
       </x:c>
-      <x:c r="B6" s="44" t="str">
+      <x:c r="B6" s="51" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="44" t="str">
+      <x:c r="C6" s="51" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent</x:v>
       </x:c>
-      <x:c r="D6" s="44" t="str">
+      <x:c r="D6" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="44" t="str">
+      <x:c r="E6" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="44" t="str">
+      <x:c r="F6" s="51" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G6" s="44" t="str">
+      <x:c r="G6" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H6" s="45" t="d">
+      <x:c r="H6" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="45" t="d">
+      <x:c r="I6" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="44" t="str">
+      <x:c r="J6" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="44" t="str">
+      <x:c r="K6" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="44" t="str">
+      <x:c r="L6" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="44" t="str">
+      <x:c r="M6" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
 2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.
 2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.
@@ -835,144 +1092,144 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="250" customHeight="1">
-      <x:c r="A7" s="46" t="str">
+      <x:c r="A7" s="50" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B7" s="44" t="str">
+      <x:c r="B7" s="51" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C7" s="44" t="str">
+      <x:c r="C7" s="51" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D7" s="44" t="str">
+      <x:c r="D7" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="44" t="str">
+      <x:c r="E7" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="44" t="str">
+      <x:c r="F7" s="51" t="str">
         <x:v>Approved temporary crest extracted and implemented. Owner will provide final header logo later.</x:v>
       </x:c>
-      <x:c r="G7" s="44" t="str">
+      <x:c r="G7" s="51" t="str">
         <x:v>Owner: supply final asset/version later; Codex: replace only approved logo.</x:v>
       </x:c>
-      <x:c r="H7" s="45" t="d">
+      <x:c r="H7" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="45" t="d">
+      <x:c r="I7" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="44" t="str">
+      <x:c r="J7" s="51" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K7" s="44" t="str">
+      <x:c r="K7" s="51" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L7" s="44" t="str">
+      <x:c r="L7" s="51" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="44" t="str">
+      <x:c r="M7" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
 2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.
 2026-10-09 foundation: Approved temporary crest extracted and implemented. Owner will provide final header logo later. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="46" t="str">
+      <x:c r="A8" s="50" t="str">
         <x:v>F32</x:v>
       </x:c>
-      <x:c r="B8" s="44" t="str">
+      <x:c r="B8" s="51" t="str">
         <x:v>Step 10A · Wireframe</x:v>
       </x:c>
-      <x:c r="C8" s="44" t="str">
+      <x:c r="C8" s="51" t="str">
         <x:v>Owner-approved login/register/account wireframe before coding</x:v>
       </x:c>
-      <x:c r="D8" s="44" t="str">
+      <x:c r="D8" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="44" t="str">
+      <x:c r="E8" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="44" t="str">
+      <x:c r="F8" s="51" t="str">
         <x:v>Admin/account screens are not part of approved V3 visuals</x:v>
       </x:c>
-      <x:c r="G8" s="44" t="str">
+      <x:c r="G8" s="51" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H8" s="45"/>
-      <x:c r="I8" s="45"/>
-      <x:c r="J8" s="44"/>
-      <x:c r="K8" s="44"/>
-      <x:c r="L8" s="44"/>
-      <x:c r="M8" s="44"/>
+      <x:c r="H8" s="52"/>
+      <x:c r="I8" s="52"/>
+      <x:c r="J8" s="51"/>
+      <x:c r="K8" s="51"/>
+      <x:c r="L8" s="51"/>
+      <x:c r="M8" s="51"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="46" t="str">
+      <x:c r="A9" s="50" t="str">
         <x:v>F34</x:v>
       </x:c>
-      <x:c r="B9" s="44" t="str">
+      <x:c r="B9" s="51" t="str">
         <x:v>Step 11A · Wireframe</x:v>
       </x:c>
-      <x:c r="C9" s="44" t="str">
+      <x:c r="C9" s="51" t="str">
         <x:v>Owner-approved responsive admin dashboard wireframe</x:v>
       </x:c>
-      <x:c r="D9" s="44" t="str">
+      <x:c r="D9" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="44" t="str">
+      <x:c r="E9" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="44" t="str">
+      <x:c r="F9" s="51" t="str">
         <x:v>Admin UI not included in V3; design approval required</x:v>
       </x:c>
-      <x:c r="G9" s="44" t="str">
+      <x:c r="G9" s="51" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H9" s="45"/>
-      <x:c r="I9" s="45"/>
-      <x:c r="J9" s="44"/>
-      <x:c r="K9" s="44"/>
-      <x:c r="L9" s="44"/>
-      <x:c r="M9" s="44"/>
+      <x:c r="H9" s="52"/>
+      <x:c r="I9" s="52"/>
+      <x:c r="J9" s="51"/>
+      <x:c r="K9" s="51"/>
+      <x:c r="L9" s="51"/>
+      <x:c r="M9" s="51"/>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="46" t="str">
+      <x:c r="A10" s="50" t="str">
         <x:v>F01</x:v>
       </x:c>
-      <x:c r="B10" s="44" t="str">
+      <x:c r="B10" s="51" t="str">
         <x:v>Step 1 · Design</x:v>
       </x:c>
-      <x:c r="C10" s="44" t="str">
+      <x:c r="C10" s="51" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives</x:v>
       </x:c>
-      <x:c r="D10" s="44" t="str">
+      <x:c r="D10" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E10" s="44" t="str">
+      <x:c r="E10" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="44" t="str">
+      <x:c r="F10" s="51" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G10" s="44" t="str">
+      <x:c r="G10" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H10" s="45" t="d">
+      <x:c r="H10" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="45" t="d">
+      <x:c r="I10" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="44" t="str">
+      <x:c r="J10" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="44" t="str">
+      <x:c r="K10" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="44" t="str">
+      <x:c r="L10" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="44" t="str">
+      <x:c r="M10" s="51" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -980,43 +1237,43 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="310" customHeight="1">
-      <x:c r="A11" s="46" t="str">
+      <x:c r="A11" s="50" t="str">
         <x:v>F04</x:v>
       </x:c>
-      <x:c r="B11" s="44" t="str">
+      <x:c r="B11" s="51" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C11" s="44" t="str">
+      <x:c r="C11" s="51" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in</x:v>
       </x:c>
-      <x:c r="D11" s="44" t="str">
+      <x:c r="D11" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E11" s="44" t="str">
+      <x:c r="E11" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="44" t="str">
+      <x:c r="F11" s="51" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G11" s="44" t="str">
+      <x:c r="G11" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H11" s="45" t="d">
+      <x:c r="H11" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I11" s="45" t="d">
+      <x:c r="I11" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="44" t="str">
+      <x:c r="J11" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K11" s="44" t="str">
+      <x:c r="K11" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L11" s="44" t="str">
+      <x:c r="L11" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M11" s="44" t="str">
+      <x:c r="M11" s="51" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1024,43 +1281,43 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="310" customHeight="1">
-      <x:c r="A12" s="46" t="str">
+      <x:c r="A12" s="50" t="str">
         <x:v>F05</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="str">
+      <x:c r="B12" s="51" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C12" s="44" t="str">
+      <x:c r="C12" s="51" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints</x:v>
       </x:c>
-      <x:c r="D12" s="44" t="str">
+      <x:c r="D12" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E12" s="44" t="str">
+      <x:c r="E12" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="44" t="str">
+      <x:c r="F12" s="51" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G12" s="44" t="str">
+      <x:c r="G12" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H12" s="45" t="d">
+      <x:c r="H12" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="45" t="d">
+      <x:c r="I12" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="44" t="str">
+      <x:c r="J12" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K12" s="44" t="str">
+      <x:c r="K12" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L12" s="44" t="str">
+      <x:c r="L12" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="44" t="str">
+      <x:c r="M12" s="51" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1068,43 +1325,43 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="310" customHeight="1">
-      <x:c r="A13" s="46" t="str">
+      <x:c r="A13" s="50" t="str">
         <x:v>F06</x:v>
       </x:c>
-      <x:c r="B13" s="44" t="str">
+      <x:c r="B13" s="51" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C13" s="44" t="str">
+      <x:c r="C13" s="51" t="str">
         <x:v>Light footer, company links, contact and PDPA link</x:v>
       </x:c>
-      <x:c r="D13" s="44" t="str">
+      <x:c r="D13" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E13" s="44" t="str">
+      <x:c r="E13" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F13" s="44" t="str">
+      <x:c r="F13" s="51" t="str">
         <x:v>Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G13" s="44" t="str">
+      <x:c r="G13" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H13" s="45" t="d">
+      <x:c r="H13" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I13" s="45" t="d">
+      <x:c r="I13" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J13" s="44" t="str">
+      <x:c r="J13" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K13" s="44" t="str">
+      <x:c r="K13" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L13" s="44" t="str">
+      <x:c r="L13" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M13" s="44" t="str">
+      <x:c r="M13" s="51" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1112,43 +1369,43 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="310" customHeight="1">
-      <x:c r="A14" s="46" t="str">
+      <x:c r="A14" s="50" t="str">
         <x:v>F07</x:v>
       </x:c>
-      <x:c r="B14" s="44" t="str">
+      <x:c r="B14" s="51" t="str">
         <x:v>Step 1 · i18n</x:v>
       </x:c>
-      <x:c r="C14" s="44" t="str">
+      <x:c r="C14" s="51" t="str">
         <x:v>Thai/English routes, language switch and localized formatting</x:v>
       </x:c>
-      <x:c r="D14" s="44" t="str">
+      <x:c r="D14" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E14" s="44" t="str">
+      <x:c r="E14" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="44" t="str">
+      <x:c r="F14" s="51" t="str">
         <x:v>Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G14" s="44" t="str">
+      <x:c r="G14" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H14" s="45" t="d">
+      <x:c r="H14" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I14" s="45" t="d">
+      <x:c r="I14" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="44" t="str">
+      <x:c r="J14" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K14" s="44" t="str">
+      <x:c r="K14" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L14" s="44" t="str">
+      <x:c r="L14" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M14" s="44" t="str">
+      <x:c r="M14" s="51" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1156,878 +1413,878 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="250" customHeight="1">
-      <x:c r="A15" s="46" t="str">
+      <x:c r="A15" s="56" t="str">
         <x:v>F08</x:v>
       </x:c>
-      <x:c r="B15" s="44" t="str">
+      <x:c r="B15" s="57" t="str">
         <x:v>Step 3 · Cards</x:v>
       </x:c>
-      <x:c r="C15" s="44" t="str">
+      <x:c r="C15" s="57" t="str">
         <x:v>Realtor-style 3:2 listing cards, photo controls, bottom-right save heart, facts/address and Contact agent dialog trigger</x:v>
       </x:c>
-      <x:c r="D15" s="44" t="str">
+      <x:c r="D15" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="44" t="str">
+      <x:c r="E15" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="44" t="str">
+      <x:c r="F15" s="57" t="str">
         <x:v>V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
       </x:c>
-      <x:c r="G15" s="44" t="str">
+      <x:c r="G15" s="57" t="str">
         <x:v>Codex: build revised card only under Step 3 authorization, after the real database step.</x:v>
       </x:c>
-      <x:c r="H15" s="45"/>
-      <x:c r="I15" s="45" t="d">
+      <x:c r="H15" s="58"/>
+      <x:c r="I15" s="58" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J15" s="44" t="str">
+      <x:c r="J15" s="57" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K15" s="44" t="str">
+      <x:c r="K15" s="57" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L15" s="44" t="str">
+      <x:c r="L15" s="57" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M15" s="44" t="str">
+      <x:c r="M15" s="57" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="46" t="str">
+      <x:c r="A16" s="56" t="str">
         <x:v>F09</x:v>
       </x:c>
-      <x:c r="B16" s="44" t="str">
+      <x:c r="B16" s="57" t="str">
         <x:v>Step 3 · Results</x:v>
       </x:c>
-      <x:c r="C16" s="44" t="str">
+      <x:c r="C16" s="57" t="str">
         <x:v>Responsive /buy, /rent and /invest results layouts</x:v>
       </x:c>
-      <x:c r="D16" s="44" t="str">
+      <x:c r="D16" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E16" s="44" t="str">
+      <x:c r="E16" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="44" t="str">
+      <x:c r="F16" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G16" s="44" t="str">
+      <x:c r="G16" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H16" s="45"/>
-      <x:c r="I16" s="45"/>
-      <x:c r="J16" s="44"/>
-      <x:c r="K16" s="44"/>
-      <x:c r="L16" s="44"/>
-      <x:c r="M16" s="44"/>
+      <x:c r="H16" s="58"/>
+      <x:c r="I16" s="58"/>
+      <x:c r="J16" s="57"/>
+      <x:c r="K16" s="57"/>
+      <x:c r="L16" s="57"/>
+      <x:c r="M16" s="57"/>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="46" t="str">
+      <x:c r="A17" s="56" t="str">
         <x:v>F10</x:v>
       </x:c>
-      <x:c r="B17" s="44" t="str">
+      <x:c r="B17" s="57" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C17" s="44" t="str">
+      <x:c r="C17" s="57" t="str">
         <x:v>Shared URL filters, active chips, sorting and navigation history</x:v>
       </x:c>
-      <x:c r="D17" s="44" t="str">
+      <x:c r="D17" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="44" t="str">
+      <x:c r="E17" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="44" t="str">
+      <x:c r="F17" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G17" s="44" t="str">
+      <x:c r="G17" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H17" s="45"/>
-      <x:c r="I17" s="45"/>
-      <x:c r="J17" s="44"/>
-      <x:c r="K17" s="44"/>
-      <x:c r="L17" s="44"/>
-      <x:c r="M17" s="44"/>
+      <x:c r="H17" s="58"/>
+      <x:c r="I17" s="58"/>
+      <x:c r="J17" s="57"/>
+      <x:c r="K17" s="57"/>
+      <x:c r="L17" s="57"/>
+      <x:c r="M17" s="57"/>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="46" t="str">
+      <x:c r="A18" s="56" t="str">
         <x:v>F11</x:v>
       </x:c>
-      <x:c r="B18" s="44" t="str">
+      <x:c r="B18" s="57" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C18" s="44" t="str">
+      <x:c r="C18" s="57" t="str">
         <x:v>Desktop popovers for price, beds, type and advanced filters</x:v>
       </x:c>
-      <x:c r="D18" s="44" t="str">
+      <x:c r="D18" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="44" t="str">
+      <x:c r="E18" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F18" s="44" t="str">
+      <x:c r="F18" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G18" s="44" t="str">
+      <x:c r="G18" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H18" s="45"/>
-      <x:c r="I18" s="45"/>
-      <x:c r="J18" s="44"/>
-      <x:c r="K18" s="44"/>
-      <x:c r="L18" s="44"/>
-      <x:c r="M18" s="44"/>
+      <x:c r="H18" s="58"/>
+      <x:c r="I18" s="58"/>
+      <x:c r="J18" s="57"/>
+      <x:c r="K18" s="57"/>
+      <x:c r="L18" s="57"/>
+      <x:c r="M18" s="57"/>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="46" t="str">
+      <x:c r="A19" s="56" t="str">
         <x:v>F12</x:v>
       </x:c>
-      <x:c r="B19" s="44" t="str">
+      <x:c r="B19" s="57" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C19" s="44" t="str">
+      <x:c r="C19" s="57" t="str">
         <x:v>Phone full-screen filter sheet, Apply and Clear</x:v>
       </x:c>
-      <x:c r="D19" s="44" t="str">
+      <x:c r="D19" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="44" t="str">
+      <x:c r="E19" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="44" t="str">
+      <x:c r="F19" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G19" s="44" t="str">
+      <x:c r="G19" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H19" s="45"/>
-      <x:c r="I19" s="45"/>
-      <x:c r="J19" s="44"/>
-      <x:c r="K19" s="44"/>
-      <x:c r="L19" s="44"/>
-      <x:c r="M19" s="44"/>
+      <x:c r="H19" s="58"/>
+      <x:c r="I19" s="58"/>
+      <x:c r="J19" s="57"/>
+      <x:c r="K19" s="57"/>
+      <x:c r="L19" s="57"/>
+      <x:c r="M19" s="57"/>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="46" t="str">
+      <x:c r="A20" s="56" t="str">
         <x:v>F13</x:v>
       </x:c>
-      <x:c r="B20" s="44" t="str">
+      <x:c r="B20" s="57" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C20" s="44" t="str">
+      <x:c r="C20" s="57" t="str">
         <x:v>Database-derived price histogram and live result count</x:v>
       </x:c>
-      <x:c r="D20" s="44" t="str">
+      <x:c r="D20" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="44" t="str">
+      <x:c r="E20" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="44" t="str">
+      <x:c r="F20" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G20" s="44" t="str">
+      <x:c r="G20" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H20" s="45"/>
-      <x:c r="I20" s="45"/>
-      <x:c r="J20" s="44"/>
-      <x:c r="K20" s="44"/>
-      <x:c r="L20" s="44"/>
-      <x:c r="M20" s="44"/>
+      <x:c r="H20" s="58"/>
+      <x:c r="I20" s="58"/>
+      <x:c r="J20" s="57"/>
+      <x:c r="K20" s="57"/>
+      <x:c r="L20" s="57"/>
+      <x:c r="M20" s="57"/>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="46" t="str">
+      <x:c r="A21" s="56" t="str">
         <x:v>F14</x:v>
       </x:c>
-      <x:c r="B21" s="44" t="str">
+      <x:c r="B21" s="57" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C21" s="44" t="str">
+      <x:c r="C21" s="57" t="str">
         <x:v>Desktop listing/map split and hover/focus pin synchronization</x:v>
       </x:c>
-      <x:c r="D21" s="44" t="str">
+      <x:c r="D21" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="44" t="str">
+      <x:c r="E21" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="44" t="str">
+      <x:c r="F21" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G21" s="44" t="str">
+      <x:c r="G21" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H21" s="45"/>
-      <x:c r="I21" s="45"/>
-      <x:c r="J21" s="44"/>
-      <x:c r="K21" s="44"/>
-      <x:c r="L21" s="44"/>
-      <x:c r="M21" s="44"/>
+      <x:c r="H21" s="58"/>
+      <x:c r="I21" s="58"/>
+      <x:c r="J21" s="57"/>
+      <x:c r="K21" s="57"/>
+      <x:c r="L21" s="57"/>
+      <x:c r="M21" s="57"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="46" t="str">
+      <x:c r="A22" s="56" t="str">
         <x:v>F15</x:v>
       </x:c>
-      <x:c r="B22" s="44" t="str">
+      <x:c r="B22" s="57" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C22" s="44" t="str">
+      <x:c r="C22" s="57" t="str">
         <x:v>Phone full-screen Map/List toggle</x:v>
       </x:c>
-      <x:c r="D22" s="44" t="str">
+      <x:c r="D22" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E22" s="44" t="str">
+      <x:c r="E22" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="44" t="str">
+      <x:c r="F22" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G22" s="44" t="str">
+      <x:c r="G22" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H22" s="45"/>
-      <x:c r="I22" s="45"/>
-      <x:c r="J22" s="44"/>
-      <x:c r="K22" s="44"/>
-      <x:c r="L22" s="44"/>
-      <x:c r="M22" s="44"/>
+      <x:c r="H22" s="58"/>
+      <x:c r="I22" s="58"/>
+      <x:c r="J22" s="57"/>
+      <x:c r="K22" s="57"/>
+      <x:c r="L22" s="57"/>
+      <x:c r="M22" s="57"/>
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
-      <x:c r="A23" s="46" t="str">
+      <x:c r="A23" s="56" t="str">
         <x:v>F16</x:v>
       </x:c>
-      <x:c r="B23" s="44" t="str">
+      <x:c r="B23" s="57" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C23" s="44" t="str">
+      <x:c r="C23" s="57" t="str">
         <x:v>Property detail photo grid and full-screen gallery</x:v>
       </x:c>
-      <x:c r="D23" s="44" t="str">
+      <x:c r="D23" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E23" s="44" t="str">
+      <x:c r="E23" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F23" s="44" t="str">
+      <x:c r="F23" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G23" s="44" t="str">
+      <x:c r="G23" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H23" s="45"/>
-      <x:c r="I23" s="45"/>
-      <x:c r="J23" s="44"/>
-      <x:c r="K23" s="44"/>
-      <x:c r="L23" s="44"/>
-      <x:c r="M23" s="44"/>
+      <x:c r="H23" s="58"/>
+      <x:c r="I23" s="58"/>
+      <x:c r="J23" s="57"/>
+      <x:c r="K23" s="57"/>
+      <x:c r="L23" s="57"/>
+      <x:c r="M23" s="57"/>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="46" t="str">
+      <x:c r="A24" s="56" t="str">
         <x:v>F17</x:v>
       </x:c>
-      <x:c r="B24" s="44" t="str">
+      <x:c r="B24" s="57" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C24" s="44" t="str">
+      <x:c r="C24" s="57" t="str">
         <x:v>Title, pricing, type-specific facts, long description and sticky tabs</x:v>
       </x:c>
-      <x:c r="D24" s="44" t="str">
+      <x:c r="D24" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E24" s="44" t="str">
+      <x:c r="E24" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="44" t="str">
+      <x:c r="F24" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G24" s="44" t="str">
+      <x:c r="G24" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H24" s="45"/>
-      <x:c r="I24" s="45"/>
-      <x:c r="J24" s="44"/>
-      <x:c r="K24" s="44"/>
-      <x:c r="L24" s="44"/>
-      <x:c r="M24" s="44"/>
+      <x:c r="H24" s="58"/>
+      <x:c r="I24" s="58"/>
+      <x:c r="J24" s="57"/>
+      <x:c r="K24" s="57"/>
+      <x:c r="L24" s="57"/>
+      <x:c r="M24" s="57"/>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="46" t="str">
+      <x:c r="A25" s="56" t="str">
         <x:v>F18</x:v>
       </x:c>
-      <x:c r="B25" s="44" t="str">
+      <x:c r="B25" s="57" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C25" s="44" t="str">
+      <x:c r="C25" s="57" t="str">
         <x:v>Floorplan/video/360 tabs, verified nearby information and map</x:v>
       </x:c>
-      <x:c r="D25" s="44" t="str">
+      <x:c r="D25" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E25" s="44" t="str">
+      <x:c r="E25" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="44" t="str">
+      <x:c r="F25" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G25" s="44" t="str">
+      <x:c r="G25" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H25" s="45"/>
-      <x:c r="I25" s="45"/>
-      <x:c r="J25" s="44"/>
-      <x:c r="K25" s="44"/>
-      <x:c r="L25" s="44"/>
-      <x:c r="M25" s="44"/>
+      <x:c r="H25" s="58"/>
+      <x:c r="I25" s="58"/>
+      <x:c r="J25" s="57"/>
+      <x:c r="K25" s="57"/>
+      <x:c r="L25" s="57"/>
+      <x:c r="M25" s="57"/>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="46" t="str">
+      <x:c r="A26" s="56" t="str">
         <x:v>F19</x:v>
       </x:c>
-      <x:c r="B26" s="44" t="str">
+      <x:c r="B26" s="57" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C26" s="44" t="str">
+      <x:c r="C26" s="57" t="str">
         <x:v>Mortgage calculator and area comparison when real data exists</x:v>
       </x:c>
-      <x:c r="D26" s="44" t="str">
+      <x:c r="D26" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E26" s="44" t="str">
+      <x:c r="E26" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="44" t="str">
+      <x:c r="F26" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G26" s="44" t="str">
+      <x:c r="G26" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H26" s="45"/>
-      <x:c r="I26" s="45"/>
-      <x:c r="J26" s="44"/>
-      <x:c r="K26" s="44"/>
-      <x:c r="L26" s="44"/>
-      <x:c r="M26" s="44"/>
+      <x:c r="H26" s="58"/>
+      <x:c r="I26" s="58"/>
+      <x:c r="J26" s="57"/>
+      <x:c r="K26" s="57"/>
+      <x:c r="L26" s="57"/>
+      <x:c r="M26" s="57"/>
     </x:row>
     <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="46" t="str">
+      <x:c r="A27" s="56" t="str">
         <x:v>F20</x:v>
       </x:c>
-      <x:c r="B27" s="44" t="str">
+      <x:c r="B27" s="57" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C27" s="44" t="str">
+      <x:c r="C27" s="57" t="str">
         <x:v>Same-project units and similar-property cards</x:v>
       </x:c>
-      <x:c r="D27" s="44" t="str">
+      <x:c r="D27" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E27" s="44" t="str">
+      <x:c r="E27" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="44" t="str">
+      <x:c r="F27" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G27" s="44" t="str">
+      <x:c r="G27" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H27" s="45"/>
-      <x:c r="I27" s="45"/>
-      <x:c r="J27" s="44"/>
-      <x:c r="K27" s="44"/>
-      <x:c r="L27" s="44"/>
-      <x:c r="M27" s="44"/>
+      <x:c r="H27" s="58"/>
+      <x:c r="I27" s="58"/>
+      <x:c r="J27" s="57"/>
+      <x:c r="K27" s="57"/>
+      <x:c r="L27" s="57"/>
+      <x:c r="M27" s="57"/>
     </x:row>
     <x:row r="28" ht="250" customHeight="1">
-      <x:c r="A28" s="46" t="str">
+      <x:c r="A28" s="56" t="str">
         <x:v>F21</x:v>
       </x:c>
-      <x:c r="B28" s="44" t="str">
+      <x:c r="B28" s="57" t="str">
         <x:v>Step 6 · Contact</x:v>
       </x:c>
-      <x:c r="C28" s="44" t="str">
+      <x:c r="C28" s="57" t="str">
         <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
       </x:c>
-      <x:c r="D28" s="44" t="str">
+      <x:c r="D28" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E28" s="44" t="str">
+      <x:c r="E28" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="44" t="str">
+      <x:c r="F28" s="57" t="str">
         <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
-      <x:c r="G28" s="44" t="str">
+      <x:c r="G28" s="57" t="str">
         <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
       </x:c>
-      <x:c r="H28" s="45"/>
-      <x:c r="I28" s="45" t="d">
+      <x:c r="H28" s="58"/>
+      <x:c r="I28" s="58" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J28" s="44" t="str">
+      <x:c r="J28" s="57" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K28" s="44" t="str">
+      <x:c r="K28" s="57" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L28" s="44" t="str">
+      <x:c r="L28" s="57" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M28" s="44" t="str">
+      <x:c r="M28" s="57" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="46" t="str">
+      <x:c r="A29" s="56" t="str">
         <x:v>F22</x:v>
       </x:c>
-      <x:c r="B29" s="44" t="str">
+      <x:c r="B29" s="57" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C29" s="44" t="str">
+      <x:c r="C29" s="57" t="str">
         <x:v>Single-image hero and compact photography-first layout</x:v>
       </x:c>
-      <x:c r="D29" s="44" t="str">
+      <x:c r="D29" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E29" s="44" t="str">
+      <x:c r="E29" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="44" t="str">
+      <x:c r="F29" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="44" t="str">
+      <x:c r="G29" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="45"/>
-      <x:c r="I29" s="45"/>
-      <x:c r="J29" s="44"/>
-      <x:c r="K29" s="44"/>
-      <x:c r="L29" s="44"/>
-      <x:c r="M29" s="44"/>
+      <x:c r="H29" s="58"/>
+      <x:c r="I29" s="58"/>
+      <x:c r="J29" s="57"/>
+      <x:c r="K29" s="57"/>
+      <x:c r="L29" s="57"/>
+      <x:c r="M29" s="57"/>
     </x:row>
     <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="46" t="str">
+      <x:c r="A30" s="56" t="str">
         <x:v>F23</x:v>
       </x:c>
-      <x:c r="B30" s="44" t="str">
+      <x:c r="B30" s="57" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C30" s="44" t="str">
+      <x:c r="C30" s="57" t="str">
         <x:v>Shared search box with Buy/Rent/Projects/Investment tabs</x:v>
       </x:c>
-      <x:c r="D30" s="44" t="str">
+      <x:c r="D30" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E30" s="44" t="str">
+      <x:c r="E30" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="44" t="str">
+      <x:c r="F30" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="44" t="str">
+      <x:c r="G30" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="45"/>
-      <x:c r="I30" s="45"/>
-      <x:c r="J30" s="44"/>
-      <x:c r="K30" s="44"/>
-      <x:c r="L30" s="44"/>
-      <x:c r="M30" s="44"/>
+      <x:c r="H30" s="58"/>
+      <x:c r="I30" s="58"/>
+      <x:c r="J30" s="57"/>
+      <x:c r="K30" s="57"/>
+      <x:c r="L30" s="57"/>
+      <x:c r="M30" s="57"/>
     </x:row>
     <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="46" t="str">
+      <x:c r="A31" s="56" t="str">
         <x:v>F24</x:v>
       </x:c>
-      <x:c r="B31" s="44" t="str">
+      <x:c r="B31" s="57" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C31" s="44" t="str">
+      <x:c r="C31" s="57" t="str">
         <x:v>Categories, recent searches and location/station suggestions</x:v>
       </x:c>
-      <x:c r="D31" s="44" t="str">
+      <x:c r="D31" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E31" s="44" t="str">
+      <x:c r="E31" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="44" t="str">
+      <x:c r="F31" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="44" t="str">
+      <x:c r="G31" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="45"/>
-      <x:c r="I31" s="45"/>
-      <x:c r="J31" s="44"/>
-      <x:c r="K31" s="44"/>
-      <x:c r="L31" s="44"/>
-      <x:c r="M31" s="44"/>
+      <x:c r="H31" s="58"/>
+      <x:c r="I31" s="58"/>
+      <x:c r="J31" s="57"/>
+      <x:c r="K31" s="57"/>
+      <x:c r="L31" s="57"/>
+      <x:c r="M31" s="57"/>
     </x:row>
     <x:row r="32" ht="250" customHeight="1">
-      <x:c r="A32" s="46" t="str">
+      <x:c r="A32" s="56" t="str">
         <x:v>F25</x:v>
       </x:c>
-      <x:c r="B32" s="44" t="str">
+      <x:c r="B32" s="57" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C32" s="44" t="str">
+      <x:c r="C32" s="57" t="str">
         <x:v>Homes for you carousel directly below search; regions with real listing counts</x:v>
       </x:c>
-      <x:c r="D32" s="44" t="str">
+      <x:c r="D32" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E32" s="44" t="str">
+      <x:c r="E32" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="44" t="str">
+      <x:c r="F32" s="57" t="str">
         <x:v>V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
-      <x:c r="G32" s="44" t="str">
+      <x:c r="G32" s="57" t="str">
         <x:v>Codex: implement approved home-page.html only under Step 7 authorization.</x:v>
       </x:c>
-      <x:c r="H32" s="45"/>
-      <x:c r="I32" s="45" t="d">
+      <x:c r="H32" s="58"/>
+      <x:c r="I32" s="58" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J32" s="44" t="str">
+      <x:c r="J32" s="57" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K32" s="44" t="str">
+      <x:c r="K32" s="57" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L32" s="44" t="str">
+      <x:c r="L32" s="57" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M32" s="44" t="str">
+      <x:c r="M32" s="57" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26" customHeight="1">
-      <x:c r="A33" s="46" t="str">
+      <x:c r="A33" s="56" t="str">
         <x:v>F26</x:v>
       </x:c>
-      <x:c r="B33" s="44" t="str">
+      <x:c r="B33" s="57" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C33" s="44" t="str">
+      <x:c r="C33" s="57" t="str">
         <x:v>New projects, tools, services and owner lead CTAs</x:v>
       </x:c>
-      <x:c r="D33" s="44" t="str">
+      <x:c r="D33" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E33" s="44" t="str">
+      <x:c r="E33" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F33" s="44" t="str">
+      <x:c r="F33" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G33" s="44" t="str">
+      <x:c r="G33" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H33" s="45"/>
-      <x:c r="I33" s="45"/>
-      <x:c r="J33" s="44"/>
-      <x:c r="K33" s="44"/>
-      <x:c r="L33" s="44"/>
-      <x:c r="M33" s="44"/>
+      <x:c r="H33" s="58"/>
+      <x:c r="I33" s="58"/>
+      <x:c r="J33" s="57"/>
+      <x:c r="K33" s="57"/>
+      <x:c r="L33" s="57"/>
+      <x:c r="M33" s="57"/>
     </x:row>
     <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="46" t="str">
+      <x:c r="A34" s="56" t="str">
         <x:v>F27</x:v>
       </x:c>
-      <x:c r="B34" s="44" t="str">
+      <x:c r="B34" s="57" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C34" s="44" t="str">
+      <x:c r="C34" s="57" t="str">
         <x:v>Projects index and responsive project detail layouts</x:v>
       </x:c>
-      <x:c r="D34" s="44" t="str">
+      <x:c r="D34" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E34" s="44" t="str">
+      <x:c r="E34" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F34" s="44" t="str">
+      <x:c r="F34" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G34" s="44" t="str">
+      <x:c r="G34" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H34" s="45"/>
-      <x:c r="I34" s="45"/>
-      <x:c r="J34" s="44"/>
-      <x:c r="K34" s="44"/>
-      <x:c r="L34" s="44"/>
-      <x:c r="M34" s="44"/>
+      <x:c r="H34" s="58"/>
+      <x:c r="I34" s="58"/>
+      <x:c r="J34" s="57"/>
+      <x:c r="K34" s="57"/>
+      <x:c r="L34" s="57"/>
+      <x:c r="M34" s="57"/>
     </x:row>
     <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="46" t="str">
+      <x:c r="A35" s="56" t="str">
         <x:v>F28</x:v>
       </x:c>
-      <x:c r="B35" s="44" t="str">
+      <x:c r="B35" s="57" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C35" s="44" t="str">
+      <x:c r="C35" s="57" t="str">
         <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
       </x:c>
-      <x:c r="D35" s="44" t="str">
+      <x:c r="D35" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E35" s="44" t="str">
+      <x:c r="E35" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F35" s="44" t="str">
+      <x:c r="F35" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G35" s="44" t="str">
+      <x:c r="G35" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H35" s="45"/>
-      <x:c r="I35" s="45"/>
-      <x:c r="J35" s="44"/>
-      <x:c r="K35" s="44"/>
-      <x:c r="L35" s="44"/>
-      <x:c r="M35" s="44"/>
+      <x:c r="H35" s="58"/>
+      <x:c r="I35" s="58"/>
+      <x:c r="J35" s="57"/>
+      <x:c r="K35" s="57"/>
+      <x:c r="L35" s="57"/>
+      <x:c r="M35" s="57"/>
     </x:row>
     <x:row r="36" ht="26" customHeight="1">
-      <x:c r="A36" s="46" t="str">
+      <x:c r="A36" s="56" t="str">
         <x:v>F29</x:v>
       </x:c>
-      <x:c r="B36" s="44" t="str">
+      <x:c r="B36" s="57" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C36" s="44" t="str">
+      <x:c r="C36" s="57" t="str">
         <x:v>Data-driven clickable project SVG plot plan</x:v>
       </x:c>
-      <x:c r="D36" s="44" t="str">
+      <x:c r="D36" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E36" s="44" t="str">
+      <x:c r="E36" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F36" s="44" t="str">
+      <x:c r="F36" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G36" s="44" t="str">
+      <x:c r="G36" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H36" s="45"/>
-      <x:c r="I36" s="45"/>
-      <x:c r="J36" s="44"/>
-      <x:c r="K36" s="44"/>
-      <x:c r="L36" s="44"/>
-      <x:c r="M36" s="44"/>
+      <x:c r="H36" s="58"/>
+      <x:c r="I36" s="58"/>
+      <x:c r="J36" s="57"/>
+      <x:c r="K36" s="57"/>
+      <x:c r="L36" s="57"/>
+      <x:c r="M36" s="57"/>
     </x:row>
     <x:row r="37" ht="26" customHeight="1">
-      <x:c r="A37" s="46" t="str">
+      <x:c r="A37" s="56" t="str">
         <x:v>F30</x:v>
       </x:c>
-      <x:c r="B37" s="44" t="str">
+      <x:c r="B37" s="57" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C37" s="44" t="str">
+      <x:c r="C37" s="57" t="str">
         <x:v>Site visit 3-step form and confirmation screens</x:v>
       </x:c>
-      <x:c r="D37" s="44" t="str">
+      <x:c r="D37" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E37" s="44" t="str">
+      <x:c r="E37" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F37" s="44" t="str">
+      <x:c r="F37" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G37" s="44" t="str">
+      <x:c r="G37" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H37" s="45"/>
-      <x:c r="I37" s="45"/>
-      <x:c r="J37" s="44"/>
-      <x:c r="K37" s="44"/>
-      <x:c r="L37" s="44"/>
-      <x:c r="M37" s="44"/>
+      <x:c r="H37" s="58"/>
+      <x:c r="I37" s="58"/>
+      <x:c r="J37" s="57"/>
+      <x:c r="K37" s="57"/>
+      <x:c r="L37" s="57"/>
+      <x:c r="M37" s="57"/>
     </x:row>
     <x:row r="38" ht="26" customHeight="1">
-      <x:c r="A38" s="46" t="str">
+      <x:c r="A38" s="56" t="str">
         <x:v>F31</x:v>
       </x:c>
-      <x:c r="B38" s="44" t="str">
+      <x:c r="B38" s="57" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C38" s="44" t="str">
+      <x:c r="C38" s="57" t="str">
         <x:v>Homes, searches and viewings; local save without account</x:v>
       </x:c>
-      <x:c r="D38" s="44" t="str">
+      <x:c r="D38" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E38" s="44" t="str">
+      <x:c r="E38" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F38" s="44" t="str">
+      <x:c r="F38" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G38" s="44" t="str">
+      <x:c r="G38" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H38" s="45"/>
-      <x:c r="I38" s="45"/>
-      <x:c r="J38" s="44"/>
-      <x:c r="K38" s="44"/>
-      <x:c r="L38" s="44"/>
-      <x:c r="M38" s="44"/>
+      <x:c r="H38" s="58"/>
+      <x:c r="I38" s="58"/>
+      <x:c r="J38" s="57"/>
+      <x:c r="K38" s="57"/>
+      <x:c r="L38" s="57"/>
+      <x:c r="M38" s="57"/>
     </x:row>
     <x:row r="39" ht="26" customHeight="1">
-      <x:c r="A39" s="46" t="str">
+      <x:c r="A39" s="56" t="str">
         <x:v>F33</x:v>
       </x:c>
-      <x:c r="B39" s="44" t="str">
+      <x:c r="B39" s="57" t="str">
         <x:v>Step 10B · Accounts</x:v>
       </x:c>
-      <x:c r="C39" s="44" t="str">
+      <x:c r="C39" s="57" t="str">
         <x:v>Build approved auth and account screens only after approval</x:v>
       </x:c>
-      <x:c r="D39" s="44" t="str">
+      <x:c r="D39" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E39" s="44" t="str">
+      <x:c r="E39" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F39" s="44" t="str">
+      <x:c r="F39" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G39" s="44" t="str">
+      <x:c r="G39" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H39" s="45"/>
-      <x:c r="I39" s="45"/>
-      <x:c r="J39" s="44"/>
-      <x:c r="K39" s="44"/>
-      <x:c r="L39" s="44"/>
-      <x:c r="M39" s="44"/>
+      <x:c r="H39" s="58"/>
+      <x:c r="I39" s="58"/>
+      <x:c r="J39" s="57"/>
+      <x:c r="K39" s="57"/>
+      <x:c r="L39" s="57"/>
+      <x:c r="M39" s="57"/>
     </x:row>
     <x:row r="40" ht="26" customHeight="1">
-      <x:c r="A40" s="46" t="str">
+      <x:c r="A40" s="56" t="str">
         <x:v>F35</x:v>
       </x:c>
-      <x:c r="B40" s="44" t="str">
+      <x:c r="B40" s="57" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C40" s="44" t="str">
+      <x:c r="C40" s="57" t="str">
         <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
       </x:c>
-      <x:c r="D40" s="44" t="str">
+      <x:c r="D40" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E40" s="44" t="str">
+      <x:c r="E40" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F40" s="44" t="str">
+      <x:c r="F40" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G40" s="44" t="str">
+      <x:c r="G40" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H40" s="45"/>
-      <x:c r="I40" s="45"/>
-      <x:c r="J40" s="44"/>
-      <x:c r="K40" s="44"/>
-      <x:c r="L40" s="44"/>
-      <x:c r="M40" s="44"/>
+      <x:c r="H40" s="58"/>
+      <x:c r="I40" s="58"/>
+      <x:c r="J40" s="57"/>
+      <x:c r="K40" s="57"/>
+      <x:c r="L40" s="57"/>
+      <x:c r="M40" s="57"/>
     </x:row>
     <x:row r="41" ht="26" customHeight="1">
-      <x:c r="A41" s="46" t="str">
+      <x:c r="A41" s="56" t="str">
         <x:v>F36</x:v>
       </x:c>
-      <x:c r="B41" s="44" t="str">
+      <x:c r="B41" s="57" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C41" s="44" t="str">
+      <x:c r="C41" s="57" t="str">
         <x:v>Admin-managed searchable filter editor with type safety</x:v>
       </x:c>
-      <x:c r="D41" s="44" t="str">
+      <x:c r="D41" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E41" s="44" t="str">
+      <x:c r="E41" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F41" s="44" t="str">
+      <x:c r="F41" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G41" s="44" t="str">
+      <x:c r="G41" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H41" s="45"/>
-      <x:c r="I41" s="45"/>
-      <x:c r="J41" s="44"/>
-      <x:c r="K41" s="44"/>
-      <x:c r="L41" s="44"/>
-      <x:c r="M41" s="44"/>
+      <x:c r="H41" s="58"/>
+      <x:c r="I41" s="58"/>
+      <x:c r="J41" s="57"/>
+      <x:c r="K41" s="57"/>
+      <x:c r="L41" s="57"/>
+      <x:c r="M41" s="57"/>
     </x:row>
     <x:row r="42" ht="26" customHeight="1">
-      <x:c r="A42" s="46" t="str">
+      <x:c r="A42" s="56" t="str">
         <x:v>F37</x:v>
       </x:c>
-      <x:c r="B42" s="44" t="str">
+      <x:c r="B42" s="57" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C42" s="44" t="str">
+      <x:c r="C42" s="57" t="str">
         <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
       </x:c>
-      <x:c r="D42" s="44" t="str">
+      <x:c r="D42" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E42" s="44" t="str">
+      <x:c r="E42" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F42" s="44" t="str">
+      <x:c r="F42" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G42" s="44" t="str">
+      <x:c r="G42" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H42" s="45"/>
-      <x:c r="I42" s="45"/>
-      <x:c r="J42" s="44"/>
-      <x:c r="K42" s="44"/>
-      <x:c r="L42" s="44"/>
-      <x:c r="M42" s="44"/>
+      <x:c r="H42" s="58"/>
+      <x:c r="I42" s="58"/>
+      <x:c r="J42" s="57"/>
+      <x:c r="K42" s="57"/>
+      <x:c r="L42" s="57"/>
+      <x:c r="M42" s="57"/>
     </x:row>
     <x:row r="43" ht="26" customHeight="1">
-      <x:c r="A43" s="46" t="str">
+      <x:c r="A43" s="56" t="str">
         <x:v>F38</x:v>
       </x:c>
-      <x:c r="B43" s="44" t="str">
+      <x:c r="B43" s="57" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C43" s="44" t="str">
+      <x:c r="C43" s="57" t="str">
         <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
       </x:c>
-      <x:c r="D43" s="44" t="str">
+      <x:c r="D43" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E43" s="44" t="str">
+      <x:c r="E43" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F43" s="44" t="str">
+      <x:c r="F43" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G43" s="44" t="str">
+      <x:c r="G43" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H43" s="45"/>
-      <x:c r="I43" s="45"/>
-      <x:c r="J43" s="44"/>
-      <x:c r="K43" s="44"/>
-      <x:c r="L43" s="44"/>
-      <x:c r="M43" s="44"/>
+      <x:c r="H43" s="58"/>
+      <x:c r="I43" s="58"/>
+      <x:c r="J43" s="57"/>
+      <x:c r="K43" s="57"/>
+      <x:c r="L43" s="57"/>
+      <x:c r="M43" s="57"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="44"/>
@@ -8889,15 +9146,15 @@
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E6:E43">
-    <x:cfRule type="expression" dxfId="0" priority="1">
-      <x:formula>E6="Pending"</x:formula>
+  <x:conditionalFormatting sqref="A6:M500">
+    <x:cfRule type="expression" dxfId="15" priority="1">
+      <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1" priority="2">
-      <x:formula>E6="Done"</x:formula>
+    <x:cfRule type="expression" dxfId="16" priority="2">
+      <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="2" priority="3">
-      <x:formula>E6="Not started"</x:formula>
+    <x:cfRule type="expression" dxfId="17" priority="3">
+      <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
@@ -8907,13 +9164,16 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13bbbb35cb3e4ec6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ee3b0fec5264935"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF202733"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
@@ -8944,7 +9204,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
+        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -9030,941 +9290,942 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="46" t="str">
+      <x:c r="A6" s="50" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B6" s="44" t="str">
+      <x:c r="B6" s="51" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C6" s="44" t="str">
+      <x:c r="C6" s="51" t="str">
         <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
-      <x:c r="D6" s="44" t="str">
+      <x:c r="D6" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E6" s="44" t="str">
+      <x:c r="E6" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="44" t="str">
+      <x:c r="F6" s="51" t="str">
         <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
-      <x:c r="G6" s="44" t="str">
+      <x:c r="G6" s="51" t="str">
         <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
       </x:c>
-      <x:c r="H6" s="45" t="d">
+      <x:c r="H6" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="45" t="d">
+      <x:c r="I6" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="44" t="str">
+      <x:c r="J6" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="44" t="str">
+      <x:c r="K6" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="44" t="str">
+      <x:c r="L6" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="44" t="str">
+      <x:c r="M6" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
 2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
 2026-10-09 Step 2: Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="46" t="str">
+      <x:c r="A7" s="50" t="str">
         <x:v>B17</x:v>
       </x:c>
-      <x:c r="B7" s="44" t="str">
+      <x:c r="B7" s="51" t="str">
         <x:v>Decision · Leads</x:v>
       </x:c>
-      <x:c r="C7" s="44" t="str">
+      <x:c r="C7" s="51" t="str">
         <x:v>Approve shared inbox versus listing agent enquiry destination</x:v>
       </x:c>
-      <x:c r="D7" s="44" t="str">
+      <x:c r="D7" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E7" s="44" t="str">
+      <x:c r="E7" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="44" t="str">
+      <x:c r="F7" s="51" t="str">
         <x:v>BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
-      <x:c r="G7" s="44" t="str">
+      <x:c r="G7" s="51" t="str">
         <x:v>Owner: select routing mode and mailbox</x:v>
       </x:c>
-      <x:c r="H7" s="45"/>
-      <x:c r="I7" s="45"/>
-      <x:c r="J7" s="44"/>
-      <x:c r="K7" s="44"/>
-      <x:c r="L7" s="44"/>
-      <x:c r="M7" s="44"/>
+      <x:c r="H7" s="52"/>
+      <x:c r="I7" s="52"/>
+      <x:c r="J7" s="51"/>
+      <x:c r="K7" s="51"/>
+      <x:c r="L7" s="51"/>
+      <x:c r="M7" s="51"/>
     </x:row>
     <x:row r="8" ht="250" customHeight="1">
-      <x:c r="A8" s="46" t="str">
+      <x:c r="A8" s="50" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B8" s="44" t="str">
+      <x:c r="B8" s="51" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C8" s="44" t="str">
+      <x:c r="C8" s="51" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D8" s="44" t="str">
+      <x:c r="D8" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="44" t="str">
+      <x:c r="E8" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="44" t="str">
+      <x:c r="F8" s="51" t="str">
         <x:v>Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending.</x:v>
       </x:c>
-      <x:c r="G8" s="44" t="str">
+      <x:c r="G8" s="51" t="str">
         <x:v>Owner: provide actual contacts/routing; Codex: integrate and review accessible contact actions later.</x:v>
       </x:c>
-      <x:c r="H8" s="45" t="d">
+      <x:c r="H8" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I8" s="45" t="d">
+      <x:c r="I8" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="44" t="str">
+      <x:c r="J8" s="51" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K8" s="44" t="str">
+      <x:c r="K8" s="51" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L8" s="44" t="str">
+      <x:c r="L8" s="51" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M8" s="44" t="str">
+      <x:c r="M8" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #4 unresolved
 2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.
 2026-10-09 foundation: Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="46" t="str">
+      <x:c r="A9" s="50" t="str">
         <x:v>B23</x:v>
       </x:c>
-      <x:c r="B9" s="44" t="str">
+      <x:c r="B9" s="51" t="str">
         <x:v>Decision · Accounts</x:v>
       </x:c>
-      <x:c r="C9" s="44" t="str">
+      <x:c r="C9" s="51" t="str">
         <x:v>Approve LINE only or LINE+Google+email sign-in</x:v>
       </x:c>
-      <x:c r="D9" s="44" t="str">
+      <x:c r="D9" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E9" s="44" t="str">
+      <x:c r="E9" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="44" t="str">
+      <x:c r="F9" s="51" t="str">
         <x:v>BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
-      <x:c r="G9" s="44" t="str">
+      <x:c r="G9" s="51" t="str">
         <x:v>Owner: approve authentication providers</x:v>
       </x:c>
-      <x:c r="H9" s="45"/>
-      <x:c r="I9" s="45"/>
-      <x:c r="J9" s="44"/>
-      <x:c r="K9" s="44"/>
-      <x:c r="L9" s="44"/>
-      <x:c r="M9" s="44"/>
+      <x:c r="H9" s="52"/>
+      <x:c r="I9" s="52"/>
+      <x:c r="J9" s="51"/>
+      <x:c r="K9" s="51"/>
+      <x:c r="L9" s="51"/>
+      <x:c r="M9" s="51"/>
     </x:row>
     <x:row r="10" ht="200" customHeight="1">
-      <x:c r="A10" s="46" t="str">
+      <x:c r="A10" s="50" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B10" s="44" t="str">
+      <x:c r="B10" s="51" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C10" s="44" t="str">
+      <x:c r="C10" s="51" t="str">
         <x:v>Approve THB only versus optional approximate FX display</x:v>
       </x:c>
-      <x:c r="D10" s="44" t="str">
+      <x:c r="D10" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="44" t="str">
+      <x:c r="E10" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="44" t="str">
+      <x:c r="F10" s="51" t="str">
         <x:v>Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
-      <x:c r="G10" s="44" t="str">
+      <x:c r="G10" s="51" t="str">
         <x:v>Codex: implement USD/THB during authorized currency work; confirm rate source.</x:v>
       </x:c>
-      <x:c r="H10" s="45"/>
-      <x:c r="I10" s="45" t="d">
+      <x:c r="H10" s="52"/>
+      <x:c r="I10" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="44" t="str">
+      <x:c r="J10" s="51" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K10" s="44" t="str">
+      <x:c r="K10" s="51" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L10" s="44" t="str">
+      <x:c r="L10" s="51" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M10" s="44" t="str">
+      <x:c r="M10" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #6 unresolved
 2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="200" customHeight="1">
-      <x:c r="A11" s="46" t="str">
+      <x:c r="A11" s="50" t="str">
         <x:v>B29</x:v>
       </x:c>
-      <x:c r="B11" s="44" t="str">
+      <x:c r="B11" s="51" t="str">
         <x:v>Decision · Projects</x:v>
       </x:c>
-      <x:c r="C11" s="44" t="str">
+      <x:c r="C11" s="51" t="str">
         <x:v>Approve public project prices versus enquiry-only price list</x:v>
       </x:c>
-      <x:c r="D11" s="44" t="str">
+      <x:c r="D11" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E11" s="44" t="str">
+      <x:c r="E11" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="44" t="str">
+      <x:c r="F11" s="51" t="str">
         <x:v>Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
-      <x:c r="G11" s="44" t="str">
+      <x:c r="G11" s="51" t="str">
         <x:v>Codex: add per-record price visibility in authorized backend/admin work after admin wireframe approval.</x:v>
       </x:c>
-      <x:c r="H11" s="45"/>
-      <x:c r="I11" s="45" t="d">
+      <x:c r="H11" s="52"/>
+      <x:c r="I11" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="44" t="str">
+      <x:c r="J11" s="51" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K11" s="44" t="str">
+      <x:c r="K11" s="51" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L11" s="44" t="str">
+      <x:c r="L11" s="51" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M11" s="44" t="str">
+      <x:c r="M11" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #7 unresolved
 2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="310" customHeight="1">
-      <x:c r="A12" s="46" t="str">
+      <x:c r="A12" s="50" t="str">
         <x:v>R01</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="str">
+      <x:c r="B12" s="51" t="str">
         <x:v>Step 0 · Preparation</x:v>
       </x:c>
-      <x:c r="C12" s="44" t="str">
+      <x:c r="C12" s="51" t="str">
         <x:v>Inspect project; establish permanent rules, documentation, Git/live mirror and tracker</x:v>
       </x:c>
-      <x:c r="D12" s="44" t="str">
+      <x:c r="D12" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E12" s="44" t="str">
+      <x:c r="E12" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="44" t="str">
+      <x:c r="F12" s="51" t="str">
         <x:v>Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request.</x:v>
       </x:c>
-      <x:c r="G12" s="44" t="str">
+      <x:c r="G12" s="51" t="str">
         <x:v>Codex: close the separate Step 0 utility/reference-review requirements only when authorized; stop before Step 3.</x:v>
       </x:c>
-      <x:c r="H12" s="45" t="d">
+      <x:c r="H12" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="45" t="d">
+      <x:c r="I12" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="44" t="str">
+      <x:c r="J12" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K12" s="44" t="str">
+      <x:c r="K12" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L12" s="44" t="str">
+      <x:c r="L12" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="44" t="str">
+      <x:c r="M12" s="51" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
 2026-10-09 foundation: Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.
-2026-10-09 Step 2: Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+2026-10-09 Step 2: Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 tracker formatting: workbook recreated with yellow Pending, light green Done and red Not started rows and status tabs. All 81 permanent IDs and prior task history preserved. Step 3 is authorized but implementation has not begun; owner requested the Excel first.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="46" t="str">
+      <x:c r="A13" s="56" t="str">
         <x:v>B05</x:v>
       </x:c>
-      <x:c r="B13" s="44" t="str">
+      <x:c r="B13" s="57" t="str">
         <x:v>Step 2 · Filters</x:v>
       </x:c>
-      <x:c r="C13" s="44" t="str">
+      <x:c r="C13" s="57" t="str">
         <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
       </x:c>
-      <x:c r="D13" s="44" t="str">
+      <x:c r="D13" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E13" s="44" t="str">
+      <x:c r="E13" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="44" t="str">
+      <x:c r="F13" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G13" s="44" t="str">
+      <x:c r="G13" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H13" s="45"/>
-      <x:c r="I13" s="45"/>
-      <x:c r="J13" s="44"/>
-      <x:c r="K13" s="44"/>
-      <x:c r="L13" s="44"/>
-      <x:c r="M13" s="44"/>
+      <x:c r="H13" s="58"/>
+      <x:c r="I13" s="58"/>
+      <x:c r="J13" s="57"/>
+      <x:c r="K13" s="57"/>
+      <x:c r="L13" s="57"/>
+      <x:c r="M13" s="57"/>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="46" t="str">
+      <x:c r="A14" s="56" t="str">
         <x:v>B06</x:v>
       </x:c>
-      <x:c r="B14" s="44" t="str">
+      <x:c r="B14" s="57" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C14" s="44" t="str">
+      <x:c r="C14" s="57" t="str">
         <x:v>Typed validated listing/search data access and pagination</x:v>
       </x:c>
-      <x:c r="D14" s="44" t="str">
+      <x:c r="D14" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E14" s="44" t="str">
+      <x:c r="E14" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F14" s="44" t="str">
+      <x:c r="F14" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G14" s="44" t="str">
+      <x:c r="G14" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H14" s="45"/>
-      <x:c r="I14" s="45"/>
-      <x:c r="J14" s="44"/>
-      <x:c r="K14" s="44"/>
-      <x:c r="L14" s="44"/>
-      <x:c r="M14" s="44"/>
+      <x:c r="H14" s="58"/>
+      <x:c r="I14" s="58"/>
+      <x:c r="J14" s="57"/>
+      <x:c r="K14" s="57"/>
+      <x:c r="L14" s="57"/>
+      <x:c r="M14" s="57"/>
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="46" t="str">
+      <x:c r="A15" s="56" t="str">
         <x:v>B07</x:v>
       </x:c>
-      <x:c r="B15" s="44" t="str">
+      <x:c r="B15" s="57" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C15" s="44" t="str">
+      <x:c r="C15" s="57" t="str">
         <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
       </x:c>
-      <x:c r="D15" s="44" t="str">
+      <x:c r="D15" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E15" s="44" t="str">
+      <x:c r="E15" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="44" t="str">
+      <x:c r="F15" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G15" s="44" t="str">
+      <x:c r="G15" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H15" s="45"/>
-      <x:c r="I15" s="45"/>
-      <x:c r="J15" s="44"/>
-      <x:c r="K15" s="44"/>
-      <x:c r="L15" s="44"/>
-      <x:c r="M15" s="44"/>
+      <x:c r="H15" s="58"/>
+      <x:c r="I15" s="58"/>
+      <x:c r="J15" s="57"/>
+      <x:c r="K15" s="57"/>
+      <x:c r="L15" s="57"/>
+      <x:c r="M15" s="57"/>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="46" t="str">
+      <x:c r="A16" s="56" t="str">
         <x:v>B08</x:v>
       </x:c>
-      <x:c r="B16" s="44" t="str">
+      <x:c r="B16" s="57" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C16" s="44" t="str">
+      <x:c r="C16" s="57" t="str">
         <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
       </x:c>
-      <x:c r="D16" s="44" t="str">
+      <x:c r="D16" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E16" s="44" t="str">
+      <x:c r="E16" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="44" t="str">
+      <x:c r="F16" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G16" s="44" t="str">
+      <x:c r="G16" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H16" s="45"/>
-      <x:c r="I16" s="45"/>
-      <x:c r="J16" s="44"/>
-      <x:c r="K16" s="44"/>
-      <x:c r="L16" s="44"/>
-      <x:c r="M16" s="44"/>
+      <x:c r="H16" s="58"/>
+      <x:c r="I16" s="58"/>
+      <x:c r="J16" s="57"/>
+      <x:c r="K16" s="57"/>
+      <x:c r="L16" s="57"/>
+      <x:c r="M16" s="57"/>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="46" t="str">
+      <x:c r="A17" s="56" t="str">
         <x:v>B10</x:v>
       </x:c>
-      <x:c r="B17" s="44" t="str">
+      <x:c r="B17" s="57" t="str">
         <x:v>Step 4 · Nearby</x:v>
       </x:c>
-      <x:c r="C17" s="44" t="str">
+      <x:c r="C17" s="57" t="str">
         <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
       </x:c>
-      <x:c r="D17" s="44" t="str">
+      <x:c r="D17" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E17" s="44" t="str">
+      <x:c r="E17" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="44" t="str">
+      <x:c r="F17" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G17" s="44" t="str">
+      <x:c r="G17" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H17" s="45"/>
-      <x:c r="I17" s="45"/>
-      <x:c r="J17" s="44"/>
-      <x:c r="K17" s="44"/>
-      <x:c r="L17" s="44"/>
-      <x:c r="M17" s="44"/>
+      <x:c r="H17" s="58"/>
+      <x:c r="I17" s="58"/>
+      <x:c r="J17" s="57"/>
+      <x:c r="K17" s="57"/>
+      <x:c r="L17" s="57"/>
+      <x:c r="M17" s="57"/>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="46" t="str">
+      <x:c r="A18" s="56" t="str">
         <x:v>B11</x:v>
       </x:c>
-      <x:c r="B18" s="44" t="str">
+      <x:c r="B18" s="57" t="str">
         <x:v>Step 5 · Media</x:v>
       </x:c>
-      <x:c r="C18" s="44" t="str">
+      <x:c r="C18" s="57" t="str">
         <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
       </x:c>
-      <x:c r="D18" s="44" t="str">
+      <x:c r="D18" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E18" s="44" t="str">
+      <x:c r="E18" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F18" s="44" t="str">
+      <x:c r="F18" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G18" s="44" t="str">
+      <x:c r="G18" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H18" s="45"/>
-      <x:c r="I18" s="45"/>
-      <x:c r="J18" s="44"/>
-      <x:c r="K18" s="44"/>
-      <x:c r="L18" s="44"/>
-      <x:c r="M18" s="44"/>
+      <x:c r="H18" s="58"/>
+      <x:c r="I18" s="58"/>
+      <x:c r="J18" s="57"/>
+      <x:c r="K18" s="57"/>
+      <x:c r="L18" s="57"/>
+      <x:c r="M18" s="57"/>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="46" t="str">
+      <x:c r="A19" s="56" t="str">
         <x:v>B12</x:v>
       </x:c>
-      <x:c r="B19" s="44" t="str">
+      <x:c r="B19" s="57" t="str">
         <x:v>Step 5 · Similar</x:v>
       </x:c>
-      <x:c r="C19" s="44" t="str">
+      <x:c r="C19" s="57" t="str">
         <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
       </x:c>
-      <x:c r="D19" s="44" t="str">
+      <x:c r="D19" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E19" s="44" t="str">
+      <x:c r="E19" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="44" t="str">
+      <x:c r="F19" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G19" s="44" t="str">
+      <x:c r="G19" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H19" s="45"/>
-      <x:c r="I19" s="45"/>
-      <x:c r="J19" s="44"/>
-      <x:c r="K19" s="44"/>
-      <x:c r="L19" s="44"/>
-      <x:c r="M19" s="44"/>
+      <x:c r="H19" s="58"/>
+      <x:c r="I19" s="58"/>
+      <x:c r="J19" s="57"/>
+      <x:c r="K19" s="57"/>
+      <x:c r="L19" s="57"/>
+      <x:c r="M19" s="57"/>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="46" t="str">
+      <x:c r="A20" s="56" t="str">
         <x:v>B13</x:v>
       </x:c>
-      <x:c r="B20" s="44" t="str">
+      <x:c r="B20" s="57" t="str">
         <x:v>Step 5 · Metrics</x:v>
       </x:c>
-      <x:c r="C20" s="44" t="str">
+      <x:c r="C20" s="57" t="str">
         <x:v>Comparable pricing/yield gated by verified sample size</x:v>
       </x:c>
-      <x:c r="D20" s="44" t="str">
+      <x:c r="D20" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E20" s="44" t="str">
+      <x:c r="E20" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="44" t="str">
+      <x:c r="F20" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G20" s="44" t="str">
+      <x:c r="G20" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H20" s="45"/>
-      <x:c r="I20" s="45"/>
-      <x:c r="J20" s="44"/>
-      <x:c r="K20" s="44"/>
-      <x:c r="L20" s="44"/>
-      <x:c r="M20" s="44"/>
+      <x:c r="H20" s="58"/>
+      <x:c r="I20" s="58"/>
+      <x:c r="J20" s="57"/>
+      <x:c r="K20" s="57"/>
+      <x:c r="L20" s="57"/>
+      <x:c r="M20" s="57"/>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="46" t="str">
+      <x:c r="A21" s="56" t="str">
         <x:v>B14</x:v>
       </x:c>
-      <x:c r="B21" s="44" t="str">
+      <x:c r="B21" s="57" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C21" s="44" t="str">
+      <x:c r="C21" s="57" t="str">
         <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
       </x:c>
-      <x:c r="D21" s="44" t="str">
+      <x:c r="D21" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E21" s="44" t="str">
+      <x:c r="E21" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="44" t="str">
+      <x:c r="F21" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G21" s="44" t="str">
+      <x:c r="G21" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H21" s="45"/>
-      <x:c r="I21" s="45"/>
-      <x:c r="J21" s="44"/>
-      <x:c r="K21" s="44"/>
-      <x:c r="L21" s="44"/>
-      <x:c r="M21" s="44"/>
+      <x:c r="H21" s="58"/>
+      <x:c r="I21" s="58"/>
+      <x:c r="J21" s="57"/>
+      <x:c r="K21" s="57"/>
+      <x:c r="L21" s="57"/>
+      <x:c r="M21" s="57"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="46" t="str">
+      <x:c r="A22" s="56" t="str">
         <x:v>B15</x:v>
       </x:c>
-      <x:c r="B22" s="44" t="str">
+      <x:c r="B22" s="57" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C22" s="44" t="str">
+      <x:c r="C22" s="57" t="str">
         <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
       </x:c>
-      <x:c r="D22" s="44" t="str">
+      <x:c r="D22" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E22" s="44" t="str">
+      <x:c r="E22" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="44" t="str">
+      <x:c r="F22" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G22" s="44" t="str">
+      <x:c r="G22" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H22" s="45"/>
-      <x:c r="I22" s="45"/>
-      <x:c r="J22" s="44"/>
-      <x:c r="K22" s="44"/>
-      <x:c r="L22" s="44"/>
-      <x:c r="M22" s="44"/>
+      <x:c r="H22" s="58"/>
+      <x:c r="I22" s="58"/>
+      <x:c r="J22" s="57"/>
+      <x:c r="K22" s="57"/>
+      <x:c r="L22" s="57"/>
+      <x:c r="M22" s="57"/>
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
-      <x:c r="A23" s="46" t="str">
+      <x:c r="A23" s="56" t="str">
         <x:v>B16</x:v>
       </x:c>
-      <x:c r="B23" s="44" t="str">
+      <x:c r="B23" s="57" t="str">
         <x:v>Step 6 · Security</x:v>
       </x:c>
-      <x:c r="C23" s="44" t="str">
+      <x:c r="C23" s="57" t="str">
         <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
       </x:c>
-      <x:c r="D23" s="44" t="str">
+      <x:c r="D23" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E23" s="44" t="str">
+      <x:c r="E23" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F23" s="44" t="str">
+      <x:c r="F23" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G23" s="44" t="str">
+      <x:c r="G23" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H23" s="45"/>
-      <x:c r="I23" s="45"/>
-      <x:c r="J23" s="44"/>
-      <x:c r="K23" s="44"/>
-      <x:c r="L23" s="44"/>
-      <x:c r="M23" s="44"/>
+      <x:c r="H23" s="58"/>
+      <x:c r="I23" s="58"/>
+      <x:c r="J23" s="57"/>
+      <x:c r="K23" s="57"/>
+      <x:c r="L23" s="57"/>
+      <x:c r="M23" s="57"/>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="46" t="str">
+      <x:c r="A24" s="56" t="str">
         <x:v>B19</x:v>
       </x:c>
-      <x:c r="B24" s="44" t="str">
+      <x:c r="B24" s="57" t="str">
         <x:v>Step 6 · Chat</x:v>
       </x:c>
-      <x:c r="C24" s="44" t="str">
+      <x:c r="C24" s="57" t="str">
         <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
       </x:c>
-      <x:c r="D24" s="44" t="str">
+      <x:c r="D24" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E24" s="44" t="str">
+      <x:c r="E24" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="44" t="str">
+      <x:c r="F24" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G24" s="44" t="str">
+      <x:c r="G24" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H24" s="45"/>
-      <x:c r="I24" s="45"/>
-      <x:c r="J24" s="44"/>
-      <x:c r="K24" s="44"/>
-      <x:c r="L24" s="44"/>
-      <x:c r="M24" s="44"/>
+      <x:c r="H24" s="58"/>
+      <x:c r="I24" s="58"/>
+      <x:c r="J24" s="57"/>
+      <x:c r="K24" s="57"/>
+      <x:c r="L24" s="57"/>
+      <x:c r="M24" s="57"/>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="46" t="str">
+      <x:c r="A25" s="56" t="str">
         <x:v>B20</x:v>
       </x:c>
-      <x:c r="B25" s="44" t="str">
+      <x:c r="B25" s="57" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C25" s="44" t="str">
+      <x:c r="C25" s="57" t="str">
         <x:v>Project/unit/plot status logic and validation</x:v>
       </x:c>
-      <x:c r="D25" s="44" t="str">
+      <x:c r="D25" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E25" s="44" t="str">
+      <x:c r="E25" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="44" t="str">
+      <x:c r="F25" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G25" s="44" t="str">
+      <x:c r="G25" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H25" s="45"/>
-      <x:c r="I25" s="45"/>
-      <x:c r="J25" s="44"/>
-      <x:c r="K25" s="44"/>
-      <x:c r="L25" s="44"/>
-      <x:c r="M25" s="44"/>
+      <x:c r="H25" s="58"/>
+      <x:c r="I25" s="58"/>
+      <x:c r="J25" s="57"/>
+      <x:c r="K25" s="57"/>
+      <x:c r="L25" s="57"/>
+      <x:c r="M25" s="57"/>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="46" t="str">
+      <x:c r="A26" s="56" t="str">
         <x:v>B21</x:v>
       </x:c>
-      <x:c r="B26" s="44" t="str">
+      <x:c r="B26" s="57" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C26" s="44" t="str">
+      <x:c r="C26" s="57" t="str">
         <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
       </x:c>
-      <x:c r="D26" s="44" t="str">
+      <x:c r="D26" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E26" s="44" t="str">
+      <x:c r="E26" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="44" t="str">
+      <x:c r="F26" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G26" s="44" t="str">
+      <x:c r="G26" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H26" s="45"/>
-      <x:c r="I26" s="45"/>
-      <x:c r="J26" s="44"/>
-      <x:c r="K26" s="44"/>
-      <x:c r="L26" s="44"/>
-      <x:c r="M26" s="44"/>
+      <x:c r="H26" s="58"/>
+      <x:c r="I26" s="58"/>
+      <x:c r="J26" s="57"/>
+      <x:c r="K26" s="57"/>
+      <x:c r="L26" s="57"/>
+      <x:c r="M26" s="57"/>
     </x:row>
     <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="46" t="str">
+      <x:c r="A27" s="56" t="str">
         <x:v>B22</x:v>
       </x:c>
-      <x:c r="B27" s="44" t="str">
+      <x:c r="B27" s="57" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C27" s="44" t="str">
+      <x:c r="C27" s="57" t="str">
         <x:v>Saved listings/searches persistence, new-match calculations</x:v>
       </x:c>
-      <x:c r="D27" s="44" t="str">
+      <x:c r="D27" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E27" s="44" t="str">
+      <x:c r="E27" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="44" t="str">
+      <x:c r="F27" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G27" s="44" t="str">
+      <x:c r="G27" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H27" s="45"/>
-      <x:c r="I27" s="45"/>
-      <x:c r="J27" s="44"/>
-      <x:c r="K27" s="44"/>
-      <x:c r="L27" s="44"/>
-      <x:c r="M27" s="44"/>
+      <x:c r="H27" s="58"/>
+      <x:c r="I27" s="58"/>
+      <x:c r="J27" s="57"/>
+      <x:c r="K27" s="57"/>
+      <x:c r="L27" s="57"/>
+      <x:c r="M27" s="57"/>
     </x:row>
     <x:row r="28" ht="26" customHeight="1">
-      <x:c r="A28" s="46" t="str">
+      <x:c r="A28" s="56" t="str">
         <x:v>B24</x:v>
       </x:c>
-      <x:c r="B28" s="44" t="str">
+      <x:c r="B28" s="57" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C28" s="44" t="str">
+      <x:c r="C28" s="57" t="str">
         <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
       </x:c>
-      <x:c r="D28" s="44" t="str">
+      <x:c r="D28" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E28" s="44" t="str">
+      <x:c r="E28" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="44" t="str">
+      <x:c r="F28" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G28" s="44" t="str">
+      <x:c r="G28" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H28" s="45"/>
-      <x:c r="I28" s="45"/>
-      <x:c r="J28" s="44"/>
-      <x:c r="K28" s="44"/>
-      <x:c r="L28" s="44"/>
-      <x:c r="M28" s="44"/>
+      <x:c r="H28" s="58"/>
+      <x:c r="I28" s="58"/>
+      <x:c r="J28" s="57"/>
+      <x:c r="K28" s="57"/>
+      <x:c r="L28" s="57"/>
+      <x:c r="M28" s="57"/>
     </x:row>
     <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="46" t="str">
+      <x:c r="A29" s="56" t="str">
         <x:v>B25</x:v>
       </x:c>
-      <x:c r="B29" s="44" t="str">
+      <x:c r="B29" s="57" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C29" s="44" t="str">
+      <x:c r="C29" s="57" t="str">
         <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
       </x:c>
-      <x:c r="D29" s="44" t="str">
+      <x:c r="D29" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E29" s="44" t="str">
+      <x:c r="E29" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="44" t="str">
+      <x:c r="F29" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="44" t="str">
+      <x:c r="G29" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="45"/>
-      <x:c r="I29" s="45"/>
-      <x:c r="J29" s="44"/>
-      <x:c r="K29" s="44"/>
-      <x:c r="L29" s="44"/>
-      <x:c r="M29" s="44"/>
+      <x:c r="H29" s="58"/>
+      <x:c r="I29" s="58"/>
+      <x:c r="J29" s="57"/>
+      <x:c r="K29" s="57"/>
+      <x:c r="L29" s="57"/>
+      <x:c r="M29" s="57"/>
     </x:row>
     <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="46" t="str">
+      <x:c r="A30" s="56" t="str">
         <x:v>B26</x:v>
       </x:c>
-      <x:c r="B30" s="44" t="str">
+      <x:c r="B30" s="57" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C30" s="44" t="str">
+      <x:c r="C30" s="57" t="str">
         <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
       </x:c>
-      <x:c r="D30" s="44" t="str">
+      <x:c r="D30" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E30" s="44" t="str">
+      <x:c r="E30" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="44" t="str">
+      <x:c r="F30" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="44" t="str">
+      <x:c r="G30" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="45"/>
-      <x:c r="I30" s="45"/>
-      <x:c r="J30" s="44"/>
-      <x:c r="K30" s="44"/>
-      <x:c r="L30" s="44"/>
-      <x:c r="M30" s="44"/>
+      <x:c r="H30" s="58"/>
+      <x:c r="I30" s="58"/>
+      <x:c r="J30" s="57"/>
+      <x:c r="K30" s="57"/>
+      <x:c r="L30" s="57"/>
+      <x:c r="M30" s="57"/>
     </x:row>
     <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="46" t="str">
+      <x:c r="A31" s="56" t="str">
         <x:v>B27</x:v>
       </x:c>
-      <x:c r="B31" s="44" t="str">
+      <x:c r="B31" s="57" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C31" s="44" t="str">
+      <x:c r="C31" s="57" t="str">
         <x:v>Admin user management, audit log and sensitive action authorization</x:v>
       </x:c>
-      <x:c r="D31" s="44" t="str">
+      <x:c r="D31" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E31" s="44" t="str">
+      <x:c r="E31" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="44" t="str">
+      <x:c r="F31" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="44" t="str">
+      <x:c r="G31" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="45"/>
-      <x:c r="I31" s="45"/>
-      <x:c r="J31" s="44"/>
-      <x:c r="K31" s="44"/>
-      <x:c r="L31" s="44"/>
-      <x:c r="M31" s="44"/>
+      <x:c r="H31" s="58"/>
+      <x:c r="I31" s="58"/>
+      <x:c r="J31" s="57"/>
+      <x:c r="K31" s="57"/>
+      <x:c r="L31" s="57"/>
+      <x:c r="M31" s="57"/>
     </x:row>
     <x:row r="32" ht="26" customHeight="1">
-      <x:c r="A32" s="46" t="str">
+      <x:c r="A32" s="56" t="str">
         <x:v>B30</x:v>
       </x:c>
-      <x:c r="B32" s="44" t="str">
+      <x:c r="B32" s="57" t="str">
         <x:v>Step 12 · Deploy</x:v>
       </x:c>
-      <x:c r="C32" s="44" t="str">
+      <x:c r="C32" s="57" t="str">
         <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
       </x:c>
-      <x:c r="D32" s="44" t="str">
+      <x:c r="D32" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E32" s="44" t="str">
+      <x:c r="E32" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="44" t="str">
+      <x:c r="F32" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G32" s="44" t="str">
+      <x:c r="G32" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H32" s="45"/>
-      <x:c r="I32" s="45"/>
-      <x:c r="J32" s="44"/>
-      <x:c r="K32" s="44"/>
-      <x:c r="L32" s="44"/>
-      <x:c r="M32" s="44"/>
+      <x:c r="H32" s="58"/>
+      <x:c r="I32" s="58"/>
+      <x:c r="J32" s="57"/>
+      <x:c r="K32" s="57"/>
+      <x:c r="L32" s="57"/>
+      <x:c r="M32" s="57"/>
     </x:row>
     <x:row r="33" ht="26" customHeight="1">
-      <x:c r="A33" s="46" t="str">
+      <x:c r="A33" s="56" t="str">
         <x:v>B31</x:v>
       </x:c>
-      <x:c r="B33" s="44" t="str">
+      <x:c r="B33" s="57" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C33" s="44" t="str">
+      <x:c r="C33" s="57" t="str">
         <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
       </x:c>
-      <x:c r="D33" s="44" t="str">
+      <x:c r="D33" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E33" s="44" t="str">
+      <x:c r="E33" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F33" s="44" t="str">
+      <x:c r="F33" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G33" s="44" t="str">
+      <x:c r="G33" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H33" s="45"/>
-      <x:c r="I33" s="45"/>
-      <x:c r="J33" s="44"/>
-      <x:c r="K33" s="44"/>
-      <x:c r="L33" s="44"/>
-      <x:c r="M33" s="44"/>
+      <x:c r="H33" s="58"/>
+      <x:c r="I33" s="58"/>
+      <x:c r="J33" s="57"/>
+      <x:c r="K33" s="57"/>
+      <x:c r="L33" s="57"/>
+      <x:c r="M33" s="57"/>
     </x:row>
     <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="46" t="str">
+      <x:c r="A34" s="56" t="str">
         <x:v>B32</x:v>
       </x:c>
-      <x:c r="B34" s="44" t="str">
+      <x:c r="B34" s="57" t="str">
         <x:v>Step 12 · Security</x:v>
       </x:c>
-      <x:c r="C34" s="44" t="str">
+      <x:c r="C34" s="57" t="str">
         <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
       </x:c>
-      <x:c r="D34" s="44" t="str">
+      <x:c r="D34" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E34" s="44" t="str">
+      <x:c r="E34" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F34" s="44" t="str">
+      <x:c r="F34" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G34" s="44" t="str">
+      <x:c r="G34" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H34" s="45"/>
-      <x:c r="I34" s="45"/>
-      <x:c r="J34" s="44"/>
-      <x:c r="K34" s="44"/>
-      <x:c r="L34" s="44"/>
-      <x:c r="M34" s="44"/>
+      <x:c r="H34" s="58"/>
+      <x:c r="I34" s="58"/>
+      <x:c r="J34" s="57"/>
+      <x:c r="K34" s="57"/>
+      <x:c r="L34" s="57"/>
+      <x:c r="M34" s="57"/>
     </x:row>
     <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="46" t="str">
+      <x:c r="A35" s="56" t="str">
         <x:v>B33</x:v>
       </x:c>
-      <x:c r="B35" s="44" t="str">
+      <x:c r="B35" s="57" t="str">
         <x:v>Step 7 · Owners</x:v>
       </x:c>
-      <x:c r="C35" s="44" t="str">
+      <x:c r="C35" s="57" t="str">
         <x:v>Home-value and service enquiry data handling</x:v>
       </x:c>
-      <x:c r="D35" s="44" t="str">
+      <x:c r="D35" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E35" s="44" t="str">
+      <x:c r="E35" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F35" s="44" t="str">
+      <x:c r="F35" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G35" s="44" t="str">
+      <x:c r="G35" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H35" s="45"/>
-      <x:c r="I35" s="45"/>
-      <x:c r="J35" s="44"/>
-      <x:c r="K35" s="44"/>
-      <x:c r="L35" s="44"/>
-      <x:c r="M35" s="44"/>
+      <x:c r="H35" s="58"/>
+      <x:c r="I35" s="58"/>
+      <x:c r="J35" s="57"/>
+      <x:c r="K35" s="57"/>
+      <x:c r="L35" s="57"/>
+      <x:c r="M35" s="57"/>
     </x:row>
     <x:row r="36" ht="26" customHeight="1">
       <x:c r="A36" s="46"/>
@@ -16946,15 +17207,15 @@
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E6:E38">
-    <x:cfRule type="expression" dxfId="3" priority="1">
-      <x:formula>E6="Pending"</x:formula>
+  <x:conditionalFormatting sqref="A6:M500">
+    <x:cfRule type="expression" dxfId="18" priority="1">
+      <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="4" priority="2">
-      <x:formula>E6="Done"</x:formula>
+    <x:cfRule type="expression" dxfId="19" priority="2">
+      <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="5" priority="3">
-      <x:formula>E6="Not started"</x:formula>
+    <x:cfRule type="expression" dxfId="20" priority="3">
+      <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
@@ -16967,13 +17228,16 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf97900a44a464015"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03129b46c54d4819"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF202733"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
@@ -17004,7 +17268,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
+        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -17090,236 +17354,236 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="46" t="str">
+      <x:c r="A6" s="56" t="str">
         <x:v>E01</x:v>
       </x:c>
-      <x:c r="B6" s="44" t="str">
+      <x:c r="B6" s="57" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C6" s="44" t="str">
+      <x:c r="C6" s="57" t="str">
         <x:v>Enquiry notification with retryable queue/outbox</x:v>
       </x:c>
-      <x:c r="D6" s="44" t="str">
+      <x:c r="D6" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E6" s="44" t="str">
+      <x:c r="E6" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F6" s="44" t="str">
+      <x:c r="F6" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G6" s="44" t="str">
+      <x:c r="G6" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H6" s="45"/>
-      <x:c r="I6" s="45"/>
-      <x:c r="J6" s="44"/>
-      <x:c r="K6" s="44"/>
-      <x:c r="L6" s="44"/>
-      <x:c r="M6" s="44"/>
+      <x:c r="H6" s="58"/>
+      <x:c r="I6" s="58"/>
+      <x:c r="J6" s="57"/>
+      <x:c r="K6" s="57"/>
+      <x:c r="L6" s="57"/>
+      <x:c r="M6" s="57"/>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="46" t="str">
+      <x:c r="A7" s="56" t="str">
         <x:v>E02</x:v>
       </x:c>
-      <x:c r="B7" s="44" t="str">
+      <x:c r="B7" s="57" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C7" s="44" t="str">
+      <x:c r="C7" s="57" t="str">
         <x:v>Thai and English buyer enquiry acknowledgments</x:v>
       </x:c>
-      <x:c r="D7" s="44" t="str">
+      <x:c r="D7" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E7" s="44" t="str">
+      <x:c r="E7" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F7" s="44" t="str">
+      <x:c r="F7" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G7" s="44" t="str">
+      <x:c r="G7" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H7" s="45"/>
-      <x:c r="I7" s="45"/>
-      <x:c r="J7" s="44"/>
-      <x:c r="K7" s="44"/>
-      <x:c r="L7" s="44"/>
-      <x:c r="M7" s="44"/>
+      <x:c r="H7" s="58"/>
+      <x:c r="I7" s="58"/>
+      <x:c r="J7" s="57"/>
+      <x:c r="K7" s="57"/>
+      <x:c r="L7" s="57"/>
+      <x:c r="M7" s="57"/>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="46" t="str">
+      <x:c r="A8" s="56" t="str">
         <x:v>E03</x:v>
       </x:c>
-      <x:c r="B8" s="44" t="str">
+      <x:c r="B8" s="57" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C8" s="44" t="str">
+      <x:c r="C8" s="57" t="str">
         <x:v>Project brochure/price list email delivery</x:v>
       </x:c>
-      <x:c r="D8" s="44" t="str">
+      <x:c r="D8" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E8" s="44" t="str">
+      <x:c r="E8" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F8" s="44" t="str">
+      <x:c r="F8" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G8" s="44" t="str">
+      <x:c r="G8" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H8" s="45"/>
-      <x:c r="I8" s="45"/>
-      <x:c r="J8" s="44"/>
-      <x:c r="K8" s="44"/>
-      <x:c r="L8" s="44"/>
-      <x:c r="M8" s="44"/>
+      <x:c r="H8" s="58"/>
+      <x:c r="I8" s="58"/>
+      <x:c r="J8" s="57"/>
+      <x:c r="K8" s="57"/>
+      <x:c r="L8" s="57"/>
+      <x:c r="M8" s="57"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="46" t="str">
+      <x:c r="A9" s="56" t="str">
         <x:v>E04</x:v>
       </x:c>
-      <x:c r="B9" s="44" t="str">
+      <x:c r="B9" s="57" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C9" s="44" t="str">
+      <x:c r="C9" s="57" t="str">
         <x:v>Site visit request and confirmation notifications</x:v>
       </x:c>
-      <x:c r="D9" s="44" t="str">
+      <x:c r="D9" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E9" s="44" t="str">
+      <x:c r="E9" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F9" s="44" t="str">
+      <x:c r="F9" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G9" s="44" t="str">
+      <x:c r="G9" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H9" s="45"/>
-      <x:c r="I9" s="45"/>
-      <x:c r="J9" s="44"/>
-      <x:c r="K9" s="44"/>
-      <x:c r="L9" s="44"/>
-      <x:c r="M9" s="44"/>
+      <x:c r="H9" s="58"/>
+      <x:c r="I9" s="58"/>
+      <x:c r="J9" s="57"/>
+      <x:c r="K9" s="57"/>
+      <x:c r="L9" s="57"/>
+      <x:c r="M9" s="57"/>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="46" t="str">
+      <x:c r="A10" s="56" t="str">
         <x:v>E05</x:v>
       </x:c>
-      <x:c r="B10" s="44" t="str">
+      <x:c r="B10" s="57" t="str">
         <x:v>Step 9 · Alerts</x:v>
       </x:c>
-      <x:c r="C10" s="44" t="str">
+      <x:c r="C10" s="57" t="str">
         <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
       </x:c>
-      <x:c r="D10" s="44" t="str">
+      <x:c r="D10" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E10" s="44" t="str">
+      <x:c r="E10" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F10" s="44" t="str">
+      <x:c r="F10" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G10" s="44" t="str">
+      <x:c r="G10" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H10" s="45"/>
-      <x:c r="I10" s="45"/>
-      <x:c r="J10" s="44"/>
-      <x:c r="K10" s="44"/>
-      <x:c r="L10" s="44"/>
-      <x:c r="M10" s="44"/>
+      <x:c r="H10" s="58"/>
+      <x:c r="I10" s="58"/>
+      <x:c r="J10" s="57"/>
+      <x:c r="K10" s="57"/>
+      <x:c r="L10" s="57"/>
+      <x:c r="M10" s="57"/>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="46" t="str">
+      <x:c r="A11" s="56" t="str">
         <x:v>E06</x:v>
       </x:c>
-      <x:c r="B11" s="44" t="str">
+      <x:c r="B11" s="57" t="str">
         <x:v>Step 10B · Email</x:v>
       </x:c>
-      <x:c r="C11" s="44" t="str">
+      <x:c r="C11" s="57" t="str">
         <x:v>Account verification and recovery messages if email auth approved</x:v>
       </x:c>
-      <x:c r="D11" s="44" t="str">
+      <x:c r="D11" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E11" s="44" t="str">
+      <x:c r="E11" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F11" s="44" t="str">
+      <x:c r="F11" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G11" s="44" t="str">
+      <x:c r="G11" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H11" s="45"/>
-      <x:c r="I11" s="45"/>
-      <x:c r="J11" s="44"/>
-      <x:c r="K11" s="44"/>
-      <x:c r="L11" s="44"/>
-      <x:c r="M11" s="44"/>
+      <x:c r="H11" s="58"/>
+      <x:c r="I11" s="58"/>
+      <x:c r="J11" s="57"/>
+      <x:c r="K11" s="57"/>
+      <x:c r="L11" s="57"/>
+      <x:c r="M11" s="57"/>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="46" t="str">
+      <x:c r="A12" s="56" t="str">
         <x:v>E07</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="str">
+      <x:c r="B12" s="57" t="str">
         <x:v>Step 11B · Email</x:v>
       </x:c>
-      <x:c r="C12" s="44" t="str">
+      <x:c r="C12" s="57" t="str">
         <x:v>Agent notification/routing administration</x:v>
       </x:c>
-      <x:c r="D12" s="44" t="str">
+      <x:c r="D12" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E12" s="44" t="str">
+      <x:c r="E12" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F12" s="44" t="str">
+      <x:c r="F12" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G12" s="44" t="str">
+      <x:c r="G12" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H12" s="45"/>
-      <x:c r="I12" s="45"/>
-      <x:c r="J12" s="44"/>
-      <x:c r="K12" s="44"/>
-      <x:c r="L12" s="44"/>
-      <x:c r="M12" s="44"/>
+      <x:c r="H12" s="58"/>
+      <x:c r="I12" s="58"/>
+      <x:c r="J12" s="57"/>
+      <x:c r="K12" s="57"/>
+      <x:c r="L12" s="57"/>
+      <x:c r="M12" s="57"/>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="46" t="str">
+      <x:c r="A13" s="56" t="str">
         <x:v>E08</x:v>
       </x:c>
-      <x:c r="B13" s="44" t="str">
+      <x:c r="B13" s="57" t="str">
         <x:v>Step 7 · Email</x:v>
       </x:c>
-      <x:c r="C13" s="44" t="str">
+      <x:c r="C13" s="57" t="str">
         <x:v>Home valuation and service enquiry replies</x:v>
       </x:c>
-      <x:c r="D13" s="44" t="str">
+      <x:c r="D13" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E13" s="44" t="str">
+      <x:c r="E13" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="44" t="str">
+      <x:c r="F13" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G13" s="44" t="str">
+      <x:c r="G13" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H13" s="45"/>
-      <x:c r="I13" s="45"/>
-      <x:c r="J13" s="44"/>
-      <x:c r="K13" s="44"/>
-      <x:c r="L13" s="44"/>
-      <x:c r="M13" s="44"/>
+      <x:c r="H13" s="58"/>
+      <x:c r="I13" s="58"/>
+      <x:c r="J13" s="57"/>
+      <x:c r="K13" s="57"/>
+      <x:c r="L13" s="57"/>
+      <x:c r="M13" s="57"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="44"/>
@@ -24631,15 +24895,15 @@
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E6:E13">
-    <x:cfRule type="expression" dxfId="6" priority="1">
-      <x:formula>E6="Pending"</x:formula>
+  <x:conditionalFormatting sqref="A6:M500">
+    <x:cfRule type="expression" dxfId="21" priority="1">
+      <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="7" priority="2">
-      <x:formula>E6="Done"</x:formula>
+    <x:cfRule type="expression" dxfId="22" priority="2">
+      <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="8" priority="3">
-      <x:formula>E6="Not started"</x:formula>
+    <x:cfRule type="expression" dxfId="23" priority="3">
+      <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
@@ -24649,13 +24913,16 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a3d0235b3e94810"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1eeb83cef3334d68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFC6EFCE"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
@@ -24686,7 +24953,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
+        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -24772,212 +25039,212 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="44" t="str">
+      <x:c r="A6" s="61" t="str">
         <x:v>B34</x:v>
       </x:c>
-      <x:c r="B6" s="44" t="str">
+      <x:c r="B6" s="61" t="str">
         <x:v>Step 1 · Health</x:v>
       </x:c>
-      <x:c r="C6" s="44" t="str">
+      <x:c r="C6" s="61" t="str">
         <x:v>Basic /api/health endpoint with accurate application and database status</x:v>
       </x:c>
-      <x:c r="D6" s="44" t="str">
+      <x:c r="D6" s="61" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E6" s="44" t="str">
+      <x:c r="E6" s="61" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F6" s="44" t="str">
+      <x:c r="F6" s="61" t="str">
         <x:v>Real /api/health now probes the migrated public view rather than an empty database select 1. Actual 200/ready true, stopped-DB 503/unavailable/ready false and recovery to 200 verified.</x:v>
       </x:c>
-      <x:c r="G6" s="44" t="str">
+      <x:c r="G6" s="61" t="str">
         <x:v>Codex: retain truthful readiness and generic errors; start localhost only under owner/test authorization.</x:v>
       </x:c>
-      <x:c r="H6" s="45" t="d">
+      <x:c r="H6" s="62" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="45" t="d">
+      <x:c r="I6" s="62" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="44" t="str">
+      <x:c r="J6" s="61" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="44" t="str">
+      <x:c r="K6" s="61" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="44" t="str">
+      <x:c r="L6" s="61" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="44" t="str">
+      <x:c r="M6" s="61" t="str">
         <x:v>2026-10-09: Health API planned. No implementation in Step 0.
 2026-10-09 foundation: Real health API implemented: HTTP 200 app ok, database not_configured, ready false before closure. Configured PostgreSQL is probed with Drizzle select 1; failure returns 503. No real database configuration exists. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Real /api/health now probes the migrated public view rather than an empty database select 1. Actual 200/ready true, stopped-DB 503/unavailable/ready false and recovery to 200 verified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="310" customHeight="1">
-      <x:c r="A7" s="44" t="str">
+      <x:c r="A7" s="61" t="str">
         <x:v>B01</x:v>
       </x:c>
-      <x:c r="B7" s="44" t="str">
+      <x:c r="B7" s="61" t="str">
         <x:v>Step 2 · Database</x:v>
       </x:c>
-      <x:c r="C7" s="44" t="str">
+      <x:c r="C7" s="61" t="str">
         <x:v>PostgreSQL/Drizzle schema for listings, projects, agents and users</x:v>
       </x:c>
-      <x:c r="D7" s="44" t="str">
+      <x:c r="D7" s="61" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E7" s="44" t="str">
+      <x:c r="E7" s="61" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F7" s="44" t="str">
+      <x:c r="F7" s="61" t="str">
         <x:v>18-table Drizzle schema implemented with bilingual fields, seven property types, sale/rent rules, explicit price visibility and separate non-superuser migration/read-only app roles. Isolated local development/test PostgreSQL configured; no shared service modified.</x:v>
       </x:c>
-      <x:c r="G7" s="44" t="str">
+      <x:c r="G7" s="61" t="str">
         <x:v>Codex: preserve schema/security contracts in later explicitly authorized stages.</x:v>
       </x:c>
-      <x:c r="H7" s="45" t="d">
+      <x:c r="H7" s="62" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="45" t="d">
+      <x:c r="I7" s="62" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="44" t="str">
+      <x:c r="J7" s="61" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K7" s="44" t="str">
+      <x:c r="K7" s="61" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L7" s="44" t="str">
+      <x:c r="L7" s="61" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="44" t="str">
+      <x:c r="M7" s="61" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: 18-table Drizzle schema implemented with bilingual fields, seven property types, sale/rent rules, explicit price visibility and separate non-superuser migration/read-only app roles. Isolated local development/test PostgreSQL configured; no shared service modified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="310" customHeight="1">
-      <x:c r="A8" s="44" t="str">
+      <x:c r="A8" s="61" t="str">
         <x:v>B02</x:v>
       </x:c>
-      <x:c r="B8" s="44" t="str">
+      <x:c r="B8" s="61" t="str">
         <x:v>Step 2 · Database</x:v>
       </x:c>
-      <x:c r="C8" s="44" t="str">
+      <x:c r="C8" s="61" t="str">
         <x:v>Migrations, foreign keys, constraints and rollback procedure</x:v>
       </x:c>
-      <x:c r="D8" s="44" t="str">
+      <x:c r="D8" s="61" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="44" t="str">
+      <x:c r="E8" s="61" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F8" s="44" t="str">
+      <x:c r="F8" s="61" t="str">
         <x:v>Generated foundation and custom relational migrations, journal/snapshots, constraints/FKs/triggers and guarded test-only initial rollback implemented. Real pg_dump/committed rollback/pg_restore/rerun pass. No production migration performed.</x:v>
       </x:c>
-      <x:c r="G8" s="44" t="str">
+      <x:c r="G8" s="61" t="str">
         <x:v>Codex: generate reviewed additive migrations for later changes; production migration requires authorization and verified backup.</x:v>
       </x:c>
-      <x:c r="H8" s="45" t="d">
+      <x:c r="H8" s="62" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I8" s="45" t="d">
+      <x:c r="I8" s="62" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="44" t="str">
+      <x:c r="J8" s="61" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K8" s="44" t="str">
+      <x:c r="K8" s="61" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L8" s="44" t="str">
+      <x:c r="L8" s="61" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M8" s="44" t="str">
+      <x:c r="M8" s="61" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Generated foundation and custom relational migrations, journal/snapshots, constraints/FKs/triggers and guarded test-only initial rollback implemented. Real pg_dump/committed rollback/pg_restore/rerun pass. No production migration performed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="310" customHeight="1">
-      <x:c r="A9" s="44" t="str">
+      <x:c r="A9" s="61" t="str">
         <x:v>B03</x:v>
       </x:c>
-      <x:c r="B9" s="44" t="str">
+      <x:c r="B9" s="61" t="str">
         <x:v>Step 2 · Demo</x:v>
       </x:c>
-      <x:c r="C9" s="44" t="str">
+      <x:c r="C9" s="61" t="str">
         <x:v>Clearly fictional seed listings, projects and agents</x:v>
       </x:c>
-      <x:c r="D9" s="44" t="str">
+      <x:c r="D9" s="61" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E9" s="44" t="str">
+      <x:c r="E9" s="61" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F9" s="44" t="str">
+      <x:c r="F9" s="61" t="str">
         <x:v>Repeatable local-only seed: 14 explicitly fictional listings, seven types/both intents and related demo records. Invalid domains, disabled users/agents, closed enquiries and off alerts. Public projection excludes demo inventory; no real prices/agents advertised.</x:v>
       </x:c>
-      <x:c r="G9" s="44" t="str">
+      <x:c r="G9" s="61" t="str">
         <x:v>Codex: keep demo data labelled and excluded from genuine inventory; seed only named local dev/test databases.</x:v>
       </x:c>
-      <x:c r="H9" s="45" t="d">
+      <x:c r="H9" s="62" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I9" s="45" t="d">
+      <x:c r="I9" s="62" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J9" s="44" t="str">
+      <x:c r="J9" s="61" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K9" s="44" t="str">
+      <x:c r="K9" s="61" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L9" s="44" t="str">
+      <x:c r="L9" s="61" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M9" s="44" t="str">
+      <x:c r="M9" s="61" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Repeatable local-only seed: 14 explicitly fictional listings, seven types/both intents and related demo records. Invalid domains, disabled users/agents, closed enquiries and off alerts. Public projection excludes demo inventory; no real prices/agents advertised. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="44" t="str">
+      <x:c r="A10" s="61" t="str">
         <x:v>B04</x:v>
       </x:c>
-      <x:c r="B10" s="44" t="str">
+      <x:c r="B10" s="61" t="str">
         <x:v>Step 2 · Search</x:v>
       </x:c>
-      <x:c r="C10" s="44" t="str">
+      <x:c r="C10" s="61" t="str">
         <x:v>Indexes for status, intent, type, price, location and title</x:v>
       </x:c>
-      <x:c r="D10" s="44" t="str">
+      <x:c r="D10" s="61" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="44" t="str">
+      <x:c r="E10" s="61" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F10" s="44" t="str">
+      <x:c r="F10" s="61" t="str">
         <x:v>Intent/type/status/price, location/status, bounding coordinates, publication/feed and bilingual simple-text indexes implemented. Catalog and EXPLAIN use checks pass. Tiny-seed plans prove indexes are usable, not production speed.</x:v>
       </x:c>
-      <x:c r="G10" s="44" t="str">
+      <x:c r="G10" s="61" t="str">
         <x:v>Codex: use parameterized typed queries in Step 3; profile against realistic volume during later QA.</x:v>
       </x:c>
-      <x:c r="H10" s="45" t="d">
+      <x:c r="H10" s="62" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="45" t="d">
+      <x:c r="I10" s="62" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="44" t="str">
+      <x:c r="J10" s="61" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="44" t="str">
+      <x:c r="K10" s="61" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="44" t="str">
+      <x:c r="L10" s="61" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="44" t="str">
+      <x:c r="M10" s="61" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Intent/type/status/price, location/status, bounding coordinates, publication/feed and bilingual simple-text indexes implemented. Catalog and EXPLAIN use checks pass. Tiny-seed plans prove indexes are usable, not production speed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
@@ -32337,6 +32604,17 @@
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="A6:M500">
+    <x:cfRule type="expression" dxfId="24" priority="1">
+      <x:formula>$E6="Pending"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="25" priority="2">
+      <x:formula>$E6="Done"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="26" priority="3">
+      <x:formula>$E6="Not started"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="E6:E10">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
@@ -32344,13 +32622,16 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58e460fd3323412f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R495b54da53904d6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFFFF2CC"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
@@ -32381,7 +32662,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
+        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -32467,43 +32748,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="46" t="str">
+      <x:c r="A6" s="50" t="str">
         <x:v>F02</x:v>
       </x:c>
-      <x:c r="B6" s="44" t="str">
+      <x:c r="B6" s="51" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="44" t="str">
+      <x:c r="C6" s="51" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent</x:v>
       </x:c>
-      <x:c r="D6" s="44" t="str">
+      <x:c r="D6" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="44" t="str">
+      <x:c r="E6" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="44" t="str">
+      <x:c r="F6" s="51" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G6" s="44" t="str">
+      <x:c r="G6" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H6" s="45" t="d">
+      <x:c r="H6" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="45" t="d">
+      <x:c r="I6" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="44" t="str">
+      <x:c r="J6" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="44" t="str">
+      <x:c r="K6" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="44" t="str">
+      <x:c r="L6" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="44" t="str">
+      <x:c r="M6" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
 2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.
 2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.
@@ -32512,414 +32793,415 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="250" customHeight="1">
-      <x:c r="A7" s="46" t="str">
+      <x:c r="A7" s="50" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B7" s="44" t="str">
+      <x:c r="B7" s="51" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C7" s="44" t="str">
+      <x:c r="C7" s="51" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D7" s="44" t="str">
+      <x:c r="D7" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="44" t="str">
+      <x:c r="E7" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="44" t="str">
+      <x:c r="F7" s="51" t="str">
         <x:v>Approved temporary crest extracted and implemented. Owner will provide final header logo later.</x:v>
       </x:c>
-      <x:c r="G7" s="44" t="str">
+      <x:c r="G7" s="51" t="str">
         <x:v>Owner: supply final asset/version later; Codex: replace only approved logo.</x:v>
       </x:c>
-      <x:c r="H7" s="45" t="d">
+      <x:c r="H7" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="45" t="d">
+      <x:c r="I7" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="44" t="str">
+      <x:c r="J7" s="51" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K7" s="44" t="str">
+      <x:c r="K7" s="51" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L7" s="44" t="str">
+      <x:c r="L7" s="51" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="44" t="str">
+      <x:c r="M7" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
 2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.
 2026-10-09 foundation: Approved temporary crest extracted and implemented. Owner will provide final header logo later. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="46" t="str">
+      <x:c r="A8" s="50" t="str">
         <x:v>F32</x:v>
       </x:c>
-      <x:c r="B8" s="44" t="str">
+      <x:c r="B8" s="51" t="str">
         <x:v>Step 10A · Wireframe</x:v>
       </x:c>
-      <x:c r="C8" s="44" t="str">
+      <x:c r="C8" s="51" t="str">
         <x:v>Owner-approved login/register/account wireframe before coding</x:v>
       </x:c>
-      <x:c r="D8" s="44" t="str">
+      <x:c r="D8" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="44" t="str">
+      <x:c r="E8" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="44" t="str">
+      <x:c r="F8" s="51" t="str">
         <x:v>Admin/account screens are not part of approved V3 visuals</x:v>
       </x:c>
-      <x:c r="G8" s="44" t="str">
+      <x:c r="G8" s="51" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H8" s="45"/>
-      <x:c r="I8" s="45"/>
-      <x:c r="J8" s="44"/>
-      <x:c r="K8" s="44"/>
-      <x:c r="L8" s="44"/>
-      <x:c r="M8" s="44"/>
+      <x:c r="H8" s="52"/>
+      <x:c r="I8" s="52"/>
+      <x:c r="J8" s="51"/>
+      <x:c r="K8" s="51"/>
+      <x:c r="L8" s="51"/>
+      <x:c r="M8" s="51"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="46" t="str">
+      <x:c r="A9" s="50" t="str">
         <x:v>F34</x:v>
       </x:c>
-      <x:c r="B9" s="44" t="str">
+      <x:c r="B9" s="51" t="str">
         <x:v>Step 11A · Wireframe</x:v>
       </x:c>
-      <x:c r="C9" s="44" t="str">
+      <x:c r="C9" s="51" t="str">
         <x:v>Owner-approved responsive admin dashboard wireframe</x:v>
       </x:c>
-      <x:c r="D9" s="44" t="str">
+      <x:c r="D9" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="44" t="str">
+      <x:c r="E9" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="44" t="str">
+      <x:c r="F9" s="51" t="str">
         <x:v>Admin UI not included in V3; design approval required</x:v>
       </x:c>
-      <x:c r="G9" s="44" t="str">
+      <x:c r="G9" s="51" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H9" s="45"/>
-      <x:c r="I9" s="45"/>
-      <x:c r="J9" s="44"/>
-      <x:c r="K9" s="44"/>
-      <x:c r="L9" s="44"/>
-      <x:c r="M9" s="44"/>
+      <x:c r="H9" s="52"/>
+      <x:c r="I9" s="52"/>
+      <x:c r="J9" s="51"/>
+      <x:c r="K9" s="51"/>
+      <x:c r="L9" s="51"/>
+      <x:c r="M9" s="51"/>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="46" t="str">
+      <x:c r="A10" s="50" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B10" s="44" t="str">
+      <x:c r="B10" s="51" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C10" s="44" t="str">
+      <x:c r="C10" s="51" t="str">
         <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
-      <x:c r="D10" s="44" t="str">
+      <x:c r="D10" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="44" t="str">
+      <x:c r="E10" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="44" t="str">
+      <x:c r="F10" s="51" t="str">
         <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
-      <x:c r="G10" s="44" t="str">
+      <x:c r="G10" s="51" t="str">
         <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
       </x:c>
-      <x:c r="H10" s="45" t="d">
+      <x:c r="H10" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="45" t="d">
+      <x:c r="I10" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="44" t="str">
+      <x:c r="J10" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="44" t="str">
+      <x:c r="K10" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="44" t="str">
+      <x:c r="L10" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="44" t="str">
+      <x:c r="M10" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
 2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
 2026-10-09 Step 2: Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="46" t="str">
+      <x:c r="A11" s="50" t="str">
         <x:v>B17</x:v>
       </x:c>
-      <x:c r="B11" s="44" t="str">
+      <x:c r="B11" s="51" t="str">
         <x:v>Decision · Leads</x:v>
       </x:c>
-      <x:c r="C11" s="44" t="str">
+      <x:c r="C11" s="51" t="str">
         <x:v>Approve shared inbox versus listing agent enquiry destination</x:v>
       </x:c>
-      <x:c r="D11" s="44" t="str">
+      <x:c r="D11" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E11" s="44" t="str">
+      <x:c r="E11" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="44" t="str">
+      <x:c r="F11" s="51" t="str">
         <x:v>BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
-      <x:c r="G11" s="44" t="str">
+      <x:c r="G11" s="51" t="str">
         <x:v>Owner: select routing mode and mailbox</x:v>
       </x:c>
-      <x:c r="H11" s="45"/>
-      <x:c r="I11" s="45"/>
-      <x:c r="J11" s="44"/>
-      <x:c r="K11" s="44"/>
-      <x:c r="L11" s="44"/>
-      <x:c r="M11" s="44"/>
+      <x:c r="H11" s="52"/>
+      <x:c r="I11" s="52"/>
+      <x:c r="J11" s="51"/>
+      <x:c r="K11" s="51"/>
+      <x:c r="L11" s="51"/>
+      <x:c r="M11" s="51"/>
     </x:row>
     <x:row r="12" ht="250" customHeight="1">
-      <x:c r="A12" s="46" t="str">
+      <x:c r="A12" s="50" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="str">
+      <x:c r="B12" s="51" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C12" s="44" t="str">
+      <x:c r="C12" s="51" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D12" s="44" t="str">
+      <x:c r="D12" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E12" s="44" t="str">
+      <x:c r="E12" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="44" t="str">
+      <x:c r="F12" s="51" t="str">
         <x:v>Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending.</x:v>
       </x:c>
-      <x:c r="G12" s="44" t="str">
+      <x:c r="G12" s="51" t="str">
         <x:v>Owner: provide actual contacts/routing; Codex: integrate and review accessible contact actions later.</x:v>
       </x:c>
-      <x:c r="H12" s="45" t="d">
+      <x:c r="H12" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="45" t="d">
+      <x:c r="I12" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="44" t="str">
+      <x:c r="J12" s="51" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K12" s="44" t="str">
+      <x:c r="K12" s="51" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L12" s="44" t="str">
+      <x:c r="L12" s="51" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="44" t="str">
+      <x:c r="M12" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #4 unresolved
 2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.
 2026-10-09 foundation: Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="46" t="str">
+      <x:c r="A13" s="50" t="str">
         <x:v>B23</x:v>
       </x:c>
-      <x:c r="B13" s="44" t="str">
+      <x:c r="B13" s="51" t="str">
         <x:v>Decision · Accounts</x:v>
       </x:c>
-      <x:c r="C13" s="44" t="str">
+      <x:c r="C13" s="51" t="str">
         <x:v>Approve LINE only or LINE+Google+email sign-in</x:v>
       </x:c>
-      <x:c r="D13" s="44" t="str">
+      <x:c r="D13" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E13" s="44" t="str">
+      <x:c r="E13" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F13" s="44" t="str">
+      <x:c r="F13" s="51" t="str">
         <x:v>BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
-      <x:c r="G13" s="44" t="str">
+      <x:c r="G13" s="51" t="str">
         <x:v>Owner: approve authentication providers</x:v>
       </x:c>
-      <x:c r="H13" s="45"/>
-      <x:c r="I13" s="45"/>
-      <x:c r="J13" s="44"/>
-      <x:c r="K13" s="44"/>
-      <x:c r="L13" s="44"/>
-      <x:c r="M13" s="44"/>
+      <x:c r="H13" s="52"/>
+      <x:c r="I13" s="52"/>
+      <x:c r="J13" s="51"/>
+      <x:c r="K13" s="51"/>
+      <x:c r="L13" s="51"/>
+      <x:c r="M13" s="51"/>
     </x:row>
     <x:row r="14" ht="200" customHeight="1">
-      <x:c r="A14" s="46" t="str">
+      <x:c r="A14" s="50" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B14" s="44" t="str">
+      <x:c r="B14" s="51" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C14" s="44" t="str">
+      <x:c r="C14" s="51" t="str">
         <x:v>Approve THB only versus optional approximate FX display</x:v>
       </x:c>
-      <x:c r="D14" s="44" t="str">
+      <x:c r="D14" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E14" s="44" t="str">
+      <x:c r="E14" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="44" t="str">
+      <x:c r="F14" s="51" t="str">
         <x:v>Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
-      <x:c r="G14" s="44" t="str">
+      <x:c r="G14" s="51" t="str">
         <x:v>Codex: implement USD/THB during authorized currency work; confirm rate source.</x:v>
       </x:c>
-      <x:c r="H14" s="45"/>
-      <x:c r="I14" s="45" t="d">
+      <x:c r="H14" s="52"/>
+      <x:c r="I14" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="44" t="str">
+      <x:c r="J14" s="51" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K14" s="44" t="str">
+      <x:c r="K14" s="51" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L14" s="44" t="str">
+      <x:c r="L14" s="51" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M14" s="44" t="str">
+      <x:c r="M14" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #6 unresolved
 2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="200" customHeight="1">
-      <x:c r="A15" s="46" t="str">
+      <x:c r="A15" s="50" t="str">
         <x:v>B29</x:v>
       </x:c>
-      <x:c r="B15" s="44" t="str">
+      <x:c r="B15" s="51" t="str">
         <x:v>Decision · Projects</x:v>
       </x:c>
-      <x:c r="C15" s="44" t="str">
+      <x:c r="C15" s="51" t="str">
         <x:v>Approve public project prices versus enquiry-only price list</x:v>
       </x:c>
-      <x:c r="D15" s="44" t="str">
+      <x:c r="D15" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E15" s="44" t="str">
+      <x:c r="E15" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F15" s="44" t="str">
+      <x:c r="F15" s="51" t="str">
         <x:v>Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
-      <x:c r="G15" s="44" t="str">
+      <x:c r="G15" s="51" t="str">
         <x:v>Codex: add per-record price visibility in authorized backend/admin work after admin wireframe approval.</x:v>
       </x:c>
-      <x:c r="H15" s="45"/>
-      <x:c r="I15" s="45" t="d">
+      <x:c r="H15" s="52"/>
+      <x:c r="I15" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J15" s="44" t="str">
+      <x:c r="J15" s="51" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K15" s="44" t="str">
+      <x:c r="K15" s="51" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L15" s="44" t="str">
+      <x:c r="L15" s="51" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M15" s="44" t="str">
+      <x:c r="M15" s="51" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #7 unresolved
 2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="310" customHeight="1">
-      <x:c r="A16" s="44" t="str">
+      <x:c r="A16" s="51" t="str">
         <x:v>R01</x:v>
       </x:c>
-      <x:c r="B16" s="44" t="str">
+      <x:c r="B16" s="51" t="str">
         <x:v>Step 0 · Preparation</x:v>
       </x:c>
-      <x:c r="C16" s="44" t="str">
+      <x:c r="C16" s="51" t="str">
         <x:v>Inspect project; establish permanent rules, documentation, Git/live mirror and tracker</x:v>
       </x:c>
-      <x:c r="D16" s="44" t="str">
+      <x:c r="D16" s="51" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E16" s="44" t="str">
+      <x:c r="E16" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F16" s="44" t="str">
+      <x:c r="F16" s="51" t="str">
         <x:v>Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request.</x:v>
       </x:c>
-      <x:c r="G16" s="44" t="str">
+      <x:c r="G16" s="51" t="str">
         <x:v>Codex: close the separate Step 0 utility/reference-review requirements only when authorized; stop before Step 3.</x:v>
       </x:c>
-      <x:c r="H16" s="45" t="d">
+      <x:c r="H16" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I16" s="45" t="d">
+      <x:c r="I16" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J16" s="44" t="str">
+      <x:c r="J16" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K16" s="44" t="str">
+      <x:c r="K16" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L16" s="44" t="str">
+      <x:c r="L16" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M16" s="44" t="str">
+      <x:c r="M16" s="51" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
 2026-10-09 foundation: Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.
-2026-10-09 Step 2: Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
+2026-10-09 Step 2: Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
+2026-10-09 tracker formatting: workbook recreated with yellow Pending, light green Done and red Not started rows and status tabs. All 81 permanent IDs and prior task history preserved. Step 3 is authorized but implementation has not begun; owner requested the Excel first.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="310" customHeight="1">
-      <x:c r="A17" s="44" t="str">
+      <x:c r="A17" s="51" t="str">
         <x:v>F01</x:v>
       </x:c>
-      <x:c r="B17" s="44" t="str">
+      <x:c r="B17" s="51" t="str">
         <x:v>Step 1 · Design</x:v>
       </x:c>
-      <x:c r="C17" s="44" t="str">
+      <x:c r="C17" s="51" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives</x:v>
       </x:c>
-      <x:c r="D17" s="44" t="str">
+      <x:c r="D17" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="44" t="str">
+      <x:c r="E17" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F17" s="44" t="str">
+      <x:c r="F17" s="51" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G17" s="44" t="str">
+      <x:c r="G17" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H17" s="45" t="d">
+      <x:c r="H17" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I17" s="45" t="d">
+      <x:c r="I17" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J17" s="44" t="str">
+      <x:c r="J17" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K17" s="44" t="str">
+      <x:c r="K17" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L17" s="44" t="str">
+      <x:c r="L17" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M17" s="44" t="str">
+      <x:c r="M17" s="51" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -32927,43 +33209,43 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="310" customHeight="1">
-      <x:c r="A18" s="44" t="str">
+      <x:c r="A18" s="51" t="str">
         <x:v>F04</x:v>
       </x:c>
-      <x:c r="B18" s="44" t="str">
+      <x:c r="B18" s="51" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C18" s="44" t="str">
+      <x:c r="C18" s="51" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in</x:v>
       </x:c>
-      <x:c r="D18" s="44" t="str">
+      <x:c r="D18" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="44" t="str">
+      <x:c r="E18" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F18" s="44" t="str">
+      <x:c r="F18" s="51" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G18" s="44" t="str">
+      <x:c r="G18" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H18" s="45" t="d">
+      <x:c r="H18" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I18" s="45" t="d">
+      <x:c r="I18" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J18" s="44" t="str">
+      <x:c r="J18" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K18" s="44" t="str">
+      <x:c r="K18" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L18" s="44" t="str">
+      <x:c r="L18" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M18" s="44" t="str">
+      <x:c r="M18" s="51" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -32971,43 +33253,43 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="310" customHeight="1">
-      <x:c r="A19" s="44" t="str">
+      <x:c r="A19" s="51" t="str">
         <x:v>F05</x:v>
       </x:c>
-      <x:c r="B19" s="44" t="str">
+      <x:c r="B19" s="51" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C19" s="44" t="str">
+      <x:c r="C19" s="51" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints</x:v>
       </x:c>
-      <x:c r="D19" s="44" t="str">
+      <x:c r="D19" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="44" t="str">
+      <x:c r="E19" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F19" s="44" t="str">
+      <x:c r="F19" s="51" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G19" s="44" t="str">
+      <x:c r="G19" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H19" s="45" t="d">
+      <x:c r="H19" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I19" s="45" t="d">
+      <x:c r="I19" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J19" s="44" t="str">
+      <x:c r="J19" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K19" s="44" t="str">
+      <x:c r="K19" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L19" s="44" t="str">
+      <x:c r="L19" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M19" s="44" t="str">
+      <x:c r="M19" s="51" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33015,43 +33297,43 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="310" customHeight="1">
-      <x:c r="A20" s="44" t="str">
+      <x:c r="A20" s="51" t="str">
         <x:v>F06</x:v>
       </x:c>
-      <x:c r="B20" s="44" t="str">
+      <x:c r="B20" s="51" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C20" s="44" t="str">
+      <x:c r="C20" s="51" t="str">
         <x:v>Light footer, company links, contact and PDPA link</x:v>
       </x:c>
-      <x:c r="D20" s="44" t="str">
+      <x:c r="D20" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="44" t="str">
+      <x:c r="E20" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F20" s="44" t="str">
+      <x:c r="F20" s="51" t="str">
         <x:v>Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G20" s="44" t="str">
+      <x:c r="G20" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H20" s="45" t="d">
+      <x:c r="H20" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I20" s="45" t="d">
+      <x:c r="I20" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J20" s="44" t="str">
+      <x:c r="J20" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K20" s="44" t="str">
+      <x:c r="K20" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L20" s="44" t="str">
+      <x:c r="L20" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M20" s="44" t="str">
+      <x:c r="M20" s="51" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33059,43 +33341,43 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="310" customHeight="1">
-      <x:c r="A21" s="44" t="str">
+      <x:c r="A21" s="51" t="str">
         <x:v>F07</x:v>
       </x:c>
-      <x:c r="B21" s="44" t="str">
+      <x:c r="B21" s="51" t="str">
         <x:v>Step 1 · i18n</x:v>
       </x:c>
-      <x:c r="C21" s="44" t="str">
+      <x:c r="C21" s="51" t="str">
         <x:v>Thai/English routes, language switch and localized formatting</x:v>
       </x:c>
-      <x:c r="D21" s="44" t="str">
+      <x:c r="D21" s="51" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="44" t="str">
+      <x:c r="E21" s="51" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F21" s="44" t="str">
+      <x:c r="F21" s="51" t="str">
         <x:v>Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G21" s="44" t="str">
+      <x:c r="G21" s="51" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H21" s="45" t="d">
+      <x:c r="H21" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I21" s="45" t="d">
+      <x:c r="I21" s="52" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J21" s="44" t="str">
+      <x:c r="J21" s="51" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K21" s="44" t="str">
+      <x:c r="K21" s="51" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L21" s="44" t="str">
+      <x:c r="L21" s="51" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M21" s="44" t="str">
+      <x:c r="M21" s="51" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -40292,15 +40574,15 @@
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E6:E15">
-    <x:cfRule type="expression" dxfId="9" priority="1">
-      <x:formula>E6="Pending"</x:formula>
+  <x:conditionalFormatting sqref="A6:M500">
+    <x:cfRule type="expression" dxfId="27" priority="1">
+      <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="10" priority="2">
-      <x:formula>E6="Done"</x:formula>
+    <x:cfRule type="expression" dxfId="28" priority="2">
+      <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="11" priority="3">
-      <x:formula>E6="Not started"</x:formula>
+    <x:cfRule type="expression" dxfId="29" priority="3">
+      <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
@@ -40313,13 +40595,16 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25f240809d04414e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabe72850259a4b3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFFF6666"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
@@ -40350,7 +40635,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 2 verified PostgreSQL schema/seed. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Preserve append-only history. Test servers stop afterward.</x:v>
+        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -40436,1777 +40721,1777 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="250" customHeight="1">
-      <x:c r="A6" s="46" t="str">
+      <x:c r="A6" s="56" t="str">
         <x:v>F08</x:v>
       </x:c>
-      <x:c r="B6" s="44" t="str">
+      <x:c r="B6" s="57" t="str">
         <x:v>Step 3 · Cards</x:v>
       </x:c>
-      <x:c r="C6" s="44" t="str">
+      <x:c r="C6" s="57" t="str">
         <x:v>Realtor-style 3:2 listing cards, photo controls, bottom-right save heart, facts/address and Contact agent dialog trigger</x:v>
       </x:c>
-      <x:c r="D6" s="44" t="str">
+      <x:c r="D6" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="44" t="str">
+      <x:c r="E6" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F6" s="44" t="str">
+      <x:c r="F6" s="57" t="str">
         <x:v>V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
       </x:c>
-      <x:c r="G6" s="44" t="str">
+      <x:c r="G6" s="57" t="str">
         <x:v>Codex: build revised card only under Step 3 authorization, after the real database step.</x:v>
       </x:c>
-      <x:c r="H6" s="45"/>
-      <x:c r="I6" s="45" t="d">
+      <x:c r="H6" s="58"/>
+      <x:c r="I6" s="58" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="44" t="str">
+      <x:c r="J6" s="57" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K6" s="44" t="str">
+      <x:c r="K6" s="57" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L6" s="44" t="str">
+      <x:c r="L6" s="57" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M6" s="44" t="str">
+      <x:c r="M6" s="57" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="46" t="str">
+      <x:c r="A7" s="56" t="str">
         <x:v>F09</x:v>
       </x:c>
-      <x:c r="B7" s="44" t="str">
+      <x:c r="B7" s="57" t="str">
         <x:v>Step 3 · Results</x:v>
       </x:c>
-      <x:c r="C7" s="44" t="str">
+      <x:c r="C7" s="57" t="str">
         <x:v>Responsive /buy, /rent and /invest results layouts</x:v>
       </x:c>
-      <x:c r="D7" s="44" t="str">
+      <x:c r="D7" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="44" t="str">
+      <x:c r="E7" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F7" s="44" t="str">
+      <x:c r="F7" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G7" s="44" t="str">
+      <x:c r="G7" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H7" s="45"/>
-      <x:c r="I7" s="45"/>
-      <x:c r="J7" s="44"/>
-      <x:c r="K7" s="44"/>
-      <x:c r="L7" s="44"/>
-      <x:c r="M7" s="44"/>
+      <x:c r="H7" s="58"/>
+      <x:c r="I7" s="58"/>
+      <x:c r="J7" s="57"/>
+      <x:c r="K7" s="57"/>
+      <x:c r="L7" s="57"/>
+      <x:c r="M7" s="57"/>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="46" t="str">
+      <x:c r="A8" s="56" t="str">
         <x:v>F10</x:v>
       </x:c>
-      <x:c r="B8" s="44" t="str">
+      <x:c r="B8" s="57" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C8" s="44" t="str">
+      <x:c r="C8" s="57" t="str">
         <x:v>Shared URL filters, active chips, sorting and navigation history</x:v>
       </x:c>
-      <x:c r="D8" s="44" t="str">
+      <x:c r="D8" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="44" t="str">
+      <x:c r="E8" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F8" s="44" t="str">
+      <x:c r="F8" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G8" s="44" t="str">
+      <x:c r="G8" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H8" s="45"/>
-      <x:c r="I8" s="45"/>
-      <x:c r="J8" s="44"/>
-      <x:c r="K8" s="44"/>
-      <x:c r="L8" s="44"/>
-      <x:c r="M8" s="44"/>
+      <x:c r="H8" s="58"/>
+      <x:c r="I8" s="58"/>
+      <x:c r="J8" s="57"/>
+      <x:c r="K8" s="57"/>
+      <x:c r="L8" s="57"/>
+      <x:c r="M8" s="57"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="46" t="str">
+      <x:c r="A9" s="56" t="str">
         <x:v>F11</x:v>
       </x:c>
-      <x:c r="B9" s="44" t="str">
+      <x:c r="B9" s="57" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C9" s="44" t="str">
+      <x:c r="C9" s="57" t="str">
         <x:v>Desktop popovers for price, beds, type and advanced filters</x:v>
       </x:c>
-      <x:c r="D9" s="44" t="str">
+      <x:c r="D9" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="44" t="str">
+      <x:c r="E9" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F9" s="44" t="str">
+      <x:c r="F9" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G9" s="44" t="str">
+      <x:c r="G9" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H9" s="45"/>
-      <x:c r="I9" s="45"/>
-      <x:c r="J9" s="44"/>
-      <x:c r="K9" s="44"/>
-      <x:c r="L9" s="44"/>
-      <x:c r="M9" s="44"/>
+      <x:c r="H9" s="58"/>
+      <x:c r="I9" s="58"/>
+      <x:c r="J9" s="57"/>
+      <x:c r="K9" s="57"/>
+      <x:c r="L9" s="57"/>
+      <x:c r="M9" s="57"/>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="46" t="str">
+      <x:c r="A10" s="56" t="str">
         <x:v>F12</x:v>
       </x:c>
-      <x:c r="B10" s="44" t="str">
+      <x:c r="B10" s="57" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C10" s="44" t="str">
+      <x:c r="C10" s="57" t="str">
         <x:v>Phone full-screen filter sheet, Apply and Clear</x:v>
       </x:c>
-      <x:c r="D10" s="44" t="str">
+      <x:c r="D10" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E10" s="44" t="str">
+      <x:c r="E10" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F10" s="44" t="str">
+      <x:c r="F10" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G10" s="44" t="str">
+      <x:c r="G10" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H10" s="45"/>
-      <x:c r="I10" s="45"/>
-      <x:c r="J10" s="44"/>
-      <x:c r="K10" s="44"/>
-      <x:c r="L10" s="44"/>
-      <x:c r="M10" s="44"/>
+      <x:c r="H10" s="58"/>
+      <x:c r="I10" s="58"/>
+      <x:c r="J10" s="57"/>
+      <x:c r="K10" s="57"/>
+      <x:c r="L10" s="57"/>
+      <x:c r="M10" s="57"/>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="46" t="str">
+      <x:c r="A11" s="56" t="str">
         <x:v>F13</x:v>
       </x:c>
-      <x:c r="B11" s="44" t="str">
+      <x:c r="B11" s="57" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C11" s="44" t="str">
+      <x:c r="C11" s="57" t="str">
         <x:v>Database-derived price histogram and live result count</x:v>
       </x:c>
-      <x:c r="D11" s="44" t="str">
+      <x:c r="D11" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E11" s="44" t="str">
+      <x:c r="E11" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F11" s="44" t="str">
+      <x:c r="F11" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G11" s="44" t="str">
+      <x:c r="G11" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H11" s="45"/>
-      <x:c r="I11" s="45"/>
-      <x:c r="J11" s="44"/>
-      <x:c r="K11" s="44"/>
-      <x:c r="L11" s="44"/>
-      <x:c r="M11" s="44"/>
+      <x:c r="H11" s="58"/>
+      <x:c r="I11" s="58"/>
+      <x:c r="J11" s="57"/>
+      <x:c r="K11" s="57"/>
+      <x:c r="L11" s="57"/>
+      <x:c r="M11" s="57"/>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="46" t="str">
+      <x:c r="A12" s="56" t="str">
         <x:v>F14</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="str">
+      <x:c r="B12" s="57" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C12" s="44" t="str">
+      <x:c r="C12" s="57" t="str">
         <x:v>Desktop listing/map split and hover/focus pin synchronization</x:v>
       </x:c>
-      <x:c r="D12" s="44" t="str">
+      <x:c r="D12" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E12" s="44" t="str">
+      <x:c r="E12" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F12" s="44" t="str">
+      <x:c r="F12" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G12" s="44" t="str">
+      <x:c r="G12" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H12" s="45"/>
-      <x:c r="I12" s="45"/>
-      <x:c r="J12" s="44"/>
-      <x:c r="K12" s="44"/>
-      <x:c r="L12" s="44"/>
-      <x:c r="M12" s="44"/>
+      <x:c r="H12" s="58"/>
+      <x:c r="I12" s="58"/>
+      <x:c r="J12" s="57"/>
+      <x:c r="K12" s="57"/>
+      <x:c r="L12" s="57"/>
+      <x:c r="M12" s="57"/>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="46" t="str">
+      <x:c r="A13" s="56" t="str">
         <x:v>F15</x:v>
       </x:c>
-      <x:c r="B13" s="44" t="str">
+      <x:c r="B13" s="57" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C13" s="44" t="str">
+      <x:c r="C13" s="57" t="str">
         <x:v>Phone full-screen Map/List toggle</x:v>
       </x:c>
-      <x:c r="D13" s="44" t="str">
+      <x:c r="D13" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E13" s="44" t="str">
+      <x:c r="E13" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="44" t="str">
+      <x:c r="F13" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G13" s="44" t="str">
+      <x:c r="G13" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H13" s="45"/>
-      <x:c r="I13" s="45"/>
-      <x:c r="J13" s="44"/>
-      <x:c r="K13" s="44"/>
-      <x:c r="L13" s="44"/>
-      <x:c r="M13" s="44"/>
+      <x:c r="H13" s="58"/>
+      <x:c r="I13" s="58"/>
+      <x:c r="J13" s="57"/>
+      <x:c r="K13" s="57"/>
+      <x:c r="L13" s="57"/>
+      <x:c r="M13" s="57"/>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="46" t="str">
+      <x:c r="A14" s="56" t="str">
         <x:v>F16</x:v>
       </x:c>
-      <x:c r="B14" s="44" t="str">
+      <x:c r="B14" s="57" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C14" s="44" t="str">
+      <x:c r="C14" s="57" t="str">
         <x:v>Property detail photo grid and full-screen gallery</x:v>
       </x:c>
-      <x:c r="D14" s="44" t="str">
+      <x:c r="D14" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E14" s="44" t="str">
+      <x:c r="E14" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F14" s="44" t="str">
+      <x:c r="F14" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G14" s="44" t="str">
+      <x:c r="G14" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H14" s="45"/>
-      <x:c r="I14" s="45"/>
-      <x:c r="J14" s="44"/>
-      <x:c r="K14" s="44"/>
-      <x:c r="L14" s="44"/>
-      <x:c r="M14" s="44"/>
+      <x:c r="H14" s="58"/>
+      <x:c r="I14" s="58"/>
+      <x:c r="J14" s="57"/>
+      <x:c r="K14" s="57"/>
+      <x:c r="L14" s="57"/>
+      <x:c r="M14" s="57"/>
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="46" t="str">
+      <x:c r="A15" s="56" t="str">
         <x:v>F17</x:v>
       </x:c>
-      <x:c r="B15" s="44" t="str">
+      <x:c r="B15" s="57" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C15" s="44" t="str">
+      <x:c r="C15" s="57" t="str">
         <x:v>Title, pricing, type-specific facts, long description and sticky tabs</x:v>
       </x:c>
-      <x:c r="D15" s="44" t="str">
+      <x:c r="D15" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="44" t="str">
+      <x:c r="E15" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="44" t="str">
+      <x:c r="F15" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G15" s="44" t="str">
+      <x:c r="G15" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H15" s="45"/>
-      <x:c r="I15" s="45"/>
-      <x:c r="J15" s="44"/>
-      <x:c r="K15" s="44"/>
-      <x:c r="L15" s="44"/>
-      <x:c r="M15" s="44"/>
+      <x:c r="H15" s="58"/>
+      <x:c r="I15" s="58"/>
+      <x:c r="J15" s="57"/>
+      <x:c r="K15" s="57"/>
+      <x:c r="L15" s="57"/>
+      <x:c r="M15" s="57"/>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="46" t="str">
+      <x:c r="A16" s="56" t="str">
         <x:v>F18</x:v>
       </x:c>
-      <x:c r="B16" s="44" t="str">
+      <x:c r="B16" s="57" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C16" s="44" t="str">
+      <x:c r="C16" s="57" t="str">
         <x:v>Floorplan/video/360 tabs, verified nearby information and map</x:v>
       </x:c>
-      <x:c r="D16" s="44" t="str">
+      <x:c r="D16" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E16" s="44" t="str">
+      <x:c r="E16" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="44" t="str">
+      <x:c r="F16" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G16" s="44" t="str">
+      <x:c r="G16" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H16" s="45"/>
-      <x:c r="I16" s="45"/>
-      <x:c r="J16" s="44"/>
-      <x:c r="K16" s="44"/>
-      <x:c r="L16" s="44"/>
-      <x:c r="M16" s="44"/>
+      <x:c r="H16" s="58"/>
+      <x:c r="I16" s="58"/>
+      <x:c r="J16" s="57"/>
+      <x:c r="K16" s="57"/>
+      <x:c r="L16" s="57"/>
+      <x:c r="M16" s="57"/>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="46" t="str">
+      <x:c r="A17" s="56" t="str">
         <x:v>F19</x:v>
       </x:c>
-      <x:c r="B17" s="44" t="str">
+      <x:c r="B17" s="57" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C17" s="44" t="str">
+      <x:c r="C17" s="57" t="str">
         <x:v>Mortgage calculator and area comparison when real data exists</x:v>
       </x:c>
-      <x:c r="D17" s="44" t="str">
+      <x:c r="D17" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="44" t="str">
+      <x:c r="E17" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="44" t="str">
+      <x:c r="F17" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G17" s="44" t="str">
+      <x:c r="G17" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H17" s="45"/>
-      <x:c r="I17" s="45"/>
-      <x:c r="J17" s="44"/>
-      <x:c r="K17" s="44"/>
-      <x:c r="L17" s="44"/>
-      <x:c r="M17" s="44"/>
+      <x:c r="H17" s="58"/>
+      <x:c r="I17" s="58"/>
+      <x:c r="J17" s="57"/>
+      <x:c r="K17" s="57"/>
+      <x:c r="L17" s="57"/>
+      <x:c r="M17" s="57"/>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="46" t="str">
+      <x:c r="A18" s="56" t="str">
         <x:v>F20</x:v>
       </x:c>
-      <x:c r="B18" s="44" t="str">
+      <x:c r="B18" s="57" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C18" s="44" t="str">
+      <x:c r="C18" s="57" t="str">
         <x:v>Same-project units and similar-property cards</x:v>
       </x:c>
-      <x:c r="D18" s="44" t="str">
+      <x:c r="D18" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="44" t="str">
+      <x:c r="E18" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F18" s="44" t="str">
+      <x:c r="F18" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G18" s="44" t="str">
+      <x:c r="G18" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H18" s="45"/>
-      <x:c r="I18" s="45"/>
-      <x:c r="J18" s="44"/>
-      <x:c r="K18" s="44"/>
-      <x:c r="L18" s="44"/>
-      <x:c r="M18" s="44"/>
+      <x:c r="H18" s="58"/>
+      <x:c r="I18" s="58"/>
+      <x:c r="J18" s="57"/>
+      <x:c r="K18" s="57"/>
+      <x:c r="L18" s="57"/>
+      <x:c r="M18" s="57"/>
     </x:row>
     <x:row r="19" ht="250" customHeight="1">
-      <x:c r="A19" s="46" t="str">
+      <x:c r="A19" s="56" t="str">
         <x:v>F21</x:v>
       </x:c>
-      <x:c r="B19" s="44" t="str">
+      <x:c r="B19" s="57" t="str">
         <x:v>Step 6 · Contact</x:v>
       </x:c>
-      <x:c r="C19" s="44" t="str">
+      <x:c r="C19" s="57" t="str">
         <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
       </x:c>
-      <x:c r="D19" s="44" t="str">
+      <x:c r="D19" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="44" t="str">
+      <x:c r="E19" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="44" t="str">
+      <x:c r="F19" s="57" t="str">
         <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
-      <x:c r="G19" s="44" t="str">
+      <x:c r="G19" s="57" t="str">
         <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
       </x:c>
-      <x:c r="H19" s="45"/>
-      <x:c r="I19" s="45" t="d">
+      <x:c r="H19" s="58"/>
+      <x:c r="I19" s="58" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J19" s="44" t="str">
+      <x:c r="J19" s="57" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K19" s="44" t="str">
+      <x:c r="K19" s="57" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L19" s="44" t="str">
+      <x:c r="L19" s="57" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M19" s="44" t="str">
+      <x:c r="M19" s="57" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="46" t="str">
+      <x:c r="A20" s="56" t="str">
         <x:v>F22</x:v>
       </x:c>
-      <x:c r="B20" s="44" t="str">
+      <x:c r="B20" s="57" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C20" s="44" t="str">
+      <x:c r="C20" s="57" t="str">
         <x:v>Single-image hero and compact photography-first layout</x:v>
       </x:c>
-      <x:c r="D20" s="44" t="str">
+      <x:c r="D20" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="44" t="str">
+      <x:c r="E20" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="44" t="str">
+      <x:c r="F20" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G20" s="44" t="str">
+      <x:c r="G20" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H20" s="45"/>
-      <x:c r="I20" s="45"/>
-      <x:c r="J20" s="44"/>
-      <x:c r="K20" s="44"/>
-      <x:c r="L20" s="44"/>
-      <x:c r="M20" s="44"/>
+      <x:c r="H20" s="58"/>
+      <x:c r="I20" s="58"/>
+      <x:c r="J20" s="57"/>
+      <x:c r="K20" s="57"/>
+      <x:c r="L20" s="57"/>
+      <x:c r="M20" s="57"/>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="46" t="str">
+      <x:c r="A21" s="56" t="str">
         <x:v>F23</x:v>
       </x:c>
-      <x:c r="B21" s="44" t="str">
+      <x:c r="B21" s="57" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C21" s="44" t="str">
+      <x:c r="C21" s="57" t="str">
         <x:v>Shared search box with Buy/Rent/Projects/Investment tabs</x:v>
       </x:c>
-      <x:c r="D21" s="44" t="str">
+      <x:c r="D21" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="44" t="str">
+      <x:c r="E21" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="44" t="str">
+      <x:c r="F21" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G21" s="44" t="str">
+      <x:c r="G21" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H21" s="45"/>
-      <x:c r="I21" s="45"/>
-      <x:c r="J21" s="44"/>
-      <x:c r="K21" s="44"/>
-      <x:c r="L21" s="44"/>
-      <x:c r="M21" s="44"/>
+      <x:c r="H21" s="58"/>
+      <x:c r="I21" s="58"/>
+      <x:c r="J21" s="57"/>
+      <x:c r="K21" s="57"/>
+      <x:c r="L21" s="57"/>
+      <x:c r="M21" s="57"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="46" t="str">
+      <x:c r="A22" s="56" t="str">
         <x:v>F24</x:v>
       </x:c>
-      <x:c r="B22" s="44" t="str">
+      <x:c r="B22" s="57" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C22" s="44" t="str">
+      <x:c r="C22" s="57" t="str">
         <x:v>Categories, recent searches and location/station suggestions</x:v>
       </x:c>
-      <x:c r="D22" s="44" t="str">
+      <x:c r="D22" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E22" s="44" t="str">
+      <x:c r="E22" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="44" t="str">
+      <x:c r="F22" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G22" s="44" t="str">
+      <x:c r="G22" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H22" s="45"/>
-      <x:c r="I22" s="45"/>
-      <x:c r="J22" s="44"/>
-      <x:c r="K22" s="44"/>
-      <x:c r="L22" s="44"/>
-      <x:c r="M22" s="44"/>
+      <x:c r="H22" s="58"/>
+      <x:c r="I22" s="58"/>
+      <x:c r="J22" s="57"/>
+      <x:c r="K22" s="57"/>
+      <x:c r="L22" s="57"/>
+      <x:c r="M22" s="57"/>
     </x:row>
     <x:row r="23" ht="250" customHeight="1">
-      <x:c r="A23" s="46" t="str">
+      <x:c r="A23" s="56" t="str">
         <x:v>F25</x:v>
       </x:c>
-      <x:c r="B23" s="44" t="str">
+      <x:c r="B23" s="57" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C23" s="44" t="str">
+      <x:c r="C23" s="57" t="str">
         <x:v>Homes for you carousel directly below search; regions with real listing counts</x:v>
       </x:c>
-      <x:c r="D23" s="44" t="str">
+      <x:c r="D23" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E23" s="44" t="str">
+      <x:c r="E23" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F23" s="44" t="str">
+      <x:c r="F23" s="57" t="str">
         <x:v>V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
-      <x:c r="G23" s="44" t="str">
+      <x:c r="G23" s="57" t="str">
         <x:v>Codex: implement approved home-page.html only under Step 7 authorization.</x:v>
       </x:c>
-      <x:c r="H23" s="45"/>
-      <x:c r="I23" s="45" t="d">
+      <x:c r="H23" s="58"/>
+      <x:c r="I23" s="58" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J23" s="44" t="str">
+      <x:c r="J23" s="57" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K23" s="44" t="str">
+      <x:c r="K23" s="57" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L23" s="44" t="str">
+      <x:c r="L23" s="57" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M23" s="44" t="str">
+      <x:c r="M23" s="57" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="46" t="str">
+      <x:c r="A24" s="56" t="str">
         <x:v>F26</x:v>
       </x:c>
-      <x:c r="B24" s="44" t="str">
+      <x:c r="B24" s="57" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C24" s="44" t="str">
+      <x:c r="C24" s="57" t="str">
         <x:v>New projects, tools, services and owner lead CTAs</x:v>
       </x:c>
-      <x:c r="D24" s="44" t="str">
+      <x:c r="D24" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E24" s="44" t="str">
+      <x:c r="E24" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="44" t="str">
+      <x:c r="F24" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G24" s="44" t="str">
+      <x:c r="G24" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H24" s="45"/>
-      <x:c r="I24" s="45"/>
-      <x:c r="J24" s="44"/>
-      <x:c r="K24" s="44"/>
-      <x:c r="L24" s="44"/>
-      <x:c r="M24" s="44"/>
+      <x:c r="H24" s="58"/>
+      <x:c r="I24" s="58"/>
+      <x:c r="J24" s="57"/>
+      <x:c r="K24" s="57"/>
+      <x:c r="L24" s="57"/>
+      <x:c r="M24" s="57"/>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="46" t="str">
+      <x:c r="A25" s="56" t="str">
         <x:v>F27</x:v>
       </x:c>
-      <x:c r="B25" s="44" t="str">
+      <x:c r="B25" s="57" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C25" s="44" t="str">
+      <x:c r="C25" s="57" t="str">
         <x:v>Projects index and responsive project detail layouts</x:v>
       </x:c>
-      <x:c r="D25" s="44" t="str">
+      <x:c r="D25" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E25" s="44" t="str">
+      <x:c r="E25" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="44" t="str">
+      <x:c r="F25" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G25" s="44" t="str">
+      <x:c r="G25" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H25" s="45"/>
-      <x:c r="I25" s="45"/>
-      <x:c r="J25" s="44"/>
-      <x:c r="K25" s="44"/>
-      <x:c r="L25" s="44"/>
-      <x:c r="M25" s="44"/>
+      <x:c r="H25" s="58"/>
+      <x:c r="I25" s="58"/>
+      <x:c r="J25" s="57"/>
+      <x:c r="K25" s="57"/>
+      <x:c r="L25" s="57"/>
+      <x:c r="M25" s="57"/>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="46" t="str">
+      <x:c r="A26" s="56" t="str">
         <x:v>F28</x:v>
       </x:c>
-      <x:c r="B26" s="44" t="str">
+      <x:c r="B26" s="57" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C26" s="44" t="str">
+      <x:c r="C26" s="57" t="str">
         <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
       </x:c>
-      <x:c r="D26" s="44" t="str">
+      <x:c r="D26" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E26" s="44" t="str">
+      <x:c r="E26" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="44" t="str">
+      <x:c r="F26" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G26" s="44" t="str">
+      <x:c r="G26" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H26" s="45"/>
-      <x:c r="I26" s="45"/>
-      <x:c r="J26" s="44"/>
-      <x:c r="K26" s="44"/>
-      <x:c r="L26" s="44"/>
-      <x:c r="M26" s="44"/>
+      <x:c r="H26" s="58"/>
+      <x:c r="I26" s="58"/>
+      <x:c r="J26" s="57"/>
+      <x:c r="K26" s="57"/>
+      <x:c r="L26" s="57"/>
+      <x:c r="M26" s="57"/>
     </x:row>
     <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="46" t="str">
+      <x:c r="A27" s="56" t="str">
         <x:v>F29</x:v>
       </x:c>
-      <x:c r="B27" s="44" t="str">
+      <x:c r="B27" s="57" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C27" s="44" t="str">
+      <x:c r="C27" s="57" t="str">
         <x:v>Data-driven clickable project SVG plot plan</x:v>
       </x:c>
-      <x:c r="D27" s="44" t="str">
+      <x:c r="D27" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E27" s="44" t="str">
+      <x:c r="E27" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="44" t="str">
+      <x:c r="F27" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G27" s="44" t="str">
+      <x:c r="G27" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H27" s="45"/>
-      <x:c r="I27" s="45"/>
-      <x:c r="J27" s="44"/>
-      <x:c r="K27" s="44"/>
-      <x:c r="L27" s="44"/>
-      <x:c r="M27" s="44"/>
+      <x:c r="H27" s="58"/>
+      <x:c r="I27" s="58"/>
+      <x:c r="J27" s="57"/>
+      <x:c r="K27" s="57"/>
+      <x:c r="L27" s="57"/>
+      <x:c r="M27" s="57"/>
     </x:row>
     <x:row r="28" ht="26" customHeight="1">
-      <x:c r="A28" s="46" t="str">
+      <x:c r="A28" s="56" t="str">
         <x:v>F30</x:v>
       </x:c>
-      <x:c r="B28" s="44" t="str">
+      <x:c r="B28" s="57" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C28" s="44" t="str">
+      <x:c r="C28" s="57" t="str">
         <x:v>Site visit 3-step form and confirmation screens</x:v>
       </x:c>
-      <x:c r="D28" s="44" t="str">
+      <x:c r="D28" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E28" s="44" t="str">
+      <x:c r="E28" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="44" t="str">
+      <x:c r="F28" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G28" s="44" t="str">
+      <x:c r="G28" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H28" s="45"/>
-      <x:c r="I28" s="45"/>
-      <x:c r="J28" s="44"/>
-      <x:c r="K28" s="44"/>
-      <x:c r="L28" s="44"/>
-      <x:c r="M28" s="44"/>
+      <x:c r="H28" s="58"/>
+      <x:c r="I28" s="58"/>
+      <x:c r="J28" s="57"/>
+      <x:c r="K28" s="57"/>
+      <x:c r="L28" s="57"/>
+      <x:c r="M28" s="57"/>
     </x:row>
     <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="46" t="str">
+      <x:c r="A29" s="56" t="str">
         <x:v>F31</x:v>
       </x:c>
-      <x:c r="B29" s="44" t="str">
+      <x:c r="B29" s="57" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C29" s="44" t="str">
+      <x:c r="C29" s="57" t="str">
         <x:v>Homes, searches and viewings; local save without account</x:v>
       </x:c>
-      <x:c r="D29" s="44" t="str">
+      <x:c r="D29" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E29" s="44" t="str">
+      <x:c r="E29" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="44" t="str">
+      <x:c r="F29" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="44" t="str">
+      <x:c r="G29" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="45"/>
-      <x:c r="I29" s="45"/>
-      <x:c r="J29" s="44"/>
-      <x:c r="K29" s="44"/>
-      <x:c r="L29" s="44"/>
-      <x:c r="M29" s="44"/>
+      <x:c r="H29" s="58"/>
+      <x:c r="I29" s="58"/>
+      <x:c r="J29" s="57"/>
+      <x:c r="K29" s="57"/>
+      <x:c r="L29" s="57"/>
+      <x:c r="M29" s="57"/>
     </x:row>
     <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="46" t="str">
+      <x:c r="A30" s="56" t="str">
         <x:v>F33</x:v>
       </x:c>
-      <x:c r="B30" s="44" t="str">
+      <x:c r="B30" s="57" t="str">
         <x:v>Step 10B · Accounts</x:v>
       </x:c>
-      <x:c r="C30" s="44" t="str">
+      <x:c r="C30" s="57" t="str">
         <x:v>Build approved auth and account screens only after approval</x:v>
       </x:c>
-      <x:c r="D30" s="44" t="str">
+      <x:c r="D30" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E30" s="44" t="str">
+      <x:c r="E30" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="44" t="str">
+      <x:c r="F30" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="44" t="str">
+      <x:c r="G30" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="45"/>
-      <x:c r="I30" s="45"/>
-      <x:c r="J30" s="44"/>
-      <x:c r="K30" s="44"/>
-      <x:c r="L30" s="44"/>
-      <x:c r="M30" s="44"/>
+      <x:c r="H30" s="58"/>
+      <x:c r="I30" s="58"/>
+      <x:c r="J30" s="57"/>
+      <x:c r="K30" s="57"/>
+      <x:c r="L30" s="57"/>
+      <x:c r="M30" s="57"/>
     </x:row>
     <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="46" t="str">
+      <x:c r="A31" s="56" t="str">
         <x:v>F35</x:v>
       </x:c>
-      <x:c r="B31" s="44" t="str">
+      <x:c r="B31" s="57" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C31" s="44" t="str">
+      <x:c r="C31" s="57" t="str">
         <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
       </x:c>
-      <x:c r="D31" s="44" t="str">
+      <x:c r="D31" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E31" s="44" t="str">
+      <x:c r="E31" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="44" t="str">
+      <x:c r="F31" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="44" t="str">
+      <x:c r="G31" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="45"/>
-      <x:c r="I31" s="45"/>
-      <x:c r="J31" s="44"/>
-      <x:c r="K31" s="44"/>
-      <x:c r="L31" s="44"/>
-      <x:c r="M31" s="44"/>
+      <x:c r="H31" s="58"/>
+      <x:c r="I31" s="58"/>
+      <x:c r="J31" s="57"/>
+      <x:c r="K31" s="57"/>
+      <x:c r="L31" s="57"/>
+      <x:c r="M31" s="57"/>
     </x:row>
     <x:row r="32" ht="26" customHeight="1">
-      <x:c r="A32" s="46" t="str">
+      <x:c r="A32" s="56" t="str">
         <x:v>F36</x:v>
       </x:c>
-      <x:c r="B32" s="44" t="str">
+      <x:c r="B32" s="57" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C32" s="44" t="str">
+      <x:c r="C32" s="57" t="str">
         <x:v>Admin-managed searchable filter editor with type safety</x:v>
       </x:c>
-      <x:c r="D32" s="44" t="str">
+      <x:c r="D32" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E32" s="44" t="str">
+      <x:c r="E32" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="44" t="str">
+      <x:c r="F32" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G32" s="44" t="str">
+      <x:c r="G32" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H32" s="45"/>
-      <x:c r="I32" s="45"/>
-      <x:c r="J32" s="44"/>
-      <x:c r="K32" s="44"/>
-      <x:c r="L32" s="44"/>
-      <x:c r="M32" s="44"/>
+      <x:c r="H32" s="58"/>
+      <x:c r="I32" s="58"/>
+      <x:c r="J32" s="57"/>
+      <x:c r="K32" s="57"/>
+      <x:c r="L32" s="57"/>
+      <x:c r="M32" s="57"/>
     </x:row>
     <x:row r="33" ht="26" customHeight="1">
-      <x:c r="A33" s="46" t="str">
+      <x:c r="A33" s="56" t="str">
         <x:v>F37</x:v>
       </x:c>
-      <x:c r="B33" s="44" t="str">
+      <x:c r="B33" s="57" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C33" s="44" t="str">
+      <x:c r="C33" s="57" t="str">
         <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
       </x:c>
-      <x:c r="D33" s="44" t="str">
+      <x:c r="D33" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E33" s="44" t="str">
+      <x:c r="E33" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F33" s="44" t="str">
+      <x:c r="F33" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G33" s="44" t="str">
+      <x:c r="G33" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H33" s="45"/>
-      <x:c r="I33" s="45"/>
-      <x:c r="J33" s="44"/>
-      <x:c r="K33" s="44"/>
-      <x:c r="L33" s="44"/>
-      <x:c r="M33" s="44"/>
+      <x:c r="H33" s="58"/>
+      <x:c r="I33" s="58"/>
+      <x:c r="J33" s="57"/>
+      <x:c r="K33" s="57"/>
+      <x:c r="L33" s="57"/>
+      <x:c r="M33" s="57"/>
     </x:row>
     <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="46" t="str">
+      <x:c r="A34" s="56" t="str">
         <x:v>F38</x:v>
       </x:c>
-      <x:c r="B34" s="44" t="str">
+      <x:c r="B34" s="57" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C34" s="44" t="str">
+      <x:c r="C34" s="57" t="str">
         <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
       </x:c>
-      <x:c r="D34" s="44" t="str">
+      <x:c r="D34" s="57" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E34" s="44" t="str">
+      <x:c r="E34" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F34" s="44" t="str">
+      <x:c r="F34" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G34" s="44" t="str">
+      <x:c r="G34" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H34" s="45"/>
-      <x:c r="I34" s="45"/>
-      <x:c r="J34" s="44"/>
-      <x:c r="K34" s="44"/>
-      <x:c r="L34" s="44"/>
-      <x:c r="M34" s="44"/>
+      <x:c r="H34" s="58"/>
+      <x:c r="I34" s="58"/>
+      <x:c r="J34" s="57"/>
+      <x:c r="K34" s="57"/>
+      <x:c r="L34" s="57"/>
+      <x:c r="M34" s="57"/>
     </x:row>
     <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="46" t="str">
+      <x:c r="A35" s="56" t="str">
         <x:v>B05</x:v>
       </x:c>
-      <x:c r="B35" s="44" t="str">
+      <x:c r="B35" s="57" t="str">
         <x:v>Step 2 · Filters</x:v>
       </x:c>
-      <x:c r="C35" s="44" t="str">
+      <x:c r="C35" s="57" t="str">
         <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
       </x:c>
-      <x:c r="D35" s="44" t="str">
+      <x:c r="D35" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E35" s="44" t="str">
+      <x:c r="E35" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F35" s="44" t="str">
+      <x:c r="F35" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G35" s="44" t="str">
+      <x:c r="G35" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H35" s="45"/>
-      <x:c r="I35" s="45"/>
-      <x:c r="J35" s="44"/>
-      <x:c r="K35" s="44"/>
-      <x:c r="L35" s="44"/>
-      <x:c r="M35" s="44"/>
+      <x:c r="H35" s="58"/>
+      <x:c r="I35" s="58"/>
+      <x:c r="J35" s="57"/>
+      <x:c r="K35" s="57"/>
+      <x:c r="L35" s="57"/>
+      <x:c r="M35" s="57"/>
     </x:row>
     <x:row r="36" ht="26" customHeight="1">
-      <x:c r="A36" s="46" t="str">
+      <x:c r="A36" s="56" t="str">
         <x:v>B06</x:v>
       </x:c>
-      <x:c r="B36" s="44" t="str">
+      <x:c r="B36" s="57" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C36" s="44" t="str">
+      <x:c r="C36" s="57" t="str">
         <x:v>Typed validated listing/search data access and pagination</x:v>
       </x:c>
-      <x:c r="D36" s="44" t="str">
+      <x:c r="D36" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E36" s="44" t="str">
+      <x:c r="E36" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F36" s="44" t="str">
+      <x:c r="F36" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G36" s="44" t="str">
+      <x:c r="G36" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H36" s="45"/>
-      <x:c r="I36" s="45"/>
-      <x:c r="J36" s="44"/>
-      <x:c r="K36" s="44"/>
-      <x:c r="L36" s="44"/>
-      <x:c r="M36" s="44"/>
+      <x:c r="H36" s="58"/>
+      <x:c r="I36" s="58"/>
+      <x:c r="J36" s="57"/>
+      <x:c r="K36" s="57"/>
+      <x:c r="L36" s="57"/>
+      <x:c r="M36" s="57"/>
     </x:row>
     <x:row r="37" ht="26" customHeight="1">
-      <x:c r="A37" s="46" t="str">
+      <x:c r="A37" s="56" t="str">
         <x:v>B07</x:v>
       </x:c>
-      <x:c r="B37" s="44" t="str">
+      <x:c r="B37" s="57" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C37" s="44" t="str">
+      <x:c r="C37" s="57" t="str">
         <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
       </x:c>
-      <x:c r="D37" s="44" t="str">
+      <x:c r="D37" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E37" s="44" t="str">
+      <x:c r="E37" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F37" s="44" t="str">
+      <x:c r="F37" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G37" s="44" t="str">
+      <x:c r="G37" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H37" s="45"/>
-      <x:c r="I37" s="45"/>
-      <x:c r="J37" s="44"/>
-      <x:c r="K37" s="44"/>
-      <x:c r="L37" s="44"/>
-      <x:c r="M37" s="44"/>
+      <x:c r="H37" s="58"/>
+      <x:c r="I37" s="58"/>
+      <x:c r="J37" s="57"/>
+      <x:c r="K37" s="57"/>
+      <x:c r="L37" s="57"/>
+      <x:c r="M37" s="57"/>
     </x:row>
     <x:row r="38" ht="26" customHeight="1">
-      <x:c r="A38" s="46" t="str">
+      <x:c r="A38" s="56" t="str">
         <x:v>B08</x:v>
       </x:c>
-      <x:c r="B38" s="44" t="str">
+      <x:c r="B38" s="57" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C38" s="44" t="str">
+      <x:c r="C38" s="57" t="str">
         <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
       </x:c>
-      <x:c r="D38" s="44" t="str">
+      <x:c r="D38" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E38" s="44" t="str">
+      <x:c r="E38" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F38" s="44" t="str">
+      <x:c r="F38" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G38" s="44" t="str">
+      <x:c r="G38" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H38" s="45"/>
-      <x:c r="I38" s="45"/>
-      <x:c r="J38" s="44"/>
-      <x:c r="K38" s="44"/>
-      <x:c r="L38" s="44"/>
-      <x:c r="M38" s="44"/>
+      <x:c r="H38" s="58"/>
+      <x:c r="I38" s="58"/>
+      <x:c r="J38" s="57"/>
+      <x:c r="K38" s="57"/>
+      <x:c r="L38" s="57"/>
+      <x:c r="M38" s="57"/>
     </x:row>
     <x:row r="39" ht="26" customHeight="1">
-      <x:c r="A39" s="46" t="str">
+      <x:c r="A39" s="56" t="str">
         <x:v>B10</x:v>
       </x:c>
-      <x:c r="B39" s="44" t="str">
+      <x:c r="B39" s="57" t="str">
         <x:v>Step 4 · Nearby</x:v>
       </x:c>
-      <x:c r="C39" s="44" t="str">
+      <x:c r="C39" s="57" t="str">
         <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
       </x:c>
-      <x:c r="D39" s="44" t="str">
+      <x:c r="D39" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E39" s="44" t="str">
+      <x:c r="E39" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F39" s="44" t="str">
+      <x:c r="F39" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G39" s="44" t="str">
+      <x:c r="G39" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H39" s="45"/>
-      <x:c r="I39" s="45"/>
-      <x:c r="J39" s="44"/>
-      <x:c r="K39" s="44"/>
-      <x:c r="L39" s="44"/>
-      <x:c r="M39" s="44"/>
+      <x:c r="H39" s="58"/>
+      <x:c r="I39" s="58"/>
+      <x:c r="J39" s="57"/>
+      <x:c r="K39" s="57"/>
+      <x:c r="L39" s="57"/>
+      <x:c r="M39" s="57"/>
     </x:row>
     <x:row r="40" ht="26" customHeight="1">
-      <x:c r="A40" s="46" t="str">
+      <x:c r="A40" s="56" t="str">
         <x:v>B11</x:v>
       </x:c>
-      <x:c r="B40" s="44" t="str">
+      <x:c r="B40" s="57" t="str">
         <x:v>Step 5 · Media</x:v>
       </x:c>
-      <x:c r="C40" s="44" t="str">
+      <x:c r="C40" s="57" t="str">
         <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
       </x:c>
-      <x:c r="D40" s="44" t="str">
+      <x:c r="D40" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E40" s="44" t="str">
+      <x:c r="E40" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F40" s="44" t="str">
+      <x:c r="F40" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G40" s="44" t="str">
+      <x:c r="G40" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H40" s="45"/>
-      <x:c r="I40" s="45"/>
-      <x:c r="J40" s="44"/>
-      <x:c r="K40" s="44"/>
-      <x:c r="L40" s="44"/>
-      <x:c r="M40" s="44"/>
+      <x:c r="H40" s="58"/>
+      <x:c r="I40" s="58"/>
+      <x:c r="J40" s="57"/>
+      <x:c r="K40" s="57"/>
+      <x:c r="L40" s="57"/>
+      <x:c r="M40" s="57"/>
     </x:row>
     <x:row r="41" ht="26" customHeight="1">
-      <x:c r="A41" s="46" t="str">
+      <x:c r="A41" s="56" t="str">
         <x:v>B12</x:v>
       </x:c>
-      <x:c r="B41" s="44" t="str">
+      <x:c r="B41" s="57" t="str">
         <x:v>Step 5 · Similar</x:v>
       </x:c>
-      <x:c r="C41" s="44" t="str">
+      <x:c r="C41" s="57" t="str">
         <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
       </x:c>
-      <x:c r="D41" s="44" t="str">
+      <x:c r="D41" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E41" s="44" t="str">
+      <x:c r="E41" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F41" s="44" t="str">
+      <x:c r="F41" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G41" s="44" t="str">
+      <x:c r="G41" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H41" s="45"/>
-      <x:c r="I41" s="45"/>
-      <x:c r="J41" s="44"/>
-      <x:c r="K41" s="44"/>
-      <x:c r="L41" s="44"/>
-      <x:c r="M41" s="44"/>
+      <x:c r="H41" s="58"/>
+      <x:c r="I41" s="58"/>
+      <x:c r="J41" s="57"/>
+      <x:c r="K41" s="57"/>
+      <x:c r="L41" s="57"/>
+      <x:c r="M41" s="57"/>
     </x:row>
     <x:row r="42" ht="26" customHeight="1">
-      <x:c r="A42" s="46" t="str">
+      <x:c r="A42" s="56" t="str">
         <x:v>B13</x:v>
       </x:c>
-      <x:c r="B42" s="44" t="str">
+      <x:c r="B42" s="57" t="str">
         <x:v>Step 5 · Metrics</x:v>
       </x:c>
-      <x:c r="C42" s="44" t="str">
+      <x:c r="C42" s="57" t="str">
         <x:v>Comparable pricing/yield gated by verified sample size</x:v>
       </x:c>
-      <x:c r="D42" s="44" t="str">
+      <x:c r="D42" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E42" s="44" t="str">
+      <x:c r="E42" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F42" s="44" t="str">
+      <x:c r="F42" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G42" s="44" t="str">
+      <x:c r="G42" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H42" s="45"/>
-      <x:c r="I42" s="45"/>
-      <x:c r="J42" s="44"/>
-      <x:c r="K42" s="44"/>
-      <x:c r="L42" s="44"/>
-      <x:c r="M42" s="44"/>
+      <x:c r="H42" s="58"/>
+      <x:c r="I42" s="58"/>
+      <x:c r="J42" s="57"/>
+      <x:c r="K42" s="57"/>
+      <x:c r="L42" s="57"/>
+      <x:c r="M42" s="57"/>
     </x:row>
     <x:row r="43" ht="26" customHeight="1">
-      <x:c r="A43" s="46" t="str">
+      <x:c r="A43" s="56" t="str">
         <x:v>B14</x:v>
       </x:c>
-      <x:c r="B43" s="44" t="str">
+      <x:c r="B43" s="57" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C43" s="44" t="str">
+      <x:c r="C43" s="57" t="str">
         <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
       </x:c>
-      <x:c r="D43" s="44" t="str">
+      <x:c r="D43" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E43" s="44" t="str">
+      <x:c r="E43" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F43" s="44" t="str">
+      <x:c r="F43" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G43" s="44" t="str">
+      <x:c r="G43" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H43" s="45"/>
-      <x:c r="I43" s="45"/>
-      <x:c r="J43" s="44"/>
-      <x:c r="K43" s="44"/>
-      <x:c r="L43" s="44"/>
-      <x:c r="M43" s="44"/>
+      <x:c r="H43" s="58"/>
+      <x:c r="I43" s="58"/>
+      <x:c r="J43" s="57"/>
+      <x:c r="K43" s="57"/>
+      <x:c r="L43" s="57"/>
+      <x:c r="M43" s="57"/>
     </x:row>
     <x:row r="44" ht="26" customHeight="1">
-      <x:c r="A44" s="46" t="str">
+      <x:c r="A44" s="56" t="str">
         <x:v>B15</x:v>
       </x:c>
-      <x:c r="B44" s="44" t="str">
+      <x:c r="B44" s="57" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C44" s="44" t="str">
+      <x:c r="C44" s="57" t="str">
         <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
       </x:c>
-      <x:c r="D44" s="44" t="str">
+      <x:c r="D44" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E44" s="44" t="str">
+      <x:c r="E44" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F44" s="44" t="str">
+      <x:c r="F44" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G44" s="44" t="str">
+      <x:c r="G44" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H44" s="45"/>
-      <x:c r="I44" s="45"/>
-      <x:c r="J44" s="44"/>
-      <x:c r="K44" s="44"/>
-      <x:c r="L44" s="44"/>
-      <x:c r="M44" s="44"/>
+      <x:c r="H44" s="58"/>
+      <x:c r="I44" s="58"/>
+      <x:c r="J44" s="57"/>
+      <x:c r="K44" s="57"/>
+      <x:c r="L44" s="57"/>
+      <x:c r="M44" s="57"/>
     </x:row>
     <x:row r="45" ht="26" customHeight="1">
-      <x:c r="A45" s="46" t="str">
+      <x:c r="A45" s="56" t="str">
         <x:v>B16</x:v>
       </x:c>
-      <x:c r="B45" s="44" t="str">
+      <x:c r="B45" s="57" t="str">
         <x:v>Step 6 · Security</x:v>
       </x:c>
-      <x:c r="C45" s="44" t="str">
+      <x:c r="C45" s="57" t="str">
         <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
       </x:c>
-      <x:c r="D45" s="44" t="str">
+      <x:c r="D45" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E45" s="44" t="str">
+      <x:c r="E45" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F45" s="44" t="str">
+      <x:c r="F45" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G45" s="44" t="str">
+      <x:c r="G45" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H45" s="45"/>
-      <x:c r="I45" s="45"/>
-      <x:c r="J45" s="44"/>
-      <x:c r="K45" s="44"/>
-      <x:c r="L45" s="44"/>
-      <x:c r="M45" s="44"/>
+      <x:c r="H45" s="58"/>
+      <x:c r="I45" s="58"/>
+      <x:c r="J45" s="57"/>
+      <x:c r="K45" s="57"/>
+      <x:c r="L45" s="57"/>
+      <x:c r="M45" s="57"/>
     </x:row>
     <x:row r="46" ht="26" customHeight="1">
-      <x:c r="A46" s="46" t="str">
+      <x:c r="A46" s="56" t="str">
         <x:v>B19</x:v>
       </x:c>
-      <x:c r="B46" s="44" t="str">
+      <x:c r="B46" s="57" t="str">
         <x:v>Step 6 · Chat</x:v>
       </x:c>
-      <x:c r="C46" s="44" t="str">
+      <x:c r="C46" s="57" t="str">
         <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
       </x:c>
-      <x:c r="D46" s="44" t="str">
+      <x:c r="D46" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E46" s="44" t="str">
+      <x:c r="E46" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F46" s="44" t="str">
+      <x:c r="F46" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G46" s="44" t="str">
+      <x:c r="G46" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H46" s="45"/>
-      <x:c r="I46" s="45"/>
-      <x:c r="J46" s="44"/>
-      <x:c r="K46" s="44"/>
-      <x:c r="L46" s="44"/>
-      <x:c r="M46" s="44"/>
+      <x:c r="H46" s="58"/>
+      <x:c r="I46" s="58"/>
+      <x:c r="J46" s="57"/>
+      <x:c r="K46" s="57"/>
+      <x:c r="L46" s="57"/>
+      <x:c r="M46" s="57"/>
     </x:row>
     <x:row r="47" ht="26" customHeight="1">
-      <x:c r="A47" s="46" t="str">
+      <x:c r="A47" s="56" t="str">
         <x:v>B20</x:v>
       </x:c>
-      <x:c r="B47" s="44" t="str">
+      <x:c r="B47" s="57" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C47" s="44" t="str">
+      <x:c r="C47" s="57" t="str">
         <x:v>Project/unit/plot status logic and validation</x:v>
       </x:c>
-      <x:c r="D47" s="44" t="str">
+      <x:c r="D47" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E47" s="44" t="str">
+      <x:c r="E47" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F47" s="44" t="str">
+      <x:c r="F47" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G47" s="44" t="str">
+      <x:c r="G47" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H47" s="45"/>
-      <x:c r="I47" s="45"/>
-      <x:c r="J47" s="44"/>
-      <x:c r="K47" s="44"/>
-      <x:c r="L47" s="44"/>
-      <x:c r="M47" s="44"/>
+      <x:c r="H47" s="58"/>
+      <x:c r="I47" s="58"/>
+      <x:c r="J47" s="57"/>
+      <x:c r="K47" s="57"/>
+      <x:c r="L47" s="57"/>
+      <x:c r="M47" s="57"/>
     </x:row>
     <x:row r="48" ht="26" customHeight="1">
-      <x:c r="A48" s="46" t="str">
+      <x:c r="A48" s="56" t="str">
         <x:v>B21</x:v>
       </x:c>
-      <x:c r="B48" s="44" t="str">
+      <x:c r="B48" s="57" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C48" s="44" t="str">
+      <x:c r="C48" s="57" t="str">
         <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
       </x:c>
-      <x:c r="D48" s="44" t="str">
+      <x:c r="D48" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E48" s="44" t="str">
+      <x:c r="E48" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F48" s="44" t="str">
+      <x:c r="F48" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G48" s="44" t="str">
+      <x:c r="G48" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H48" s="45"/>
-      <x:c r="I48" s="45"/>
-      <x:c r="J48" s="44"/>
-      <x:c r="K48" s="44"/>
-      <x:c r="L48" s="44"/>
-      <x:c r="M48" s="44"/>
+      <x:c r="H48" s="58"/>
+      <x:c r="I48" s="58"/>
+      <x:c r="J48" s="57"/>
+      <x:c r="K48" s="57"/>
+      <x:c r="L48" s="57"/>
+      <x:c r="M48" s="57"/>
     </x:row>
     <x:row r="49" ht="26" customHeight="1">
-      <x:c r="A49" s="46" t="str">
+      <x:c r="A49" s="56" t="str">
         <x:v>B22</x:v>
       </x:c>
-      <x:c r="B49" s="44" t="str">
+      <x:c r="B49" s="57" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C49" s="44" t="str">
+      <x:c r="C49" s="57" t="str">
         <x:v>Saved listings/searches persistence, new-match calculations</x:v>
       </x:c>
-      <x:c r="D49" s="44" t="str">
+      <x:c r="D49" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E49" s="44" t="str">
+      <x:c r="E49" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F49" s="44" t="str">
+      <x:c r="F49" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G49" s="44" t="str">
+      <x:c r="G49" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H49" s="45"/>
-      <x:c r="I49" s="45"/>
-      <x:c r="J49" s="44"/>
-      <x:c r="K49" s="44"/>
-      <x:c r="L49" s="44"/>
-      <x:c r="M49" s="44"/>
+      <x:c r="H49" s="58"/>
+      <x:c r="I49" s="58"/>
+      <x:c r="J49" s="57"/>
+      <x:c r="K49" s="57"/>
+      <x:c r="L49" s="57"/>
+      <x:c r="M49" s="57"/>
     </x:row>
     <x:row r="50" ht="26" customHeight="1">
-      <x:c r="A50" s="46" t="str">
+      <x:c r="A50" s="56" t="str">
         <x:v>B24</x:v>
       </x:c>
-      <x:c r="B50" s="44" t="str">
+      <x:c r="B50" s="57" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C50" s="44" t="str">
+      <x:c r="C50" s="57" t="str">
         <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
       </x:c>
-      <x:c r="D50" s="44" t="str">
+      <x:c r="D50" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E50" s="44" t="str">
+      <x:c r="E50" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F50" s="44" t="str">
+      <x:c r="F50" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G50" s="44" t="str">
+      <x:c r="G50" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H50" s="45"/>
-      <x:c r="I50" s="45"/>
-      <x:c r="J50" s="44"/>
-      <x:c r="K50" s="44"/>
-      <x:c r="L50" s="44"/>
-      <x:c r="M50" s="44"/>
+      <x:c r="H50" s="58"/>
+      <x:c r="I50" s="58"/>
+      <x:c r="J50" s="57"/>
+      <x:c r="K50" s="57"/>
+      <x:c r="L50" s="57"/>
+      <x:c r="M50" s="57"/>
     </x:row>
     <x:row r="51" ht="26" customHeight="1">
-      <x:c r="A51" s="46" t="str">
+      <x:c r="A51" s="56" t="str">
         <x:v>B25</x:v>
       </x:c>
-      <x:c r="B51" s="44" t="str">
+      <x:c r="B51" s="57" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C51" s="44" t="str">
+      <x:c r="C51" s="57" t="str">
         <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
       </x:c>
-      <x:c r="D51" s="44" t="str">
+      <x:c r="D51" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E51" s="44" t="str">
+      <x:c r="E51" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F51" s="44" t="str">
+      <x:c r="F51" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G51" s="44" t="str">
+      <x:c r="G51" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H51" s="45"/>
-      <x:c r="I51" s="45"/>
-      <x:c r="J51" s="44"/>
-      <x:c r="K51" s="44"/>
-      <x:c r="L51" s="44"/>
-      <x:c r="M51" s="44"/>
+      <x:c r="H51" s="58"/>
+      <x:c r="I51" s="58"/>
+      <x:c r="J51" s="57"/>
+      <x:c r="K51" s="57"/>
+      <x:c r="L51" s="57"/>
+      <x:c r="M51" s="57"/>
     </x:row>
     <x:row r="52" ht="26" customHeight="1">
-      <x:c r="A52" s="46" t="str">
+      <x:c r="A52" s="56" t="str">
         <x:v>B26</x:v>
       </x:c>
-      <x:c r="B52" s="44" t="str">
+      <x:c r="B52" s="57" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C52" s="44" t="str">
+      <x:c r="C52" s="57" t="str">
         <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
       </x:c>
-      <x:c r="D52" s="44" t="str">
+      <x:c r="D52" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E52" s="44" t="str">
+      <x:c r="E52" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F52" s="44" t="str">
+      <x:c r="F52" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G52" s="44" t="str">
+      <x:c r="G52" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H52" s="45"/>
-      <x:c r="I52" s="45"/>
-      <x:c r="J52" s="44"/>
-      <x:c r="K52" s="44"/>
-      <x:c r="L52" s="44"/>
-      <x:c r="M52" s="44"/>
+      <x:c r="H52" s="58"/>
+      <x:c r="I52" s="58"/>
+      <x:c r="J52" s="57"/>
+      <x:c r="K52" s="57"/>
+      <x:c r="L52" s="57"/>
+      <x:c r="M52" s="57"/>
     </x:row>
     <x:row r="53" ht="26" customHeight="1">
-      <x:c r="A53" s="46" t="str">
+      <x:c r="A53" s="56" t="str">
         <x:v>B27</x:v>
       </x:c>
-      <x:c r="B53" s="44" t="str">
+      <x:c r="B53" s="57" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C53" s="44" t="str">
+      <x:c r="C53" s="57" t="str">
         <x:v>Admin user management, audit log and sensitive action authorization</x:v>
       </x:c>
-      <x:c r="D53" s="44" t="str">
+      <x:c r="D53" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E53" s="44" t="str">
+      <x:c r="E53" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F53" s="44" t="str">
+      <x:c r="F53" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G53" s="44" t="str">
+      <x:c r="G53" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H53" s="45"/>
-      <x:c r="I53" s="45"/>
-      <x:c r="J53" s="44"/>
-      <x:c r="K53" s="44"/>
-      <x:c r="L53" s="44"/>
-      <x:c r="M53" s="44"/>
+      <x:c r="H53" s="58"/>
+      <x:c r="I53" s="58"/>
+      <x:c r="J53" s="57"/>
+      <x:c r="K53" s="57"/>
+      <x:c r="L53" s="57"/>
+      <x:c r="M53" s="57"/>
     </x:row>
     <x:row r="54" ht="26" customHeight="1">
-      <x:c r="A54" s="46" t="str">
+      <x:c r="A54" s="56" t="str">
         <x:v>B30</x:v>
       </x:c>
-      <x:c r="B54" s="44" t="str">
+      <x:c r="B54" s="57" t="str">
         <x:v>Step 12 · Deploy</x:v>
       </x:c>
-      <x:c r="C54" s="44" t="str">
+      <x:c r="C54" s="57" t="str">
         <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
       </x:c>
-      <x:c r="D54" s="44" t="str">
+      <x:c r="D54" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E54" s="44" t="str">
+      <x:c r="E54" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F54" s="44" t="str">
+      <x:c r="F54" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G54" s="44" t="str">
+      <x:c r="G54" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H54" s="45"/>
-      <x:c r="I54" s="45"/>
-      <x:c r="J54" s="44"/>
-      <x:c r="K54" s="44"/>
-      <x:c r="L54" s="44"/>
-      <x:c r="M54" s="44"/>
+      <x:c r="H54" s="58"/>
+      <x:c r="I54" s="58"/>
+      <x:c r="J54" s="57"/>
+      <x:c r="K54" s="57"/>
+      <x:c r="L54" s="57"/>
+      <x:c r="M54" s="57"/>
     </x:row>
     <x:row r="55" ht="26" customHeight="1">
-      <x:c r="A55" s="46" t="str">
+      <x:c r="A55" s="56" t="str">
         <x:v>B31</x:v>
       </x:c>
-      <x:c r="B55" s="44" t="str">
+      <x:c r="B55" s="57" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C55" s="44" t="str">
+      <x:c r="C55" s="57" t="str">
         <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
       </x:c>
-      <x:c r="D55" s="44" t="str">
+      <x:c r="D55" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E55" s="44" t="str">
+      <x:c r="E55" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F55" s="44" t="str">
+      <x:c r="F55" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G55" s="44" t="str">
+      <x:c r="G55" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H55" s="45"/>
-      <x:c r="I55" s="45"/>
-      <x:c r="J55" s="44"/>
-      <x:c r="K55" s="44"/>
-      <x:c r="L55" s="44"/>
-      <x:c r="M55" s="44"/>
+      <x:c r="H55" s="58"/>
+      <x:c r="I55" s="58"/>
+      <x:c r="J55" s="57"/>
+      <x:c r="K55" s="57"/>
+      <x:c r="L55" s="57"/>
+      <x:c r="M55" s="57"/>
     </x:row>
     <x:row r="56" ht="26" customHeight="1">
-      <x:c r="A56" s="46" t="str">
+      <x:c r="A56" s="56" t="str">
         <x:v>B32</x:v>
       </x:c>
-      <x:c r="B56" s="44" t="str">
+      <x:c r="B56" s="57" t="str">
         <x:v>Step 12 · Security</x:v>
       </x:c>
-      <x:c r="C56" s="44" t="str">
+      <x:c r="C56" s="57" t="str">
         <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
       </x:c>
-      <x:c r="D56" s="44" t="str">
+      <x:c r="D56" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E56" s="44" t="str">
+      <x:c r="E56" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F56" s="44" t="str">
+      <x:c r="F56" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G56" s="44" t="str">
+      <x:c r="G56" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H56" s="45"/>
-      <x:c r="I56" s="45"/>
-      <x:c r="J56" s="44"/>
-      <x:c r="K56" s="44"/>
-      <x:c r="L56" s="44"/>
-      <x:c r="M56" s="44"/>
+      <x:c r="H56" s="58"/>
+      <x:c r="I56" s="58"/>
+      <x:c r="J56" s="57"/>
+      <x:c r="K56" s="57"/>
+      <x:c r="L56" s="57"/>
+      <x:c r="M56" s="57"/>
     </x:row>
     <x:row r="57" ht="26" customHeight="1">
-      <x:c r="A57" s="46" t="str">
+      <x:c r="A57" s="56" t="str">
         <x:v>B33</x:v>
       </x:c>
-      <x:c r="B57" s="44" t="str">
+      <x:c r="B57" s="57" t="str">
         <x:v>Step 7 · Owners</x:v>
       </x:c>
-      <x:c r="C57" s="44" t="str">
+      <x:c r="C57" s="57" t="str">
         <x:v>Home-value and service enquiry data handling</x:v>
       </x:c>
-      <x:c r="D57" s="44" t="str">
+      <x:c r="D57" s="57" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E57" s="44" t="str">
+      <x:c r="E57" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F57" s="44" t="str">
+      <x:c r="F57" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G57" s="44" t="str">
+      <x:c r="G57" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H57" s="45"/>
-      <x:c r="I57" s="45"/>
-      <x:c r="J57" s="44"/>
-      <x:c r="K57" s="44"/>
-      <x:c r="L57" s="44"/>
-      <x:c r="M57" s="44"/>
+      <x:c r="H57" s="58"/>
+      <x:c r="I57" s="58"/>
+      <x:c r="J57" s="57"/>
+      <x:c r="K57" s="57"/>
+      <x:c r="L57" s="57"/>
+      <x:c r="M57" s="57"/>
     </x:row>
     <x:row r="58" ht="26" customHeight="1">
-      <x:c r="A58" s="46" t="str">
+      <x:c r="A58" s="56" t="str">
         <x:v>E01</x:v>
       </x:c>
-      <x:c r="B58" s="44" t="str">
+      <x:c r="B58" s="57" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C58" s="44" t="str">
+      <x:c r="C58" s="57" t="str">
         <x:v>Enquiry notification with retryable queue/outbox</x:v>
       </x:c>
-      <x:c r="D58" s="44" t="str">
+      <x:c r="D58" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E58" s="44" t="str">
+      <x:c r="E58" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F58" s="44" t="str">
+      <x:c r="F58" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G58" s="44" t="str">
+      <x:c r="G58" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H58" s="45"/>
-      <x:c r="I58" s="45"/>
-      <x:c r="J58" s="44"/>
-      <x:c r="K58" s="44"/>
-      <x:c r="L58" s="44"/>
-      <x:c r="M58" s="44"/>
+      <x:c r="H58" s="58"/>
+      <x:c r="I58" s="58"/>
+      <x:c r="J58" s="57"/>
+      <x:c r="K58" s="57"/>
+      <x:c r="L58" s="57"/>
+      <x:c r="M58" s="57"/>
     </x:row>
     <x:row r="59" ht="26" customHeight="1">
-      <x:c r="A59" s="46" t="str">
+      <x:c r="A59" s="56" t="str">
         <x:v>E02</x:v>
       </x:c>
-      <x:c r="B59" s="44" t="str">
+      <x:c r="B59" s="57" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C59" s="44" t="str">
+      <x:c r="C59" s="57" t="str">
         <x:v>Thai and English buyer enquiry acknowledgments</x:v>
       </x:c>
-      <x:c r="D59" s="44" t="str">
+      <x:c r="D59" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E59" s="44" t="str">
+      <x:c r="E59" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F59" s="44" t="str">
+      <x:c r="F59" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G59" s="44" t="str">
+      <x:c r="G59" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H59" s="45"/>
-      <x:c r="I59" s="45"/>
-      <x:c r="J59" s="44"/>
-      <x:c r="K59" s="44"/>
-      <x:c r="L59" s="44"/>
-      <x:c r="M59" s="44"/>
+      <x:c r="H59" s="58"/>
+      <x:c r="I59" s="58"/>
+      <x:c r="J59" s="57"/>
+      <x:c r="K59" s="57"/>
+      <x:c r="L59" s="57"/>
+      <x:c r="M59" s="57"/>
     </x:row>
     <x:row r="60" ht="26" customHeight="1">
-      <x:c r="A60" s="46" t="str">
+      <x:c r="A60" s="56" t="str">
         <x:v>E03</x:v>
       </x:c>
-      <x:c r="B60" s="44" t="str">
+      <x:c r="B60" s="57" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C60" s="44" t="str">
+      <x:c r="C60" s="57" t="str">
         <x:v>Project brochure/price list email delivery</x:v>
       </x:c>
-      <x:c r="D60" s="44" t="str">
+      <x:c r="D60" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E60" s="44" t="str">
+      <x:c r="E60" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F60" s="44" t="str">
+      <x:c r="F60" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G60" s="44" t="str">
+      <x:c r="G60" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H60" s="45"/>
-      <x:c r="I60" s="45"/>
-      <x:c r="J60" s="44"/>
-      <x:c r="K60" s="44"/>
-      <x:c r="L60" s="44"/>
-      <x:c r="M60" s="44"/>
+      <x:c r="H60" s="58"/>
+      <x:c r="I60" s="58"/>
+      <x:c r="J60" s="57"/>
+      <x:c r="K60" s="57"/>
+      <x:c r="L60" s="57"/>
+      <x:c r="M60" s="57"/>
     </x:row>
     <x:row r="61" ht="26" customHeight="1">
-      <x:c r="A61" s="46" t="str">
+      <x:c r="A61" s="56" t="str">
         <x:v>E04</x:v>
       </x:c>
-      <x:c r="B61" s="44" t="str">
+      <x:c r="B61" s="57" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C61" s="44" t="str">
+      <x:c r="C61" s="57" t="str">
         <x:v>Site visit request and confirmation notifications</x:v>
       </x:c>
-      <x:c r="D61" s="44" t="str">
+      <x:c r="D61" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E61" s="44" t="str">
+      <x:c r="E61" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F61" s="44" t="str">
+      <x:c r="F61" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G61" s="44" t="str">
+      <x:c r="G61" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H61" s="45"/>
-      <x:c r="I61" s="45"/>
-      <x:c r="J61" s="44"/>
-      <x:c r="K61" s="44"/>
-      <x:c r="L61" s="44"/>
-      <x:c r="M61" s="44"/>
+      <x:c r="H61" s="58"/>
+      <x:c r="I61" s="58"/>
+      <x:c r="J61" s="57"/>
+      <x:c r="K61" s="57"/>
+      <x:c r="L61" s="57"/>
+      <x:c r="M61" s="57"/>
     </x:row>
     <x:row r="62" ht="26" customHeight="1">
-      <x:c r="A62" s="46" t="str">
+      <x:c r="A62" s="56" t="str">
         <x:v>E05</x:v>
       </x:c>
-      <x:c r="B62" s="44" t="str">
+      <x:c r="B62" s="57" t="str">
         <x:v>Step 9 · Alerts</x:v>
       </x:c>
-      <x:c r="C62" s="44" t="str">
+      <x:c r="C62" s="57" t="str">
         <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
       </x:c>
-      <x:c r="D62" s="44" t="str">
+      <x:c r="D62" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E62" s="44" t="str">
+      <x:c r="E62" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F62" s="44" t="str">
+      <x:c r="F62" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G62" s="44" t="str">
+      <x:c r="G62" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H62" s="45"/>
-      <x:c r="I62" s="45"/>
-      <x:c r="J62" s="44"/>
-      <x:c r="K62" s="44"/>
-      <x:c r="L62" s="44"/>
-      <x:c r="M62" s="44"/>
+      <x:c r="H62" s="58"/>
+      <x:c r="I62" s="58"/>
+      <x:c r="J62" s="57"/>
+      <x:c r="K62" s="57"/>
+      <x:c r="L62" s="57"/>
+      <x:c r="M62" s="57"/>
     </x:row>
     <x:row r="63" ht="26" customHeight="1">
-      <x:c r="A63" s="46" t="str">
+      <x:c r="A63" s="56" t="str">
         <x:v>E06</x:v>
       </x:c>
-      <x:c r="B63" s="44" t="str">
+      <x:c r="B63" s="57" t="str">
         <x:v>Step 10B · Email</x:v>
       </x:c>
-      <x:c r="C63" s="44" t="str">
+      <x:c r="C63" s="57" t="str">
         <x:v>Account verification and recovery messages if email auth approved</x:v>
       </x:c>
-      <x:c r="D63" s="44" t="str">
+      <x:c r="D63" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E63" s="44" t="str">
+      <x:c r="E63" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F63" s="44" t="str">
+      <x:c r="F63" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G63" s="44" t="str">
+      <x:c r="G63" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H63" s="45"/>
-      <x:c r="I63" s="45"/>
-      <x:c r="J63" s="44"/>
-      <x:c r="K63" s="44"/>
-      <x:c r="L63" s="44"/>
-      <x:c r="M63" s="44"/>
+      <x:c r="H63" s="58"/>
+      <x:c r="I63" s="58"/>
+      <x:c r="J63" s="57"/>
+      <x:c r="K63" s="57"/>
+      <x:c r="L63" s="57"/>
+      <x:c r="M63" s="57"/>
     </x:row>
     <x:row r="64" ht="26" customHeight="1">
-      <x:c r="A64" s="46" t="str">
+      <x:c r="A64" s="56" t="str">
         <x:v>E07</x:v>
       </x:c>
-      <x:c r="B64" s="44" t="str">
+      <x:c r="B64" s="57" t="str">
         <x:v>Step 11B · Email</x:v>
       </x:c>
-      <x:c r="C64" s="44" t="str">
+      <x:c r="C64" s="57" t="str">
         <x:v>Agent notification/routing administration</x:v>
       </x:c>
-      <x:c r="D64" s="44" t="str">
+      <x:c r="D64" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E64" s="44" t="str">
+      <x:c r="E64" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F64" s="44" t="str">
+      <x:c r="F64" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G64" s="44" t="str">
+      <x:c r="G64" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H64" s="45"/>
-      <x:c r="I64" s="45"/>
-      <x:c r="J64" s="44"/>
-      <x:c r="K64" s="44"/>
-      <x:c r="L64" s="44"/>
-      <x:c r="M64" s="44"/>
+      <x:c r="H64" s="58"/>
+      <x:c r="I64" s="58"/>
+      <x:c r="J64" s="57"/>
+      <x:c r="K64" s="57"/>
+      <x:c r="L64" s="57"/>
+      <x:c r="M64" s="57"/>
     </x:row>
     <x:row r="65" ht="26" customHeight="1">
-      <x:c r="A65" s="46" t="str">
+      <x:c r="A65" s="56" t="str">
         <x:v>E08</x:v>
       </x:c>
-      <x:c r="B65" s="44" t="str">
+      <x:c r="B65" s="57" t="str">
         <x:v>Step 7 · Email</x:v>
       </x:c>
-      <x:c r="C65" s="44" t="str">
+      <x:c r="C65" s="57" t="str">
         <x:v>Home valuation and service enquiry replies</x:v>
       </x:c>
-      <x:c r="D65" s="44" t="str">
+      <x:c r="D65" s="57" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E65" s="44" t="str">
+      <x:c r="E65" s="57" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F65" s="44" t="str">
+      <x:c r="F65" s="57" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G65" s="44" t="str">
+      <x:c r="G65" s="57" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H65" s="45"/>
-      <x:c r="I65" s="45"/>
-      <x:c r="J65" s="44"/>
-      <x:c r="K65" s="44"/>
-      <x:c r="L65" s="44"/>
-      <x:c r="M65" s="44"/>
+      <x:c r="H65" s="58"/>
+      <x:c r="I65" s="58"/>
+      <x:c r="J65" s="57"/>
+      <x:c r="K65" s="57"/>
+      <x:c r="L65" s="57"/>
+      <x:c r="M65" s="57"/>
     </x:row>
     <x:row r="66" ht="26" customHeight="1">
       <x:c r="A66" s="46"/>
@@ -48738,15 +49023,15 @@
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E6:E74">
-    <x:cfRule type="expression" dxfId="12" priority="1">
-      <x:formula>E6="Pending"</x:formula>
+  <x:conditionalFormatting sqref="A6:M500">
+    <x:cfRule type="expression" dxfId="30" priority="1">
+      <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="13" priority="2">
-      <x:formula>E6="Done"</x:formula>
+    <x:cfRule type="expression" dxfId="31" priority="2">
+      <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="14" priority="3">
-      <x:formula>E6="Not started"</x:formula>
+    <x:cfRule type="expression" dxfId="32" priority="3">
+      <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
@@ -48762,7 +49047,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22c0e574be984312"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4207507c36da4d49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Mstar-Property-Task-Tracker.xlsx
+++ b/Mstar-Property-Task-Tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R27626f1841ef4132"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R1b22002ff2cb479e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R0989bca6f4704ce0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="Rbffd9243c811433b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="Re71fca11b8984ef5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="R19c5979771d742c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R7b1e58856b4f4dde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R994730cfbb2f457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R3390228af212415c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="Ra6e38bd544964f31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R557ca3424aab4f96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="R2cd2d7eda59d4a25"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -430,7 +430,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -440,7 +440,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -450,7 +450,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFF6666"/>
         </x:patternFill>
       </x:fill>
@@ -460,7 +460,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -470,7 +470,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -480,7 +480,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFF6666"/>
         </x:patternFill>
       </x:fill>
@@ -490,7 +490,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -500,7 +500,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -510,7 +510,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFF6666"/>
         </x:patternFill>
       </x:fill>
@@ -520,7 +520,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -530,7 +530,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -540,7 +540,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFF6666"/>
         </x:patternFill>
       </x:fill>
@@ -550,7 +550,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -560,7 +560,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -570,7 +570,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFF6666"/>
         </x:patternFill>
       </x:fill>
@@ -580,7 +580,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -590,7 +590,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -600,7 +600,7 @@
         <x:color rgb="FF000000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFF6666"/>
         </x:patternFill>
       </x:fill>
@@ -9164,7 +9164,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ee3b0fec5264935"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7e326bc49d5487a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9557,7 +9557,8 @@
 2026-10-09 foundation: Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.
 2026-10-09 Step 2: Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
-2026-10-09 tracker formatting: workbook recreated with yellow Pending, light green Done and red Not started rows and status tabs. All 81 permanent IDs and prior task history preserved. Step 3 is authorized but implementation has not begun; owner requested the Excel first.</x:v>
+2026-10-09 tracker formatting: workbook recreated with yellow Pending, light green Done and red Not started rows and status tabs. All 81 permanent IDs and prior task history preserved. Step 3 is authorized but implementation has not begun; owner requested the Excel first.
+2026-10-09 Claude handoff: owner requested CLAUDE.md to share the current project context with Claude. Documented sources, Git/live paths, implemented shell/Step 2, unimplemented authorized Step 3, open decisions, safety, tests, servers and completion gates. Documentation/link checks and workbook ID/history/colour checks pass. No application change or new runtime test is claimed. R01 remains Pending for existing Step 0 blockers; Git/live synchronization and push are verified during finalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
@@ -17228,7 +17229,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03129b46c54d4819"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2317a333e2f4812"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24913,7 +24914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1eeb83cef3334d68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R585041451a67453f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32622,7 +32623,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R495b54da53904d6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfeedefc58826454b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33161,7 +33162,8 @@
 2026-10-09 foundation: Preparation and foundation implemented; docs/tracker/source mirror updated. Build passes; 12/16 browser/API tests passed before owner-requested closure. Four preference/search flows need retesting after fixes; PostgreSQL is unconfigured; port 3000 is closed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.
 2026-10-09 Step 2: Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
-2026-10-09 tracker formatting: workbook recreated with yellow Pending, light green Done and red Not started rows and status tabs. All 81 permanent IDs and prior task history preserved. Step 3 is authorized but implementation has not begun; owner requested the Excel first.</x:v>
+2026-10-09 tracker formatting: workbook recreated with yellow Pending, light green Done and red Not started rows and status tabs. All 81 permanent IDs and prior task history preserved. Step 3 is authorized but implementation has not begun; owner requested the Excel first.
+2026-10-09 Claude handoff: owner requested CLAUDE.md to share the current project context with Claude. Documented sources, Git/live paths, implemented shell/Step 2, unimplemented authorized Step 3, open decisions, safety, tests, servers and completion gates. Documentation/link checks and workbook ID/history/colour checks pass. No application change or new runtime test is claimed. R01 remains Pending for existing Step 0 blockers; Git/live synchronization and push are verified during finalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="310" customHeight="1">
@@ -40595,7 +40597,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabe72850259a4b3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re737f28ca1634620"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49047,7 +49049,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4207507c36da4d49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67d3535895ac4ce3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Mstar-Property-Task-Tracker.xlsx
+++ b/Mstar-Property-Task-Tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R7b1e58856b4f4dde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R994730cfbb2f457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R3390228af212415c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="Ra6e38bd544964f31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R557ca3424aab4f96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="R2cd2d7eda59d4a25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R866ed8a80a8e4152"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R179e190ad4154f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R3c72ac5ee7a54cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="R89555a801afa41bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R59978eb8e3f8416b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="Rfcb54769f3744b94"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -118,6 +118,21 @@
         <x:fgColor rgb="FFC6EFCE"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFF6666"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC6EFCE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -126,7 +141,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="63">
+  <x:cellXfs count="73">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -270,11 +285,41 @@
     <x:xf numFmtId="200" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="33">
+  <x:dxfs count="51">
     <x:dxf>
       <x:font>
         <x:color rgb="FF92400E"/>
@@ -605,12 +650,192 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="34" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -631,7 +856,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="35" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -652,7 +877,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="36" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -673,7 +898,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="MstarDoneTasks" displayName="MstarDoneTasks" ref="A5:M10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="37" name="MstarDoneTasks" displayName="MstarDoneTasks" ref="A5:M20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -694,7 +919,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="38" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -715,7 +940,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="33" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M65" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="39" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M56" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -961,7 +1186,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
+        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -976,14 +1201,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -1002,7 +1227,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -1047,43 +1272,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="50" t="str">
+      <x:c r="A6" s="63" t="str">
         <x:v>F02</x:v>
       </x:c>
-      <x:c r="B6" s="51" t="str">
+      <x:c r="B6" s="64" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="51" t="str">
+      <x:c r="C6" s="64" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent</x:v>
       </x:c>
-      <x:c r="D6" s="51" t="str">
+      <x:c r="D6" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="51" t="str">
+      <x:c r="E6" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="51" t="str">
+      <x:c r="F6" s="64" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G6" s="51" t="str">
+      <x:c r="G6" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H6" s="52" t="d">
+      <x:c r="H6" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="52" t="d">
+      <x:c r="I6" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="51" t="str">
+      <x:c r="J6" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="51" t="str">
+      <x:c r="K6" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="51" t="str">
+      <x:c r="L6" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="51" t="str">
+      <x:c r="M6" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
 2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.
 2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.
@@ -1092,144 +1317,144 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="250" customHeight="1">
-      <x:c r="A7" s="50" t="str">
+      <x:c r="A7" s="63" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B7" s="51" t="str">
+      <x:c r="B7" s="64" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C7" s="51" t="str">
+      <x:c r="C7" s="64" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D7" s="51" t="str">
+      <x:c r="D7" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="51" t="str">
+      <x:c r="E7" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="51" t="str">
+      <x:c r="F7" s="64" t="str">
         <x:v>Approved temporary crest extracted and implemented. Owner will provide final header logo later.</x:v>
       </x:c>
-      <x:c r="G7" s="51" t="str">
+      <x:c r="G7" s="64" t="str">
         <x:v>Owner: supply final asset/version later; Codex: replace only approved logo.</x:v>
       </x:c>
-      <x:c r="H7" s="52" t="d">
+      <x:c r="H7" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="52" t="d">
+      <x:c r="I7" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="51" t="str">
+      <x:c r="J7" s="64" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K7" s="51" t="str">
+      <x:c r="K7" s="64" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L7" s="51" t="str">
+      <x:c r="L7" s="64" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="51" t="str">
+      <x:c r="M7" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
 2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.
 2026-10-09 foundation: Approved temporary crest extracted and implemented. Owner will provide final header logo later. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="50" t="str">
+      <x:c r="A8" s="63" t="str">
         <x:v>F32</x:v>
       </x:c>
-      <x:c r="B8" s="51" t="str">
+      <x:c r="B8" s="64" t="str">
         <x:v>Step 10A · Wireframe</x:v>
       </x:c>
-      <x:c r="C8" s="51" t="str">
+      <x:c r="C8" s="64" t="str">
         <x:v>Owner-approved login/register/account wireframe before coding</x:v>
       </x:c>
-      <x:c r="D8" s="51" t="str">
+      <x:c r="D8" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="51" t="str">
+      <x:c r="E8" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="51" t="str">
+      <x:c r="F8" s="64" t="str">
         <x:v>Admin/account screens are not part of approved V3 visuals</x:v>
       </x:c>
-      <x:c r="G8" s="51" t="str">
+      <x:c r="G8" s="64" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H8" s="52"/>
-      <x:c r="I8" s="52"/>
-      <x:c r="J8" s="51"/>
-      <x:c r="K8" s="51"/>
-      <x:c r="L8" s="51"/>
-      <x:c r="M8" s="51"/>
+      <x:c r="H8" s="65"/>
+      <x:c r="I8" s="65"/>
+      <x:c r="J8" s="64"/>
+      <x:c r="K8" s="64"/>
+      <x:c r="L8" s="64"/>
+      <x:c r="M8" s="64"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="50" t="str">
+      <x:c r="A9" s="63" t="str">
         <x:v>F34</x:v>
       </x:c>
-      <x:c r="B9" s="51" t="str">
+      <x:c r="B9" s="64" t="str">
         <x:v>Step 11A · Wireframe</x:v>
       </x:c>
-      <x:c r="C9" s="51" t="str">
+      <x:c r="C9" s="64" t="str">
         <x:v>Owner-approved responsive admin dashboard wireframe</x:v>
       </x:c>
-      <x:c r="D9" s="51" t="str">
+      <x:c r="D9" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="51" t="str">
+      <x:c r="E9" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="51" t="str">
+      <x:c r="F9" s="64" t="str">
         <x:v>Admin UI not included in V3; design approval required</x:v>
       </x:c>
-      <x:c r="G9" s="51" t="str">
+      <x:c r="G9" s="64" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H9" s="52"/>
-      <x:c r="I9" s="52"/>
-      <x:c r="J9" s="51"/>
-      <x:c r="K9" s="51"/>
-      <x:c r="L9" s="51"/>
-      <x:c r="M9" s="51"/>
+      <x:c r="H9" s="65"/>
+      <x:c r="I9" s="65"/>
+      <x:c r="J9" s="64"/>
+      <x:c r="K9" s="64"/>
+      <x:c r="L9" s="64"/>
+      <x:c r="M9" s="64"/>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="50" t="str">
+      <x:c r="A10" s="63" t="str">
         <x:v>F01</x:v>
       </x:c>
-      <x:c r="B10" s="51" t="str">
+      <x:c r="B10" s="64" t="str">
         <x:v>Step 1 · Design</x:v>
       </x:c>
-      <x:c r="C10" s="51" t="str">
+      <x:c r="C10" s="64" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives</x:v>
       </x:c>
-      <x:c r="D10" s="51" t="str">
+      <x:c r="D10" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E10" s="51" t="str">
+      <x:c r="E10" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="51" t="str">
+      <x:c r="F10" s="64" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G10" s="51" t="str">
+      <x:c r="G10" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H10" s="52" t="d">
+      <x:c r="H10" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="52" t="d">
+      <x:c r="I10" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="51" t="str">
+      <x:c r="J10" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="51" t="str">
+      <x:c r="K10" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="51" t="str">
+      <x:c r="L10" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="51" t="str">
+      <x:c r="M10" s="64" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1237,43 +1462,43 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="310" customHeight="1">
-      <x:c r="A11" s="50" t="str">
+      <x:c r="A11" s="63" t="str">
         <x:v>F04</x:v>
       </x:c>
-      <x:c r="B11" s="51" t="str">
+      <x:c r="B11" s="64" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C11" s="51" t="str">
+      <x:c r="C11" s="64" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in</x:v>
       </x:c>
-      <x:c r="D11" s="51" t="str">
+      <x:c r="D11" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E11" s="51" t="str">
+      <x:c r="E11" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="51" t="str">
+      <x:c r="F11" s="64" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G11" s="51" t="str">
+      <x:c r="G11" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H11" s="52" t="d">
+      <x:c r="H11" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I11" s="52" t="d">
+      <x:c r="I11" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="51" t="str">
+      <x:c r="J11" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K11" s="51" t="str">
+      <x:c r="K11" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L11" s="51" t="str">
+      <x:c r="L11" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M11" s="51" t="str">
+      <x:c r="M11" s="64" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1281,43 +1506,43 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="310" customHeight="1">
-      <x:c r="A12" s="50" t="str">
+      <x:c r="A12" s="63" t="str">
         <x:v>F05</x:v>
       </x:c>
-      <x:c r="B12" s="51" t="str">
+      <x:c r="B12" s="64" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C12" s="51" t="str">
+      <x:c r="C12" s="64" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints</x:v>
       </x:c>
-      <x:c r="D12" s="51" t="str">
+      <x:c r="D12" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E12" s="51" t="str">
+      <x:c r="E12" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="51" t="str">
+      <x:c r="F12" s="64" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G12" s="51" t="str">
+      <x:c r="G12" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H12" s="52" t="d">
+      <x:c r="H12" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="52" t="d">
+      <x:c r="I12" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="51" t="str">
+      <x:c r="J12" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K12" s="51" t="str">
+      <x:c r="K12" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L12" s="51" t="str">
+      <x:c r="L12" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="51" t="str">
+      <x:c r="M12" s="64" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1325,43 +1550,43 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="310" customHeight="1">
-      <x:c r="A13" s="50" t="str">
+      <x:c r="A13" s="63" t="str">
         <x:v>F06</x:v>
       </x:c>
-      <x:c r="B13" s="51" t="str">
+      <x:c r="B13" s="64" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C13" s="51" t="str">
+      <x:c r="C13" s="64" t="str">
         <x:v>Light footer, company links, contact and PDPA link</x:v>
       </x:c>
-      <x:c r="D13" s="51" t="str">
+      <x:c r="D13" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E13" s="51" t="str">
+      <x:c r="E13" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F13" s="51" t="str">
+      <x:c r="F13" s="64" t="str">
         <x:v>Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G13" s="51" t="str">
+      <x:c r="G13" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H13" s="52" t="d">
+      <x:c r="H13" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I13" s="52" t="d">
+      <x:c r="I13" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J13" s="51" t="str">
+      <x:c r="J13" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K13" s="51" t="str">
+      <x:c r="K13" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L13" s="51" t="str">
+      <x:c r="L13" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M13" s="51" t="str">
+      <x:c r="M13" s="64" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1369,43 +1594,43 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="310" customHeight="1">
-      <x:c r="A14" s="50" t="str">
+      <x:c r="A14" s="63" t="str">
         <x:v>F07</x:v>
       </x:c>
-      <x:c r="B14" s="51" t="str">
+      <x:c r="B14" s="64" t="str">
         <x:v>Step 1 · i18n</x:v>
       </x:c>
-      <x:c r="C14" s="51" t="str">
+      <x:c r="C14" s="64" t="str">
         <x:v>Thai/English routes, language switch and localized formatting</x:v>
       </x:c>
-      <x:c r="D14" s="51" t="str">
+      <x:c r="D14" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E14" s="51" t="str">
+      <x:c r="E14" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="51" t="str">
+      <x:c r="F14" s="64" t="str">
         <x:v>Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G14" s="51" t="str">
+      <x:c r="G14" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H14" s="52" t="d">
+      <x:c r="H14" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I14" s="52" t="d">
+      <x:c r="I14" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="51" t="str">
+      <x:c r="J14" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K14" s="51" t="str">
+      <x:c r="K14" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L14" s="51" t="str">
+      <x:c r="L14" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M14" s="51" t="str">
+      <x:c r="M14" s="64" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1413,727 +1638,702 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="250" customHeight="1">
-      <x:c r="A15" s="56" t="str">
-        <x:v>F08</x:v>
-      </x:c>
-      <x:c r="B15" s="57" t="str">
-        <x:v>Step 3 · Cards</x:v>
-      </x:c>
-      <x:c r="C15" s="57" t="str">
-        <x:v>Realtor-style 3:2 listing cards, photo controls, bottom-right save heart, facts/address and Contact agent dialog trigger</x:v>
-      </x:c>
-      <x:c r="D15" s="57" t="str">
+      <x:c r="A15" s="66" t="str">
+        <x:v>F14</x:v>
+      </x:c>
+      <x:c r="B15" s="67" t="str">
+        <x:v>Step 4 · Map</x:v>
+      </x:c>
+      <x:c r="C15" s="67" t="str">
+        <x:v>Desktop listing/map split and hover/focus pin synchronization</x:v>
+      </x:c>
+      <x:c r="D15" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="57" t="str">
+      <x:c r="E15" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="57" t="str">
-        <x:v>V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
-      </x:c>
-      <x:c r="G15" s="57" t="str">
-        <x:v>Codex: build revised card only under Step 3 authorization, after the real database step.</x:v>
-      </x:c>
-      <x:c r="H15" s="58"/>
-      <x:c r="I15" s="58" t="d">
+      <x:c r="F15" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G15" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H15" s="68"/>
+      <x:c r="I15" s="68"/>
+      <x:c r="J15" s="67"/>
+      <x:c r="K15" s="67"/>
+      <x:c r="L15" s="67"/>
+      <x:c r="M15" s="67"/>
+    </x:row>
+    <x:row r="16" ht="26" customHeight="1">
+      <x:c r="A16" s="66" t="str">
+        <x:v>F15</x:v>
+      </x:c>
+      <x:c r="B16" s="67" t="str">
+        <x:v>Step 4 · Map</x:v>
+      </x:c>
+      <x:c r="C16" s="67" t="str">
+        <x:v>Phone full-screen Map/List toggle</x:v>
+      </x:c>
+      <x:c r="D16" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E16" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F16" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G16" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H16" s="68"/>
+      <x:c r="I16" s="68"/>
+      <x:c r="J16" s="67"/>
+      <x:c r="K16" s="67"/>
+      <x:c r="L16" s="67"/>
+      <x:c r="M16" s="67"/>
+    </x:row>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="66" t="str">
+        <x:v>F16</x:v>
+      </x:c>
+      <x:c r="B17" s="67" t="str">
+        <x:v>Step 5 · Property</x:v>
+      </x:c>
+      <x:c r="C17" s="67" t="str">
+        <x:v>Property detail photo grid and full-screen gallery</x:v>
+      </x:c>
+      <x:c r="D17" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E17" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F17" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G17" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H17" s="68"/>
+      <x:c r="I17" s="68"/>
+      <x:c r="J17" s="67"/>
+      <x:c r="K17" s="67"/>
+      <x:c r="L17" s="67"/>
+      <x:c r="M17" s="67"/>
+    </x:row>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="66" t="str">
+        <x:v>F17</x:v>
+      </x:c>
+      <x:c r="B18" s="67" t="str">
+        <x:v>Step 5 · Property</x:v>
+      </x:c>
+      <x:c r="C18" s="67" t="str">
+        <x:v>Title, pricing, type-specific facts, long description and sticky tabs</x:v>
+      </x:c>
+      <x:c r="D18" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E18" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F18" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G18" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H18" s="68"/>
+      <x:c r="I18" s="68"/>
+      <x:c r="J18" s="67"/>
+      <x:c r="K18" s="67"/>
+      <x:c r="L18" s="67"/>
+      <x:c r="M18" s="67"/>
+    </x:row>
+    <x:row r="19" ht="26" customHeight="1">
+      <x:c r="A19" s="66" t="str">
+        <x:v>F18</x:v>
+      </x:c>
+      <x:c r="B19" s="67" t="str">
+        <x:v>Step 5 · Property</x:v>
+      </x:c>
+      <x:c r="C19" s="67" t="str">
+        <x:v>Floorplan/video/360 tabs, verified nearby information and map</x:v>
+      </x:c>
+      <x:c r="D19" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E19" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F19" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G19" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H19" s="68"/>
+      <x:c r="I19" s="68"/>
+      <x:c r="J19" s="67"/>
+      <x:c r="K19" s="67"/>
+      <x:c r="L19" s="67"/>
+      <x:c r="M19" s="67"/>
+    </x:row>
+    <x:row r="20" ht="26" customHeight="1">
+      <x:c r="A20" s="66" t="str">
+        <x:v>F19</x:v>
+      </x:c>
+      <x:c r="B20" s="67" t="str">
+        <x:v>Step 5 · Property</x:v>
+      </x:c>
+      <x:c r="C20" s="67" t="str">
+        <x:v>Mortgage calculator and area comparison when real data exists</x:v>
+      </x:c>
+      <x:c r="D20" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E20" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F20" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G20" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H20" s="68"/>
+      <x:c r="I20" s="68"/>
+      <x:c r="J20" s="67"/>
+      <x:c r="K20" s="67"/>
+      <x:c r="L20" s="67"/>
+      <x:c r="M20" s="67"/>
+    </x:row>
+    <x:row r="21" ht="26" customHeight="1">
+      <x:c r="A21" s="66" t="str">
+        <x:v>F20</x:v>
+      </x:c>
+      <x:c r="B21" s="67" t="str">
+        <x:v>Step 5 · Property</x:v>
+      </x:c>
+      <x:c r="C21" s="67" t="str">
+        <x:v>Same-project units and similar-property cards</x:v>
+      </x:c>
+      <x:c r="D21" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E21" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F21" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G21" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H21" s="68"/>
+      <x:c r="I21" s="68"/>
+      <x:c r="J21" s="67"/>
+      <x:c r="K21" s="67"/>
+      <x:c r="L21" s="67"/>
+      <x:c r="M21" s="67"/>
+    </x:row>
+    <x:row r="22" ht="26" customHeight="1">
+      <x:c r="A22" s="66" t="str">
+        <x:v>F21</x:v>
+      </x:c>
+      <x:c r="B22" s="67" t="str">
+        <x:v>Step 6 · Contact</x:v>
+      </x:c>
+      <x:c r="C22" s="67" t="str">
+        <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
+      </x:c>
+      <x:c r="D22" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E22" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F22" s="67" t="str">
+        <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
+      </x:c>
+      <x:c r="G22" s="67" t="str">
+        <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
+      </x:c>
+      <x:c r="H22" s="68"/>
+      <x:c r="I22" s="68" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J15" s="57" t="str">
+      <x:c r="J22" s="67" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K15" s="57" t="str">
+      <x:c r="K22" s="67" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L15" s="57" t="str">
+      <x:c r="L22" s="67" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M15" s="57" t="str">
-        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 V5 adoption: V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="56" t="str">
-        <x:v>F09</x:v>
-      </x:c>
-      <x:c r="B16" s="57" t="str">
-        <x:v>Step 3 · Results</x:v>
-      </x:c>
-      <x:c r="C16" s="57" t="str">
-        <x:v>Responsive /buy, /rent and /invest results layouts</x:v>
-      </x:c>
-      <x:c r="D16" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E16" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F16" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G16" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H16" s="58"/>
-      <x:c r="I16" s="58"/>
-      <x:c r="J16" s="57"/>
-      <x:c r="K16" s="57"/>
-      <x:c r="L16" s="57"/>
-      <x:c r="M16" s="57"/>
-    </x:row>
-    <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="56" t="str">
-        <x:v>F10</x:v>
-      </x:c>
-      <x:c r="B17" s="57" t="str">
-        <x:v>Step 3 · Filters</x:v>
-      </x:c>
-      <x:c r="C17" s="57" t="str">
-        <x:v>Shared URL filters, active chips, sorting and navigation history</x:v>
-      </x:c>
-      <x:c r="D17" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E17" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F17" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G17" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H17" s="58"/>
-      <x:c r="I17" s="58"/>
-      <x:c r="J17" s="57"/>
-      <x:c r="K17" s="57"/>
-      <x:c r="L17" s="57"/>
-      <x:c r="M17" s="57"/>
-    </x:row>
-    <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="56" t="str">
-        <x:v>F11</x:v>
-      </x:c>
-      <x:c r="B18" s="57" t="str">
-        <x:v>Step 3 · Filters</x:v>
-      </x:c>
-      <x:c r="C18" s="57" t="str">
-        <x:v>Desktop popovers for price, beds, type and advanced filters</x:v>
-      </x:c>
-      <x:c r="D18" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E18" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F18" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G18" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H18" s="58"/>
-      <x:c r="I18" s="58"/>
-      <x:c r="J18" s="57"/>
-      <x:c r="K18" s="57"/>
-      <x:c r="L18" s="57"/>
-      <x:c r="M18" s="57"/>
-    </x:row>
-    <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="56" t="str">
-        <x:v>F12</x:v>
-      </x:c>
-      <x:c r="B19" s="57" t="str">
-        <x:v>Step 3 · Filters</x:v>
-      </x:c>
-      <x:c r="C19" s="57" t="str">
-        <x:v>Phone full-screen filter sheet, Apply and Clear</x:v>
-      </x:c>
-      <x:c r="D19" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E19" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F19" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G19" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H19" s="58"/>
-      <x:c r="I19" s="58"/>
-      <x:c r="J19" s="57"/>
-      <x:c r="K19" s="57"/>
-      <x:c r="L19" s="57"/>
-      <x:c r="M19" s="57"/>
-    </x:row>
-    <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="56" t="str">
-        <x:v>F13</x:v>
-      </x:c>
-      <x:c r="B20" s="57" t="str">
-        <x:v>Step 3 · Search</x:v>
-      </x:c>
-      <x:c r="C20" s="57" t="str">
-        <x:v>Database-derived price histogram and live result count</x:v>
-      </x:c>
-      <x:c r="D20" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E20" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F20" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G20" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H20" s="58"/>
-      <x:c r="I20" s="58"/>
-      <x:c r="J20" s="57"/>
-      <x:c r="K20" s="57"/>
-      <x:c r="L20" s="57"/>
-      <x:c r="M20" s="57"/>
-    </x:row>
-    <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="56" t="str">
-        <x:v>F14</x:v>
-      </x:c>
-      <x:c r="B21" s="57" t="str">
-        <x:v>Step 4 · Map</x:v>
-      </x:c>
-      <x:c r="C21" s="57" t="str">
-        <x:v>Desktop listing/map split and hover/focus pin synchronization</x:v>
-      </x:c>
-      <x:c r="D21" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E21" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F21" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G21" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H21" s="58"/>
-      <x:c r="I21" s="58"/>
-      <x:c r="J21" s="57"/>
-      <x:c r="K21" s="57"/>
-      <x:c r="L21" s="57"/>
-      <x:c r="M21" s="57"/>
-    </x:row>
-    <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="56" t="str">
-        <x:v>F15</x:v>
-      </x:c>
-      <x:c r="B22" s="57" t="str">
-        <x:v>Step 4 · Map</x:v>
-      </x:c>
-      <x:c r="C22" s="57" t="str">
-        <x:v>Phone full-screen Map/List toggle</x:v>
-      </x:c>
-      <x:c r="D22" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E22" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F22" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G22" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H22" s="58"/>
-      <x:c r="I22" s="58"/>
-      <x:c r="J22" s="57"/>
-      <x:c r="K22" s="57"/>
-      <x:c r="L22" s="57"/>
-      <x:c r="M22" s="57"/>
-    </x:row>
-    <x:row r="23" ht="26" customHeight="1">
-      <x:c r="A23" s="56" t="str">
-        <x:v>F16</x:v>
-      </x:c>
-      <x:c r="B23" s="57" t="str">
-        <x:v>Step 5 · Property</x:v>
-      </x:c>
-      <x:c r="C23" s="57" t="str">
-        <x:v>Property detail photo grid and full-screen gallery</x:v>
-      </x:c>
-      <x:c r="D23" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E23" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F23" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G23" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H23" s="58"/>
-      <x:c r="I23" s="58"/>
-      <x:c r="J23" s="57"/>
-      <x:c r="K23" s="57"/>
-      <x:c r="L23" s="57"/>
-      <x:c r="M23" s="57"/>
-    </x:row>
-    <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="56" t="str">
-        <x:v>F17</x:v>
-      </x:c>
-      <x:c r="B24" s="57" t="str">
-        <x:v>Step 5 · Property</x:v>
-      </x:c>
-      <x:c r="C24" s="57" t="str">
-        <x:v>Title, pricing, type-specific facts, long description and sticky tabs</x:v>
-      </x:c>
-      <x:c r="D24" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E24" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F24" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G24" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H24" s="58"/>
-      <x:c r="I24" s="58"/>
-      <x:c r="J24" s="57"/>
-      <x:c r="K24" s="57"/>
-      <x:c r="L24" s="57"/>
-      <x:c r="M24" s="57"/>
-    </x:row>
-    <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="56" t="str">
-        <x:v>F18</x:v>
-      </x:c>
-      <x:c r="B25" s="57" t="str">
-        <x:v>Step 5 · Property</x:v>
-      </x:c>
-      <x:c r="C25" s="57" t="str">
-        <x:v>Floorplan/video/360 tabs, verified nearby information and map</x:v>
-      </x:c>
-      <x:c r="D25" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E25" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F25" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G25" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H25" s="58"/>
-      <x:c r="I25" s="58"/>
-      <x:c r="J25" s="57"/>
-      <x:c r="K25" s="57"/>
-      <x:c r="L25" s="57"/>
-      <x:c r="M25" s="57"/>
-    </x:row>
-    <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="56" t="str">
-        <x:v>F19</x:v>
-      </x:c>
-      <x:c r="B26" s="57" t="str">
-        <x:v>Step 5 · Property</x:v>
-      </x:c>
-      <x:c r="C26" s="57" t="str">
-        <x:v>Mortgage calculator and area comparison when real data exists</x:v>
-      </x:c>
-      <x:c r="D26" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E26" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F26" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G26" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H26" s="58"/>
-      <x:c r="I26" s="58"/>
-      <x:c r="J26" s="57"/>
-      <x:c r="K26" s="57"/>
-      <x:c r="L26" s="57"/>
-      <x:c r="M26" s="57"/>
-    </x:row>
-    <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="56" t="str">
-        <x:v>F20</x:v>
-      </x:c>
-      <x:c r="B27" s="57" t="str">
-        <x:v>Step 5 · Property</x:v>
-      </x:c>
-      <x:c r="C27" s="57" t="str">
-        <x:v>Same-project units and similar-property cards</x:v>
-      </x:c>
-      <x:c r="D27" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E27" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F27" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G27" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H27" s="58"/>
-      <x:c r="I27" s="58"/>
-      <x:c r="J27" s="57"/>
-      <x:c r="K27" s="57"/>
-      <x:c r="L27" s="57"/>
-      <x:c r="M27" s="57"/>
-    </x:row>
-    <x:row r="28" ht="250" customHeight="1">
-      <x:c r="A28" s="56" t="str">
-        <x:v>F21</x:v>
-      </x:c>
-      <x:c r="B28" s="57" t="str">
-        <x:v>Step 6 · Contact</x:v>
-      </x:c>
-      <x:c r="C28" s="57" t="str">
-        <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
-      </x:c>
-      <x:c r="D28" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E28" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F28" s="57" t="str">
-        <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
-      </x:c>
-      <x:c r="G28" s="57" t="str">
-        <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
-      </x:c>
-      <x:c r="H28" s="58"/>
-      <x:c r="I28" s="58" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="J28" s="57" t="str">
-        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
-      </x:c>
-      <x:c r="K28" s="57" t="str">
-        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
-      </x:c>
-      <x:c r="L28" s="57" t="str">
-        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
-      </x:c>
-      <x:c r="M28" s="57" t="str">
+      <x:c r="M22" s="67" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="56" t="str">
+    <x:row r="23" ht="26" customHeight="1">
+      <x:c r="A23" s="66" t="str">
         <x:v>F22</x:v>
       </x:c>
-      <x:c r="B29" s="57" t="str">
+      <x:c r="B23" s="67" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C29" s="57" t="str">
+      <x:c r="C23" s="67" t="str">
         <x:v>Single-image hero and compact photography-first layout</x:v>
       </x:c>
-      <x:c r="D29" s="57" t="str">
+      <x:c r="D23" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E29" s="57" t="str">
+      <x:c r="E23" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="57" t="str">
+      <x:c r="F23" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="57" t="str">
+      <x:c r="G23" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="58"/>
-      <x:c r="I29" s="58"/>
-      <x:c r="J29" s="57"/>
-      <x:c r="K29" s="57"/>
-      <x:c r="L29" s="57"/>
-      <x:c r="M29" s="57"/>
-    </x:row>
-    <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="56" t="str">
+      <x:c r="H23" s="68"/>
+      <x:c r="I23" s="68"/>
+      <x:c r="J23" s="67"/>
+      <x:c r="K23" s="67"/>
+      <x:c r="L23" s="67"/>
+      <x:c r="M23" s="67"/>
+    </x:row>
+    <x:row r="24" ht="26" customHeight="1">
+      <x:c r="A24" s="66" t="str">
         <x:v>F23</x:v>
       </x:c>
-      <x:c r="B30" s="57" t="str">
+      <x:c r="B24" s="67" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C30" s="57" t="str">
+      <x:c r="C24" s="67" t="str">
         <x:v>Shared search box with Buy/Rent/Projects/Investment tabs</x:v>
       </x:c>
-      <x:c r="D30" s="57" t="str">
+      <x:c r="D24" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E30" s="57" t="str">
+      <x:c r="E24" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="57" t="str">
+      <x:c r="F24" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="57" t="str">
+      <x:c r="G24" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="58"/>
-      <x:c r="I30" s="58"/>
-      <x:c r="J30" s="57"/>
-      <x:c r="K30" s="57"/>
-      <x:c r="L30" s="57"/>
-      <x:c r="M30" s="57"/>
-    </x:row>
-    <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="56" t="str">
+      <x:c r="H24" s="68"/>
+      <x:c r="I24" s="68"/>
+      <x:c r="J24" s="67"/>
+      <x:c r="K24" s="67"/>
+      <x:c r="L24" s="67"/>
+      <x:c r="M24" s="67"/>
+    </x:row>
+    <x:row r="25" ht="26" customHeight="1">
+      <x:c r="A25" s="66" t="str">
         <x:v>F24</x:v>
       </x:c>
-      <x:c r="B31" s="57" t="str">
+      <x:c r="B25" s="67" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C31" s="57" t="str">
+      <x:c r="C25" s="67" t="str">
         <x:v>Categories, recent searches and location/station suggestions</x:v>
       </x:c>
-      <x:c r="D31" s="57" t="str">
+      <x:c r="D25" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E31" s="57" t="str">
+      <x:c r="E25" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="57" t="str">
+      <x:c r="F25" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="57" t="str">
+      <x:c r="G25" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="58"/>
-      <x:c r="I31" s="58"/>
-      <x:c r="J31" s="57"/>
-      <x:c r="K31" s="57"/>
-      <x:c r="L31" s="57"/>
-      <x:c r="M31" s="57"/>
-    </x:row>
-    <x:row r="32" ht="250" customHeight="1">
-      <x:c r="A32" s="56" t="str">
+      <x:c r="H25" s="68"/>
+      <x:c r="I25" s="68"/>
+      <x:c r="J25" s="67"/>
+      <x:c r="K25" s="67"/>
+      <x:c r="L25" s="67"/>
+      <x:c r="M25" s="67"/>
+    </x:row>
+    <x:row r="26" ht="26" customHeight="1">
+      <x:c r="A26" s="66" t="str">
         <x:v>F25</x:v>
       </x:c>
-      <x:c r="B32" s="57" t="str">
+      <x:c r="B26" s="67" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C32" s="57" t="str">
+      <x:c r="C26" s="67" t="str">
         <x:v>Homes for you carousel directly below search; regions with real listing counts</x:v>
       </x:c>
-      <x:c r="D32" s="57" t="str">
+      <x:c r="D26" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E32" s="57" t="str">
+      <x:c r="E26" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="57" t="str">
+      <x:c r="F26" s="67" t="str">
         <x:v>V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
-      <x:c r="G32" s="57" t="str">
+      <x:c r="G26" s="67" t="str">
         <x:v>Codex: implement approved home-page.html only under Step 7 authorization.</x:v>
       </x:c>
-      <x:c r="H32" s="58"/>
-      <x:c r="I32" s="58" t="d">
+      <x:c r="H26" s="68"/>
+      <x:c r="I26" s="68" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J32" s="57" t="str">
+      <x:c r="J26" s="67" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K32" s="57" t="str">
+      <x:c r="K26" s="67" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L32" s="57" t="str">
+      <x:c r="L26" s="67" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M32" s="57" t="str">
+      <x:c r="M26" s="67" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
     </x:row>
+    <x:row r="27" ht="26" customHeight="1">
+      <x:c r="A27" s="66" t="str">
+        <x:v>F26</x:v>
+      </x:c>
+      <x:c r="B27" s="67" t="str">
+        <x:v>Step 7 · Home</x:v>
+      </x:c>
+      <x:c r="C27" s="67" t="str">
+        <x:v>New projects, tools, services and owner lead CTAs</x:v>
+      </x:c>
+      <x:c r="D27" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E27" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F27" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G27" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H27" s="68"/>
+      <x:c r="I27" s="68"/>
+      <x:c r="J27" s="67"/>
+      <x:c r="K27" s="67"/>
+      <x:c r="L27" s="67"/>
+      <x:c r="M27" s="67"/>
+    </x:row>
+    <x:row r="28" ht="250" customHeight="1">
+      <x:c r="A28" s="66" t="str">
+        <x:v>F27</x:v>
+      </x:c>
+      <x:c r="B28" s="67" t="str">
+        <x:v>Step 8 · Projects</x:v>
+      </x:c>
+      <x:c r="C28" s="67" t="str">
+        <x:v>Projects index and responsive project detail layouts</x:v>
+      </x:c>
+      <x:c r="D28" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E28" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F28" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G28" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H28" s="68"/>
+      <x:c r="I28" s="68"/>
+      <x:c r="J28" s="67"/>
+      <x:c r="K28" s="67"/>
+      <x:c r="L28" s="67"/>
+      <x:c r="M28" s="67"/>
+    </x:row>
+    <x:row r="29" ht="26" customHeight="1">
+      <x:c r="A29" s="66" t="str">
+        <x:v>F28</x:v>
+      </x:c>
+      <x:c r="B29" s="67" t="str">
+        <x:v>Step 8 · Projects</x:v>
+      </x:c>
+      <x:c r="C29" s="67" t="str">
+        <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
+      </x:c>
+      <x:c r="D29" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E29" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F29" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G29" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H29" s="68"/>
+      <x:c r="I29" s="68"/>
+      <x:c r="J29" s="67"/>
+      <x:c r="K29" s="67"/>
+      <x:c r="L29" s="67"/>
+      <x:c r="M29" s="67"/>
+    </x:row>
+    <x:row r="30" ht="26" customHeight="1">
+      <x:c r="A30" s="66" t="str">
+        <x:v>F29</x:v>
+      </x:c>
+      <x:c r="B30" s="67" t="str">
+        <x:v>Step 8 · Projects</x:v>
+      </x:c>
+      <x:c r="C30" s="67" t="str">
+        <x:v>Data-driven clickable project SVG plot plan</x:v>
+      </x:c>
+      <x:c r="D30" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E30" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F30" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G30" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H30" s="68"/>
+      <x:c r="I30" s="68"/>
+      <x:c r="J30" s="67"/>
+      <x:c r="K30" s="67"/>
+      <x:c r="L30" s="67"/>
+      <x:c r="M30" s="67"/>
+    </x:row>
+    <x:row r="31" ht="26" customHeight="1">
+      <x:c r="A31" s="66" t="str">
+        <x:v>F30</x:v>
+      </x:c>
+      <x:c r="B31" s="67" t="str">
+        <x:v>Step 8 · Booking</x:v>
+      </x:c>
+      <x:c r="C31" s="67" t="str">
+        <x:v>Site visit 3-step form and confirmation screens</x:v>
+      </x:c>
+      <x:c r="D31" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E31" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F31" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G31" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H31" s="68"/>
+      <x:c r="I31" s="68"/>
+      <x:c r="J31" s="67"/>
+      <x:c r="K31" s="67"/>
+      <x:c r="L31" s="67"/>
+      <x:c r="M31" s="67"/>
+    </x:row>
+    <x:row r="32" ht="250" customHeight="1">
+      <x:c r="A32" s="66" t="str">
+        <x:v>F31</x:v>
+      </x:c>
+      <x:c r="B32" s="67" t="str">
+        <x:v>Step 9 · Saved</x:v>
+      </x:c>
+      <x:c r="C32" s="67" t="str">
+        <x:v>Homes, searches and viewings; local save without account</x:v>
+      </x:c>
+      <x:c r="D32" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E32" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F32" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G32" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H32" s="68"/>
+      <x:c r="I32" s="68"/>
+      <x:c r="J32" s="67"/>
+      <x:c r="K32" s="67"/>
+      <x:c r="L32" s="67"/>
+      <x:c r="M32" s="67"/>
+    </x:row>
     <x:row r="33" ht="26" customHeight="1">
-      <x:c r="A33" s="56" t="str">
-        <x:v>F26</x:v>
-      </x:c>
-      <x:c r="B33" s="57" t="str">
-        <x:v>Step 7 · Home</x:v>
-      </x:c>
-      <x:c r="C33" s="57" t="str">
-        <x:v>New projects, tools, services and owner lead CTAs</x:v>
-      </x:c>
-      <x:c r="D33" s="57" t="str">
+      <x:c r="A33" s="66" t="str">
+        <x:v>F33</x:v>
+      </x:c>
+      <x:c r="B33" s="67" t="str">
+        <x:v>Step 10B · Accounts</x:v>
+      </x:c>
+      <x:c r="C33" s="67" t="str">
+        <x:v>Build approved auth and account screens only after approval</x:v>
+      </x:c>
+      <x:c r="D33" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E33" s="57" t="str">
+      <x:c r="E33" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F33" s="57" t="str">
+      <x:c r="F33" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G33" s="57" t="str">
+      <x:c r="G33" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H33" s="58"/>
-      <x:c r="I33" s="58"/>
-      <x:c r="J33" s="57"/>
-      <x:c r="K33" s="57"/>
-      <x:c r="L33" s="57"/>
-      <x:c r="M33" s="57"/>
+      <x:c r="H33" s="68"/>
+      <x:c r="I33" s="68"/>
+      <x:c r="J33" s="67"/>
+      <x:c r="K33" s="67"/>
+      <x:c r="L33" s="67"/>
+      <x:c r="M33" s="67"/>
     </x:row>
     <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="56" t="str">
-        <x:v>F27</x:v>
-      </x:c>
-      <x:c r="B34" s="57" t="str">
-        <x:v>Step 8 · Projects</x:v>
-      </x:c>
-      <x:c r="C34" s="57" t="str">
-        <x:v>Projects index and responsive project detail layouts</x:v>
-      </x:c>
-      <x:c r="D34" s="57" t="str">
+      <x:c r="A34" s="66" t="str">
+        <x:v>F35</x:v>
+      </x:c>
+      <x:c r="B34" s="67" t="str">
+        <x:v>Step 11B · Admin</x:v>
+      </x:c>
+      <x:c r="C34" s="67" t="str">
+        <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
+      </x:c>
+      <x:c r="D34" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E34" s="57" t="str">
+      <x:c r="E34" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F34" s="57" t="str">
+      <x:c r="F34" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G34" s="57" t="str">
+      <x:c r="G34" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H34" s="58"/>
-      <x:c r="I34" s="58"/>
-      <x:c r="J34" s="57"/>
-      <x:c r="K34" s="57"/>
-      <x:c r="L34" s="57"/>
-      <x:c r="M34" s="57"/>
+      <x:c r="H34" s="68"/>
+      <x:c r="I34" s="68"/>
+      <x:c r="J34" s="67"/>
+      <x:c r="K34" s="67"/>
+      <x:c r="L34" s="67"/>
+      <x:c r="M34" s="67"/>
     </x:row>
     <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="56" t="str">
-        <x:v>F28</x:v>
-      </x:c>
-      <x:c r="B35" s="57" t="str">
-        <x:v>Step 8 · Projects</x:v>
-      </x:c>
-      <x:c r="C35" s="57" t="str">
-        <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
-      </x:c>
-      <x:c r="D35" s="57" t="str">
+      <x:c r="A35" s="66" t="str">
+        <x:v>F36</x:v>
+      </x:c>
+      <x:c r="B35" s="67" t="str">
+        <x:v>Step 11B · Admin</x:v>
+      </x:c>
+      <x:c r="C35" s="67" t="str">
+        <x:v>Admin-managed searchable filter editor with type safety</x:v>
+      </x:c>
+      <x:c r="D35" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E35" s="57" t="str">
+      <x:c r="E35" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F35" s="57" t="str">
+      <x:c r="F35" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G35" s="57" t="str">
+      <x:c r="G35" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H35" s="58"/>
-      <x:c r="I35" s="58"/>
-      <x:c r="J35" s="57"/>
-      <x:c r="K35" s="57"/>
-      <x:c r="L35" s="57"/>
-      <x:c r="M35" s="57"/>
+      <x:c r="H35" s="68"/>
+      <x:c r="I35" s="68"/>
+      <x:c r="J35" s="67"/>
+      <x:c r="K35" s="67"/>
+      <x:c r="L35" s="67"/>
+      <x:c r="M35" s="67"/>
     </x:row>
     <x:row r="36" ht="26" customHeight="1">
-      <x:c r="A36" s="56" t="str">
-        <x:v>F29</x:v>
-      </x:c>
-      <x:c r="B36" s="57" t="str">
-        <x:v>Step 8 · Projects</x:v>
-      </x:c>
-      <x:c r="C36" s="57" t="str">
-        <x:v>Data-driven clickable project SVG plot plan</x:v>
-      </x:c>
-      <x:c r="D36" s="57" t="str">
+      <x:c r="A36" s="66" t="str">
+        <x:v>F37</x:v>
+      </x:c>
+      <x:c r="B36" s="67" t="str">
+        <x:v>Step 12 · Quality</x:v>
+      </x:c>
+      <x:c r="C36" s="67" t="str">
+        <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
+      </x:c>
+      <x:c r="D36" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E36" s="57" t="str">
+      <x:c r="E36" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F36" s="57" t="str">
+      <x:c r="F36" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G36" s="57" t="str">
+      <x:c r="G36" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H36" s="58"/>
-      <x:c r="I36" s="58"/>
-      <x:c r="J36" s="57"/>
-      <x:c r="K36" s="57"/>
-      <x:c r="L36" s="57"/>
-      <x:c r="M36" s="57"/>
+      <x:c r="H36" s="68"/>
+      <x:c r="I36" s="68"/>
+      <x:c r="J36" s="67"/>
+      <x:c r="K36" s="67"/>
+      <x:c r="L36" s="67"/>
+      <x:c r="M36" s="67"/>
     </x:row>
     <x:row r="37" ht="26" customHeight="1">
-      <x:c r="A37" s="56" t="str">
-        <x:v>F30</x:v>
-      </x:c>
-      <x:c r="B37" s="57" t="str">
-        <x:v>Step 8 · Booking</x:v>
-      </x:c>
-      <x:c r="C37" s="57" t="str">
-        <x:v>Site visit 3-step form and confirmation screens</x:v>
-      </x:c>
-      <x:c r="D37" s="57" t="str">
+      <x:c r="A37" s="66" t="str">
+        <x:v>F38</x:v>
+      </x:c>
+      <x:c r="B37" s="67" t="str">
+        <x:v>Step 12 · Quality</x:v>
+      </x:c>
+      <x:c r="C37" s="67" t="str">
+        <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
+      </x:c>
+      <x:c r="D37" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E37" s="57" t="str">
+      <x:c r="E37" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F37" s="57" t="str">
+      <x:c r="F37" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G37" s="57" t="str">
+      <x:c r="G37" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H37" s="58"/>
-      <x:c r="I37" s="58"/>
-      <x:c r="J37" s="57"/>
-      <x:c r="K37" s="57"/>
-      <x:c r="L37" s="57"/>
-      <x:c r="M37" s="57"/>
+      <x:c r="H37" s="68"/>
+      <x:c r="I37" s="68"/>
+      <x:c r="J37" s="67"/>
+      <x:c r="K37" s="67"/>
+      <x:c r="L37" s="67"/>
+      <x:c r="M37" s="67"/>
     </x:row>
     <x:row r="38" ht="26" customHeight="1">
-      <x:c r="A38" s="56" t="str">
-        <x:v>F31</x:v>
-      </x:c>
-      <x:c r="B38" s="57" t="str">
-        <x:v>Step 9 · Saved</x:v>
-      </x:c>
-      <x:c r="C38" s="57" t="str">
-        <x:v>Homes, searches and viewings; local save without account</x:v>
-      </x:c>
-      <x:c r="D38" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E38" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F38" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G38" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A38" s="56"/>
+      <x:c r="B38" s="57"/>
+      <x:c r="C38" s="57"/>
+      <x:c r="D38" s="57"/>
+      <x:c r="E38" s="57"/>
+      <x:c r="F38" s="57"/>
+      <x:c r="G38" s="57"/>
       <x:c r="H38" s="58"/>
       <x:c r="I38" s="58"/>
       <x:c r="J38" s="57"/>
@@ -2142,27 +2342,13 @@
       <x:c r="M38" s="57"/>
     </x:row>
     <x:row r="39" ht="26" customHeight="1">
-      <x:c r="A39" s="56" t="str">
-        <x:v>F33</x:v>
-      </x:c>
-      <x:c r="B39" s="57" t="str">
-        <x:v>Step 10B · Accounts</x:v>
-      </x:c>
-      <x:c r="C39" s="57" t="str">
-        <x:v>Build approved auth and account screens only after approval</x:v>
-      </x:c>
-      <x:c r="D39" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E39" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F39" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G39" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A39" s="56"/>
+      <x:c r="B39" s="57"/>
+      <x:c r="C39" s="57"/>
+      <x:c r="D39" s="57"/>
+      <x:c r="E39" s="57"/>
+      <x:c r="F39" s="57"/>
+      <x:c r="G39" s="57"/>
       <x:c r="H39" s="58"/>
       <x:c r="I39" s="58"/>
       <x:c r="J39" s="57"/>
@@ -2171,27 +2357,13 @@
       <x:c r="M39" s="57"/>
     </x:row>
     <x:row r="40" ht="26" customHeight="1">
-      <x:c r="A40" s="56" t="str">
-        <x:v>F35</x:v>
-      </x:c>
-      <x:c r="B40" s="57" t="str">
-        <x:v>Step 11B · Admin</x:v>
-      </x:c>
-      <x:c r="C40" s="57" t="str">
-        <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
-      </x:c>
-      <x:c r="D40" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E40" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F40" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G40" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A40" s="56"/>
+      <x:c r="B40" s="57"/>
+      <x:c r="C40" s="57"/>
+      <x:c r="D40" s="57"/>
+      <x:c r="E40" s="57"/>
+      <x:c r="F40" s="57"/>
+      <x:c r="G40" s="57"/>
       <x:c r="H40" s="58"/>
       <x:c r="I40" s="58"/>
       <x:c r="J40" s="57"/>
@@ -2200,27 +2372,13 @@
       <x:c r="M40" s="57"/>
     </x:row>
     <x:row r="41" ht="26" customHeight="1">
-      <x:c r="A41" s="56" t="str">
-        <x:v>F36</x:v>
-      </x:c>
-      <x:c r="B41" s="57" t="str">
-        <x:v>Step 11B · Admin</x:v>
-      </x:c>
-      <x:c r="C41" s="57" t="str">
-        <x:v>Admin-managed searchable filter editor with type safety</x:v>
-      </x:c>
-      <x:c r="D41" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E41" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F41" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G41" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A41" s="56"/>
+      <x:c r="B41" s="57"/>
+      <x:c r="C41" s="57"/>
+      <x:c r="D41" s="57"/>
+      <x:c r="E41" s="57"/>
+      <x:c r="F41" s="57"/>
+      <x:c r="G41" s="57"/>
       <x:c r="H41" s="58"/>
       <x:c r="I41" s="58"/>
       <x:c r="J41" s="57"/>
@@ -2229,27 +2387,13 @@
       <x:c r="M41" s="57"/>
     </x:row>
     <x:row r="42" ht="26" customHeight="1">
-      <x:c r="A42" s="56" t="str">
-        <x:v>F37</x:v>
-      </x:c>
-      <x:c r="B42" s="57" t="str">
-        <x:v>Step 12 · Quality</x:v>
-      </x:c>
-      <x:c r="C42" s="57" t="str">
-        <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
-      </x:c>
-      <x:c r="D42" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E42" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F42" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G42" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A42" s="56"/>
+      <x:c r="B42" s="57"/>
+      <x:c r="C42" s="57"/>
+      <x:c r="D42" s="57"/>
+      <x:c r="E42" s="57"/>
+      <x:c r="F42" s="57"/>
+      <x:c r="G42" s="57"/>
       <x:c r="H42" s="58"/>
       <x:c r="I42" s="58"/>
       <x:c r="J42" s="57"/>
@@ -2258,27 +2402,13 @@
       <x:c r="M42" s="57"/>
     </x:row>
     <x:row r="43" ht="26" customHeight="1">
-      <x:c r="A43" s="56" t="str">
-        <x:v>F38</x:v>
-      </x:c>
-      <x:c r="B43" s="57" t="str">
-        <x:v>Step 12 · Quality</x:v>
-      </x:c>
-      <x:c r="C43" s="57" t="str">
-        <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
-      </x:c>
-      <x:c r="D43" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E43" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F43" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G43" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A43" s="56"/>
+      <x:c r="B43" s="57"/>
+      <x:c r="C43" s="57"/>
+      <x:c r="D43" s="57"/>
+      <x:c r="E43" s="57"/>
+      <x:c r="F43" s="57"/>
+      <x:c r="G43" s="57"/>
       <x:c r="H43" s="58"/>
       <x:c r="I43" s="58"/>
       <x:c r="J43" s="57"/>
@@ -9147,24 +9277,27 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="15" priority="1">
+    <x:cfRule type="expression" dxfId="33" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="16" priority="2">
+    <x:cfRule type="expression" dxfId="34" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="17" priority="3">
+    <x:cfRule type="expression" dxfId="35" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E43">
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="E38:E43">
+      <x:formula1>"Done,Pending,Not started"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E6:E37">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7e326bc49d5487a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70e58c766c37460c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9204,7 +9337,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
+        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -9219,14 +9352,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -9245,7 +9378,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -9290,267 +9423,267 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="50" t="str">
+      <x:c r="A6" s="63" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B6" s="51" t="str">
+      <x:c r="B6" s="64" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C6" s="51" t="str">
+      <x:c r="C6" s="64" t="str">
         <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
-      <x:c r="D6" s="51" t="str">
+      <x:c r="D6" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E6" s="51" t="str">
+      <x:c r="E6" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="51" t="str">
+      <x:c r="F6" s="64" t="str">
         <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
-      <x:c r="G6" s="51" t="str">
+      <x:c r="G6" s="64" t="str">
         <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
       </x:c>
-      <x:c r="H6" s="52" t="d">
+      <x:c r="H6" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="52" t="d">
+      <x:c r="I6" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="51" t="str">
+      <x:c r="J6" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="51" t="str">
+      <x:c r="K6" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="51" t="str">
+      <x:c r="L6" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="51" t="str">
+      <x:c r="M6" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
 2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
 2026-10-09 Step 2: Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="50" t="str">
+      <x:c r="A7" s="63" t="str">
         <x:v>B17</x:v>
       </x:c>
-      <x:c r="B7" s="51" t="str">
+      <x:c r="B7" s="64" t="str">
         <x:v>Decision · Leads</x:v>
       </x:c>
-      <x:c r="C7" s="51" t="str">
+      <x:c r="C7" s="64" t="str">
         <x:v>Approve shared inbox versus listing agent enquiry destination</x:v>
       </x:c>
-      <x:c r="D7" s="51" t="str">
+      <x:c r="D7" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E7" s="51" t="str">
+      <x:c r="E7" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="51" t="str">
+      <x:c r="F7" s="64" t="str">
         <x:v>BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
-      <x:c r="G7" s="51" t="str">
+      <x:c r="G7" s="64" t="str">
         <x:v>Owner: select routing mode and mailbox</x:v>
       </x:c>
-      <x:c r="H7" s="52"/>
-      <x:c r="I7" s="52"/>
-      <x:c r="J7" s="51"/>
-      <x:c r="K7" s="51"/>
-      <x:c r="L7" s="51"/>
-      <x:c r="M7" s="51"/>
+      <x:c r="H7" s="65"/>
+      <x:c r="I7" s="65"/>
+      <x:c r="J7" s="64"/>
+      <x:c r="K7" s="64"/>
+      <x:c r="L7" s="64"/>
+      <x:c r="M7" s="64"/>
     </x:row>
     <x:row r="8" ht="250" customHeight="1">
-      <x:c r="A8" s="50" t="str">
+      <x:c r="A8" s="63" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B8" s="51" t="str">
+      <x:c r="B8" s="64" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C8" s="51" t="str">
+      <x:c r="C8" s="64" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D8" s="51" t="str">
+      <x:c r="D8" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="51" t="str">
+      <x:c r="E8" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="51" t="str">
+      <x:c r="F8" s="64" t="str">
         <x:v>Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending.</x:v>
       </x:c>
-      <x:c r="G8" s="51" t="str">
+      <x:c r="G8" s="64" t="str">
         <x:v>Owner: provide actual contacts/routing; Codex: integrate and review accessible contact actions later.</x:v>
       </x:c>
-      <x:c r="H8" s="52" t="d">
+      <x:c r="H8" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I8" s="52" t="d">
+      <x:c r="I8" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="51" t="str">
+      <x:c r="J8" s="64" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K8" s="51" t="str">
+      <x:c r="K8" s="64" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L8" s="51" t="str">
+      <x:c r="L8" s="64" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M8" s="51" t="str">
+      <x:c r="M8" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #4 unresolved
 2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.
 2026-10-09 foundation: Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="50" t="str">
+      <x:c r="A9" s="63" t="str">
         <x:v>B23</x:v>
       </x:c>
-      <x:c r="B9" s="51" t="str">
+      <x:c r="B9" s="64" t="str">
         <x:v>Decision · Accounts</x:v>
       </x:c>
-      <x:c r="C9" s="51" t="str">
+      <x:c r="C9" s="64" t="str">
         <x:v>Approve LINE only or LINE+Google+email sign-in</x:v>
       </x:c>
-      <x:c r="D9" s="51" t="str">
+      <x:c r="D9" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E9" s="51" t="str">
+      <x:c r="E9" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="51" t="str">
+      <x:c r="F9" s="64" t="str">
         <x:v>BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
-      <x:c r="G9" s="51" t="str">
+      <x:c r="G9" s="64" t="str">
         <x:v>Owner: approve authentication providers</x:v>
       </x:c>
-      <x:c r="H9" s="52"/>
-      <x:c r="I9" s="52"/>
-      <x:c r="J9" s="51"/>
-      <x:c r="K9" s="51"/>
-      <x:c r="L9" s="51"/>
-      <x:c r="M9" s="51"/>
+      <x:c r="H9" s="65"/>
+      <x:c r="I9" s="65"/>
+      <x:c r="J9" s="64"/>
+      <x:c r="K9" s="64"/>
+      <x:c r="L9" s="64"/>
+      <x:c r="M9" s="64"/>
     </x:row>
     <x:row r="10" ht="200" customHeight="1">
-      <x:c r="A10" s="50" t="str">
+      <x:c r="A10" s="63" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B10" s="51" t="str">
+      <x:c r="B10" s="64" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C10" s="51" t="str">
+      <x:c r="C10" s="64" t="str">
         <x:v>Approve THB only versus optional approximate FX display</x:v>
       </x:c>
-      <x:c r="D10" s="51" t="str">
+      <x:c r="D10" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="51" t="str">
+      <x:c r="E10" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="51" t="str">
+      <x:c r="F10" s="64" t="str">
         <x:v>Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
-      <x:c r="G10" s="51" t="str">
+      <x:c r="G10" s="64" t="str">
         <x:v>Codex: implement USD/THB during authorized currency work; confirm rate source.</x:v>
       </x:c>
-      <x:c r="H10" s="52"/>
-      <x:c r="I10" s="52" t="d">
+      <x:c r="H10" s="65"/>
+      <x:c r="I10" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="51" t="str">
+      <x:c r="J10" s="64" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K10" s="51" t="str">
+      <x:c r="K10" s="64" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L10" s="51" t="str">
+      <x:c r="L10" s="64" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M10" s="51" t="str">
+      <x:c r="M10" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #6 unresolved
 2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="200" customHeight="1">
-      <x:c r="A11" s="50" t="str">
+      <x:c r="A11" s="63" t="str">
         <x:v>B29</x:v>
       </x:c>
-      <x:c r="B11" s="51" t="str">
+      <x:c r="B11" s="64" t="str">
         <x:v>Decision · Projects</x:v>
       </x:c>
-      <x:c r="C11" s="51" t="str">
+      <x:c r="C11" s="64" t="str">
         <x:v>Approve public project prices versus enquiry-only price list</x:v>
       </x:c>
-      <x:c r="D11" s="51" t="str">
+      <x:c r="D11" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E11" s="51" t="str">
+      <x:c r="E11" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="51" t="str">
+      <x:c r="F11" s="64" t="str">
         <x:v>Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
-      <x:c r="G11" s="51" t="str">
+      <x:c r="G11" s="64" t="str">
         <x:v>Codex: add per-record price visibility in authorized backend/admin work after admin wireframe approval.</x:v>
       </x:c>
-      <x:c r="H11" s="52"/>
-      <x:c r="I11" s="52" t="d">
+      <x:c r="H11" s="65"/>
+      <x:c r="I11" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="51" t="str">
+      <x:c r="J11" s="64" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K11" s="51" t="str">
+      <x:c r="K11" s="64" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L11" s="51" t="str">
+      <x:c r="L11" s="64" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M11" s="51" t="str">
+      <x:c r="M11" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #7 unresolved
 2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="310" customHeight="1">
-      <x:c r="A12" s="50" t="str">
+      <x:c r="A12" s="63" t="str">
         <x:v>R01</x:v>
       </x:c>
-      <x:c r="B12" s="51" t="str">
+      <x:c r="B12" s="64" t="str">
         <x:v>Step 0 · Preparation</x:v>
       </x:c>
-      <x:c r="C12" s="51" t="str">
+      <x:c r="C12" s="64" t="str">
         <x:v>Inspect project; establish permanent rules, documentation, Git/live mirror and tracker</x:v>
       </x:c>
-      <x:c r="D12" s="51" t="str">
+      <x:c r="D12" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E12" s="51" t="str">
+      <x:c r="E12" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="51" t="str">
+      <x:c r="F12" s="64" t="str">
         <x:v>Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request.</x:v>
       </x:c>
-      <x:c r="G12" s="51" t="str">
+      <x:c r="G12" s="64" t="str">
         <x:v>Codex: close the separate Step 0 utility/reference-review requirements only when authorized; stop before Step 3.</x:v>
       </x:c>
-      <x:c r="H12" s="52" t="d">
+      <x:c r="H12" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="52" t="d">
+      <x:c r="I12" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="51" t="str">
+      <x:c r="J12" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K12" s="51" t="str">
+      <x:c r="K12" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L12" s="51" t="str">
+      <x:c r="L12" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="51" t="str">
+      <x:c r="M12" s="64" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
@@ -9558,611 +9691,598 @@
 2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.
 2026-10-09 Step 2: Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
 2026-10-09 tracker formatting: workbook recreated with yellow Pending, light green Done and red Not started rows and status tabs. All 81 permanent IDs and prior task history preserved. Step 3 is authorized but implementation has not begun; owner requested the Excel first.
-2026-10-09 Claude handoff: owner requested CLAUDE.md to share the current project context with Claude. Documented sources, Git/live paths, implemented shell/Step 2, unimplemented authorized Step 3, open decisions, safety, tests, servers and completion gates. Documentation/link checks and workbook ID/history/colour checks pass. No application change or new runtime test is claimed. R01 remains Pending for existing Step 0 blockers; Git/live synchronization and push are verified during finalization.</x:v>
+2026-10-09 Claude handoff: owner requested CLAUDE.md to share the current project context with Claude. Documented sources, Git/live paths, implemented shell/Step 2, unimplemented authorized Step 3, open decisions, safety, tests, servers and completion gates. Documentation/link checks and workbook ID/history/colour checks pass. No application change or new runtime test is claimed. R01 remains Pending for existing Step 0 blockers; Git/live synchronization and push are verified during finalization.
+2026-10-09 Step 3 completed only after its gates. F08-F13/B05-B07 and R02 record current proof. Existing Step 0 blockers remain Pending; no duplicate preparation ID or fabricated rendered-reference comparison. All nine maintained Markdown updated; approved source files preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="56" t="str">
-        <x:v>B05</x:v>
-      </x:c>
-      <x:c r="B13" s="57" t="str">
-        <x:v>Step 2 · Filters</x:v>
-      </x:c>
-      <x:c r="C13" s="57" t="str">
-        <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
-      </x:c>
-      <x:c r="D13" s="57" t="str">
+      <x:c r="A13" s="66" t="str">
+        <x:v>B08</x:v>
+      </x:c>
+      <x:c r="B13" s="67" t="str">
+        <x:v>Step 4 · Map</x:v>
+      </x:c>
+      <x:c r="C13" s="67" t="str">
+        <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
+      </x:c>
+      <x:c r="D13" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E13" s="57" t="str">
+      <x:c r="E13" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="57" t="str">
+      <x:c r="F13" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G13" s="57" t="str">
+      <x:c r="G13" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H13" s="58"/>
-      <x:c r="I13" s="58"/>
-      <x:c r="J13" s="57"/>
-      <x:c r="K13" s="57"/>
-      <x:c r="L13" s="57"/>
-      <x:c r="M13" s="57"/>
+      <x:c r="H13" s="68"/>
+      <x:c r="I13" s="68"/>
+      <x:c r="J13" s="67"/>
+      <x:c r="K13" s="67"/>
+      <x:c r="L13" s="67"/>
+      <x:c r="M13" s="67"/>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="56" t="str">
-        <x:v>B06</x:v>
-      </x:c>
-      <x:c r="B14" s="57" t="str">
-        <x:v>Step 3 · Search</x:v>
-      </x:c>
-      <x:c r="C14" s="57" t="str">
-        <x:v>Typed validated listing/search data access and pagination</x:v>
-      </x:c>
-      <x:c r="D14" s="57" t="str">
+      <x:c r="A14" s="66" t="str">
+        <x:v>B10</x:v>
+      </x:c>
+      <x:c r="B14" s="67" t="str">
+        <x:v>Step 4 · Nearby</x:v>
+      </x:c>
+      <x:c r="C14" s="67" t="str">
+        <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
+      </x:c>
+      <x:c r="D14" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E14" s="57" t="str">
+      <x:c r="E14" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F14" s="57" t="str">
+      <x:c r="F14" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G14" s="57" t="str">
+      <x:c r="G14" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H14" s="58"/>
-      <x:c r="I14" s="58"/>
-      <x:c r="J14" s="57"/>
-      <x:c r="K14" s="57"/>
-      <x:c r="L14" s="57"/>
-      <x:c r="M14" s="57"/>
+      <x:c r="H14" s="68"/>
+      <x:c r="I14" s="68"/>
+      <x:c r="J14" s="67"/>
+      <x:c r="K14" s="67"/>
+      <x:c r="L14" s="67"/>
+      <x:c r="M14" s="67"/>
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="56" t="str">
-        <x:v>B07</x:v>
-      </x:c>
-      <x:c r="B15" s="57" t="str">
-        <x:v>Step 3 · Search</x:v>
-      </x:c>
-      <x:c r="C15" s="57" t="str">
-        <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
-      </x:c>
-      <x:c r="D15" s="57" t="str">
+      <x:c r="A15" s="66" t="str">
+        <x:v>B11</x:v>
+      </x:c>
+      <x:c r="B15" s="67" t="str">
+        <x:v>Step 5 · Media</x:v>
+      </x:c>
+      <x:c r="C15" s="67" t="str">
+        <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
+      </x:c>
+      <x:c r="D15" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E15" s="57" t="str">
+      <x:c r="E15" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="57" t="str">
+      <x:c r="F15" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G15" s="57" t="str">
+      <x:c r="G15" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H15" s="58"/>
-      <x:c r="I15" s="58"/>
-      <x:c r="J15" s="57"/>
-      <x:c r="K15" s="57"/>
-      <x:c r="L15" s="57"/>
-      <x:c r="M15" s="57"/>
+      <x:c r="H15" s="68"/>
+      <x:c r="I15" s="68"/>
+      <x:c r="J15" s="67"/>
+      <x:c r="K15" s="67"/>
+      <x:c r="L15" s="67"/>
+      <x:c r="M15" s="67"/>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="56" t="str">
-        <x:v>B08</x:v>
-      </x:c>
-      <x:c r="B16" s="57" t="str">
-        <x:v>Step 4 · Map</x:v>
-      </x:c>
-      <x:c r="C16" s="57" t="str">
-        <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
-      </x:c>
-      <x:c r="D16" s="57" t="str">
+      <x:c r="A16" s="66" t="str">
+        <x:v>B12</x:v>
+      </x:c>
+      <x:c r="B16" s="67" t="str">
+        <x:v>Step 5 · Similar</x:v>
+      </x:c>
+      <x:c r="C16" s="67" t="str">
+        <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
+      </x:c>
+      <x:c r="D16" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E16" s="57" t="str">
+      <x:c r="E16" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="57" t="str">
+      <x:c r="F16" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G16" s="57" t="str">
+      <x:c r="G16" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H16" s="58"/>
-      <x:c r="I16" s="58"/>
-      <x:c r="J16" s="57"/>
-      <x:c r="K16" s="57"/>
-      <x:c r="L16" s="57"/>
-      <x:c r="M16" s="57"/>
+      <x:c r="H16" s="68"/>
+      <x:c r="I16" s="68"/>
+      <x:c r="J16" s="67"/>
+      <x:c r="K16" s="67"/>
+      <x:c r="L16" s="67"/>
+      <x:c r="M16" s="67"/>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="56" t="str">
-        <x:v>B10</x:v>
-      </x:c>
-      <x:c r="B17" s="57" t="str">
-        <x:v>Step 4 · Nearby</x:v>
-      </x:c>
-      <x:c r="C17" s="57" t="str">
-        <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
-      </x:c>
-      <x:c r="D17" s="57" t="str">
+      <x:c r="A17" s="66" t="str">
+        <x:v>B13</x:v>
+      </x:c>
+      <x:c r="B17" s="67" t="str">
+        <x:v>Step 5 · Metrics</x:v>
+      </x:c>
+      <x:c r="C17" s="67" t="str">
+        <x:v>Comparable pricing/yield gated by verified sample size</x:v>
+      </x:c>
+      <x:c r="D17" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E17" s="57" t="str">
+      <x:c r="E17" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="57" t="str">
+      <x:c r="F17" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G17" s="57" t="str">
+      <x:c r="G17" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H17" s="58"/>
-      <x:c r="I17" s="58"/>
-      <x:c r="J17" s="57"/>
-      <x:c r="K17" s="57"/>
-      <x:c r="L17" s="57"/>
-      <x:c r="M17" s="57"/>
+      <x:c r="H17" s="68"/>
+      <x:c r="I17" s="68"/>
+      <x:c r="J17" s="67"/>
+      <x:c r="K17" s="67"/>
+      <x:c r="L17" s="67"/>
+      <x:c r="M17" s="67"/>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="56" t="str">
-        <x:v>B11</x:v>
-      </x:c>
-      <x:c r="B18" s="57" t="str">
-        <x:v>Step 5 · Media</x:v>
-      </x:c>
-      <x:c r="C18" s="57" t="str">
-        <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
-      </x:c>
-      <x:c r="D18" s="57" t="str">
+      <x:c r="A18" s="66" t="str">
+        <x:v>B14</x:v>
+      </x:c>
+      <x:c r="B18" s="67" t="str">
+        <x:v>Step 6 · Leads</x:v>
+      </x:c>
+      <x:c r="C18" s="67" t="str">
+        <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
+      </x:c>
+      <x:c r="D18" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E18" s="57" t="str">
+      <x:c r="E18" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F18" s="57" t="str">
+      <x:c r="F18" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G18" s="57" t="str">
+      <x:c r="G18" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H18" s="58"/>
-      <x:c r="I18" s="58"/>
-      <x:c r="J18" s="57"/>
-      <x:c r="K18" s="57"/>
-      <x:c r="L18" s="57"/>
-      <x:c r="M18" s="57"/>
+      <x:c r="H18" s="68"/>
+      <x:c r="I18" s="68"/>
+      <x:c r="J18" s="67"/>
+      <x:c r="K18" s="67"/>
+      <x:c r="L18" s="67"/>
+      <x:c r="M18" s="67"/>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="56" t="str">
-        <x:v>B12</x:v>
-      </x:c>
-      <x:c r="B19" s="57" t="str">
-        <x:v>Step 5 · Similar</x:v>
-      </x:c>
-      <x:c r="C19" s="57" t="str">
-        <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
-      </x:c>
-      <x:c r="D19" s="57" t="str">
+      <x:c r="A19" s="66" t="str">
+        <x:v>B15</x:v>
+      </x:c>
+      <x:c r="B19" s="67" t="str">
+        <x:v>Step 6 · Leads</x:v>
+      </x:c>
+      <x:c r="C19" s="67" t="str">
+        <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
+      </x:c>
+      <x:c r="D19" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E19" s="57" t="str">
+      <x:c r="E19" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="57" t="str">
+      <x:c r="F19" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G19" s="57" t="str">
+      <x:c r="G19" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H19" s="58"/>
-      <x:c r="I19" s="58"/>
-      <x:c r="J19" s="57"/>
-      <x:c r="K19" s="57"/>
-      <x:c r="L19" s="57"/>
-      <x:c r="M19" s="57"/>
+      <x:c r="H19" s="68"/>
+      <x:c r="I19" s="68"/>
+      <x:c r="J19" s="67"/>
+      <x:c r="K19" s="67"/>
+      <x:c r="L19" s="67"/>
+      <x:c r="M19" s="67"/>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="56" t="str">
-        <x:v>B13</x:v>
-      </x:c>
-      <x:c r="B20" s="57" t="str">
-        <x:v>Step 5 · Metrics</x:v>
-      </x:c>
-      <x:c r="C20" s="57" t="str">
-        <x:v>Comparable pricing/yield gated by verified sample size</x:v>
-      </x:c>
-      <x:c r="D20" s="57" t="str">
+      <x:c r="A20" s="66" t="str">
+        <x:v>B16</x:v>
+      </x:c>
+      <x:c r="B20" s="67" t="str">
+        <x:v>Step 6 · Security</x:v>
+      </x:c>
+      <x:c r="C20" s="67" t="str">
+        <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
+      </x:c>
+      <x:c r="D20" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E20" s="57" t="str">
+      <x:c r="E20" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="57" t="str">
+      <x:c r="F20" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G20" s="57" t="str">
+      <x:c r="G20" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H20" s="58"/>
-      <x:c r="I20" s="58"/>
-      <x:c r="J20" s="57"/>
-      <x:c r="K20" s="57"/>
-      <x:c r="L20" s="57"/>
-      <x:c r="M20" s="57"/>
+      <x:c r="H20" s="68"/>
+      <x:c r="I20" s="68"/>
+      <x:c r="J20" s="67"/>
+      <x:c r="K20" s="67"/>
+      <x:c r="L20" s="67"/>
+      <x:c r="M20" s="67"/>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="56" t="str">
-        <x:v>B14</x:v>
-      </x:c>
-      <x:c r="B21" s="57" t="str">
-        <x:v>Step 6 · Leads</x:v>
-      </x:c>
-      <x:c r="C21" s="57" t="str">
-        <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
-      </x:c>
-      <x:c r="D21" s="57" t="str">
+      <x:c r="A21" s="66" t="str">
+        <x:v>B19</x:v>
+      </x:c>
+      <x:c r="B21" s="67" t="str">
+        <x:v>Step 6 · Chat</x:v>
+      </x:c>
+      <x:c r="C21" s="67" t="str">
+        <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
+      </x:c>
+      <x:c r="D21" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E21" s="57" t="str">
+      <x:c r="E21" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="57" t="str">
+      <x:c r="F21" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G21" s="57" t="str">
+      <x:c r="G21" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H21" s="58"/>
-      <x:c r="I21" s="58"/>
-      <x:c r="J21" s="57"/>
-      <x:c r="K21" s="57"/>
-      <x:c r="L21" s="57"/>
-      <x:c r="M21" s="57"/>
+      <x:c r="H21" s="68"/>
+      <x:c r="I21" s="68"/>
+      <x:c r="J21" s="67"/>
+      <x:c r="K21" s="67"/>
+      <x:c r="L21" s="67"/>
+      <x:c r="M21" s="67"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="56" t="str">
-        <x:v>B15</x:v>
-      </x:c>
-      <x:c r="B22" s="57" t="str">
-        <x:v>Step 6 · Leads</x:v>
-      </x:c>
-      <x:c r="C22" s="57" t="str">
-        <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
-      </x:c>
-      <x:c r="D22" s="57" t="str">
+      <x:c r="A22" s="66" t="str">
+        <x:v>B20</x:v>
+      </x:c>
+      <x:c r="B22" s="67" t="str">
+        <x:v>Step 8 · Projects</x:v>
+      </x:c>
+      <x:c r="C22" s="67" t="str">
+        <x:v>Project/unit/plot status logic and validation</x:v>
+      </x:c>
+      <x:c r="D22" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E22" s="57" t="str">
+      <x:c r="E22" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="57" t="str">
+      <x:c r="F22" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G22" s="57" t="str">
+      <x:c r="G22" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H22" s="58"/>
-      <x:c r="I22" s="58"/>
-      <x:c r="J22" s="57"/>
-      <x:c r="K22" s="57"/>
-      <x:c r="L22" s="57"/>
-      <x:c r="M22" s="57"/>
+      <x:c r="H22" s="68"/>
+      <x:c r="I22" s="68"/>
+      <x:c r="J22" s="67"/>
+      <x:c r="K22" s="67"/>
+      <x:c r="L22" s="67"/>
+      <x:c r="M22" s="67"/>
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
-      <x:c r="A23" s="56" t="str">
-        <x:v>B16</x:v>
-      </x:c>
-      <x:c r="B23" s="57" t="str">
-        <x:v>Step 6 · Security</x:v>
-      </x:c>
-      <x:c r="C23" s="57" t="str">
-        <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
-      </x:c>
-      <x:c r="D23" s="57" t="str">
+      <x:c r="A23" s="66" t="str">
+        <x:v>B21</x:v>
+      </x:c>
+      <x:c r="B23" s="67" t="str">
+        <x:v>Step 8 · Booking</x:v>
+      </x:c>
+      <x:c r="C23" s="67" t="str">
+        <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
+      </x:c>
+      <x:c r="D23" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E23" s="57" t="str">
+      <x:c r="E23" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F23" s="57" t="str">
+      <x:c r="F23" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G23" s="57" t="str">
+      <x:c r="G23" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H23" s="58"/>
-      <x:c r="I23" s="58"/>
-      <x:c r="J23" s="57"/>
-      <x:c r="K23" s="57"/>
-      <x:c r="L23" s="57"/>
-      <x:c r="M23" s="57"/>
+      <x:c r="H23" s="68"/>
+      <x:c r="I23" s="68"/>
+      <x:c r="J23" s="67"/>
+      <x:c r="K23" s="67"/>
+      <x:c r="L23" s="67"/>
+      <x:c r="M23" s="67"/>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="56" t="str">
-        <x:v>B19</x:v>
-      </x:c>
-      <x:c r="B24" s="57" t="str">
-        <x:v>Step 6 · Chat</x:v>
-      </x:c>
-      <x:c r="C24" s="57" t="str">
-        <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
-      </x:c>
-      <x:c r="D24" s="57" t="str">
+      <x:c r="A24" s="66" t="str">
+        <x:v>B22</x:v>
+      </x:c>
+      <x:c r="B24" s="67" t="str">
+        <x:v>Step 9 · Saved</x:v>
+      </x:c>
+      <x:c r="C24" s="67" t="str">
+        <x:v>Saved listings/searches persistence, new-match calculations</x:v>
+      </x:c>
+      <x:c r="D24" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E24" s="57" t="str">
+      <x:c r="E24" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="57" t="str">
+      <x:c r="F24" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G24" s="57" t="str">
+      <x:c r="G24" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H24" s="58"/>
-      <x:c r="I24" s="58"/>
-      <x:c r="J24" s="57"/>
-      <x:c r="K24" s="57"/>
-      <x:c r="L24" s="57"/>
-      <x:c r="M24" s="57"/>
+      <x:c r="H24" s="68"/>
+      <x:c r="I24" s="68"/>
+      <x:c r="J24" s="67"/>
+      <x:c r="K24" s="67"/>
+      <x:c r="L24" s="67"/>
+      <x:c r="M24" s="67"/>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="56" t="str">
-        <x:v>B20</x:v>
-      </x:c>
-      <x:c r="B25" s="57" t="str">
-        <x:v>Step 8 · Projects</x:v>
-      </x:c>
-      <x:c r="C25" s="57" t="str">
-        <x:v>Project/unit/plot status logic and validation</x:v>
-      </x:c>
-      <x:c r="D25" s="57" t="str">
+      <x:c r="A25" s="66" t="str">
+        <x:v>B24</x:v>
+      </x:c>
+      <x:c r="B25" s="67" t="str">
+        <x:v>Step 10B · Auth</x:v>
+      </x:c>
+      <x:c r="C25" s="67" t="str">
+        <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
+      </x:c>
+      <x:c r="D25" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E25" s="57" t="str">
+      <x:c r="E25" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="57" t="str">
+      <x:c r="F25" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G25" s="57" t="str">
+      <x:c r="G25" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H25" s="58"/>
-      <x:c r="I25" s="58"/>
-      <x:c r="J25" s="57"/>
-      <x:c r="K25" s="57"/>
-      <x:c r="L25" s="57"/>
-      <x:c r="M25" s="57"/>
+      <x:c r="H25" s="68"/>
+      <x:c r="I25" s="68"/>
+      <x:c r="J25" s="67"/>
+      <x:c r="K25" s="67"/>
+      <x:c r="L25" s="67"/>
+      <x:c r="M25" s="67"/>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="56" t="str">
-        <x:v>B21</x:v>
-      </x:c>
-      <x:c r="B26" s="57" t="str">
-        <x:v>Step 8 · Booking</x:v>
-      </x:c>
-      <x:c r="C26" s="57" t="str">
-        <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
-      </x:c>
-      <x:c r="D26" s="57" t="str">
+      <x:c r="A26" s="66" t="str">
+        <x:v>B25</x:v>
+      </x:c>
+      <x:c r="B26" s="67" t="str">
+        <x:v>Step 10B · Auth</x:v>
+      </x:c>
+      <x:c r="C26" s="67" t="str">
+        <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
+      </x:c>
+      <x:c r="D26" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E26" s="57" t="str">
+      <x:c r="E26" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="57" t="str">
+      <x:c r="F26" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G26" s="57" t="str">
+      <x:c r="G26" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H26" s="58"/>
-      <x:c r="I26" s="58"/>
-      <x:c r="J26" s="57"/>
-      <x:c r="K26" s="57"/>
-      <x:c r="L26" s="57"/>
-      <x:c r="M26" s="57"/>
+      <x:c r="H26" s="68"/>
+      <x:c r="I26" s="68"/>
+      <x:c r="J26" s="67"/>
+      <x:c r="K26" s="67"/>
+      <x:c r="L26" s="67"/>
+      <x:c r="M26" s="67"/>
     </x:row>
     <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="56" t="str">
-        <x:v>B22</x:v>
-      </x:c>
-      <x:c r="B27" s="57" t="str">
-        <x:v>Step 9 · Saved</x:v>
-      </x:c>
-      <x:c r="C27" s="57" t="str">
-        <x:v>Saved listings/searches persistence, new-match calculations</x:v>
-      </x:c>
-      <x:c r="D27" s="57" t="str">
+      <x:c r="A27" s="66" t="str">
+        <x:v>B26</x:v>
+      </x:c>
+      <x:c r="B27" s="67" t="str">
+        <x:v>Step 11B · Admin</x:v>
+      </x:c>
+      <x:c r="C27" s="67" t="str">
+        <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
+      </x:c>
+      <x:c r="D27" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E27" s="57" t="str">
+      <x:c r="E27" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="57" t="str">
+      <x:c r="F27" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G27" s="57" t="str">
+      <x:c r="G27" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H27" s="58"/>
-      <x:c r="I27" s="58"/>
-      <x:c r="J27" s="57"/>
-      <x:c r="K27" s="57"/>
-      <x:c r="L27" s="57"/>
-      <x:c r="M27" s="57"/>
+      <x:c r="H27" s="68"/>
+      <x:c r="I27" s="68"/>
+      <x:c r="J27" s="67"/>
+      <x:c r="K27" s="67"/>
+      <x:c r="L27" s="67"/>
+      <x:c r="M27" s="67"/>
     </x:row>
     <x:row r="28" ht="26" customHeight="1">
-      <x:c r="A28" s="56" t="str">
-        <x:v>B24</x:v>
-      </x:c>
-      <x:c r="B28" s="57" t="str">
-        <x:v>Step 10B · Auth</x:v>
-      </x:c>
-      <x:c r="C28" s="57" t="str">
-        <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
-      </x:c>
-      <x:c r="D28" s="57" t="str">
+      <x:c r="A28" s="66" t="str">
+        <x:v>B27</x:v>
+      </x:c>
+      <x:c r="B28" s="67" t="str">
+        <x:v>Step 11B · Admin</x:v>
+      </x:c>
+      <x:c r="C28" s="67" t="str">
+        <x:v>Admin user management, audit log and sensitive action authorization</x:v>
+      </x:c>
+      <x:c r="D28" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E28" s="57" t="str">
+      <x:c r="E28" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="57" t="str">
+      <x:c r="F28" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G28" s="57" t="str">
+      <x:c r="G28" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H28" s="58"/>
-      <x:c r="I28" s="58"/>
-      <x:c r="J28" s="57"/>
-      <x:c r="K28" s="57"/>
-      <x:c r="L28" s="57"/>
-      <x:c r="M28" s="57"/>
+      <x:c r="H28" s="68"/>
+      <x:c r="I28" s="68"/>
+      <x:c r="J28" s="67"/>
+      <x:c r="K28" s="67"/>
+      <x:c r="L28" s="67"/>
+      <x:c r="M28" s="67"/>
     </x:row>
     <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="56" t="str">
-        <x:v>B25</x:v>
-      </x:c>
-      <x:c r="B29" s="57" t="str">
-        <x:v>Step 10B · Auth</x:v>
-      </x:c>
-      <x:c r="C29" s="57" t="str">
-        <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
-      </x:c>
-      <x:c r="D29" s="57" t="str">
+      <x:c r="A29" s="66" t="str">
+        <x:v>B30</x:v>
+      </x:c>
+      <x:c r="B29" s="67" t="str">
+        <x:v>Step 12 · Deploy</x:v>
+      </x:c>
+      <x:c r="C29" s="67" t="str">
+        <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
+      </x:c>
+      <x:c r="D29" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E29" s="57" t="str">
+      <x:c r="E29" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="57" t="str">
+      <x:c r="F29" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="57" t="str">
+      <x:c r="G29" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="58"/>
-      <x:c r="I29" s="58"/>
-      <x:c r="J29" s="57"/>
-      <x:c r="K29" s="57"/>
-      <x:c r="L29" s="57"/>
-      <x:c r="M29" s="57"/>
+      <x:c r="H29" s="68"/>
+      <x:c r="I29" s="68"/>
+      <x:c r="J29" s="67"/>
+      <x:c r="K29" s="67"/>
+      <x:c r="L29" s="67"/>
+      <x:c r="M29" s="67"/>
     </x:row>
     <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="56" t="str">
-        <x:v>B26</x:v>
-      </x:c>
-      <x:c r="B30" s="57" t="str">
-        <x:v>Step 11B · Admin</x:v>
-      </x:c>
-      <x:c r="C30" s="57" t="str">
-        <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
-      </x:c>
-      <x:c r="D30" s="57" t="str">
+      <x:c r="A30" s="66" t="str">
+        <x:v>B31</x:v>
+      </x:c>
+      <x:c r="B30" s="67" t="str">
+        <x:v>Step 12 · Quality</x:v>
+      </x:c>
+      <x:c r="C30" s="67" t="str">
+        <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
+      </x:c>
+      <x:c r="D30" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E30" s="57" t="str">
+      <x:c r="E30" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="57" t="str">
+      <x:c r="F30" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="57" t="str">
+      <x:c r="G30" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="58"/>
-      <x:c r="I30" s="58"/>
-      <x:c r="J30" s="57"/>
-      <x:c r="K30" s="57"/>
-      <x:c r="L30" s="57"/>
-      <x:c r="M30" s="57"/>
+      <x:c r="H30" s="68"/>
+      <x:c r="I30" s="68"/>
+      <x:c r="J30" s="67"/>
+      <x:c r="K30" s="67"/>
+      <x:c r="L30" s="67"/>
+      <x:c r="M30" s="67"/>
     </x:row>
     <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="56" t="str">
-        <x:v>B27</x:v>
-      </x:c>
-      <x:c r="B31" s="57" t="str">
-        <x:v>Step 11B · Admin</x:v>
-      </x:c>
-      <x:c r="C31" s="57" t="str">
-        <x:v>Admin user management, audit log and sensitive action authorization</x:v>
-      </x:c>
-      <x:c r="D31" s="57" t="str">
+      <x:c r="A31" s="66" t="str">
+        <x:v>B32</x:v>
+      </x:c>
+      <x:c r="B31" s="67" t="str">
+        <x:v>Step 12 · Security</x:v>
+      </x:c>
+      <x:c r="C31" s="67" t="str">
+        <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
+      </x:c>
+      <x:c r="D31" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E31" s="57" t="str">
+      <x:c r="E31" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="57" t="str">
+      <x:c r="F31" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="57" t="str">
+      <x:c r="G31" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="58"/>
-      <x:c r="I31" s="58"/>
-      <x:c r="J31" s="57"/>
-      <x:c r="K31" s="57"/>
-      <x:c r="L31" s="57"/>
-      <x:c r="M31" s="57"/>
+      <x:c r="H31" s="68"/>
+      <x:c r="I31" s="68"/>
+      <x:c r="J31" s="67"/>
+      <x:c r="K31" s="67"/>
+      <x:c r="L31" s="67"/>
+      <x:c r="M31" s="67"/>
     </x:row>
     <x:row r="32" ht="26" customHeight="1">
-      <x:c r="A32" s="56" t="str">
-        <x:v>B30</x:v>
-      </x:c>
-      <x:c r="B32" s="57" t="str">
-        <x:v>Step 12 · Deploy</x:v>
-      </x:c>
-      <x:c r="C32" s="57" t="str">
-        <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
-      </x:c>
-      <x:c r="D32" s="57" t="str">
+      <x:c r="A32" s="66" t="str">
+        <x:v>B33</x:v>
+      </x:c>
+      <x:c r="B32" s="67" t="str">
+        <x:v>Step 7 · Owners</x:v>
+      </x:c>
+      <x:c r="C32" s="67" t="str">
+        <x:v>Home-value and service enquiry data handling</x:v>
+      </x:c>
+      <x:c r="D32" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E32" s="57" t="str">
+      <x:c r="E32" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="57" t="str">
+      <x:c r="F32" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G32" s="57" t="str">
+      <x:c r="G32" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H32" s="58"/>
-      <x:c r="I32" s="58"/>
-      <x:c r="J32" s="57"/>
-      <x:c r="K32" s="57"/>
-      <x:c r="L32" s="57"/>
-      <x:c r="M32" s="57"/>
+      <x:c r="H32" s="68"/>
+      <x:c r="I32" s="68"/>
+      <x:c r="J32" s="67"/>
+      <x:c r="K32" s="67"/>
+      <x:c r="L32" s="67"/>
+      <x:c r="M32" s="67"/>
     </x:row>
     <x:row r="33" ht="26" customHeight="1">
-      <x:c r="A33" s="56" t="str">
-        <x:v>B31</x:v>
-      </x:c>
-      <x:c r="B33" s="57" t="str">
-        <x:v>Step 12 · Quality</x:v>
-      </x:c>
-      <x:c r="C33" s="57" t="str">
-        <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
-      </x:c>
-      <x:c r="D33" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E33" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F33" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G33" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A33" s="56"/>
+      <x:c r="B33" s="57"/>
+      <x:c r="C33" s="57"/>
+      <x:c r="D33" s="57"/>
+      <x:c r="E33" s="57"/>
+      <x:c r="F33" s="57"/>
+      <x:c r="G33" s="57"/>
       <x:c r="H33" s="58"/>
       <x:c r="I33" s="58"/>
       <x:c r="J33" s="57"/>
@@ -10171,27 +10291,13 @@
       <x:c r="M33" s="57"/>
     </x:row>
     <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="56" t="str">
-        <x:v>B32</x:v>
-      </x:c>
-      <x:c r="B34" s="57" t="str">
-        <x:v>Step 12 · Security</x:v>
-      </x:c>
-      <x:c r="C34" s="57" t="str">
-        <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
-      </x:c>
-      <x:c r="D34" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E34" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F34" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G34" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A34" s="56"/>
+      <x:c r="B34" s="57"/>
+      <x:c r="C34" s="57"/>
+      <x:c r="D34" s="57"/>
+      <x:c r="E34" s="57"/>
+      <x:c r="F34" s="57"/>
+      <x:c r="G34" s="57"/>
       <x:c r="H34" s="58"/>
       <x:c r="I34" s="58"/>
       <x:c r="J34" s="57"/>
@@ -10200,27 +10306,13 @@
       <x:c r="M34" s="57"/>
     </x:row>
     <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="56" t="str">
-        <x:v>B33</x:v>
-      </x:c>
-      <x:c r="B35" s="57" t="str">
-        <x:v>Step 7 · Owners</x:v>
-      </x:c>
-      <x:c r="C35" s="57" t="str">
-        <x:v>Home-value and service enquiry data handling</x:v>
-      </x:c>
-      <x:c r="D35" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E35" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F35" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G35" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A35" s="56"/>
+      <x:c r="B35" s="57"/>
+      <x:c r="C35" s="57"/>
+      <x:c r="D35" s="57"/>
+      <x:c r="E35" s="57"/>
+      <x:c r="F35" s="57"/>
+      <x:c r="G35" s="57"/>
       <x:c r="H35" s="58"/>
       <x:c r="I35" s="58"/>
       <x:c r="J35" s="57"/>
@@ -17209,27 +17301,30 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="18" priority="1">
+    <x:cfRule type="expression" dxfId="36" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="19" priority="2">
+    <x:cfRule type="expression" dxfId="37" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="20" priority="3">
+    <x:cfRule type="expression" dxfId="38" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="E36:E40">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="E6:E35">
+    <x:dataValidation type="list" sqref="E33:E35">
+      <x:formula1>"Done,Pending,Not started"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E6:E32">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2317a333e2f4812"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56204676537644da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17269,7 +17364,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
+        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -17284,14 +17379,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -17310,7 +17405,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -17355,236 +17450,236 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="56" t="str">
+      <x:c r="A6" s="66" t="str">
         <x:v>E01</x:v>
       </x:c>
-      <x:c r="B6" s="57" t="str">
+      <x:c r="B6" s="67" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C6" s="57" t="str">
+      <x:c r="C6" s="67" t="str">
         <x:v>Enquiry notification with retryable queue/outbox</x:v>
       </x:c>
-      <x:c r="D6" s="57" t="str">
+      <x:c r="D6" s="67" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E6" s="57" t="str">
+      <x:c r="E6" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F6" s="57" t="str">
+      <x:c r="F6" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G6" s="57" t="str">
+      <x:c r="G6" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H6" s="58"/>
-      <x:c r="I6" s="58"/>
-      <x:c r="J6" s="57"/>
-      <x:c r="K6" s="57"/>
-      <x:c r="L6" s="57"/>
-      <x:c r="M6" s="57"/>
+      <x:c r="H6" s="68"/>
+      <x:c r="I6" s="68"/>
+      <x:c r="J6" s="67"/>
+      <x:c r="K6" s="67"/>
+      <x:c r="L6" s="67"/>
+      <x:c r="M6" s="67"/>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="56" t="str">
+      <x:c r="A7" s="66" t="str">
         <x:v>E02</x:v>
       </x:c>
-      <x:c r="B7" s="57" t="str">
+      <x:c r="B7" s="67" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C7" s="57" t="str">
+      <x:c r="C7" s="67" t="str">
         <x:v>Thai and English buyer enquiry acknowledgments</x:v>
       </x:c>
-      <x:c r="D7" s="57" t="str">
+      <x:c r="D7" s="67" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E7" s="57" t="str">
+      <x:c r="E7" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F7" s="57" t="str">
+      <x:c r="F7" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G7" s="57" t="str">
+      <x:c r="G7" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H7" s="58"/>
-      <x:c r="I7" s="58"/>
-      <x:c r="J7" s="57"/>
-      <x:c r="K7" s="57"/>
-      <x:c r="L7" s="57"/>
-      <x:c r="M7" s="57"/>
+      <x:c r="H7" s="68"/>
+      <x:c r="I7" s="68"/>
+      <x:c r="J7" s="67"/>
+      <x:c r="K7" s="67"/>
+      <x:c r="L7" s="67"/>
+      <x:c r="M7" s="67"/>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="56" t="str">
+      <x:c r="A8" s="66" t="str">
         <x:v>E03</x:v>
       </x:c>
-      <x:c r="B8" s="57" t="str">
+      <x:c r="B8" s="67" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C8" s="57" t="str">
+      <x:c r="C8" s="67" t="str">
         <x:v>Project brochure/price list email delivery</x:v>
       </x:c>
-      <x:c r="D8" s="57" t="str">
+      <x:c r="D8" s="67" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E8" s="57" t="str">
+      <x:c r="E8" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F8" s="57" t="str">
+      <x:c r="F8" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G8" s="57" t="str">
+      <x:c r="G8" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H8" s="58"/>
-      <x:c r="I8" s="58"/>
-      <x:c r="J8" s="57"/>
-      <x:c r="K8" s="57"/>
-      <x:c r="L8" s="57"/>
-      <x:c r="M8" s="57"/>
+      <x:c r="H8" s="68"/>
+      <x:c r="I8" s="68"/>
+      <x:c r="J8" s="67"/>
+      <x:c r="K8" s="67"/>
+      <x:c r="L8" s="67"/>
+      <x:c r="M8" s="67"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="56" t="str">
+      <x:c r="A9" s="66" t="str">
         <x:v>E04</x:v>
       </x:c>
-      <x:c r="B9" s="57" t="str">
+      <x:c r="B9" s="67" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C9" s="57" t="str">
+      <x:c r="C9" s="67" t="str">
         <x:v>Site visit request and confirmation notifications</x:v>
       </x:c>
-      <x:c r="D9" s="57" t="str">
+      <x:c r="D9" s="67" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E9" s="57" t="str">
+      <x:c r="E9" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F9" s="57" t="str">
+      <x:c r="F9" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G9" s="57" t="str">
+      <x:c r="G9" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H9" s="58"/>
-      <x:c r="I9" s="58"/>
-      <x:c r="J9" s="57"/>
-      <x:c r="K9" s="57"/>
-      <x:c r="L9" s="57"/>
-      <x:c r="M9" s="57"/>
+      <x:c r="H9" s="68"/>
+      <x:c r="I9" s="68"/>
+      <x:c r="J9" s="67"/>
+      <x:c r="K9" s="67"/>
+      <x:c r="L9" s="67"/>
+      <x:c r="M9" s="67"/>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="56" t="str">
+      <x:c r="A10" s="66" t="str">
         <x:v>E05</x:v>
       </x:c>
-      <x:c r="B10" s="57" t="str">
+      <x:c r="B10" s="67" t="str">
         <x:v>Step 9 · Alerts</x:v>
       </x:c>
-      <x:c r="C10" s="57" t="str">
+      <x:c r="C10" s="67" t="str">
         <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
       </x:c>
-      <x:c r="D10" s="57" t="str">
+      <x:c r="D10" s="67" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E10" s="57" t="str">
+      <x:c r="E10" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F10" s="57" t="str">
+      <x:c r="F10" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G10" s="57" t="str">
+      <x:c r="G10" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H10" s="58"/>
-      <x:c r="I10" s="58"/>
-      <x:c r="J10" s="57"/>
-      <x:c r="K10" s="57"/>
-      <x:c r="L10" s="57"/>
-      <x:c r="M10" s="57"/>
+      <x:c r="H10" s="68"/>
+      <x:c r="I10" s="68"/>
+      <x:c r="J10" s="67"/>
+      <x:c r="K10" s="67"/>
+      <x:c r="L10" s="67"/>
+      <x:c r="M10" s="67"/>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="56" t="str">
+      <x:c r="A11" s="66" t="str">
         <x:v>E06</x:v>
       </x:c>
-      <x:c r="B11" s="57" t="str">
+      <x:c r="B11" s="67" t="str">
         <x:v>Step 10B · Email</x:v>
       </x:c>
-      <x:c r="C11" s="57" t="str">
+      <x:c r="C11" s="67" t="str">
         <x:v>Account verification and recovery messages if email auth approved</x:v>
       </x:c>
-      <x:c r="D11" s="57" t="str">
+      <x:c r="D11" s="67" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E11" s="57" t="str">
+      <x:c r="E11" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F11" s="57" t="str">
+      <x:c r="F11" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G11" s="57" t="str">
+      <x:c r="G11" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H11" s="58"/>
-      <x:c r="I11" s="58"/>
-      <x:c r="J11" s="57"/>
-      <x:c r="K11" s="57"/>
-      <x:c r="L11" s="57"/>
-      <x:c r="M11" s="57"/>
+      <x:c r="H11" s="68"/>
+      <x:c r="I11" s="68"/>
+      <x:c r="J11" s="67"/>
+      <x:c r="K11" s="67"/>
+      <x:c r="L11" s="67"/>
+      <x:c r="M11" s="67"/>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="56" t="str">
+      <x:c r="A12" s="66" t="str">
         <x:v>E07</x:v>
       </x:c>
-      <x:c r="B12" s="57" t="str">
+      <x:c r="B12" s="67" t="str">
         <x:v>Step 11B · Email</x:v>
       </x:c>
-      <x:c r="C12" s="57" t="str">
+      <x:c r="C12" s="67" t="str">
         <x:v>Agent notification/routing administration</x:v>
       </x:c>
-      <x:c r="D12" s="57" t="str">
+      <x:c r="D12" s="67" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E12" s="57" t="str">
+      <x:c r="E12" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F12" s="57" t="str">
+      <x:c r="F12" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G12" s="57" t="str">
+      <x:c r="G12" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H12" s="58"/>
-      <x:c r="I12" s="58"/>
-      <x:c r="J12" s="57"/>
-      <x:c r="K12" s="57"/>
-      <x:c r="L12" s="57"/>
-      <x:c r="M12" s="57"/>
+      <x:c r="H12" s="68"/>
+      <x:c r="I12" s="68"/>
+      <x:c r="J12" s="67"/>
+      <x:c r="K12" s="67"/>
+      <x:c r="L12" s="67"/>
+      <x:c r="M12" s="67"/>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="56" t="str">
+      <x:c r="A13" s="66" t="str">
         <x:v>E08</x:v>
       </x:c>
-      <x:c r="B13" s="57" t="str">
+      <x:c r="B13" s="67" t="str">
         <x:v>Step 7 · Email</x:v>
       </x:c>
-      <x:c r="C13" s="57" t="str">
+      <x:c r="C13" s="67" t="str">
         <x:v>Home valuation and service enquiry replies</x:v>
       </x:c>
-      <x:c r="D13" s="57" t="str">
+      <x:c r="D13" s="67" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E13" s="57" t="str">
+      <x:c r="E13" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="57" t="str">
+      <x:c r="F13" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G13" s="57" t="str">
+      <x:c r="G13" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H13" s="58"/>
-      <x:c r="I13" s="58"/>
-      <x:c r="J13" s="57"/>
-      <x:c r="K13" s="57"/>
-      <x:c r="L13" s="57"/>
-      <x:c r="M13" s="57"/>
+      <x:c r="H13" s="68"/>
+      <x:c r="I13" s="68"/>
+      <x:c r="J13" s="67"/>
+      <x:c r="K13" s="67"/>
+      <x:c r="L13" s="67"/>
+      <x:c r="M13" s="67"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="44"/>
@@ -24897,13 +24992,13 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="21" priority="1">
+    <x:cfRule type="expression" dxfId="39" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="22" priority="2">
+    <x:cfRule type="expression" dxfId="40" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="23" priority="3">
+    <x:cfRule type="expression" dxfId="41" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -24914,7 +25009,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R585041451a67453f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf923c7a382534c0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24954,7 +25049,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
+        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -24969,14 +25064,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -24995,7 +25090,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -25040,365 +25135,636 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="61" t="str">
+      <x:c r="A6" s="69" t="str">
         <x:v>B34</x:v>
       </x:c>
-      <x:c r="B6" s="61" t="str">
+      <x:c r="B6" s="69" t="str">
         <x:v>Step 1 · Health</x:v>
       </x:c>
-      <x:c r="C6" s="61" t="str">
+      <x:c r="C6" s="69" t="str">
         <x:v>Basic /api/health endpoint with accurate application and database status</x:v>
       </x:c>
-      <x:c r="D6" s="61" t="str">
+      <x:c r="D6" s="69" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E6" s="61" t="str">
+      <x:c r="E6" s="69" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F6" s="61" t="str">
+      <x:c r="F6" s="69" t="str">
         <x:v>Real /api/health now probes the migrated public view rather than an empty database select 1. Actual 200/ready true, stopped-DB 503/unavailable/ready false and recovery to 200 verified.</x:v>
       </x:c>
-      <x:c r="G6" s="61" t="str">
+      <x:c r="G6" s="69" t="str">
         <x:v>Codex: retain truthful readiness and generic errors; start localhost only under owner/test authorization.</x:v>
       </x:c>
-      <x:c r="H6" s="62" t="d">
+      <x:c r="H6" s="70" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="62" t="d">
+      <x:c r="I6" s="70" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="61" t="str">
+      <x:c r="J6" s="69" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="61" t="str">
+      <x:c r="K6" s="69" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="61" t="str">
+      <x:c r="L6" s="69" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="61" t="str">
+      <x:c r="M6" s="69" t="str">
         <x:v>2026-10-09: Health API planned. No implementation in Step 0.
 2026-10-09 foundation: Real health API implemented: HTTP 200 app ok, database not_configured, ready false before closure. Configured PostgreSQL is probed with Drizzle select 1; failure returns 503. No real database configuration exists. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Real /api/health now probes the migrated public view rather than an empty database select 1. Actual 200/ready true, stopped-DB 503/unavailable/ready false and recovery to 200 verified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="310" customHeight="1">
-      <x:c r="A7" s="61" t="str">
+      <x:c r="A7" s="69" t="str">
         <x:v>B01</x:v>
       </x:c>
-      <x:c r="B7" s="61" t="str">
+      <x:c r="B7" s="69" t="str">
         <x:v>Step 2 · Database</x:v>
       </x:c>
-      <x:c r="C7" s="61" t="str">
+      <x:c r="C7" s="69" t="str">
         <x:v>PostgreSQL/Drizzle schema for listings, projects, agents and users</x:v>
       </x:c>
-      <x:c r="D7" s="61" t="str">
+      <x:c r="D7" s="69" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E7" s="61" t="str">
+      <x:c r="E7" s="69" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F7" s="61" t="str">
+      <x:c r="F7" s="69" t="str">
         <x:v>18-table Drizzle schema implemented with bilingual fields, seven property types, sale/rent rules, explicit price visibility and separate non-superuser migration/read-only app roles. Isolated local development/test PostgreSQL configured; no shared service modified.</x:v>
       </x:c>
-      <x:c r="G7" s="61" t="str">
+      <x:c r="G7" s="69" t="str">
         <x:v>Codex: preserve schema/security contracts in later explicitly authorized stages.</x:v>
       </x:c>
-      <x:c r="H7" s="62" t="d">
+      <x:c r="H7" s="70" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="62" t="d">
+      <x:c r="I7" s="70" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="61" t="str">
+      <x:c r="J7" s="69" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K7" s="61" t="str">
+      <x:c r="K7" s="69" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L7" s="61" t="str">
+      <x:c r="L7" s="69" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="61" t="str">
+      <x:c r="M7" s="69" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: 18-table Drizzle schema implemented with bilingual fields, seven property types, sale/rent rules, explicit price visibility and separate non-superuser migration/read-only app roles. Isolated local development/test PostgreSQL configured; no shared service modified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="310" customHeight="1">
-      <x:c r="A8" s="61" t="str">
+      <x:c r="A8" s="69" t="str">
         <x:v>B02</x:v>
       </x:c>
-      <x:c r="B8" s="61" t="str">
+      <x:c r="B8" s="69" t="str">
         <x:v>Step 2 · Database</x:v>
       </x:c>
-      <x:c r="C8" s="61" t="str">
+      <x:c r="C8" s="69" t="str">
         <x:v>Migrations, foreign keys, constraints and rollback procedure</x:v>
       </x:c>
-      <x:c r="D8" s="61" t="str">
+      <x:c r="D8" s="69" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="61" t="str">
+      <x:c r="E8" s="69" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F8" s="61" t="str">
+      <x:c r="F8" s="69" t="str">
         <x:v>Generated foundation and custom relational migrations, journal/snapshots, constraints/FKs/triggers and guarded test-only initial rollback implemented. Real pg_dump/committed rollback/pg_restore/rerun pass. No production migration performed.</x:v>
       </x:c>
-      <x:c r="G8" s="61" t="str">
+      <x:c r="G8" s="69" t="str">
         <x:v>Codex: generate reviewed additive migrations for later changes; production migration requires authorization and verified backup.</x:v>
       </x:c>
-      <x:c r="H8" s="62" t="d">
+      <x:c r="H8" s="70" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I8" s="62" t="d">
+      <x:c r="I8" s="70" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="61" t="str">
+      <x:c r="J8" s="69" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K8" s="61" t="str">
+      <x:c r="K8" s="69" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L8" s="61" t="str">
+      <x:c r="L8" s="69" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M8" s="61" t="str">
+      <x:c r="M8" s="69" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Generated foundation and custom relational migrations, journal/snapshots, constraints/FKs/triggers and guarded test-only initial rollback implemented. Real pg_dump/committed rollback/pg_restore/rerun pass. No production migration performed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="310" customHeight="1">
-      <x:c r="A9" s="61" t="str">
+      <x:c r="A9" s="69" t="str">
         <x:v>B03</x:v>
       </x:c>
-      <x:c r="B9" s="61" t="str">
+      <x:c r="B9" s="69" t="str">
         <x:v>Step 2 · Demo</x:v>
       </x:c>
-      <x:c r="C9" s="61" t="str">
+      <x:c r="C9" s="69" t="str">
         <x:v>Clearly fictional seed listings, projects and agents</x:v>
       </x:c>
-      <x:c r="D9" s="61" t="str">
+      <x:c r="D9" s="69" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E9" s="61" t="str">
+      <x:c r="E9" s="69" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F9" s="61" t="str">
+      <x:c r="F9" s="69" t="str">
         <x:v>Repeatable local-only seed: 14 explicitly fictional listings, seven types/both intents and related demo records. Invalid domains, disabled users/agents, closed enquiries and off alerts. Public projection excludes demo inventory; no real prices/agents advertised.</x:v>
       </x:c>
-      <x:c r="G9" s="61" t="str">
+      <x:c r="G9" s="69" t="str">
         <x:v>Codex: keep demo data labelled and excluded from genuine inventory; seed only named local dev/test databases.</x:v>
       </x:c>
-      <x:c r="H9" s="62" t="d">
+      <x:c r="H9" s="70" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I9" s="62" t="d">
+      <x:c r="I9" s="70" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J9" s="61" t="str">
+      <x:c r="J9" s="69" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K9" s="61" t="str">
+      <x:c r="K9" s="69" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L9" s="61" t="str">
+      <x:c r="L9" s="69" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M9" s="61" t="str">
+      <x:c r="M9" s="69" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Repeatable local-only seed: 14 explicitly fictional listings, seven types/both intents and related demo records. Invalid domains, disabled users/agents, closed enquiries and off alerts. Public projection excludes demo inventory; no real prices/agents advertised. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="61" t="str">
+      <x:c r="A10" s="69" t="str">
         <x:v>B04</x:v>
       </x:c>
-      <x:c r="B10" s="61" t="str">
+      <x:c r="B10" s="69" t="str">
         <x:v>Step 2 · Search</x:v>
       </x:c>
-      <x:c r="C10" s="61" t="str">
+      <x:c r="C10" s="69" t="str">
         <x:v>Indexes for status, intent, type, price, location and title</x:v>
       </x:c>
-      <x:c r="D10" s="61" t="str">
+      <x:c r="D10" s="69" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="61" t="str">
+      <x:c r="E10" s="69" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F10" s="61" t="str">
+      <x:c r="F10" s="69" t="str">
         <x:v>Intent/type/status/price, location/status, bounding coordinates, publication/feed and bilingual simple-text indexes implemented. Catalog and EXPLAIN use checks pass. Tiny-seed plans prove indexes are usable, not production speed.</x:v>
       </x:c>
-      <x:c r="G10" s="61" t="str">
+      <x:c r="G10" s="69" t="str">
         <x:v>Codex: use parameterized typed queries in Step 3; profile against realistic volume during later QA.</x:v>
       </x:c>
-      <x:c r="H10" s="62" t="d">
+      <x:c r="H10" s="70" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="62" t="d">
+      <x:c r="I10" s="70" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="61" t="str">
+      <x:c r="J10" s="69" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="61" t="str">
+      <x:c r="K10" s="69" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="61" t="str">
+      <x:c r="L10" s="69" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="61" t="str">
+      <x:c r="M10" s="69" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Intent/type/status/price, location/status, bounding coordinates, publication/feed and bilingual simple-text indexes implemented. Catalog and EXPLAIN use checks pass. Tiny-seed plans prove indexes are usable, not production speed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="44"/>
-      <x:c r="B11" s="44"/>
-      <x:c r="C11" s="44"/>
-      <x:c r="D11" s="44"/>
-      <x:c r="E11" s="44"/>
-      <x:c r="F11" s="44"/>
-      <x:c r="G11" s="44"/>
-      <x:c r="H11" s="45"/>
-      <x:c r="I11" s="45"/>
-      <x:c r="J11" s="44"/>
-      <x:c r="K11" s="44"/>
-      <x:c r="L11" s="44"/>
-      <x:c r="M11" s="44"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="44"/>
-      <x:c r="B12" s="44"/>
-      <x:c r="C12" s="44"/>
-      <x:c r="D12" s="44"/>
-      <x:c r="E12" s="44"/>
-      <x:c r="F12" s="44"/>
-      <x:c r="G12" s="44"/>
-      <x:c r="H12" s="45"/>
-      <x:c r="I12" s="45"/>
-      <x:c r="J12" s="44"/>
-      <x:c r="K12" s="44"/>
-      <x:c r="L12" s="44"/>
-      <x:c r="M12" s="44"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="44"/>
-      <x:c r="B13" s="44"/>
-      <x:c r="C13" s="44"/>
-      <x:c r="D13" s="44"/>
-      <x:c r="E13" s="44"/>
-      <x:c r="F13" s="44"/>
-      <x:c r="G13" s="44"/>
-      <x:c r="H13" s="45"/>
-      <x:c r="I13" s="45"/>
-      <x:c r="J13" s="44"/>
-      <x:c r="K13" s="44"/>
-      <x:c r="L13" s="44"/>
-      <x:c r="M13" s="44"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="44"/>
-      <x:c r="B14" s="44"/>
-      <x:c r="C14" s="44"/>
-      <x:c r="D14" s="44"/>
-      <x:c r="E14" s="44"/>
-      <x:c r="F14" s="44"/>
-      <x:c r="G14" s="44"/>
-      <x:c r="H14" s="45"/>
-      <x:c r="I14" s="45"/>
-      <x:c r="J14" s="44"/>
-      <x:c r="K14" s="44"/>
-      <x:c r="L14" s="44"/>
-      <x:c r="M14" s="44"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="44"/>
-      <x:c r="B15" s="44"/>
-      <x:c r="C15" s="44"/>
-      <x:c r="D15" s="44"/>
-      <x:c r="E15" s="44"/>
-      <x:c r="F15" s="44"/>
-      <x:c r="G15" s="44"/>
-      <x:c r="H15" s="45"/>
-      <x:c r="I15" s="45"/>
-      <x:c r="J15" s="44"/>
-      <x:c r="K15" s="44"/>
-      <x:c r="L15" s="44"/>
-      <x:c r="M15" s="44"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="44"/>
-      <x:c r="B16" s="44"/>
-      <x:c r="C16" s="44"/>
-      <x:c r="D16" s="44"/>
-      <x:c r="E16" s="44"/>
-      <x:c r="F16" s="44"/>
-      <x:c r="G16" s="44"/>
-      <x:c r="H16" s="45"/>
-      <x:c r="I16" s="45"/>
-      <x:c r="J16" s="44"/>
-      <x:c r="K16" s="44"/>
-      <x:c r="L16" s="44"/>
-      <x:c r="M16" s="44"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="44"/>
-      <x:c r="B17" s="44"/>
-      <x:c r="C17" s="44"/>
-      <x:c r="D17" s="44"/>
-      <x:c r="E17" s="44"/>
-      <x:c r="F17" s="44"/>
-      <x:c r="G17" s="44"/>
-      <x:c r="H17" s="45"/>
-      <x:c r="I17" s="45"/>
-      <x:c r="J17" s="44"/>
-      <x:c r="K17" s="44"/>
-      <x:c r="L17" s="44"/>
-      <x:c r="M17" s="44"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="44"/>
-      <x:c r="B18" s="44"/>
-      <x:c r="C18" s="44"/>
-      <x:c r="D18" s="44"/>
-      <x:c r="E18" s="44"/>
-      <x:c r="F18" s="44"/>
-      <x:c r="G18" s="44"/>
-      <x:c r="H18" s="45"/>
-      <x:c r="I18" s="45"/>
-      <x:c r="J18" s="44"/>
-      <x:c r="K18" s="44"/>
-      <x:c r="L18" s="44"/>
-      <x:c r="M18" s="44"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="44"/>
-      <x:c r="B19" s="44"/>
-      <x:c r="C19" s="44"/>
-      <x:c r="D19" s="44"/>
-      <x:c r="E19" s="44"/>
-      <x:c r="F19" s="44"/>
-      <x:c r="G19" s="44"/>
-      <x:c r="H19" s="45"/>
-      <x:c r="I19" s="45"/>
-      <x:c r="J19" s="44"/>
-      <x:c r="K19" s="44"/>
-      <x:c r="L19" s="44"/>
-      <x:c r="M19" s="44"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="44"/>
-      <x:c r="B20" s="44"/>
-      <x:c r="C20" s="44"/>
-      <x:c r="D20" s="44"/>
-      <x:c r="E20" s="44"/>
-      <x:c r="F20" s="44"/>
-      <x:c r="G20" s="44"/>
-      <x:c r="H20" s="45"/>
-      <x:c r="I20" s="45"/>
-      <x:c r="J20" s="44"/>
-      <x:c r="K20" s="44"/>
-      <x:c r="L20" s="44"/>
-      <x:c r="M20" s="44"/>
+    <x:row r="11" ht="400" customHeight="1">
+      <x:c r="A11" s="69" t="str">
+        <x:v>F08</x:v>
+      </x:c>
+      <x:c r="B11" s="69" t="str">
+        <x:v>Step 3 · Cards</x:v>
+      </x:c>
+      <x:c r="C11" s="69" t="str">
+        <x:v>Realtor-style 3:2 listing cards, photo controls, bottom-right save heart, facts/address and Contact agent dialog trigger</x:v>
+      </x:c>
+      <x:c r="D11" s="69" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E11" s="69" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F11" s="69" t="str">
+        <x:v>One V3 Realtor-style card: 3:2 photo, five-photo arrows/dots/native swipe, pill badges, persistent device save heart, type-specific facts, honest THB/gated price and drop, two-line address and accessible contact dialog. No fabricated real photos/agents; submit remains unavailable until Step 6.</x:v>
+      </x:c>
+      <x:c r="G11" s="69" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H11" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I11" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J11" s="69" t="str">
+        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+      <x:c r="K11" s="69" t="str">
+        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
+      </x:c>
+      <x:c r="L11" s="69" t="str">
+        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
+      </x:c>
+      <x:c r="M11" s="69" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 V5 adoption: V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.
+2026-10-09 Step 3: One V3 Realtor-style card: 3:2 photo, five-photo arrows/dots/native swipe, pill badges, persistent device save heart, type-specific facts, honest THB/gated price and drop, two-line address and accessible contact dialog. No fabricated real photos/agents; submit remains unavailable until Step 6. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="400" customHeight="1">
+      <x:c r="A12" s="69" t="str">
+        <x:v>F09</x:v>
+      </x:c>
+      <x:c r="B12" s="69" t="str">
+        <x:v>Step 3 · Results</x:v>
+      </x:c>
+      <x:c r="C12" s="69" t="str">
+        <x:v>Responsive /buy, /rent and /invest results layouts</x:v>
+      </x:c>
+      <x:c r="D12" s="69" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E12" s="69" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F12" s="69" t="str">
+        <x:v>Server-rendered /th and /en buy/rent/invest routes. Two desktop card columns, one phone column; empty state, readable heading and cumulative Show more homes. Reserved blank desktop map column; no fake map. Property link reaches an explicit unfinished detail route, not an implemented Step 5 page.</x:v>
+      </x:c>
+      <x:c r="G12" s="69" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H12" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I12" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J12" s="69" t="str">
+        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+      <x:c r="K12" s="69" t="str">
+        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
+      </x:c>
+      <x:c r="L12" s="69" t="str">
+        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
+      </x:c>
+      <x:c r="M12" s="69" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 3: Server-rendered /th and /en buy/rent/invest routes. Two desktop card columns, one phone column; empty state, readable heading and cumulative Show more homes. Reserved blank desktop map column; no fake map. Property link reaches an explicit unfinished detail route, not an implemented Step 5 page. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="400" customHeight="1">
+      <x:c r="A13" s="69" t="str">
+        <x:v>F10</x:v>
+      </x:c>
+      <x:c r="B13" s="69" t="str">
+        <x:v>Step 3 · Filters</x:v>
+      </x:c>
+      <x:c r="C13" s="69" t="str">
+        <x:v>Shared URL filters, active chips, sorting and navigation history</x:v>
+      </x:c>
+      <x:c r="D13" s="69" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E13" s="69" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F13" s="69" t="str">
+        <x:v>Shared validated URL state for homepage/results; active chips, Clear all, sorting and cumulative page state. Applied changes use Next router.push without full reload to preserve meaningful back/forward history; uncommitted popup drafts do not change URLs. Refresh/back/forward tested.</x:v>
+      </x:c>
+      <x:c r="G13" s="69" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H13" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I13" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J13" s="69" t="str">
+        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+      <x:c r="K13" s="69" t="str">
+        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
+      </x:c>
+      <x:c r="L13" s="69" t="str">
+        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
+      </x:c>
+      <x:c r="M13" s="69" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 3: Shared validated URL state for homepage/results; active chips, Clear all, sorting and cumulative page state. Applied changes use Next router.push without full reload to preserve meaningful back/forward history; uncommitted popup drafts do not change URLs. Refresh/back/forward tested. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="400" customHeight="1">
+      <x:c r="A14" s="69" t="str">
+        <x:v>F11</x:v>
+      </x:c>
+      <x:c r="B14" s="69" t="str">
+        <x:v>Step 3 · Filters</x:v>
+      </x:c>
+      <x:c r="C14" s="69" t="str">
+        <x:v>Desktop popovers for price, beds, type and advanced filters</x:v>
+      </x:c>
+      <x:c r="D14" s="69" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E14" s="69" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F14" s="69" t="str">
+        <x:v>Accessible native-dialog desktop popovers for location, intent, price, beds, property types and advanced/DB-defined typed filters. Actual metadata options and live price count tested; Escape, focus trapping and focus restoration verified.</x:v>
+      </x:c>
+      <x:c r="G14" s="69" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H14" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I14" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J14" s="69" t="str">
+        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+      <x:c r="K14" s="69" t="str">
+        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
+      </x:c>
+      <x:c r="L14" s="69" t="str">
+        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
+      </x:c>
+      <x:c r="M14" s="69" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 3: Accessible native-dialog desktop popovers for location, intent, price, beds, property types and advanced/DB-defined typed filters. Actual metadata options and live price count tested; Escape, focus trapping and focus restoration verified. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="400" customHeight="1">
+      <x:c r="A15" s="69" t="str">
+        <x:v>F12</x:v>
+      </x:c>
+      <x:c r="B15" s="69" t="str">
+        <x:v>Step 3 · Filters</x:v>
+      </x:c>
+      <x:c r="C15" s="69" t="str">
+        <x:v>Phone full-screen filter sheet, Apply and Clear</x:v>
+      </x:c>
+      <x:c r="D15" s="69" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E15" s="69" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F15" s="69" t="str">
+        <x:v>Phone full-screen filter sheets with Apply/Clear, labels, focus controls and no page overflow. Native Chromium phone input proves card swipe; UI checked at 390/768/1024/1440 in Thai/English.</x:v>
+      </x:c>
+      <x:c r="G15" s="69" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H15" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I15" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J15" s="69" t="str">
+        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+      <x:c r="K15" s="69" t="str">
+        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
+      </x:c>
+      <x:c r="L15" s="69" t="str">
+        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
+      </x:c>
+      <x:c r="M15" s="69" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 3: Phone full-screen filter sheets with Apply/Clear, labels, focus controls and no page overflow. Native Chromium phone input proves card swipe; UI checked at 390/768/1024/1440 in Thai/English. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="400" customHeight="1">
+      <x:c r="A16" s="69" t="str">
+        <x:v>F13</x:v>
+      </x:c>
+      <x:c r="B16" s="69" t="str">
+        <x:v>Step 3 · Search</x:v>
+      </x:c>
+      <x:c r="C16" s="69" t="str">
+        <x:v>Database-derived price histogram and live result count</x:v>
+      </x:c>
+      <x:c r="D16" s="69" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E16" s="69" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F16" s="69" t="str">
+        <x:v>Histogram uses actual matching PUBLIC-price rows, excluding only current min/max range. Gated prices are excluded from price predicates, price ordering and histogram. Debounced actual API count and bounded deterministic queries implemented.</x:v>
+      </x:c>
+      <x:c r="G16" s="69" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H16" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I16" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J16" s="69" t="str">
+        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+      <x:c r="K16" s="69" t="str">
+        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
+      </x:c>
+      <x:c r="L16" s="69" t="str">
+        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
+      </x:c>
+      <x:c r="M16" s="69" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 3: Histogram uses actual matching PUBLIC-price rows, excluding only current min/max range. Gated prices are excluded from price predicates, price ordering and histogram. Debounced actual API count and bounded deterministic queries implemented. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="400" customHeight="1">
+      <x:c r="A17" s="69" t="str">
+        <x:v>B05</x:v>
+      </x:c>
+      <x:c r="B17" s="69" t="str">
+        <x:v>Step 2 · Filters</x:v>
+      </x:c>
+      <x:c r="C17" s="69" t="str">
+        <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
+      </x:c>
+      <x:c r="D17" s="69" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E17" s="69" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F17" s="69" t="str">
+        <x:v>Existing typed filter definition/option/value tables are consumed safely by results. Only active metadata in the selected genuine/demo partition is exposed. Single/multi/number/boolean kinds, allowed options and property scope validated with parameterized SQL. Production admin CRUD remains Step 11.</x:v>
+      </x:c>
+      <x:c r="G17" s="69" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H17" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I17" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J17" s="69" t="str">
+        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+      <x:c r="K17" s="69" t="str">
+        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
+      </x:c>
+      <x:c r="L17" s="69" t="str">
+        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
+      </x:c>
+      <x:c r="M17" s="69" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 3: Existing typed filter definition/option/value tables are consumed safely by results. Only active metadata in the selected genuine/demo partition is exposed. Single/multi/number/boolean kinds, allowed options and property scope validated with parameterized SQL. Production admin CRUD remains Step 11. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="400" customHeight="1">
+      <x:c r="A18" s="69" t="str">
+        <x:v>B06</x:v>
+      </x:c>
+      <x:c r="B18" s="69" t="str">
+        <x:v>Step 3 · Search</x:v>
+      </x:c>
+      <x:c r="C18" s="69" t="str">
+        <x:v>Typed validated listing/search data access and pagination</x:v>
+      </x:c>
+      <x:c r="D18" s="69" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E18" s="69" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F18" s="69" t="str">
+        <x:v>Server-only bounded, parameterized listing queries and GET /api/listings: sale/rent/invest, location hierarchy/station slugs, beds/baths/size/land/year/amenities/project, sorting/pagination. No contacts, exact hidden location or gated prices in result DTOs. Local demo requires explicit flag and named local DB/trusted Host.</x:v>
+      </x:c>
+      <x:c r="G18" s="69" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H18" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I18" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J18" s="69" t="str">
+        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+      <x:c r="K18" s="69" t="str">
+        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
+      </x:c>
+      <x:c r="L18" s="69" t="str">
+        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
+      </x:c>
+      <x:c r="M18" s="69" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 3: Server-only bounded, parameterized listing queries and GET /api/listings: sale/rent/invest, location hierarchy/station slugs, beds/baths/size/land/year/amenities/project, sorting/pagination. No contacts, exact hidden location or gated prices in result DTOs. Local demo requires explicit flag and named local DB/trusted Host. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="400" customHeight="1">
+      <x:c r="A19" s="69" t="str">
+        <x:v>B07</x:v>
+      </x:c>
+      <x:c r="B19" s="69" t="str">
+        <x:v>Step 3 · Search</x:v>
+      </x:c>
+      <x:c r="C19" s="69" t="str">
+        <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
+      </x:c>
+      <x:c r="D19" s="69" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E19" s="69" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F19" s="69" t="str">
+        <x:v>Validated shared URL parser, actual counts/sort/histogram and DB metadata filters. Additive 0002_station_search_slug migration provides unique non-null station slugs. Real pre-migration development backup, three-migration rerun and isolated dump/rollback/restore regression passed. Demo search seed rerun is idempotent.</x:v>
+      </x:c>
+      <x:c r="G19" s="69" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H19" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I19" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J19" s="69" t="str">
+        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+      <x:c r="K19" s="69" t="str">
+        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
+      </x:c>
+      <x:c r="L19" s="69" t="str">
+        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
+      </x:c>
+      <x:c r="M19" s="69" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 3: Validated shared URL parser, actual counts/sort/histogram and DB metadata filters. Additive 0002_station_search_slug migration provides unique non-null station slugs. Real pre-migration development backup, three-migration rerun and isolated dump/rollback/restore regression passed. Demo search seed rerun is idempotent. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="400" customHeight="1">
+      <x:c r="A20" s="69" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="B20" s="69" t="str">
+        <x:v>Step 3 · Accessibility</x:v>
+      </x:c>
+      <x:c r="C20" s="69" t="str">
+        <x:v>Fix contact autofocus and swipe/keyboard link handling (F01/F08)</x:v>
+      </x:c>
+      <x:c r="D20" s="69" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E20" s="69" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F20" s="69" t="str">
+        <x:v>Fix linked to F01/F08: dialog autofocus now occurs after native showModal and preserves the trigger for restoration. Swipe cancels only the immediate synthetic pointer click, allowing subsequent keyboard Enter. Streaming-page keyboard test waits for visible focused links. All affected regressions pass.</x:v>
+      </x:c>
+      <x:c r="G20" s="69" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H20" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I20" s="70" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J20" s="69" t="str">
+        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
+      <x:c r="K20" s="69" t="str">
+        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
+      </x:c>
+      <x:c r="L20" s="69" t="str">
+        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
+      </x:c>
+      <x:c r="M20" s="69" t="str">
+        <x:v>2026-10-09 discovered during Step 3 real browser testing: contact input lacked focus; swipe suppression blocked the next keyboard activation. Linked to F01/F08.
+2026-10-09 Step 3: Fix linked to F01/F08: dialog autofocus now occurs after native showModal and preserves the trigger for restoration. Swipe cancels only the immediate synthetic pointer click, allowing subsequent keyboard Enter. Streaming-page keyboard test waits for visible focused links. All affected regressions pass. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="44"/>
@@ -32606,24 +32972,24 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="24" priority="1">
+    <x:cfRule type="expression" dxfId="42" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="25" priority="2">
+    <x:cfRule type="expression" dxfId="43" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="26" priority="3">
+    <x:cfRule type="expression" dxfId="44" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E10">
+    <x:dataValidation type="list" sqref="E6:E20">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfeedefc58826454b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27d186b9c102497d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32663,7 +33029,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
+        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -32678,14 +33044,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -32704,7 +33070,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -32749,43 +33115,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="50" t="str">
+      <x:c r="A6" s="63" t="str">
         <x:v>F02</x:v>
       </x:c>
-      <x:c r="B6" s="51" t="str">
+      <x:c r="B6" s="64" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="51" t="str">
+      <x:c r="C6" s="64" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent</x:v>
       </x:c>
-      <x:c r="D6" s="51" t="str">
+      <x:c r="D6" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="51" t="str">
+      <x:c r="E6" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="51" t="str">
+      <x:c r="F6" s="64" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G6" s="51" t="str">
+      <x:c r="G6" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H6" s="52" t="d">
+      <x:c r="H6" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="52" t="d">
+      <x:c r="I6" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="51" t="str">
+      <x:c r="J6" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="51" t="str">
+      <x:c r="K6" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="51" t="str">
+      <x:c r="L6" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="51" t="str">
+      <x:c r="M6" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
 2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.
 2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.
@@ -32794,368 +33160,368 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="250" customHeight="1">
-      <x:c r="A7" s="50" t="str">
+      <x:c r="A7" s="63" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B7" s="51" t="str">
+      <x:c r="B7" s="64" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C7" s="51" t="str">
+      <x:c r="C7" s="64" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D7" s="51" t="str">
+      <x:c r="D7" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="51" t="str">
+      <x:c r="E7" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="51" t="str">
+      <x:c r="F7" s="64" t="str">
         <x:v>Approved temporary crest extracted and implemented. Owner will provide final header logo later.</x:v>
       </x:c>
-      <x:c r="G7" s="51" t="str">
+      <x:c r="G7" s="64" t="str">
         <x:v>Owner: supply final asset/version later; Codex: replace only approved logo.</x:v>
       </x:c>
-      <x:c r="H7" s="52" t="d">
+      <x:c r="H7" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="52" t="d">
+      <x:c r="I7" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="51" t="str">
+      <x:c r="J7" s="64" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K7" s="51" t="str">
+      <x:c r="K7" s="64" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L7" s="51" t="str">
+      <x:c r="L7" s="64" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="51" t="str">
+      <x:c r="M7" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
 2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.
 2026-10-09 foundation: Approved temporary crest extracted and implemented. Owner will provide final header logo later. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="50" t="str">
+      <x:c r="A8" s="63" t="str">
         <x:v>F32</x:v>
       </x:c>
-      <x:c r="B8" s="51" t="str">
+      <x:c r="B8" s="64" t="str">
         <x:v>Step 10A · Wireframe</x:v>
       </x:c>
-      <x:c r="C8" s="51" t="str">
+      <x:c r="C8" s="64" t="str">
         <x:v>Owner-approved login/register/account wireframe before coding</x:v>
       </x:c>
-      <x:c r="D8" s="51" t="str">
+      <x:c r="D8" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="51" t="str">
+      <x:c r="E8" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="51" t="str">
+      <x:c r="F8" s="64" t="str">
         <x:v>Admin/account screens are not part of approved V3 visuals</x:v>
       </x:c>
-      <x:c r="G8" s="51" t="str">
+      <x:c r="G8" s="64" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H8" s="52"/>
-      <x:c r="I8" s="52"/>
-      <x:c r="J8" s="51"/>
-      <x:c r="K8" s="51"/>
-      <x:c r="L8" s="51"/>
-      <x:c r="M8" s="51"/>
+      <x:c r="H8" s="65"/>
+      <x:c r="I8" s="65"/>
+      <x:c r="J8" s="64"/>
+      <x:c r="K8" s="64"/>
+      <x:c r="L8" s="64"/>
+      <x:c r="M8" s="64"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="50" t="str">
+      <x:c r="A9" s="63" t="str">
         <x:v>F34</x:v>
       </x:c>
-      <x:c r="B9" s="51" t="str">
+      <x:c r="B9" s="64" t="str">
         <x:v>Step 11A · Wireframe</x:v>
       </x:c>
-      <x:c r="C9" s="51" t="str">
+      <x:c r="C9" s="64" t="str">
         <x:v>Owner-approved responsive admin dashboard wireframe</x:v>
       </x:c>
-      <x:c r="D9" s="51" t="str">
+      <x:c r="D9" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="51" t="str">
+      <x:c r="E9" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="51" t="str">
+      <x:c r="F9" s="64" t="str">
         <x:v>Admin UI not included in V3; design approval required</x:v>
       </x:c>
-      <x:c r="G9" s="51" t="str">
+      <x:c r="G9" s="64" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H9" s="52"/>
-      <x:c r="I9" s="52"/>
-      <x:c r="J9" s="51"/>
-      <x:c r="K9" s="51"/>
-      <x:c r="L9" s="51"/>
-      <x:c r="M9" s="51"/>
+      <x:c r="H9" s="65"/>
+      <x:c r="I9" s="65"/>
+      <x:c r="J9" s="64"/>
+      <x:c r="K9" s="64"/>
+      <x:c r="L9" s="64"/>
+      <x:c r="M9" s="64"/>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="50" t="str">
+      <x:c r="A10" s="63" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B10" s="51" t="str">
+      <x:c r="B10" s="64" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C10" s="51" t="str">
+      <x:c r="C10" s="64" t="str">
         <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
-      <x:c r="D10" s="51" t="str">
+      <x:c r="D10" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="51" t="str">
+      <x:c r="E10" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="51" t="str">
+      <x:c r="F10" s="64" t="str">
         <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
-      <x:c r="G10" s="51" t="str">
+      <x:c r="G10" s="64" t="str">
         <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
       </x:c>
-      <x:c r="H10" s="52" t="d">
+      <x:c r="H10" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="52" t="d">
+      <x:c r="I10" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="51" t="str">
+      <x:c r="J10" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="51" t="str">
+      <x:c r="K10" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="51" t="str">
+      <x:c r="L10" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="51" t="str">
+      <x:c r="M10" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
 2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
 2026-10-09 Step 2: Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="50" t="str">
+      <x:c r="A11" s="63" t="str">
         <x:v>B17</x:v>
       </x:c>
-      <x:c r="B11" s="51" t="str">
+      <x:c r="B11" s="64" t="str">
         <x:v>Decision · Leads</x:v>
       </x:c>
-      <x:c r="C11" s="51" t="str">
+      <x:c r="C11" s="64" t="str">
         <x:v>Approve shared inbox versus listing agent enquiry destination</x:v>
       </x:c>
-      <x:c r="D11" s="51" t="str">
+      <x:c r="D11" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E11" s="51" t="str">
+      <x:c r="E11" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="51" t="str">
+      <x:c r="F11" s="64" t="str">
         <x:v>BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
-      <x:c r="G11" s="51" t="str">
+      <x:c r="G11" s="64" t="str">
         <x:v>Owner: select routing mode and mailbox</x:v>
       </x:c>
-      <x:c r="H11" s="52"/>
-      <x:c r="I11" s="52"/>
-      <x:c r="J11" s="51"/>
-      <x:c r="K11" s="51"/>
-      <x:c r="L11" s="51"/>
-      <x:c r="M11" s="51"/>
+      <x:c r="H11" s="65"/>
+      <x:c r="I11" s="65"/>
+      <x:c r="J11" s="64"/>
+      <x:c r="K11" s="64"/>
+      <x:c r="L11" s="64"/>
+      <x:c r="M11" s="64"/>
     </x:row>
     <x:row r="12" ht="250" customHeight="1">
-      <x:c r="A12" s="50" t="str">
+      <x:c r="A12" s="63" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B12" s="51" t="str">
+      <x:c r="B12" s="64" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C12" s="51" t="str">
+      <x:c r="C12" s="64" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D12" s="51" t="str">
+      <x:c r="D12" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E12" s="51" t="str">
+      <x:c r="E12" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="51" t="str">
+      <x:c r="F12" s="64" t="str">
         <x:v>Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending.</x:v>
       </x:c>
-      <x:c r="G12" s="51" t="str">
+      <x:c r="G12" s="64" t="str">
         <x:v>Owner: provide actual contacts/routing; Codex: integrate and review accessible contact actions later.</x:v>
       </x:c>
-      <x:c r="H12" s="52" t="d">
+      <x:c r="H12" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="52" t="d">
+      <x:c r="I12" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="51" t="str">
+      <x:c r="J12" s="64" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K12" s="51" t="str">
+      <x:c r="K12" s="64" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L12" s="51" t="str">
+      <x:c r="L12" s="64" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="51" t="str">
+      <x:c r="M12" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #4 unresolved
 2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.
 2026-10-09 foundation: Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="50" t="str">
+      <x:c r="A13" s="63" t="str">
         <x:v>B23</x:v>
       </x:c>
-      <x:c r="B13" s="51" t="str">
+      <x:c r="B13" s="64" t="str">
         <x:v>Decision · Accounts</x:v>
       </x:c>
-      <x:c r="C13" s="51" t="str">
+      <x:c r="C13" s="64" t="str">
         <x:v>Approve LINE only or LINE+Google+email sign-in</x:v>
       </x:c>
-      <x:c r="D13" s="51" t="str">
+      <x:c r="D13" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E13" s="51" t="str">
+      <x:c r="E13" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F13" s="51" t="str">
+      <x:c r="F13" s="64" t="str">
         <x:v>BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
-      <x:c r="G13" s="51" t="str">
+      <x:c r="G13" s="64" t="str">
         <x:v>Owner: approve authentication providers</x:v>
       </x:c>
-      <x:c r="H13" s="52"/>
-      <x:c r="I13" s="52"/>
-      <x:c r="J13" s="51"/>
-      <x:c r="K13" s="51"/>
-      <x:c r="L13" s="51"/>
-      <x:c r="M13" s="51"/>
+      <x:c r="H13" s="65"/>
+      <x:c r="I13" s="65"/>
+      <x:c r="J13" s="64"/>
+      <x:c r="K13" s="64"/>
+      <x:c r="L13" s="64"/>
+      <x:c r="M13" s="64"/>
     </x:row>
     <x:row r="14" ht="200" customHeight="1">
-      <x:c r="A14" s="50" t="str">
+      <x:c r="A14" s="63" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B14" s="51" t="str">
+      <x:c r="B14" s="64" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C14" s="51" t="str">
+      <x:c r="C14" s="64" t="str">
         <x:v>Approve THB only versus optional approximate FX display</x:v>
       </x:c>
-      <x:c r="D14" s="51" t="str">
+      <x:c r="D14" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E14" s="51" t="str">
+      <x:c r="E14" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="51" t="str">
+      <x:c r="F14" s="64" t="str">
         <x:v>Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
-      <x:c r="G14" s="51" t="str">
+      <x:c r="G14" s="64" t="str">
         <x:v>Codex: implement USD/THB during authorized currency work; confirm rate source.</x:v>
       </x:c>
-      <x:c r="H14" s="52"/>
-      <x:c r="I14" s="52" t="d">
+      <x:c r="H14" s="65"/>
+      <x:c r="I14" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="51" t="str">
+      <x:c r="J14" s="64" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K14" s="51" t="str">
+      <x:c r="K14" s="64" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L14" s="51" t="str">
+      <x:c r="L14" s="64" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M14" s="51" t="str">
+      <x:c r="M14" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #6 unresolved
 2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="200" customHeight="1">
-      <x:c r="A15" s="50" t="str">
+      <x:c r="A15" s="63" t="str">
         <x:v>B29</x:v>
       </x:c>
-      <x:c r="B15" s="51" t="str">
+      <x:c r="B15" s="64" t="str">
         <x:v>Decision · Projects</x:v>
       </x:c>
-      <x:c r="C15" s="51" t="str">
+      <x:c r="C15" s="64" t="str">
         <x:v>Approve public project prices versus enquiry-only price list</x:v>
       </x:c>
-      <x:c r="D15" s="51" t="str">
+      <x:c r="D15" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E15" s="51" t="str">
+      <x:c r="E15" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F15" s="51" t="str">
+      <x:c r="F15" s="64" t="str">
         <x:v>Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
-      <x:c r="G15" s="51" t="str">
+      <x:c r="G15" s="64" t="str">
         <x:v>Codex: add per-record price visibility in authorized backend/admin work after admin wireframe approval.</x:v>
       </x:c>
-      <x:c r="H15" s="52"/>
-      <x:c r="I15" s="52" t="d">
+      <x:c r="H15" s="65"/>
+      <x:c r="I15" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J15" s="51" t="str">
+      <x:c r="J15" s="64" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K15" s="51" t="str">
+      <x:c r="K15" s="64" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L15" s="51" t="str">
+      <x:c r="L15" s="64" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M15" s="51" t="str">
+      <x:c r="M15" s="64" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #7 unresolved
 2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="310" customHeight="1">
-      <x:c r="A16" s="51" t="str">
+      <x:c r="A16" s="64" t="str">
         <x:v>R01</x:v>
       </x:c>
-      <x:c r="B16" s="51" t="str">
+      <x:c r="B16" s="64" t="str">
         <x:v>Step 0 · Preparation</x:v>
       </x:c>
-      <x:c r="C16" s="51" t="str">
+      <x:c r="C16" s="64" t="str">
         <x:v>Inspect project; establish permanent rules, documentation, Git/live mirror and tracker</x:v>
       </x:c>
-      <x:c r="D16" s="51" t="str">
+      <x:c r="D16" s="64" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E16" s="51" t="str">
+      <x:c r="E16" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F16" s="51" t="str">
+      <x:c r="F16" s="64" t="str">
         <x:v>Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request.</x:v>
       </x:c>
-      <x:c r="G16" s="51" t="str">
+      <x:c r="G16" s="64" t="str">
         <x:v>Codex: close the separate Step 0 utility/reference-review requirements only when authorized; stop before Step 3.</x:v>
       </x:c>
-      <x:c r="H16" s="52" t="d">
+      <x:c r="H16" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I16" s="52" t="d">
+      <x:c r="I16" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J16" s="51" t="str">
+      <x:c r="J16" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K16" s="51" t="str">
+      <x:c r="K16" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L16" s="51" t="str">
+      <x:c r="L16" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M16" s="51" t="str">
+      <x:c r="M16" s="64" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
@@ -33163,47 +33529,48 @@
 2026-10-09 V5 adoption: V5 adopted as active stage guide; updated owner-supplied V3 references preserved. No new application step started. Existing foundation Pending: browser tests deferred by owner; PostgreSQL unconfigured. Preview is open at owner request.
 2026-10-09 Step 2: Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
 2026-10-09 tracker formatting: workbook recreated with yellow Pending, light green Done and red Not started rows and status tabs. All 81 permanent IDs and prior task history preserved. Step 3 is authorized but implementation has not begun; owner requested the Excel first.
-2026-10-09 Claude handoff: owner requested CLAUDE.md to share the current project context with Claude. Documented sources, Git/live paths, implemented shell/Step 2, unimplemented authorized Step 3, open decisions, safety, tests, servers and completion gates. Documentation/link checks and workbook ID/history/colour checks pass. No application change or new runtime test is claimed. R01 remains Pending for existing Step 0 blockers; Git/live synchronization and push are verified during finalization.</x:v>
+2026-10-09 Claude handoff: owner requested CLAUDE.md to share the current project context with Claude. Documented sources, Git/live paths, implemented shell/Step 2, unimplemented authorized Step 3, open decisions, safety, tests, servers and completion gates. Documentation/link checks and workbook ID/history/colour checks pass. No application change or new runtime test is claimed. R01 remains Pending for existing Step 0 blockers; Git/live synchronization and push are verified during finalization.
+2026-10-09 Step 3 completed only after its gates. F08-F13/B05-B07 and R02 record current proof. Existing Step 0 blockers remain Pending; no duplicate preparation ID or fabricated rendered-reference comparison. All nine maintained Markdown updated; approved source files preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="310" customHeight="1">
-      <x:c r="A17" s="51" t="str">
+      <x:c r="A17" s="64" t="str">
         <x:v>F01</x:v>
       </x:c>
-      <x:c r="B17" s="51" t="str">
+      <x:c r="B17" s="64" t="str">
         <x:v>Step 1 · Design</x:v>
       </x:c>
-      <x:c r="C17" s="51" t="str">
+      <x:c r="C17" s="64" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives</x:v>
       </x:c>
-      <x:c r="D17" s="51" t="str">
+      <x:c r="D17" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="51" t="str">
+      <x:c r="E17" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F17" s="51" t="str">
+      <x:c r="F17" s="64" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G17" s="51" t="str">
+      <x:c r="G17" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H17" s="52" t="d">
+      <x:c r="H17" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I17" s="52" t="d">
+      <x:c r="I17" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J17" s="51" t="str">
+      <x:c r="J17" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K17" s="51" t="str">
+      <x:c r="K17" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L17" s="51" t="str">
+      <x:c r="L17" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M17" s="51" t="str">
+      <x:c r="M17" s="64" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33211,43 +33578,43 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="310" customHeight="1">
-      <x:c r="A18" s="51" t="str">
+      <x:c r="A18" s="64" t="str">
         <x:v>F04</x:v>
       </x:c>
-      <x:c r="B18" s="51" t="str">
+      <x:c r="B18" s="64" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C18" s="51" t="str">
+      <x:c r="C18" s="64" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in</x:v>
       </x:c>
-      <x:c r="D18" s="51" t="str">
+      <x:c r="D18" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="51" t="str">
+      <x:c r="E18" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F18" s="51" t="str">
+      <x:c r="F18" s="64" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G18" s="51" t="str">
+      <x:c r="G18" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H18" s="52" t="d">
+      <x:c r="H18" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I18" s="52" t="d">
+      <x:c r="I18" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J18" s="51" t="str">
+      <x:c r="J18" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K18" s="51" t="str">
+      <x:c r="K18" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L18" s="51" t="str">
+      <x:c r="L18" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M18" s="51" t="str">
+      <x:c r="M18" s="64" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33255,43 +33622,43 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="310" customHeight="1">
-      <x:c r="A19" s="51" t="str">
+      <x:c r="A19" s="64" t="str">
         <x:v>F05</x:v>
       </x:c>
-      <x:c r="B19" s="51" t="str">
+      <x:c r="B19" s="64" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C19" s="51" t="str">
+      <x:c r="C19" s="64" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints</x:v>
       </x:c>
-      <x:c r="D19" s="51" t="str">
+      <x:c r="D19" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="51" t="str">
+      <x:c r="E19" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F19" s="51" t="str">
+      <x:c r="F19" s="64" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G19" s="51" t="str">
+      <x:c r="G19" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H19" s="52" t="d">
+      <x:c r="H19" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I19" s="52" t="d">
+      <x:c r="I19" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J19" s="51" t="str">
+      <x:c r="J19" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K19" s="51" t="str">
+      <x:c r="K19" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L19" s="51" t="str">
+      <x:c r="L19" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M19" s="51" t="str">
+      <x:c r="M19" s="64" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33299,43 +33666,43 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="310" customHeight="1">
-      <x:c r="A20" s="51" t="str">
+      <x:c r="A20" s="64" t="str">
         <x:v>F06</x:v>
       </x:c>
-      <x:c r="B20" s="51" t="str">
+      <x:c r="B20" s="64" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C20" s="51" t="str">
+      <x:c r="C20" s="64" t="str">
         <x:v>Light footer, company links, contact and PDPA link</x:v>
       </x:c>
-      <x:c r="D20" s="51" t="str">
+      <x:c r="D20" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="51" t="str">
+      <x:c r="E20" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F20" s="51" t="str">
+      <x:c r="F20" s="64" t="str">
         <x:v>Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G20" s="51" t="str">
+      <x:c r="G20" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H20" s="52" t="d">
+      <x:c r="H20" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I20" s="52" t="d">
+      <x:c r="I20" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J20" s="51" t="str">
+      <x:c r="J20" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K20" s="51" t="str">
+      <x:c r="K20" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L20" s="51" t="str">
+      <x:c r="L20" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M20" s="51" t="str">
+      <x:c r="M20" s="64" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33343,43 +33710,43 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="310" customHeight="1">
-      <x:c r="A21" s="51" t="str">
+      <x:c r="A21" s="64" t="str">
         <x:v>F07</x:v>
       </x:c>
-      <x:c r="B21" s="51" t="str">
+      <x:c r="B21" s="64" t="str">
         <x:v>Step 1 · i18n</x:v>
       </x:c>
-      <x:c r="C21" s="51" t="str">
+      <x:c r="C21" s="64" t="str">
         <x:v>Thai/English routes, language switch and localized formatting</x:v>
       </x:c>
-      <x:c r="D21" s="51" t="str">
+      <x:c r="D21" s="64" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="51" t="str">
+      <x:c r="E21" s="64" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F21" s="51" t="str">
+      <x:c r="F21" s="64" t="str">
         <x:v>Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G21" s="51" t="str">
+      <x:c r="G21" s="64" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H21" s="52" t="d">
+      <x:c r="H21" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I21" s="52" t="d">
+      <x:c r="I21" s="65" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J21" s="51" t="str">
+      <x:c r="J21" s="64" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K21" s="51" t="str">
+      <x:c r="K21" s="64" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L21" s="51" t="str">
+      <x:c r="L21" s="64" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M21" s="51" t="str">
+      <x:c r="M21" s="64" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -40577,13 +40944,13 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="27" priority="1">
+    <x:cfRule type="expression" dxfId="45" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="28" priority="2">
+    <x:cfRule type="expression" dxfId="46" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="29" priority="3">
+    <x:cfRule type="expression" dxfId="47" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -40597,7 +40964,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re737f28ca1634620"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcafe3d4607aa4b42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40637,7 +41004,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09 | Yellow: Pending; light green: Done; red: Not started. 81 permanent IDs: 5 Done, 16 Pending, 60 Not started. Category tabs show open tasks; status tabs retain all tasks and history.</x:v>
+        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -40652,14 +41019,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -40678,7 +41045,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -40723,1539 +41090,1514 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="250" customHeight="1">
-      <x:c r="A6" s="56" t="str">
-        <x:v>F08</x:v>
-      </x:c>
-      <x:c r="B6" s="57" t="str">
-        <x:v>Step 3 · Cards</x:v>
-      </x:c>
-      <x:c r="C6" s="57" t="str">
-        <x:v>Realtor-style 3:2 listing cards, photo controls, bottom-right save heart, facts/address and Contact agent dialog trigger</x:v>
-      </x:c>
-      <x:c r="D6" s="57" t="str">
+      <x:c r="A6" s="66" t="str">
+        <x:v>F14</x:v>
+      </x:c>
+      <x:c r="B6" s="67" t="str">
+        <x:v>Step 4 · Map</x:v>
+      </x:c>
+      <x:c r="C6" s="67" t="str">
+        <x:v>Desktop listing/map split and hover/focus pin synchronization</x:v>
+      </x:c>
+      <x:c r="D6" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="57" t="str">
+      <x:c r="E6" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F6" s="57" t="str">
-        <x:v>V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
-      </x:c>
-      <x:c r="G6" s="57" t="str">
-        <x:v>Codex: build revised card only under Step 3 authorization, after the real database step.</x:v>
-      </x:c>
-      <x:c r="H6" s="58"/>
-      <x:c r="I6" s="58" t="d">
+      <x:c r="F6" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G6" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H6" s="68"/>
+      <x:c r="I6" s="68"/>
+      <x:c r="J6" s="67"/>
+      <x:c r="K6" s="67"/>
+      <x:c r="L6" s="67"/>
+      <x:c r="M6" s="67"/>
+    </x:row>
+    <x:row r="7" ht="26" customHeight="1">
+      <x:c r="A7" s="66" t="str">
+        <x:v>F15</x:v>
+      </x:c>
+      <x:c r="B7" s="67" t="str">
+        <x:v>Step 4 · Map</x:v>
+      </x:c>
+      <x:c r="C7" s="67" t="str">
+        <x:v>Phone full-screen Map/List toggle</x:v>
+      </x:c>
+      <x:c r="D7" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E7" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F7" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G7" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H7" s="68"/>
+      <x:c r="I7" s="68"/>
+      <x:c r="J7" s="67"/>
+      <x:c r="K7" s="67"/>
+      <x:c r="L7" s="67"/>
+      <x:c r="M7" s="67"/>
+    </x:row>
+    <x:row r="8" ht="26" customHeight="1">
+      <x:c r="A8" s="66" t="str">
+        <x:v>F16</x:v>
+      </x:c>
+      <x:c r="B8" s="67" t="str">
+        <x:v>Step 5 · Property</x:v>
+      </x:c>
+      <x:c r="C8" s="67" t="str">
+        <x:v>Property detail photo grid and full-screen gallery</x:v>
+      </x:c>
+      <x:c r="D8" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E8" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F8" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G8" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H8" s="68"/>
+      <x:c r="I8" s="68"/>
+      <x:c r="J8" s="67"/>
+      <x:c r="K8" s="67"/>
+      <x:c r="L8" s="67"/>
+      <x:c r="M8" s="67"/>
+    </x:row>
+    <x:row r="9" ht="26" customHeight="1">
+      <x:c r="A9" s="66" t="str">
+        <x:v>F17</x:v>
+      </x:c>
+      <x:c r="B9" s="67" t="str">
+        <x:v>Step 5 · Property</x:v>
+      </x:c>
+      <x:c r="C9" s="67" t="str">
+        <x:v>Title, pricing, type-specific facts, long description and sticky tabs</x:v>
+      </x:c>
+      <x:c r="D9" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E9" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F9" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G9" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H9" s="68"/>
+      <x:c r="I9" s="68"/>
+      <x:c r="J9" s="67"/>
+      <x:c r="K9" s="67"/>
+      <x:c r="L9" s="67"/>
+      <x:c r="M9" s="67"/>
+    </x:row>
+    <x:row r="10" ht="26" customHeight="1">
+      <x:c r="A10" s="66" t="str">
+        <x:v>F18</x:v>
+      </x:c>
+      <x:c r="B10" s="67" t="str">
+        <x:v>Step 5 · Property</x:v>
+      </x:c>
+      <x:c r="C10" s="67" t="str">
+        <x:v>Floorplan/video/360 tabs, verified nearby information and map</x:v>
+      </x:c>
+      <x:c r="D10" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E10" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F10" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G10" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H10" s="68"/>
+      <x:c r="I10" s="68"/>
+      <x:c r="J10" s="67"/>
+      <x:c r="K10" s="67"/>
+      <x:c r="L10" s="67"/>
+      <x:c r="M10" s="67"/>
+    </x:row>
+    <x:row r="11" ht="26" customHeight="1">
+      <x:c r="A11" s="66" t="str">
+        <x:v>F19</x:v>
+      </x:c>
+      <x:c r="B11" s="67" t="str">
+        <x:v>Step 5 · Property</x:v>
+      </x:c>
+      <x:c r="C11" s="67" t="str">
+        <x:v>Mortgage calculator and area comparison when real data exists</x:v>
+      </x:c>
+      <x:c r="D11" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E11" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F11" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G11" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H11" s="68"/>
+      <x:c r="I11" s="68"/>
+      <x:c r="J11" s="67"/>
+      <x:c r="K11" s="67"/>
+      <x:c r="L11" s="67"/>
+      <x:c r="M11" s="67"/>
+    </x:row>
+    <x:row r="12" ht="26" customHeight="1">
+      <x:c r="A12" s="66" t="str">
+        <x:v>F20</x:v>
+      </x:c>
+      <x:c r="B12" s="67" t="str">
+        <x:v>Step 5 · Property</x:v>
+      </x:c>
+      <x:c r="C12" s="67" t="str">
+        <x:v>Same-project units and similar-property cards</x:v>
+      </x:c>
+      <x:c r="D12" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E12" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F12" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G12" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H12" s="68"/>
+      <x:c r="I12" s="68"/>
+      <x:c r="J12" s="67"/>
+      <x:c r="K12" s="67"/>
+      <x:c r="L12" s="67"/>
+      <x:c r="M12" s="67"/>
+    </x:row>
+    <x:row r="13" ht="26" customHeight="1">
+      <x:c r="A13" s="66" t="str">
+        <x:v>F21</x:v>
+      </x:c>
+      <x:c r="B13" s="67" t="str">
+        <x:v>Step 6 · Contact</x:v>
+      </x:c>
+      <x:c r="C13" s="67" t="str">
+        <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
+      </x:c>
+      <x:c r="D13" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E13" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F13" s="67" t="str">
+        <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
+      </x:c>
+      <x:c r="G13" s="67" t="str">
+        <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
+      </x:c>
+      <x:c r="H13" s="68"/>
+      <x:c r="I13" s="68" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="57" t="str">
+      <x:c r="J13" s="67" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K6" s="57" t="str">
+      <x:c r="K13" s="67" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L6" s="57" t="str">
+      <x:c r="L13" s="67" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M6" s="57" t="str">
-        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 V5 adoption: V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="56" t="str">
-        <x:v>F09</x:v>
-      </x:c>
-      <x:c r="B7" s="57" t="str">
-        <x:v>Step 3 · Results</x:v>
-      </x:c>
-      <x:c r="C7" s="57" t="str">
-        <x:v>Responsive /buy, /rent and /invest results layouts</x:v>
-      </x:c>
-      <x:c r="D7" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E7" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F7" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G7" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H7" s="58"/>
-      <x:c r="I7" s="58"/>
-      <x:c r="J7" s="57"/>
-      <x:c r="K7" s="57"/>
-      <x:c r="L7" s="57"/>
-      <x:c r="M7" s="57"/>
-    </x:row>
-    <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="56" t="str">
-        <x:v>F10</x:v>
-      </x:c>
-      <x:c r="B8" s="57" t="str">
-        <x:v>Step 3 · Filters</x:v>
-      </x:c>
-      <x:c r="C8" s="57" t="str">
-        <x:v>Shared URL filters, active chips, sorting and navigation history</x:v>
-      </x:c>
-      <x:c r="D8" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E8" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F8" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G8" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H8" s="58"/>
-      <x:c r="I8" s="58"/>
-      <x:c r="J8" s="57"/>
-      <x:c r="K8" s="57"/>
-      <x:c r="L8" s="57"/>
-      <x:c r="M8" s="57"/>
-    </x:row>
-    <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="56" t="str">
-        <x:v>F11</x:v>
-      </x:c>
-      <x:c r="B9" s="57" t="str">
-        <x:v>Step 3 · Filters</x:v>
-      </x:c>
-      <x:c r="C9" s="57" t="str">
-        <x:v>Desktop popovers for price, beds, type and advanced filters</x:v>
-      </x:c>
-      <x:c r="D9" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E9" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F9" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G9" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H9" s="58"/>
-      <x:c r="I9" s="58"/>
-      <x:c r="J9" s="57"/>
-      <x:c r="K9" s="57"/>
-      <x:c r="L9" s="57"/>
-      <x:c r="M9" s="57"/>
-    </x:row>
-    <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="56" t="str">
-        <x:v>F12</x:v>
-      </x:c>
-      <x:c r="B10" s="57" t="str">
-        <x:v>Step 3 · Filters</x:v>
-      </x:c>
-      <x:c r="C10" s="57" t="str">
-        <x:v>Phone full-screen filter sheet, Apply and Clear</x:v>
-      </x:c>
-      <x:c r="D10" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E10" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F10" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G10" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H10" s="58"/>
-      <x:c r="I10" s="58"/>
-      <x:c r="J10" s="57"/>
-      <x:c r="K10" s="57"/>
-      <x:c r="L10" s="57"/>
-      <x:c r="M10" s="57"/>
-    </x:row>
-    <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="56" t="str">
-        <x:v>F13</x:v>
-      </x:c>
-      <x:c r="B11" s="57" t="str">
-        <x:v>Step 3 · Search</x:v>
-      </x:c>
-      <x:c r="C11" s="57" t="str">
-        <x:v>Database-derived price histogram and live result count</x:v>
-      </x:c>
-      <x:c r="D11" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E11" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F11" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G11" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H11" s="58"/>
-      <x:c r="I11" s="58"/>
-      <x:c r="J11" s="57"/>
-      <x:c r="K11" s="57"/>
-      <x:c r="L11" s="57"/>
-      <x:c r="M11" s="57"/>
-    </x:row>
-    <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="56" t="str">
-        <x:v>F14</x:v>
-      </x:c>
-      <x:c r="B12" s="57" t="str">
-        <x:v>Step 4 · Map</x:v>
-      </x:c>
-      <x:c r="C12" s="57" t="str">
-        <x:v>Desktop listing/map split and hover/focus pin synchronization</x:v>
-      </x:c>
-      <x:c r="D12" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E12" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F12" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G12" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H12" s="58"/>
-      <x:c r="I12" s="58"/>
-      <x:c r="J12" s="57"/>
-      <x:c r="K12" s="57"/>
-      <x:c r="L12" s="57"/>
-      <x:c r="M12" s="57"/>
-    </x:row>
-    <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="56" t="str">
-        <x:v>F15</x:v>
-      </x:c>
-      <x:c r="B13" s="57" t="str">
-        <x:v>Step 4 · Map</x:v>
-      </x:c>
-      <x:c r="C13" s="57" t="str">
-        <x:v>Phone full-screen Map/List toggle</x:v>
-      </x:c>
-      <x:c r="D13" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E13" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F13" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G13" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H13" s="58"/>
-      <x:c r="I13" s="58"/>
-      <x:c r="J13" s="57"/>
-      <x:c r="K13" s="57"/>
-      <x:c r="L13" s="57"/>
-      <x:c r="M13" s="57"/>
-    </x:row>
-    <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="56" t="str">
-        <x:v>F16</x:v>
-      </x:c>
-      <x:c r="B14" s="57" t="str">
-        <x:v>Step 5 · Property</x:v>
-      </x:c>
-      <x:c r="C14" s="57" t="str">
-        <x:v>Property detail photo grid and full-screen gallery</x:v>
-      </x:c>
-      <x:c r="D14" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E14" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F14" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G14" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H14" s="58"/>
-      <x:c r="I14" s="58"/>
-      <x:c r="J14" s="57"/>
-      <x:c r="K14" s="57"/>
-      <x:c r="L14" s="57"/>
-      <x:c r="M14" s="57"/>
-    </x:row>
-    <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="56" t="str">
-        <x:v>F17</x:v>
-      </x:c>
-      <x:c r="B15" s="57" t="str">
-        <x:v>Step 5 · Property</x:v>
-      </x:c>
-      <x:c r="C15" s="57" t="str">
-        <x:v>Title, pricing, type-specific facts, long description and sticky tabs</x:v>
-      </x:c>
-      <x:c r="D15" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E15" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F15" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G15" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H15" s="58"/>
-      <x:c r="I15" s="58"/>
-      <x:c r="J15" s="57"/>
-      <x:c r="K15" s="57"/>
-      <x:c r="L15" s="57"/>
-      <x:c r="M15" s="57"/>
-    </x:row>
-    <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="56" t="str">
-        <x:v>F18</x:v>
-      </x:c>
-      <x:c r="B16" s="57" t="str">
-        <x:v>Step 5 · Property</x:v>
-      </x:c>
-      <x:c r="C16" s="57" t="str">
-        <x:v>Floorplan/video/360 tabs, verified nearby information and map</x:v>
-      </x:c>
-      <x:c r="D16" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E16" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F16" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G16" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H16" s="58"/>
-      <x:c r="I16" s="58"/>
-      <x:c r="J16" s="57"/>
-      <x:c r="K16" s="57"/>
-      <x:c r="L16" s="57"/>
-      <x:c r="M16" s="57"/>
-    </x:row>
-    <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="56" t="str">
-        <x:v>F19</x:v>
-      </x:c>
-      <x:c r="B17" s="57" t="str">
-        <x:v>Step 5 · Property</x:v>
-      </x:c>
-      <x:c r="C17" s="57" t="str">
-        <x:v>Mortgage calculator and area comparison when real data exists</x:v>
-      </x:c>
-      <x:c r="D17" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E17" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F17" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G17" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H17" s="58"/>
-      <x:c r="I17" s="58"/>
-      <x:c r="J17" s="57"/>
-      <x:c r="K17" s="57"/>
-      <x:c r="L17" s="57"/>
-      <x:c r="M17" s="57"/>
-    </x:row>
-    <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="56" t="str">
-        <x:v>F20</x:v>
-      </x:c>
-      <x:c r="B18" s="57" t="str">
-        <x:v>Step 5 · Property</x:v>
-      </x:c>
-      <x:c r="C18" s="57" t="str">
-        <x:v>Same-project units and similar-property cards</x:v>
-      </x:c>
-      <x:c r="D18" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E18" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F18" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G18" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H18" s="58"/>
-      <x:c r="I18" s="58"/>
-      <x:c r="J18" s="57"/>
-      <x:c r="K18" s="57"/>
-      <x:c r="L18" s="57"/>
-      <x:c r="M18" s="57"/>
-    </x:row>
-    <x:row r="19" ht="250" customHeight="1">
-      <x:c r="A19" s="56" t="str">
-        <x:v>F21</x:v>
-      </x:c>
-      <x:c r="B19" s="57" t="str">
-        <x:v>Step 6 · Contact</x:v>
-      </x:c>
-      <x:c r="C19" s="57" t="str">
-        <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
-      </x:c>
-      <x:c r="D19" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E19" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F19" s="57" t="str">
-        <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
-      </x:c>
-      <x:c r="G19" s="57" t="str">
-        <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
-      </x:c>
-      <x:c r="H19" s="58"/>
-      <x:c r="I19" s="58" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="J19" s="57" t="str">
-        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
-      </x:c>
-      <x:c r="K19" s="57" t="str">
-        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
-      </x:c>
-      <x:c r="L19" s="57" t="str">
-        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
-      </x:c>
-      <x:c r="M19" s="57" t="str">
+      <x:c r="M13" s="67" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="56" t="str">
+    <x:row r="14" ht="26" customHeight="1">
+      <x:c r="A14" s="66" t="str">
         <x:v>F22</x:v>
       </x:c>
-      <x:c r="B20" s="57" t="str">
+      <x:c r="B14" s="67" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C20" s="57" t="str">
+      <x:c r="C14" s="67" t="str">
         <x:v>Single-image hero and compact photography-first layout</x:v>
       </x:c>
-      <x:c r="D20" s="57" t="str">
+      <x:c r="D14" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="57" t="str">
+      <x:c r="E14" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="57" t="str">
+      <x:c r="F14" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G20" s="57" t="str">
+      <x:c r="G14" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H20" s="58"/>
-      <x:c r="I20" s="58"/>
-      <x:c r="J20" s="57"/>
-      <x:c r="K20" s="57"/>
-      <x:c r="L20" s="57"/>
-      <x:c r="M20" s="57"/>
-    </x:row>
-    <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="56" t="str">
+      <x:c r="H14" s="68"/>
+      <x:c r="I14" s="68"/>
+      <x:c r="J14" s="67"/>
+      <x:c r="K14" s="67"/>
+      <x:c r="L14" s="67"/>
+      <x:c r="M14" s="67"/>
+    </x:row>
+    <x:row r="15" ht="26" customHeight="1">
+      <x:c r="A15" s="66" t="str">
         <x:v>F23</x:v>
       </x:c>
-      <x:c r="B21" s="57" t="str">
+      <x:c r="B15" s="67" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C21" s="57" t="str">
+      <x:c r="C15" s="67" t="str">
         <x:v>Shared search box with Buy/Rent/Projects/Investment tabs</x:v>
       </x:c>
-      <x:c r="D21" s="57" t="str">
+      <x:c r="D15" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="57" t="str">
+      <x:c r="E15" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="57" t="str">
+      <x:c r="F15" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G21" s="57" t="str">
+      <x:c r="G15" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H21" s="58"/>
-      <x:c r="I21" s="58"/>
-      <x:c r="J21" s="57"/>
-      <x:c r="K21" s="57"/>
-      <x:c r="L21" s="57"/>
-      <x:c r="M21" s="57"/>
-    </x:row>
-    <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="56" t="str">
+      <x:c r="H15" s="68"/>
+      <x:c r="I15" s="68"/>
+      <x:c r="J15" s="67"/>
+      <x:c r="K15" s="67"/>
+      <x:c r="L15" s="67"/>
+      <x:c r="M15" s="67"/>
+    </x:row>
+    <x:row r="16" ht="26" customHeight="1">
+      <x:c r="A16" s="66" t="str">
         <x:v>F24</x:v>
       </x:c>
-      <x:c r="B22" s="57" t="str">
+      <x:c r="B16" s="67" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C22" s="57" t="str">
+      <x:c r="C16" s="67" t="str">
         <x:v>Categories, recent searches and location/station suggestions</x:v>
       </x:c>
-      <x:c r="D22" s="57" t="str">
+      <x:c r="D16" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E22" s="57" t="str">
+      <x:c r="E16" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="57" t="str">
+      <x:c r="F16" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G22" s="57" t="str">
+      <x:c r="G16" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H22" s="58"/>
-      <x:c r="I22" s="58"/>
-      <x:c r="J22" s="57"/>
-      <x:c r="K22" s="57"/>
-      <x:c r="L22" s="57"/>
-      <x:c r="M22" s="57"/>
-    </x:row>
-    <x:row r="23" ht="250" customHeight="1">
-      <x:c r="A23" s="56" t="str">
+      <x:c r="H16" s="68"/>
+      <x:c r="I16" s="68"/>
+      <x:c r="J16" s="67"/>
+      <x:c r="K16" s="67"/>
+      <x:c r="L16" s="67"/>
+      <x:c r="M16" s="67"/>
+    </x:row>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="66" t="str">
         <x:v>F25</x:v>
       </x:c>
-      <x:c r="B23" s="57" t="str">
+      <x:c r="B17" s="67" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C23" s="57" t="str">
+      <x:c r="C17" s="67" t="str">
         <x:v>Homes for you carousel directly below search; regions with real listing counts</x:v>
       </x:c>
-      <x:c r="D23" s="57" t="str">
+      <x:c r="D17" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E23" s="57" t="str">
+      <x:c r="E17" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F23" s="57" t="str">
+      <x:c r="F17" s="67" t="str">
         <x:v>V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
-      <x:c r="G23" s="57" t="str">
+      <x:c r="G17" s="67" t="str">
         <x:v>Codex: implement approved home-page.html only under Step 7 authorization.</x:v>
       </x:c>
-      <x:c r="H23" s="58"/>
-      <x:c r="I23" s="58" t="d">
+      <x:c r="H17" s="68"/>
+      <x:c r="I17" s="68" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J23" s="57" t="str">
+      <x:c r="J17" s="67" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K23" s="57" t="str">
+      <x:c r="K17" s="67" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L23" s="57" t="str">
+      <x:c r="L17" s="67" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M23" s="57" t="str">
+      <x:c r="M17" s="67" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
     </x:row>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="66" t="str">
+        <x:v>F26</x:v>
+      </x:c>
+      <x:c r="B18" s="67" t="str">
+        <x:v>Step 7 · Home</x:v>
+      </x:c>
+      <x:c r="C18" s="67" t="str">
+        <x:v>New projects, tools, services and owner lead CTAs</x:v>
+      </x:c>
+      <x:c r="D18" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E18" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F18" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G18" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H18" s="68"/>
+      <x:c r="I18" s="68"/>
+      <x:c r="J18" s="67"/>
+      <x:c r="K18" s="67"/>
+      <x:c r="L18" s="67"/>
+      <x:c r="M18" s="67"/>
+    </x:row>
+    <x:row r="19" ht="250" customHeight="1">
+      <x:c r="A19" s="66" t="str">
+        <x:v>F27</x:v>
+      </x:c>
+      <x:c r="B19" s="67" t="str">
+        <x:v>Step 8 · Projects</x:v>
+      </x:c>
+      <x:c r="C19" s="67" t="str">
+        <x:v>Projects index and responsive project detail layouts</x:v>
+      </x:c>
+      <x:c r="D19" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E19" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F19" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G19" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H19" s="68"/>
+      <x:c r="I19" s="68"/>
+      <x:c r="J19" s="67"/>
+      <x:c r="K19" s="67"/>
+      <x:c r="L19" s="67"/>
+      <x:c r="M19" s="67"/>
+    </x:row>
+    <x:row r="20" ht="26" customHeight="1">
+      <x:c r="A20" s="66" t="str">
+        <x:v>F28</x:v>
+      </x:c>
+      <x:c r="B20" s="67" t="str">
+        <x:v>Step 8 · Projects</x:v>
+      </x:c>
+      <x:c r="C20" s="67" t="str">
+        <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
+      </x:c>
+      <x:c r="D20" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E20" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F20" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G20" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H20" s="68"/>
+      <x:c r="I20" s="68"/>
+      <x:c r="J20" s="67"/>
+      <x:c r="K20" s="67"/>
+      <x:c r="L20" s="67"/>
+      <x:c r="M20" s="67"/>
+    </x:row>
+    <x:row r="21" ht="26" customHeight="1">
+      <x:c r="A21" s="66" t="str">
+        <x:v>F29</x:v>
+      </x:c>
+      <x:c r="B21" s="67" t="str">
+        <x:v>Step 8 · Projects</x:v>
+      </x:c>
+      <x:c r="C21" s="67" t="str">
+        <x:v>Data-driven clickable project SVG plot plan</x:v>
+      </x:c>
+      <x:c r="D21" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E21" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F21" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G21" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H21" s="68"/>
+      <x:c r="I21" s="68"/>
+      <x:c r="J21" s="67"/>
+      <x:c r="K21" s="67"/>
+      <x:c r="L21" s="67"/>
+      <x:c r="M21" s="67"/>
+    </x:row>
+    <x:row r="22" ht="26" customHeight="1">
+      <x:c r="A22" s="66" t="str">
+        <x:v>F30</x:v>
+      </x:c>
+      <x:c r="B22" s="67" t="str">
+        <x:v>Step 8 · Booking</x:v>
+      </x:c>
+      <x:c r="C22" s="67" t="str">
+        <x:v>Site visit 3-step form and confirmation screens</x:v>
+      </x:c>
+      <x:c r="D22" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E22" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F22" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G22" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H22" s="68"/>
+      <x:c r="I22" s="68"/>
+      <x:c r="J22" s="67"/>
+      <x:c r="K22" s="67"/>
+      <x:c r="L22" s="67"/>
+      <x:c r="M22" s="67"/>
+    </x:row>
+    <x:row r="23" ht="250" customHeight="1">
+      <x:c r="A23" s="66" t="str">
+        <x:v>F31</x:v>
+      </x:c>
+      <x:c r="B23" s="67" t="str">
+        <x:v>Step 9 · Saved</x:v>
+      </x:c>
+      <x:c r="C23" s="67" t="str">
+        <x:v>Homes, searches and viewings; local save without account</x:v>
+      </x:c>
+      <x:c r="D23" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E23" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F23" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G23" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H23" s="68"/>
+      <x:c r="I23" s="68"/>
+      <x:c r="J23" s="67"/>
+      <x:c r="K23" s="67"/>
+      <x:c r="L23" s="67"/>
+      <x:c r="M23" s="67"/>
+    </x:row>
     <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="56" t="str">
-        <x:v>F26</x:v>
-      </x:c>
-      <x:c r="B24" s="57" t="str">
-        <x:v>Step 7 · Home</x:v>
-      </x:c>
-      <x:c r="C24" s="57" t="str">
-        <x:v>New projects, tools, services and owner lead CTAs</x:v>
-      </x:c>
-      <x:c r="D24" s="57" t="str">
+      <x:c r="A24" s="66" t="str">
+        <x:v>F33</x:v>
+      </x:c>
+      <x:c r="B24" s="67" t="str">
+        <x:v>Step 10B · Accounts</x:v>
+      </x:c>
+      <x:c r="C24" s="67" t="str">
+        <x:v>Build approved auth and account screens only after approval</x:v>
+      </x:c>
+      <x:c r="D24" s="67" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E24" s="57" t="str">
+      <x:c r="E24" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="57" t="str">
+      <x:c r="F24" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G24" s="57" t="str">
+      <x:c r="G24" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H24" s="58"/>
-      <x:c r="I24" s="58"/>
-      <x:c r="J24" s="57"/>
-      <x:c r="K24" s="57"/>
-      <x:c r="L24" s="57"/>
-      <x:c r="M24" s="57"/>
+      <x:c r="H24" s="68"/>
+      <x:c r="I24" s="68"/>
+      <x:c r="J24" s="67"/>
+      <x:c r="K24" s="67"/>
+      <x:c r="L24" s="67"/>
+      <x:c r="M24" s="67"/>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="56" t="str">
-        <x:v>F27</x:v>
-      </x:c>
-      <x:c r="B25" s="57" t="str">
+      <x:c r="A25" s="66" t="str">
+        <x:v>F35</x:v>
+      </x:c>
+      <x:c r="B25" s="67" t="str">
+        <x:v>Step 11B · Admin</x:v>
+      </x:c>
+      <x:c r="C25" s="67" t="str">
+        <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
+      </x:c>
+      <x:c r="D25" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E25" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F25" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G25" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H25" s="68"/>
+      <x:c r="I25" s="68"/>
+      <x:c r="J25" s="67"/>
+      <x:c r="K25" s="67"/>
+      <x:c r="L25" s="67"/>
+      <x:c r="M25" s="67"/>
+    </x:row>
+    <x:row r="26" ht="26" customHeight="1">
+      <x:c r="A26" s="66" t="str">
+        <x:v>F36</x:v>
+      </x:c>
+      <x:c r="B26" s="67" t="str">
+        <x:v>Step 11B · Admin</x:v>
+      </x:c>
+      <x:c r="C26" s="67" t="str">
+        <x:v>Admin-managed searchable filter editor with type safety</x:v>
+      </x:c>
+      <x:c r="D26" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E26" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F26" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G26" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H26" s="68"/>
+      <x:c r="I26" s="68"/>
+      <x:c r="J26" s="67"/>
+      <x:c r="K26" s="67"/>
+      <x:c r="L26" s="67"/>
+      <x:c r="M26" s="67"/>
+    </x:row>
+    <x:row r="27" ht="26" customHeight="1">
+      <x:c r="A27" s="66" t="str">
+        <x:v>F37</x:v>
+      </x:c>
+      <x:c r="B27" s="67" t="str">
+        <x:v>Step 12 · Quality</x:v>
+      </x:c>
+      <x:c r="C27" s="67" t="str">
+        <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
+      </x:c>
+      <x:c r="D27" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E27" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F27" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G27" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H27" s="68"/>
+      <x:c r="I27" s="68"/>
+      <x:c r="J27" s="67"/>
+      <x:c r="K27" s="67"/>
+      <x:c r="L27" s="67"/>
+      <x:c r="M27" s="67"/>
+    </x:row>
+    <x:row r="28" ht="26" customHeight="1">
+      <x:c r="A28" s="66" t="str">
+        <x:v>F38</x:v>
+      </x:c>
+      <x:c r="B28" s="67" t="str">
+        <x:v>Step 12 · Quality</x:v>
+      </x:c>
+      <x:c r="C28" s="67" t="str">
+        <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
+      </x:c>
+      <x:c r="D28" s="67" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E28" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F28" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G28" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H28" s="68"/>
+      <x:c r="I28" s="68"/>
+      <x:c r="J28" s="67"/>
+      <x:c r="K28" s="67"/>
+      <x:c r="L28" s="67"/>
+      <x:c r="M28" s="67"/>
+    </x:row>
+    <x:row r="29" ht="26" customHeight="1">
+      <x:c r="A29" s="66" t="str">
+        <x:v>B08</x:v>
+      </x:c>
+      <x:c r="B29" s="67" t="str">
+        <x:v>Step 4 · Map</x:v>
+      </x:c>
+      <x:c r="C29" s="67" t="str">
+        <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
+      </x:c>
+      <x:c r="D29" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E29" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F29" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G29" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H29" s="68"/>
+      <x:c r="I29" s="68"/>
+      <x:c r="J29" s="67"/>
+      <x:c r="K29" s="67"/>
+      <x:c r="L29" s="67"/>
+      <x:c r="M29" s="67"/>
+    </x:row>
+    <x:row r="30" ht="26" customHeight="1">
+      <x:c r="A30" s="66" t="str">
+        <x:v>B10</x:v>
+      </x:c>
+      <x:c r="B30" s="67" t="str">
+        <x:v>Step 4 · Nearby</x:v>
+      </x:c>
+      <x:c r="C30" s="67" t="str">
+        <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
+      </x:c>
+      <x:c r="D30" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E30" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F30" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G30" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H30" s="68"/>
+      <x:c r="I30" s="68"/>
+      <x:c r="J30" s="67"/>
+      <x:c r="K30" s="67"/>
+      <x:c r="L30" s="67"/>
+      <x:c r="M30" s="67"/>
+    </x:row>
+    <x:row r="31" ht="26" customHeight="1">
+      <x:c r="A31" s="66" t="str">
+        <x:v>B11</x:v>
+      </x:c>
+      <x:c r="B31" s="67" t="str">
+        <x:v>Step 5 · Media</x:v>
+      </x:c>
+      <x:c r="C31" s="67" t="str">
+        <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
+      </x:c>
+      <x:c r="D31" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E31" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F31" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G31" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H31" s="68"/>
+      <x:c r="I31" s="68"/>
+      <x:c r="J31" s="67"/>
+      <x:c r="K31" s="67"/>
+      <x:c r="L31" s="67"/>
+      <x:c r="M31" s="67"/>
+    </x:row>
+    <x:row r="32" ht="26" customHeight="1">
+      <x:c r="A32" s="66" t="str">
+        <x:v>B12</x:v>
+      </x:c>
+      <x:c r="B32" s="67" t="str">
+        <x:v>Step 5 · Similar</x:v>
+      </x:c>
+      <x:c r="C32" s="67" t="str">
+        <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
+      </x:c>
+      <x:c r="D32" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E32" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F32" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G32" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H32" s="68"/>
+      <x:c r="I32" s="68"/>
+      <x:c r="J32" s="67"/>
+      <x:c r="K32" s="67"/>
+      <x:c r="L32" s="67"/>
+      <x:c r="M32" s="67"/>
+    </x:row>
+    <x:row r="33" ht="26" customHeight="1">
+      <x:c r="A33" s="66" t="str">
+        <x:v>B13</x:v>
+      </x:c>
+      <x:c r="B33" s="67" t="str">
+        <x:v>Step 5 · Metrics</x:v>
+      </x:c>
+      <x:c r="C33" s="67" t="str">
+        <x:v>Comparable pricing/yield gated by verified sample size</x:v>
+      </x:c>
+      <x:c r="D33" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E33" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F33" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G33" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H33" s="68"/>
+      <x:c r="I33" s="68"/>
+      <x:c r="J33" s="67"/>
+      <x:c r="K33" s="67"/>
+      <x:c r="L33" s="67"/>
+      <x:c r="M33" s="67"/>
+    </x:row>
+    <x:row r="34" ht="26" customHeight="1">
+      <x:c r="A34" s="66" t="str">
+        <x:v>B14</x:v>
+      </x:c>
+      <x:c r="B34" s="67" t="str">
+        <x:v>Step 6 · Leads</x:v>
+      </x:c>
+      <x:c r="C34" s="67" t="str">
+        <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
+      </x:c>
+      <x:c r="D34" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E34" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F34" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G34" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H34" s="68"/>
+      <x:c r="I34" s="68"/>
+      <x:c r="J34" s="67"/>
+      <x:c r="K34" s="67"/>
+      <x:c r="L34" s="67"/>
+      <x:c r="M34" s="67"/>
+    </x:row>
+    <x:row r="35" ht="26" customHeight="1">
+      <x:c r="A35" s="66" t="str">
+        <x:v>B15</x:v>
+      </x:c>
+      <x:c r="B35" s="67" t="str">
+        <x:v>Step 6 · Leads</x:v>
+      </x:c>
+      <x:c r="C35" s="67" t="str">
+        <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
+      </x:c>
+      <x:c r="D35" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E35" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F35" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G35" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H35" s="68"/>
+      <x:c r="I35" s="68"/>
+      <x:c r="J35" s="67"/>
+      <x:c r="K35" s="67"/>
+      <x:c r="L35" s="67"/>
+      <x:c r="M35" s="67"/>
+    </x:row>
+    <x:row r="36" ht="26" customHeight="1">
+      <x:c r="A36" s="66" t="str">
+        <x:v>B16</x:v>
+      </x:c>
+      <x:c r="B36" s="67" t="str">
+        <x:v>Step 6 · Security</x:v>
+      </x:c>
+      <x:c r="C36" s="67" t="str">
+        <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
+      </x:c>
+      <x:c r="D36" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E36" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F36" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G36" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H36" s="68"/>
+      <x:c r="I36" s="68"/>
+      <x:c r="J36" s="67"/>
+      <x:c r="K36" s="67"/>
+      <x:c r="L36" s="67"/>
+      <x:c r="M36" s="67"/>
+    </x:row>
+    <x:row r="37" ht="26" customHeight="1">
+      <x:c r="A37" s="66" t="str">
+        <x:v>B19</x:v>
+      </x:c>
+      <x:c r="B37" s="67" t="str">
+        <x:v>Step 6 · Chat</x:v>
+      </x:c>
+      <x:c r="C37" s="67" t="str">
+        <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
+      </x:c>
+      <x:c r="D37" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E37" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F37" s="67" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G37" s="67" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H37" s="68"/>
+      <x:c r="I37" s="68"/>
+      <x:c r="J37" s="67"/>
+      <x:c r="K37" s="67"/>
+      <x:c r="L37" s="67"/>
+      <x:c r="M37" s="67"/>
+    </x:row>
+    <x:row r="38" ht="26" customHeight="1">
+      <x:c r="A38" s="66" t="str">
+        <x:v>B20</x:v>
+      </x:c>
+      <x:c r="B38" s="67" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C25" s="57" t="str">
-        <x:v>Projects index and responsive project detail layouts</x:v>
-      </x:c>
-      <x:c r="D25" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E25" s="57" t="str">
+      <x:c r="C38" s="67" t="str">
+        <x:v>Project/unit/plot status logic and validation</x:v>
+      </x:c>
+      <x:c r="D38" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E38" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="57" t="str">
+      <x:c r="F38" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G25" s="57" t="str">
+      <x:c r="G38" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H25" s="58"/>
-      <x:c r="I25" s="58"/>
-      <x:c r="J25" s="57"/>
-      <x:c r="K25" s="57"/>
-      <x:c r="L25" s="57"/>
-      <x:c r="M25" s="57"/>
-    </x:row>
-    <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="56" t="str">
-        <x:v>F28</x:v>
-      </x:c>
-      <x:c r="B26" s="57" t="str">
-        <x:v>Step 8 · Projects</x:v>
-      </x:c>
-      <x:c r="C26" s="57" t="str">
-        <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
-      </x:c>
-      <x:c r="D26" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E26" s="57" t="str">
+      <x:c r="H38" s="68"/>
+      <x:c r="I38" s="68"/>
+      <x:c r="J38" s="67"/>
+      <x:c r="K38" s="67"/>
+      <x:c r="L38" s="67"/>
+      <x:c r="M38" s="67"/>
+    </x:row>
+    <x:row r="39" ht="26" customHeight="1">
+      <x:c r="A39" s="66" t="str">
+        <x:v>B21</x:v>
+      </x:c>
+      <x:c r="B39" s="67" t="str">
+        <x:v>Step 8 · Booking</x:v>
+      </x:c>
+      <x:c r="C39" s="67" t="str">
+        <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
+      </x:c>
+      <x:c r="D39" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E39" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="57" t="str">
+      <x:c r="F39" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G26" s="57" t="str">
+      <x:c r="G39" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H26" s="58"/>
-      <x:c r="I26" s="58"/>
-      <x:c r="J26" s="57"/>
-      <x:c r="K26" s="57"/>
-      <x:c r="L26" s="57"/>
-      <x:c r="M26" s="57"/>
-    </x:row>
-    <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="56" t="str">
-        <x:v>F29</x:v>
-      </x:c>
-      <x:c r="B27" s="57" t="str">
-        <x:v>Step 8 · Projects</x:v>
-      </x:c>
-      <x:c r="C27" s="57" t="str">
-        <x:v>Data-driven clickable project SVG plot plan</x:v>
-      </x:c>
-      <x:c r="D27" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E27" s="57" t="str">
+      <x:c r="H39" s="68"/>
+      <x:c r="I39" s="68"/>
+      <x:c r="J39" s="67"/>
+      <x:c r="K39" s="67"/>
+      <x:c r="L39" s="67"/>
+      <x:c r="M39" s="67"/>
+    </x:row>
+    <x:row r="40" ht="26" customHeight="1">
+      <x:c r="A40" s="66" t="str">
+        <x:v>B22</x:v>
+      </x:c>
+      <x:c r="B40" s="67" t="str">
+        <x:v>Step 9 · Saved</x:v>
+      </x:c>
+      <x:c r="C40" s="67" t="str">
+        <x:v>Saved listings/searches persistence, new-match calculations</x:v>
+      </x:c>
+      <x:c r="D40" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E40" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="57" t="str">
+      <x:c r="F40" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G27" s="57" t="str">
+      <x:c r="G40" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H27" s="58"/>
-      <x:c r="I27" s="58"/>
-      <x:c r="J27" s="57"/>
-      <x:c r="K27" s="57"/>
-      <x:c r="L27" s="57"/>
-      <x:c r="M27" s="57"/>
-    </x:row>
-    <x:row r="28" ht="26" customHeight="1">
-      <x:c r="A28" s="56" t="str">
-        <x:v>F30</x:v>
-      </x:c>
-      <x:c r="B28" s="57" t="str">
-        <x:v>Step 8 · Booking</x:v>
-      </x:c>
-      <x:c r="C28" s="57" t="str">
-        <x:v>Site visit 3-step form and confirmation screens</x:v>
-      </x:c>
-      <x:c r="D28" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E28" s="57" t="str">
+      <x:c r="H40" s="68"/>
+      <x:c r="I40" s="68"/>
+      <x:c r="J40" s="67"/>
+      <x:c r="K40" s="67"/>
+      <x:c r="L40" s="67"/>
+      <x:c r="M40" s="67"/>
+    </x:row>
+    <x:row r="41" ht="26" customHeight="1">
+      <x:c r="A41" s="66" t="str">
+        <x:v>B24</x:v>
+      </x:c>
+      <x:c r="B41" s="67" t="str">
+        <x:v>Step 10B · Auth</x:v>
+      </x:c>
+      <x:c r="C41" s="67" t="str">
+        <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
+      </x:c>
+      <x:c r="D41" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E41" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="57" t="str">
+      <x:c r="F41" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G28" s="57" t="str">
+      <x:c r="G41" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H28" s="58"/>
-      <x:c r="I28" s="58"/>
-      <x:c r="J28" s="57"/>
-      <x:c r="K28" s="57"/>
-      <x:c r="L28" s="57"/>
-      <x:c r="M28" s="57"/>
-    </x:row>
-    <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="56" t="str">
-        <x:v>F31</x:v>
-      </x:c>
-      <x:c r="B29" s="57" t="str">
-        <x:v>Step 9 · Saved</x:v>
-      </x:c>
-      <x:c r="C29" s="57" t="str">
-        <x:v>Homes, searches and viewings; local save without account</x:v>
-      </x:c>
-      <x:c r="D29" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E29" s="57" t="str">
+      <x:c r="H41" s="68"/>
+      <x:c r="I41" s="68"/>
+      <x:c r="J41" s="67"/>
+      <x:c r="K41" s="67"/>
+      <x:c r="L41" s="67"/>
+      <x:c r="M41" s="67"/>
+    </x:row>
+    <x:row r="42" ht="26" customHeight="1">
+      <x:c r="A42" s="66" t="str">
+        <x:v>B25</x:v>
+      </x:c>
+      <x:c r="B42" s="67" t="str">
+        <x:v>Step 10B · Auth</x:v>
+      </x:c>
+      <x:c r="C42" s="67" t="str">
+        <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
+      </x:c>
+      <x:c r="D42" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E42" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="57" t="str">
+      <x:c r="F42" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="57" t="str">
+      <x:c r="G42" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="58"/>
-      <x:c r="I29" s="58"/>
-      <x:c r="J29" s="57"/>
-      <x:c r="K29" s="57"/>
-      <x:c r="L29" s="57"/>
-      <x:c r="M29" s="57"/>
-    </x:row>
-    <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="56" t="str">
-        <x:v>F33</x:v>
-      </x:c>
-      <x:c r="B30" s="57" t="str">
-        <x:v>Step 10B · Accounts</x:v>
-      </x:c>
-      <x:c r="C30" s="57" t="str">
-        <x:v>Build approved auth and account screens only after approval</x:v>
-      </x:c>
-      <x:c r="D30" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E30" s="57" t="str">
+      <x:c r="H42" s="68"/>
+      <x:c r="I42" s="68"/>
+      <x:c r="J42" s="67"/>
+      <x:c r="K42" s="67"/>
+      <x:c r="L42" s="67"/>
+      <x:c r="M42" s="67"/>
+    </x:row>
+    <x:row r="43" ht="26" customHeight="1">
+      <x:c r="A43" s="66" t="str">
+        <x:v>B26</x:v>
+      </x:c>
+      <x:c r="B43" s="67" t="str">
+        <x:v>Step 11B · Admin</x:v>
+      </x:c>
+      <x:c r="C43" s="67" t="str">
+        <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
+      </x:c>
+      <x:c r="D43" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E43" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="57" t="str">
+      <x:c r="F43" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="57" t="str">
+      <x:c r="G43" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="58"/>
-      <x:c r="I30" s="58"/>
-      <x:c r="J30" s="57"/>
-      <x:c r="K30" s="57"/>
-      <x:c r="L30" s="57"/>
-      <x:c r="M30" s="57"/>
-    </x:row>
-    <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="56" t="str">
-        <x:v>F35</x:v>
-      </x:c>
-      <x:c r="B31" s="57" t="str">
+      <x:c r="H43" s="68"/>
+      <x:c r="I43" s="68"/>
+      <x:c r="J43" s="67"/>
+      <x:c r="K43" s="67"/>
+      <x:c r="L43" s="67"/>
+      <x:c r="M43" s="67"/>
+    </x:row>
+    <x:row r="44" ht="26" customHeight="1">
+      <x:c r="A44" s="66" t="str">
+        <x:v>B27</x:v>
+      </x:c>
+      <x:c r="B44" s="67" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C31" s="57" t="str">
-        <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
-      </x:c>
-      <x:c r="D31" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E31" s="57" t="str">
+      <x:c r="C44" s="67" t="str">
+        <x:v>Admin user management, audit log and sensitive action authorization</x:v>
+      </x:c>
+      <x:c r="D44" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E44" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="57" t="str">
+      <x:c r="F44" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="57" t="str">
+      <x:c r="G44" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="58"/>
-      <x:c r="I31" s="58"/>
-      <x:c r="J31" s="57"/>
-      <x:c r="K31" s="57"/>
-      <x:c r="L31" s="57"/>
-      <x:c r="M31" s="57"/>
-    </x:row>
-    <x:row r="32" ht="26" customHeight="1">
-      <x:c r="A32" s="56" t="str">
-        <x:v>F36</x:v>
-      </x:c>
-      <x:c r="B32" s="57" t="str">
-        <x:v>Step 11B · Admin</x:v>
-      </x:c>
-      <x:c r="C32" s="57" t="str">
-        <x:v>Admin-managed searchable filter editor with type safety</x:v>
-      </x:c>
-      <x:c r="D32" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E32" s="57" t="str">
+      <x:c r="H44" s="68"/>
+      <x:c r="I44" s="68"/>
+      <x:c r="J44" s="67"/>
+      <x:c r="K44" s="67"/>
+      <x:c r="L44" s="67"/>
+      <x:c r="M44" s="67"/>
+    </x:row>
+    <x:row r="45" ht="26" customHeight="1">
+      <x:c r="A45" s="66" t="str">
+        <x:v>B30</x:v>
+      </x:c>
+      <x:c r="B45" s="67" t="str">
+        <x:v>Step 12 · Deploy</x:v>
+      </x:c>
+      <x:c r="C45" s="67" t="str">
+        <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
+      </x:c>
+      <x:c r="D45" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E45" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="57" t="str">
+      <x:c r="F45" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G32" s="57" t="str">
+      <x:c r="G45" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H32" s="58"/>
-      <x:c r="I32" s="58"/>
-      <x:c r="J32" s="57"/>
-      <x:c r="K32" s="57"/>
-      <x:c r="L32" s="57"/>
-      <x:c r="M32" s="57"/>
-    </x:row>
-    <x:row r="33" ht="26" customHeight="1">
-      <x:c r="A33" s="56" t="str">
-        <x:v>F37</x:v>
-      </x:c>
-      <x:c r="B33" s="57" t="str">
+      <x:c r="H45" s="68"/>
+      <x:c r="I45" s="68"/>
+      <x:c r="J45" s="67"/>
+      <x:c r="K45" s="67"/>
+      <x:c r="L45" s="67"/>
+      <x:c r="M45" s="67"/>
+    </x:row>
+    <x:row r="46" ht="26" customHeight="1">
+      <x:c r="A46" s="66" t="str">
+        <x:v>B31</x:v>
+      </x:c>
+      <x:c r="B46" s="67" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C33" s="57" t="str">
-        <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
-      </x:c>
-      <x:c r="D33" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E33" s="57" t="str">
+      <x:c r="C46" s="67" t="str">
+        <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
+      </x:c>
+      <x:c r="D46" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E46" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F33" s="57" t="str">
+      <x:c r="F46" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G33" s="57" t="str">
+      <x:c r="G46" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H33" s="58"/>
-      <x:c r="I33" s="58"/>
-      <x:c r="J33" s="57"/>
-      <x:c r="K33" s="57"/>
-      <x:c r="L33" s="57"/>
-      <x:c r="M33" s="57"/>
-    </x:row>
-    <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="56" t="str">
-        <x:v>F38</x:v>
-      </x:c>
-      <x:c r="B34" s="57" t="str">
-        <x:v>Step 12 · Quality</x:v>
-      </x:c>
-      <x:c r="C34" s="57" t="str">
-        <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
-      </x:c>
-      <x:c r="D34" s="57" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E34" s="57" t="str">
+      <x:c r="H46" s="68"/>
+      <x:c r="I46" s="68"/>
+      <x:c r="J46" s="67"/>
+      <x:c r="K46" s="67"/>
+      <x:c r="L46" s="67"/>
+      <x:c r="M46" s="67"/>
+    </x:row>
+    <x:row r="47" ht="26" customHeight="1">
+      <x:c r="A47" s="66" t="str">
+        <x:v>B32</x:v>
+      </x:c>
+      <x:c r="B47" s="67" t="str">
+        <x:v>Step 12 · Security</x:v>
+      </x:c>
+      <x:c r="C47" s="67" t="str">
+        <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
+      </x:c>
+      <x:c r="D47" s="67" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E47" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F34" s="57" t="str">
+      <x:c r="F47" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G34" s="57" t="str">
+      <x:c r="G47" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H34" s="58"/>
-      <x:c r="I34" s="58"/>
-      <x:c r="J34" s="57"/>
-      <x:c r="K34" s="57"/>
-      <x:c r="L34" s="57"/>
-      <x:c r="M34" s="57"/>
-    </x:row>
-    <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="56" t="str">
-        <x:v>B05</x:v>
-      </x:c>
-      <x:c r="B35" s="57" t="str">
-        <x:v>Step 2 · Filters</x:v>
-      </x:c>
-      <x:c r="C35" s="57" t="str">
-        <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
-      </x:c>
-      <x:c r="D35" s="57" t="str">
+      <x:c r="H47" s="68"/>
+      <x:c r="I47" s="68"/>
+      <x:c r="J47" s="67"/>
+      <x:c r="K47" s="67"/>
+      <x:c r="L47" s="67"/>
+      <x:c r="M47" s="67"/>
+    </x:row>
+    <x:row r="48" ht="26" customHeight="1">
+      <x:c r="A48" s="66" t="str">
+        <x:v>B33</x:v>
+      </x:c>
+      <x:c r="B48" s="67" t="str">
+        <x:v>Step 7 · Owners</x:v>
+      </x:c>
+      <x:c r="C48" s="67" t="str">
+        <x:v>Home-value and service enquiry data handling</x:v>
+      </x:c>
+      <x:c r="D48" s="67" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E35" s="57" t="str">
+      <x:c r="E48" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F35" s="57" t="str">
+      <x:c r="F48" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G35" s="57" t="str">
+      <x:c r="G48" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H35" s="58"/>
-      <x:c r="I35" s="58"/>
-      <x:c r="J35" s="57"/>
-      <x:c r="K35" s="57"/>
-      <x:c r="L35" s="57"/>
-      <x:c r="M35" s="57"/>
-    </x:row>
-    <x:row r="36" ht="26" customHeight="1">
-      <x:c r="A36" s="56" t="str">
-        <x:v>B06</x:v>
-      </x:c>
-      <x:c r="B36" s="57" t="str">
-        <x:v>Step 3 · Search</x:v>
-      </x:c>
-      <x:c r="C36" s="57" t="str">
-        <x:v>Typed validated listing/search data access and pagination</x:v>
-      </x:c>
-      <x:c r="D36" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E36" s="57" t="str">
+      <x:c r="H48" s="68"/>
+      <x:c r="I48" s="68"/>
+      <x:c r="J48" s="67"/>
+      <x:c r="K48" s="67"/>
+      <x:c r="L48" s="67"/>
+      <x:c r="M48" s="67"/>
+    </x:row>
+    <x:row r="49" ht="26" customHeight="1">
+      <x:c r="A49" s="66" t="str">
+        <x:v>E01</x:v>
+      </x:c>
+      <x:c r="B49" s="67" t="str">
+        <x:v>Step 6 · Email</x:v>
+      </x:c>
+      <x:c r="C49" s="67" t="str">
+        <x:v>Enquiry notification with retryable queue/outbox</x:v>
+      </x:c>
+      <x:c r="D49" s="67" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E49" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F36" s="57" t="str">
+      <x:c r="F49" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G36" s="57" t="str">
+      <x:c r="G49" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H36" s="58"/>
-      <x:c r="I36" s="58"/>
-      <x:c r="J36" s="57"/>
-      <x:c r="K36" s="57"/>
-      <x:c r="L36" s="57"/>
-      <x:c r="M36" s="57"/>
-    </x:row>
-    <x:row r="37" ht="26" customHeight="1">
-      <x:c r="A37" s="56" t="str">
-        <x:v>B07</x:v>
-      </x:c>
-      <x:c r="B37" s="57" t="str">
-        <x:v>Step 3 · Search</x:v>
-      </x:c>
-      <x:c r="C37" s="57" t="str">
-        <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
-      </x:c>
-      <x:c r="D37" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E37" s="57" t="str">
+      <x:c r="H49" s="68"/>
+      <x:c r="I49" s="68"/>
+      <x:c r="J49" s="67"/>
+      <x:c r="K49" s="67"/>
+      <x:c r="L49" s="67"/>
+      <x:c r="M49" s="67"/>
+    </x:row>
+    <x:row r="50" ht="26" customHeight="1">
+      <x:c r="A50" s="66" t="str">
+        <x:v>E02</x:v>
+      </x:c>
+      <x:c r="B50" s="67" t="str">
+        <x:v>Step 6 · Email</x:v>
+      </x:c>
+      <x:c r="C50" s="67" t="str">
+        <x:v>Thai and English buyer enquiry acknowledgments</x:v>
+      </x:c>
+      <x:c r="D50" s="67" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E50" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F37" s="57" t="str">
+      <x:c r="F50" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G37" s="57" t="str">
+      <x:c r="G50" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H37" s="58"/>
-      <x:c r="I37" s="58"/>
-      <x:c r="J37" s="57"/>
-      <x:c r="K37" s="57"/>
-      <x:c r="L37" s="57"/>
-      <x:c r="M37" s="57"/>
-    </x:row>
-    <x:row r="38" ht="26" customHeight="1">
-      <x:c r="A38" s="56" t="str">
-        <x:v>B08</x:v>
-      </x:c>
-      <x:c r="B38" s="57" t="str">
-        <x:v>Step 4 · Map</x:v>
-      </x:c>
-      <x:c r="C38" s="57" t="str">
-        <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
-      </x:c>
-      <x:c r="D38" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E38" s="57" t="str">
+      <x:c r="H50" s="68"/>
+      <x:c r="I50" s="68"/>
+      <x:c r="J50" s="67"/>
+      <x:c r="K50" s="67"/>
+      <x:c r="L50" s="67"/>
+      <x:c r="M50" s="67"/>
+    </x:row>
+    <x:row r="51" ht="26" customHeight="1">
+      <x:c r="A51" s="66" t="str">
+        <x:v>E03</x:v>
+      </x:c>
+      <x:c r="B51" s="67" t="str">
+        <x:v>Step 8 · Email</x:v>
+      </x:c>
+      <x:c r="C51" s="67" t="str">
+        <x:v>Project brochure/price list email delivery</x:v>
+      </x:c>
+      <x:c r="D51" s="67" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E51" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F38" s="57" t="str">
+      <x:c r="F51" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G38" s="57" t="str">
+      <x:c r="G51" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H38" s="58"/>
-      <x:c r="I38" s="58"/>
-      <x:c r="J38" s="57"/>
-      <x:c r="K38" s="57"/>
-      <x:c r="L38" s="57"/>
-      <x:c r="M38" s="57"/>
-    </x:row>
-    <x:row r="39" ht="26" customHeight="1">
-      <x:c r="A39" s="56" t="str">
-        <x:v>B10</x:v>
-      </x:c>
-      <x:c r="B39" s="57" t="str">
-        <x:v>Step 4 · Nearby</x:v>
-      </x:c>
-      <x:c r="C39" s="57" t="str">
-        <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
-      </x:c>
-      <x:c r="D39" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E39" s="57" t="str">
+      <x:c r="H51" s="68"/>
+      <x:c r="I51" s="68"/>
+      <x:c r="J51" s="67"/>
+      <x:c r="K51" s="67"/>
+      <x:c r="L51" s="67"/>
+      <x:c r="M51" s="67"/>
+    </x:row>
+    <x:row r="52" ht="26" customHeight="1">
+      <x:c r="A52" s="66" t="str">
+        <x:v>E04</x:v>
+      </x:c>
+      <x:c r="B52" s="67" t="str">
+        <x:v>Step 8 · Email</x:v>
+      </x:c>
+      <x:c r="C52" s="67" t="str">
+        <x:v>Site visit request and confirmation notifications</x:v>
+      </x:c>
+      <x:c r="D52" s="67" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E52" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F39" s="57" t="str">
+      <x:c r="F52" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G39" s="57" t="str">
+      <x:c r="G52" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H39" s="58"/>
-      <x:c r="I39" s="58"/>
-      <x:c r="J39" s="57"/>
-      <x:c r="K39" s="57"/>
-      <x:c r="L39" s="57"/>
-      <x:c r="M39" s="57"/>
-    </x:row>
-    <x:row r="40" ht="26" customHeight="1">
-      <x:c r="A40" s="56" t="str">
-        <x:v>B11</x:v>
-      </x:c>
-      <x:c r="B40" s="57" t="str">
-        <x:v>Step 5 · Media</x:v>
-      </x:c>
-      <x:c r="C40" s="57" t="str">
-        <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
-      </x:c>
-      <x:c r="D40" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E40" s="57" t="str">
+      <x:c r="H52" s="68"/>
+      <x:c r="I52" s="68"/>
+      <x:c r="J52" s="67"/>
+      <x:c r="K52" s="67"/>
+      <x:c r="L52" s="67"/>
+      <x:c r="M52" s="67"/>
+    </x:row>
+    <x:row r="53" ht="26" customHeight="1">
+      <x:c r="A53" s="66" t="str">
+        <x:v>E05</x:v>
+      </x:c>
+      <x:c r="B53" s="67" t="str">
+        <x:v>Step 9 · Alerts</x:v>
+      </x:c>
+      <x:c r="C53" s="67" t="str">
+        <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
+      </x:c>
+      <x:c r="D53" s="67" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E53" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F40" s="57" t="str">
+      <x:c r="F53" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G40" s="57" t="str">
+      <x:c r="G53" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H40" s="58"/>
-      <x:c r="I40" s="58"/>
-      <x:c r="J40" s="57"/>
-      <x:c r="K40" s="57"/>
-      <x:c r="L40" s="57"/>
-      <x:c r="M40" s="57"/>
-    </x:row>
-    <x:row r="41" ht="26" customHeight="1">
-      <x:c r="A41" s="56" t="str">
-        <x:v>B12</x:v>
-      </x:c>
-      <x:c r="B41" s="57" t="str">
-        <x:v>Step 5 · Similar</x:v>
-      </x:c>
-      <x:c r="C41" s="57" t="str">
-        <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
-      </x:c>
-      <x:c r="D41" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E41" s="57" t="str">
+      <x:c r="H53" s="68"/>
+      <x:c r="I53" s="68"/>
+      <x:c r="J53" s="67"/>
+      <x:c r="K53" s="67"/>
+      <x:c r="L53" s="67"/>
+      <x:c r="M53" s="67"/>
+    </x:row>
+    <x:row r="54" ht="26" customHeight="1">
+      <x:c r="A54" s="66" t="str">
+        <x:v>E06</x:v>
+      </x:c>
+      <x:c r="B54" s="67" t="str">
+        <x:v>Step 10B · Email</x:v>
+      </x:c>
+      <x:c r="C54" s="67" t="str">
+        <x:v>Account verification and recovery messages if email auth approved</x:v>
+      </x:c>
+      <x:c r="D54" s="67" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E54" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F41" s="57" t="str">
+      <x:c r="F54" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G41" s="57" t="str">
+      <x:c r="G54" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H41" s="58"/>
-      <x:c r="I41" s="58"/>
-      <x:c r="J41" s="57"/>
-      <x:c r="K41" s="57"/>
-      <x:c r="L41" s="57"/>
-      <x:c r="M41" s="57"/>
-    </x:row>
-    <x:row r="42" ht="26" customHeight="1">
-      <x:c r="A42" s="56" t="str">
-        <x:v>B13</x:v>
-      </x:c>
-      <x:c r="B42" s="57" t="str">
-        <x:v>Step 5 · Metrics</x:v>
-      </x:c>
-      <x:c r="C42" s="57" t="str">
-        <x:v>Comparable pricing/yield gated by verified sample size</x:v>
-      </x:c>
-      <x:c r="D42" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E42" s="57" t="str">
+      <x:c r="H54" s="68"/>
+      <x:c r="I54" s="68"/>
+      <x:c r="J54" s="67"/>
+      <x:c r="K54" s="67"/>
+      <x:c r="L54" s="67"/>
+      <x:c r="M54" s="67"/>
+    </x:row>
+    <x:row r="55" ht="26" customHeight="1">
+      <x:c r="A55" s="66" t="str">
+        <x:v>E07</x:v>
+      </x:c>
+      <x:c r="B55" s="67" t="str">
+        <x:v>Step 11B · Email</x:v>
+      </x:c>
+      <x:c r="C55" s="67" t="str">
+        <x:v>Agent notification/routing administration</x:v>
+      </x:c>
+      <x:c r="D55" s="67" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E55" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F42" s="57" t="str">
+      <x:c r="F55" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G42" s="57" t="str">
+      <x:c r="G55" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H42" s="58"/>
-      <x:c r="I42" s="58"/>
-      <x:c r="J42" s="57"/>
-      <x:c r="K42" s="57"/>
-      <x:c r="L42" s="57"/>
-      <x:c r="M42" s="57"/>
-    </x:row>
-    <x:row r="43" ht="26" customHeight="1">
-      <x:c r="A43" s="56" t="str">
-        <x:v>B14</x:v>
-      </x:c>
-      <x:c r="B43" s="57" t="str">
-        <x:v>Step 6 · Leads</x:v>
-      </x:c>
-      <x:c r="C43" s="57" t="str">
-        <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
-      </x:c>
-      <x:c r="D43" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E43" s="57" t="str">
+      <x:c r="H55" s="68"/>
+      <x:c r="I55" s="68"/>
+      <x:c r="J55" s="67"/>
+      <x:c r="K55" s="67"/>
+      <x:c r="L55" s="67"/>
+      <x:c r="M55" s="67"/>
+    </x:row>
+    <x:row r="56" ht="26" customHeight="1">
+      <x:c r="A56" s="66" t="str">
+        <x:v>E08</x:v>
+      </x:c>
+      <x:c r="B56" s="67" t="str">
+        <x:v>Step 7 · Email</x:v>
+      </x:c>
+      <x:c r="C56" s="67" t="str">
+        <x:v>Home valuation and service enquiry replies</x:v>
+      </x:c>
+      <x:c r="D56" s="67" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E56" s="67" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F43" s="57" t="str">
+      <x:c r="F56" s="67" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G43" s="57" t="str">
+      <x:c r="G56" s="67" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H43" s="58"/>
-      <x:c r="I43" s="58"/>
-      <x:c r="J43" s="57"/>
-      <x:c r="K43" s="57"/>
-      <x:c r="L43" s="57"/>
-      <x:c r="M43" s="57"/>
-    </x:row>
-    <x:row r="44" ht="26" customHeight="1">
-      <x:c r="A44" s="56" t="str">
-        <x:v>B15</x:v>
-      </x:c>
-      <x:c r="B44" s="57" t="str">
-        <x:v>Step 6 · Leads</x:v>
-      </x:c>
-      <x:c r="C44" s="57" t="str">
-        <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
-      </x:c>
-      <x:c r="D44" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E44" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F44" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G44" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H44" s="58"/>
-      <x:c r="I44" s="58"/>
-      <x:c r="J44" s="57"/>
-      <x:c r="K44" s="57"/>
-      <x:c r="L44" s="57"/>
-      <x:c r="M44" s="57"/>
-    </x:row>
-    <x:row r="45" ht="26" customHeight="1">
-      <x:c r="A45" s="56" t="str">
-        <x:v>B16</x:v>
-      </x:c>
-      <x:c r="B45" s="57" t="str">
-        <x:v>Step 6 · Security</x:v>
-      </x:c>
-      <x:c r="C45" s="57" t="str">
-        <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
-      </x:c>
-      <x:c r="D45" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E45" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F45" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G45" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H45" s="58"/>
-      <x:c r="I45" s="58"/>
-      <x:c r="J45" s="57"/>
-      <x:c r="K45" s="57"/>
-      <x:c r="L45" s="57"/>
-      <x:c r="M45" s="57"/>
-    </x:row>
-    <x:row r="46" ht="26" customHeight="1">
-      <x:c r="A46" s="56" t="str">
-        <x:v>B19</x:v>
-      </x:c>
-      <x:c r="B46" s="57" t="str">
-        <x:v>Step 6 · Chat</x:v>
-      </x:c>
-      <x:c r="C46" s="57" t="str">
-        <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
-      </x:c>
-      <x:c r="D46" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E46" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F46" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G46" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H46" s="58"/>
-      <x:c r="I46" s="58"/>
-      <x:c r="J46" s="57"/>
-      <x:c r="K46" s="57"/>
-      <x:c r="L46" s="57"/>
-      <x:c r="M46" s="57"/>
-    </x:row>
-    <x:row r="47" ht="26" customHeight="1">
-      <x:c r="A47" s="56" t="str">
-        <x:v>B20</x:v>
-      </x:c>
-      <x:c r="B47" s="57" t="str">
-        <x:v>Step 8 · Projects</x:v>
-      </x:c>
-      <x:c r="C47" s="57" t="str">
-        <x:v>Project/unit/plot status logic and validation</x:v>
-      </x:c>
-      <x:c r="D47" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E47" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F47" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G47" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H47" s="58"/>
-      <x:c r="I47" s="58"/>
-      <x:c r="J47" s="57"/>
-      <x:c r="K47" s="57"/>
-      <x:c r="L47" s="57"/>
-      <x:c r="M47" s="57"/>
-    </x:row>
-    <x:row r="48" ht="26" customHeight="1">
-      <x:c r="A48" s="56" t="str">
-        <x:v>B21</x:v>
-      </x:c>
-      <x:c r="B48" s="57" t="str">
-        <x:v>Step 8 · Booking</x:v>
-      </x:c>
-      <x:c r="C48" s="57" t="str">
-        <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
-      </x:c>
-      <x:c r="D48" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E48" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F48" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G48" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H48" s="58"/>
-      <x:c r="I48" s="58"/>
-      <x:c r="J48" s="57"/>
-      <x:c r="K48" s="57"/>
-      <x:c r="L48" s="57"/>
-      <x:c r="M48" s="57"/>
-    </x:row>
-    <x:row r="49" ht="26" customHeight="1">
-      <x:c r="A49" s="56" t="str">
-        <x:v>B22</x:v>
-      </x:c>
-      <x:c r="B49" s="57" t="str">
-        <x:v>Step 9 · Saved</x:v>
-      </x:c>
-      <x:c r="C49" s="57" t="str">
-        <x:v>Saved listings/searches persistence, new-match calculations</x:v>
-      </x:c>
-      <x:c r="D49" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E49" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F49" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G49" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H49" s="58"/>
-      <x:c r="I49" s="58"/>
-      <x:c r="J49" s="57"/>
-      <x:c r="K49" s="57"/>
-      <x:c r="L49" s="57"/>
-      <x:c r="M49" s="57"/>
-    </x:row>
-    <x:row r="50" ht="26" customHeight="1">
-      <x:c r="A50" s="56" t="str">
-        <x:v>B24</x:v>
-      </x:c>
-      <x:c r="B50" s="57" t="str">
-        <x:v>Step 10B · Auth</x:v>
-      </x:c>
-      <x:c r="C50" s="57" t="str">
-        <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
-      </x:c>
-      <x:c r="D50" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E50" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F50" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G50" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H50" s="58"/>
-      <x:c r="I50" s="58"/>
-      <x:c r="J50" s="57"/>
-      <x:c r="K50" s="57"/>
-      <x:c r="L50" s="57"/>
-      <x:c r="M50" s="57"/>
-    </x:row>
-    <x:row r="51" ht="26" customHeight="1">
-      <x:c r="A51" s="56" t="str">
-        <x:v>B25</x:v>
-      </x:c>
-      <x:c r="B51" s="57" t="str">
-        <x:v>Step 10B · Auth</x:v>
-      </x:c>
-      <x:c r="C51" s="57" t="str">
-        <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
-      </x:c>
-      <x:c r="D51" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E51" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F51" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G51" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H51" s="58"/>
-      <x:c r="I51" s="58"/>
-      <x:c r="J51" s="57"/>
-      <x:c r="K51" s="57"/>
-      <x:c r="L51" s="57"/>
-      <x:c r="M51" s="57"/>
-    </x:row>
-    <x:row r="52" ht="26" customHeight="1">
-      <x:c r="A52" s="56" t="str">
-        <x:v>B26</x:v>
-      </x:c>
-      <x:c r="B52" s="57" t="str">
-        <x:v>Step 11B · Admin</x:v>
-      </x:c>
-      <x:c r="C52" s="57" t="str">
-        <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
-      </x:c>
-      <x:c r="D52" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E52" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F52" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G52" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H52" s="58"/>
-      <x:c r="I52" s="58"/>
-      <x:c r="J52" s="57"/>
-      <x:c r="K52" s="57"/>
-      <x:c r="L52" s="57"/>
-      <x:c r="M52" s="57"/>
-    </x:row>
-    <x:row r="53" ht="26" customHeight="1">
-      <x:c r="A53" s="56" t="str">
-        <x:v>B27</x:v>
-      </x:c>
-      <x:c r="B53" s="57" t="str">
-        <x:v>Step 11B · Admin</x:v>
-      </x:c>
-      <x:c r="C53" s="57" t="str">
-        <x:v>Admin user management, audit log and sensitive action authorization</x:v>
-      </x:c>
-      <x:c r="D53" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E53" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F53" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G53" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H53" s="58"/>
-      <x:c r="I53" s="58"/>
-      <x:c r="J53" s="57"/>
-      <x:c r="K53" s="57"/>
-      <x:c r="L53" s="57"/>
-      <x:c r="M53" s="57"/>
-    </x:row>
-    <x:row r="54" ht="26" customHeight="1">
-      <x:c r="A54" s="56" t="str">
-        <x:v>B30</x:v>
-      </x:c>
-      <x:c r="B54" s="57" t="str">
-        <x:v>Step 12 · Deploy</x:v>
-      </x:c>
-      <x:c r="C54" s="57" t="str">
-        <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
-      </x:c>
-      <x:c r="D54" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E54" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F54" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G54" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H54" s="58"/>
-      <x:c r="I54" s="58"/>
-      <x:c r="J54" s="57"/>
-      <x:c r="K54" s="57"/>
-      <x:c r="L54" s="57"/>
-      <x:c r="M54" s="57"/>
-    </x:row>
-    <x:row r="55" ht="26" customHeight="1">
-      <x:c r="A55" s="56" t="str">
-        <x:v>B31</x:v>
-      </x:c>
-      <x:c r="B55" s="57" t="str">
-        <x:v>Step 12 · Quality</x:v>
-      </x:c>
-      <x:c r="C55" s="57" t="str">
-        <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
-      </x:c>
-      <x:c r="D55" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E55" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F55" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G55" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H55" s="58"/>
-      <x:c r="I55" s="58"/>
-      <x:c r="J55" s="57"/>
-      <x:c r="K55" s="57"/>
-      <x:c r="L55" s="57"/>
-      <x:c r="M55" s="57"/>
-    </x:row>
-    <x:row r="56" ht="26" customHeight="1">
-      <x:c r="A56" s="56" t="str">
-        <x:v>B32</x:v>
-      </x:c>
-      <x:c r="B56" s="57" t="str">
-        <x:v>Step 12 · Security</x:v>
-      </x:c>
-      <x:c r="C56" s="57" t="str">
-        <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
-      </x:c>
-      <x:c r="D56" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E56" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F56" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G56" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H56" s="58"/>
-      <x:c r="I56" s="58"/>
-      <x:c r="J56" s="57"/>
-      <x:c r="K56" s="57"/>
-      <x:c r="L56" s="57"/>
-      <x:c r="M56" s="57"/>
+      <x:c r="H56" s="68"/>
+      <x:c r="I56" s="68"/>
+      <x:c r="J56" s="67"/>
+      <x:c r="K56" s="67"/>
+      <x:c r="L56" s="67"/>
+      <x:c r="M56" s="67"/>
     </x:row>
     <x:row r="57" ht="26" customHeight="1">
-      <x:c r="A57" s="56" t="str">
-        <x:v>B33</x:v>
-      </x:c>
-      <x:c r="B57" s="57" t="str">
-        <x:v>Step 7 · Owners</x:v>
-      </x:c>
-      <x:c r="C57" s="57" t="str">
-        <x:v>Home-value and service enquiry data handling</x:v>
-      </x:c>
-      <x:c r="D57" s="57" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E57" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F57" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G57" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A57" s="56"/>
+      <x:c r="B57" s="57"/>
+      <x:c r="C57" s="57"/>
+      <x:c r="D57" s="57"/>
+      <x:c r="E57" s="57"/>
+      <x:c r="F57" s="57"/>
+      <x:c r="G57" s="57"/>
       <x:c r="H57" s="58"/>
       <x:c r="I57" s="58"/>
       <x:c r="J57" s="57"/>
@@ -42264,27 +42606,13 @@
       <x:c r="M57" s="57"/>
     </x:row>
     <x:row r="58" ht="26" customHeight="1">
-      <x:c r="A58" s="56" t="str">
-        <x:v>E01</x:v>
-      </x:c>
-      <x:c r="B58" s="57" t="str">
-        <x:v>Step 6 · Email</x:v>
-      </x:c>
-      <x:c r="C58" s="57" t="str">
-        <x:v>Enquiry notification with retryable queue/outbox</x:v>
-      </x:c>
-      <x:c r="D58" s="57" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E58" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F58" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G58" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A58" s="56"/>
+      <x:c r="B58" s="57"/>
+      <x:c r="C58" s="57"/>
+      <x:c r="D58" s="57"/>
+      <x:c r="E58" s="57"/>
+      <x:c r="F58" s="57"/>
+      <x:c r="G58" s="57"/>
       <x:c r="H58" s="58"/>
       <x:c r="I58" s="58"/>
       <x:c r="J58" s="57"/>
@@ -42293,27 +42621,13 @@
       <x:c r="M58" s="57"/>
     </x:row>
     <x:row r="59" ht="26" customHeight="1">
-      <x:c r="A59" s="56" t="str">
-        <x:v>E02</x:v>
-      </x:c>
-      <x:c r="B59" s="57" t="str">
-        <x:v>Step 6 · Email</x:v>
-      </x:c>
-      <x:c r="C59" s="57" t="str">
-        <x:v>Thai and English buyer enquiry acknowledgments</x:v>
-      </x:c>
-      <x:c r="D59" s="57" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E59" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F59" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G59" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A59" s="56"/>
+      <x:c r="B59" s="57"/>
+      <x:c r="C59" s="57"/>
+      <x:c r="D59" s="57"/>
+      <x:c r="E59" s="57"/>
+      <x:c r="F59" s="57"/>
+      <x:c r="G59" s="57"/>
       <x:c r="H59" s="58"/>
       <x:c r="I59" s="58"/>
       <x:c r="J59" s="57"/>
@@ -42322,27 +42636,13 @@
       <x:c r="M59" s="57"/>
     </x:row>
     <x:row r="60" ht="26" customHeight="1">
-      <x:c r="A60" s="56" t="str">
-        <x:v>E03</x:v>
-      </x:c>
-      <x:c r="B60" s="57" t="str">
-        <x:v>Step 8 · Email</x:v>
-      </x:c>
-      <x:c r="C60" s="57" t="str">
-        <x:v>Project brochure/price list email delivery</x:v>
-      </x:c>
-      <x:c r="D60" s="57" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E60" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F60" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G60" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A60" s="56"/>
+      <x:c r="B60" s="57"/>
+      <x:c r="C60" s="57"/>
+      <x:c r="D60" s="57"/>
+      <x:c r="E60" s="57"/>
+      <x:c r="F60" s="57"/>
+      <x:c r="G60" s="57"/>
       <x:c r="H60" s="58"/>
       <x:c r="I60" s="58"/>
       <x:c r="J60" s="57"/>
@@ -42351,27 +42651,13 @@
       <x:c r="M60" s="57"/>
     </x:row>
     <x:row r="61" ht="26" customHeight="1">
-      <x:c r="A61" s="56" t="str">
-        <x:v>E04</x:v>
-      </x:c>
-      <x:c r="B61" s="57" t="str">
-        <x:v>Step 8 · Email</x:v>
-      </x:c>
-      <x:c r="C61" s="57" t="str">
-        <x:v>Site visit request and confirmation notifications</x:v>
-      </x:c>
-      <x:c r="D61" s="57" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E61" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F61" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G61" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A61" s="56"/>
+      <x:c r="B61" s="57"/>
+      <x:c r="C61" s="57"/>
+      <x:c r="D61" s="57"/>
+      <x:c r="E61" s="57"/>
+      <x:c r="F61" s="57"/>
+      <x:c r="G61" s="57"/>
       <x:c r="H61" s="58"/>
       <x:c r="I61" s="58"/>
       <x:c r="J61" s="57"/>
@@ -42380,27 +42666,13 @@
       <x:c r="M61" s="57"/>
     </x:row>
     <x:row r="62" ht="26" customHeight="1">
-      <x:c r="A62" s="56" t="str">
-        <x:v>E05</x:v>
-      </x:c>
-      <x:c r="B62" s="57" t="str">
-        <x:v>Step 9 · Alerts</x:v>
-      </x:c>
-      <x:c r="C62" s="57" t="str">
-        <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
-      </x:c>
-      <x:c r="D62" s="57" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E62" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F62" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G62" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A62" s="56"/>
+      <x:c r="B62" s="57"/>
+      <x:c r="C62" s="57"/>
+      <x:c r="D62" s="57"/>
+      <x:c r="E62" s="57"/>
+      <x:c r="F62" s="57"/>
+      <x:c r="G62" s="57"/>
       <x:c r="H62" s="58"/>
       <x:c r="I62" s="58"/>
       <x:c r="J62" s="57"/>
@@ -42409,27 +42681,13 @@
       <x:c r="M62" s="57"/>
     </x:row>
     <x:row r="63" ht="26" customHeight="1">
-      <x:c r="A63" s="56" t="str">
-        <x:v>E06</x:v>
-      </x:c>
-      <x:c r="B63" s="57" t="str">
-        <x:v>Step 10B · Email</x:v>
-      </x:c>
-      <x:c r="C63" s="57" t="str">
-        <x:v>Account verification and recovery messages if email auth approved</x:v>
-      </x:c>
-      <x:c r="D63" s="57" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E63" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F63" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G63" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A63" s="56"/>
+      <x:c r="B63" s="57"/>
+      <x:c r="C63" s="57"/>
+      <x:c r="D63" s="57"/>
+      <x:c r="E63" s="57"/>
+      <x:c r="F63" s="57"/>
+      <x:c r="G63" s="57"/>
       <x:c r="H63" s="58"/>
       <x:c r="I63" s="58"/>
       <x:c r="J63" s="57"/>
@@ -42438,27 +42696,13 @@
       <x:c r="M63" s="57"/>
     </x:row>
     <x:row r="64" ht="26" customHeight="1">
-      <x:c r="A64" s="56" t="str">
-        <x:v>E07</x:v>
-      </x:c>
-      <x:c r="B64" s="57" t="str">
-        <x:v>Step 11B · Email</x:v>
-      </x:c>
-      <x:c r="C64" s="57" t="str">
-        <x:v>Agent notification/routing administration</x:v>
-      </x:c>
-      <x:c r="D64" s="57" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E64" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F64" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G64" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A64" s="56"/>
+      <x:c r="B64" s="57"/>
+      <x:c r="C64" s="57"/>
+      <x:c r="D64" s="57"/>
+      <x:c r="E64" s="57"/>
+      <x:c r="F64" s="57"/>
+      <x:c r="G64" s="57"/>
       <x:c r="H64" s="58"/>
       <x:c r="I64" s="58"/>
       <x:c r="J64" s="57"/>
@@ -42467,27 +42711,13 @@
       <x:c r="M64" s="57"/>
     </x:row>
     <x:row r="65" ht="26" customHeight="1">
-      <x:c r="A65" s="56" t="str">
-        <x:v>E08</x:v>
-      </x:c>
-      <x:c r="B65" s="57" t="str">
-        <x:v>Step 7 · Email</x:v>
-      </x:c>
-      <x:c r="C65" s="57" t="str">
-        <x:v>Home valuation and service enquiry replies</x:v>
-      </x:c>
-      <x:c r="D65" s="57" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E65" s="57" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F65" s="57" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G65" s="57" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
+      <x:c r="A65" s="56"/>
+      <x:c r="B65" s="57"/>
+      <x:c r="C65" s="57"/>
+      <x:c r="D65" s="57"/>
+      <x:c r="E65" s="57"/>
+      <x:c r="F65" s="57"/>
+      <x:c r="G65" s="57"/>
       <x:c r="H65" s="58"/>
       <x:c r="I65" s="58"/>
       <x:c r="J65" s="57"/>
@@ -49026,30 +49256,33 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="30" priority="1">
+    <x:cfRule type="expression" dxfId="48" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="31" priority="2">
+    <x:cfRule type="expression" dxfId="49" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="32" priority="3">
+    <x:cfRule type="expression" dxfId="50" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="3">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="E70:E75">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E66:E69">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="E6:E65">
+    <x:dataValidation type="list" sqref="E57:E65">
+      <x:formula1>"Done,Pending,Not started"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E6:E56">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67d3535895ac4ce3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b0b6c89df874021"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Mstar-Property-Task-Tracker.xlsx
+++ b/Mstar-Property-Task-Tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R866ed8a80a8e4152"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R179e190ad4154f90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R3c72ac5ee7a54cda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="R89555a801afa41bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R59978eb8e3f8416b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="Rfcb54769f3744b94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R76812f7c00e54ca0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R58d8913d6cac47b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R18c7389186a744d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="R7a73b5917bd245ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R876aa2b2a2ba4faf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="R6e5b00681f7f4fb2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="13">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -133,6 +133,21 @@
         <x:fgColor rgb="FFC6EFCE"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFF6666"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC6EFCE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -141,7 +156,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="73">
+  <x:cellXfs count="83">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -315,11 +330,41 @@
     <x:xf numFmtId="200" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="51">
+  <x:dxfs count="69">
     <x:dxf>
       <x:font>
         <x:color rgb="FF92400E"/>
@@ -467,6 +512,186 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFEFF4FB"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -835,7 +1060,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="34" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="40" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -856,7 +1081,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="35" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -877,7 +1102,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="36" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -898,7 +1123,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="37" name="MstarDoneTasks" displayName="MstarDoneTasks" ref="A5:M20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="MstarDoneTasks" displayName="MstarDoneTasks" ref="A5:M21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -919,7 +1144,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="38" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -940,7 +1165,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="39" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M56" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M56" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1186,7 +1411,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
+        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -1201,14 +1426,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -1272,43 +1497,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="63" t="str">
+      <x:c r="A6" s="73" t="str">
         <x:v>F02</x:v>
       </x:c>
-      <x:c r="B6" s="64" t="str">
+      <x:c r="B6" s="74" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="64" t="str">
+      <x:c r="C6" s="74" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent</x:v>
       </x:c>
-      <x:c r="D6" s="64" t="str">
+      <x:c r="D6" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="64" t="str">
+      <x:c r="E6" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="64" t="str">
+      <x:c r="F6" s="74" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G6" s="64" t="str">
+      <x:c r="G6" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H6" s="65" t="d">
+      <x:c r="H6" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="65" t="d">
+      <x:c r="I6" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="64" t="str">
+      <x:c r="J6" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="64" t="str">
+      <x:c r="K6" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="64" t="str">
+      <x:c r="L6" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="64" t="str">
+      <x:c r="M6" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
 2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.
 2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.
@@ -1317,144 +1542,144 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="250" customHeight="1">
-      <x:c r="A7" s="63" t="str">
+      <x:c r="A7" s="73" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B7" s="64" t="str">
+      <x:c r="B7" s="74" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C7" s="64" t="str">
+      <x:c r="C7" s="74" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D7" s="64" t="str">
+      <x:c r="D7" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="64" t="str">
+      <x:c r="E7" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="64" t="str">
+      <x:c r="F7" s="74" t="str">
         <x:v>Approved temporary crest extracted and implemented. Owner will provide final header logo later.</x:v>
       </x:c>
-      <x:c r="G7" s="64" t="str">
+      <x:c r="G7" s="74" t="str">
         <x:v>Owner: supply final asset/version later; Codex: replace only approved logo.</x:v>
       </x:c>
-      <x:c r="H7" s="65" t="d">
+      <x:c r="H7" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="65" t="d">
+      <x:c r="I7" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="64" t="str">
+      <x:c r="J7" s="74" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K7" s="64" t="str">
+      <x:c r="K7" s="74" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L7" s="64" t="str">
+      <x:c r="L7" s="74" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="64" t="str">
+      <x:c r="M7" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
 2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.
 2026-10-09 foundation: Approved temporary crest extracted and implemented. Owner will provide final header logo later. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="63" t="str">
+      <x:c r="A8" s="73" t="str">
         <x:v>F32</x:v>
       </x:c>
-      <x:c r="B8" s="64" t="str">
+      <x:c r="B8" s="74" t="str">
         <x:v>Step 10A · Wireframe</x:v>
       </x:c>
-      <x:c r="C8" s="64" t="str">
+      <x:c r="C8" s="74" t="str">
         <x:v>Owner-approved login/register/account wireframe before coding</x:v>
       </x:c>
-      <x:c r="D8" s="64" t="str">
+      <x:c r="D8" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="64" t="str">
+      <x:c r="E8" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="64" t="str">
+      <x:c r="F8" s="74" t="str">
         <x:v>Admin/account screens are not part of approved V3 visuals</x:v>
       </x:c>
-      <x:c r="G8" s="64" t="str">
+      <x:c r="G8" s="74" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H8" s="65"/>
-      <x:c r="I8" s="65"/>
-      <x:c r="J8" s="64"/>
-      <x:c r="K8" s="64"/>
-      <x:c r="L8" s="64"/>
-      <x:c r="M8" s="64"/>
+      <x:c r="H8" s="75"/>
+      <x:c r="I8" s="75"/>
+      <x:c r="J8" s="74"/>
+      <x:c r="K8" s="74"/>
+      <x:c r="L8" s="74"/>
+      <x:c r="M8" s="74"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="63" t="str">
+      <x:c r="A9" s="73" t="str">
         <x:v>F34</x:v>
       </x:c>
-      <x:c r="B9" s="64" t="str">
+      <x:c r="B9" s="74" t="str">
         <x:v>Step 11A · Wireframe</x:v>
       </x:c>
-      <x:c r="C9" s="64" t="str">
+      <x:c r="C9" s="74" t="str">
         <x:v>Owner-approved responsive admin dashboard wireframe</x:v>
       </x:c>
-      <x:c r="D9" s="64" t="str">
+      <x:c r="D9" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="64" t="str">
+      <x:c r="E9" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="64" t="str">
+      <x:c r="F9" s="74" t="str">
         <x:v>Admin UI not included in V3; design approval required</x:v>
       </x:c>
-      <x:c r="G9" s="64" t="str">
+      <x:c r="G9" s="74" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H9" s="65"/>
-      <x:c r="I9" s="65"/>
-      <x:c r="J9" s="64"/>
-      <x:c r="K9" s="64"/>
-      <x:c r="L9" s="64"/>
-      <x:c r="M9" s="64"/>
+      <x:c r="H9" s="75"/>
+      <x:c r="I9" s="75"/>
+      <x:c r="J9" s="74"/>
+      <x:c r="K9" s="74"/>
+      <x:c r="L9" s="74"/>
+      <x:c r="M9" s="74"/>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="63" t="str">
+      <x:c r="A10" s="73" t="str">
         <x:v>F01</x:v>
       </x:c>
-      <x:c r="B10" s="64" t="str">
+      <x:c r="B10" s="74" t="str">
         <x:v>Step 1 · Design</x:v>
       </x:c>
-      <x:c r="C10" s="64" t="str">
+      <x:c r="C10" s="74" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives</x:v>
       </x:c>
-      <x:c r="D10" s="64" t="str">
+      <x:c r="D10" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E10" s="64" t="str">
+      <x:c r="E10" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="64" t="str">
+      <x:c r="F10" s="74" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G10" s="64" t="str">
+      <x:c r="G10" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H10" s="65" t="d">
+      <x:c r="H10" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="65" t="d">
+      <x:c r="I10" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="64" t="str">
+      <x:c r="J10" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="64" t="str">
+      <x:c r="K10" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="64" t="str">
+      <x:c r="L10" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="64" t="str">
+      <x:c r="M10" s="74" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1462,43 +1687,43 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="310" customHeight="1">
-      <x:c r="A11" s="63" t="str">
+      <x:c r="A11" s="73" t="str">
         <x:v>F04</x:v>
       </x:c>
-      <x:c r="B11" s="64" t="str">
+      <x:c r="B11" s="74" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C11" s="64" t="str">
+      <x:c r="C11" s="74" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in</x:v>
       </x:c>
-      <x:c r="D11" s="64" t="str">
+      <x:c r="D11" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E11" s="64" t="str">
+      <x:c r="E11" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="64" t="str">
+      <x:c r="F11" s="74" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G11" s="64" t="str">
+      <x:c r="G11" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H11" s="65" t="d">
+      <x:c r="H11" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I11" s="65" t="d">
+      <x:c r="I11" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="64" t="str">
+      <x:c r="J11" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K11" s="64" t="str">
+      <x:c r="K11" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L11" s="64" t="str">
+      <x:c r="L11" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M11" s="64" t="str">
+      <x:c r="M11" s="74" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1506,43 +1731,43 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="310" customHeight="1">
-      <x:c r="A12" s="63" t="str">
+      <x:c r="A12" s="73" t="str">
         <x:v>F05</x:v>
       </x:c>
-      <x:c r="B12" s="64" t="str">
+      <x:c r="B12" s="74" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C12" s="64" t="str">
+      <x:c r="C12" s="74" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints</x:v>
       </x:c>
-      <x:c r="D12" s="64" t="str">
+      <x:c r="D12" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E12" s="64" t="str">
+      <x:c r="E12" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="64" t="str">
+      <x:c r="F12" s="74" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G12" s="64" t="str">
+      <x:c r="G12" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H12" s="65" t="d">
+      <x:c r="H12" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="65" t="d">
+      <x:c r="I12" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="64" t="str">
+      <x:c r="J12" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K12" s="64" t="str">
+      <x:c r="K12" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L12" s="64" t="str">
+      <x:c r="L12" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="64" t="str">
+      <x:c r="M12" s="74" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1550,43 +1775,43 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="310" customHeight="1">
-      <x:c r="A13" s="63" t="str">
+      <x:c r="A13" s="73" t="str">
         <x:v>F06</x:v>
       </x:c>
-      <x:c r="B13" s="64" t="str">
+      <x:c r="B13" s="74" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C13" s="64" t="str">
+      <x:c r="C13" s="74" t="str">
         <x:v>Light footer, company links, contact and PDPA link</x:v>
       </x:c>
-      <x:c r="D13" s="64" t="str">
+      <x:c r="D13" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E13" s="64" t="str">
+      <x:c r="E13" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F13" s="64" t="str">
+      <x:c r="F13" s="74" t="str">
         <x:v>Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G13" s="64" t="str">
+      <x:c r="G13" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H13" s="65" t="d">
+      <x:c r="H13" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I13" s="65" t="d">
+      <x:c r="I13" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J13" s="64" t="str">
+      <x:c r="J13" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K13" s="64" t="str">
+      <x:c r="K13" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L13" s="64" t="str">
+      <x:c r="L13" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M13" s="64" t="str">
+      <x:c r="M13" s="74" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1594,43 +1819,43 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="310" customHeight="1">
-      <x:c r="A14" s="63" t="str">
+      <x:c r="A14" s="73" t="str">
         <x:v>F07</x:v>
       </x:c>
-      <x:c r="B14" s="64" t="str">
+      <x:c r="B14" s="74" t="str">
         <x:v>Step 1 · i18n</x:v>
       </x:c>
-      <x:c r="C14" s="64" t="str">
+      <x:c r="C14" s="74" t="str">
         <x:v>Thai/English routes, language switch and localized formatting</x:v>
       </x:c>
-      <x:c r="D14" s="64" t="str">
+      <x:c r="D14" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E14" s="64" t="str">
+      <x:c r="E14" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="64" t="str">
+      <x:c r="F14" s="74" t="str">
         <x:v>Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G14" s="64" t="str">
+      <x:c r="G14" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H14" s="65" t="d">
+      <x:c r="H14" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I14" s="65" t="d">
+      <x:c r="I14" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="64" t="str">
+      <x:c r="J14" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K14" s="64" t="str">
+      <x:c r="K14" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L14" s="64" t="str">
+      <x:c r="L14" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M14" s="64" t="str">
+      <x:c r="M14" s="74" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1638,693 +1863,693 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="250" customHeight="1">
-      <x:c r="A15" s="66" t="str">
+      <x:c r="A15" s="76" t="str">
         <x:v>F14</x:v>
       </x:c>
-      <x:c r="B15" s="67" t="str">
+      <x:c r="B15" s="77" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C15" s="67" t="str">
+      <x:c r="C15" s="77" t="str">
         <x:v>Desktop listing/map split and hover/focus pin synchronization</x:v>
       </x:c>
-      <x:c r="D15" s="67" t="str">
+      <x:c r="D15" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="67" t="str">
+      <x:c r="E15" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="67" t="str">
+      <x:c r="F15" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G15" s="67" t="str">
+      <x:c r="G15" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H15" s="68"/>
-      <x:c r="I15" s="68"/>
-      <x:c r="J15" s="67"/>
-      <x:c r="K15" s="67"/>
-      <x:c r="L15" s="67"/>
-      <x:c r="M15" s="67"/>
+      <x:c r="H15" s="78"/>
+      <x:c r="I15" s="78"/>
+      <x:c r="J15" s="77"/>
+      <x:c r="K15" s="77"/>
+      <x:c r="L15" s="77"/>
+      <x:c r="M15" s="77"/>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="66" t="str">
+      <x:c r="A16" s="76" t="str">
         <x:v>F15</x:v>
       </x:c>
-      <x:c r="B16" s="67" t="str">
+      <x:c r="B16" s="77" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C16" s="67" t="str">
+      <x:c r="C16" s="77" t="str">
         <x:v>Phone full-screen Map/List toggle</x:v>
       </x:c>
-      <x:c r="D16" s="67" t="str">
+      <x:c r="D16" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E16" s="67" t="str">
+      <x:c r="E16" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="67" t="str">
+      <x:c r="F16" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G16" s="67" t="str">
+      <x:c r="G16" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H16" s="68"/>
-      <x:c r="I16" s="68"/>
-      <x:c r="J16" s="67"/>
-      <x:c r="K16" s="67"/>
-      <x:c r="L16" s="67"/>
-      <x:c r="M16" s="67"/>
+      <x:c r="H16" s="78"/>
+      <x:c r="I16" s="78"/>
+      <x:c r="J16" s="77"/>
+      <x:c r="K16" s="77"/>
+      <x:c r="L16" s="77"/>
+      <x:c r="M16" s="77"/>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="66" t="str">
+      <x:c r="A17" s="76" t="str">
         <x:v>F16</x:v>
       </x:c>
-      <x:c r="B17" s="67" t="str">
+      <x:c r="B17" s="77" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C17" s="67" t="str">
+      <x:c r="C17" s="77" t="str">
         <x:v>Property detail photo grid and full-screen gallery</x:v>
       </x:c>
-      <x:c r="D17" s="67" t="str">
+      <x:c r="D17" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="67" t="str">
+      <x:c r="E17" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="67" t="str">
+      <x:c r="F17" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G17" s="67" t="str">
+      <x:c r="G17" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H17" s="68"/>
-      <x:c r="I17" s="68"/>
-      <x:c r="J17" s="67"/>
-      <x:c r="K17" s="67"/>
-      <x:c r="L17" s="67"/>
-      <x:c r="M17" s="67"/>
+      <x:c r="H17" s="78"/>
+      <x:c r="I17" s="78"/>
+      <x:c r="J17" s="77"/>
+      <x:c r="K17" s="77"/>
+      <x:c r="L17" s="77"/>
+      <x:c r="M17" s="77"/>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="66" t="str">
+      <x:c r="A18" s="76" t="str">
         <x:v>F17</x:v>
       </x:c>
-      <x:c r="B18" s="67" t="str">
+      <x:c r="B18" s="77" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C18" s="67" t="str">
+      <x:c r="C18" s="77" t="str">
         <x:v>Title, pricing, type-specific facts, long description and sticky tabs</x:v>
       </x:c>
-      <x:c r="D18" s="67" t="str">
+      <x:c r="D18" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="67" t="str">
+      <x:c r="E18" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F18" s="67" t="str">
+      <x:c r="F18" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G18" s="67" t="str">
+      <x:c r="G18" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H18" s="68"/>
-      <x:c r="I18" s="68"/>
-      <x:c r="J18" s="67"/>
-      <x:c r="K18" s="67"/>
-      <x:c r="L18" s="67"/>
-      <x:c r="M18" s="67"/>
+      <x:c r="H18" s="78"/>
+      <x:c r="I18" s="78"/>
+      <x:c r="J18" s="77"/>
+      <x:c r="K18" s="77"/>
+      <x:c r="L18" s="77"/>
+      <x:c r="M18" s="77"/>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="66" t="str">
+      <x:c r="A19" s="76" t="str">
         <x:v>F18</x:v>
       </x:c>
-      <x:c r="B19" s="67" t="str">
+      <x:c r="B19" s="77" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C19" s="67" t="str">
+      <x:c r="C19" s="77" t="str">
         <x:v>Floorplan/video/360 tabs, verified nearby information and map</x:v>
       </x:c>
-      <x:c r="D19" s="67" t="str">
+      <x:c r="D19" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="67" t="str">
+      <x:c r="E19" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="67" t="str">
+      <x:c r="F19" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G19" s="67" t="str">
+      <x:c r="G19" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H19" s="68"/>
-      <x:c r="I19" s="68"/>
-      <x:c r="J19" s="67"/>
-      <x:c r="K19" s="67"/>
-      <x:c r="L19" s="67"/>
-      <x:c r="M19" s="67"/>
+      <x:c r="H19" s="78"/>
+      <x:c r="I19" s="78"/>
+      <x:c r="J19" s="77"/>
+      <x:c r="K19" s="77"/>
+      <x:c r="L19" s="77"/>
+      <x:c r="M19" s="77"/>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="66" t="str">
+      <x:c r="A20" s="76" t="str">
         <x:v>F19</x:v>
       </x:c>
-      <x:c r="B20" s="67" t="str">
+      <x:c r="B20" s="77" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C20" s="67" t="str">
+      <x:c r="C20" s="77" t="str">
         <x:v>Mortgage calculator and area comparison when real data exists</x:v>
       </x:c>
-      <x:c r="D20" s="67" t="str">
+      <x:c r="D20" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="67" t="str">
+      <x:c r="E20" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="67" t="str">
+      <x:c r="F20" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G20" s="67" t="str">
+      <x:c r="G20" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H20" s="68"/>
-      <x:c r="I20" s="68"/>
-      <x:c r="J20" s="67"/>
-      <x:c r="K20" s="67"/>
-      <x:c r="L20" s="67"/>
-      <x:c r="M20" s="67"/>
+      <x:c r="H20" s="78"/>
+      <x:c r="I20" s="78"/>
+      <x:c r="J20" s="77"/>
+      <x:c r="K20" s="77"/>
+      <x:c r="L20" s="77"/>
+      <x:c r="M20" s="77"/>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="66" t="str">
+      <x:c r="A21" s="76" t="str">
         <x:v>F20</x:v>
       </x:c>
-      <x:c r="B21" s="67" t="str">
+      <x:c r="B21" s="77" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C21" s="67" t="str">
+      <x:c r="C21" s="77" t="str">
         <x:v>Same-project units and similar-property cards</x:v>
       </x:c>
-      <x:c r="D21" s="67" t="str">
+      <x:c r="D21" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="67" t="str">
+      <x:c r="E21" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="67" t="str">
+      <x:c r="F21" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G21" s="67" t="str">
+      <x:c r="G21" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H21" s="68"/>
-      <x:c r="I21" s="68"/>
-      <x:c r="J21" s="67"/>
-      <x:c r="K21" s="67"/>
-      <x:c r="L21" s="67"/>
-      <x:c r="M21" s="67"/>
+      <x:c r="H21" s="78"/>
+      <x:c r="I21" s="78"/>
+      <x:c r="J21" s="77"/>
+      <x:c r="K21" s="77"/>
+      <x:c r="L21" s="77"/>
+      <x:c r="M21" s="77"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="66" t="str">
+      <x:c r="A22" s="76" t="str">
         <x:v>F21</x:v>
       </x:c>
-      <x:c r="B22" s="67" t="str">
+      <x:c r="B22" s="77" t="str">
         <x:v>Step 6 · Contact</x:v>
       </x:c>
-      <x:c r="C22" s="67" t="str">
+      <x:c r="C22" s="77" t="str">
         <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
       </x:c>
-      <x:c r="D22" s="67" t="str">
+      <x:c r="D22" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E22" s="67" t="str">
+      <x:c r="E22" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="67" t="str">
+      <x:c r="F22" s="77" t="str">
         <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
-      <x:c r="G22" s="67" t="str">
+      <x:c r="G22" s="77" t="str">
         <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
       </x:c>
-      <x:c r="H22" s="68"/>
-      <x:c r="I22" s="68" t="d">
+      <x:c r="H22" s="78"/>
+      <x:c r="I22" s="78" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J22" s="67" t="str">
+      <x:c r="J22" s="77" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K22" s="67" t="str">
+      <x:c r="K22" s="77" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L22" s="67" t="str">
+      <x:c r="L22" s="77" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M22" s="67" t="str">
+      <x:c r="M22" s="77" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
-      <x:c r="A23" s="66" t="str">
+      <x:c r="A23" s="76" t="str">
         <x:v>F22</x:v>
       </x:c>
-      <x:c r="B23" s="67" t="str">
+      <x:c r="B23" s="77" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C23" s="67" t="str">
+      <x:c r="C23" s="77" t="str">
         <x:v>Single-image hero and compact photography-first layout</x:v>
       </x:c>
-      <x:c r="D23" s="67" t="str">
+      <x:c r="D23" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E23" s="67" t="str">
+      <x:c r="E23" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F23" s="67" t="str">
+      <x:c r="F23" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G23" s="67" t="str">
+      <x:c r="G23" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H23" s="68"/>
-      <x:c r="I23" s="68"/>
-      <x:c r="J23" s="67"/>
-      <x:c r="K23" s="67"/>
-      <x:c r="L23" s="67"/>
-      <x:c r="M23" s="67"/>
+      <x:c r="H23" s="78"/>
+      <x:c r="I23" s="78"/>
+      <x:c r="J23" s="77"/>
+      <x:c r="K23" s="77"/>
+      <x:c r="L23" s="77"/>
+      <x:c r="M23" s="77"/>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="66" t="str">
+      <x:c r="A24" s="76" t="str">
         <x:v>F23</x:v>
       </x:c>
-      <x:c r="B24" s="67" t="str">
+      <x:c r="B24" s="77" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C24" s="67" t="str">
+      <x:c r="C24" s="77" t="str">
         <x:v>Shared search box with Buy/Rent/Projects/Investment tabs</x:v>
       </x:c>
-      <x:c r="D24" s="67" t="str">
+      <x:c r="D24" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E24" s="67" t="str">
+      <x:c r="E24" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="67" t="str">
+      <x:c r="F24" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G24" s="67" t="str">
+      <x:c r="G24" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H24" s="68"/>
-      <x:c r="I24" s="68"/>
-      <x:c r="J24" s="67"/>
-      <x:c r="K24" s="67"/>
-      <x:c r="L24" s="67"/>
-      <x:c r="M24" s="67"/>
+      <x:c r="H24" s="78"/>
+      <x:c r="I24" s="78"/>
+      <x:c r="J24" s="77"/>
+      <x:c r="K24" s="77"/>
+      <x:c r="L24" s="77"/>
+      <x:c r="M24" s="77"/>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="66" t="str">
+      <x:c r="A25" s="76" t="str">
         <x:v>F24</x:v>
       </x:c>
-      <x:c r="B25" s="67" t="str">
+      <x:c r="B25" s="77" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C25" s="67" t="str">
+      <x:c r="C25" s="77" t="str">
         <x:v>Categories, recent searches and location/station suggestions</x:v>
       </x:c>
-      <x:c r="D25" s="67" t="str">
+      <x:c r="D25" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E25" s="67" t="str">
+      <x:c r="E25" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="67" t="str">
+      <x:c r="F25" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G25" s="67" t="str">
+      <x:c r="G25" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H25" s="68"/>
-      <x:c r="I25" s="68"/>
-      <x:c r="J25" s="67"/>
-      <x:c r="K25" s="67"/>
-      <x:c r="L25" s="67"/>
-      <x:c r="M25" s="67"/>
+      <x:c r="H25" s="78"/>
+      <x:c r="I25" s="78"/>
+      <x:c r="J25" s="77"/>
+      <x:c r="K25" s="77"/>
+      <x:c r="L25" s="77"/>
+      <x:c r="M25" s="77"/>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="66" t="str">
+      <x:c r="A26" s="76" t="str">
         <x:v>F25</x:v>
       </x:c>
-      <x:c r="B26" s="67" t="str">
+      <x:c r="B26" s="77" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C26" s="67" t="str">
+      <x:c r="C26" s="77" t="str">
         <x:v>Homes for you carousel directly below search; regions with real listing counts</x:v>
       </x:c>
-      <x:c r="D26" s="67" t="str">
+      <x:c r="D26" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E26" s="67" t="str">
+      <x:c r="E26" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="67" t="str">
+      <x:c r="F26" s="77" t="str">
         <x:v>V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
-      <x:c r="G26" s="67" t="str">
+      <x:c r="G26" s="77" t="str">
         <x:v>Codex: implement approved home-page.html only under Step 7 authorization.</x:v>
       </x:c>
-      <x:c r="H26" s="68"/>
-      <x:c r="I26" s="68" t="d">
+      <x:c r="H26" s="78"/>
+      <x:c r="I26" s="78" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J26" s="67" t="str">
+      <x:c r="J26" s="77" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K26" s="67" t="str">
+      <x:c r="K26" s="77" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L26" s="67" t="str">
+      <x:c r="L26" s="77" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M26" s="67" t="str">
+      <x:c r="M26" s="77" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="66" t="str">
+      <x:c r="A27" s="76" t="str">
         <x:v>F26</x:v>
       </x:c>
-      <x:c r="B27" s="67" t="str">
+      <x:c r="B27" s="77" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C27" s="67" t="str">
+      <x:c r="C27" s="77" t="str">
         <x:v>New projects, tools, services and owner lead CTAs</x:v>
       </x:c>
-      <x:c r="D27" s="67" t="str">
+      <x:c r="D27" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E27" s="67" t="str">
+      <x:c r="E27" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="67" t="str">
+      <x:c r="F27" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G27" s="67" t="str">
+      <x:c r="G27" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H27" s="68"/>
-      <x:c r="I27" s="68"/>
-      <x:c r="J27" s="67"/>
-      <x:c r="K27" s="67"/>
-      <x:c r="L27" s="67"/>
-      <x:c r="M27" s="67"/>
+      <x:c r="H27" s="78"/>
+      <x:c r="I27" s="78"/>
+      <x:c r="J27" s="77"/>
+      <x:c r="K27" s="77"/>
+      <x:c r="L27" s="77"/>
+      <x:c r="M27" s="77"/>
     </x:row>
     <x:row r="28" ht="250" customHeight="1">
-      <x:c r="A28" s="66" t="str">
+      <x:c r="A28" s="76" t="str">
         <x:v>F27</x:v>
       </x:c>
-      <x:c r="B28" s="67" t="str">
+      <x:c r="B28" s="77" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C28" s="67" t="str">
+      <x:c r="C28" s="77" t="str">
         <x:v>Projects index and responsive project detail layouts</x:v>
       </x:c>
-      <x:c r="D28" s="67" t="str">
+      <x:c r="D28" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E28" s="67" t="str">
+      <x:c r="E28" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="67" t="str">
+      <x:c r="F28" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G28" s="67" t="str">
+      <x:c r="G28" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H28" s="68"/>
-      <x:c r="I28" s="68"/>
-      <x:c r="J28" s="67"/>
-      <x:c r="K28" s="67"/>
-      <x:c r="L28" s="67"/>
-      <x:c r="M28" s="67"/>
+      <x:c r="H28" s="78"/>
+      <x:c r="I28" s="78"/>
+      <x:c r="J28" s="77"/>
+      <x:c r="K28" s="77"/>
+      <x:c r="L28" s="77"/>
+      <x:c r="M28" s="77"/>
     </x:row>
     <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="66" t="str">
+      <x:c r="A29" s="76" t="str">
         <x:v>F28</x:v>
       </x:c>
-      <x:c r="B29" s="67" t="str">
+      <x:c r="B29" s="77" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C29" s="67" t="str">
+      <x:c r="C29" s="77" t="str">
         <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
       </x:c>
-      <x:c r="D29" s="67" t="str">
+      <x:c r="D29" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E29" s="67" t="str">
+      <x:c r="E29" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="67" t="str">
+      <x:c r="F29" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="67" t="str">
+      <x:c r="G29" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="68"/>
-      <x:c r="I29" s="68"/>
-      <x:c r="J29" s="67"/>
-      <x:c r="K29" s="67"/>
-      <x:c r="L29" s="67"/>
-      <x:c r="M29" s="67"/>
+      <x:c r="H29" s="78"/>
+      <x:c r="I29" s="78"/>
+      <x:c r="J29" s="77"/>
+      <x:c r="K29" s="77"/>
+      <x:c r="L29" s="77"/>
+      <x:c r="M29" s="77"/>
     </x:row>
     <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="66" t="str">
+      <x:c r="A30" s="76" t="str">
         <x:v>F29</x:v>
       </x:c>
-      <x:c r="B30" s="67" t="str">
+      <x:c r="B30" s="77" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C30" s="67" t="str">
+      <x:c r="C30" s="77" t="str">
         <x:v>Data-driven clickable project SVG plot plan</x:v>
       </x:c>
-      <x:c r="D30" s="67" t="str">
+      <x:c r="D30" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E30" s="67" t="str">
+      <x:c r="E30" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="67" t="str">
+      <x:c r="F30" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="67" t="str">
+      <x:c r="G30" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="68"/>
-      <x:c r="I30" s="68"/>
-      <x:c r="J30" s="67"/>
-      <x:c r="K30" s="67"/>
-      <x:c r="L30" s="67"/>
-      <x:c r="M30" s="67"/>
+      <x:c r="H30" s="78"/>
+      <x:c r="I30" s="78"/>
+      <x:c r="J30" s="77"/>
+      <x:c r="K30" s="77"/>
+      <x:c r="L30" s="77"/>
+      <x:c r="M30" s="77"/>
     </x:row>
     <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="66" t="str">
+      <x:c r="A31" s="76" t="str">
         <x:v>F30</x:v>
       </x:c>
-      <x:c r="B31" s="67" t="str">
+      <x:c r="B31" s="77" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C31" s="67" t="str">
+      <x:c r="C31" s="77" t="str">
         <x:v>Site visit 3-step form and confirmation screens</x:v>
       </x:c>
-      <x:c r="D31" s="67" t="str">
+      <x:c r="D31" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E31" s="67" t="str">
+      <x:c r="E31" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="67" t="str">
+      <x:c r="F31" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="67" t="str">
+      <x:c r="G31" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="68"/>
-      <x:c r="I31" s="68"/>
-      <x:c r="J31" s="67"/>
-      <x:c r="K31" s="67"/>
-      <x:c r="L31" s="67"/>
-      <x:c r="M31" s="67"/>
+      <x:c r="H31" s="78"/>
+      <x:c r="I31" s="78"/>
+      <x:c r="J31" s="77"/>
+      <x:c r="K31" s="77"/>
+      <x:c r="L31" s="77"/>
+      <x:c r="M31" s="77"/>
     </x:row>
     <x:row r="32" ht="250" customHeight="1">
-      <x:c r="A32" s="66" t="str">
+      <x:c r="A32" s="76" t="str">
         <x:v>F31</x:v>
       </x:c>
-      <x:c r="B32" s="67" t="str">
+      <x:c r="B32" s="77" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C32" s="67" t="str">
+      <x:c r="C32" s="77" t="str">
         <x:v>Homes, searches and viewings; local save without account</x:v>
       </x:c>
-      <x:c r="D32" s="67" t="str">
+      <x:c r="D32" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E32" s="67" t="str">
+      <x:c r="E32" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="67" t="str">
+      <x:c r="F32" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G32" s="67" t="str">
+      <x:c r="G32" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H32" s="68"/>
-      <x:c r="I32" s="68"/>
-      <x:c r="J32" s="67"/>
-      <x:c r="K32" s="67"/>
-      <x:c r="L32" s="67"/>
-      <x:c r="M32" s="67"/>
+      <x:c r="H32" s="78"/>
+      <x:c r="I32" s="78"/>
+      <x:c r="J32" s="77"/>
+      <x:c r="K32" s="77"/>
+      <x:c r="L32" s="77"/>
+      <x:c r="M32" s="77"/>
     </x:row>
     <x:row r="33" ht="26" customHeight="1">
-      <x:c r="A33" s="66" t="str">
+      <x:c r="A33" s="76" t="str">
         <x:v>F33</x:v>
       </x:c>
-      <x:c r="B33" s="67" t="str">
+      <x:c r="B33" s="77" t="str">
         <x:v>Step 10B · Accounts</x:v>
       </x:c>
-      <x:c r="C33" s="67" t="str">
+      <x:c r="C33" s="77" t="str">
         <x:v>Build approved auth and account screens only after approval</x:v>
       </x:c>
-      <x:c r="D33" s="67" t="str">
+      <x:c r="D33" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E33" s="67" t="str">
+      <x:c r="E33" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F33" s="67" t="str">
+      <x:c r="F33" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G33" s="67" t="str">
+      <x:c r="G33" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H33" s="68"/>
-      <x:c r="I33" s="68"/>
-      <x:c r="J33" s="67"/>
-      <x:c r="K33" s="67"/>
-      <x:c r="L33" s="67"/>
-      <x:c r="M33" s="67"/>
+      <x:c r="H33" s="78"/>
+      <x:c r="I33" s="78"/>
+      <x:c r="J33" s="77"/>
+      <x:c r="K33" s="77"/>
+      <x:c r="L33" s="77"/>
+      <x:c r="M33" s="77"/>
     </x:row>
     <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="66" t="str">
+      <x:c r="A34" s="76" t="str">
         <x:v>F35</x:v>
       </x:c>
-      <x:c r="B34" s="67" t="str">
+      <x:c r="B34" s="77" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C34" s="67" t="str">
+      <x:c r="C34" s="77" t="str">
         <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
       </x:c>
-      <x:c r="D34" s="67" t="str">
+      <x:c r="D34" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E34" s="67" t="str">
+      <x:c r="E34" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F34" s="67" t="str">
+      <x:c r="F34" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G34" s="67" t="str">
+      <x:c r="G34" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H34" s="68"/>
-      <x:c r="I34" s="68"/>
-      <x:c r="J34" s="67"/>
-      <x:c r="K34" s="67"/>
-      <x:c r="L34" s="67"/>
-      <x:c r="M34" s="67"/>
+      <x:c r="H34" s="78"/>
+      <x:c r="I34" s="78"/>
+      <x:c r="J34" s="77"/>
+      <x:c r="K34" s="77"/>
+      <x:c r="L34" s="77"/>
+      <x:c r="M34" s="77"/>
     </x:row>
     <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="66" t="str">
+      <x:c r="A35" s="76" t="str">
         <x:v>F36</x:v>
       </x:c>
-      <x:c r="B35" s="67" t="str">
+      <x:c r="B35" s="77" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C35" s="67" t="str">
+      <x:c r="C35" s="77" t="str">
         <x:v>Admin-managed searchable filter editor with type safety</x:v>
       </x:c>
-      <x:c r="D35" s="67" t="str">
+      <x:c r="D35" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E35" s="67" t="str">
+      <x:c r="E35" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F35" s="67" t="str">
+      <x:c r="F35" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G35" s="67" t="str">
+      <x:c r="G35" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H35" s="68"/>
-      <x:c r="I35" s="68"/>
-      <x:c r="J35" s="67"/>
-      <x:c r="K35" s="67"/>
-      <x:c r="L35" s="67"/>
-      <x:c r="M35" s="67"/>
+      <x:c r="H35" s="78"/>
+      <x:c r="I35" s="78"/>
+      <x:c r="J35" s="77"/>
+      <x:c r="K35" s="77"/>
+      <x:c r="L35" s="77"/>
+      <x:c r="M35" s="77"/>
     </x:row>
     <x:row r="36" ht="26" customHeight="1">
-      <x:c r="A36" s="66" t="str">
+      <x:c r="A36" s="76" t="str">
         <x:v>F37</x:v>
       </x:c>
-      <x:c r="B36" s="67" t="str">
+      <x:c r="B36" s="77" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C36" s="67" t="str">
+      <x:c r="C36" s="77" t="str">
         <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
       </x:c>
-      <x:c r="D36" s="67" t="str">
+      <x:c r="D36" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E36" s="67" t="str">
+      <x:c r="E36" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F36" s="67" t="str">
+      <x:c r="F36" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G36" s="67" t="str">
+      <x:c r="G36" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H36" s="68"/>
-      <x:c r="I36" s="68"/>
-      <x:c r="J36" s="67"/>
-      <x:c r="K36" s="67"/>
-      <x:c r="L36" s="67"/>
-      <x:c r="M36" s="67"/>
+      <x:c r="H36" s="78"/>
+      <x:c r="I36" s="78"/>
+      <x:c r="J36" s="77"/>
+      <x:c r="K36" s="77"/>
+      <x:c r="L36" s="77"/>
+      <x:c r="M36" s="77"/>
     </x:row>
     <x:row r="37" ht="26" customHeight="1">
-      <x:c r="A37" s="66" t="str">
+      <x:c r="A37" s="76" t="str">
         <x:v>F38</x:v>
       </x:c>
-      <x:c r="B37" s="67" t="str">
+      <x:c r="B37" s="77" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C37" s="67" t="str">
+      <x:c r="C37" s="77" t="str">
         <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
       </x:c>
-      <x:c r="D37" s="67" t="str">
+      <x:c r="D37" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E37" s="67" t="str">
+      <x:c r="E37" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F37" s="67" t="str">
+      <x:c r="F37" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G37" s="67" t="str">
+      <x:c r="G37" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H37" s="68"/>
-      <x:c r="I37" s="68"/>
-      <x:c r="J37" s="67"/>
-      <x:c r="K37" s="67"/>
-      <x:c r="L37" s="67"/>
-      <x:c r="M37" s="67"/>
+      <x:c r="H37" s="78"/>
+      <x:c r="I37" s="78"/>
+      <x:c r="J37" s="77"/>
+      <x:c r="K37" s="77"/>
+      <x:c r="L37" s="77"/>
+      <x:c r="M37" s="77"/>
     </x:row>
     <x:row r="38" ht="26" customHeight="1">
       <x:c r="A38" s="56"/>
@@ -9277,13 +9502,13 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="33" priority="1">
+    <x:cfRule type="expression" dxfId="51" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="34" priority="2">
+    <x:cfRule type="expression" dxfId="52" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="35" priority="3">
+    <x:cfRule type="expression" dxfId="53" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -9297,7 +9522,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70e58c766c37460c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40870228cde24e95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9337,7 +9562,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
+        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -9352,14 +9577,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -9423,267 +9648,267 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="63" t="str">
+      <x:c r="A6" s="73" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B6" s="64" t="str">
+      <x:c r="B6" s="74" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C6" s="64" t="str">
+      <x:c r="C6" s="74" t="str">
         <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
-      <x:c r="D6" s="64" t="str">
+      <x:c r="D6" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E6" s="64" t="str">
+      <x:c r="E6" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="64" t="str">
+      <x:c r="F6" s="74" t="str">
         <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
-      <x:c r="G6" s="64" t="str">
+      <x:c r="G6" s="74" t="str">
         <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
       </x:c>
-      <x:c r="H6" s="65" t="d">
+      <x:c r="H6" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="65" t="d">
+      <x:c r="I6" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="64" t="str">
+      <x:c r="J6" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="64" t="str">
+      <x:c r="K6" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="64" t="str">
+      <x:c r="L6" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="64" t="str">
+      <x:c r="M6" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
 2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
 2026-10-09 Step 2: Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="63" t="str">
+      <x:c r="A7" s="73" t="str">
         <x:v>B17</x:v>
       </x:c>
-      <x:c r="B7" s="64" t="str">
+      <x:c r="B7" s="74" t="str">
         <x:v>Decision · Leads</x:v>
       </x:c>
-      <x:c r="C7" s="64" t="str">
+      <x:c r="C7" s="74" t="str">
         <x:v>Approve shared inbox versus listing agent enquiry destination</x:v>
       </x:c>
-      <x:c r="D7" s="64" t="str">
+      <x:c r="D7" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E7" s="64" t="str">
+      <x:c r="E7" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="64" t="str">
+      <x:c r="F7" s="74" t="str">
         <x:v>BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
-      <x:c r="G7" s="64" t="str">
+      <x:c r="G7" s="74" t="str">
         <x:v>Owner: select routing mode and mailbox</x:v>
       </x:c>
-      <x:c r="H7" s="65"/>
-      <x:c r="I7" s="65"/>
-      <x:c r="J7" s="64"/>
-      <x:c r="K7" s="64"/>
-      <x:c r="L7" s="64"/>
-      <x:c r="M7" s="64"/>
+      <x:c r="H7" s="75"/>
+      <x:c r="I7" s="75"/>
+      <x:c r="J7" s="74"/>
+      <x:c r="K7" s="74"/>
+      <x:c r="L7" s="74"/>
+      <x:c r="M7" s="74"/>
     </x:row>
     <x:row r="8" ht="250" customHeight="1">
-      <x:c r="A8" s="63" t="str">
+      <x:c r="A8" s="73" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B8" s="64" t="str">
+      <x:c r="B8" s="74" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C8" s="64" t="str">
+      <x:c r="C8" s="74" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D8" s="64" t="str">
+      <x:c r="D8" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="64" t="str">
+      <x:c r="E8" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="64" t="str">
+      <x:c r="F8" s="74" t="str">
         <x:v>Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending.</x:v>
       </x:c>
-      <x:c r="G8" s="64" t="str">
+      <x:c r="G8" s="74" t="str">
         <x:v>Owner: provide actual contacts/routing; Codex: integrate and review accessible contact actions later.</x:v>
       </x:c>
-      <x:c r="H8" s="65" t="d">
+      <x:c r="H8" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I8" s="65" t="d">
+      <x:c r="I8" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="64" t="str">
+      <x:c r="J8" s="74" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K8" s="64" t="str">
+      <x:c r="K8" s="74" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L8" s="64" t="str">
+      <x:c r="L8" s="74" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M8" s="64" t="str">
+      <x:c r="M8" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #4 unresolved
 2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.
 2026-10-09 foundation: Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="63" t="str">
+      <x:c r="A9" s="73" t="str">
         <x:v>B23</x:v>
       </x:c>
-      <x:c r="B9" s="64" t="str">
+      <x:c r="B9" s="74" t="str">
         <x:v>Decision · Accounts</x:v>
       </x:c>
-      <x:c r="C9" s="64" t="str">
+      <x:c r="C9" s="74" t="str">
         <x:v>Approve LINE only or LINE+Google+email sign-in</x:v>
       </x:c>
-      <x:c r="D9" s="64" t="str">
+      <x:c r="D9" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E9" s="64" t="str">
+      <x:c r="E9" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="64" t="str">
+      <x:c r="F9" s="74" t="str">
         <x:v>BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
-      <x:c r="G9" s="64" t="str">
+      <x:c r="G9" s="74" t="str">
         <x:v>Owner: approve authentication providers</x:v>
       </x:c>
-      <x:c r="H9" s="65"/>
-      <x:c r="I9" s="65"/>
-      <x:c r="J9" s="64"/>
-      <x:c r="K9" s="64"/>
-      <x:c r="L9" s="64"/>
-      <x:c r="M9" s="64"/>
+      <x:c r="H9" s="75"/>
+      <x:c r="I9" s="75"/>
+      <x:c r="J9" s="74"/>
+      <x:c r="K9" s="74"/>
+      <x:c r="L9" s="74"/>
+      <x:c r="M9" s="74"/>
     </x:row>
     <x:row r="10" ht="200" customHeight="1">
-      <x:c r="A10" s="63" t="str">
+      <x:c r="A10" s="73" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B10" s="64" t="str">
+      <x:c r="B10" s="74" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C10" s="64" t="str">
+      <x:c r="C10" s="74" t="str">
         <x:v>Approve THB only versus optional approximate FX display</x:v>
       </x:c>
-      <x:c r="D10" s="64" t="str">
+      <x:c r="D10" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="64" t="str">
+      <x:c r="E10" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="64" t="str">
+      <x:c r="F10" s="74" t="str">
         <x:v>Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
-      <x:c r="G10" s="64" t="str">
+      <x:c r="G10" s="74" t="str">
         <x:v>Codex: implement USD/THB during authorized currency work; confirm rate source.</x:v>
       </x:c>
-      <x:c r="H10" s="65"/>
-      <x:c r="I10" s="65" t="d">
+      <x:c r="H10" s="75"/>
+      <x:c r="I10" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="64" t="str">
+      <x:c r="J10" s="74" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K10" s="64" t="str">
+      <x:c r="K10" s="74" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L10" s="64" t="str">
+      <x:c r="L10" s="74" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M10" s="64" t="str">
+      <x:c r="M10" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #6 unresolved
 2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="200" customHeight="1">
-      <x:c r="A11" s="63" t="str">
+      <x:c r="A11" s="73" t="str">
         <x:v>B29</x:v>
       </x:c>
-      <x:c r="B11" s="64" t="str">
+      <x:c r="B11" s="74" t="str">
         <x:v>Decision · Projects</x:v>
       </x:c>
-      <x:c r="C11" s="64" t="str">
+      <x:c r="C11" s="74" t="str">
         <x:v>Approve public project prices versus enquiry-only price list</x:v>
       </x:c>
-      <x:c r="D11" s="64" t="str">
+      <x:c r="D11" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E11" s="64" t="str">
+      <x:c r="E11" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="64" t="str">
+      <x:c r="F11" s="74" t="str">
         <x:v>Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
-      <x:c r="G11" s="64" t="str">
+      <x:c r="G11" s="74" t="str">
         <x:v>Codex: add per-record price visibility in authorized backend/admin work after admin wireframe approval.</x:v>
       </x:c>
-      <x:c r="H11" s="65"/>
-      <x:c r="I11" s="65" t="d">
+      <x:c r="H11" s="75"/>
+      <x:c r="I11" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="64" t="str">
+      <x:c r="J11" s="74" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K11" s="64" t="str">
+      <x:c r="K11" s="74" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L11" s="64" t="str">
+      <x:c r="L11" s="74" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M11" s="64" t="str">
+      <x:c r="M11" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #7 unresolved
 2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="310" customHeight="1">
-      <x:c r="A12" s="63" t="str">
+      <x:c r="A12" s="73" t="str">
         <x:v>R01</x:v>
       </x:c>
-      <x:c r="B12" s="64" t="str">
+      <x:c r="B12" s="74" t="str">
         <x:v>Step 0 · Preparation</x:v>
       </x:c>
-      <x:c r="C12" s="64" t="str">
+      <x:c r="C12" s="74" t="str">
         <x:v>Inspect project; establish permanent rules, documentation, Git/live mirror and tracker</x:v>
       </x:c>
-      <x:c r="D12" s="64" t="str">
+      <x:c r="D12" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E12" s="64" t="str">
+      <x:c r="E12" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="64" t="str">
+      <x:c r="F12" s="74" t="str">
         <x:v>Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request.</x:v>
       </x:c>
-      <x:c r="G12" s="64" t="str">
+      <x:c r="G12" s="74" t="str">
         <x:v>Codex: close the separate Step 0 utility/reference-review requirements only when authorized; stop before Step 3.</x:v>
       </x:c>
-      <x:c r="H12" s="65" t="d">
+      <x:c r="H12" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="65" t="d">
+      <x:c r="I12" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="64" t="str">
+      <x:c r="J12" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K12" s="64" t="str">
+      <x:c r="K12" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L12" s="64" t="str">
+      <x:c r="L12" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="64" t="str">
+      <x:c r="M12" s="74" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
@@ -9696,584 +9921,584 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="66" t="str">
+      <x:c r="A13" s="76" t="str">
         <x:v>B08</x:v>
       </x:c>
-      <x:c r="B13" s="67" t="str">
+      <x:c r="B13" s="77" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C13" s="67" t="str">
+      <x:c r="C13" s="77" t="str">
         <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
       </x:c>
-      <x:c r="D13" s="67" t="str">
+      <x:c r="D13" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E13" s="67" t="str">
+      <x:c r="E13" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="67" t="str">
+      <x:c r="F13" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G13" s="67" t="str">
+      <x:c r="G13" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H13" s="68"/>
-      <x:c r="I13" s="68"/>
-      <x:c r="J13" s="67"/>
-      <x:c r="K13" s="67"/>
-      <x:c r="L13" s="67"/>
-      <x:c r="M13" s="67"/>
+      <x:c r="H13" s="78"/>
+      <x:c r="I13" s="78"/>
+      <x:c r="J13" s="77"/>
+      <x:c r="K13" s="77"/>
+      <x:c r="L13" s="77"/>
+      <x:c r="M13" s="77"/>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="66" t="str">
+      <x:c r="A14" s="76" t="str">
         <x:v>B10</x:v>
       </x:c>
-      <x:c r="B14" s="67" t="str">
+      <x:c r="B14" s="77" t="str">
         <x:v>Step 4 · Nearby</x:v>
       </x:c>
-      <x:c r="C14" s="67" t="str">
+      <x:c r="C14" s="77" t="str">
         <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
       </x:c>
-      <x:c r="D14" s="67" t="str">
+      <x:c r="D14" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E14" s="67" t="str">
+      <x:c r="E14" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F14" s="67" t="str">
+      <x:c r="F14" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G14" s="67" t="str">
+      <x:c r="G14" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H14" s="68"/>
-      <x:c r="I14" s="68"/>
-      <x:c r="J14" s="67"/>
-      <x:c r="K14" s="67"/>
-      <x:c r="L14" s="67"/>
-      <x:c r="M14" s="67"/>
+      <x:c r="H14" s="78"/>
+      <x:c r="I14" s="78"/>
+      <x:c r="J14" s="77"/>
+      <x:c r="K14" s="77"/>
+      <x:c r="L14" s="77"/>
+      <x:c r="M14" s="77"/>
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="66" t="str">
+      <x:c r="A15" s="76" t="str">
         <x:v>B11</x:v>
       </x:c>
-      <x:c r="B15" s="67" t="str">
+      <x:c r="B15" s="77" t="str">
         <x:v>Step 5 · Media</x:v>
       </x:c>
-      <x:c r="C15" s="67" t="str">
+      <x:c r="C15" s="77" t="str">
         <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
       </x:c>
-      <x:c r="D15" s="67" t="str">
+      <x:c r="D15" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E15" s="67" t="str">
+      <x:c r="E15" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="67" t="str">
+      <x:c r="F15" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G15" s="67" t="str">
+      <x:c r="G15" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H15" s="68"/>
-      <x:c r="I15" s="68"/>
-      <x:c r="J15" s="67"/>
-      <x:c r="K15" s="67"/>
-      <x:c r="L15" s="67"/>
-      <x:c r="M15" s="67"/>
+      <x:c r="H15" s="78"/>
+      <x:c r="I15" s="78"/>
+      <x:c r="J15" s="77"/>
+      <x:c r="K15" s="77"/>
+      <x:c r="L15" s="77"/>
+      <x:c r="M15" s="77"/>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="66" t="str">
+      <x:c r="A16" s="76" t="str">
         <x:v>B12</x:v>
       </x:c>
-      <x:c r="B16" s="67" t="str">
+      <x:c r="B16" s="77" t="str">
         <x:v>Step 5 · Similar</x:v>
       </x:c>
-      <x:c r="C16" s="67" t="str">
+      <x:c r="C16" s="77" t="str">
         <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
       </x:c>
-      <x:c r="D16" s="67" t="str">
+      <x:c r="D16" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E16" s="67" t="str">
+      <x:c r="E16" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="67" t="str">
+      <x:c r="F16" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G16" s="67" t="str">
+      <x:c r="G16" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H16" s="68"/>
-      <x:c r="I16" s="68"/>
-      <x:c r="J16" s="67"/>
-      <x:c r="K16" s="67"/>
-      <x:c r="L16" s="67"/>
-      <x:c r="M16" s="67"/>
+      <x:c r="H16" s="78"/>
+      <x:c r="I16" s="78"/>
+      <x:c r="J16" s="77"/>
+      <x:c r="K16" s="77"/>
+      <x:c r="L16" s="77"/>
+      <x:c r="M16" s="77"/>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="66" t="str">
+      <x:c r="A17" s="76" t="str">
         <x:v>B13</x:v>
       </x:c>
-      <x:c r="B17" s="67" t="str">
+      <x:c r="B17" s="77" t="str">
         <x:v>Step 5 · Metrics</x:v>
       </x:c>
-      <x:c r="C17" s="67" t="str">
+      <x:c r="C17" s="77" t="str">
         <x:v>Comparable pricing/yield gated by verified sample size</x:v>
       </x:c>
-      <x:c r="D17" s="67" t="str">
+      <x:c r="D17" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E17" s="67" t="str">
+      <x:c r="E17" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="67" t="str">
+      <x:c r="F17" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G17" s="67" t="str">
+      <x:c r="G17" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H17" s="68"/>
-      <x:c r="I17" s="68"/>
-      <x:c r="J17" s="67"/>
-      <x:c r="K17" s="67"/>
-      <x:c r="L17" s="67"/>
-      <x:c r="M17" s="67"/>
+      <x:c r="H17" s="78"/>
+      <x:c r="I17" s="78"/>
+      <x:c r="J17" s="77"/>
+      <x:c r="K17" s="77"/>
+      <x:c r="L17" s="77"/>
+      <x:c r="M17" s="77"/>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="66" t="str">
+      <x:c r="A18" s="76" t="str">
         <x:v>B14</x:v>
       </x:c>
-      <x:c r="B18" s="67" t="str">
+      <x:c r="B18" s="77" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C18" s="67" t="str">
+      <x:c r="C18" s="77" t="str">
         <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
       </x:c>
-      <x:c r="D18" s="67" t="str">
+      <x:c r="D18" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E18" s="67" t="str">
+      <x:c r="E18" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F18" s="67" t="str">
+      <x:c r="F18" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G18" s="67" t="str">
+      <x:c r="G18" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H18" s="68"/>
-      <x:c r="I18" s="68"/>
-      <x:c r="J18" s="67"/>
-      <x:c r="K18" s="67"/>
-      <x:c r="L18" s="67"/>
-      <x:c r="M18" s="67"/>
+      <x:c r="H18" s="78"/>
+      <x:c r="I18" s="78"/>
+      <x:c r="J18" s="77"/>
+      <x:c r="K18" s="77"/>
+      <x:c r="L18" s="77"/>
+      <x:c r="M18" s="77"/>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="66" t="str">
+      <x:c r="A19" s="76" t="str">
         <x:v>B15</x:v>
       </x:c>
-      <x:c r="B19" s="67" t="str">
+      <x:c r="B19" s="77" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C19" s="67" t="str">
+      <x:c r="C19" s="77" t="str">
         <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
       </x:c>
-      <x:c r="D19" s="67" t="str">
+      <x:c r="D19" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E19" s="67" t="str">
+      <x:c r="E19" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="67" t="str">
+      <x:c r="F19" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G19" s="67" t="str">
+      <x:c r="G19" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H19" s="68"/>
-      <x:c r="I19" s="68"/>
-      <x:c r="J19" s="67"/>
-      <x:c r="K19" s="67"/>
-      <x:c r="L19" s="67"/>
-      <x:c r="M19" s="67"/>
+      <x:c r="H19" s="78"/>
+      <x:c r="I19" s="78"/>
+      <x:c r="J19" s="77"/>
+      <x:c r="K19" s="77"/>
+      <x:c r="L19" s="77"/>
+      <x:c r="M19" s="77"/>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="66" t="str">
+      <x:c r="A20" s="76" t="str">
         <x:v>B16</x:v>
       </x:c>
-      <x:c r="B20" s="67" t="str">
+      <x:c r="B20" s="77" t="str">
         <x:v>Step 6 · Security</x:v>
       </x:c>
-      <x:c r="C20" s="67" t="str">
+      <x:c r="C20" s="77" t="str">
         <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
       </x:c>
-      <x:c r="D20" s="67" t="str">
+      <x:c r="D20" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E20" s="67" t="str">
+      <x:c r="E20" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="67" t="str">
+      <x:c r="F20" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G20" s="67" t="str">
+      <x:c r="G20" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H20" s="68"/>
-      <x:c r="I20" s="68"/>
-      <x:c r="J20" s="67"/>
-      <x:c r="K20" s="67"/>
-      <x:c r="L20" s="67"/>
-      <x:c r="M20" s="67"/>
+      <x:c r="H20" s="78"/>
+      <x:c r="I20" s="78"/>
+      <x:c r="J20" s="77"/>
+      <x:c r="K20" s="77"/>
+      <x:c r="L20" s="77"/>
+      <x:c r="M20" s="77"/>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="66" t="str">
+      <x:c r="A21" s="76" t="str">
         <x:v>B19</x:v>
       </x:c>
-      <x:c r="B21" s="67" t="str">
+      <x:c r="B21" s="77" t="str">
         <x:v>Step 6 · Chat</x:v>
       </x:c>
-      <x:c r="C21" s="67" t="str">
+      <x:c r="C21" s="77" t="str">
         <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
       </x:c>
-      <x:c r="D21" s="67" t="str">
+      <x:c r="D21" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E21" s="67" t="str">
+      <x:c r="E21" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="67" t="str">
+      <x:c r="F21" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G21" s="67" t="str">
+      <x:c r="G21" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H21" s="68"/>
-      <x:c r="I21" s="68"/>
-      <x:c r="J21" s="67"/>
-      <x:c r="K21" s="67"/>
-      <x:c r="L21" s="67"/>
-      <x:c r="M21" s="67"/>
+      <x:c r="H21" s="78"/>
+      <x:c r="I21" s="78"/>
+      <x:c r="J21" s="77"/>
+      <x:c r="K21" s="77"/>
+      <x:c r="L21" s="77"/>
+      <x:c r="M21" s="77"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="66" t="str">
+      <x:c r="A22" s="76" t="str">
         <x:v>B20</x:v>
       </x:c>
-      <x:c r="B22" s="67" t="str">
+      <x:c r="B22" s="77" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C22" s="67" t="str">
+      <x:c r="C22" s="77" t="str">
         <x:v>Project/unit/plot status logic and validation</x:v>
       </x:c>
-      <x:c r="D22" s="67" t="str">
+      <x:c r="D22" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E22" s="67" t="str">
+      <x:c r="E22" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="67" t="str">
+      <x:c r="F22" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G22" s="67" t="str">
+      <x:c r="G22" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H22" s="68"/>
-      <x:c r="I22" s="68"/>
-      <x:c r="J22" s="67"/>
-      <x:c r="K22" s="67"/>
-      <x:c r="L22" s="67"/>
-      <x:c r="M22" s="67"/>
+      <x:c r="H22" s="78"/>
+      <x:c r="I22" s="78"/>
+      <x:c r="J22" s="77"/>
+      <x:c r="K22" s="77"/>
+      <x:c r="L22" s="77"/>
+      <x:c r="M22" s="77"/>
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
-      <x:c r="A23" s="66" t="str">
+      <x:c r="A23" s="76" t="str">
         <x:v>B21</x:v>
       </x:c>
-      <x:c r="B23" s="67" t="str">
+      <x:c r="B23" s="77" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C23" s="67" t="str">
+      <x:c r="C23" s="77" t="str">
         <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
       </x:c>
-      <x:c r="D23" s="67" t="str">
+      <x:c r="D23" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E23" s="67" t="str">
+      <x:c r="E23" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F23" s="67" t="str">
+      <x:c r="F23" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G23" s="67" t="str">
+      <x:c r="G23" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H23" s="68"/>
-      <x:c r="I23" s="68"/>
-      <x:c r="J23" s="67"/>
-      <x:c r="K23" s="67"/>
-      <x:c r="L23" s="67"/>
-      <x:c r="M23" s="67"/>
+      <x:c r="H23" s="78"/>
+      <x:c r="I23" s="78"/>
+      <x:c r="J23" s="77"/>
+      <x:c r="K23" s="77"/>
+      <x:c r="L23" s="77"/>
+      <x:c r="M23" s="77"/>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="66" t="str">
+      <x:c r="A24" s="76" t="str">
         <x:v>B22</x:v>
       </x:c>
-      <x:c r="B24" s="67" t="str">
+      <x:c r="B24" s="77" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C24" s="67" t="str">
+      <x:c r="C24" s="77" t="str">
         <x:v>Saved listings/searches persistence, new-match calculations</x:v>
       </x:c>
-      <x:c r="D24" s="67" t="str">
+      <x:c r="D24" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E24" s="67" t="str">
+      <x:c r="E24" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="67" t="str">
+      <x:c r="F24" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G24" s="67" t="str">
+      <x:c r="G24" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H24" s="68"/>
-      <x:c r="I24" s="68"/>
-      <x:c r="J24" s="67"/>
-      <x:c r="K24" s="67"/>
-      <x:c r="L24" s="67"/>
-      <x:c r="M24" s="67"/>
+      <x:c r="H24" s="78"/>
+      <x:c r="I24" s="78"/>
+      <x:c r="J24" s="77"/>
+      <x:c r="K24" s="77"/>
+      <x:c r="L24" s="77"/>
+      <x:c r="M24" s="77"/>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="66" t="str">
+      <x:c r="A25" s="76" t="str">
         <x:v>B24</x:v>
       </x:c>
-      <x:c r="B25" s="67" t="str">
+      <x:c r="B25" s="77" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C25" s="67" t="str">
+      <x:c r="C25" s="77" t="str">
         <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
       </x:c>
-      <x:c r="D25" s="67" t="str">
+      <x:c r="D25" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E25" s="67" t="str">
+      <x:c r="E25" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="67" t="str">
+      <x:c r="F25" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G25" s="67" t="str">
+      <x:c r="G25" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H25" s="68"/>
-      <x:c r="I25" s="68"/>
-      <x:c r="J25" s="67"/>
-      <x:c r="K25" s="67"/>
-      <x:c r="L25" s="67"/>
-      <x:c r="M25" s="67"/>
+      <x:c r="H25" s="78"/>
+      <x:c r="I25" s="78"/>
+      <x:c r="J25" s="77"/>
+      <x:c r="K25" s="77"/>
+      <x:c r="L25" s="77"/>
+      <x:c r="M25" s="77"/>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="66" t="str">
+      <x:c r="A26" s="76" t="str">
         <x:v>B25</x:v>
       </x:c>
-      <x:c r="B26" s="67" t="str">
+      <x:c r="B26" s="77" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C26" s="67" t="str">
+      <x:c r="C26" s="77" t="str">
         <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
       </x:c>
-      <x:c r="D26" s="67" t="str">
+      <x:c r="D26" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E26" s="67" t="str">
+      <x:c r="E26" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="67" t="str">
+      <x:c r="F26" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G26" s="67" t="str">
+      <x:c r="G26" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H26" s="68"/>
-      <x:c r="I26" s="68"/>
-      <x:c r="J26" s="67"/>
-      <x:c r="K26" s="67"/>
-      <x:c r="L26" s="67"/>
-      <x:c r="M26" s="67"/>
+      <x:c r="H26" s="78"/>
+      <x:c r="I26" s="78"/>
+      <x:c r="J26" s="77"/>
+      <x:c r="K26" s="77"/>
+      <x:c r="L26" s="77"/>
+      <x:c r="M26" s="77"/>
     </x:row>
     <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="66" t="str">
+      <x:c r="A27" s="76" t="str">
         <x:v>B26</x:v>
       </x:c>
-      <x:c r="B27" s="67" t="str">
+      <x:c r="B27" s="77" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C27" s="67" t="str">
+      <x:c r="C27" s="77" t="str">
         <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
       </x:c>
-      <x:c r="D27" s="67" t="str">
+      <x:c r="D27" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E27" s="67" t="str">
+      <x:c r="E27" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="67" t="str">
+      <x:c r="F27" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G27" s="67" t="str">
+      <x:c r="G27" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H27" s="68"/>
-      <x:c r="I27" s="68"/>
-      <x:c r="J27" s="67"/>
-      <x:c r="K27" s="67"/>
-      <x:c r="L27" s="67"/>
-      <x:c r="M27" s="67"/>
+      <x:c r="H27" s="78"/>
+      <x:c r="I27" s="78"/>
+      <x:c r="J27" s="77"/>
+      <x:c r="K27" s="77"/>
+      <x:c r="L27" s="77"/>
+      <x:c r="M27" s="77"/>
     </x:row>
     <x:row r="28" ht="26" customHeight="1">
-      <x:c r="A28" s="66" t="str">
+      <x:c r="A28" s="76" t="str">
         <x:v>B27</x:v>
       </x:c>
-      <x:c r="B28" s="67" t="str">
+      <x:c r="B28" s="77" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C28" s="67" t="str">
+      <x:c r="C28" s="77" t="str">
         <x:v>Admin user management, audit log and sensitive action authorization</x:v>
       </x:c>
-      <x:c r="D28" s="67" t="str">
+      <x:c r="D28" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E28" s="67" t="str">
+      <x:c r="E28" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="67" t="str">
+      <x:c r="F28" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G28" s="67" t="str">
+      <x:c r="G28" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H28" s="68"/>
-      <x:c r="I28" s="68"/>
-      <x:c r="J28" s="67"/>
-      <x:c r="K28" s="67"/>
-      <x:c r="L28" s="67"/>
-      <x:c r="M28" s="67"/>
+      <x:c r="H28" s="78"/>
+      <x:c r="I28" s="78"/>
+      <x:c r="J28" s="77"/>
+      <x:c r="K28" s="77"/>
+      <x:c r="L28" s="77"/>
+      <x:c r="M28" s="77"/>
     </x:row>
     <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="66" t="str">
+      <x:c r="A29" s="76" t="str">
         <x:v>B30</x:v>
       </x:c>
-      <x:c r="B29" s="67" t="str">
+      <x:c r="B29" s="77" t="str">
         <x:v>Step 12 · Deploy</x:v>
       </x:c>
-      <x:c r="C29" s="67" t="str">
+      <x:c r="C29" s="77" t="str">
         <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
       </x:c>
-      <x:c r="D29" s="67" t="str">
+      <x:c r="D29" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E29" s="67" t="str">
+      <x:c r="E29" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="67" t="str">
+      <x:c r="F29" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="67" t="str">
+      <x:c r="G29" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="68"/>
-      <x:c r="I29" s="68"/>
-      <x:c r="J29" s="67"/>
-      <x:c r="K29" s="67"/>
-      <x:c r="L29" s="67"/>
-      <x:c r="M29" s="67"/>
+      <x:c r="H29" s="78"/>
+      <x:c r="I29" s="78"/>
+      <x:c r="J29" s="77"/>
+      <x:c r="K29" s="77"/>
+      <x:c r="L29" s="77"/>
+      <x:c r="M29" s="77"/>
     </x:row>
     <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="66" t="str">
+      <x:c r="A30" s="76" t="str">
         <x:v>B31</x:v>
       </x:c>
-      <x:c r="B30" s="67" t="str">
+      <x:c r="B30" s="77" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C30" s="67" t="str">
+      <x:c r="C30" s="77" t="str">
         <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
       </x:c>
-      <x:c r="D30" s="67" t="str">
+      <x:c r="D30" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E30" s="67" t="str">
+      <x:c r="E30" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="67" t="str">
+      <x:c r="F30" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="67" t="str">
+      <x:c r="G30" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="68"/>
-      <x:c r="I30" s="68"/>
-      <x:c r="J30" s="67"/>
-      <x:c r="K30" s="67"/>
-      <x:c r="L30" s="67"/>
-      <x:c r="M30" s="67"/>
+      <x:c r="H30" s="78"/>
+      <x:c r="I30" s="78"/>
+      <x:c r="J30" s="77"/>
+      <x:c r="K30" s="77"/>
+      <x:c r="L30" s="77"/>
+      <x:c r="M30" s="77"/>
     </x:row>
     <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="66" t="str">
+      <x:c r="A31" s="76" t="str">
         <x:v>B32</x:v>
       </x:c>
-      <x:c r="B31" s="67" t="str">
+      <x:c r="B31" s="77" t="str">
         <x:v>Step 12 · Security</x:v>
       </x:c>
-      <x:c r="C31" s="67" t="str">
+      <x:c r="C31" s="77" t="str">
         <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
       </x:c>
-      <x:c r="D31" s="67" t="str">
+      <x:c r="D31" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E31" s="67" t="str">
+      <x:c r="E31" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="67" t="str">
+      <x:c r="F31" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="67" t="str">
+      <x:c r="G31" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="68"/>
-      <x:c r="I31" s="68"/>
-      <x:c r="J31" s="67"/>
-      <x:c r="K31" s="67"/>
-      <x:c r="L31" s="67"/>
-      <x:c r="M31" s="67"/>
+      <x:c r="H31" s="78"/>
+      <x:c r="I31" s="78"/>
+      <x:c r="J31" s="77"/>
+      <x:c r="K31" s="77"/>
+      <x:c r="L31" s="77"/>
+      <x:c r="M31" s="77"/>
     </x:row>
     <x:row r="32" ht="26" customHeight="1">
-      <x:c r="A32" s="66" t="str">
+      <x:c r="A32" s="76" t="str">
         <x:v>B33</x:v>
       </x:c>
-      <x:c r="B32" s="67" t="str">
+      <x:c r="B32" s="77" t="str">
         <x:v>Step 7 · Owners</x:v>
       </x:c>
-      <x:c r="C32" s="67" t="str">
+      <x:c r="C32" s="77" t="str">
         <x:v>Home-value and service enquiry data handling</x:v>
       </x:c>
-      <x:c r="D32" s="67" t="str">
+      <x:c r="D32" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E32" s="67" t="str">
+      <x:c r="E32" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="67" t="str">
+      <x:c r="F32" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G32" s="67" t="str">
+      <x:c r="G32" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H32" s="68"/>
-      <x:c r="I32" s="68"/>
-      <x:c r="J32" s="67"/>
-      <x:c r="K32" s="67"/>
-      <x:c r="L32" s="67"/>
-      <x:c r="M32" s="67"/>
+      <x:c r="H32" s="78"/>
+      <x:c r="I32" s="78"/>
+      <x:c r="J32" s="77"/>
+      <x:c r="K32" s="77"/>
+      <x:c r="L32" s="77"/>
+      <x:c r="M32" s="77"/>
     </x:row>
     <x:row r="33" ht="26" customHeight="1">
       <x:c r="A33" s="56"/>
@@ -17301,13 +17526,13 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="36" priority="1">
+    <x:cfRule type="expression" dxfId="54" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="37" priority="2">
+    <x:cfRule type="expression" dxfId="55" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="38" priority="3">
+    <x:cfRule type="expression" dxfId="56" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -17324,7 +17549,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56204676537644da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3465b1c52ffa4139"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17364,7 +17589,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
+        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -17379,14 +17604,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -17450,236 +17675,236 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="66" t="str">
+      <x:c r="A6" s="76" t="str">
         <x:v>E01</x:v>
       </x:c>
-      <x:c r="B6" s="67" t="str">
+      <x:c r="B6" s="77" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C6" s="67" t="str">
+      <x:c r="C6" s="77" t="str">
         <x:v>Enquiry notification with retryable queue/outbox</x:v>
       </x:c>
-      <x:c r="D6" s="67" t="str">
+      <x:c r="D6" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E6" s="67" t="str">
+      <x:c r="E6" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F6" s="67" t="str">
+      <x:c r="F6" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G6" s="67" t="str">
+      <x:c r="G6" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H6" s="68"/>
-      <x:c r="I6" s="68"/>
-      <x:c r="J6" s="67"/>
-      <x:c r="K6" s="67"/>
-      <x:c r="L6" s="67"/>
-      <x:c r="M6" s="67"/>
+      <x:c r="H6" s="78"/>
+      <x:c r="I6" s="78"/>
+      <x:c r="J6" s="77"/>
+      <x:c r="K6" s="77"/>
+      <x:c r="L6" s="77"/>
+      <x:c r="M6" s="77"/>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="66" t="str">
+      <x:c r="A7" s="76" t="str">
         <x:v>E02</x:v>
       </x:c>
-      <x:c r="B7" s="67" t="str">
+      <x:c r="B7" s="77" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C7" s="67" t="str">
+      <x:c r="C7" s="77" t="str">
         <x:v>Thai and English buyer enquiry acknowledgments</x:v>
       </x:c>
-      <x:c r="D7" s="67" t="str">
+      <x:c r="D7" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E7" s="67" t="str">
+      <x:c r="E7" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F7" s="67" t="str">
+      <x:c r="F7" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G7" s="67" t="str">
+      <x:c r="G7" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H7" s="68"/>
-      <x:c r="I7" s="68"/>
-      <x:c r="J7" s="67"/>
-      <x:c r="K7" s="67"/>
-      <x:c r="L7" s="67"/>
-      <x:c r="M7" s="67"/>
+      <x:c r="H7" s="78"/>
+      <x:c r="I7" s="78"/>
+      <x:c r="J7" s="77"/>
+      <x:c r="K7" s="77"/>
+      <x:c r="L7" s="77"/>
+      <x:c r="M7" s="77"/>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="66" t="str">
+      <x:c r="A8" s="76" t="str">
         <x:v>E03</x:v>
       </x:c>
-      <x:c r="B8" s="67" t="str">
+      <x:c r="B8" s="77" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C8" s="67" t="str">
+      <x:c r="C8" s="77" t="str">
         <x:v>Project brochure/price list email delivery</x:v>
       </x:c>
-      <x:c r="D8" s="67" t="str">
+      <x:c r="D8" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E8" s="67" t="str">
+      <x:c r="E8" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F8" s="67" t="str">
+      <x:c r="F8" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G8" s="67" t="str">
+      <x:c r="G8" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H8" s="68"/>
-      <x:c r="I8" s="68"/>
-      <x:c r="J8" s="67"/>
-      <x:c r="K8" s="67"/>
-      <x:c r="L8" s="67"/>
-      <x:c r="M8" s="67"/>
+      <x:c r="H8" s="78"/>
+      <x:c r="I8" s="78"/>
+      <x:c r="J8" s="77"/>
+      <x:c r="K8" s="77"/>
+      <x:c r="L8" s="77"/>
+      <x:c r="M8" s="77"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="66" t="str">
+      <x:c r="A9" s="76" t="str">
         <x:v>E04</x:v>
       </x:c>
-      <x:c r="B9" s="67" t="str">
+      <x:c r="B9" s="77" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C9" s="67" t="str">
+      <x:c r="C9" s="77" t="str">
         <x:v>Site visit request and confirmation notifications</x:v>
       </x:c>
-      <x:c r="D9" s="67" t="str">
+      <x:c r="D9" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E9" s="67" t="str">
+      <x:c r="E9" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F9" s="67" t="str">
+      <x:c r="F9" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G9" s="67" t="str">
+      <x:c r="G9" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H9" s="68"/>
-      <x:c r="I9" s="68"/>
-      <x:c r="J9" s="67"/>
-      <x:c r="K9" s="67"/>
-      <x:c r="L9" s="67"/>
-      <x:c r="M9" s="67"/>
+      <x:c r="H9" s="78"/>
+      <x:c r="I9" s="78"/>
+      <x:c r="J9" s="77"/>
+      <x:c r="K9" s="77"/>
+      <x:c r="L9" s="77"/>
+      <x:c r="M9" s="77"/>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="66" t="str">
+      <x:c r="A10" s="76" t="str">
         <x:v>E05</x:v>
       </x:c>
-      <x:c r="B10" s="67" t="str">
+      <x:c r="B10" s="77" t="str">
         <x:v>Step 9 · Alerts</x:v>
       </x:c>
-      <x:c r="C10" s="67" t="str">
+      <x:c r="C10" s="77" t="str">
         <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
       </x:c>
-      <x:c r="D10" s="67" t="str">
+      <x:c r="D10" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E10" s="67" t="str">
+      <x:c r="E10" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F10" s="67" t="str">
+      <x:c r="F10" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G10" s="67" t="str">
+      <x:c r="G10" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H10" s="68"/>
-      <x:c r="I10" s="68"/>
-      <x:c r="J10" s="67"/>
-      <x:c r="K10" s="67"/>
-      <x:c r="L10" s="67"/>
-      <x:c r="M10" s="67"/>
+      <x:c r="H10" s="78"/>
+      <x:c r="I10" s="78"/>
+      <x:c r="J10" s="77"/>
+      <x:c r="K10" s="77"/>
+      <x:c r="L10" s="77"/>
+      <x:c r="M10" s="77"/>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="66" t="str">
+      <x:c r="A11" s="76" t="str">
         <x:v>E06</x:v>
       </x:c>
-      <x:c r="B11" s="67" t="str">
+      <x:c r="B11" s="77" t="str">
         <x:v>Step 10B · Email</x:v>
       </x:c>
-      <x:c r="C11" s="67" t="str">
+      <x:c r="C11" s="77" t="str">
         <x:v>Account verification and recovery messages if email auth approved</x:v>
       </x:c>
-      <x:c r="D11" s="67" t="str">
+      <x:c r="D11" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E11" s="67" t="str">
+      <x:c r="E11" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F11" s="67" t="str">
+      <x:c r="F11" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G11" s="67" t="str">
+      <x:c r="G11" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H11" s="68"/>
-      <x:c r="I11" s="68"/>
-      <x:c r="J11" s="67"/>
-      <x:c r="K11" s="67"/>
-      <x:c r="L11" s="67"/>
-      <x:c r="M11" s="67"/>
+      <x:c r="H11" s="78"/>
+      <x:c r="I11" s="78"/>
+      <x:c r="J11" s="77"/>
+      <x:c r="K11" s="77"/>
+      <x:c r="L11" s="77"/>
+      <x:c r="M11" s="77"/>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="66" t="str">
+      <x:c r="A12" s="76" t="str">
         <x:v>E07</x:v>
       </x:c>
-      <x:c r="B12" s="67" t="str">
+      <x:c r="B12" s="77" t="str">
         <x:v>Step 11B · Email</x:v>
       </x:c>
-      <x:c r="C12" s="67" t="str">
+      <x:c r="C12" s="77" t="str">
         <x:v>Agent notification/routing administration</x:v>
       </x:c>
-      <x:c r="D12" s="67" t="str">
+      <x:c r="D12" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E12" s="67" t="str">
+      <x:c r="E12" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F12" s="67" t="str">
+      <x:c r="F12" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G12" s="67" t="str">
+      <x:c r="G12" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H12" s="68"/>
-      <x:c r="I12" s="68"/>
-      <x:c r="J12" s="67"/>
-      <x:c r="K12" s="67"/>
-      <x:c r="L12" s="67"/>
-      <x:c r="M12" s="67"/>
+      <x:c r="H12" s="78"/>
+      <x:c r="I12" s="78"/>
+      <x:c r="J12" s="77"/>
+      <x:c r="K12" s="77"/>
+      <x:c r="L12" s="77"/>
+      <x:c r="M12" s="77"/>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="66" t="str">
+      <x:c r="A13" s="76" t="str">
         <x:v>E08</x:v>
       </x:c>
-      <x:c r="B13" s="67" t="str">
+      <x:c r="B13" s="77" t="str">
         <x:v>Step 7 · Email</x:v>
       </x:c>
-      <x:c r="C13" s="67" t="str">
+      <x:c r="C13" s="77" t="str">
         <x:v>Home valuation and service enquiry replies</x:v>
       </x:c>
-      <x:c r="D13" s="67" t="str">
+      <x:c r="D13" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E13" s="67" t="str">
+      <x:c r="E13" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="67" t="str">
+      <x:c r="F13" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G13" s="67" t="str">
+      <x:c r="G13" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H13" s="68"/>
-      <x:c r="I13" s="68"/>
-      <x:c r="J13" s="67"/>
-      <x:c r="K13" s="67"/>
-      <x:c r="L13" s="67"/>
-      <x:c r="M13" s="67"/>
+      <x:c r="H13" s="78"/>
+      <x:c r="I13" s="78"/>
+      <x:c r="J13" s="77"/>
+      <x:c r="K13" s="77"/>
+      <x:c r="L13" s="77"/>
+      <x:c r="M13" s="77"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="44"/>
@@ -24992,13 +25217,13 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="39" priority="1">
+    <x:cfRule type="expression" dxfId="57" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="40" priority="2">
+    <x:cfRule type="expression" dxfId="58" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="41" priority="3">
+    <x:cfRule type="expression" dxfId="59" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -25009,7 +25234,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf923c7a382534c0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6550d38adfae48ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25049,7 +25274,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
+        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -25064,14 +25289,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -25135,651 +25360,681 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="69" t="str">
+      <x:c r="A6" s="79" t="str">
         <x:v>B34</x:v>
       </x:c>
-      <x:c r="B6" s="69" t="str">
+      <x:c r="B6" s="79" t="str">
         <x:v>Step 1 · Health</x:v>
       </x:c>
-      <x:c r="C6" s="69" t="str">
+      <x:c r="C6" s="79" t="str">
         <x:v>Basic /api/health endpoint with accurate application and database status</x:v>
       </x:c>
-      <x:c r="D6" s="69" t="str">
+      <x:c r="D6" s="79" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E6" s="69" t="str">
+      <x:c r="E6" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F6" s="69" t="str">
+      <x:c r="F6" s="79" t="str">
         <x:v>Real /api/health now probes the migrated public view rather than an empty database select 1. Actual 200/ready true, stopped-DB 503/unavailable/ready false and recovery to 200 verified.</x:v>
       </x:c>
-      <x:c r="G6" s="69" t="str">
+      <x:c r="G6" s="79" t="str">
         <x:v>Codex: retain truthful readiness and generic errors; start localhost only under owner/test authorization.</x:v>
       </x:c>
-      <x:c r="H6" s="70" t="d">
+      <x:c r="H6" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="70" t="d">
+      <x:c r="I6" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="69" t="str">
+      <x:c r="J6" s="79" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="69" t="str">
+      <x:c r="K6" s="79" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="69" t="str">
+      <x:c r="L6" s="79" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="69" t="str">
+      <x:c r="M6" s="79" t="str">
         <x:v>2026-10-09: Health API planned. No implementation in Step 0.
 2026-10-09 foundation: Real health API implemented: HTTP 200 app ok, database not_configured, ready false before closure. Configured PostgreSQL is probed with Drizzle select 1; failure returns 503. No real database configuration exists. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Real /api/health now probes the migrated public view rather than an empty database select 1. Actual 200/ready true, stopped-DB 503/unavailable/ready false and recovery to 200 verified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="310" customHeight="1">
-      <x:c r="A7" s="69" t="str">
+      <x:c r="A7" s="79" t="str">
         <x:v>B01</x:v>
       </x:c>
-      <x:c r="B7" s="69" t="str">
+      <x:c r="B7" s="79" t="str">
         <x:v>Step 2 · Database</x:v>
       </x:c>
-      <x:c r="C7" s="69" t="str">
+      <x:c r="C7" s="79" t="str">
         <x:v>PostgreSQL/Drizzle schema for listings, projects, agents and users</x:v>
       </x:c>
-      <x:c r="D7" s="69" t="str">
+      <x:c r="D7" s="79" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E7" s="69" t="str">
+      <x:c r="E7" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F7" s="69" t="str">
+      <x:c r="F7" s="79" t="str">
         <x:v>18-table Drizzle schema implemented with bilingual fields, seven property types, sale/rent rules, explicit price visibility and separate non-superuser migration/read-only app roles. Isolated local development/test PostgreSQL configured; no shared service modified.</x:v>
       </x:c>
-      <x:c r="G7" s="69" t="str">
+      <x:c r="G7" s="79" t="str">
         <x:v>Codex: preserve schema/security contracts in later explicitly authorized stages.</x:v>
       </x:c>
-      <x:c r="H7" s="70" t="d">
+      <x:c r="H7" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="70" t="d">
+      <x:c r="I7" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="69" t="str">
+      <x:c r="J7" s="79" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K7" s="69" t="str">
+      <x:c r="K7" s="79" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L7" s="69" t="str">
+      <x:c r="L7" s="79" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="69" t="str">
+      <x:c r="M7" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: 18-table Drizzle schema implemented with bilingual fields, seven property types, sale/rent rules, explicit price visibility and separate non-superuser migration/read-only app roles. Isolated local development/test PostgreSQL configured; no shared service modified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="310" customHeight="1">
-      <x:c r="A8" s="69" t="str">
+      <x:c r="A8" s="79" t="str">
         <x:v>B02</x:v>
       </x:c>
-      <x:c r="B8" s="69" t="str">
+      <x:c r="B8" s="79" t="str">
         <x:v>Step 2 · Database</x:v>
       </x:c>
-      <x:c r="C8" s="69" t="str">
+      <x:c r="C8" s="79" t="str">
         <x:v>Migrations, foreign keys, constraints and rollback procedure</x:v>
       </x:c>
-      <x:c r="D8" s="69" t="str">
+      <x:c r="D8" s="79" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="69" t="str">
+      <x:c r="E8" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F8" s="69" t="str">
+      <x:c r="F8" s="79" t="str">
         <x:v>Generated foundation and custom relational migrations, journal/snapshots, constraints/FKs/triggers and guarded test-only initial rollback implemented. Real pg_dump/committed rollback/pg_restore/rerun pass. No production migration performed.</x:v>
       </x:c>
-      <x:c r="G8" s="69" t="str">
+      <x:c r="G8" s="79" t="str">
         <x:v>Codex: generate reviewed additive migrations for later changes; production migration requires authorization and verified backup.</x:v>
       </x:c>
-      <x:c r="H8" s="70" t="d">
+      <x:c r="H8" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I8" s="70" t="d">
+      <x:c r="I8" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="69" t="str">
+      <x:c r="J8" s="79" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K8" s="69" t="str">
+      <x:c r="K8" s="79" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L8" s="69" t="str">
+      <x:c r="L8" s="79" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M8" s="69" t="str">
+      <x:c r="M8" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Generated foundation and custom relational migrations, journal/snapshots, constraints/FKs/triggers and guarded test-only initial rollback implemented. Real pg_dump/committed rollback/pg_restore/rerun pass. No production migration performed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="310" customHeight="1">
-      <x:c r="A9" s="69" t="str">
+      <x:c r="A9" s="79" t="str">
         <x:v>B03</x:v>
       </x:c>
-      <x:c r="B9" s="69" t="str">
+      <x:c r="B9" s="79" t="str">
         <x:v>Step 2 · Demo</x:v>
       </x:c>
-      <x:c r="C9" s="69" t="str">
+      <x:c r="C9" s="79" t="str">
         <x:v>Clearly fictional seed listings, projects and agents</x:v>
       </x:c>
-      <x:c r="D9" s="69" t="str">
+      <x:c r="D9" s="79" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E9" s="69" t="str">
+      <x:c r="E9" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F9" s="69" t="str">
+      <x:c r="F9" s="79" t="str">
         <x:v>Repeatable local-only seed: 14 explicitly fictional listings, seven types/both intents and related demo records. Invalid domains, disabled users/agents, closed enquiries and off alerts. Public projection excludes demo inventory; no real prices/agents advertised.</x:v>
       </x:c>
-      <x:c r="G9" s="69" t="str">
+      <x:c r="G9" s="79" t="str">
         <x:v>Codex: keep demo data labelled and excluded from genuine inventory; seed only named local dev/test databases.</x:v>
       </x:c>
-      <x:c r="H9" s="70" t="d">
+      <x:c r="H9" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I9" s="70" t="d">
+      <x:c r="I9" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J9" s="69" t="str">
+      <x:c r="J9" s="79" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K9" s="69" t="str">
+      <x:c r="K9" s="79" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L9" s="69" t="str">
+      <x:c r="L9" s="79" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M9" s="69" t="str">
+      <x:c r="M9" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Repeatable local-only seed: 14 explicitly fictional listings, seven types/both intents and related demo records. Invalid domains, disabled users/agents, closed enquiries and off alerts. Public projection excludes demo inventory; no real prices/agents advertised. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="69" t="str">
+      <x:c r="A10" s="79" t="str">
         <x:v>B04</x:v>
       </x:c>
-      <x:c r="B10" s="69" t="str">
+      <x:c r="B10" s="79" t="str">
         <x:v>Step 2 · Search</x:v>
       </x:c>
-      <x:c r="C10" s="69" t="str">
+      <x:c r="C10" s="79" t="str">
         <x:v>Indexes for status, intent, type, price, location and title</x:v>
       </x:c>
-      <x:c r="D10" s="69" t="str">
+      <x:c r="D10" s="79" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="69" t="str">
+      <x:c r="E10" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F10" s="69" t="str">
+      <x:c r="F10" s="79" t="str">
         <x:v>Intent/type/status/price, location/status, bounding coordinates, publication/feed and bilingual simple-text indexes implemented. Catalog and EXPLAIN use checks pass. Tiny-seed plans prove indexes are usable, not production speed.</x:v>
       </x:c>
-      <x:c r="G10" s="69" t="str">
+      <x:c r="G10" s="79" t="str">
         <x:v>Codex: use parameterized typed queries in Step 3; profile against realistic volume during later QA.</x:v>
       </x:c>
-      <x:c r="H10" s="70" t="d">
+      <x:c r="H10" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="70" t="d">
+      <x:c r="I10" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="69" t="str">
+      <x:c r="J10" s="79" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="69" t="str">
+      <x:c r="K10" s="79" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="69" t="str">
+      <x:c r="L10" s="79" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="69" t="str">
+      <x:c r="M10" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Intent/type/status/price, location/status, bounding coordinates, publication/feed and bilingual simple-text indexes implemented. Catalog and EXPLAIN use checks pass. Tiny-seed plans prove indexes are usable, not production speed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="400" customHeight="1">
-      <x:c r="A11" s="69" t="str">
+      <x:c r="A11" s="79" t="str">
         <x:v>F08</x:v>
       </x:c>
-      <x:c r="B11" s="69" t="str">
+      <x:c r="B11" s="79" t="str">
         <x:v>Step 3 · Cards</x:v>
       </x:c>
-      <x:c r="C11" s="69" t="str">
+      <x:c r="C11" s="79" t="str">
         <x:v>Realtor-style 3:2 listing cards, photo controls, bottom-right save heart, facts/address and Contact agent dialog trigger</x:v>
       </x:c>
-      <x:c r="D11" s="69" t="str">
+      <x:c r="D11" s="79" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E11" s="69" t="str">
+      <x:c r="E11" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F11" s="69" t="str">
-        <x:v>One V3 Realtor-style card: 3:2 photo, five-photo arrows/dots/native swipe, pill badges, persistent device save heart, type-specific facts, honest THB/gated price and drop, two-line address and accessible contact dialog. No fabricated real photos/agents; submit remains unavailable until Step 6.</x:v>
-      </x:c>
-      <x:c r="G11" s="69" t="str">
+      <x:c r="F11" s="79" t="str">
+        <x:v>One V3 Realtor-style card: 3:2 photo, five-photo arrows/dots/native swipe, pill badges, persistent device save heart, type-specific facts, honest THB/gated price and drop, two-line address and accessible contact dialog. No fabricated real photos/agents; submit remains unavailable until Step 6.
+2026-10-10 R03: Owner requested local development samples with a visible Sample badge. NODE_ENV must equal development; explicit flag, loopback Host/SITE_URL and named local DB are also required. Request and query/metadata boundaries ignore samples in production even when MSTAR_DEMO_MODE=1. Public hosts are denied. Existing fictional notice and privacy constraints remain.</x:v>
+      </x:c>
+      <x:c r="G11" s="79" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H11" s="70" t="d">
+      <x:c r="H11" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I11" s="70" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="J11" s="69" t="str">
-        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
-      </x:c>
-      <x:c r="K11" s="69" t="str">
-        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
-      </x:c>
-      <x:c r="L11" s="69" t="str">
-        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
-      </x:c>
-      <x:c r="M11" s="69" t="str">
+      <x:c r="I11" s="80" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J11" s="79" t="str">
+        <x:v>PASS: all 44 development Chromium checks covered (42 initially passed; two homepage cold-load timeouts passed in a focused 2/2 warm rerun), Thai/English at 390/768/1024/1440; Sample badge on each buy/rent/invest card and no overflow. PASS: eight production browser checks on actual next build/next start with sample flag still 1; no sample cards, notice, DTOs or metadata; query override and public Host cannot enable samples. PASS: five development and six production actual app/PostgreSQL checks prove 16 published fictional rows remain seeded, production counts match genuine inventory, forced internal sample queries/metadata are denied and configured public SITE_URL rejects samples. PASS: 12 development search groups, TypeScript and production build. Servers stopped afterward; no admin/form submission.</x:v>
+      </x:c>
+      <x:c r="K11" s="79" t="str">
+        <x:v>Preceding c7ca2f8 pushed. This fix commit/push is verified at finalization; exact hash in final report. Revert R03 to Pending if a final gate fails.</x:v>
+      </x:c>
+      <x:c r="L11" s="79" t="str">
+        <x:v>80-file Git/live baseline checked before changes. Safe intended source/config/docs/tracker synchronization and final SHA-256 pairs verified at closeout; no secrets/dependencies/build/test state copied.</x:v>
+      </x:c>
+      <x:c r="M11" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.
-2026-10-09 Step 3: One V3 Realtor-style card: 3:2 photo, five-photo arrows/dots/native swipe, pill badges, persistent device save heart, type-specific facts, honest THB/gated price and drop, two-line address and accessible contact dialog. No fabricated real photos/agents; submit remains unavailable until Step 6. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
+2026-10-09 Step 3: One V3 Realtor-style card: 3:2 photo, five-photo arrows/dots/native swipe, pill badges, persistent device save heart, type-specific facts, honest THB/gated price and drop, two-line address and accessible contact dialog. No fabricated real photos/agents; submit remains unavailable until Step 6. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
+2026-10-10 R03: local development only; Sample badge on each fictional card. Production hard-denies samples and metadata even with flag=1. 44 development checks covered after two cold-load retries; 8 production browser checks, 5 development/6 production DB visibility checks and 12 search groups pass. See R03 and current test evidence; prior history preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="400" customHeight="1">
-      <x:c r="A12" s="69" t="str">
+      <x:c r="A12" s="79" t="str">
         <x:v>F09</x:v>
       </x:c>
-      <x:c r="B12" s="69" t="str">
+      <x:c r="B12" s="79" t="str">
         <x:v>Step 3 · Results</x:v>
       </x:c>
-      <x:c r="C12" s="69" t="str">
+      <x:c r="C12" s="79" t="str">
         <x:v>Responsive /buy, /rent and /invest results layouts</x:v>
       </x:c>
-      <x:c r="D12" s="69" t="str">
+      <x:c r="D12" s="79" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E12" s="69" t="str">
+      <x:c r="E12" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F12" s="69" t="str">
+      <x:c r="F12" s="79" t="str">
         <x:v>Server-rendered /th and /en buy/rent/invest routes. Two desktop card columns, one phone column; empty state, readable heading and cumulative Show more homes. Reserved blank desktop map column; no fake map. Property link reaches an explicit unfinished detail route, not an implemented Step 5 page.</x:v>
       </x:c>
-      <x:c r="G12" s="69" t="str">
+      <x:c r="G12" s="79" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H12" s="70" t="d">
+      <x:c r="H12" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="70" t="d">
+      <x:c r="I12" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="69" t="str">
+      <x:c r="J12" s="79" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K12" s="69" t="str">
+      <x:c r="K12" s="79" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L12" s="69" t="str">
+      <x:c r="L12" s="79" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="69" t="str">
+      <x:c r="M12" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Server-rendered /th and /en buy/rent/invest routes. Two desktop card columns, one phone column; empty state, readable heading and cumulative Show more homes. Reserved blank desktop map column; no fake map. Property link reaches an explicit unfinished detail route, not an implemented Step 5 page. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="400" customHeight="1">
-      <x:c r="A13" s="69" t="str">
+      <x:c r="A13" s="79" t="str">
         <x:v>F10</x:v>
       </x:c>
-      <x:c r="B13" s="69" t="str">
+      <x:c r="B13" s="79" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C13" s="69" t="str">
+      <x:c r="C13" s="79" t="str">
         <x:v>Shared URL filters, active chips, sorting and navigation history</x:v>
       </x:c>
-      <x:c r="D13" s="69" t="str">
+      <x:c r="D13" s="79" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E13" s="69" t="str">
+      <x:c r="E13" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F13" s="69" t="str">
+      <x:c r="F13" s="79" t="str">
         <x:v>Shared validated URL state for homepage/results; active chips, Clear all, sorting and cumulative page state. Applied changes use Next router.push without full reload to preserve meaningful back/forward history; uncommitted popup drafts do not change URLs. Refresh/back/forward tested.</x:v>
       </x:c>
-      <x:c r="G13" s="69" t="str">
+      <x:c r="G13" s="79" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H13" s="70" t="d">
+      <x:c r="H13" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I13" s="70" t="d">
+      <x:c r="I13" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J13" s="69" t="str">
+      <x:c r="J13" s="79" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K13" s="69" t="str">
+      <x:c r="K13" s="79" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L13" s="69" t="str">
+      <x:c r="L13" s="79" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M13" s="69" t="str">
+      <x:c r="M13" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Shared validated URL state for homepage/results; active chips, Clear all, sorting and cumulative page state. Applied changes use Next router.push without full reload to preserve meaningful back/forward history; uncommitted popup drafts do not change URLs. Refresh/back/forward tested. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="400" customHeight="1">
-      <x:c r="A14" s="69" t="str">
+      <x:c r="A14" s="79" t="str">
         <x:v>F11</x:v>
       </x:c>
-      <x:c r="B14" s="69" t="str">
+      <x:c r="B14" s="79" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C14" s="69" t="str">
+      <x:c r="C14" s="79" t="str">
         <x:v>Desktop popovers for price, beds, type and advanced filters</x:v>
       </x:c>
-      <x:c r="D14" s="69" t="str">
+      <x:c r="D14" s="79" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E14" s="69" t="str">
+      <x:c r="E14" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F14" s="69" t="str">
+      <x:c r="F14" s="79" t="str">
         <x:v>Accessible native-dialog desktop popovers for location, intent, price, beds, property types and advanced/DB-defined typed filters. Actual metadata options and live price count tested; Escape, focus trapping and focus restoration verified.</x:v>
       </x:c>
-      <x:c r="G14" s="69" t="str">
+      <x:c r="G14" s="79" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H14" s="70" t="d">
+      <x:c r="H14" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I14" s="70" t="d">
+      <x:c r="I14" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="69" t="str">
+      <x:c r="J14" s="79" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K14" s="69" t="str">
+      <x:c r="K14" s="79" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L14" s="69" t="str">
+      <x:c r="L14" s="79" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M14" s="69" t="str">
+      <x:c r="M14" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Accessible native-dialog desktop popovers for location, intent, price, beds, property types and advanced/DB-defined typed filters. Actual metadata options and live price count tested; Escape, focus trapping and focus restoration verified. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="400" customHeight="1">
-      <x:c r="A15" s="69" t="str">
+      <x:c r="A15" s="79" t="str">
         <x:v>F12</x:v>
       </x:c>
-      <x:c r="B15" s="69" t="str">
+      <x:c r="B15" s="79" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C15" s="69" t="str">
+      <x:c r="C15" s="79" t="str">
         <x:v>Phone full-screen filter sheet, Apply and Clear</x:v>
       </x:c>
-      <x:c r="D15" s="69" t="str">
+      <x:c r="D15" s="79" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="69" t="str">
+      <x:c r="E15" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F15" s="69" t="str">
+      <x:c r="F15" s="79" t="str">
         <x:v>Phone full-screen filter sheets with Apply/Clear, labels, focus controls and no page overflow. Native Chromium phone input proves card swipe; UI checked at 390/768/1024/1440 in Thai/English.</x:v>
       </x:c>
-      <x:c r="G15" s="69" t="str">
+      <x:c r="G15" s="79" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H15" s="70" t="d">
+      <x:c r="H15" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I15" s="70" t="d">
+      <x:c r="I15" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J15" s="69" t="str">
+      <x:c r="J15" s="79" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K15" s="69" t="str">
+      <x:c r="K15" s="79" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L15" s="69" t="str">
+      <x:c r="L15" s="79" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M15" s="69" t="str">
+      <x:c r="M15" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Phone full-screen filter sheets with Apply/Clear, labels, focus controls and no page overflow. Native Chromium phone input proves card swipe; UI checked at 390/768/1024/1440 in Thai/English. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="400" customHeight="1">
-      <x:c r="A16" s="69" t="str">
+      <x:c r="A16" s="79" t="str">
         <x:v>F13</x:v>
       </x:c>
-      <x:c r="B16" s="69" t="str">
+      <x:c r="B16" s="79" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C16" s="69" t="str">
+      <x:c r="C16" s="79" t="str">
         <x:v>Database-derived price histogram and live result count</x:v>
       </x:c>
-      <x:c r="D16" s="69" t="str">
+      <x:c r="D16" s="79" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E16" s="69" t="str">
+      <x:c r="E16" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F16" s="69" t="str">
+      <x:c r="F16" s="79" t="str">
         <x:v>Histogram uses actual matching PUBLIC-price rows, excluding only current min/max range. Gated prices are excluded from price predicates, price ordering and histogram. Debounced actual API count and bounded deterministic queries implemented.</x:v>
       </x:c>
-      <x:c r="G16" s="69" t="str">
+      <x:c r="G16" s="79" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H16" s="70" t="d">
+      <x:c r="H16" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I16" s="70" t="d">
+      <x:c r="I16" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J16" s="69" t="str">
+      <x:c r="J16" s="79" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K16" s="69" t="str">
+      <x:c r="K16" s="79" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L16" s="69" t="str">
+      <x:c r="L16" s="79" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M16" s="69" t="str">
+      <x:c r="M16" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Histogram uses actual matching PUBLIC-price rows, excluding only current min/max range. Gated prices are excluded from price predicates, price ordering and histogram. Debounced actual API count and bounded deterministic queries implemented. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="400" customHeight="1">
-      <x:c r="A17" s="69" t="str">
+      <x:c r="A17" s="79" t="str">
         <x:v>B05</x:v>
       </x:c>
-      <x:c r="B17" s="69" t="str">
+      <x:c r="B17" s="79" t="str">
         <x:v>Step 2 · Filters</x:v>
       </x:c>
-      <x:c r="C17" s="69" t="str">
+      <x:c r="C17" s="79" t="str">
         <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
       </x:c>
-      <x:c r="D17" s="69" t="str">
+      <x:c r="D17" s="79" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E17" s="69" t="str">
+      <x:c r="E17" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F17" s="69" t="str">
+      <x:c r="F17" s="79" t="str">
         <x:v>Existing typed filter definition/option/value tables are consumed safely by results. Only active metadata in the selected genuine/demo partition is exposed. Single/multi/number/boolean kinds, allowed options and property scope validated with parameterized SQL. Production admin CRUD remains Step 11.</x:v>
       </x:c>
-      <x:c r="G17" s="69" t="str">
+      <x:c r="G17" s="79" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H17" s="70" t="d">
+      <x:c r="H17" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I17" s="70" t="d">
+      <x:c r="I17" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J17" s="69" t="str">
+      <x:c r="J17" s="79" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K17" s="69" t="str">
+      <x:c r="K17" s="79" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L17" s="69" t="str">
+      <x:c r="L17" s="79" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M17" s="69" t="str">
+      <x:c r="M17" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Existing typed filter definition/option/value tables are consumed safely by results. Only active metadata in the selected genuine/demo partition is exposed. Single/multi/number/boolean kinds, allowed options and property scope validated with parameterized SQL. Production admin CRUD remains Step 11. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="400" customHeight="1">
-      <x:c r="A18" s="69" t="str">
+      <x:c r="A18" s="79" t="str">
         <x:v>B06</x:v>
       </x:c>
-      <x:c r="B18" s="69" t="str">
+      <x:c r="B18" s="79" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C18" s="69" t="str">
+      <x:c r="C18" s="79" t="str">
         <x:v>Typed validated listing/search data access and pagination</x:v>
       </x:c>
-      <x:c r="D18" s="69" t="str">
+      <x:c r="D18" s="79" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E18" s="69" t="str">
+      <x:c r="E18" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F18" s="69" t="str">
-        <x:v>Server-only bounded, parameterized listing queries and GET /api/listings: sale/rent/invest, location hierarchy/station slugs, beds/baths/size/land/year/amenities/project, sorting/pagination. No contacts, exact hidden location or gated prices in result DTOs. Local demo requires explicit flag and named local DB/trusted Host.</x:v>
-      </x:c>
-      <x:c r="G18" s="69" t="str">
+      <x:c r="F18" s="79" t="str">
+        <x:v>Server-only bounded, parameterized listing queries and GET /api/listings: sale/rent/invest, location hierarchy/station slugs, beds/baths/size/land/year/amenities/project, sorting/pagination. No contacts, exact hidden location or gated prices in result DTOs. Local demo requires explicit flag and named local DB/trusted Host.
+2026-10-10 R03: Owner requested local development samples with a visible Sample badge. NODE_ENV must equal development; explicit flag, loopback Host/SITE_URL and named local DB are also required. Request and query/metadata boundaries ignore samples in production even when MSTAR_DEMO_MODE=1. Public hosts are denied. Existing fictional notice and privacy constraints remain.</x:v>
+      </x:c>
+      <x:c r="G18" s="79" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H18" s="70" t="d">
+      <x:c r="H18" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I18" s="70" t="d">
+      <x:c r="I18" s="80" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J18" s="79" t="str">
+        <x:v>PASS: all 44 development Chromium checks covered (42 initially passed; two homepage cold-load timeouts passed in a focused 2/2 warm rerun), Thai/English at 390/768/1024/1440; Sample badge on each buy/rent/invest card and no overflow. PASS: eight production browser checks on actual next build/next start with sample flag still 1; no sample cards, notice, DTOs or metadata; query override and public Host cannot enable samples. PASS: five development and six production actual app/PostgreSQL checks prove 16 published fictional rows remain seeded, production counts match genuine inventory, forced internal sample queries/metadata are denied and configured public SITE_URL rejects samples. PASS: 12 development search groups, TypeScript and production build. Servers stopped afterward; no admin/form submission.</x:v>
+      </x:c>
+      <x:c r="K18" s="79" t="str">
+        <x:v>Preceding c7ca2f8 pushed. This fix commit/push is verified at finalization; exact hash in final report. Revert R03 to Pending if a final gate fails.</x:v>
+      </x:c>
+      <x:c r="L18" s="79" t="str">
+        <x:v>80-file Git/live baseline checked before changes. Safe intended source/config/docs/tracker synchronization and final SHA-256 pairs verified at closeout; no secrets/dependencies/build/test state copied.</x:v>
+      </x:c>
+      <x:c r="M18" s="79" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 3: Server-only bounded, parameterized listing queries and GET /api/listings: sale/rent/invest, location hierarchy/station slugs, beds/baths/size/land/year/amenities/project, sorting/pagination. No contacts, exact hidden location or gated prices in result DTOs. Local demo requires explicit flag and named local DB/trusted Host. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
+2026-10-10 R03: local development only; Sample badge on each fictional card. Production hard-denies samples and metadata even with flag=1. 44 development checks covered after two cold-load retries; 8 production browser checks, 5 development/6 production DB visibility checks and 12 search groups pass. See R03 and current test evidence; prior history preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="400" customHeight="1">
+      <x:c r="A19" s="79" t="str">
+        <x:v>B07</x:v>
+      </x:c>
+      <x:c r="B19" s="79" t="str">
+        <x:v>Step 3 · Search</x:v>
+      </x:c>
+      <x:c r="C19" s="79" t="str">
+        <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
+      </x:c>
+      <x:c r="D19" s="79" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E19" s="79" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F19" s="79" t="str">
+        <x:v>Validated shared URL parser, actual counts/sort/histogram and DB metadata filters. Additive 0002_station_search_slug migration provides unique non-null station slugs. Real pre-migration development backup, three-migration rerun and isolated dump/rollback/restore regression passed. Demo search seed rerun is idempotent.</x:v>
+      </x:c>
+      <x:c r="G19" s="79" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H19" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J18" s="69" t="str">
+      <x:c r="I19" s="80" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J19" s="79" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K18" s="69" t="str">
+      <x:c r="K19" s="79" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L18" s="69" t="str">
+      <x:c r="L19" s="79" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M18" s="69" t="str">
-        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 Step 3: Server-only bounded, parameterized listing queries and GET /api/listings: sale/rent/invest, location hierarchy/station slugs, beds/baths/size/land/year/amenities/project, sorting/pagination. No contacts, exact hidden location or gated prices in result DTOs. Local demo requires explicit flag and named local DB/trusted Host. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="400" customHeight="1">
-      <x:c r="A19" s="69" t="str">
-        <x:v>B07</x:v>
-      </x:c>
-      <x:c r="B19" s="69" t="str">
-        <x:v>Step 3 · Search</x:v>
-      </x:c>
-      <x:c r="C19" s="69" t="str">
-        <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
-      </x:c>
-      <x:c r="D19" s="69" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E19" s="69" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="F19" s="69" t="str">
-        <x:v>Validated shared URL parser, actual counts/sort/histogram and DB metadata filters. Additive 0002_station_search_slug migration provides unique non-null station slugs. Real pre-migration development backup, three-migration rerun and isolated dump/rollback/restore regression passed. Demo search seed rerun is idempotent.</x:v>
-      </x:c>
-      <x:c r="G19" s="69" t="str">
-        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
-      </x:c>
-      <x:c r="H19" s="70" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="I19" s="70" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="J19" s="69" t="str">
-        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
-      </x:c>
-      <x:c r="K19" s="69" t="str">
-        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
-      </x:c>
-      <x:c r="L19" s="69" t="str">
-        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
-      </x:c>
-      <x:c r="M19" s="69" t="str">
+      <x:c r="M19" s="79" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Validated shared URL parser, actual counts/sort/histogram and DB metadata filters. Additive 0002_station_search_slug migration provides unique non-null station slugs. Real pre-migration development backup, three-migration rerun and isolated dump/rollback/restore regression passed. Demo search seed rerun is idempotent. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="400" customHeight="1">
-      <x:c r="A20" s="69" t="str">
+      <x:c r="A20" s="79" t="str">
         <x:v>R02</x:v>
       </x:c>
-      <x:c r="B20" s="69" t="str">
+      <x:c r="B20" s="79" t="str">
         <x:v>Step 3 · Accessibility</x:v>
       </x:c>
-      <x:c r="C20" s="69" t="str">
+      <x:c r="C20" s="79" t="str">
         <x:v>Fix contact autofocus and swipe/keyboard link handling (F01/F08)</x:v>
       </x:c>
-      <x:c r="D20" s="69" t="str">
+      <x:c r="D20" s="79" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="69" t="str">
+      <x:c r="E20" s="79" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F20" s="69" t="str">
+      <x:c r="F20" s="79" t="str">
         <x:v>Fix linked to F01/F08: dialog autofocus now occurs after native showModal and preserves the trigger for restoration. Swipe cancels only the immediate synthetic pointer click, allowing subsequent keyboard Enter. Streaming-page keyboard test waits for visible focused links. All affected regressions pass.</x:v>
       </x:c>
-      <x:c r="G20" s="69" t="str">
+      <x:c r="G20" s="79" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H20" s="70" t="d">
+      <x:c r="H20" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I20" s="70" t="d">
+      <x:c r="I20" s="80" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J20" s="69" t="str">
+      <x:c r="J20" s="79" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K20" s="69" t="str">
+      <x:c r="K20" s="79" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L20" s="69" t="str">
+      <x:c r="L20" s="79" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M20" s="69" t="str">
+      <x:c r="M20" s="79" t="str">
         <x:v>2026-10-09 discovered during Step 3 real browser testing: contact input lacked focus; swipe suppression blocked the next keyboard activation. Linked to F01/F08.
 2026-10-09 Step 3: Fix linked to F01/F08: dialog autofocus now occurs after native showModal and preserves the trigger for restoration. Swipe cancels only the immediate synthetic pointer click, allowing subsequent keyboard Enter. Streaming-page keyboard test waits for visible focused links. All affected regressions pass. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="44"/>
-      <x:c r="B21" s="44"/>
-      <x:c r="C21" s="44"/>
-      <x:c r="D21" s="44"/>
-      <x:c r="E21" s="44"/>
-      <x:c r="F21" s="44"/>
-      <x:c r="G21" s="44"/>
-      <x:c r="H21" s="45"/>
-      <x:c r="I21" s="45"/>
-      <x:c r="J21" s="44"/>
-      <x:c r="K21" s="44"/>
-      <x:c r="L21" s="44"/>
-      <x:c r="M21" s="44"/>
+    <x:row r="21" ht="400" customHeight="1">
+      <x:c r="A21" s="79" t="str">
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="B21" s="79" t="str">
+        <x:v>Step 3 · Sample safety</x:v>
+      </x:c>
+      <x:c r="C21" s="79" t="str">
+        <x:v>Restrict fictional sample preview to local development; label each card Sample (F08/B06)</x:v>
+      </x:c>
+      <x:c r="D21" s="79" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E21" s="79" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F21" s="79" t="str">
+        <x:v>Owner requested local development samples with a visible Sample badge. NODE_ENV must equal development; explicit flag, loopback Host/SITE_URL and named local DB are also required. Request and query/metadata boundaries ignore samples in production even when MSTAR_DEMO_MODE=1. Public hosts are denied. Existing fictional notice and privacy constraints remain.</x:v>
+      </x:c>
+      <x:c r="G21" s="79" t="str">
+        <x:v>Codex: preserve this deny-by-default policy for every future public listing consumer. Use npm run dev for samples; next start must show genuine stock only. Stop before Step 4.</x:v>
+      </x:c>
+      <x:c r="H21" s="80" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I21" s="80" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J21" s="79" t="str">
+        <x:v>PASS: all 44 development Chromium checks covered (42 initially passed; two homepage cold-load timeouts passed in a focused 2/2 warm rerun), Thai/English at 390/768/1024/1440; Sample badge on each buy/rent/invest card and no overflow. PASS: eight production browser checks on actual next build/next start with sample flag still 1; no sample cards, notice, DTOs or metadata; query override and public Host cannot enable samples. PASS: five development and six production actual app/PostgreSQL checks prove 16 published fictional rows remain seeded, production counts match genuine inventory, forced internal sample queries/metadata are denied and configured public SITE_URL rejects samples. PASS: 12 development search groups, TypeScript and production build. Servers stopped afterward; no admin/form submission.</x:v>
+      </x:c>
+      <x:c r="K21" s="79" t="str">
+        <x:v>Preceding c7ca2f8 pushed. This fix commit/push is verified at finalization; exact hash in final report. Revert R03 to Pending if a final gate fails.</x:v>
+      </x:c>
+      <x:c r="L21" s="79" t="str">
+        <x:v>80-file Git/live baseline checked before changes. Safe intended source/config/docs/tracker synchronization and final SHA-256 pairs verified at closeout; no secrets/dependencies/build/test state copied.</x:v>
+      </x:c>
+      <x:c r="M21" s="79" t="str">
+        <x:v>2026-10-10 R03 created from owner clarification: prior preview lacked a NODE_ENV guard and could appear under next start. Linked F08/B06. Owner requested local development samples with a visible Sample badge. NODE_ENV must equal development; explicit flag, loopback Host/SITE_URL and named local DB are also required. Request and query/metadata boundaries ignore samples in production even when MSTAR_DEMO_MODE=1. Public hosts are denied. Existing fictional notice and privacy constraints remain. PASS: all 44 development Chromium checks covered (42 initially passed; two homepage cold-load timeouts passed in a focused 2/2 warm rerun), Thai/English at 390/768/1024/1440; Sample badge on each buy/rent/invest card and no overflow. PASS: eight production browser checks on actual next build/next start with sample flag still 1; no sample cards, notice, DTOs or metadata; query override and public Host cannot enable samples. PASS: five development and six production actual app/PostgreSQL checks prove 16 published fictional rows remain seeded, production counts match genuine inventory, forced internal sample queries/metadata are denied and configured public SITE_URL rejects samples. PASS: 12 development search groups, TypeScript and production build. Servers stopped afterward; no admin/form submission.</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="44"/>
@@ -32972,24 +33227,24 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="42" priority="1">
+    <x:cfRule type="expression" dxfId="60" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="43" priority="2">
+    <x:cfRule type="expression" dxfId="61" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="44" priority="3">
+    <x:cfRule type="expression" dxfId="62" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E20">
+    <x:dataValidation type="list" sqref="E6:E21">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27d186b9c102497d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab3d923ae9004ec6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33029,7 +33284,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
+        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -33044,14 +33299,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -33115,43 +33370,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="63" t="str">
+      <x:c r="A6" s="73" t="str">
         <x:v>F02</x:v>
       </x:c>
-      <x:c r="B6" s="64" t="str">
+      <x:c r="B6" s="74" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="64" t="str">
+      <x:c r="C6" s="74" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent</x:v>
       </x:c>
-      <x:c r="D6" s="64" t="str">
+      <x:c r="D6" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="64" t="str">
+      <x:c r="E6" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="64" t="str">
+      <x:c r="F6" s="74" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G6" s="64" t="str">
+      <x:c r="G6" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H6" s="65" t="d">
+      <x:c r="H6" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="65" t="d">
+      <x:c r="I6" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="64" t="str">
+      <x:c r="J6" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="64" t="str">
+      <x:c r="K6" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="64" t="str">
+      <x:c r="L6" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="64" t="str">
+      <x:c r="M6" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
 2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.
 2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.
@@ -33160,368 +33415,368 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="250" customHeight="1">
-      <x:c r="A7" s="63" t="str">
+      <x:c r="A7" s="73" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B7" s="64" t="str">
+      <x:c r="B7" s="74" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C7" s="64" t="str">
+      <x:c r="C7" s="74" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D7" s="64" t="str">
+      <x:c r="D7" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="64" t="str">
+      <x:c r="E7" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="64" t="str">
+      <x:c r="F7" s="74" t="str">
         <x:v>Approved temporary crest extracted and implemented. Owner will provide final header logo later.</x:v>
       </x:c>
-      <x:c r="G7" s="64" t="str">
+      <x:c r="G7" s="74" t="str">
         <x:v>Owner: supply final asset/version later; Codex: replace only approved logo.</x:v>
       </x:c>
-      <x:c r="H7" s="65" t="d">
+      <x:c r="H7" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="65" t="d">
+      <x:c r="I7" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="64" t="str">
+      <x:c r="J7" s="74" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K7" s="64" t="str">
+      <x:c r="K7" s="74" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L7" s="64" t="str">
+      <x:c r="L7" s="74" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="64" t="str">
+      <x:c r="M7" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
 2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.
 2026-10-09 foundation: Approved temporary crest extracted and implemented. Owner will provide final header logo later. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="63" t="str">
+      <x:c r="A8" s="73" t="str">
         <x:v>F32</x:v>
       </x:c>
-      <x:c r="B8" s="64" t="str">
+      <x:c r="B8" s="74" t="str">
         <x:v>Step 10A · Wireframe</x:v>
       </x:c>
-      <x:c r="C8" s="64" t="str">
+      <x:c r="C8" s="74" t="str">
         <x:v>Owner-approved login/register/account wireframe before coding</x:v>
       </x:c>
-      <x:c r="D8" s="64" t="str">
+      <x:c r="D8" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="64" t="str">
+      <x:c r="E8" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="64" t="str">
+      <x:c r="F8" s="74" t="str">
         <x:v>Admin/account screens are not part of approved V3 visuals</x:v>
       </x:c>
-      <x:c r="G8" s="64" t="str">
+      <x:c r="G8" s="74" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H8" s="65"/>
-      <x:c r="I8" s="65"/>
-      <x:c r="J8" s="64"/>
-      <x:c r="K8" s="64"/>
-      <x:c r="L8" s="64"/>
-      <x:c r="M8" s="64"/>
+      <x:c r="H8" s="75"/>
+      <x:c r="I8" s="75"/>
+      <x:c r="J8" s="74"/>
+      <x:c r="K8" s="74"/>
+      <x:c r="L8" s="74"/>
+      <x:c r="M8" s="74"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="63" t="str">
+      <x:c r="A9" s="73" t="str">
         <x:v>F34</x:v>
       </x:c>
-      <x:c r="B9" s="64" t="str">
+      <x:c r="B9" s="74" t="str">
         <x:v>Step 11A · Wireframe</x:v>
       </x:c>
-      <x:c r="C9" s="64" t="str">
+      <x:c r="C9" s="74" t="str">
         <x:v>Owner-approved responsive admin dashboard wireframe</x:v>
       </x:c>
-      <x:c r="D9" s="64" t="str">
+      <x:c r="D9" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="64" t="str">
+      <x:c r="E9" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="64" t="str">
+      <x:c r="F9" s="74" t="str">
         <x:v>Admin UI not included in V3; design approval required</x:v>
       </x:c>
-      <x:c r="G9" s="64" t="str">
+      <x:c r="G9" s="74" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H9" s="65"/>
-      <x:c r="I9" s="65"/>
-      <x:c r="J9" s="64"/>
-      <x:c r="K9" s="64"/>
-      <x:c r="L9" s="64"/>
-      <x:c r="M9" s="64"/>
+      <x:c r="H9" s="75"/>
+      <x:c r="I9" s="75"/>
+      <x:c r="J9" s="74"/>
+      <x:c r="K9" s="74"/>
+      <x:c r="L9" s="74"/>
+      <x:c r="M9" s="74"/>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="63" t="str">
+      <x:c r="A10" s="73" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B10" s="64" t="str">
+      <x:c r="B10" s="74" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C10" s="64" t="str">
+      <x:c r="C10" s="74" t="str">
         <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
-      <x:c r="D10" s="64" t="str">
+      <x:c r="D10" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="64" t="str">
+      <x:c r="E10" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="64" t="str">
+      <x:c r="F10" s="74" t="str">
         <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
-      <x:c r="G10" s="64" t="str">
+      <x:c r="G10" s="74" t="str">
         <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
       </x:c>
-      <x:c r="H10" s="65" t="d">
+      <x:c r="H10" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="65" t="d">
+      <x:c r="I10" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="64" t="str">
+      <x:c r="J10" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="64" t="str">
+      <x:c r="K10" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="64" t="str">
+      <x:c r="L10" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="64" t="str">
+      <x:c r="M10" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
 2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
 2026-10-09 Step 2: Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="63" t="str">
+      <x:c r="A11" s="73" t="str">
         <x:v>B17</x:v>
       </x:c>
-      <x:c r="B11" s="64" t="str">
+      <x:c r="B11" s="74" t="str">
         <x:v>Decision · Leads</x:v>
       </x:c>
-      <x:c r="C11" s="64" t="str">
+      <x:c r="C11" s="74" t="str">
         <x:v>Approve shared inbox versus listing agent enquiry destination</x:v>
       </x:c>
-      <x:c r="D11" s="64" t="str">
+      <x:c r="D11" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E11" s="64" t="str">
+      <x:c r="E11" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="64" t="str">
+      <x:c r="F11" s="74" t="str">
         <x:v>BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
-      <x:c r="G11" s="64" t="str">
+      <x:c r="G11" s="74" t="str">
         <x:v>Owner: select routing mode and mailbox</x:v>
       </x:c>
-      <x:c r="H11" s="65"/>
-      <x:c r="I11" s="65"/>
-      <x:c r="J11" s="64"/>
-      <x:c r="K11" s="64"/>
-      <x:c r="L11" s="64"/>
-      <x:c r="M11" s="64"/>
+      <x:c r="H11" s="75"/>
+      <x:c r="I11" s="75"/>
+      <x:c r="J11" s="74"/>
+      <x:c r="K11" s="74"/>
+      <x:c r="L11" s="74"/>
+      <x:c r="M11" s="74"/>
     </x:row>
     <x:row r="12" ht="250" customHeight="1">
-      <x:c r="A12" s="63" t="str">
+      <x:c r="A12" s="73" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B12" s="64" t="str">
+      <x:c r="B12" s="74" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C12" s="64" t="str">
+      <x:c r="C12" s="74" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D12" s="64" t="str">
+      <x:c r="D12" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E12" s="64" t="str">
+      <x:c r="E12" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="64" t="str">
+      <x:c r="F12" s="74" t="str">
         <x:v>Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending.</x:v>
       </x:c>
-      <x:c r="G12" s="64" t="str">
+      <x:c r="G12" s="74" t="str">
         <x:v>Owner: provide actual contacts/routing; Codex: integrate and review accessible contact actions later.</x:v>
       </x:c>
-      <x:c r="H12" s="65" t="d">
+      <x:c r="H12" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="65" t="d">
+      <x:c r="I12" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="64" t="str">
+      <x:c r="J12" s="74" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K12" s="64" t="str">
+      <x:c r="K12" s="74" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L12" s="64" t="str">
+      <x:c r="L12" s="74" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="64" t="str">
+      <x:c r="M12" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #4 unresolved
 2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.
 2026-10-09 foundation: Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="63" t="str">
+      <x:c r="A13" s="73" t="str">
         <x:v>B23</x:v>
       </x:c>
-      <x:c r="B13" s="64" t="str">
+      <x:c r="B13" s="74" t="str">
         <x:v>Decision · Accounts</x:v>
       </x:c>
-      <x:c r="C13" s="64" t="str">
+      <x:c r="C13" s="74" t="str">
         <x:v>Approve LINE only or LINE+Google+email sign-in</x:v>
       </x:c>
-      <x:c r="D13" s="64" t="str">
+      <x:c r="D13" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E13" s="64" t="str">
+      <x:c r="E13" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F13" s="64" t="str">
+      <x:c r="F13" s="74" t="str">
         <x:v>BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
-      <x:c r="G13" s="64" t="str">
+      <x:c r="G13" s="74" t="str">
         <x:v>Owner: approve authentication providers</x:v>
       </x:c>
-      <x:c r="H13" s="65"/>
-      <x:c r="I13" s="65"/>
-      <x:c r="J13" s="64"/>
-      <x:c r="K13" s="64"/>
-      <x:c r="L13" s="64"/>
-      <x:c r="M13" s="64"/>
+      <x:c r="H13" s="75"/>
+      <x:c r="I13" s="75"/>
+      <x:c r="J13" s="74"/>
+      <x:c r="K13" s="74"/>
+      <x:c r="L13" s="74"/>
+      <x:c r="M13" s="74"/>
     </x:row>
     <x:row r="14" ht="200" customHeight="1">
-      <x:c r="A14" s="63" t="str">
+      <x:c r="A14" s="73" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B14" s="64" t="str">
+      <x:c r="B14" s="74" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C14" s="64" t="str">
+      <x:c r="C14" s="74" t="str">
         <x:v>Approve THB only versus optional approximate FX display</x:v>
       </x:c>
-      <x:c r="D14" s="64" t="str">
+      <x:c r="D14" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E14" s="64" t="str">
+      <x:c r="E14" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="64" t="str">
+      <x:c r="F14" s="74" t="str">
         <x:v>Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
-      <x:c r="G14" s="64" t="str">
+      <x:c r="G14" s="74" t="str">
         <x:v>Codex: implement USD/THB during authorized currency work; confirm rate source.</x:v>
       </x:c>
-      <x:c r="H14" s="65"/>
-      <x:c r="I14" s="65" t="d">
+      <x:c r="H14" s="75"/>
+      <x:c r="I14" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="64" t="str">
+      <x:c r="J14" s="74" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K14" s="64" t="str">
+      <x:c r="K14" s="74" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L14" s="64" t="str">
+      <x:c r="L14" s="74" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M14" s="64" t="str">
+      <x:c r="M14" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #6 unresolved
 2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="200" customHeight="1">
-      <x:c r="A15" s="63" t="str">
+      <x:c r="A15" s="73" t="str">
         <x:v>B29</x:v>
       </x:c>
-      <x:c r="B15" s="64" t="str">
+      <x:c r="B15" s="74" t="str">
         <x:v>Decision · Projects</x:v>
       </x:c>
-      <x:c r="C15" s="64" t="str">
+      <x:c r="C15" s="74" t="str">
         <x:v>Approve public project prices versus enquiry-only price list</x:v>
       </x:c>
-      <x:c r="D15" s="64" t="str">
+      <x:c r="D15" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E15" s="64" t="str">
+      <x:c r="E15" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F15" s="64" t="str">
+      <x:c r="F15" s="74" t="str">
         <x:v>Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
-      <x:c r="G15" s="64" t="str">
+      <x:c r="G15" s="74" t="str">
         <x:v>Codex: add per-record price visibility in authorized backend/admin work after admin wireframe approval.</x:v>
       </x:c>
-      <x:c r="H15" s="65"/>
-      <x:c r="I15" s="65" t="d">
+      <x:c r="H15" s="75"/>
+      <x:c r="I15" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J15" s="64" t="str">
+      <x:c r="J15" s="74" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K15" s="64" t="str">
+      <x:c r="K15" s="74" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L15" s="64" t="str">
+      <x:c r="L15" s="74" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M15" s="64" t="str">
+      <x:c r="M15" s="74" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #7 unresolved
 2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="310" customHeight="1">
-      <x:c r="A16" s="64" t="str">
+      <x:c r="A16" s="74" t="str">
         <x:v>R01</x:v>
       </x:c>
-      <x:c r="B16" s="64" t="str">
+      <x:c r="B16" s="74" t="str">
         <x:v>Step 0 · Preparation</x:v>
       </x:c>
-      <x:c r="C16" s="64" t="str">
+      <x:c r="C16" s="74" t="str">
         <x:v>Inspect project; establish permanent rules, documentation, Git/live mirror and tracker</x:v>
       </x:c>
-      <x:c r="D16" s="64" t="str">
+      <x:c r="D16" s="74" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E16" s="64" t="str">
+      <x:c r="E16" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F16" s="64" t="str">
+      <x:c r="F16" s="74" t="str">
         <x:v>Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request.</x:v>
       </x:c>
-      <x:c r="G16" s="64" t="str">
+      <x:c r="G16" s="74" t="str">
         <x:v>Codex: close the separate Step 0 utility/reference-review requirements only when authorized; stop before Step 3.</x:v>
       </x:c>
-      <x:c r="H16" s="65" t="d">
+      <x:c r="H16" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I16" s="65" t="d">
+      <x:c r="I16" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J16" s="64" t="str">
+      <x:c r="J16" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K16" s="64" t="str">
+      <x:c r="K16" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L16" s="64" t="str">
+      <x:c r="L16" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M16" s="64" t="str">
+      <x:c r="M16" s="74" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
@@ -33534,43 +33789,43 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="310" customHeight="1">
-      <x:c r="A17" s="64" t="str">
+      <x:c r="A17" s="74" t="str">
         <x:v>F01</x:v>
       </x:c>
-      <x:c r="B17" s="64" t="str">
+      <x:c r="B17" s="74" t="str">
         <x:v>Step 1 · Design</x:v>
       </x:c>
-      <x:c r="C17" s="64" t="str">
+      <x:c r="C17" s="74" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives</x:v>
       </x:c>
-      <x:c r="D17" s="64" t="str">
+      <x:c r="D17" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="64" t="str">
+      <x:c r="E17" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F17" s="64" t="str">
+      <x:c r="F17" s="74" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G17" s="64" t="str">
+      <x:c r="G17" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H17" s="65" t="d">
+      <x:c r="H17" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I17" s="65" t="d">
+      <x:c r="I17" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J17" s="64" t="str">
+      <x:c r="J17" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K17" s="64" t="str">
+      <x:c r="K17" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L17" s="64" t="str">
+      <x:c r="L17" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M17" s="64" t="str">
+      <x:c r="M17" s="74" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33578,43 +33833,43 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="310" customHeight="1">
-      <x:c r="A18" s="64" t="str">
+      <x:c r="A18" s="74" t="str">
         <x:v>F04</x:v>
       </x:c>
-      <x:c r="B18" s="64" t="str">
+      <x:c r="B18" s="74" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C18" s="64" t="str">
+      <x:c r="C18" s="74" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in</x:v>
       </x:c>
-      <x:c r="D18" s="64" t="str">
+      <x:c r="D18" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="64" t="str">
+      <x:c r="E18" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F18" s="64" t="str">
+      <x:c r="F18" s="74" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G18" s="64" t="str">
+      <x:c r="G18" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H18" s="65" t="d">
+      <x:c r="H18" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I18" s="65" t="d">
+      <x:c r="I18" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J18" s="64" t="str">
+      <x:c r="J18" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K18" s="64" t="str">
+      <x:c r="K18" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L18" s="64" t="str">
+      <x:c r="L18" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M18" s="64" t="str">
+      <x:c r="M18" s="74" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33622,43 +33877,43 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="310" customHeight="1">
-      <x:c r="A19" s="64" t="str">
+      <x:c r="A19" s="74" t="str">
         <x:v>F05</x:v>
       </x:c>
-      <x:c r="B19" s="64" t="str">
+      <x:c r="B19" s="74" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C19" s="64" t="str">
+      <x:c r="C19" s="74" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints</x:v>
       </x:c>
-      <x:c r="D19" s="64" t="str">
+      <x:c r="D19" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="64" t="str">
+      <x:c r="E19" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F19" s="64" t="str">
+      <x:c r="F19" s="74" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G19" s="64" t="str">
+      <x:c r="G19" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H19" s="65" t="d">
+      <x:c r="H19" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I19" s="65" t="d">
+      <x:c r="I19" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J19" s="64" t="str">
+      <x:c r="J19" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K19" s="64" t="str">
+      <x:c r="K19" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L19" s="64" t="str">
+      <x:c r="L19" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M19" s="64" t="str">
+      <x:c r="M19" s="74" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33666,43 +33921,43 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="310" customHeight="1">
-      <x:c r="A20" s="64" t="str">
+      <x:c r="A20" s="74" t="str">
         <x:v>F06</x:v>
       </x:c>
-      <x:c r="B20" s="64" t="str">
+      <x:c r="B20" s="74" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C20" s="64" t="str">
+      <x:c r="C20" s="74" t="str">
         <x:v>Light footer, company links, contact and PDPA link</x:v>
       </x:c>
-      <x:c r="D20" s="64" t="str">
+      <x:c r="D20" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="64" t="str">
+      <x:c r="E20" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F20" s="64" t="str">
+      <x:c r="F20" s="74" t="str">
         <x:v>Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G20" s="64" t="str">
+      <x:c r="G20" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H20" s="65" t="d">
+      <x:c r="H20" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I20" s="65" t="d">
+      <x:c r="I20" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J20" s="64" t="str">
+      <x:c r="J20" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K20" s="64" t="str">
+      <x:c r="K20" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L20" s="64" t="str">
+      <x:c r="L20" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M20" s="64" t="str">
+      <x:c r="M20" s="74" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33710,43 +33965,43 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="310" customHeight="1">
-      <x:c r="A21" s="64" t="str">
+      <x:c r="A21" s="74" t="str">
         <x:v>F07</x:v>
       </x:c>
-      <x:c r="B21" s="64" t="str">
+      <x:c r="B21" s="74" t="str">
         <x:v>Step 1 · i18n</x:v>
       </x:c>
-      <x:c r="C21" s="64" t="str">
+      <x:c r="C21" s="74" t="str">
         <x:v>Thai/English routes, language switch and localized formatting</x:v>
       </x:c>
-      <x:c r="D21" s="64" t="str">
+      <x:c r="D21" s="74" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="64" t="str">
+      <x:c r="E21" s="74" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F21" s="64" t="str">
+      <x:c r="F21" s="74" t="str">
         <x:v>Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G21" s="64" t="str">
+      <x:c r="G21" s="74" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H21" s="65" t="d">
+      <x:c r="H21" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I21" s="65" t="d">
+      <x:c r="I21" s="75" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J21" s="64" t="str">
+      <x:c r="J21" s="74" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K21" s="64" t="str">
+      <x:c r="K21" s="74" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L21" s="64" t="str">
+      <x:c r="L21" s="74" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M21" s="64" t="str">
+      <x:c r="M21" s="74" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -40944,13 +41199,13 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="45" priority="1">
+    <x:cfRule type="expression" dxfId="63" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="46" priority="2">
+    <x:cfRule type="expression" dxfId="64" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="47" priority="3">
+    <x:cfRule type="expression" dxfId="65" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -40964,7 +41219,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcafe3d4607aa4b42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R865a040151a84c94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41004,7 +41259,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-09: Step 3 verified. 82 permanent IDs: 15 Done, 16 Pending, 51 Not started. R02 links F01/F08 interaction fixes. Yellow Pending; light green Done; red Not started. Status sheets canonical; category sheets open views.</x:v>
+        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -41019,14 +41274,14 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -41090,1505 +41345,1505 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="250" customHeight="1">
-      <x:c r="A6" s="66" t="str">
+      <x:c r="A6" s="76" t="str">
         <x:v>F14</x:v>
       </x:c>
-      <x:c r="B6" s="67" t="str">
+      <x:c r="B6" s="77" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C6" s="67" t="str">
+      <x:c r="C6" s="77" t="str">
         <x:v>Desktop listing/map split and hover/focus pin synchronization</x:v>
       </x:c>
-      <x:c r="D6" s="67" t="str">
+      <x:c r="D6" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="67" t="str">
+      <x:c r="E6" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F6" s="67" t="str">
+      <x:c r="F6" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G6" s="67" t="str">
+      <x:c r="G6" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H6" s="68"/>
-      <x:c r="I6" s="68"/>
-      <x:c r="J6" s="67"/>
-      <x:c r="K6" s="67"/>
-      <x:c r="L6" s="67"/>
-      <x:c r="M6" s="67"/>
+      <x:c r="H6" s="78"/>
+      <x:c r="I6" s="78"/>
+      <x:c r="J6" s="77"/>
+      <x:c r="K6" s="77"/>
+      <x:c r="L6" s="77"/>
+      <x:c r="M6" s="77"/>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="66" t="str">
+      <x:c r="A7" s="76" t="str">
         <x:v>F15</x:v>
       </x:c>
-      <x:c r="B7" s="67" t="str">
+      <x:c r="B7" s="77" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C7" s="67" t="str">
+      <x:c r="C7" s="77" t="str">
         <x:v>Phone full-screen Map/List toggle</x:v>
       </x:c>
-      <x:c r="D7" s="67" t="str">
+      <x:c r="D7" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="67" t="str">
+      <x:c r="E7" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F7" s="67" t="str">
+      <x:c r="F7" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G7" s="67" t="str">
+      <x:c r="G7" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H7" s="68"/>
-      <x:c r="I7" s="68"/>
-      <x:c r="J7" s="67"/>
-      <x:c r="K7" s="67"/>
-      <x:c r="L7" s="67"/>
-      <x:c r="M7" s="67"/>
+      <x:c r="H7" s="78"/>
+      <x:c r="I7" s="78"/>
+      <x:c r="J7" s="77"/>
+      <x:c r="K7" s="77"/>
+      <x:c r="L7" s="77"/>
+      <x:c r="M7" s="77"/>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="66" t="str">
+      <x:c r="A8" s="76" t="str">
         <x:v>F16</x:v>
       </x:c>
-      <x:c r="B8" s="67" t="str">
+      <x:c r="B8" s="77" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C8" s="67" t="str">
+      <x:c r="C8" s="77" t="str">
         <x:v>Property detail photo grid and full-screen gallery</x:v>
       </x:c>
-      <x:c r="D8" s="67" t="str">
+      <x:c r="D8" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="67" t="str">
+      <x:c r="E8" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F8" s="67" t="str">
+      <x:c r="F8" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G8" s="67" t="str">
+      <x:c r="G8" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H8" s="68"/>
-      <x:c r="I8" s="68"/>
-      <x:c r="J8" s="67"/>
-      <x:c r="K8" s="67"/>
-      <x:c r="L8" s="67"/>
-      <x:c r="M8" s="67"/>
+      <x:c r="H8" s="78"/>
+      <x:c r="I8" s="78"/>
+      <x:c r="J8" s="77"/>
+      <x:c r="K8" s="77"/>
+      <x:c r="L8" s="77"/>
+      <x:c r="M8" s="77"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="66" t="str">
+      <x:c r="A9" s="76" t="str">
         <x:v>F17</x:v>
       </x:c>
-      <x:c r="B9" s="67" t="str">
+      <x:c r="B9" s="77" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C9" s="67" t="str">
+      <x:c r="C9" s="77" t="str">
         <x:v>Title, pricing, type-specific facts, long description and sticky tabs</x:v>
       </x:c>
-      <x:c r="D9" s="67" t="str">
+      <x:c r="D9" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="67" t="str">
+      <x:c r="E9" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F9" s="67" t="str">
+      <x:c r="F9" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G9" s="67" t="str">
+      <x:c r="G9" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H9" s="68"/>
-      <x:c r="I9" s="68"/>
-      <x:c r="J9" s="67"/>
-      <x:c r="K9" s="67"/>
-      <x:c r="L9" s="67"/>
-      <x:c r="M9" s="67"/>
+      <x:c r="H9" s="78"/>
+      <x:c r="I9" s="78"/>
+      <x:c r="J9" s="77"/>
+      <x:c r="K9" s="77"/>
+      <x:c r="L9" s="77"/>
+      <x:c r="M9" s="77"/>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="66" t="str">
+      <x:c r="A10" s="76" t="str">
         <x:v>F18</x:v>
       </x:c>
-      <x:c r="B10" s="67" t="str">
+      <x:c r="B10" s="77" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C10" s="67" t="str">
+      <x:c r="C10" s="77" t="str">
         <x:v>Floorplan/video/360 tabs, verified nearby information and map</x:v>
       </x:c>
-      <x:c r="D10" s="67" t="str">
+      <x:c r="D10" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E10" s="67" t="str">
+      <x:c r="E10" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F10" s="67" t="str">
+      <x:c r="F10" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G10" s="67" t="str">
+      <x:c r="G10" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H10" s="68"/>
-      <x:c r="I10" s="68"/>
-      <x:c r="J10" s="67"/>
-      <x:c r="K10" s="67"/>
-      <x:c r="L10" s="67"/>
-      <x:c r="M10" s="67"/>
+      <x:c r="H10" s="78"/>
+      <x:c r="I10" s="78"/>
+      <x:c r="J10" s="77"/>
+      <x:c r="K10" s="77"/>
+      <x:c r="L10" s="77"/>
+      <x:c r="M10" s="77"/>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="66" t="str">
+      <x:c r="A11" s="76" t="str">
         <x:v>F19</x:v>
       </x:c>
-      <x:c r="B11" s="67" t="str">
+      <x:c r="B11" s="77" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C11" s="67" t="str">
+      <x:c r="C11" s="77" t="str">
         <x:v>Mortgage calculator and area comparison when real data exists</x:v>
       </x:c>
-      <x:c r="D11" s="67" t="str">
+      <x:c r="D11" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E11" s="67" t="str">
+      <x:c r="E11" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F11" s="67" t="str">
+      <x:c r="F11" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G11" s="67" t="str">
+      <x:c r="G11" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H11" s="68"/>
-      <x:c r="I11" s="68"/>
-      <x:c r="J11" s="67"/>
-      <x:c r="K11" s="67"/>
-      <x:c r="L11" s="67"/>
-      <x:c r="M11" s="67"/>
+      <x:c r="H11" s="78"/>
+      <x:c r="I11" s="78"/>
+      <x:c r="J11" s="77"/>
+      <x:c r="K11" s="77"/>
+      <x:c r="L11" s="77"/>
+      <x:c r="M11" s="77"/>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="66" t="str">
+      <x:c r="A12" s="76" t="str">
         <x:v>F20</x:v>
       </x:c>
-      <x:c r="B12" s="67" t="str">
+      <x:c r="B12" s="77" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C12" s="67" t="str">
+      <x:c r="C12" s="77" t="str">
         <x:v>Same-project units and similar-property cards</x:v>
       </x:c>
-      <x:c r="D12" s="67" t="str">
+      <x:c r="D12" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E12" s="67" t="str">
+      <x:c r="E12" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F12" s="67" t="str">
+      <x:c r="F12" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G12" s="67" t="str">
+      <x:c r="G12" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H12" s="68"/>
-      <x:c r="I12" s="68"/>
-      <x:c r="J12" s="67"/>
-      <x:c r="K12" s="67"/>
-      <x:c r="L12" s="67"/>
-      <x:c r="M12" s="67"/>
+      <x:c r="H12" s="78"/>
+      <x:c r="I12" s="78"/>
+      <x:c r="J12" s="77"/>
+      <x:c r="K12" s="77"/>
+      <x:c r="L12" s="77"/>
+      <x:c r="M12" s="77"/>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="66" t="str">
+      <x:c r="A13" s="76" t="str">
         <x:v>F21</x:v>
       </x:c>
-      <x:c r="B13" s="67" t="str">
+      <x:c r="B13" s="77" t="str">
         <x:v>Step 6 · Contact</x:v>
       </x:c>
-      <x:c r="C13" s="67" t="str">
+      <x:c r="C13" s="77" t="str">
         <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
       </x:c>
-      <x:c r="D13" s="67" t="str">
+      <x:c r="D13" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E13" s="67" t="str">
+      <x:c r="E13" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="67" t="str">
+      <x:c r="F13" s="77" t="str">
         <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
-      <x:c r="G13" s="67" t="str">
+      <x:c r="G13" s="77" t="str">
         <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
       </x:c>
-      <x:c r="H13" s="68"/>
-      <x:c r="I13" s="68" t="d">
+      <x:c r="H13" s="78"/>
+      <x:c r="I13" s="78" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J13" s="67" t="str">
+      <x:c r="J13" s="77" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K13" s="67" t="str">
+      <x:c r="K13" s="77" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L13" s="67" t="str">
+      <x:c r="L13" s="77" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M13" s="67" t="str">
+      <x:c r="M13" s="77" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="66" t="str">
+      <x:c r="A14" s="76" t="str">
         <x:v>F22</x:v>
       </x:c>
-      <x:c r="B14" s="67" t="str">
+      <x:c r="B14" s="77" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C14" s="67" t="str">
+      <x:c r="C14" s="77" t="str">
         <x:v>Single-image hero and compact photography-first layout</x:v>
       </x:c>
-      <x:c r="D14" s="67" t="str">
+      <x:c r="D14" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E14" s="67" t="str">
+      <x:c r="E14" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F14" s="67" t="str">
+      <x:c r="F14" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G14" s="67" t="str">
+      <x:c r="G14" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H14" s="68"/>
-      <x:c r="I14" s="68"/>
-      <x:c r="J14" s="67"/>
-      <x:c r="K14" s="67"/>
-      <x:c r="L14" s="67"/>
-      <x:c r="M14" s="67"/>
+      <x:c r="H14" s="78"/>
+      <x:c r="I14" s="78"/>
+      <x:c r="J14" s="77"/>
+      <x:c r="K14" s="77"/>
+      <x:c r="L14" s="77"/>
+      <x:c r="M14" s="77"/>
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="66" t="str">
+      <x:c r="A15" s="76" t="str">
         <x:v>F23</x:v>
       </x:c>
-      <x:c r="B15" s="67" t="str">
+      <x:c r="B15" s="77" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C15" s="67" t="str">
+      <x:c r="C15" s="77" t="str">
         <x:v>Shared search box with Buy/Rent/Projects/Investment tabs</x:v>
       </x:c>
-      <x:c r="D15" s="67" t="str">
+      <x:c r="D15" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="67" t="str">
+      <x:c r="E15" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="67" t="str">
+      <x:c r="F15" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G15" s="67" t="str">
+      <x:c r="G15" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H15" s="68"/>
-      <x:c r="I15" s="68"/>
-      <x:c r="J15" s="67"/>
-      <x:c r="K15" s="67"/>
-      <x:c r="L15" s="67"/>
-      <x:c r="M15" s="67"/>
+      <x:c r="H15" s="78"/>
+      <x:c r="I15" s="78"/>
+      <x:c r="J15" s="77"/>
+      <x:c r="K15" s="77"/>
+      <x:c r="L15" s="77"/>
+      <x:c r="M15" s="77"/>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="66" t="str">
+      <x:c r="A16" s="76" t="str">
         <x:v>F24</x:v>
       </x:c>
-      <x:c r="B16" s="67" t="str">
+      <x:c r="B16" s="77" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C16" s="67" t="str">
+      <x:c r="C16" s="77" t="str">
         <x:v>Categories, recent searches and location/station suggestions</x:v>
       </x:c>
-      <x:c r="D16" s="67" t="str">
+      <x:c r="D16" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E16" s="67" t="str">
+      <x:c r="E16" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="67" t="str">
+      <x:c r="F16" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G16" s="67" t="str">
+      <x:c r="G16" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H16" s="68"/>
-      <x:c r="I16" s="68"/>
-      <x:c r="J16" s="67"/>
-      <x:c r="K16" s="67"/>
-      <x:c r="L16" s="67"/>
-      <x:c r="M16" s="67"/>
+      <x:c r="H16" s="78"/>
+      <x:c r="I16" s="78"/>
+      <x:c r="J16" s="77"/>
+      <x:c r="K16" s="77"/>
+      <x:c r="L16" s="77"/>
+      <x:c r="M16" s="77"/>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="66" t="str">
+      <x:c r="A17" s="76" t="str">
         <x:v>F25</x:v>
       </x:c>
-      <x:c r="B17" s="67" t="str">
+      <x:c r="B17" s="77" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C17" s="67" t="str">
+      <x:c r="C17" s="77" t="str">
         <x:v>Homes for you carousel directly below search; regions with real listing counts</x:v>
       </x:c>
-      <x:c r="D17" s="67" t="str">
+      <x:c r="D17" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="67" t="str">
+      <x:c r="E17" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="67" t="str">
+      <x:c r="F17" s="77" t="str">
         <x:v>V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
-      <x:c r="G17" s="67" t="str">
+      <x:c r="G17" s="77" t="str">
         <x:v>Codex: implement approved home-page.html only under Step 7 authorization.</x:v>
       </x:c>
-      <x:c r="H17" s="68"/>
-      <x:c r="I17" s="68" t="d">
+      <x:c r="H17" s="78"/>
+      <x:c r="I17" s="78" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J17" s="67" t="str">
+      <x:c r="J17" s="77" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K17" s="67" t="str">
+      <x:c r="K17" s="77" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L17" s="67" t="str">
+      <x:c r="L17" s="77" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M17" s="67" t="str">
+      <x:c r="M17" s="77" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="66" t="str">
+      <x:c r="A18" s="76" t="str">
         <x:v>F26</x:v>
       </x:c>
-      <x:c r="B18" s="67" t="str">
+      <x:c r="B18" s="77" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C18" s="67" t="str">
+      <x:c r="C18" s="77" t="str">
         <x:v>New projects, tools, services and owner lead CTAs</x:v>
       </x:c>
-      <x:c r="D18" s="67" t="str">
+      <x:c r="D18" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="67" t="str">
+      <x:c r="E18" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F18" s="67" t="str">
+      <x:c r="F18" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G18" s="67" t="str">
+      <x:c r="G18" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H18" s="68"/>
-      <x:c r="I18" s="68"/>
-      <x:c r="J18" s="67"/>
-      <x:c r="K18" s="67"/>
-      <x:c r="L18" s="67"/>
-      <x:c r="M18" s="67"/>
+      <x:c r="H18" s="78"/>
+      <x:c r="I18" s="78"/>
+      <x:c r="J18" s="77"/>
+      <x:c r="K18" s="77"/>
+      <x:c r="L18" s="77"/>
+      <x:c r="M18" s="77"/>
     </x:row>
     <x:row r="19" ht="250" customHeight="1">
-      <x:c r="A19" s="66" t="str">
+      <x:c r="A19" s="76" t="str">
         <x:v>F27</x:v>
       </x:c>
-      <x:c r="B19" s="67" t="str">
+      <x:c r="B19" s="77" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C19" s="67" t="str">
+      <x:c r="C19" s="77" t="str">
         <x:v>Projects index and responsive project detail layouts</x:v>
       </x:c>
-      <x:c r="D19" s="67" t="str">
+      <x:c r="D19" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="67" t="str">
+      <x:c r="E19" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="67" t="str">
+      <x:c r="F19" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G19" s="67" t="str">
+      <x:c r="G19" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H19" s="68"/>
-      <x:c r="I19" s="68"/>
-      <x:c r="J19" s="67"/>
-      <x:c r="K19" s="67"/>
-      <x:c r="L19" s="67"/>
-      <x:c r="M19" s="67"/>
+      <x:c r="H19" s="78"/>
+      <x:c r="I19" s="78"/>
+      <x:c r="J19" s="77"/>
+      <x:c r="K19" s="77"/>
+      <x:c r="L19" s="77"/>
+      <x:c r="M19" s="77"/>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="66" t="str">
+      <x:c r="A20" s="76" t="str">
         <x:v>F28</x:v>
       </x:c>
-      <x:c r="B20" s="67" t="str">
+      <x:c r="B20" s="77" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C20" s="67" t="str">
+      <x:c r="C20" s="77" t="str">
         <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
       </x:c>
-      <x:c r="D20" s="67" t="str">
+      <x:c r="D20" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="67" t="str">
+      <x:c r="E20" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="67" t="str">
+      <x:c r="F20" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G20" s="67" t="str">
+      <x:c r="G20" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H20" s="68"/>
-      <x:c r="I20" s="68"/>
-      <x:c r="J20" s="67"/>
-      <x:c r="K20" s="67"/>
-      <x:c r="L20" s="67"/>
-      <x:c r="M20" s="67"/>
+      <x:c r="H20" s="78"/>
+      <x:c r="I20" s="78"/>
+      <x:c r="J20" s="77"/>
+      <x:c r="K20" s="77"/>
+      <x:c r="L20" s="77"/>
+      <x:c r="M20" s="77"/>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="66" t="str">
+      <x:c r="A21" s="76" t="str">
         <x:v>F29</x:v>
       </x:c>
-      <x:c r="B21" s="67" t="str">
+      <x:c r="B21" s="77" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C21" s="67" t="str">
+      <x:c r="C21" s="77" t="str">
         <x:v>Data-driven clickable project SVG plot plan</x:v>
       </x:c>
-      <x:c r="D21" s="67" t="str">
+      <x:c r="D21" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="67" t="str">
+      <x:c r="E21" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="67" t="str">
+      <x:c r="F21" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G21" s="67" t="str">
+      <x:c r="G21" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H21" s="68"/>
-      <x:c r="I21" s="68"/>
-      <x:c r="J21" s="67"/>
-      <x:c r="K21" s="67"/>
-      <x:c r="L21" s="67"/>
-      <x:c r="M21" s="67"/>
+      <x:c r="H21" s="78"/>
+      <x:c r="I21" s="78"/>
+      <x:c r="J21" s="77"/>
+      <x:c r="K21" s="77"/>
+      <x:c r="L21" s="77"/>
+      <x:c r="M21" s="77"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="66" t="str">
+      <x:c r="A22" s="76" t="str">
         <x:v>F30</x:v>
       </x:c>
-      <x:c r="B22" s="67" t="str">
+      <x:c r="B22" s="77" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C22" s="67" t="str">
+      <x:c r="C22" s="77" t="str">
         <x:v>Site visit 3-step form and confirmation screens</x:v>
       </x:c>
-      <x:c r="D22" s="67" t="str">
+      <x:c r="D22" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E22" s="67" t="str">
+      <x:c r="E22" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="67" t="str">
+      <x:c r="F22" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G22" s="67" t="str">
+      <x:c r="G22" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H22" s="68"/>
-      <x:c r="I22" s="68"/>
-      <x:c r="J22" s="67"/>
-      <x:c r="K22" s="67"/>
-      <x:c r="L22" s="67"/>
-      <x:c r="M22" s="67"/>
+      <x:c r="H22" s="78"/>
+      <x:c r="I22" s="78"/>
+      <x:c r="J22" s="77"/>
+      <x:c r="K22" s="77"/>
+      <x:c r="L22" s="77"/>
+      <x:c r="M22" s="77"/>
     </x:row>
     <x:row r="23" ht="250" customHeight="1">
-      <x:c r="A23" s="66" t="str">
+      <x:c r="A23" s="76" t="str">
         <x:v>F31</x:v>
       </x:c>
-      <x:c r="B23" s="67" t="str">
+      <x:c r="B23" s="77" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C23" s="67" t="str">
+      <x:c r="C23" s="77" t="str">
         <x:v>Homes, searches and viewings; local save without account</x:v>
       </x:c>
-      <x:c r="D23" s="67" t="str">
+      <x:c r="D23" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E23" s="67" t="str">
+      <x:c r="E23" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F23" s="67" t="str">
+      <x:c r="F23" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G23" s="67" t="str">
+      <x:c r="G23" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H23" s="68"/>
-      <x:c r="I23" s="68"/>
-      <x:c r="J23" s="67"/>
-      <x:c r="K23" s="67"/>
-      <x:c r="L23" s="67"/>
-      <x:c r="M23" s="67"/>
+      <x:c r="H23" s="78"/>
+      <x:c r="I23" s="78"/>
+      <x:c r="J23" s="77"/>
+      <x:c r="K23" s="77"/>
+      <x:c r="L23" s="77"/>
+      <x:c r="M23" s="77"/>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="66" t="str">
+      <x:c r="A24" s="76" t="str">
         <x:v>F33</x:v>
       </x:c>
-      <x:c r="B24" s="67" t="str">
+      <x:c r="B24" s="77" t="str">
         <x:v>Step 10B · Accounts</x:v>
       </x:c>
-      <x:c r="C24" s="67" t="str">
+      <x:c r="C24" s="77" t="str">
         <x:v>Build approved auth and account screens only after approval</x:v>
       </x:c>
-      <x:c r="D24" s="67" t="str">
+      <x:c r="D24" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E24" s="67" t="str">
+      <x:c r="E24" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="67" t="str">
+      <x:c r="F24" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G24" s="67" t="str">
+      <x:c r="G24" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H24" s="68"/>
-      <x:c r="I24" s="68"/>
-      <x:c r="J24" s="67"/>
-      <x:c r="K24" s="67"/>
-      <x:c r="L24" s="67"/>
-      <x:c r="M24" s="67"/>
+      <x:c r="H24" s="78"/>
+      <x:c r="I24" s="78"/>
+      <x:c r="J24" s="77"/>
+      <x:c r="K24" s="77"/>
+      <x:c r="L24" s="77"/>
+      <x:c r="M24" s="77"/>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="66" t="str">
+      <x:c r="A25" s="76" t="str">
         <x:v>F35</x:v>
       </x:c>
-      <x:c r="B25" s="67" t="str">
+      <x:c r="B25" s="77" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C25" s="67" t="str">
+      <x:c r="C25" s="77" t="str">
         <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
       </x:c>
-      <x:c r="D25" s="67" t="str">
+      <x:c r="D25" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E25" s="67" t="str">
+      <x:c r="E25" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="67" t="str">
+      <x:c r="F25" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G25" s="67" t="str">
+      <x:c r="G25" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H25" s="68"/>
-      <x:c r="I25" s="68"/>
-      <x:c r="J25" s="67"/>
-      <x:c r="K25" s="67"/>
-      <x:c r="L25" s="67"/>
-      <x:c r="M25" s="67"/>
+      <x:c r="H25" s="78"/>
+      <x:c r="I25" s="78"/>
+      <x:c r="J25" s="77"/>
+      <x:c r="K25" s="77"/>
+      <x:c r="L25" s="77"/>
+      <x:c r="M25" s="77"/>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="66" t="str">
+      <x:c r="A26" s="76" t="str">
         <x:v>F36</x:v>
       </x:c>
-      <x:c r="B26" s="67" t="str">
+      <x:c r="B26" s="77" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C26" s="67" t="str">
+      <x:c r="C26" s="77" t="str">
         <x:v>Admin-managed searchable filter editor with type safety</x:v>
       </x:c>
-      <x:c r="D26" s="67" t="str">
+      <x:c r="D26" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E26" s="67" t="str">
+      <x:c r="E26" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="67" t="str">
+      <x:c r="F26" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G26" s="67" t="str">
+      <x:c r="G26" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H26" s="68"/>
-      <x:c r="I26" s="68"/>
-      <x:c r="J26" s="67"/>
-      <x:c r="K26" s="67"/>
-      <x:c r="L26" s="67"/>
-      <x:c r="M26" s="67"/>
+      <x:c r="H26" s="78"/>
+      <x:c r="I26" s="78"/>
+      <x:c r="J26" s="77"/>
+      <x:c r="K26" s="77"/>
+      <x:c r="L26" s="77"/>
+      <x:c r="M26" s="77"/>
     </x:row>
     <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="66" t="str">
+      <x:c r="A27" s="76" t="str">
         <x:v>F37</x:v>
       </x:c>
-      <x:c r="B27" s="67" t="str">
+      <x:c r="B27" s="77" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C27" s="67" t="str">
+      <x:c r="C27" s="77" t="str">
         <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
       </x:c>
-      <x:c r="D27" s="67" t="str">
+      <x:c r="D27" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E27" s="67" t="str">
+      <x:c r="E27" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="67" t="str">
+      <x:c r="F27" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G27" s="67" t="str">
+      <x:c r="G27" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H27" s="68"/>
-      <x:c r="I27" s="68"/>
-      <x:c r="J27" s="67"/>
-      <x:c r="K27" s="67"/>
-      <x:c r="L27" s="67"/>
-      <x:c r="M27" s="67"/>
+      <x:c r="H27" s="78"/>
+      <x:c r="I27" s="78"/>
+      <x:c r="J27" s="77"/>
+      <x:c r="K27" s="77"/>
+      <x:c r="L27" s="77"/>
+      <x:c r="M27" s="77"/>
     </x:row>
     <x:row r="28" ht="26" customHeight="1">
-      <x:c r="A28" s="66" t="str">
+      <x:c r="A28" s="76" t="str">
         <x:v>F38</x:v>
       </x:c>
-      <x:c r="B28" s="67" t="str">
+      <x:c r="B28" s="77" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C28" s="67" t="str">
+      <x:c r="C28" s="77" t="str">
         <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
       </x:c>
-      <x:c r="D28" s="67" t="str">
+      <x:c r="D28" s="77" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E28" s="67" t="str">
+      <x:c r="E28" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="67" t="str">
+      <x:c r="F28" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G28" s="67" t="str">
+      <x:c r="G28" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H28" s="68"/>
-      <x:c r="I28" s="68"/>
-      <x:c r="J28" s="67"/>
-      <x:c r="K28" s="67"/>
-      <x:c r="L28" s="67"/>
-      <x:c r="M28" s="67"/>
+      <x:c r="H28" s="78"/>
+      <x:c r="I28" s="78"/>
+      <x:c r="J28" s="77"/>
+      <x:c r="K28" s="77"/>
+      <x:c r="L28" s="77"/>
+      <x:c r="M28" s="77"/>
     </x:row>
     <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="66" t="str">
+      <x:c r="A29" s="76" t="str">
         <x:v>B08</x:v>
       </x:c>
-      <x:c r="B29" s="67" t="str">
+      <x:c r="B29" s="77" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C29" s="67" t="str">
+      <x:c r="C29" s="77" t="str">
         <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
       </x:c>
-      <x:c r="D29" s="67" t="str">
+      <x:c r="D29" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E29" s="67" t="str">
+      <x:c r="E29" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="67" t="str">
+      <x:c r="F29" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="67" t="str">
+      <x:c r="G29" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="68"/>
-      <x:c r="I29" s="68"/>
-      <x:c r="J29" s="67"/>
-      <x:c r="K29" s="67"/>
-      <x:c r="L29" s="67"/>
-      <x:c r="M29" s="67"/>
+      <x:c r="H29" s="78"/>
+      <x:c r="I29" s="78"/>
+      <x:c r="J29" s="77"/>
+      <x:c r="K29" s="77"/>
+      <x:c r="L29" s="77"/>
+      <x:c r="M29" s="77"/>
     </x:row>
     <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="66" t="str">
+      <x:c r="A30" s="76" t="str">
         <x:v>B10</x:v>
       </x:c>
-      <x:c r="B30" s="67" t="str">
+      <x:c r="B30" s="77" t="str">
         <x:v>Step 4 · Nearby</x:v>
       </x:c>
-      <x:c r="C30" s="67" t="str">
+      <x:c r="C30" s="77" t="str">
         <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
       </x:c>
-      <x:c r="D30" s="67" t="str">
+      <x:c r="D30" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E30" s="67" t="str">
+      <x:c r="E30" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="67" t="str">
+      <x:c r="F30" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="67" t="str">
+      <x:c r="G30" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="68"/>
-      <x:c r="I30" s="68"/>
-      <x:c r="J30" s="67"/>
-      <x:c r="K30" s="67"/>
-      <x:c r="L30" s="67"/>
-      <x:c r="M30" s="67"/>
+      <x:c r="H30" s="78"/>
+      <x:c r="I30" s="78"/>
+      <x:c r="J30" s="77"/>
+      <x:c r="K30" s="77"/>
+      <x:c r="L30" s="77"/>
+      <x:c r="M30" s="77"/>
     </x:row>
     <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="66" t="str">
+      <x:c r="A31" s="76" t="str">
         <x:v>B11</x:v>
       </x:c>
-      <x:c r="B31" s="67" t="str">
+      <x:c r="B31" s="77" t="str">
         <x:v>Step 5 · Media</x:v>
       </x:c>
-      <x:c r="C31" s="67" t="str">
+      <x:c r="C31" s="77" t="str">
         <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
       </x:c>
-      <x:c r="D31" s="67" t="str">
+      <x:c r="D31" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E31" s="67" t="str">
+      <x:c r="E31" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="67" t="str">
+      <x:c r="F31" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="67" t="str">
+      <x:c r="G31" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="68"/>
-      <x:c r="I31" s="68"/>
-      <x:c r="J31" s="67"/>
-      <x:c r="K31" s="67"/>
-      <x:c r="L31" s="67"/>
-      <x:c r="M31" s="67"/>
+      <x:c r="H31" s="78"/>
+      <x:c r="I31" s="78"/>
+      <x:c r="J31" s="77"/>
+      <x:c r="K31" s="77"/>
+      <x:c r="L31" s="77"/>
+      <x:c r="M31" s="77"/>
     </x:row>
     <x:row r="32" ht="26" customHeight="1">
-      <x:c r="A32" s="66" t="str">
+      <x:c r="A32" s="76" t="str">
         <x:v>B12</x:v>
       </x:c>
-      <x:c r="B32" s="67" t="str">
+      <x:c r="B32" s="77" t="str">
         <x:v>Step 5 · Similar</x:v>
       </x:c>
-      <x:c r="C32" s="67" t="str">
+      <x:c r="C32" s="77" t="str">
         <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
       </x:c>
-      <x:c r="D32" s="67" t="str">
+      <x:c r="D32" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E32" s="67" t="str">
+      <x:c r="E32" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="67" t="str">
+      <x:c r="F32" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G32" s="67" t="str">
+      <x:c r="G32" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H32" s="68"/>
-      <x:c r="I32" s="68"/>
-      <x:c r="J32" s="67"/>
-      <x:c r="K32" s="67"/>
-      <x:c r="L32" s="67"/>
-      <x:c r="M32" s="67"/>
+      <x:c r="H32" s="78"/>
+      <x:c r="I32" s="78"/>
+      <x:c r="J32" s="77"/>
+      <x:c r="K32" s="77"/>
+      <x:c r="L32" s="77"/>
+      <x:c r="M32" s="77"/>
     </x:row>
     <x:row r="33" ht="26" customHeight="1">
-      <x:c r="A33" s="66" t="str">
+      <x:c r="A33" s="76" t="str">
         <x:v>B13</x:v>
       </x:c>
-      <x:c r="B33" s="67" t="str">
+      <x:c r="B33" s="77" t="str">
         <x:v>Step 5 · Metrics</x:v>
       </x:c>
-      <x:c r="C33" s="67" t="str">
+      <x:c r="C33" s="77" t="str">
         <x:v>Comparable pricing/yield gated by verified sample size</x:v>
       </x:c>
-      <x:c r="D33" s="67" t="str">
+      <x:c r="D33" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E33" s="67" t="str">
+      <x:c r="E33" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F33" s="67" t="str">
+      <x:c r="F33" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G33" s="67" t="str">
+      <x:c r="G33" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H33" s="68"/>
-      <x:c r="I33" s="68"/>
-      <x:c r="J33" s="67"/>
-      <x:c r="K33" s="67"/>
-      <x:c r="L33" s="67"/>
-      <x:c r="M33" s="67"/>
+      <x:c r="H33" s="78"/>
+      <x:c r="I33" s="78"/>
+      <x:c r="J33" s="77"/>
+      <x:c r="K33" s="77"/>
+      <x:c r="L33" s="77"/>
+      <x:c r="M33" s="77"/>
     </x:row>
     <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="66" t="str">
+      <x:c r="A34" s="76" t="str">
         <x:v>B14</x:v>
       </x:c>
-      <x:c r="B34" s="67" t="str">
+      <x:c r="B34" s="77" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C34" s="67" t="str">
+      <x:c r="C34" s="77" t="str">
         <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
       </x:c>
-      <x:c r="D34" s="67" t="str">
+      <x:c r="D34" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E34" s="67" t="str">
+      <x:c r="E34" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F34" s="67" t="str">
+      <x:c r="F34" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G34" s="67" t="str">
+      <x:c r="G34" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H34" s="68"/>
-      <x:c r="I34" s="68"/>
-      <x:c r="J34" s="67"/>
-      <x:c r="K34" s="67"/>
-      <x:c r="L34" s="67"/>
-      <x:c r="M34" s="67"/>
+      <x:c r="H34" s="78"/>
+      <x:c r="I34" s="78"/>
+      <x:c r="J34" s="77"/>
+      <x:c r="K34" s="77"/>
+      <x:c r="L34" s="77"/>
+      <x:c r="M34" s="77"/>
     </x:row>
     <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="66" t="str">
+      <x:c r="A35" s="76" t="str">
         <x:v>B15</x:v>
       </x:c>
-      <x:c r="B35" s="67" t="str">
+      <x:c r="B35" s="77" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C35" s="67" t="str">
+      <x:c r="C35" s="77" t="str">
         <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
       </x:c>
-      <x:c r="D35" s="67" t="str">
+      <x:c r="D35" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E35" s="67" t="str">
+      <x:c r="E35" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F35" s="67" t="str">
+      <x:c r="F35" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G35" s="67" t="str">
+      <x:c r="G35" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H35" s="68"/>
-      <x:c r="I35" s="68"/>
-      <x:c r="J35" s="67"/>
-      <x:c r="K35" s="67"/>
-      <x:c r="L35" s="67"/>
-      <x:c r="M35" s="67"/>
+      <x:c r="H35" s="78"/>
+      <x:c r="I35" s="78"/>
+      <x:c r="J35" s="77"/>
+      <x:c r="K35" s="77"/>
+      <x:c r="L35" s="77"/>
+      <x:c r="M35" s="77"/>
     </x:row>
     <x:row r="36" ht="26" customHeight="1">
-      <x:c r="A36" s="66" t="str">
+      <x:c r="A36" s="76" t="str">
         <x:v>B16</x:v>
       </x:c>
-      <x:c r="B36" s="67" t="str">
+      <x:c r="B36" s="77" t="str">
         <x:v>Step 6 · Security</x:v>
       </x:c>
-      <x:c r="C36" s="67" t="str">
+      <x:c r="C36" s="77" t="str">
         <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
       </x:c>
-      <x:c r="D36" s="67" t="str">
+      <x:c r="D36" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E36" s="67" t="str">
+      <x:c r="E36" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F36" s="67" t="str">
+      <x:c r="F36" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G36" s="67" t="str">
+      <x:c r="G36" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H36" s="68"/>
-      <x:c r="I36" s="68"/>
-      <x:c r="J36" s="67"/>
-      <x:c r="K36" s="67"/>
-      <x:c r="L36" s="67"/>
-      <x:c r="M36" s="67"/>
+      <x:c r="H36" s="78"/>
+      <x:c r="I36" s="78"/>
+      <x:c r="J36" s="77"/>
+      <x:c r="K36" s="77"/>
+      <x:c r="L36" s="77"/>
+      <x:c r="M36" s="77"/>
     </x:row>
     <x:row r="37" ht="26" customHeight="1">
-      <x:c r="A37" s="66" t="str">
+      <x:c r="A37" s="76" t="str">
         <x:v>B19</x:v>
       </x:c>
-      <x:c r="B37" s="67" t="str">
+      <x:c r="B37" s="77" t="str">
         <x:v>Step 6 · Chat</x:v>
       </x:c>
-      <x:c r="C37" s="67" t="str">
+      <x:c r="C37" s="77" t="str">
         <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
       </x:c>
-      <x:c r="D37" s="67" t="str">
+      <x:c r="D37" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E37" s="67" t="str">
+      <x:c r="E37" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F37" s="67" t="str">
+      <x:c r="F37" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G37" s="67" t="str">
+      <x:c r="G37" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H37" s="68"/>
-      <x:c r="I37" s="68"/>
-      <x:c r="J37" s="67"/>
-      <x:c r="K37" s="67"/>
-      <x:c r="L37" s="67"/>
-      <x:c r="M37" s="67"/>
+      <x:c r="H37" s="78"/>
+      <x:c r="I37" s="78"/>
+      <x:c r="J37" s="77"/>
+      <x:c r="K37" s="77"/>
+      <x:c r="L37" s="77"/>
+      <x:c r="M37" s="77"/>
     </x:row>
     <x:row r="38" ht="26" customHeight="1">
-      <x:c r="A38" s="66" t="str">
+      <x:c r="A38" s="76" t="str">
         <x:v>B20</x:v>
       </x:c>
-      <x:c r="B38" s="67" t="str">
+      <x:c r="B38" s="77" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C38" s="67" t="str">
+      <x:c r="C38" s="77" t="str">
         <x:v>Project/unit/plot status logic and validation</x:v>
       </x:c>
-      <x:c r="D38" s="67" t="str">
+      <x:c r="D38" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E38" s="67" t="str">
+      <x:c r="E38" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F38" s="67" t="str">
+      <x:c r="F38" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G38" s="67" t="str">
+      <x:c r="G38" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H38" s="68"/>
-      <x:c r="I38" s="68"/>
-      <x:c r="J38" s="67"/>
-      <x:c r="K38" s="67"/>
-      <x:c r="L38" s="67"/>
-      <x:c r="M38" s="67"/>
+      <x:c r="H38" s="78"/>
+      <x:c r="I38" s="78"/>
+      <x:c r="J38" s="77"/>
+      <x:c r="K38" s="77"/>
+      <x:c r="L38" s="77"/>
+      <x:c r="M38" s="77"/>
     </x:row>
     <x:row r="39" ht="26" customHeight="1">
-      <x:c r="A39" s="66" t="str">
+      <x:c r="A39" s="76" t="str">
         <x:v>B21</x:v>
       </x:c>
-      <x:c r="B39" s="67" t="str">
+      <x:c r="B39" s="77" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C39" s="67" t="str">
+      <x:c r="C39" s="77" t="str">
         <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
       </x:c>
-      <x:c r="D39" s="67" t="str">
+      <x:c r="D39" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E39" s="67" t="str">
+      <x:c r="E39" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F39" s="67" t="str">
+      <x:c r="F39" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G39" s="67" t="str">
+      <x:c r="G39" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H39" s="68"/>
-      <x:c r="I39" s="68"/>
-      <x:c r="J39" s="67"/>
-      <x:c r="K39" s="67"/>
-      <x:c r="L39" s="67"/>
-      <x:c r="M39" s="67"/>
+      <x:c r="H39" s="78"/>
+      <x:c r="I39" s="78"/>
+      <x:c r="J39" s="77"/>
+      <x:c r="K39" s="77"/>
+      <x:c r="L39" s="77"/>
+      <x:c r="M39" s="77"/>
     </x:row>
     <x:row r="40" ht="26" customHeight="1">
-      <x:c r="A40" s="66" t="str">
+      <x:c r="A40" s="76" t="str">
         <x:v>B22</x:v>
       </x:c>
-      <x:c r="B40" s="67" t="str">
+      <x:c r="B40" s="77" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C40" s="67" t="str">
+      <x:c r="C40" s="77" t="str">
         <x:v>Saved listings/searches persistence, new-match calculations</x:v>
       </x:c>
-      <x:c r="D40" s="67" t="str">
+      <x:c r="D40" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E40" s="67" t="str">
+      <x:c r="E40" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F40" s="67" t="str">
+      <x:c r="F40" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G40" s="67" t="str">
+      <x:c r="G40" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H40" s="68"/>
-      <x:c r="I40" s="68"/>
-      <x:c r="J40" s="67"/>
-      <x:c r="K40" s="67"/>
-      <x:c r="L40" s="67"/>
-      <x:c r="M40" s="67"/>
+      <x:c r="H40" s="78"/>
+      <x:c r="I40" s="78"/>
+      <x:c r="J40" s="77"/>
+      <x:c r="K40" s="77"/>
+      <x:c r="L40" s="77"/>
+      <x:c r="M40" s="77"/>
     </x:row>
     <x:row r="41" ht="26" customHeight="1">
-      <x:c r="A41" s="66" t="str">
+      <x:c r="A41" s="76" t="str">
         <x:v>B24</x:v>
       </x:c>
-      <x:c r="B41" s="67" t="str">
+      <x:c r="B41" s="77" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C41" s="67" t="str">
+      <x:c r="C41" s="77" t="str">
         <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
       </x:c>
-      <x:c r="D41" s="67" t="str">
+      <x:c r="D41" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E41" s="67" t="str">
+      <x:c r="E41" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F41" s="67" t="str">
+      <x:c r="F41" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G41" s="67" t="str">
+      <x:c r="G41" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H41" s="68"/>
-      <x:c r="I41" s="68"/>
-      <x:c r="J41" s="67"/>
-      <x:c r="K41" s="67"/>
-      <x:c r="L41" s="67"/>
-      <x:c r="M41" s="67"/>
+      <x:c r="H41" s="78"/>
+      <x:c r="I41" s="78"/>
+      <x:c r="J41" s="77"/>
+      <x:c r="K41" s="77"/>
+      <x:c r="L41" s="77"/>
+      <x:c r="M41" s="77"/>
     </x:row>
     <x:row r="42" ht="26" customHeight="1">
-      <x:c r="A42" s="66" t="str">
+      <x:c r="A42" s="76" t="str">
         <x:v>B25</x:v>
       </x:c>
-      <x:c r="B42" s="67" t="str">
+      <x:c r="B42" s="77" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C42" s="67" t="str">
+      <x:c r="C42" s="77" t="str">
         <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
       </x:c>
-      <x:c r="D42" s="67" t="str">
+      <x:c r="D42" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E42" s="67" t="str">
+      <x:c r="E42" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F42" s="67" t="str">
+      <x:c r="F42" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G42" s="67" t="str">
+      <x:c r="G42" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H42" s="68"/>
-      <x:c r="I42" s="68"/>
-      <x:c r="J42" s="67"/>
-      <x:c r="K42" s="67"/>
-      <x:c r="L42" s="67"/>
-      <x:c r="M42" s="67"/>
+      <x:c r="H42" s="78"/>
+      <x:c r="I42" s="78"/>
+      <x:c r="J42" s="77"/>
+      <x:c r="K42" s="77"/>
+      <x:c r="L42" s="77"/>
+      <x:c r="M42" s="77"/>
     </x:row>
     <x:row r="43" ht="26" customHeight="1">
-      <x:c r="A43" s="66" t="str">
+      <x:c r="A43" s="76" t="str">
         <x:v>B26</x:v>
       </x:c>
-      <x:c r="B43" s="67" t="str">
+      <x:c r="B43" s="77" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C43" s="67" t="str">
+      <x:c r="C43" s="77" t="str">
         <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
       </x:c>
-      <x:c r="D43" s="67" t="str">
+      <x:c r="D43" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E43" s="67" t="str">
+      <x:c r="E43" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F43" s="67" t="str">
+      <x:c r="F43" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G43" s="67" t="str">
+      <x:c r="G43" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H43" s="68"/>
-      <x:c r="I43" s="68"/>
-      <x:c r="J43" s="67"/>
-      <x:c r="K43" s="67"/>
-      <x:c r="L43" s="67"/>
-      <x:c r="M43" s="67"/>
+      <x:c r="H43" s="78"/>
+      <x:c r="I43" s="78"/>
+      <x:c r="J43" s="77"/>
+      <x:c r="K43" s="77"/>
+      <x:c r="L43" s="77"/>
+      <x:c r="M43" s="77"/>
     </x:row>
     <x:row r="44" ht="26" customHeight="1">
-      <x:c r="A44" s="66" t="str">
+      <x:c r="A44" s="76" t="str">
         <x:v>B27</x:v>
       </x:c>
-      <x:c r="B44" s="67" t="str">
+      <x:c r="B44" s="77" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C44" s="67" t="str">
+      <x:c r="C44" s="77" t="str">
         <x:v>Admin user management, audit log and sensitive action authorization</x:v>
       </x:c>
-      <x:c r="D44" s="67" t="str">
+      <x:c r="D44" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E44" s="67" t="str">
+      <x:c r="E44" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F44" s="67" t="str">
+      <x:c r="F44" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G44" s="67" t="str">
+      <x:c r="G44" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H44" s="68"/>
-      <x:c r="I44" s="68"/>
-      <x:c r="J44" s="67"/>
-      <x:c r="K44" s="67"/>
-      <x:c r="L44" s="67"/>
-      <x:c r="M44" s="67"/>
+      <x:c r="H44" s="78"/>
+      <x:c r="I44" s="78"/>
+      <x:c r="J44" s="77"/>
+      <x:c r="K44" s="77"/>
+      <x:c r="L44" s="77"/>
+      <x:c r="M44" s="77"/>
     </x:row>
     <x:row r="45" ht="26" customHeight="1">
-      <x:c r="A45" s="66" t="str">
+      <x:c r="A45" s="76" t="str">
         <x:v>B30</x:v>
       </x:c>
-      <x:c r="B45" s="67" t="str">
+      <x:c r="B45" s="77" t="str">
         <x:v>Step 12 · Deploy</x:v>
       </x:c>
-      <x:c r="C45" s="67" t="str">
+      <x:c r="C45" s="77" t="str">
         <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
       </x:c>
-      <x:c r="D45" s="67" t="str">
+      <x:c r="D45" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E45" s="67" t="str">
+      <x:c r="E45" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F45" s="67" t="str">
+      <x:c r="F45" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G45" s="67" t="str">
+      <x:c r="G45" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H45" s="68"/>
-      <x:c r="I45" s="68"/>
-      <x:c r="J45" s="67"/>
-      <x:c r="K45" s="67"/>
-      <x:c r="L45" s="67"/>
-      <x:c r="M45" s="67"/>
+      <x:c r="H45" s="78"/>
+      <x:c r="I45" s="78"/>
+      <x:c r="J45" s="77"/>
+      <x:c r="K45" s="77"/>
+      <x:c r="L45" s="77"/>
+      <x:c r="M45" s="77"/>
     </x:row>
     <x:row r="46" ht="26" customHeight="1">
-      <x:c r="A46" s="66" t="str">
+      <x:c r="A46" s="76" t="str">
         <x:v>B31</x:v>
       </x:c>
-      <x:c r="B46" s="67" t="str">
+      <x:c r="B46" s="77" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C46" s="67" t="str">
+      <x:c r="C46" s="77" t="str">
         <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
       </x:c>
-      <x:c r="D46" s="67" t="str">
+      <x:c r="D46" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E46" s="67" t="str">
+      <x:c r="E46" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F46" s="67" t="str">
+      <x:c r="F46" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G46" s="67" t="str">
+      <x:c r="G46" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H46" s="68"/>
-      <x:c r="I46" s="68"/>
-      <x:c r="J46" s="67"/>
-      <x:c r="K46" s="67"/>
-      <x:c r="L46" s="67"/>
-      <x:c r="M46" s="67"/>
+      <x:c r="H46" s="78"/>
+      <x:c r="I46" s="78"/>
+      <x:c r="J46" s="77"/>
+      <x:c r="K46" s="77"/>
+      <x:c r="L46" s="77"/>
+      <x:c r="M46" s="77"/>
     </x:row>
     <x:row r="47" ht="26" customHeight="1">
-      <x:c r="A47" s="66" t="str">
+      <x:c r="A47" s="76" t="str">
         <x:v>B32</x:v>
       </x:c>
-      <x:c r="B47" s="67" t="str">
+      <x:c r="B47" s="77" t="str">
         <x:v>Step 12 · Security</x:v>
       </x:c>
-      <x:c r="C47" s="67" t="str">
+      <x:c r="C47" s="77" t="str">
         <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
       </x:c>
-      <x:c r="D47" s="67" t="str">
+      <x:c r="D47" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E47" s="67" t="str">
+      <x:c r="E47" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F47" s="67" t="str">
+      <x:c r="F47" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G47" s="67" t="str">
+      <x:c r="G47" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H47" s="68"/>
-      <x:c r="I47" s="68"/>
-      <x:c r="J47" s="67"/>
-      <x:c r="K47" s="67"/>
-      <x:c r="L47" s="67"/>
-      <x:c r="M47" s="67"/>
+      <x:c r="H47" s="78"/>
+      <x:c r="I47" s="78"/>
+      <x:c r="J47" s="77"/>
+      <x:c r="K47" s="77"/>
+      <x:c r="L47" s="77"/>
+      <x:c r="M47" s="77"/>
     </x:row>
     <x:row r="48" ht="26" customHeight="1">
-      <x:c r="A48" s="66" t="str">
+      <x:c r="A48" s="76" t="str">
         <x:v>B33</x:v>
       </x:c>
-      <x:c r="B48" s="67" t="str">
+      <x:c r="B48" s="77" t="str">
         <x:v>Step 7 · Owners</x:v>
       </x:c>
-      <x:c r="C48" s="67" t="str">
+      <x:c r="C48" s="77" t="str">
         <x:v>Home-value and service enquiry data handling</x:v>
       </x:c>
-      <x:c r="D48" s="67" t="str">
+      <x:c r="D48" s="77" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E48" s="67" t="str">
+      <x:c r="E48" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F48" s="67" t="str">
+      <x:c r="F48" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G48" s="67" t="str">
+      <x:c r="G48" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H48" s="68"/>
-      <x:c r="I48" s="68"/>
-      <x:c r="J48" s="67"/>
-      <x:c r="K48" s="67"/>
-      <x:c r="L48" s="67"/>
-      <x:c r="M48" s="67"/>
+      <x:c r="H48" s="78"/>
+      <x:c r="I48" s="78"/>
+      <x:c r="J48" s="77"/>
+      <x:c r="K48" s="77"/>
+      <x:c r="L48" s="77"/>
+      <x:c r="M48" s="77"/>
     </x:row>
     <x:row r="49" ht="26" customHeight="1">
-      <x:c r="A49" s="66" t="str">
+      <x:c r="A49" s="76" t="str">
         <x:v>E01</x:v>
       </x:c>
-      <x:c r="B49" s="67" t="str">
+      <x:c r="B49" s="77" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C49" s="67" t="str">
+      <x:c r="C49" s="77" t="str">
         <x:v>Enquiry notification with retryable queue/outbox</x:v>
       </x:c>
-      <x:c r="D49" s="67" t="str">
+      <x:c r="D49" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E49" s="67" t="str">
+      <x:c r="E49" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F49" s="67" t="str">
+      <x:c r="F49" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G49" s="67" t="str">
+      <x:c r="G49" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H49" s="68"/>
-      <x:c r="I49" s="68"/>
-      <x:c r="J49" s="67"/>
-      <x:c r="K49" s="67"/>
-      <x:c r="L49" s="67"/>
-      <x:c r="M49" s="67"/>
+      <x:c r="H49" s="78"/>
+      <x:c r="I49" s="78"/>
+      <x:c r="J49" s="77"/>
+      <x:c r="K49" s="77"/>
+      <x:c r="L49" s="77"/>
+      <x:c r="M49" s="77"/>
     </x:row>
     <x:row r="50" ht="26" customHeight="1">
-      <x:c r="A50" s="66" t="str">
+      <x:c r="A50" s="76" t="str">
         <x:v>E02</x:v>
       </x:c>
-      <x:c r="B50" s="67" t="str">
+      <x:c r="B50" s="77" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C50" s="67" t="str">
+      <x:c r="C50" s="77" t="str">
         <x:v>Thai and English buyer enquiry acknowledgments</x:v>
       </x:c>
-      <x:c r="D50" s="67" t="str">
+      <x:c r="D50" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E50" s="67" t="str">
+      <x:c r="E50" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F50" s="67" t="str">
+      <x:c r="F50" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G50" s="67" t="str">
+      <x:c r="G50" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H50" s="68"/>
-      <x:c r="I50" s="68"/>
-      <x:c r="J50" s="67"/>
-      <x:c r="K50" s="67"/>
-      <x:c r="L50" s="67"/>
-      <x:c r="M50" s="67"/>
+      <x:c r="H50" s="78"/>
+      <x:c r="I50" s="78"/>
+      <x:c r="J50" s="77"/>
+      <x:c r="K50" s="77"/>
+      <x:c r="L50" s="77"/>
+      <x:c r="M50" s="77"/>
     </x:row>
     <x:row r="51" ht="26" customHeight="1">
-      <x:c r="A51" s="66" t="str">
+      <x:c r="A51" s="76" t="str">
         <x:v>E03</x:v>
       </x:c>
-      <x:c r="B51" s="67" t="str">
+      <x:c r="B51" s="77" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C51" s="67" t="str">
+      <x:c r="C51" s="77" t="str">
         <x:v>Project brochure/price list email delivery</x:v>
       </x:c>
-      <x:c r="D51" s="67" t="str">
+      <x:c r="D51" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E51" s="67" t="str">
+      <x:c r="E51" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F51" s="67" t="str">
+      <x:c r="F51" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G51" s="67" t="str">
+      <x:c r="G51" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H51" s="68"/>
-      <x:c r="I51" s="68"/>
-      <x:c r="J51" s="67"/>
-      <x:c r="K51" s="67"/>
-      <x:c r="L51" s="67"/>
-      <x:c r="M51" s="67"/>
+      <x:c r="H51" s="78"/>
+      <x:c r="I51" s="78"/>
+      <x:c r="J51" s="77"/>
+      <x:c r="K51" s="77"/>
+      <x:c r="L51" s="77"/>
+      <x:c r="M51" s="77"/>
     </x:row>
     <x:row r="52" ht="26" customHeight="1">
-      <x:c r="A52" s="66" t="str">
+      <x:c r="A52" s="76" t="str">
         <x:v>E04</x:v>
       </x:c>
-      <x:c r="B52" s="67" t="str">
+      <x:c r="B52" s="77" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C52" s="67" t="str">
+      <x:c r="C52" s="77" t="str">
         <x:v>Site visit request and confirmation notifications</x:v>
       </x:c>
-      <x:c r="D52" s="67" t="str">
+      <x:c r="D52" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E52" s="67" t="str">
+      <x:c r="E52" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F52" s="67" t="str">
+      <x:c r="F52" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G52" s="67" t="str">
+      <x:c r="G52" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H52" s="68"/>
-      <x:c r="I52" s="68"/>
-      <x:c r="J52" s="67"/>
-      <x:c r="K52" s="67"/>
-      <x:c r="L52" s="67"/>
-      <x:c r="M52" s="67"/>
+      <x:c r="H52" s="78"/>
+      <x:c r="I52" s="78"/>
+      <x:c r="J52" s="77"/>
+      <x:c r="K52" s="77"/>
+      <x:c r="L52" s="77"/>
+      <x:c r="M52" s="77"/>
     </x:row>
     <x:row r="53" ht="26" customHeight="1">
-      <x:c r="A53" s="66" t="str">
+      <x:c r="A53" s="76" t="str">
         <x:v>E05</x:v>
       </x:c>
-      <x:c r="B53" s="67" t="str">
+      <x:c r="B53" s="77" t="str">
         <x:v>Step 9 · Alerts</x:v>
       </x:c>
-      <x:c r="C53" s="67" t="str">
+      <x:c r="C53" s="77" t="str">
         <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
       </x:c>
-      <x:c r="D53" s="67" t="str">
+      <x:c r="D53" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E53" s="67" t="str">
+      <x:c r="E53" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F53" s="67" t="str">
+      <x:c r="F53" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G53" s="67" t="str">
+      <x:c r="G53" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H53" s="68"/>
-      <x:c r="I53" s="68"/>
-      <x:c r="J53" s="67"/>
-      <x:c r="K53" s="67"/>
-      <x:c r="L53" s="67"/>
-      <x:c r="M53" s="67"/>
+      <x:c r="H53" s="78"/>
+      <x:c r="I53" s="78"/>
+      <x:c r="J53" s="77"/>
+      <x:c r="K53" s="77"/>
+      <x:c r="L53" s="77"/>
+      <x:c r="M53" s="77"/>
     </x:row>
     <x:row r="54" ht="26" customHeight="1">
-      <x:c r="A54" s="66" t="str">
+      <x:c r="A54" s="76" t="str">
         <x:v>E06</x:v>
       </x:c>
-      <x:c r="B54" s="67" t="str">
+      <x:c r="B54" s="77" t="str">
         <x:v>Step 10B · Email</x:v>
       </x:c>
-      <x:c r="C54" s="67" t="str">
+      <x:c r="C54" s="77" t="str">
         <x:v>Account verification and recovery messages if email auth approved</x:v>
       </x:c>
-      <x:c r="D54" s="67" t="str">
+      <x:c r="D54" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E54" s="67" t="str">
+      <x:c r="E54" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F54" s="67" t="str">
+      <x:c r="F54" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G54" s="67" t="str">
+      <x:c r="G54" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H54" s="68"/>
-      <x:c r="I54" s="68"/>
-      <x:c r="J54" s="67"/>
-      <x:c r="K54" s="67"/>
-      <x:c r="L54" s="67"/>
-      <x:c r="M54" s="67"/>
+      <x:c r="H54" s="78"/>
+      <x:c r="I54" s="78"/>
+      <x:c r="J54" s="77"/>
+      <x:c r="K54" s="77"/>
+      <x:c r="L54" s="77"/>
+      <x:c r="M54" s="77"/>
     </x:row>
     <x:row r="55" ht="26" customHeight="1">
-      <x:c r="A55" s="66" t="str">
+      <x:c r="A55" s="76" t="str">
         <x:v>E07</x:v>
       </x:c>
-      <x:c r="B55" s="67" t="str">
+      <x:c r="B55" s="77" t="str">
         <x:v>Step 11B · Email</x:v>
       </x:c>
-      <x:c r="C55" s="67" t="str">
+      <x:c r="C55" s="77" t="str">
         <x:v>Agent notification/routing administration</x:v>
       </x:c>
-      <x:c r="D55" s="67" t="str">
+      <x:c r="D55" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E55" s="67" t="str">
+      <x:c r="E55" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F55" s="67" t="str">
+      <x:c r="F55" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G55" s="67" t="str">
+      <x:c r="G55" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H55" s="68"/>
-      <x:c r="I55" s="68"/>
-      <x:c r="J55" s="67"/>
-      <x:c r="K55" s="67"/>
-      <x:c r="L55" s="67"/>
-      <x:c r="M55" s="67"/>
+      <x:c r="H55" s="78"/>
+      <x:c r="I55" s="78"/>
+      <x:c r="J55" s="77"/>
+      <x:c r="K55" s="77"/>
+      <x:c r="L55" s="77"/>
+      <x:c r="M55" s="77"/>
     </x:row>
     <x:row r="56" ht="26" customHeight="1">
-      <x:c r="A56" s="66" t="str">
+      <x:c r="A56" s="76" t="str">
         <x:v>E08</x:v>
       </x:c>
-      <x:c r="B56" s="67" t="str">
+      <x:c r="B56" s="77" t="str">
         <x:v>Step 7 · Email</x:v>
       </x:c>
-      <x:c r="C56" s="67" t="str">
+      <x:c r="C56" s="77" t="str">
         <x:v>Home valuation and service enquiry replies</x:v>
       </x:c>
-      <x:c r="D56" s="67" t="str">
+      <x:c r="D56" s="77" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E56" s="67" t="str">
+      <x:c r="E56" s="77" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F56" s="67" t="str">
+      <x:c r="F56" s="77" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G56" s="67" t="str">
+      <x:c r="G56" s="77" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H56" s="68"/>
-      <x:c r="I56" s="68"/>
-      <x:c r="J56" s="67"/>
-      <x:c r="K56" s="67"/>
-      <x:c r="L56" s="67"/>
-      <x:c r="M56" s="67"/>
+      <x:c r="H56" s="78"/>
+      <x:c r="I56" s="78"/>
+      <x:c r="J56" s="77"/>
+      <x:c r="K56" s="77"/>
+      <x:c r="L56" s="77"/>
+      <x:c r="M56" s="77"/>
     </x:row>
     <x:row r="57" ht="26" customHeight="1">
       <x:c r="A57" s="56"/>
@@ -49256,13 +49511,13 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="48" priority="1">
+    <x:cfRule type="expression" dxfId="66" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="49" priority="2">
+    <x:cfRule type="expression" dxfId="67" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="50" priority="3">
+    <x:cfRule type="expression" dxfId="68" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -49282,7 +49537,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b0b6c89df874021"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7cdf360283842d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Mstar-Property-Task-Tracker.xlsx
+++ b/Mstar-Property-Task-Tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R76812f7c00e54ca0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R58d8913d6cac47b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R18c7389186a744d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="R7a73b5917bd245ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R876aa2b2a2ba4faf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="R6e5b00681f7f4fb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="Rcd7b20ee7162440f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="Rf5c0d2a07aff412a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="Rd321a4ce1fa94f25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="Rae7c8fcb872e4aa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="Rc22c344212234c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="Rb3683df33d874acd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -148,6 +148,21 @@
         <x:fgColor rgb="FFC6EFCE"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFF6666"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC6EFCE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -156,7 +171,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="83">
+  <x:cellXfs count="95">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -360,11 +375,47 @@
     <x:xf numFmtId="200" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="69">
+  <x:dxfs count="87">
     <x:dxf>
       <x:font>
         <x:color rgb="FF92400E"/>
@@ -512,6 +563,186 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFEFF4FB"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFF6666"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -1060,7 +1291,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="40" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1081,7 +1312,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1102,7 +1333,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="48" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1123,7 +1354,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="MstarDoneTasks" displayName="MstarDoneTasks" ref="A5:M21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="49" name="MstarDoneTasks" displayName="MstarDoneTasks" ref="A5:M22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1144,7 +1375,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="50" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1165,7 +1396,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M56" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="51" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M55" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1411,7 +1642,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
+        <x:v>2026-10-10: Step 3B / R04 verified. 84 permanent IDs: 17 Done, 17 Pending, 50 Not started. F25 Pending for Step 7 regional tiles. Prior IDs/history retained. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -1426,21 +1657,21 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -1452,7 +1683,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -1497,43 +1728,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="73" t="str">
+      <x:c r="A6" s="83" t="str">
         <x:v>F02</x:v>
       </x:c>
-      <x:c r="B6" s="74" t="str">
+      <x:c r="B6" s="84" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="74" t="str">
+      <x:c r="C6" s="84" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent</x:v>
       </x:c>
-      <x:c r="D6" s="74" t="str">
+      <x:c r="D6" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="74" t="str">
+      <x:c r="E6" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="74" t="str">
+      <x:c r="F6" s="84" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G6" s="74" t="str">
+      <x:c r="G6" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H6" s="75" t="d">
+      <x:c r="H6" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="75" t="d">
+      <x:c r="I6" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="74" t="str">
+      <x:c r="J6" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="74" t="str">
+      <x:c r="K6" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="74" t="str">
+      <x:c r="L6" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="74" t="str">
+      <x:c r="M6" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
 2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.
 2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.
@@ -1542,144 +1773,144 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="250" customHeight="1">
-      <x:c r="A7" s="73" t="str">
+      <x:c r="A7" s="83" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B7" s="74" t="str">
+      <x:c r="B7" s="84" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C7" s="74" t="str">
+      <x:c r="C7" s="84" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D7" s="74" t="str">
+      <x:c r="D7" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="74" t="str">
+      <x:c r="E7" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="74" t="str">
+      <x:c r="F7" s="84" t="str">
         <x:v>Approved temporary crest extracted and implemented. Owner will provide final header logo later.</x:v>
       </x:c>
-      <x:c r="G7" s="74" t="str">
+      <x:c r="G7" s="84" t="str">
         <x:v>Owner: supply final asset/version later; Codex: replace only approved logo.</x:v>
       </x:c>
-      <x:c r="H7" s="75" t="d">
+      <x:c r="H7" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="75" t="d">
+      <x:c r="I7" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="74" t="str">
+      <x:c r="J7" s="84" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K7" s="74" t="str">
+      <x:c r="K7" s="84" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L7" s="74" t="str">
+      <x:c r="L7" s="84" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="74" t="str">
+      <x:c r="M7" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
 2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.
 2026-10-09 foundation: Approved temporary crest extracted and implemented. Owner will provide final header logo later. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="73" t="str">
+      <x:c r="A8" s="83" t="str">
         <x:v>F32</x:v>
       </x:c>
-      <x:c r="B8" s="74" t="str">
+      <x:c r="B8" s="84" t="str">
         <x:v>Step 10A · Wireframe</x:v>
       </x:c>
-      <x:c r="C8" s="74" t="str">
+      <x:c r="C8" s="84" t="str">
         <x:v>Owner-approved login/register/account wireframe before coding</x:v>
       </x:c>
-      <x:c r="D8" s="74" t="str">
+      <x:c r="D8" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="74" t="str">
+      <x:c r="E8" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="74" t="str">
+      <x:c r="F8" s="84" t="str">
         <x:v>Admin/account screens are not part of approved V3 visuals</x:v>
       </x:c>
-      <x:c r="G8" s="74" t="str">
+      <x:c r="G8" s="84" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H8" s="75"/>
-      <x:c r="I8" s="75"/>
-      <x:c r="J8" s="74"/>
-      <x:c r="K8" s="74"/>
-      <x:c r="L8" s="74"/>
-      <x:c r="M8" s="74"/>
+      <x:c r="H8" s="85"/>
+      <x:c r="I8" s="85"/>
+      <x:c r="J8" s="84"/>
+      <x:c r="K8" s="84"/>
+      <x:c r="L8" s="84"/>
+      <x:c r="M8" s="84"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="73" t="str">
+      <x:c r="A9" s="83" t="str">
         <x:v>F34</x:v>
       </x:c>
-      <x:c r="B9" s="74" t="str">
+      <x:c r="B9" s="84" t="str">
         <x:v>Step 11A · Wireframe</x:v>
       </x:c>
-      <x:c r="C9" s="74" t="str">
+      <x:c r="C9" s="84" t="str">
         <x:v>Owner-approved responsive admin dashboard wireframe</x:v>
       </x:c>
-      <x:c r="D9" s="74" t="str">
+      <x:c r="D9" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="74" t="str">
+      <x:c r="E9" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="74" t="str">
+      <x:c r="F9" s="84" t="str">
         <x:v>Admin UI not included in V3; design approval required</x:v>
       </x:c>
-      <x:c r="G9" s="74" t="str">
+      <x:c r="G9" s="84" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H9" s="75"/>
-      <x:c r="I9" s="75"/>
-      <x:c r="J9" s="74"/>
-      <x:c r="K9" s="74"/>
-      <x:c r="L9" s="74"/>
-      <x:c r="M9" s="74"/>
+      <x:c r="H9" s="85"/>
+      <x:c r="I9" s="85"/>
+      <x:c r="J9" s="84"/>
+      <x:c r="K9" s="84"/>
+      <x:c r="L9" s="84"/>
+      <x:c r="M9" s="84"/>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="73" t="str">
+      <x:c r="A10" s="83" t="str">
         <x:v>F01</x:v>
       </x:c>
-      <x:c r="B10" s="74" t="str">
+      <x:c r="B10" s="84" t="str">
         <x:v>Step 1 · Design</x:v>
       </x:c>
-      <x:c r="C10" s="74" t="str">
+      <x:c r="C10" s="84" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives</x:v>
       </x:c>
-      <x:c r="D10" s="74" t="str">
+      <x:c r="D10" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E10" s="74" t="str">
+      <x:c r="E10" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="74" t="str">
+      <x:c r="F10" s="84" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G10" s="74" t="str">
+      <x:c r="G10" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H10" s="75" t="d">
+      <x:c r="H10" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="75" t="d">
+      <x:c r="I10" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="74" t="str">
+      <x:c r="J10" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="74" t="str">
+      <x:c r="K10" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="74" t="str">
+      <x:c r="L10" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="74" t="str">
+      <x:c r="M10" s="84" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1687,43 +1918,43 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="310" customHeight="1">
-      <x:c r="A11" s="73" t="str">
+      <x:c r="A11" s="83" t="str">
         <x:v>F04</x:v>
       </x:c>
-      <x:c r="B11" s="74" t="str">
+      <x:c r="B11" s="84" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C11" s="74" t="str">
+      <x:c r="C11" s="84" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in</x:v>
       </x:c>
-      <x:c r="D11" s="74" t="str">
+      <x:c r="D11" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E11" s="74" t="str">
+      <x:c r="E11" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="74" t="str">
+      <x:c r="F11" s="84" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G11" s="74" t="str">
+      <x:c r="G11" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H11" s="75" t="d">
+      <x:c r="H11" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I11" s="75" t="d">
+      <x:c r="I11" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="74" t="str">
+      <x:c r="J11" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K11" s="74" t="str">
+      <x:c r="K11" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L11" s="74" t="str">
+      <x:c r="L11" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M11" s="74" t="str">
+      <x:c r="M11" s="84" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1731,43 +1962,43 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="310" customHeight="1">
-      <x:c r="A12" s="73" t="str">
+      <x:c r="A12" s="83" t="str">
         <x:v>F05</x:v>
       </x:c>
-      <x:c r="B12" s="74" t="str">
+      <x:c r="B12" s="84" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C12" s="74" t="str">
+      <x:c r="C12" s="84" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints</x:v>
       </x:c>
-      <x:c r="D12" s="74" t="str">
+      <x:c r="D12" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E12" s="74" t="str">
+      <x:c r="E12" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="74" t="str">
+      <x:c r="F12" s="84" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G12" s="74" t="str">
+      <x:c r="G12" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H12" s="75" t="d">
+      <x:c r="H12" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="75" t="d">
+      <x:c r="I12" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="74" t="str">
+      <x:c r="J12" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K12" s="74" t="str">
+      <x:c r="K12" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L12" s="74" t="str">
+      <x:c r="L12" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="74" t="str">
+      <x:c r="M12" s="84" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1775,43 +2006,43 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="310" customHeight="1">
-      <x:c r="A13" s="73" t="str">
+      <x:c r="A13" s="83" t="str">
         <x:v>F06</x:v>
       </x:c>
-      <x:c r="B13" s="74" t="str">
+      <x:c r="B13" s="84" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C13" s="74" t="str">
+      <x:c r="C13" s="84" t="str">
         <x:v>Light footer, company links, contact and PDPA link</x:v>
       </x:c>
-      <x:c r="D13" s="74" t="str">
+      <x:c r="D13" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E13" s="74" t="str">
+      <x:c r="E13" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F13" s="74" t="str">
+      <x:c r="F13" s="84" t="str">
         <x:v>Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G13" s="74" t="str">
+      <x:c r="G13" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H13" s="75" t="d">
+      <x:c r="H13" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I13" s="75" t="d">
+      <x:c r="I13" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J13" s="74" t="str">
+      <x:c r="J13" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K13" s="74" t="str">
+      <x:c r="K13" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L13" s="74" t="str">
+      <x:c r="L13" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M13" s="74" t="str">
+      <x:c r="M13" s="84" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1819,43 +2050,43 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="310" customHeight="1">
-      <x:c r="A14" s="73" t="str">
+      <x:c r="A14" s="83" t="str">
         <x:v>F07</x:v>
       </x:c>
-      <x:c r="B14" s="74" t="str">
+      <x:c r="B14" s="84" t="str">
         <x:v>Step 1 · i18n</x:v>
       </x:c>
-      <x:c r="C14" s="74" t="str">
+      <x:c r="C14" s="84" t="str">
         <x:v>Thai/English routes, language switch and localized formatting</x:v>
       </x:c>
-      <x:c r="D14" s="74" t="str">
+      <x:c r="D14" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E14" s="74" t="str">
+      <x:c r="E14" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="74" t="str">
+      <x:c r="F14" s="84" t="str">
         <x:v>Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G14" s="74" t="str">
+      <x:c r="G14" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H14" s="75" t="d">
+      <x:c r="H14" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I14" s="75" t="d">
+      <x:c r="I14" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="74" t="str">
+      <x:c r="J14" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K14" s="74" t="str">
+      <x:c r="K14" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L14" s="74" t="str">
+      <x:c r="L14" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M14" s="74" t="str">
+      <x:c r="M14" s="84" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -1863,693 +2094,694 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="250" customHeight="1">
-      <x:c r="A15" s="76" t="str">
+      <x:c r="A15" s="86" t="str">
         <x:v>F14</x:v>
       </x:c>
-      <x:c r="B15" s="77" t="str">
+      <x:c r="B15" s="87" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C15" s="77" t="str">
+      <x:c r="C15" s="87" t="str">
         <x:v>Desktop listing/map split and hover/focus pin synchronization</x:v>
       </x:c>
-      <x:c r="D15" s="77" t="str">
+      <x:c r="D15" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="77" t="str">
+      <x:c r="E15" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="77" t="str">
+      <x:c r="F15" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G15" s="77" t="str">
+      <x:c r="G15" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H15" s="78"/>
-      <x:c r="I15" s="78"/>
-      <x:c r="J15" s="77"/>
-      <x:c r="K15" s="77"/>
-      <x:c r="L15" s="77"/>
-      <x:c r="M15" s="77"/>
+      <x:c r="H15" s="88"/>
+      <x:c r="I15" s="88"/>
+      <x:c r="J15" s="87"/>
+      <x:c r="K15" s="87"/>
+      <x:c r="L15" s="87"/>
+      <x:c r="M15" s="87"/>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="76" t="str">
+      <x:c r="A16" s="86" t="str">
         <x:v>F15</x:v>
       </x:c>
-      <x:c r="B16" s="77" t="str">
+      <x:c r="B16" s="87" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C16" s="77" t="str">
+      <x:c r="C16" s="87" t="str">
         <x:v>Phone full-screen Map/List toggle</x:v>
       </x:c>
-      <x:c r="D16" s="77" t="str">
+      <x:c r="D16" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E16" s="77" t="str">
+      <x:c r="E16" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="77" t="str">
+      <x:c r="F16" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G16" s="77" t="str">
+      <x:c r="G16" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H16" s="78"/>
-      <x:c r="I16" s="78"/>
-      <x:c r="J16" s="77"/>
-      <x:c r="K16" s="77"/>
-      <x:c r="L16" s="77"/>
-      <x:c r="M16" s="77"/>
+      <x:c r="H16" s="88"/>
+      <x:c r="I16" s="88"/>
+      <x:c r="J16" s="87"/>
+      <x:c r="K16" s="87"/>
+      <x:c r="L16" s="87"/>
+      <x:c r="M16" s="87"/>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="76" t="str">
+      <x:c r="A17" s="86" t="str">
         <x:v>F16</x:v>
       </x:c>
-      <x:c r="B17" s="77" t="str">
+      <x:c r="B17" s="87" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C17" s="77" t="str">
+      <x:c r="C17" s="87" t="str">
         <x:v>Property detail photo grid and full-screen gallery</x:v>
       </x:c>
-      <x:c r="D17" s="77" t="str">
+      <x:c r="D17" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="77" t="str">
+      <x:c r="E17" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="77" t="str">
+      <x:c r="F17" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G17" s="77" t="str">
+      <x:c r="G17" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H17" s="78"/>
-      <x:c r="I17" s="78"/>
-      <x:c r="J17" s="77"/>
-      <x:c r="K17" s="77"/>
-      <x:c r="L17" s="77"/>
-      <x:c r="M17" s="77"/>
+      <x:c r="H17" s="88"/>
+      <x:c r="I17" s="88"/>
+      <x:c r="J17" s="87"/>
+      <x:c r="K17" s="87"/>
+      <x:c r="L17" s="87"/>
+      <x:c r="M17" s="87"/>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="76" t="str">
+      <x:c r="A18" s="86" t="str">
         <x:v>F17</x:v>
       </x:c>
-      <x:c r="B18" s="77" t="str">
+      <x:c r="B18" s="87" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C18" s="77" t="str">
+      <x:c r="C18" s="87" t="str">
         <x:v>Title, pricing, type-specific facts, long description and sticky tabs</x:v>
       </x:c>
-      <x:c r="D18" s="77" t="str">
+      <x:c r="D18" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="77" t="str">
+      <x:c r="E18" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F18" s="77" t="str">
+      <x:c r="F18" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G18" s="77" t="str">
+      <x:c r="G18" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H18" s="78"/>
-      <x:c r="I18" s="78"/>
-      <x:c r="J18" s="77"/>
-      <x:c r="K18" s="77"/>
-      <x:c r="L18" s="77"/>
-      <x:c r="M18" s="77"/>
+      <x:c r="H18" s="88"/>
+      <x:c r="I18" s="88"/>
+      <x:c r="J18" s="87"/>
+      <x:c r="K18" s="87"/>
+      <x:c r="L18" s="87"/>
+      <x:c r="M18" s="87"/>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="76" t="str">
+      <x:c r="A19" s="86" t="str">
         <x:v>F18</x:v>
       </x:c>
-      <x:c r="B19" s="77" t="str">
+      <x:c r="B19" s="87" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C19" s="77" t="str">
+      <x:c r="C19" s="87" t="str">
         <x:v>Floorplan/video/360 tabs, verified nearby information and map</x:v>
       </x:c>
-      <x:c r="D19" s="77" t="str">
+      <x:c r="D19" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="77" t="str">
+      <x:c r="E19" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="77" t="str">
+      <x:c r="F19" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G19" s="77" t="str">
+      <x:c r="G19" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H19" s="78"/>
-      <x:c r="I19" s="78"/>
-      <x:c r="J19" s="77"/>
-      <x:c r="K19" s="77"/>
-      <x:c r="L19" s="77"/>
-      <x:c r="M19" s="77"/>
+      <x:c r="H19" s="88"/>
+      <x:c r="I19" s="88"/>
+      <x:c r="J19" s="87"/>
+      <x:c r="K19" s="87"/>
+      <x:c r="L19" s="87"/>
+      <x:c r="M19" s="87"/>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="76" t="str">
+      <x:c r="A20" s="86" t="str">
         <x:v>F19</x:v>
       </x:c>
-      <x:c r="B20" s="77" t="str">
+      <x:c r="B20" s="87" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C20" s="77" t="str">
+      <x:c r="C20" s="87" t="str">
         <x:v>Mortgage calculator and area comparison when real data exists</x:v>
       </x:c>
-      <x:c r="D20" s="77" t="str">
+      <x:c r="D20" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="77" t="str">
+      <x:c r="E20" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="77" t="str">
+      <x:c r="F20" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G20" s="77" t="str">
+      <x:c r="G20" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H20" s="78"/>
-      <x:c r="I20" s="78"/>
-      <x:c r="J20" s="77"/>
-      <x:c r="K20" s="77"/>
-      <x:c r="L20" s="77"/>
-      <x:c r="M20" s="77"/>
+      <x:c r="H20" s="88"/>
+      <x:c r="I20" s="88"/>
+      <x:c r="J20" s="87"/>
+      <x:c r="K20" s="87"/>
+      <x:c r="L20" s="87"/>
+      <x:c r="M20" s="87"/>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="76" t="str">
+      <x:c r="A21" s="86" t="str">
         <x:v>F20</x:v>
       </x:c>
-      <x:c r="B21" s="77" t="str">
+      <x:c r="B21" s="87" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C21" s="77" t="str">
+      <x:c r="C21" s="87" t="str">
         <x:v>Same-project units and similar-property cards</x:v>
       </x:c>
-      <x:c r="D21" s="77" t="str">
+      <x:c r="D21" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="77" t="str">
+      <x:c r="E21" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="77" t="str">
+      <x:c r="F21" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G21" s="77" t="str">
+      <x:c r="G21" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H21" s="78"/>
-      <x:c r="I21" s="78"/>
-      <x:c r="J21" s="77"/>
-      <x:c r="K21" s="77"/>
-      <x:c r="L21" s="77"/>
-      <x:c r="M21" s="77"/>
+      <x:c r="H21" s="88"/>
+      <x:c r="I21" s="88"/>
+      <x:c r="J21" s="87"/>
+      <x:c r="K21" s="87"/>
+      <x:c r="L21" s="87"/>
+      <x:c r="M21" s="87"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="76" t="str">
+      <x:c r="A22" s="86" t="str">
         <x:v>F21</x:v>
       </x:c>
-      <x:c r="B22" s="77" t="str">
+      <x:c r="B22" s="87" t="str">
         <x:v>Step 6 · Contact</x:v>
       </x:c>
-      <x:c r="C22" s="77" t="str">
+      <x:c r="C22" s="87" t="str">
         <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
       </x:c>
-      <x:c r="D22" s="77" t="str">
+      <x:c r="D22" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E22" s="77" t="str">
+      <x:c r="E22" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="77" t="str">
+      <x:c r="F22" s="87" t="str">
         <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
-      <x:c r="G22" s="77" t="str">
+      <x:c r="G22" s="87" t="str">
         <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
       </x:c>
-      <x:c r="H22" s="78"/>
-      <x:c r="I22" s="78" t="d">
+      <x:c r="H22" s="88"/>
+      <x:c r="I22" s="88" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J22" s="77" t="str">
+      <x:c r="J22" s="87" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K22" s="77" t="str">
+      <x:c r="K22" s="87" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L22" s="77" t="str">
+      <x:c r="L22" s="87" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M22" s="77" t="str">
+      <x:c r="M22" s="87" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
-      <x:c r="A23" s="76" t="str">
+      <x:c r="A23" s="86" t="str">
         <x:v>F22</x:v>
       </x:c>
-      <x:c r="B23" s="77" t="str">
+      <x:c r="B23" s="87" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C23" s="77" t="str">
+      <x:c r="C23" s="87" t="str">
         <x:v>Single-image hero and compact photography-first layout</x:v>
       </x:c>
-      <x:c r="D23" s="77" t="str">
+      <x:c r="D23" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E23" s="77" t="str">
+      <x:c r="E23" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F23" s="77" t="str">
+      <x:c r="F23" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G23" s="77" t="str">
+      <x:c r="G23" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H23" s="78"/>
-      <x:c r="I23" s="78"/>
-      <x:c r="J23" s="77"/>
-      <x:c r="K23" s="77"/>
-      <x:c r="L23" s="77"/>
-      <x:c r="M23" s="77"/>
+      <x:c r="H23" s="88"/>
+      <x:c r="I23" s="88"/>
+      <x:c r="J23" s="87"/>
+      <x:c r="K23" s="87"/>
+      <x:c r="L23" s="87"/>
+      <x:c r="M23" s="87"/>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="76" t="str">
+      <x:c r="A24" s="86" t="str">
         <x:v>F23</x:v>
       </x:c>
-      <x:c r="B24" s="77" t="str">
+      <x:c r="B24" s="87" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C24" s="77" t="str">
+      <x:c r="C24" s="87" t="str">
         <x:v>Shared search box with Buy/Rent/Projects/Investment tabs</x:v>
       </x:c>
-      <x:c r="D24" s="77" t="str">
+      <x:c r="D24" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E24" s="77" t="str">
+      <x:c r="E24" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="77" t="str">
+      <x:c r="F24" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G24" s="77" t="str">
+      <x:c r="G24" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H24" s="78"/>
-      <x:c r="I24" s="78"/>
-      <x:c r="J24" s="77"/>
-      <x:c r="K24" s="77"/>
-      <x:c r="L24" s="77"/>
-      <x:c r="M24" s="77"/>
+      <x:c r="H24" s="88"/>
+      <x:c r="I24" s="88"/>
+      <x:c r="J24" s="87"/>
+      <x:c r="K24" s="87"/>
+      <x:c r="L24" s="87"/>
+      <x:c r="M24" s="87"/>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="76" t="str">
+      <x:c r="A25" s="86" t="str">
         <x:v>F24</x:v>
       </x:c>
-      <x:c r="B25" s="77" t="str">
+      <x:c r="B25" s="87" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C25" s="77" t="str">
+      <x:c r="C25" s="87" t="str">
         <x:v>Categories, recent searches and location/station suggestions</x:v>
       </x:c>
-      <x:c r="D25" s="77" t="str">
+      <x:c r="D25" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E25" s="77" t="str">
+      <x:c r="E25" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="77" t="str">
+      <x:c r="F25" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G25" s="77" t="str">
+      <x:c r="G25" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H25" s="78"/>
-      <x:c r="I25" s="78"/>
-      <x:c r="J25" s="77"/>
-      <x:c r="K25" s="77"/>
-      <x:c r="L25" s="77"/>
-      <x:c r="M25" s="77"/>
-    </x:row>
-    <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="76" t="str">
+      <x:c r="H25" s="88"/>
+      <x:c r="I25" s="88"/>
+      <x:c r="J25" s="87"/>
+      <x:c r="K25" s="87"/>
+      <x:c r="L25" s="87"/>
+      <x:c r="M25" s="87"/>
+    </x:row>
+    <x:row r="26" ht="400" customHeight="1">
+      <x:c r="A26" s="83" t="str">
         <x:v>F25</x:v>
       </x:c>
-      <x:c r="B26" s="77" t="str">
+      <x:c r="B26" s="84" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C26" s="77" t="str">
-        <x:v>Homes for you carousel directly below search; regions with real listing counts</x:v>
-      </x:c>
-      <x:c r="D26" s="77" t="str">
+      <x:c r="C26" s="84" t="str">
+        <x:v>Small home listing rows; regional tiles with real listing counts (Steps 3B/7)</x:v>
+      </x:c>
+      <x:c r="D26" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E26" s="77" t="str">
+      <x:c r="E26" s="84" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F26" s="84" t="str">
+        <x:v>Step 3B implements approved topic rows, separate small cards, responsive rails, featured/newest safe queries, saves and honest local samples. Regional tiles/live location counts remain Step 7 and are not implemented. This broad task is therefore Pending; the scoped Step 3B work is R04 Done.</x:v>
+      </x:c>
+      <x:c r="G26" s="84" t="str">
+        <x:v>Codex: wait for Step 7 authorization to add regional tiles/live counts. Future admin row management requires its approved stage. Stop before Step 4 now.</x:v>
+      </x:c>
+      <x:c r="H26" s="85" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I26" s="85"/>
+      <x:c r="J26" s="84" t="str">
+        <x:v>PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
+      </x:c>
+      <x:c r="K26" s="84" t="str">
+        <x:v>Preceding 830e037 pushed. Current commit/push verified at finalization; exact hash in final report. Revert affected tasks to Pending if a final gate fails.</x:v>
+      </x:c>
+      <x:c r="L26" s="84" t="str">
+        <x:v>82-file live baseline rechecked before sync. Owner reference revisions adopted without rewriting their input hashes; 91 intended Git/live source/config/docs/tracker pairs verified at closeout. Secrets/dependencies/runtime/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M26" s="84" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.
+2026-10-10 R04: owner replaced the older big carousel with small topic rows and authorized this portion in Step 3B. Rows implemented/tested; regional tiles remain Step 7. Not started to Pending for partial scope; original history retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="26" customHeight="1">
+      <x:c r="A27" s="86" t="str">
+        <x:v>F26</x:v>
+      </x:c>
+      <x:c r="B27" s="87" t="str">
+        <x:v>Step 7 · Home</x:v>
+      </x:c>
+      <x:c r="C27" s="87" t="str">
+        <x:v>New projects, tools, services and owner lead CTAs</x:v>
+      </x:c>
+      <x:c r="D27" s="87" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E27" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="77" t="str">
-        <x:v>V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
-      </x:c>
-      <x:c r="G26" s="77" t="str">
-        <x:v>Codex: implement approved home-page.html only under Step 7 authorization.</x:v>
-      </x:c>
-      <x:c r="H26" s="78"/>
-      <x:c r="I26" s="78" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="J26" s="77" t="str">
-        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
-      </x:c>
-      <x:c r="K26" s="77" t="str">
-        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
-      </x:c>
-      <x:c r="L26" s="77" t="str">
-        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
-      </x:c>
-      <x:c r="M26" s="77" t="str">
-        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="76" t="str">
-        <x:v>F26</x:v>
-      </x:c>
-      <x:c r="B27" s="77" t="str">
-        <x:v>Step 7 · Home</x:v>
-      </x:c>
-      <x:c r="C27" s="77" t="str">
-        <x:v>New projects, tools, services and owner lead CTAs</x:v>
-      </x:c>
-      <x:c r="D27" s="77" t="str">
+      <x:c r="F27" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G27" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H27" s="88"/>
+      <x:c r="I27" s="88"/>
+      <x:c r="J27" s="87"/>
+      <x:c r="K27" s="87"/>
+      <x:c r="L27" s="87"/>
+      <x:c r="M27" s="87"/>
+    </x:row>
+    <x:row r="28" ht="250" customHeight="1">
+      <x:c r="A28" s="86" t="str">
+        <x:v>F27</x:v>
+      </x:c>
+      <x:c r="B28" s="87" t="str">
+        <x:v>Step 8 · Projects</x:v>
+      </x:c>
+      <x:c r="C28" s="87" t="str">
+        <x:v>Projects index and responsive project detail layouts</x:v>
+      </x:c>
+      <x:c r="D28" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E27" s="77" t="str">
+      <x:c r="E28" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="77" t="str">
+      <x:c r="F28" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G27" s="77" t="str">
+      <x:c r="G28" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H27" s="78"/>
-      <x:c r="I27" s="78"/>
-      <x:c r="J27" s="77"/>
-      <x:c r="K27" s="77"/>
-      <x:c r="L27" s="77"/>
-      <x:c r="M27" s="77"/>
-    </x:row>
-    <x:row r="28" ht="250" customHeight="1">
-      <x:c r="A28" s="76" t="str">
-        <x:v>F27</x:v>
-      </x:c>
-      <x:c r="B28" s="77" t="str">
+      <x:c r="H28" s="88"/>
+      <x:c r="I28" s="88"/>
+      <x:c r="J28" s="87"/>
+      <x:c r="K28" s="87"/>
+      <x:c r="L28" s="87"/>
+      <x:c r="M28" s="87"/>
+    </x:row>
+    <x:row r="29" ht="26" customHeight="1">
+      <x:c r="A29" s="86" t="str">
+        <x:v>F28</x:v>
+      </x:c>
+      <x:c r="B29" s="87" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C28" s="77" t="str">
-        <x:v>Projects index and responsive project detail layouts</x:v>
-      </x:c>
-      <x:c r="D28" s="77" t="str">
+      <x:c r="C29" s="87" t="str">
+        <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
+      </x:c>
+      <x:c r="D29" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E28" s="77" t="str">
+      <x:c r="E29" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="77" t="str">
+      <x:c r="F29" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G28" s="77" t="str">
+      <x:c r="G29" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H28" s="78"/>
-      <x:c r="I28" s="78"/>
-      <x:c r="J28" s="77"/>
-      <x:c r="K28" s="77"/>
-      <x:c r="L28" s="77"/>
-      <x:c r="M28" s="77"/>
-    </x:row>
-    <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="76" t="str">
-        <x:v>F28</x:v>
-      </x:c>
-      <x:c r="B29" s="77" t="str">
+      <x:c r="H29" s="88"/>
+      <x:c r="I29" s="88"/>
+      <x:c r="J29" s="87"/>
+      <x:c r="K29" s="87"/>
+      <x:c r="L29" s="87"/>
+      <x:c r="M29" s="87"/>
+    </x:row>
+    <x:row r="30" ht="26" customHeight="1">
+      <x:c r="A30" s="86" t="str">
+        <x:v>F29</x:v>
+      </x:c>
+      <x:c r="B30" s="87" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C29" s="77" t="str">
-        <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
-      </x:c>
-      <x:c r="D29" s="77" t="str">
+      <x:c r="C30" s="87" t="str">
+        <x:v>Data-driven clickable project SVG plot plan</x:v>
+      </x:c>
+      <x:c r="D30" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E29" s="77" t="str">
+      <x:c r="E30" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="77" t="str">
+      <x:c r="F30" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="77" t="str">
+      <x:c r="G30" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="78"/>
-      <x:c r="I29" s="78"/>
-      <x:c r="J29" s="77"/>
-      <x:c r="K29" s="77"/>
-      <x:c r="L29" s="77"/>
-      <x:c r="M29" s="77"/>
-    </x:row>
-    <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="76" t="str">
-        <x:v>F29</x:v>
-      </x:c>
-      <x:c r="B30" s="77" t="str">
-        <x:v>Step 8 · Projects</x:v>
-      </x:c>
-      <x:c r="C30" s="77" t="str">
-        <x:v>Data-driven clickable project SVG plot plan</x:v>
-      </x:c>
-      <x:c r="D30" s="77" t="str">
+      <x:c r="H30" s="88"/>
+      <x:c r="I30" s="88"/>
+      <x:c r="J30" s="87"/>
+      <x:c r="K30" s="87"/>
+      <x:c r="L30" s="87"/>
+      <x:c r="M30" s="87"/>
+    </x:row>
+    <x:row r="31" ht="26" customHeight="1">
+      <x:c r="A31" s="86" t="str">
+        <x:v>F30</x:v>
+      </x:c>
+      <x:c r="B31" s="87" t="str">
+        <x:v>Step 8 · Booking</x:v>
+      </x:c>
+      <x:c r="C31" s="87" t="str">
+        <x:v>Site visit 3-step form and confirmation screens</x:v>
+      </x:c>
+      <x:c r="D31" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E30" s="77" t="str">
+      <x:c r="E31" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="77" t="str">
+      <x:c r="F31" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="77" t="str">
+      <x:c r="G31" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="78"/>
-      <x:c r="I30" s="78"/>
-      <x:c r="J30" s="77"/>
-      <x:c r="K30" s="77"/>
-      <x:c r="L30" s="77"/>
-      <x:c r="M30" s="77"/>
-    </x:row>
-    <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="76" t="str">
-        <x:v>F30</x:v>
-      </x:c>
-      <x:c r="B31" s="77" t="str">
-        <x:v>Step 8 · Booking</x:v>
-      </x:c>
-      <x:c r="C31" s="77" t="str">
-        <x:v>Site visit 3-step form and confirmation screens</x:v>
-      </x:c>
-      <x:c r="D31" s="77" t="str">
+      <x:c r="H31" s="88"/>
+      <x:c r="I31" s="88"/>
+      <x:c r="J31" s="87"/>
+      <x:c r="K31" s="87"/>
+      <x:c r="L31" s="87"/>
+      <x:c r="M31" s="87"/>
+    </x:row>
+    <x:row r="32" ht="250" customHeight="1">
+      <x:c r="A32" s="86" t="str">
+        <x:v>F31</x:v>
+      </x:c>
+      <x:c r="B32" s="87" t="str">
+        <x:v>Step 9 · Saved</x:v>
+      </x:c>
+      <x:c r="C32" s="87" t="str">
+        <x:v>Homes, searches and viewings; local save without account</x:v>
+      </x:c>
+      <x:c r="D32" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E31" s="77" t="str">
+      <x:c r="E32" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="77" t="str">
+      <x:c r="F32" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="77" t="str">
+      <x:c r="G32" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="78"/>
-      <x:c r="I31" s="78"/>
-      <x:c r="J31" s="77"/>
-      <x:c r="K31" s="77"/>
-      <x:c r="L31" s="77"/>
-      <x:c r="M31" s="77"/>
-    </x:row>
-    <x:row r="32" ht="250" customHeight="1">
-      <x:c r="A32" s="76" t="str">
-        <x:v>F31</x:v>
-      </x:c>
-      <x:c r="B32" s="77" t="str">
-        <x:v>Step 9 · Saved</x:v>
-      </x:c>
-      <x:c r="C32" s="77" t="str">
-        <x:v>Homes, searches and viewings; local save without account</x:v>
-      </x:c>
-      <x:c r="D32" s="77" t="str">
+      <x:c r="H32" s="88"/>
+      <x:c r="I32" s="88"/>
+      <x:c r="J32" s="87"/>
+      <x:c r="K32" s="87"/>
+      <x:c r="L32" s="87"/>
+      <x:c r="M32" s="87"/>
+    </x:row>
+    <x:row r="33" ht="26" customHeight="1">
+      <x:c r="A33" s="86" t="str">
+        <x:v>F33</x:v>
+      </x:c>
+      <x:c r="B33" s="87" t="str">
+        <x:v>Step 10B · Accounts</x:v>
+      </x:c>
+      <x:c r="C33" s="87" t="str">
+        <x:v>Build approved auth and account screens only after approval</x:v>
+      </x:c>
+      <x:c r="D33" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E32" s="77" t="str">
+      <x:c r="E33" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="77" t="str">
+      <x:c r="F33" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G32" s="77" t="str">
+      <x:c r="G33" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H32" s="78"/>
-      <x:c r="I32" s="78"/>
-      <x:c r="J32" s="77"/>
-      <x:c r="K32" s="77"/>
-      <x:c r="L32" s="77"/>
-      <x:c r="M32" s="77"/>
-    </x:row>
-    <x:row r="33" ht="26" customHeight="1">
-      <x:c r="A33" s="76" t="str">
-        <x:v>F33</x:v>
-      </x:c>
-      <x:c r="B33" s="77" t="str">
-        <x:v>Step 10B · Accounts</x:v>
-      </x:c>
-      <x:c r="C33" s="77" t="str">
-        <x:v>Build approved auth and account screens only after approval</x:v>
-      </x:c>
-      <x:c r="D33" s="77" t="str">
+      <x:c r="H33" s="88"/>
+      <x:c r="I33" s="88"/>
+      <x:c r="J33" s="87"/>
+      <x:c r="K33" s="87"/>
+      <x:c r="L33" s="87"/>
+      <x:c r="M33" s="87"/>
+    </x:row>
+    <x:row r="34" ht="26" customHeight="1">
+      <x:c r="A34" s="86" t="str">
+        <x:v>F35</x:v>
+      </x:c>
+      <x:c r="B34" s="87" t="str">
+        <x:v>Step 11B · Admin</x:v>
+      </x:c>
+      <x:c r="C34" s="87" t="str">
+        <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
+      </x:c>
+      <x:c r="D34" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E33" s="77" t="str">
+      <x:c r="E34" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F33" s="77" t="str">
+      <x:c r="F34" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G33" s="77" t="str">
+      <x:c r="G34" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H33" s="78"/>
-      <x:c r="I33" s="78"/>
-      <x:c r="J33" s="77"/>
-      <x:c r="K33" s="77"/>
-      <x:c r="L33" s="77"/>
-      <x:c r="M33" s="77"/>
-    </x:row>
-    <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="76" t="str">
-        <x:v>F35</x:v>
-      </x:c>
-      <x:c r="B34" s="77" t="str">
+      <x:c r="H34" s="88"/>
+      <x:c r="I34" s="88"/>
+      <x:c r="J34" s="87"/>
+      <x:c r="K34" s="87"/>
+      <x:c r="L34" s="87"/>
+      <x:c r="M34" s="87"/>
+    </x:row>
+    <x:row r="35" ht="26" customHeight="1">
+      <x:c r="A35" s="86" t="str">
+        <x:v>F36</x:v>
+      </x:c>
+      <x:c r="B35" s="87" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C34" s="77" t="str">
-        <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
-      </x:c>
-      <x:c r="D34" s="77" t="str">
+      <x:c r="C35" s="87" t="str">
+        <x:v>Admin-managed searchable filter editor with type safety</x:v>
+      </x:c>
+      <x:c r="D35" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E34" s="77" t="str">
+      <x:c r="E35" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F34" s="77" t="str">
+      <x:c r="F35" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G34" s="77" t="str">
+      <x:c r="G35" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H34" s="78"/>
-      <x:c r="I34" s="78"/>
-      <x:c r="J34" s="77"/>
-      <x:c r="K34" s="77"/>
-      <x:c r="L34" s="77"/>
-      <x:c r="M34" s="77"/>
-    </x:row>
-    <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="76" t="str">
-        <x:v>F36</x:v>
-      </x:c>
-      <x:c r="B35" s="77" t="str">
-        <x:v>Step 11B · Admin</x:v>
-      </x:c>
-      <x:c r="C35" s="77" t="str">
-        <x:v>Admin-managed searchable filter editor with type safety</x:v>
-      </x:c>
-      <x:c r="D35" s="77" t="str">
+      <x:c r="H35" s="88"/>
+      <x:c r="I35" s="88"/>
+      <x:c r="J35" s="87"/>
+      <x:c r="K35" s="87"/>
+      <x:c r="L35" s="87"/>
+      <x:c r="M35" s="87"/>
+    </x:row>
+    <x:row r="36" ht="26" customHeight="1">
+      <x:c r="A36" s="86" t="str">
+        <x:v>F37</x:v>
+      </x:c>
+      <x:c r="B36" s="87" t="str">
+        <x:v>Step 12 · Quality</x:v>
+      </x:c>
+      <x:c r="C36" s="87" t="str">
+        <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
+      </x:c>
+      <x:c r="D36" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E35" s="77" t="str">
+      <x:c r="E36" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F35" s="77" t="str">
+      <x:c r="F36" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G35" s="77" t="str">
+      <x:c r="G36" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H35" s="78"/>
-      <x:c r="I35" s="78"/>
-      <x:c r="J35" s="77"/>
-      <x:c r="K35" s="77"/>
-      <x:c r="L35" s="77"/>
-      <x:c r="M35" s="77"/>
-    </x:row>
-    <x:row r="36" ht="26" customHeight="1">
-      <x:c r="A36" s="76" t="str">
-        <x:v>F37</x:v>
-      </x:c>
-      <x:c r="B36" s="77" t="str">
+      <x:c r="H36" s="88"/>
+      <x:c r="I36" s="88"/>
+      <x:c r="J36" s="87"/>
+      <x:c r="K36" s="87"/>
+      <x:c r="L36" s="87"/>
+      <x:c r="M36" s="87"/>
+    </x:row>
+    <x:row r="37" ht="26" customHeight="1">
+      <x:c r="A37" s="86" t="str">
+        <x:v>F38</x:v>
+      </x:c>
+      <x:c r="B37" s="87" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C36" s="77" t="str">
-        <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
-      </x:c>
-      <x:c r="D36" s="77" t="str">
+      <x:c r="C37" s="87" t="str">
+        <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
+      </x:c>
+      <x:c r="D37" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E36" s="77" t="str">
+      <x:c r="E37" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F36" s="77" t="str">
+      <x:c r="F37" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G36" s="77" t="str">
+      <x:c r="G37" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H36" s="78"/>
-      <x:c r="I36" s="78"/>
-      <x:c r="J36" s="77"/>
-      <x:c r="K36" s="77"/>
-      <x:c r="L36" s="77"/>
-      <x:c r="M36" s="77"/>
-    </x:row>
-    <x:row r="37" ht="26" customHeight="1">
-      <x:c r="A37" s="76" t="str">
-        <x:v>F38</x:v>
-      </x:c>
-      <x:c r="B37" s="77" t="str">
-        <x:v>Step 12 · Quality</x:v>
-      </x:c>
-      <x:c r="C37" s="77" t="str">
-        <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
-      </x:c>
-      <x:c r="D37" s="77" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E37" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F37" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G37" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H37" s="78"/>
-      <x:c r="I37" s="78"/>
-      <x:c r="J37" s="77"/>
-      <x:c r="K37" s="77"/>
-      <x:c r="L37" s="77"/>
-      <x:c r="M37" s="77"/>
+      <x:c r="H37" s="88"/>
+      <x:c r="I37" s="88"/>
+      <x:c r="J37" s="87"/>
+      <x:c r="K37" s="87"/>
+      <x:c r="L37" s="87"/>
+      <x:c r="M37" s="87"/>
     </x:row>
     <x:row r="38" ht="26" customHeight="1">
       <x:c r="A38" s="56"/>
@@ -9502,13 +9734,13 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="51" priority="1">
+    <x:cfRule type="expression" dxfId="69" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="52" priority="2">
+    <x:cfRule type="expression" dxfId="70" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="53" priority="3">
+    <x:cfRule type="expression" dxfId="71" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -9522,7 +9754,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40870228cde24e95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a75a87e331d4e5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9562,7 +9794,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
+        <x:v>2026-10-10: Step 3B / R04 verified. 84 permanent IDs: 17 Done, 17 Pending, 50 Not started. F25 Pending for Step 7 regional tiles. Prior IDs/history retained. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -9577,21 +9809,21 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -9603,7 +9835,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -9648,267 +9880,267 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="73" t="str">
+      <x:c r="A6" s="83" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B6" s="74" t="str">
+      <x:c r="B6" s="84" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C6" s="74" t="str">
+      <x:c r="C6" s="84" t="str">
         <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
-      <x:c r="D6" s="74" t="str">
+      <x:c r="D6" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E6" s="74" t="str">
+      <x:c r="E6" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="74" t="str">
+      <x:c r="F6" s="84" t="str">
         <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
-      <x:c r="G6" s="74" t="str">
+      <x:c r="G6" s="84" t="str">
         <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
       </x:c>
-      <x:c r="H6" s="75" t="d">
+      <x:c r="H6" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="75" t="d">
+      <x:c r="I6" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="74" t="str">
+      <x:c r="J6" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="74" t="str">
+      <x:c r="K6" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="74" t="str">
+      <x:c r="L6" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="74" t="str">
+      <x:c r="M6" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
 2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
 2026-10-09 Step 2: Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="73" t="str">
+      <x:c r="A7" s="83" t="str">
         <x:v>B17</x:v>
       </x:c>
-      <x:c r="B7" s="74" t="str">
+      <x:c r="B7" s="84" t="str">
         <x:v>Decision · Leads</x:v>
       </x:c>
-      <x:c r="C7" s="74" t="str">
+      <x:c r="C7" s="84" t="str">
         <x:v>Approve shared inbox versus listing agent enquiry destination</x:v>
       </x:c>
-      <x:c r="D7" s="74" t="str">
+      <x:c r="D7" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E7" s="74" t="str">
+      <x:c r="E7" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="74" t="str">
+      <x:c r="F7" s="84" t="str">
         <x:v>BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
-      <x:c r="G7" s="74" t="str">
+      <x:c r="G7" s="84" t="str">
         <x:v>Owner: select routing mode and mailbox</x:v>
       </x:c>
-      <x:c r="H7" s="75"/>
-      <x:c r="I7" s="75"/>
-      <x:c r="J7" s="74"/>
-      <x:c r="K7" s="74"/>
-      <x:c r="L7" s="74"/>
-      <x:c r="M7" s="74"/>
+      <x:c r="H7" s="85"/>
+      <x:c r="I7" s="85"/>
+      <x:c r="J7" s="84"/>
+      <x:c r="K7" s="84"/>
+      <x:c r="L7" s="84"/>
+      <x:c r="M7" s="84"/>
     </x:row>
     <x:row r="8" ht="250" customHeight="1">
-      <x:c r="A8" s="73" t="str">
+      <x:c r="A8" s="83" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B8" s="74" t="str">
+      <x:c r="B8" s="84" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C8" s="74" t="str">
+      <x:c r="C8" s="84" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D8" s="74" t="str">
+      <x:c r="D8" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="74" t="str">
+      <x:c r="E8" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="74" t="str">
+      <x:c r="F8" s="84" t="str">
         <x:v>Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending.</x:v>
       </x:c>
-      <x:c r="G8" s="74" t="str">
+      <x:c r="G8" s="84" t="str">
         <x:v>Owner: provide actual contacts/routing; Codex: integrate and review accessible contact actions later.</x:v>
       </x:c>
-      <x:c r="H8" s="75" t="d">
+      <x:c r="H8" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I8" s="75" t="d">
+      <x:c r="I8" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="74" t="str">
+      <x:c r="J8" s="84" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K8" s="74" t="str">
+      <x:c r="K8" s="84" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L8" s="74" t="str">
+      <x:c r="L8" s="84" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M8" s="74" t="str">
+      <x:c r="M8" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #4 unresolved
 2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.
 2026-10-09 foundation: Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="73" t="str">
+      <x:c r="A9" s="83" t="str">
         <x:v>B23</x:v>
       </x:c>
-      <x:c r="B9" s="74" t="str">
+      <x:c r="B9" s="84" t="str">
         <x:v>Decision · Accounts</x:v>
       </x:c>
-      <x:c r="C9" s="74" t="str">
+      <x:c r="C9" s="84" t="str">
         <x:v>Approve LINE only or LINE+Google+email sign-in</x:v>
       </x:c>
-      <x:c r="D9" s="74" t="str">
+      <x:c r="D9" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E9" s="74" t="str">
+      <x:c r="E9" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="74" t="str">
+      <x:c r="F9" s="84" t="str">
         <x:v>BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
-      <x:c r="G9" s="74" t="str">
+      <x:c r="G9" s="84" t="str">
         <x:v>Owner: approve authentication providers</x:v>
       </x:c>
-      <x:c r="H9" s="75"/>
-      <x:c r="I9" s="75"/>
-      <x:c r="J9" s="74"/>
-      <x:c r="K9" s="74"/>
-      <x:c r="L9" s="74"/>
-      <x:c r="M9" s="74"/>
+      <x:c r="H9" s="85"/>
+      <x:c r="I9" s="85"/>
+      <x:c r="J9" s="84"/>
+      <x:c r="K9" s="84"/>
+      <x:c r="L9" s="84"/>
+      <x:c r="M9" s="84"/>
     </x:row>
     <x:row r="10" ht="200" customHeight="1">
-      <x:c r="A10" s="73" t="str">
+      <x:c r="A10" s="83" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B10" s="74" t="str">
+      <x:c r="B10" s="84" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C10" s="74" t="str">
+      <x:c r="C10" s="84" t="str">
         <x:v>Approve THB only versus optional approximate FX display</x:v>
       </x:c>
-      <x:c r="D10" s="74" t="str">
+      <x:c r="D10" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="74" t="str">
+      <x:c r="E10" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="74" t="str">
+      <x:c r="F10" s="84" t="str">
         <x:v>Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
-      <x:c r="G10" s="74" t="str">
+      <x:c r="G10" s="84" t="str">
         <x:v>Codex: implement USD/THB during authorized currency work; confirm rate source.</x:v>
       </x:c>
-      <x:c r="H10" s="75"/>
-      <x:c r="I10" s="75" t="d">
+      <x:c r="H10" s="85"/>
+      <x:c r="I10" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="74" t="str">
+      <x:c r="J10" s="84" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K10" s="74" t="str">
+      <x:c r="K10" s="84" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L10" s="74" t="str">
+      <x:c r="L10" s="84" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M10" s="74" t="str">
+      <x:c r="M10" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #6 unresolved
 2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="200" customHeight="1">
-      <x:c r="A11" s="73" t="str">
+      <x:c r="A11" s="83" t="str">
         <x:v>B29</x:v>
       </x:c>
-      <x:c r="B11" s="74" t="str">
+      <x:c r="B11" s="84" t="str">
         <x:v>Decision · Projects</x:v>
       </x:c>
-      <x:c r="C11" s="74" t="str">
+      <x:c r="C11" s="84" t="str">
         <x:v>Approve public project prices versus enquiry-only price list</x:v>
       </x:c>
-      <x:c r="D11" s="74" t="str">
+      <x:c r="D11" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E11" s="74" t="str">
+      <x:c r="E11" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="74" t="str">
+      <x:c r="F11" s="84" t="str">
         <x:v>Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
-      <x:c r="G11" s="74" t="str">
+      <x:c r="G11" s="84" t="str">
         <x:v>Codex: add per-record price visibility in authorized backend/admin work after admin wireframe approval.</x:v>
       </x:c>
-      <x:c r="H11" s="75"/>
-      <x:c r="I11" s="75" t="d">
+      <x:c r="H11" s="85"/>
+      <x:c r="I11" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="74" t="str">
+      <x:c r="J11" s="84" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K11" s="74" t="str">
+      <x:c r="K11" s="84" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L11" s="74" t="str">
+      <x:c r="L11" s="84" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M11" s="74" t="str">
+      <x:c r="M11" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #7 unresolved
 2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="310" customHeight="1">
-      <x:c r="A12" s="73" t="str">
+      <x:c r="A12" s="83" t="str">
         <x:v>R01</x:v>
       </x:c>
-      <x:c r="B12" s="74" t="str">
+      <x:c r="B12" s="84" t="str">
         <x:v>Step 0 · Preparation</x:v>
       </x:c>
-      <x:c r="C12" s="74" t="str">
+      <x:c r="C12" s="84" t="str">
         <x:v>Inspect project; establish permanent rules, documentation, Git/live mirror and tracker</x:v>
       </x:c>
-      <x:c r="D12" s="74" t="str">
+      <x:c r="D12" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E12" s="74" t="str">
+      <x:c r="E12" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="74" t="str">
+      <x:c r="F12" s="84" t="str">
         <x:v>Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request.</x:v>
       </x:c>
-      <x:c r="G12" s="74" t="str">
+      <x:c r="G12" s="84" t="str">
         <x:v>Codex: close the separate Step 0 utility/reference-review requirements only when authorized; stop before Step 3.</x:v>
       </x:c>
-      <x:c r="H12" s="75" t="d">
+      <x:c r="H12" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="75" t="d">
+      <x:c r="I12" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="74" t="str">
+      <x:c r="J12" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K12" s="74" t="str">
+      <x:c r="K12" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L12" s="74" t="str">
+      <x:c r="L12" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="74" t="str">
+      <x:c r="M12" s="84" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
@@ -9921,584 +10153,584 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="76" t="str">
+      <x:c r="A13" s="86" t="str">
         <x:v>B08</x:v>
       </x:c>
-      <x:c r="B13" s="77" t="str">
+      <x:c r="B13" s="87" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C13" s="77" t="str">
+      <x:c r="C13" s="87" t="str">
         <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
       </x:c>
-      <x:c r="D13" s="77" t="str">
+      <x:c r="D13" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E13" s="77" t="str">
+      <x:c r="E13" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="77" t="str">
+      <x:c r="F13" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G13" s="77" t="str">
+      <x:c r="G13" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H13" s="78"/>
-      <x:c r="I13" s="78"/>
-      <x:c r="J13" s="77"/>
-      <x:c r="K13" s="77"/>
-      <x:c r="L13" s="77"/>
-      <x:c r="M13" s="77"/>
+      <x:c r="H13" s="88"/>
+      <x:c r="I13" s="88"/>
+      <x:c r="J13" s="87"/>
+      <x:c r="K13" s="87"/>
+      <x:c r="L13" s="87"/>
+      <x:c r="M13" s="87"/>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="76" t="str">
+      <x:c r="A14" s="86" t="str">
         <x:v>B10</x:v>
       </x:c>
-      <x:c r="B14" s="77" t="str">
+      <x:c r="B14" s="87" t="str">
         <x:v>Step 4 · Nearby</x:v>
       </x:c>
-      <x:c r="C14" s="77" t="str">
+      <x:c r="C14" s="87" t="str">
         <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
       </x:c>
-      <x:c r="D14" s="77" t="str">
+      <x:c r="D14" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E14" s="77" t="str">
+      <x:c r="E14" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F14" s="77" t="str">
+      <x:c r="F14" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G14" s="77" t="str">
+      <x:c r="G14" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H14" s="78"/>
-      <x:c r="I14" s="78"/>
-      <x:c r="J14" s="77"/>
-      <x:c r="K14" s="77"/>
-      <x:c r="L14" s="77"/>
-      <x:c r="M14" s="77"/>
+      <x:c r="H14" s="88"/>
+      <x:c r="I14" s="88"/>
+      <x:c r="J14" s="87"/>
+      <x:c r="K14" s="87"/>
+      <x:c r="L14" s="87"/>
+      <x:c r="M14" s="87"/>
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="76" t="str">
+      <x:c r="A15" s="86" t="str">
         <x:v>B11</x:v>
       </x:c>
-      <x:c r="B15" s="77" t="str">
+      <x:c r="B15" s="87" t="str">
         <x:v>Step 5 · Media</x:v>
       </x:c>
-      <x:c r="C15" s="77" t="str">
+      <x:c r="C15" s="87" t="str">
         <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
       </x:c>
-      <x:c r="D15" s="77" t="str">
+      <x:c r="D15" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E15" s="77" t="str">
+      <x:c r="E15" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="77" t="str">
+      <x:c r="F15" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G15" s="77" t="str">
+      <x:c r="G15" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H15" s="78"/>
-      <x:c r="I15" s="78"/>
-      <x:c r="J15" s="77"/>
-      <x:c r="K15" s="77"/>
-      <x:c r="L15" s="77"/>
-      <x:c r="M15" s="77"/>
+      <x:c r="H15" s="88"/>
+      <x:c r="I15" s="88"/>
+      <x:c r="J15" s="87"/>
+      <x:c r="K15" s="87"/>
+      <x:c r="L15" s="87"/>
+      <x:c r="M15" s="87"/>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="76" t="str">
+      <x:c r="A16" s="86" t="str">
         <x:v>B12</x:v>
       </x:c>
-      <x:c r="B16" s="77" t="str">
+      <x:c r="B16" s="87" t="str">
         <x:v>Step 5 · Similar</x:v>
       </x:c>
-      <x:c r="C16" s="77" t="str">
+      <x:c r="C16" s="87" t="str">
         <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
       </x:c>
-      <x:c r="D16" s="77" t="str">
+      <x:c r="D16" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E16" s="77" t="str">
+      <x:c r="E16" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="77" t="str">
+      <x:c r="F16" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G16" s="77" t="str">
+      <x:c r="G16" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H16" s="78"/>
-      <x:c r="I16" s="78"/>
-      <x:c r="J16" s="77"/>
-      <x:c r="K16" s="77"/>
-      <x:c r="L16" s="77"/>
-      <x:c r="M16" s="77"/>
+      <x:c r="H16" s="88"/>
+      <x:c r="I16" s="88"/>
+      <x:c r="J16" s="87"/>
+      <x:c r="K16" s="87"/>
+      <x:c r="L16" s="87"/>
+      <x:c r="M16" s="87"/>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="76" t="str">
+      <x:c r="A17" s="86" t="str">
         <x:v>B13</x:v>
       </x:c>
-      <x:c r="B17" s="77" t="str">
+      <x:c r="B17" s="87" t="str">
         <x:v>Step 5 · Metrics</x:v>
       </x:c>
-      <x:c r="C17" s="77" t="str">
+      <x:c r="C17" s="87" t="str">
         <x:v>Comparable pricing/yield gated by verified sample size</x:v>
       </x:c>
-      <x:c r="D17" s="77" t="str">
+      <x:c r="D17" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E17" s="77" t="str">
+      <x:c r="E17" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="77" t="str">
+      <x:c r="F17" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G17" s="77" t="str">
+      <x:c r="G17" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H17" s="78"/>
-      <x:c r="I17" s="78"/>
-      <x:c r="J17" s="77"/>
-      <x:c r="K17" s="77"/>
-      <x:c r="L17" s="77"/>
-      <x:c r="M17" s="77"/>
+      <x:c r="H17" s="88"/>
+      <x:c r="I17" s="88"/>
+      <x:c r="J17" s="87"/>
+      <x:c r="K17" s="87"/>
+      <x:c r="L17" s="87"/>
+      <x:c r="M17" s="87"/>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="76" t="str">
+      <x:c r="A18" s="86" t="str">
         <x:v>B14</x:v>
       </x:c>
-      <x:c r="B18" s="77" t="str">
+      <x:c r="B18" s="87" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C18" s="77" t="str">
+      <x:c r="C18" s="87" t="str">
         <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
       </x:c>
-      <x:c r="D18" s="77" t="str">
+      <x:c r="D18" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E18" s="77" t="str">
+      <x:c r="E18" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F18" s="77" t="str">
+      <x:c r="F18" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G18" s="77" t="str">
+      <x:c r="G18" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H18" s="78"/>
-      <x:c r="I18" s="78"/>
-      <x:c r="J18" s="77"/>
-      <x:c r="K18" s="77"/>
-      <x:c r="L18" s="77"/>
-      <x:c r="M18" s="77"/>
+      <x:c r="H18" s="88"/>
+      <x:c r="I18" s="88"/>
+      <x:c r="J18" s="87"/>
+      <x:c r="K18" s="87"/>
+      <x:c r="L18" s="87"/>
+      <x:c r="M18" s="87"/>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="76" t="str">
+      <x:c r="A19" s="86" t="str">
         <x:v>B15</x:v>
       </x:c>
-      <x:c r="B19" s="77" t="str">
+      <x:c r="B19" s="87" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C19" s="77" t="str">
+      <x:c r="C19" s="87" t="str">
         <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
       </x:c>
-      <x:c r="D19" s="77" t="str">
+      <x:c r="D19" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E19" s="77" t="str">
+      <x:c r="E19" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="77" t="str">
+      <x:c r="F19" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G19" s="77" t="str">
+      <x:c r="G19" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H19" s="78"/>
-      <x:c r="I19" s="78"/>
-      <x:c r="J19" s="77"/>
-      <x:c r="K19" s="77"/>
-      <x:c r="L19" s="77"/>
-      <x:c r="M19" s="77"/>
+      <x:c r="H19" s="88"/>
+      <x:c r="I19" s="88"/>
+      <x:c r="J19" s="87"/>
+      <x:c r="K19" s="87"/>
+      <x:c r="L19" s="87"/>
+      <x:c r="M19" s="87"/>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="76" t="str">
+      <x:c r="A20" s="86" t="str">
         <x:v>B16</x:v>
       </x:c>
-      <x:c r="B20" s="77" t="str">
+      <x:c r="B20" s="87" t="str">
         <x:v>Step 6 · Security</x:v>
       </x:c>
-      <x:c r="C20" s="77" t="str">
+      <x:c r="C20" s="87" t="str">
         <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
       </x:c>
-      <x:c r="D20" s="77" t="str">
+      <x:c r="D20" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E20" s="77" t="str">
+      <x:c r="E20" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="77" t="str">
+      <x:c r="F20" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G20" s="77" t="str">
+      <x:c r="G20" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H20" s="78"/>
-      <x:c r="I20" s="78"/>
-      <x:c r="J20" s="77"/>
-      <x:c r="K20" s="77"/>
-      <x:c r="L20" s="77"/>
-      <x:c r="M20" s="77"/>
+      <x:c r="H20" s="88"/>
+      <x:c r="I20" s="88"/>
+      <x:c r="J20" s="87"/>
+      <x:c r="K20" s="87"/>
+      <x:c r="L20" s="87"/>
+      <x:c r="M20" s="87"/>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="76" t="str">
+      <x:c r="A21" s="86" t="str">
         <x:v>B19</x:v>
       </x:c>
-      <x:c r="B21" s="77" t="str">
+      <x:c r="B21" s="87" t="str">
         <x:v>Step 6 · Chat</x:v>
       </x:c>
-      <x:c r="C21" s="77" t="str">
+      <x:c r="C21" s="87" t="str">
         <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
       </x:c>
-      <x:c r="D21" s="77" t="str">
+      <x:c r="D21" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E21" s="77" t="str">
+      <x:c r="E21" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="77" t="str">
+      <x:c r="F21" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G21" s="77" t="str">
+      <x:c r="G21" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H21" s="78"/>
-      <x:c r="I21" s="78"/>
-      <x:c r="J21" s="77"/>
-      <x:c r="K21" s="77"/>
-      <x:c r="L21" s="77"/>
-      <x:c r="M21" s="77"/>
+      <x:c r="H21" s="88"/>
+      <x:c r="I21" s="88"/>
+      <x:c r="J21" s="87"/>
+      <x:c r="K21" s="87"/>
+      <x:c r="L21" s="87"/>
+      <x:c r="M21" s="87"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="76" t="str">
+      <x:c r="A22" s="86" t="str">
         <x:v>B20</x:v>
       </x:c>
-      <x:c r="B22" s="77" t="str">
+      <x:c r="B22" s="87" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C22" s="77" t="str">
+      <x:c r="C22" s="87" t="str">
         <x:v>Project/unit/plot status logic and validation</x:v>
       </x:c>
-      <x:c r="D22" s="77" t="str">
+      <x:c r="D22" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E22" s="77" t="str">
+      <x:c r="E22" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="77" t="str">
+      <x:c r="F22" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G22" s="77" t="str">
+      <x:c r="G22" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H22" s="78"/>
-      <x:c r="I22" s="78"/>
-      <x:c r="J22" s="77"/>
-      <x:c r="K22" s="77"/>
-      <x:c r="L22" s="77"/>
-      <x:c r="M22" s="77"/>
+      <x:c r="H22" s="88"/>
+      <x:c r="I22" s="88"/>
+      <x:c r="J22" s="87"/>
+      <x:c r="K22" s="87"/>
+      <x:c r="L22" s="87"/>
+      <x:c r="M22" s="87"/>
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
-      <x:c r="A23" s="76" t="str">
+      <x:c r="A23" s="86" t="str">
         <x:v>B21</x:v>
       </x:c>
-      <x:c r="B23" s="77" t="str">
+      <x:c r="B23" s="87" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C23" s="77" t="str">
+      <x:c r="C23" s="87" t="str">
         <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
       </x:c>
-      <x:c r="D23" s="77" t="str">
+      <x:c r="D23" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E23" s="77" t="str">
+      <x:c r="E23" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F23" s="77" t="str">
+      <x:c r="F23" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G23" s="77" t="str">
+      <x:c r="G23" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H23" s="78"/>
-      <x:c r="I23" s="78"/>
-      <x:c r="J23" s="77"/>
-      <x:c r="K23" s="77"/>
-      <x:c r="L23" s="77"/>
-      <x:c r="M23" s="77"/>
+      <x:c r="H23" s="88"/>
+      <x:c r="I23" s="88"/>
+      <x:c r="J23" s="87"/>
+      <x:c r="K23" s="87"/>
+      <x:c r="L23" s="87"/>
+      <x:c r="M23" s="87"/>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="76" t="str">
+      <x:c r="A24" s="86" t="str">
         <x:v>B22</x:v>
       </x:c>
-      <x:c r="B24" s="77" t="str">
+      <x:c r="B24" s="87" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C24" s="77" t="str">
+      <x:c r="C24" s="87" t="str">
         <x:v>Saved listings/searches persistence, new-match calculations</x:v>
       </x:c>
-      <x:c r="D24" s="77" t="str">
+      <x:c r="D24" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E24" s="77" t="str">
+      <x:c r="E24" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="77" t="str">
+      <x:c r="F24" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G24" s="77" t="str">
+      <x:c r="G24" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H24" s="78"/>
-      <x:c r="I24" s="78"/>
-      <x:c r="J24" s="77"/>
-      <x:c r="K24" s="77"/>
-      <x:c r="L24" s="77"/>
-      <x:c r="M24" s="77"/>
+      <x:c r="H24" s="88"/>
+      <x:c r="I24" s="88"/>
+      <x:c r="J24" s="87"/>
+      <x:c r="K24" s="87"/>
+      <x:c r="L24" s="87"/>
+      <x:c r="M24" s="87"/>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="76" t="str">
+      <x:c r="A25" s="86" t="str">
         <x:v>B24</x:v>
       </x:c>
-      <x:c r="B25" s="77" t="str">
+      <x:c r="B25" s="87" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C25" s="77" t="str">
+      <x:c r="C25" s="87" t="str">
         <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
       </x:c>
-      <x:c r="D25" s="77" t="str">
+      <x:c r="D25" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E25" s="77" t="str">
+      <x:c r="E25" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="77" t="str">
+      <x:c r="F25" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G25" s="77" t="str">
+      <x:c r="G25" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H25" s="78"/>
-      <x:c r="I25" s="78"/>
-      <x:c r="J25" s="77"/>
-      <x:c r="K25" s="77"/>
-      <x:c r="L25" s="77"/>
-      <x:c r="M25" s="77"/>
+      <x:c r="H25" s="88"/>
+      <x:c r="I25" s="88"/>
+      <x:c r="J25" s="87"/>
+      <x:c r="K25" s="87"/>
+      <x:c r="L25" s="87"/>
+      <x:c r="M25" s="87"/>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="76" t="str">
+      <x:c r="A26" s="86" t="str">
         <x:v>B25</x:v>
       </x:c>
-      <x:c r="B26" s="77" t="str">
+      <x:c r="B26" s="87" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C26" s="77" t="str">
+      <x:c r="C26" s="87" t="str">
         <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
       </x:c>
-      <x:c r="D26" s="77" t="str">
+      <x:c r="D26" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E26" s="77" t="str">
+      <x:c r="E26" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="77" t="str">
+      <x:c r="F26" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G26" s="77" t="str">
+      <x:c r="G26" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H26" s="78"/>
-      <x:c r="I26" s="78"/>
-      <x:c r="J26" s="77"/>
-      <x:c r="K26" s="77"/>
-      <x:c r="L26" s="77"/>
-      <x:c r="M26" s="77"/>
+      <x:c r="H26" s="88"/>
+      <x:c r="I26" s="88"/>
+      <x:c r="J26" s="87"/>
+      <x:c r="K26" s="87"/>
+      <x:c r="L26" s="87"/>
+      <x:c r="M26" s="87"/>
     </x:row>
     <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="76" t="str">
+      <x:c r="A27" s="86" t="str">
         <x:v>B26</x:v>
       </x:c>
-      <x:c r="B27" s="77" t="str">
+      <x:c r="B27" s="87" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C27" s="77" t="str">
+      <x:c r="C27" s="87" t="str">
         <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
       </x:c>
-      <x:c r="D27" s="77" t="str">
+      <x:c r="D27" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E27" s="77" t="str">
+      <x:c r="E27" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="77" t="str">
+      <x:c r="F27" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G27" s="77" t="str">
+      <x:c r="G27" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H27" s="78"/>
-      <x:c r="I27" s="78"/>
-      <x:c r="J27" s="77"/>
-      <x:c r="K27" s="77"/>
-      <x:c r="L27" s="77"/>
-      <x:c r="M27" s="77"/>
+      <x:c r="H27" s="88"/>
+      <x:c r="I27" s="88"/>
+      <x:c r="J27" s="87"/>
+      <x:c r="K27" s="87"/>
+      <x:c r="L27" s="87"/>
+      <x:c r="M27" s="87"/>
     </x:row>
     <x:row r="28" ht="26" customHeight="1">
-      <x:c r="A28" s="76" t="str">
+      <x:c r="A28" s="86" t="str">
         <x:v>B27</x:v>
       </x:c>
-      <x:c r="B28" s="77" t="str">
+      <x:c r="B28" s="87" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C28" s="77" t="str">
+      <x:c r="C28" s="87" t="str">
         <x:v>Admin user management, audit log and sensitive action authorization</x:v>
       </x:c>
-      <x:c r="D28" s="77" t="str">
+      <x:c r="D28" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E28" s="77" t="str">
+      <x:c r="E28" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="77" t="str">
+      <x:c r="F28" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G28" s="77" t="str">
+      <x:c r="G28" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H28" s="78"/>
-      <x:c r="I28" s="78"/>
-      <x:c r="J28" s="77"/>
-      <x:c r="K28" s="77"/>
-      <x:c r="L28" s="77"/>
-      <x:c r="M28" s="77"/>
+      <x:c r="H28" s="88"/>
+      <x:c r="I28" s="88"/>
+      <x:c r="J28" s="87"/>
+      <x:c r="K28" s="87"/>
+      <x:c r="L28" s="87"/>
+      <x:c r="M28" s="87"/>
     </x:row>
     <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="76" t="str">
+      <x:c r="A29" s="86" t="str">
         <x:v>B30</x:v>
       </x:c>
-      <x:c r="B29" s="77" t="str">
+      <x:c r="B29" s="87" t="str">
         <x:v>Step 12 · Deploy</x:v>
       </x:c>
-      <x:c r="C29" s="77" t="str">
+      <x:c r="C29" s="87" t="str">
         <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
       </x:c>
-      <x:c r="D29" s="77" t="str">
+      <x:c r="D29" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E29" s="77" t="str">
+      <x:c r="E29" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="77" t="str">
+      <x:c r="F29" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="77" t="str">
+      <x:c r="G29" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="78"/>
-      <x:c r="I29" s="78"/>
-      <x:c r="J29" s="77"/>
-      <x:c r="K29" s="77"/>
-      <x:c r="L29" s="77"/>
-      <x:c r="M29" s="77"/>
+      <x:c r="H29" s="88"/>
+      <x:c r="I29" s="88"/>
+      <x:c r="J29" s="87"/>
+      <x:c r="K29" s="87"/>
+      <x:c r="L29" s="87"/>
+      <x:c r="M29" s="87"/>
     </x:row>
     <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="76" t="str">
+      <x:c r="A30" s="86" t="str">
         <x:v>B31</x:v>
       </x:c>
-      <x:c r="B30" s="77" t="str">
+      <x:c r="B30" s="87" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C30" s="77" t="str">
+      <x:c r="C30" s="87" t="str">
         <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
       </x:c>
-      <x:c r="D30" s="77" t="str">
+      <x:c r="D30" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E30" s="77" t="str">
+      <x:c r="E30" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="77" t="str">
+      <x:c r="F30" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="77" t="str">
+      <x:c r="G30" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="78"/>
-      <x:c r="I30" s="78"/>
-      <x:c r="J30" s="77"/>
-      <x:c r="K30" s="77"/>
-      <x:c r="L30" s="77"/>
-      <x:c r="M30" s="77"/>
+      <x:c r="H30" s="88"/>
+      <x:c r="I30" s="88"/>
+      <x:c r="J30" s="87"/>
+      <x:c r="K30" s="87"/>
+      <x:c r="L30" s="87"/>
+      <x:c r="M30" s="87"/>
     </x:row>
     <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="76" t="str">
+      <x:c r="A31" s="86" t="str">
         <x:v>B32</x:v>
       </x:c>
-      <x:c r="B31" s="77" t="str">
+      <x:c r="B31" s="87" t="str">
         <x:v>Step 12 · Security</x:v>
       </x:c>
-      <x:c r="C31" s="77" t="str">
+      <x:c r="C31" s="87" t="str">
         <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
       </x:c>
-      <x:c r="D31" s="77" t="str">
+      <x:c r="D31" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E31" s="77" t="str">
+      <x:c r="E31" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="77" t="str">
+      <x:c r="F31" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="77" t="str">
+      <x:c r="G31" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="78"/>
-      <x:c r="I31" s="78"/>
-      <x:c r="J31" s="77"/>
-      <x:c r="K31" s="77"/>
-      <x:c r="L31" s="77"/>
-      <x:c r="M31" s="77"/>
+      <x:c r="H31" s="88"/>
+      <x:c r="I31" s="88"/>
+      <x:c r="J31" s="87"/>
+      <x:c r="K31" s="87"/>
+      <x:c r="L31" s="87"/>
+      <x:c r="M31" s="87"/>
     </x:row>
     <x:row r="32" ht="26" customHeight="1">
-      <x:c r="A32" s="76" t="str">
+      <x:c r="A32" s="86" t="str">
         <x:v>B33</x:v>
       </x:c>
-      <x:c r="B32" s="77" t="str">
+      <x:c r="B32" s="87" t="str">
         <x:v>Step 7 · Owners</x:v>
       </x:c>
-      <x:c r="C32" s="77" t="str">
+      <x:c r="C32" s="87" t="str">
         <x:v>Home-value and service enquiry data handling</x:v>
       </x:c>
-      <x:c r="D32" s="77" t="str">
+      <x:c r="D32" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E32" s="77" t="str">
+      <x:c r="E32" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="77" t="str">
+      <x:c r="F32" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G32" s="77" t="str">
+      <x:c r="G32" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H32" s="78"/>
-      <x:c r="I32" s="78"/>
-      <x:c r="J32" s="77"/>
-      <x:c r="K32" s="77"/>
-      <x:c r="L32" s="77"/>
-      <x:c r="M32" s="77"/>
+      <x:c r="H32" s="88"/>
+      <x:c r="I32" s="88"/>
+      <x:c r="J32" s="87"/>
+      <x:c r="K32" s="87"/>
+      <x:c r="L32" s="87"/>
+      <x:c r="M32" s="87"/>
     </x:row>
     <x:row r="33" ht="26" customHeight="1">
       <x:c r="A33" s="56"/>
@@ -17526,13 +17758,13 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="54" priority="1">
+    <x:cfRule type="expression" dxfId="72" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="55" priority="2">
+    <x:cfRule type="expression" dxfId="73" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="56" priority="3">
+    <x:cfRule type="expression" dxfId="74" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -17549,7 +17781,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3465b1c52ffa4139"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30284266e3a44820"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17589,7 +17821,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
+        <x:v>2026-10-10: Step 3B / R04 verified. 84 permanent IDs: 17 Done, 17 Pending, 50 Not started. F25 Pending for Step 7 regional tiles. Prior IDs/history retained. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -17604,21 +17836,21 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -17630,7 +17862,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -17675,236 +17907,236 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="76" t="str">
+      <x:c r="A6" s="86" t="str">
         <x:v>E01</x:v>
       </x:c>
-      <x:c r="B6" s="77" t="str">
+      <x:c r="B6" s="87" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C6" s="77" t="str">
+      <x:c r="C6" s="87" t="str">
         <x:v>Enquiry notification with retryable queue/outbox</x:v>
       </x:c>
-      <x:c r="D6" s="77" t="str">
+      <x:c r="D6" s="87" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E6" s="77" t="str">
+      <x:c r="E6" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F6" s="77" t="str">
+      <x:c r="F6" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G6" s="77" t="str">
+      <x:c r="G6" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H6" s="78"/>
-      <x:c r="I6" s="78"/>
-      <x:c r="J6" s="77"/>
-      <x:c r="K6" s="77"/>
-      <x:c r="L6" s="77"/>
-      <x:c r="M6" s="77"/>
+      <x:c r="H6" s="88"/>
+      <x:c r="I6" s="88"/>
+      <x:c r="J6" s="87"/>
+      <x:c r="K6" s="87"/>
+      <x:c r="L6" s="87"/>
+      <x:c r="M6" s="87"/>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="76" t="str">
+      <x:c r="A7" s="86" t="str">
         <x:v>E02</x:v>
       </x:c>
-      <x:c r="B7" s="77" t="str">
+      <x:c r="B7" s="87" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C7" s="77" t="str">
+      <x:c r="C7" s="87" t="str">
         <x:v>Thai and English buyer enquiry acknowledgments</x:v>
       </x:c>
-      <x:c r="D7" s="77" t="str">
+      <x:c r="D7" s="87" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E7" s="77" t="str">
+      <x:c r="E7" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F7" s="77" t="str">
+      <x:c r="F7" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G7" s="77" t="str">
+      <x:c r="G7" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H7" s="78"/>
-      <x:c r="I7" s="78"/>
-      <x:c r="J7" s="77"/>
-      <x:c r="K7" s="77"/>
-      <x:c r="L7" s="77"/>
-      <x:c r="M7" s="77"/>
+      <x:c r="H7" s="88"/>
+      <x:c r="I7" s="88"/>
+      <x:c r="J7" s="87"/>
+      <x:c r="K7" s="87"/>
+      <x:c r="L7" s="87"/>
+      <x:c r="M7" s="87"/>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="76" t="str">
+      <x:c r="A8" s="86" t="str">
         <x:v>E03</x:v>
       </x:c>
-      <x:c r="B8" s="77" t="str">
+      <x:c r="B8" s="87" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C8" s="77" t="str">
+      <x:c r="C8" s="87" t="str">
         <x:v>Project brochure/price list email delivery</x:v>
       </x:c>
-      <x:c r="D8" s="77" t="str">
+      <x:c r="D8" s="87" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E8" s="77" t="str">
+      <x:c r="E8" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F8" s="77" t="str">
+      <x:c r="F8" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G8" s="77" t="str">
+      <x:c r="G8" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H8" s="78"/>
-      <x:c r="I8" s="78"/>
-      <x:c r="J8" s="77"/>
-      <x:c r="K8" s="77"/>
-      <x:c r="L8" s="77"/>
-      <x:c r="M8" s="77"/>
+      <x:c r="H8" s="88"/>
+      <x:c r="I8" s="88"/>
+      <x:c r="J8" s="87"/>
+      <x:c r="K8" s="87"/>
+      <x:c r="L8" s="87"/>
+      <x:c r="M8" s="87"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="76" t="str">
+      <x:c r="A9" s="86" t="str">
         <x:v>E04</x:v>
       </x:c>
-      <x:c r="B9" s="77" t="str">
+      <x:c r="B9" s="87" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C9" s="77" t="str">
+      <x:c r="C9" s="87" t="str">
         <x:v>Site visit request and confirmation notifications</x:v>
       </x:c>
-      <x:c r="D9" s="77" t="str">
+      <x:c r="D9" s="87" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E9" s="77" t="str">
+      <x:c r="E9" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F9" s="77" t="str">
+      <x:c r="F9" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G9" s="77" t="str">
+      <x:c r="G9" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H9" s="78"/>
-      <x:c r="I9" s="78"/>
-      <x:c r="J9" s="77"/>
-      <x:c r="K9" s="77"/>
-      <x:c r="L9" s="77"/>
-      <x:c r="M9" s="77"/>
+      <x:c r="H9" s="88"/>
+      <x:c r="I9" s="88"/>
+      <x:c r="J9" s="87"/>
+      <x:c r="K9" s="87"/>
+      <x:c r="L9" s="87"/>
+      <x:c r="M9" s="87"/>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="76" t="str">
+      <x:c r="A10" s="86" t="str">
         <x:v>E05</x:v>
       </x:c>
-      <x:c r="B10" s="77" t="str">
+      <x:c r="B10" s="87" t="str">
         <x:v>Step 9 · Alerts</x:v>
       </x:c>
-      <x:c r="C10" s="77" t="str">
+      <x:c r="C10" s="87" t="str">
         <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
       </x:c>
-      <x:c r="D10" s="77" t="str">
+      <x:c r="D10" s="87" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E10" s="77" t="str">
+      <x:c r="E10" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F10" s="77" t="str">
+      <x:c r="F10" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G10" s="77" t="str">
+      <x:c r="G10" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H10" s="78"/>
-      <x:c r="I10" s="78"/>
-      <x:c r="J10" s="77"/>
-      <x:c r="K10" s="77"/>
-      <x:c r="L10" s="77"/>
-      <x:c r="M10" s="77"/>
+      <x:c r="H10" s="88"/>
+      <x:c r="I10" s="88"/>
+      <x:c r="J10" s="87"/>
+      <x:c r="K10" s="87"/>
+      <x:c r="L10" s="87"/>
+      <x:c r="M10" s="87"/>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="76" t="str">
+      <x:c r="A11" s="86" t="str">
         <x:v>E06</x:v>
       </x:c>
-      <x:c r="B11" s="77" t="str">
+      <x:c r="B11" s="87" t="str">
         <x:v>Step 10B · Email</x:v>
       </x:c>
-      <x:c r="C11" s="77" t="str">
+      <x:c r="C11" s="87" t="str">
         <x:v>Account verification and recovery messages if email auth approved</x:v>
       </x:c>
-      <x:c r="D11" s="77" t="str">
+      <x:c r="D11" s="87" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E11" s="77" t="str">
+      <x:c r="E11" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F11" s="77" t="str">
+      <x:c r="F11" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G11" s="77" t="str">
+      <x:c r="G11" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H11" s="78"/>
-      <x:c r="I11" s="78"/>
-      <x:c r="J11" s="77"/>
-      <x:c r="K11" s="77"/>
-      <x:c r="L11" s="77"/>
-      <x:c r="M11" s="77"/>
+      <x:c r="H11" s="88"/>
+      <x:c r="I11" s="88"/>
+      <x:c r="J11" s="87"/>
+      <x:c r="K11" s="87"/>
+      <x:c r="L11" s="87"/>
+      <x:c r="M11" s="87"/>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="76" t="str">
+      <x:c r="A12" s="86" t="str">
         <x:v>E07</x:v>
       </x:c>
-      <x:c r="B12" s="77" t="str">
+      <x:c r="B12" s="87" t="str">
         <x:v>Step 11B · Email</x:v>
       </x:c>
-      <x:c r="C12" s="77" t="str">
+      <x:c r="C12" s="87" t="str">
         <x:v>Agent notification/routing administration</x:v>
       </x:c>
-      <x:c r="D12" s="77" t="str">
+      <x:c r="D12" s="87" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E12" s="77" t="str">
+      <x:c r="E12" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F12" s="77" t="str">
+      <x:c r="F12" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G12" s="77" t="str">
+      <x:c r="G12" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H12" s="78"/>
-      <x:c r="I12" s="78"/>
-      <x:c r="J12" s="77"/>
-      <x:c r="K12" s="77"/>
-      <x:c r="L12" s="77"/>
-      <x:c r="M12" s="77"/>
+      <x:c r="H12" s="88"/>
+      <x:c r="I12" s="88"/>
+      <x:c r="J12" s="87"/>
+      <x:c r="K12" s="87"/>
+      <x:c r="L12" s="87"/>
+      <x:c r="M12" s="87"/>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="76" t="str">
+      <x:c r="A13" s="86" t="str">
         <x:v>E08</x:v>
       </x:c>
-      <x:c r="B13" s="77" t="str">
+      <x:c r="B13" s="87" t="str">
         <x:v>Step 7 · Email</x:v>
       </x:c>
-      <x:c r="C13" s="77" t="str">
+      <x:c r="C13" s="87" t="str">
         <x:v>Home valuation and service enquiry replies</x:v>
       </x:c>
-      <x:c r="D13" s="77" t="str">
+      <x:c r="D13" s="87" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E13" s="77" t="str">
+      <x:c r="E13" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="77" t="str">
+      <x:c r="F13" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G13" s="77" t="str">
+      <x:c r="G13" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H13" s="78"/>
-      <x:c r="I13" s="78"/>
-      <x:c r="J13" s="77"/>
-      <x:c r="K13" s="77"/>
-      <x:c r="L13" s="77"/>
-      <x:c r="M13" s="77"/>
+      <x:c r="H13" s="88"/>
+      <x:c r="I13" s="88"/>
+      <x:c r="J13" s="87"/>
+      <x:c r="K13" s="87"/>
+      <x:c r="L13" s="87"/>
+      <x:c r="M13" s="87"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="44"/>
@@ -25217,13 +25449,13 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="57" priority="1">
+    <x:cfRule type="expression" dxfId="75" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="58" priority="2">
+    <x:cfRule type="expression" dxfId="76" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="59" priority="3">
+    <x:cfRule type="expression" dxfId="77" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -25234,7 +25466,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6550d38adfae48ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f983a1bed174c13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25274,7 +25506,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
+        <x:v>2026-10-10: Step 3B / R04 verified. 84 permanent IDs: 17 Done, 17 Pending, 50 Not started. F25 Pending for Step 7 regional tiles. Prior IDs/history retained. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -25289,21 +25521,21 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -25315,7 +25547,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -25360,696 +25592,730 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="79" t="str">
+      <x:c r="A6" s="89" t="str">
         <x:v>B34</x:v>
       </x:c>
-      <x:c r="B6" s="79" t="str">
+      <x:c r="B6" s="89" t="str">
         <x:v>Step 1 · Health</x:v>
       </x:c>
-      <x:c r="C6" s="79" t="str">
+      <x:c r="C6" s="89" t="str">
         <x:v>Basic /api/health endpoint with accurate application and database status</x:v>
       </x:c>
-      <x:c r="D6" s="79" t="str">
+      <x:c r="D6" s="89" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E6" s="79" t="str">
+      <x:c r="E6" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F6" s="79" t="str">
+      <x:c r="F6" s="89" t="str">
         <x:v>Real /api/health now probes the migrated public view rather than an empty database select 1. Actual 200/ready true, stopped-DB 503/unavailable/ready false and recovery to 200 verified.</x:v>
       </x:c>
-      <x:c r="G6" s="79" t="str">
+      <x:c r="G6" s="89" t="str">
         <x:v>Codex: retain truthful readiness and generic errors; start localhost only under owner/test authorization.</x:v>
       </x:c>
-      <x:c r="H6" s="80" t="d">
+      <x:c r="H6" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="80" t="d">
+      <x:c r="I6" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="79" t="str">
+      <x:c r="J6" s="89" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="79" t="str">
+      <x:c r="K6" s="89" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="79" t="str">
+      <x:c r="L6" s="89" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="79" t="str">
+      <x:c r="M6" s="89" t="str">
         <x:v>2026-10-09: Health API planned. No implementation in Step 0.
 2026-10-09 foundation: Real health API implemented: HTTP 200 app ok, database not_configured, ready false before closure. Configured PostgreSQL is probed with Drizzle select 1; failure returns 503. No real database configuration exists. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Real /api/health now probes the migrated public view rather than an empty database select 1. Actual 200/ready true, stopped-DB 503/unavailable/ready false and recovery to 200 verified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="310" customHeight="1">
-      <x:c r="A7" s="79" t="str">
+      <x:c r="A7" s="89" t="str">
         <x:v>B01</x:v>
       </x:c>
-      <x:c r="B7" s="79" t="str">
+      <x:c r="B7" s="89" t="str">
         <x:v>Step 2 · Database</x:v>
       </x:c>
-      <x:c r="C7" s="79" t="str">
+      <x:c r="C7" s="89" t="str">
         <x:v>PostgreSQL/Drizzle schema for listings, projects, agents and users</x:v>
       </x:c>
-      <x:c r="D7" s="79" t="str">
+      <x:c r="D7" s="89" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E7" s="79" t="str">
+      <x:c r="E7" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F7" s="79" t="str">
+      <x:c r="F7" s="89" t="str">
         <x:v>18-table Drizzle schema implemented with bilingual fields, seven property types, sale/rent rules, explicit price visibility and separate non-superuser migration/read-only app roles. Isolated local development/test PostgreSQL configured; no shared service modified.</x:v>
       </x:c>
-      <x:c r="G7" s="79" t="str">
+      <x:c r="G7" s="89" t="str">
         <x:v>Codex: preserve schema/security contracts in later explicitly authorized stages.</x:v>
       </x:c>
-      <x:c r="H7" s="80" t="d">
+      <x:c r="H7" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="80" t="d">
+      <x:c r="I7" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="79" t="str">
+      <x:c r="J7" s="89" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K7" s="79" t="str">
+      <x:c r="K7" s="89" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L7" s="79" t="str">
+      <x:c r="L7" s="89" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="79" t="str">
+      <x:c r="M7" s="89" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: 18-table Drizzle schema implemented with bilingual fields, seven property types, sale/rent rules, explicit price visibility and separate non-superuser migration/read-only app roles. Isolated local development/test PostgreSQL configured; no shared service modified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="310" customHeight="1">
-      <x:c r="A8" s="79" t="str">
+      <x:c r="A8" s="89" t="str">
         <x:v>B02</x:v>
       </x:c>
-      <x:c r="B8" s="79" t="str">
+      <x:c r="B8" s="89" t="str">
         <x:v>Step 2 · Database</x:v>
       </x:c>
-      <x:c r="C8" s="79" t="str">
+      <x:c r="C8" s="89" t="str">
         <x:v>Migrations, foreign keys, constraints and rollback procedure</x:v>
       </x:c>
-      <x:c r="D8" s="79" t="str">
+      <x:c r="D8" s="89" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="79" t="str">
+      <x:c r="E8" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F8" s="79" t="str">
+      <x:c r="F8" s="89" t="str">
         <x:v>Generated foundation and custom relational migrations, journal/snapshots, constraints/FKs/triggers and guarded test-only initial rollback implemented. Real pg_dump/committed rollback/pg_restore/rerun pass. No production migration performed.</x:v>
       </x:c>
-      <x:c r="G8" s="79" t="str">
+      <x:c r="G8" s="89" t="str">
         <x:v>Codex: generate reviewed additive migrations for later changes; production migration requires authorization and verified backup.</x:v>
       </x:c>
-      <x:c r="H8" s="80" t="d">
+      <x:c r="H8" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I8" s="80" t="d">
+      <x:c r="I8" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="79" t="str">
+      <x:c r="J8" s="89" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K8" s="79" t="str">
+      <x:c r="K8" s="89" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L8" s="79" t="str">
+      <x:c r="L8" s="89" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M8" s="79" t="str">
+      <x:c r="M8" s="89" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Generated foundation and custom relational migrations, journal/snapshots, constraints/FKs/triggers and guarded test-only initial rollback implemented. Real pg_dump/committed rollback/pg_restore/rerun pass. No production migration performed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="310" customHeight="1">
-      <x:c r="A9" s="79" t="str">
+      <x:c r="A9" s="89" t="str">
         <x:v>B03</x:v>
       </x:c>
-      <x:c r="B9" s="79" t="str">
+      <x:c r="B9" s="89" t="str">
         <x:v>Step 2 · Demo</x:v>
       </x:c>
-      <x:c r="C9" s="79" t="str">
+      <x:c r="C9" s="89" t="str">
         <x:v>Clearly fictional seed listings, projects and agents</x:v>
       </x:c>
-      <x:c r="D9" s="79" t="str">
+      <x:c r="D9" s="89" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E9" s="79" t="str">
+      <x:c r="E9" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F9" s="79" t="str">
+      <x:c r="F9" s="89" t="str">
         <x:v>Repeatable local-only seed: 14 explicitly fictional listings, seven types/both intents and related demo records. Invalid domains, disabled users/agents, closed enquiries and off alerts. Public projection excludes demo inventory; no real prices/agents advertised.</x:v>
       </x:c>
-      <x:c r="G9" s="79" t="str">
+      <x:c r="G9" s="89" t="str">
         <x:v>Codex: keep demo data labelled and excluded from genuine inventory; seed only named local dev/test databases.</x:v>
       </x:c>
-      <x:c r="H9" s="80" t="d">
+      <x:c r="H9" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I9" s="80" t="d">
+      <x:c r="I9" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J9" s="79" t="str">
+      <x:c r="J9" s="89" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K9" s="79" t="str">
+      <x:c r="K9" s="89" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L9" s="79" t="str">
+      <x:c r="L9" s="89" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M9" s="79" t="str">
+      <x:c r="M9" s="89" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Repeatable local-only seed: 14 explicitly fictional listings, seven types/both intents and related demo records. Invalid domains, disabled users/agents, closed enquiries and off alerts. Public projection excludes demo inventory; no real prices/agents advertised. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="79" t="str">
+      <x:c r="A10" s="89" t="str">
         <x:v>B04</x:v>
       </x:c>
-      <x:c r="B10" s="79" t="str">
+      <x:c r="B10" s="89" t="str">
         <x:v>Step 2 · Search</x:v>
       </x:c>
-      <x:c r="C10" s="79" t="str">
+      <x:c r="C10" s="89" t="str">
         <x:v>Indexes for status, intent, type, price, location and title</x:v>
       </x:c>
-      <x:c r="D10" s="79" t="str">
+      <x:c r="D10" s="89" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="79" t="str">
+      <x:c r="E10" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F10" s="79" t="str">
+      <x:c r="F10" s="89" t="str">
         <x:v>Intent/type/status/price, location/status, bounding coordinates, publication/feed and bilingual simple-text indexes implemented. Catalog and EXPLAIN use checks pass. Tiny-seed plans prove indexes are usable, not production speed.</x:v>
       </x:c>
-      <x:c r="G10" s="79" t="str">
+      <x:c r="G10" s="89" t="str">
         <x:v>Codex: use parameterized typed queries in Step 3; profile against realistic volume during later QA.</x:v>
       </x:c>
-      <x:c r="H10" s="80" t="d">
+      <x:c r="H10" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="80" t="d">
+      <x:c r="I10" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="79" t="str">
+      <x:c r="J10" s="89" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="79" t="str">
+      <x:c r="K10" s="89" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="79" t="str">
+      <x:c r="L10" s="89" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="79" t="str">
+      <x:c r="M10" s="89" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Intent/type/status/price, location/status, bounding coordinates, publication/feed and bilingual simple-text indexes implemented. Catalog and EXPLAIN use checks pass. Tiny-seed plans prove indexes are usable, not production speed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="400" customHeight="1">
-      <x:c r="A11" s="79" t="str">
+      <x:c r="A11" s="89" t="str">
         <x:v>F08</x:v>
       </x:c>
-      <x:c r="B11" s="79" t="str">
+      <x:c r="B11" s="89" t="str">
         <x:v>Step 3 · Cards</x:v>
       </x:c>
-      <x:c r="C11" s="79" t="str">
+      <x:c r="C11" s="89" t="str">
         <x:v>Realtor-style 3:2 listing cards, photo controls, bottom-right save heart, facts/address and Contact agent dialog trigger</x:v>
       </x:c>
-      <x:c r="D11" s="79" t="str">
+      <x:c r="D11" s="89" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E11" s="79" t="str">
+      <x:c r="E11" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F11" s="79" t="str">
+      <x:c r="F11" s="89" t="str">
         <x:v>One V3 Realtor-style card: 3:2 photo, five-photo arrows/dots/native swipe, pill badges, persistent device save heart, type-specific facts, honest THB/gated price and drop, two-line address and accessible contact dialog. No fabricated real photos/agents; submit remains unavailable until Step 6.
-2026-10-10 R03: Owner requested local development samples with a visible Sample badge. NODE_ENV must equal development; explicit flag, loopback Host/SITE_URL and named local DB are also required. Request and query/metadata boundaries ignore samples in production even when MSTAR_DEMO_MODE=1. Public hosts are denied. Existing fictional notice and privacy constraints remain.</x:v>
-      </x:c>
-      <x:c r="G11" s="79" t="str">
+2026-10-10 R03: Owner requested local development samples with a visible Sample badge. NODE_ENV must equal development; explicit flag, loopback Host/SITE_URL and named local DB are also required. Request and query/metadata boundaries ignore samples in production even when MSTAR_DEMO_MODE=1. Public hosts are denied. Existing fictional notice and privacy constraints remain.
+2026-10-10 R04: Owner-approved Step 3B: full-width 3/2/1 results grid, 12-home batches, whole land units, actual transit line, Thai ตัวอย่าง badge and small Airbnb-style home topic rows. Config queries reuse safe search; featured/newest order, 12-card cap, empty-row hiding and shared device hearts. Fictional rows keep fictional titles/locations; production and live-site sample guards stay unchanged.</x:v>
+      </x:c>
+      <x:c r="G11" s="89" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H11" s="80" t="d">
+      <x:c r="H11" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I11" s="80" t="d">
+      <x:c r="I11" s="90" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="79" t="str">
-        <x:v>PASS: all 44 development Chromium checks covered (42 initially passed; two homepage cold-load timeouts passed in a focused 2/2 warm rerun), Thai/English at 390/768/1024/1440; Sample badge on each buy/rent/invest card and no overflow. PASS: eight production browser checks on actual next build/next start with sample flag still 1; no sample cards, notice, DTOs or metadata; query override and public Host cannot enable samples. PASS: five development and six production actual app/PostgreSQL checks prove 16 published fictional rows remain seeded, production counts match genuine inventory, forced internal sample queries/metadata are denied and configured public SITE_URL rejects samples. PASS: 12 development search groups, TypeScript and production build. Servers stopped afterward; no admin/form submission.</x:v>
-      </x:c>
-      <x:c r="K11" s="79" t="str">
-        <x:v>Preceding c7ca2f8 pushed. This fix commit/push is verified at finalization; exact hash in final report. Revert R03 to Pending if a final gate fails.</x:v>
-      </x:c>
-      <x:c r="L11" s="79" t="str">
-        <x:v>80-file Git/live baseline checked before changes. Safe intended source/config/docs/tracker synchronization and final SHA-256 pairs verified at closeout; no secrets/dependencies/build/test state copied.</x:v>
-      </x:c>
-      <x:c r="M11" s="79" t="str">
+      <x:c r="J11" s="89" t="str">
+        <x:v>PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
+      </x:c>
+      <x:c r="K11" s="89" t="str">
+        <x:v>Preceding 830e037 pushed. Current commit/push verified at finalization; exact hash in final report. Revert affected tasks to Pending if a final gate fails.</x:v>
+      </x:c>
+      <x:c r="L11" s="89" t="str">
+        <x:v>82-file live baseline rechecked before sync. Owner reference revisions adopted without rewriting their input hashes; 91 intended Git/live source/config/docs/tracker pairs verified at closeout. Secrets/dependencies/runtime/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M11" s="89" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.
 2026-10-09 Step 3: One V3 Realtor-style card: 3:2 photo, five-photo arrows/dots/native swipe, pill badges, persistent device save heart, type-specific facts, honest THB/gated price and drop, two-line address and accessible contact dialog. No fabricated real photos/agents; submit remains unavailable until Step 6. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
-2026-10-10 R03: local development only; Sample badge on each fictional card. Production hard-denies samples and metadata even with flag=1. 44 development checks covered after two cold-load retries; 8 production browser checks, 5 development/6 production DB visibility checks and 12 search groups pass. See R03 and current test evidence; prior history preserved.</x:v>
+2026-10-10 R03: local development only; Sample badge on each fictional card. Production hard-denies samples and metadata even with flag=1. 44 development checks covered after two cold-load retries; 8 production browser checks, 5 development/6 production DB visibility checks and 12 search groups pass. See R03 and current test evidence; prior history preserved.
+2026-10-10 R04: approved grid/card/home-row correction. 91 development, 18 real-DB fixture and 12 production browser checks covered; build/TypeScript/DB proof pass. See R04/testing.md. Prior history retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="400" customHeight="1">
-      <x:c r="A12" s="79" t="str">
+      <x:c r="A12" s="89" t="str">
         <x:v>F09</x:v>
       </x:c>
-      <x:c r="B12" s="79" t="str">
+      <x:c r="B12" s="89" t="str">
         <x:v>Step 3 · Results</x:v>
       </x:c>
-      <x:c r="C12" s="79" t="str">
+      <x:c r="C12" s="89" t="str">
         <x:v>Responsive /buy, /rent and /invest results layouts</x:v>
       </x:c>
-      <x:c r="D12" s="79" t="str">
+      <x:c r="D12" s="89" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E12" s="79" t="str">
+      <x:c r="E12" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F12" s="79" t="str">
-        <x:v>Server-rendered /th and /en buy/rent/invest routes. Two desktop card columns, one phone column; empty state, readable heading and cumulative Show more homes. Reserved blank desktop map column; no fake map. Property link reaches an explicit unfinished detail route, not an implemented Step 5 page.</x:v>
-      </x:c>
-      <x:c r="G12" s="79" t="str">
+      <x:c r="F12" s="89" t="str">
+        <x:v>Server-rendered /th and /en buy/rent/invest routes. Two desktop card columns, one phone column; empty state, readable heading and cumulative Show more homes. Reserved blank desktop map column; no fake map. Property link reaches an explicit unfinished detail route, not an implemented Step 5 page.
+2026-10-10 R04: Owner-approved Step 3B: full-width 3/2/1 results grid, 12-home batches, whole land units, actual transit line, Thai ตัวอย่าง badge and small Airbnb-style home topic rows. Config queries reuse safe search; featured/newest order, 12-card cap, empty-row hiding and shared device hearts. Fictional rows keep fictional titles/locations; production and live-site sample guards stay unchanged.</x:v>
+      </x:c>
+      <x:c r="G12" s="89" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H12" s="80" t="d">
+      <x:c r="H12" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="80" t="d">
+      <x:c r="I12" s="90" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J12" s="89" t="str">
+        <x:v>PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
+      </x:c>
+      <x:c r="K12" s="89" t="str">
+        <x:v>Preceding 830e037 pushed. Current commit/push verified at finalization; exact hash in final report. Revert affected tasks to Pending if a final gate fails.</x:v>
+      </x:c>
+      <x:c r="L12" s="89" t="str">
+        <x:v>82-file live baseline rechecked before sync. Owner reference revisions adopted without rewriting their input hashes; 91 intended Git/live source/config/docs/tracker pairs verified at closeout. Secrets/dependencies/runtime/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M12" s="89" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 3: Server-rendered /th and /en buy/rent/invest routes. Two desktop card columns, one phone column; empty state, readable heading and cumulative Show more homes. Reserved blank desktop map column; no fake map. Property link reaches an explicit unfinished detail route, not an implemented Step 5 page. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
+2026-10-10 R04: approved grid/card/home-row correction. 91 development, 18 real-DB fixture and 12 production browser checks covered; build/TypeScript/DB proof pass. See R04/testing.md. Prior history retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="400" customHeight="1">
+      <x:c r="A13" s="89" t="str">
+        <x:v>F10</x:v>
+      </x:c>
+      <x:c r="B13" s="89" t="str">
+        <x:v>Step 3 · Filters</x:v>
+      </x:c>
+      <x:c r="C13" s="89" t="str">
+        <x:v>Shared URL filters, active chips, sorting and navigation history</x:v>
+      </x:c>
+      <x:c r="D13" s="89" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E13" s="89" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F13" s="89" t="str">
+        <x:v>Shared validated URL state for homepage/results; active chips, Clear all, sorting and cumulative page state. Applied changes use Next router.push without full reload to preserve meaningful back/forward history; uncommitted popup drafts do not change URLs. Refresh/back/forward tested.
+2026-10-10 R04: Owner-approved Step 3B: full-width 3/2/1 results grid, 12-home batches, whole land units, actual transit line, Thai ตัวอย่าง badge and small Airbnb-style home topic rows. Config queries reuse safe search; featured/newest order, 12-card cap, empty-row hiding and shared device hearts. Fictional rows keep fictional titles/locations; production and live-site sample guards stay unchanged.</x:v>
+      </x:c>
+      <x:c r="G13" s="89" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H13" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="79" t="str">
+      <x:c r="I13" s="90" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J13" s="89" t="str">
+        <x:v>PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
+      </x:c>
+      <x:c r="K13" s="89" t="str">
+        <x:v>Preceding 830e037 pushed. Current commit/push verified at finalization; exact hash in final report. Revert affected tasks to Pending if a final gate fails.</x:v>
+      </x:c>
+      <x:c r="L13" s="89" t="str">
+        <x:v>82-file live baseline rechecked before sync. Owner reference revisions adopted without rewriting their input hashes; 91 intended Git/live source/config/docs/tracker pairs verified at closeout. Secrets/dependencies/runtime/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M13" s="89" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 Step 3: Shared validated URL state for homepage/results; active chips, Clear all, sorting and cumulative page state. Applied changes use Next router.push without full reload to preserve meaningful back/forward history; uncommitted popup drafts do not change URLs. Refresh/back/forward tested. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
+2026-10-10 R04: approved grid/card/home-row correction. 91 development, 18 real-DB fixture and 12 production browser checks covered; build/TypeScript/DB proof pass. See R04/testing.md. Prior history retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="400" customHeight="1">
+      <x:c r="A14" s="89" t="str">
+        <x:v>F11</x:v>
+      </x:c>
+      <x:c r="B14" s="89" t="str">
+        <x:v>Step 3 · Filters</x:v>
+      </x:c>
+      <x:c r="C14" s="89" t="str">
+        <x:v>Desktop popovers for price, beds, type and advanced filters</x:v>
+      </x:c>
+      <x:c r="D14" s="89" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E14" s="89" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F14" s="89" t="str">
+        <x:v>Accessible native-dialog desktop popovers for location, intent, price, beds, property types and advanced/DB-defined typed filters. Actual metadata options and live price count tested; Escape, focus trapping and focus restoration verified.</x:v>
+      </x:c>
+      <x:c r="G14" s="89" t="str">
+        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
+      </x:c>
+      <x:c r="H14" s="90" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I14" s="90" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J14" s="89" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K12" s="79" t="str">
+      <x:c r="K14" s="89" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L12" s="79" t="str">
+      <x:c r="L14" s="89" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="79" t="str">
-        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 Step 3: Server-rendered /th and /en buy/rent/invest routes. Two desktop card columns, one phone column; empty state, readable heading and cumulative Show more homes. Reserved blank desktop map column; no fake map. Property link reaches an explicit unfinished detail route, not an implemented Step 5 page. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="400" customHeight="1">
-      <x:c r="A13" s="79" t="str">
-        <x:v>F10</x:v>
-      </x:c>
-      <x:c r="B13" s="79" t="str">
-        <x:v>Step 3 · Filters</x:v>
-      </x:c>
-      <x:c r="C13" s="79" t="str">
-        <x:v>Shared URL filters, active chips, sorting and navigation history</x:v>
-      </x:c>
-      <x:c r="D13" s="79" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E13" s="79" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="F13" s="79" t="str">
-        <x:v>Shared validated URL state for homepage/results; active chips, Clear all, sorting and cumulative page state. Applied changes use Next router.push without full reload to preserve meaningful back/forward history; uncommitted popup drafts do not change URLs. Refresh/back/forward tested.</x:v>
-      </x:c>
-      <x:c r="G13" s="79" t="str">
-        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
-      </x:c>
-      <x:c r="H13" s="80" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="I13" s="80" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="J13" s="79" t="str">
-        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
-      </x:c>
-      <x:c r="K13" s="79" t="str">
-        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
-      </x:c>
-      <x:c r="L13" s="79" t="str">
-        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
-      </x:c>
-      <x:c r="M13" s="79" t="str">
-        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 Step 3: Shared validated URL state for homepage/results; active chips, Clear all, sorting and cumulative page state. Applied changes use Next router.push without full reload to preserve meaningful back/forward history; uncommitted popup drafts do not change URLs. Refresh/back/forward tested. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="400" customHeight="1">
-      <x:c r="A14" s="79" t="str">
-        <x:v>F11</x:v>
-      </x:c>
-      <x:c r="B14" s="79" t="str">
-        <x:v>Step 3 · Filters</x:v>
-      </x:c>
-      <x:c r="C14" s="79" t="str">
-        <x:v>Desktop popovers for price, beds, type and advanced filters</x:v>
-      </x:c>
-      <x:c r="D14" s="79" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E14" s="79" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="F14" s="79" t="str">
-        <x:v>Accessible native-dialog desktop popovers for location, intent, price, beds, property types and advanced/DB-defined typed filters. Actual metadata options and live price count tested; Escape, focus trapping and focus restoration verified.</x:v>
-      </x:c>
-      <x:c r="G14" s="79" t="str">
-        <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
-      </x:c>
-      <x:c r="H14" s="80" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="I14" s="80" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="J14" s="79" t="str">
-        <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
-      </x:c>
-      <x:c r="K14" s="79" t="str">
-        <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
-      </x:c>
-      <x:c r="L14" s="79" t="str">
-        <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
-      </x:c>
-      <x:c r="M14" s="79" t="str">
+      <x:c r="M14" s="89" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Accessible native-dialog desktop popovers for location, intent, price, beds, property types and advanced/DB-defined typed filters. Actual metadata options and live price count tested; Escape, focus trapping and focus restoration verified. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="400" customHeight="1">
-      <x:c r="A15" s="79" t="str">
+      <x:c r="A15" s="89" t="str">
         <x:v>F12</x:v>
       </x:c>
-      <x:c r="B15" s="79" t="str">
+      <x:c r="B15" s="89" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C15" s="79" t="str">
+      <x:c r="C15" s="89" t="str">
         <x:v>Phone full-screen filter sheet, Apply and Clear</x:v>
       </x:c>
-      <x:c r="D15" s="79" t="str">
+      <x:c r="D15" s="89" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="79" t="str">
+      <x:c r="E15" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F15" s="79" t="str">
+      <x:c r="F15" s="89" t="str">
         <x:v>Phone full-screen filter sheets with Apply/Clear, labels, focus controls and no page overflow. Native Chromium phone input proves card swipe; UI checked at 390/768/1024/1440 in Thai/English.</x:v>
       </x:c>
-      <x:c r="G15" s="79" t="str">
+      <x:c r="G15" s="89" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H15" s="80" t="d">
+      <x:c r="H15" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I15" s="80" t="d">
+      <x:c r="I15" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J15" s="79" t="str">
+      <x:c r="J15" s="89" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K15" s="79" t="str">
+      <x:c r="K15" s="89" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L15" s="79" t="str">
+      <x:c r="L15" s="89" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M15" s="79" t="str">
+      <x:c r="M15" s="89" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Phone full-screen filter sheets with Apply/Clear, labels, focus controls and no page overflow. Native Chromium phone input proves card swipe; UI checked at 390/768/1024/1440 in Thai/English. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="400" customHeight="1">
-      <x:c r="A16" s="79" t="str">
+      <x:c r="A16" s="89" t="str">
         <x:v>F13</x:v>
       </x:c>
-      <x:c r="B16" s="79" t="str">
+      <x:c r="B16" s="89" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C16" s="79" t="str">
+      <x:c r="C16" s="89" t="str">
         <x:v>Database-derived price histogram and live result count</x:v>
       </x:c>
-      <x:c r="D16" s="79" t="str">
+      <x:c r="D16" s="89" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E16" s="79" t="str">
+      <x:c r="E16" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F16" s="79" t="str">
+      <x:c r="F16" s="89" t="str">
         <x:v>Histogram uses actual matching PUBLIC-price rows, excluding only current min/max range. Gated prices are excluded from price predicates, price ordering and histogram. Debounced actual API count and bounded deterministic queries implemented.</x:v>
       </x:c>
-      <x:c r="G16" s="79" t="str">
+      <x:c r="G16" s="89" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H16" s="80" t="d">
+      <x:c r="H16" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I16" s="80" t="d">
+      <x:c r="I16" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J16" s="79" t="str">
+      <x:c r="J16" s="89" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K16" s="79" t="str">
+      <x:c r="K16" s="89" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L16" s="79" t="str">
+      <x:c r="L16" s="89" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M16" s="79" t="str">
+      <x:c r="M16" s="89" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Histogram uses actual matching PUBLIC-price rows, excluding only current min/max range. Gated prices are excluded from price predicates, price ordering and histogram. Debounced actual API count and bounded deterministic queries implemented. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="400" customHeight="1">
-      <x:c r="A17" s="79" t="str">
+      <x:c r="A17" s="89" t="str">
         <x:v>B05</x:v>
       </x:c>
-      <x:c r="B17" s="79" t="str">
+      <x:c r="B17" s="89" t="str">
         <x:v>Step 2 · Filters</x:v>
       </x:c>
-      <x:c r="C17" s="79" t="str">
+      <x:c r="C17" s="89" t="str">
         <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
       </x:c>
-      <x:c r="D17" s="79" t="str">
+      <x:c r="D17" s="89" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E17" s="79" t="str">
+      <x:c r="E17" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F17" s="79" t="str">
+      <x:c r="F17" s="89" t="str">
         <x:v>Existing typed filter definition/option/value tables are consumed safely by results. Only active metadata in the selected genuine/demo partition is exposed. Single/multi/number/boolean kinds, allowed options and property scope validated with parameterized SQL. Production admin CRUD remains Step 11.</x:v>
       </x:c>
-      <x:c r="G17" s="79" t="str">
+      <x:c r="G17" s="89" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H17" s="80" t="d">
+      <x:c r="H17" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I17" s="80" t="d">
+      <x:c r="I17" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J17" s="79" t="str">
+      <x:c r="J17" s="89" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K17" s="79" t="str">
+      <x:c r="K17" s="89" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L17" s="79" t="str">
+      <x:c r="L17" s="89" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M17" s="79" t="str">
+      <x:c r="M17" s="89" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Existing typed filter definition/option/value tables are consumed safely by results. Only active metadata in the selected genuine/demo partition is exposed. Single/multi/number/boolean kinds, allowed options and property scope validated with parameterized SQL. Production admin CRUD remains Step 11. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="400" customHeight="1">
-      <x:c r="A18" s="79" t="str">
+      <x:c r="A18" s="89" t="str">
         <x:v>B06</x:v>
       </x:c>
-      <x:c r="B18" s="79" t="str">
+      <x:c r="B18" s="89" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C18" s="79" t="str">
+      <x:c r="C18" s="89" t="str">
         <x:v>Typed validated listing/search data access and pagination</x:v>
       </x:c>
-      <x:c r="D18" s="79" t="str">
+      <x:c r="D18" s="89" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E18" s="79" t="str">
+      <x:c r="E18" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F18" s="79" t="str">
+      <x:c r="F18" s="89" t="str">
         <x:v>Server-only bounded, parameterized listing queries and GET /api/listings: sale/rent/invest, location hierarchy/station slugs, beds/baths/size/land/year/amenities/project, sorting/pagination. No contacts, exact hidden location or gated prices in result DTOs. Local demo requires explicit flag and named local DB/trusted Host.
-2026-10-10 R03: Owner requested local development samples with a visible Sample badge. NODE_ENV must equal development; explicit flag, loopback Host/SITE_URL and named local DB are also required. Request and query/metadata boundaries ignore samples in production even when MSTAR_DEMO_MODE=1. Public hosts are denied. Existing fictional notice and privacy constraints remain.</x:v>
-      </x:c>
-      <x:c r="G18" s="79" t="str">
+2026-10-10 R03: Owner requested local development samples with a visible Sample badge. NODE_ENV must equal development; explicit flag, loopback Host/SITE_URL and named local DB are also required. Request and query/metadata boundaries ignore samples in production even when MSTAR_DEMO_MODE=1. Public hosts are denied. Existing fictional notice and privacy constraints remain.
+2026-10-10 R04: Owner-approved Step 3B: full-width 3/2/1 results grid, 12-home batches, whole land units, actual transit line, Thai ตัวอย่าง badge and small Airbnb-style home topic rows. Config queries reuse safe search; featured/newest order, 12-card cap, empty-row hiding and shared device hearts. Fictional rows keep fictional titles/locations; production and live-site sample guards stay unchanged.</x:v>
+      </x:c>
+      <x:c r="G18" s="89" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H18" s="80" t="d">
+      <x:c r="H18" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I18" s="80" t="d">
+      <x:c r="I18" s="90" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J18" s="79" t="str">
-        <x:v>PASS: all 44 development Chromium checks covered (42 initially passed; two homepage cold-load timeouts passed in a focused 2/2 warm rerun), Thai/English at 390/768/1024/1440; Sample badge on each buy/rent/invest card and no overflow. PASS: eight production browser checks on actual next build/next start with sample flag still 1; no sample cards, notice, DTOs or metadata; query override and public Host cannot enable samples. PASS: five development and six production actual app/PostgreSQL checks prove 16 published fictional rows remain seeded, production counts match genuine inventory, forced internal sample queries/metadata are denied and configured public SITE_URL rejects samples. PASS: 12 development search groups, TypeScript and production build. Servers stopped afterward; no admin/form submission.</x:v>
-      </x:c>
-      <x:c r="K18" s="79" t="str">
-        <x:v>Preceding c7ca2f8 pushed. This fix commit/push is verified at finalization; exact hash in final report. Revert R03 to Pending if a final gate fails.</x:v>
-      </x:c>
-      <x:c r="L18" s="79" t="str">
-        <x:v>80-file Git/live baseline checked before changes. Safe intended source/config/docs/tracker synchronization and final SHA-256 pairs verified at closeout; no secrets/dependencies/build/test state copied.</x:v>
-      </x:c>
-      <x:c r="M18" s="79" t="str">
+      <x:c r="J18" s="89" t="str">
+        <x:v>PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
+      </x:c>
+      <x:c r="K18" s="89" t="str">
+        <x:v>Preceding 830e037 pushed. Current commit/push verified at finalization; exact hash in final report. Revert affected tasks to Pending if a final gate fails.</x:v>
+      </x:c>
+      <x:c r="L18" s="89" t="str">
+        <x:v>82-file live baseline rechecked before sync. Owner reference revisions adopted without rewriting their input hashes; 91 intended Git/live source/config/docs/tracker pairs verified at closeout. Secrets/dependencies/runtime/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M18" s="89" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Server-only bounded, parameterized listing queries and GET /api/listings: sale/rent/invest, location hierarchy/station slugs, beds/baths/size/land/year/amenities/project, sorting/pagination. No contacts, exact hidden location or gated prices in result DTOs. Local demo requires explicit flag and named local DB/trusted Host. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
-2026-10-10 R03: local development only; Sample badge on each fictional card. Production hard-denies samples and metadata even with flag=1. 44 development checks covered after two cold-load retries; 8 production browser checks, 5 development/6 production DB visibility checks and 12 search groups pass. See R03 and current test evidence; prior history preserved.</x:v>
+2026-10-10 R03: local development only; Sample badge on each fictional card. Production hard-denies samples and metadata even with flag=1. 44 development checks covered after two cold-load retries; 8 production browser checks, 5 development/6 production DB visibility checks and 12 search groups pass. See R03 and current test evidence; prior history preserved.
+2026-10-10 R04: approved grid/card/home-row correction. 91 development, 18 real-DB fixture and 12 production browser checks covered; build/TypeScript/DB proof pass. See R04/testing.md. Prior history retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="400" customHeight="1">
-      <x:c r="A19" s="79" t="str">
+      <x:c r="A19" s="89" t="str">
         <x:v>B07</x:v>
       </x:c>
-      <x:c r="B19" s="79" t="str">
+      <x:c r="B19" s="89" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C19" s="79" t="str">
+      <x:c r="C19" s="89" t="str">
         <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
       </x:c>
-      <x:c r="D19" s="79" t="str">
+      <x:c r="D19" s="89" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E19" s="79" t="str">
+      <x:c r="E19" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F19" s="79" t="str">
+      <x:c r="F19" s="89" t="str">
         <x:v>Validated shared URL parser, actual counts/sort/histogram and DB metadata filters. Additive 0002_station_search_slug migration provides unique non-null station slugs. Real pre-migration development backup, three-migration rerun and isolated dump/rollback/restore regression passed. Demo search seed rerun is idempotent.</x:v>
       </x:c>
-      <x:c r="G19" s="79" t="str">
+      <x:c r="G19" s="89" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H19" s="80" t="d">
+      <x:c r="H19" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I19" s="80" t="d">
+      <x:c r="I19" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J19" s="79" t="str">
+      <x:c r="J19" s="89" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K19" s="79" t="str">
+      <x:c r="K19" s="89" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L19" s="79" t="str">
+      <x:c r="L19" s="89" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M19" s="79" t="str">
+      <x:c r="M19" s="89" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Validated shared URL parser, actual counts/sort/histogram and DB metadata filters. Additive 0002_station_search_slug migration provides unique non-null station slugs. Real pre-migration development backup, three-migration rerun and isolated dump/rollback/restore regression passed. Demo search seed rerun is idempotent. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="400" customHeight="1">
-      <x:c r="A20" s="79" t="str">
+      <x:c r="A20" s="89" t="str">
         <x:v>R02</x:v>
       </x:c>
-      <x:c r="B20" s="79" t="str">
+      <x:c r="B20" s="89" t="str">
         <x:v>Step 3 · Accessibility</x:v>
       </x:c>
-      <x:c r="C20" s="79" t="str">
+      <x:c r="C20" s="89" t="str">
         <x:v>Fix contact autofocus and swipe/keyboard link handling (F01/F08)</x:v>
       </x:c>
-      <x:c r="D20" s="79" t="str">
+      <x:c r="D20" s="89" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="79" t="str">
+      <x:c r="E20" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F20" s="79" t="str">
+      <x:c r="F20" s="89" t="str">
         <x:v>Fix linked to F01/F08: dialog autofocus now occurs after native showModal and preserves the trigger for restoration. Swipe cancels only the immediate synthetic pointer click, allowing subsequent keyboard Enter. Streaming-page keyboard test waits for visible focused links. All affected regressions pass.</x:v>
       </x:c>
-      <x:c r="G20" s="79" t="str">
+      <x:c r="G20" s="89" t="str">
         <x:v>Codex: preserve these tested Step 3 contracts. Stop before Step 4; implement maps, real enquiry submission, homepage carousel and Saved page only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H20" s="80" t="d">
+      <x:c r="H20" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I20" s="80" t="d">
+      <x:c r="I20" s="90" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J20" s="79" t="str">
+      <x:c r="J20" s="89" t="str">
         <x:v>PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K20" s="79" t="str">
+      <x:c r="K20" s="89" t="str">
         <x:v>Preceding Claude handoff commit 9327797 pushed. Step 3 commit/push verified at finalization; exact hash is supplied in final report. Revert affected status to Pending if final push or sync fails.</x:v>
       </x:c>
-      <x:c r="L20" s="79" t="str">
+      <x:c r="L20" s="89" t="str">
         <x:v>59 baseline Git/live hashes matched before work; safe intended source/config/docs/tracker sync and final SHA-256 verification required. Credentials, cluster, backups, dependencies and caches excluded.</x:v>
       </x:c>
-      <x:c r="M20" s="79" t="str">
+      <x:c r="M20" s="89" t="str">
         <x:v>2026-10-09 discovered during Step 3 real browser testing: contact input lacked focus; swipe suppression blocked the next keyboard activation. Linked to F01/F08.
 2026-10-09 Step 3: Fix linked to F01/F08: dialog autofocus now occurs after native showModal and preserves the trigger for restoration. Swipe cancels only the immediate synthetic pointer click, allowing subsequent keyboard Enter. Streaming-page keyboard test waits for visible focused links. All affected regressions pass. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="400" customHeight="1">
-      <x:c r="A21" s="79" t="str">
+      <x:c r="A21" s="89" t="str">
         <x:v>R03</x:v>
       </x:c>
-      <x:c r="B21" s="79" t="str">
+      <x:c r="B21" s="89" t="str">
         <x:v>Step 3 · Sample safety</x:v>
       </x:c>
-      <x:c r="C21" s="79" t="str">
+      <x:c r="C21" s="89" t="str">
         <x:v>Restrict fictional sample preview to local development; label each card Sample (F08/B06)</x:v>
       </x:c>
-      <x:c r="D21" s="79" t="str">
+      <x:c r="D21" s="89" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E21" s="79" t="str">
+      <x:c r="E21" s="89" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F21" s="79" t="str">
+      <x:c r="F21" s="89" t="str">
         <x:v>Owner requested local development samples with a visible Sample badge. NODE_ENV must equal development; explicit flag, loopback Host/SITE_URL and named local DB are also required. Request and query/metadata boundaries ignore samples in production even when MSTAR_DEMO_MODE=1. Public hosts are denied. Existing fictional notice and privacy constraints remain.</x:v>
       </x:c>
-      <x:c r="G21" s="79" t="str">
+      <x:c r="G21" s="89" t="str">
         <x:v>Codex: preserve this deny-by-default policy for every future public listing consumer. Use npm run dev for samples; next start must show genuine stock only. Stop before Step 4.</x:v>
       </x:c>
-      <x:c r="H21" s="80" t="d">
+      <x:c r="H21" s="90" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I21" s="80" t="d">
+      <x:c r="I21" s="90" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J21" s="79" t="str">
+      <x:c r="J21" s="89" t="str">
         <x:v>PASS: all 44 development Chromium checks covered (42 initially passed; two homepage cold-load timeouts passed in a focused 2/2 warm rerun), Thai/English at 390/768/1024/1440; Sample badge on each buy/rent/invest card and no overflow. PASS: eight production browser checks on actual next build/next start with sample flag still 1; no sample cards, notice, DTOs or metadata; query override and public Host cannot enable samples. PASS: five development and six production actual app/PostgreSQL checks prove 16 published fictional rows remain seeded, production counts match genuine inventory, forced internal sample queries/metadata are denied and configured public SITE_URL rejects samples. PASS: 12 development search groups, TypeScript and production build. Servers stopped afterward; no admin/form submission.</x:v>
       </x:c>
-      <x:c r="K21" s="79" t="str">
+      <x:c r="K21" s="89" t="str">
         <x:v>Preceding c7ca2f8 pushed. This fix commit/push is verified at finalization; exact hash in final report. Revert R03 to Pending if a final gate fails.</x:v>
       </x:c>
-      <x:c r="L21" s="79" t="str">
+      <x:c r="L21" s="89" t="str">
         <x:v>80-file Git/live baseline checked before changes. Safe intended source/config/docs/tracker synchronization and final SHA-256 pairs verified at closeout; no secrets/dependencies/build/test state copied.</x:v>
       </x:c>
-      <x:c r="M21" s="79" t="str">
+      <x:c r="M21" s="89" t="str">
         <x:v>2026-10-10 R03 created from owner clarification: prior preview lacked a NODE_ENV guard and could appear under next start. Linked F08/B06. Owner requested local development samples with a visible Sample badge. NODE_ENV must equal development; explicit flag, loopback Host/SITE_URL and named local DB are also required. Request and query/metadata boundaries ignore samples in production even when MSTAR_DEMO_MODE=1. Public hosts are denied. Existing fictional notice and privacy constraints remain. PASS: all 44 development Chromium checks covered (42 initially passed; two homepage cold-load timeouts passed in a focused 2/2 warm rerun), Thai/English at 390/768/1024/1440; Sample badge on each buy/rent/invest card and no overflow. PASS: eight production browser checks on actual next build/next start with sample flag still 1; no sample cards, notice, DTOs or metadata; query override and public Host cannot enable samples. PASS: five development and six production actual app/PostgreSQL checks prove 16 published fictional rows remain seeded, production counts match genuine inventory, forced internal sample queries/metadata are denied and configured public SITE_URL rejects samples. PASS: 12 development search groups, TypeScript and production build. Servers stopped afterward; no admin/form submission.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="44"/>
-      <x:c r="B22" s="44"/>
-      <x:c r="C22" s="44"/>
-      <x:c r="D22" s="44"/>
-      <x:c r="E22" s="44"/>
-      <x:c r="F22" s="44"/>
-      <x:c r="G22" s="44"/>
-      <x:c r="H22" s="45"/>
-      <x:c r="I22" s="45"/>
-      <x:c r="J22" s="44"/>
-      <x:c r="K22" s="44"/>
-      <x:c r="L22" s="44"/>
-      <x:c r="M22" s="44"/>
+    <x:row r="22" ht="400" customHeight="1">
+      <x:c r="A22" s="89" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="B22" s="89" t="str">
+        <x:v>Step 3B</x:v>
+      </x:c>
+      <x:c r="C22" s="89" t="str">
+        <x:v>Full-width results, card corrections and small home topic rows (F08/F09/F10/B06/F25)</x:v>
+      </x:c>
+      <x:c r="D22" s="89" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E22" s="89" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F22" s="89" t="str">
+        <x:v>Owner-approved Step 3B: full-width 3/2/1 results grid, 12-home batches, whole land units, actual transit line, Thai ตัวอย่าง badge and small Airbnb-style home topic rows. Config queries reuse safe search; featured/newest order, 12-card cap, empty-row hiding and shared device hearts. Fictional rows keep fictional titles/locations; production and live-site sample guards stay unchanged.</x:v>
+      </x:c>
+      <x:c r="G22" s="89" t="str">
+        <x:v>Codex: stop before Step 4. Keep sample and price/location protections; wait for the next authorized stage.</x:v>
+      </x:c>
+      <x:c r="H22" s="90" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I22" s="90" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J22" s="89" t="str">
+        <x:v>PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
+      </x:c>
+      <x:c r="K22" s="89" t="str">
+        <x:v>Preceding 830e037 pushed. Current commit/push verified at finalization; exact hash in final report. Revert affected tasks to Pending if a final gate fails.</x:v>
+      </x:c>
+      <x:c r="L22" s="89" t="str">
+        <x:v>82-file live baseline rechecked before sync. Owner reference revisions adopted without rewriting their input hashes; 91 intended Git/live source/config/docs/tracker pairs verified at closeout. Secrets/dependencies/runtime/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M22" s="89" t="str">
+        <x:v>2026-10-10 R04 created for the owner-approved Step 3B change. Linked F08/F09/F10/B06/F25. Implemented grid/card/home-row scope only. Initial new browser checks needed streamed-content visibility/focus waits; final checks pass. 91 development checks covered, 18 fixture checks and 12 production checks pass; real PostgreSQL ranking/pagination/cleanup and sample denial verified. No permanent seed/schema changes. Original histories are retained. Stop before Step 4.</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="44"/>
@@ -33227,24 +33493,24 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="60" priority="1">
+    <x:cfRule type="expression" dxfId="78" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="61" priority="2">
+    <x:cfRule type="expression" dxfId="79" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="62" priority="3">
+    <x:cfRule type="expression" dxfId="80" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E21">
+    <x:dataValidation type="list" sqref="E6:E22">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab3d923ae9004ec6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47bc810102a34663"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33284,7 +33550,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
+        <x:v>2026-10-10: Step 3B / R04 verified. 84 permanent IDs: 17 Done, 17 Pending, 50 Not started. F25 Pending for Step 7 regional tiles. Prior IDs/history retained. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -33299,21 +33565,21 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -33325,7 +33591,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -33370,43 +33636,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="310" customHeight="1">
-      <x:c r="A6" s="73" t="str">
+      <x:c r="A6" s="83" t="str">
         <x:v>F02</x:v>
       </x:c>
-      <x:c r="B6" s="74" t="str">
+      <x:c r="B6" s="84" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="74" t="str">
+      <x:c r="C6" s="84" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent</x:v>
       </x:c>
-      <x:c r="D6" s="74" t="str">
+      <x:c r="D6" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="74" t="str">
+      <x:c r="E6" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="74" t="str">
+      <x:c r="F6" s="84" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G6" s="74" t="str">
+      <x:c r="G6" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H6" s="75" t="d">
+      <x:c r="H6" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="75" t="d">
+      <x:c r="I6" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="74" t="str">
+      <x:c r="J6" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="74" t="str">
+      <x:c r="K6" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L6" s="74" t="str">
+      <x:c r="L6" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M6" s="74" t="str">
+      <x:c r="M6" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
 2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.
 2026-10-09 foundation: Approved gold and all section 2 colour tokens implemented and checked in eight shell tests. Overall runtime gates remain pending. Owner requested localhost closure; do not reopen automatically.
@@ -33415,368 +33681,368 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="250" customHeight="1">
-      <x:c r="A7" s="73" t="str">
+      <x:c r="A7" s="83" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B7" s="74" t="str">
+      <x:c r="B7" s="84" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C7" s="74" t="str">
+      <x:c r="C7" s="84" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D7" s="74" t="str">
+      <x:c r="D7" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="74" t="str">
+      <x:c r="E7" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="74" t="str">
+      <x:c r="F7" s="84" t="str">
         <x:v>Approved temporary crest extracted and implemented. Owner will provide final header logo later.</x:v>
       </x:c>
-      <x:c r="G7" s="74" t="str">
+      <x:c r="G7" s="84" t="str">
         <x:v>Owner: supply final asset/version later; Codex: replace only approved logo.</x:v>
       </x:c>
-      <x:c r="H7" s="75" t="d">
+      <x:c r="H7" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="75" t="d">
+      <x:c r="I7" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="74" t="str">
+      <x:c r="J7" s="84" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K7" s="74" t="str">
+      <x:c r="K7" s="84" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L7" s="74" t="str">
+      <x:c r="L7" s="84" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M7" s="74" t="str">
+      <x:c r="M7" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
 2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.
 2026-10-09 foundation: Approved temporary crest extracted and implemented. Owner will provide final header logo later. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="73" t="str">
+      <x:c r="A8" s="83" t="str">
         <x:v>F32</x:v>
       </x:c>
-      <x:c r="B8" s="74" t="str">
+      <x:c r="B8" s="84" t="str">
         <x:v>Step 10A · Wireframe</x:v>
       </x:c>
-      <x:c r="C8" s="74" t="str">
+      <x:c r="C8" s="84" t="str">
         <x:v>Owner-approved login/register/account wireframe before coding</x:v>
       </x:c>
-      <x:c r="D8" s="74" t="str">
+      <x:c r="D8" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="74" t="str">
+      <x:c r="E8" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="74" t="str">
+      <x:c r="F8" s="84" t="str">
         <x:v>Admin/account screens are not part of approved V3 visuals</x:v>
       </x:c>
-      <x:c r="G8" s="74" t="str">
+      <x:c r="G8" s="84" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H8" s="75"/>
-      <x:c r="I8" s="75"/>
-      <x:c r="J8" s="74"/>
-      <x:c r="K8" s="74"/>
-      <x:c r="L8" s="74"/>
-      <x:c r="M8" s="74"/>
+      <x:c r="H8" s="85"/>
+      <x:c r="I8" s="85"/>
+      <x:c r="J8" s="84"/>
+      <x:c r="K8" s="84"/>
+      <x:c r="L8" s="84"/>
+      <x:c r="M8" s="84"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="73" t="str">
+      <x:c r="A9" s="83" t="str">
         <x:v>F34</x:v>
       </x:c>
-      <x:c r="B9" s="74" t="str">
+      <x:c r="B9" s="84" t="str">
         <x:v>Step 11A · Wireframe</x:v>
       </x:c>
-      <x:c r="C9" s="74" t="str">
+      <x:c r="C9" s="84" t="str">
         <x:v>Owner-approved responsive admin dashboard wireframe</x:v>
       </x:c>
-      <x:c r="D9" s="74" t="str">
+      <x:c r="D9" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="74" t="str">
+      <x:c r="E9" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="74" t="str">
+      <x:c r="F9" s="84" t="str">
         <x:v>Admin UI not included in V3; design approval required</x:v>
       </x:c>
-      <x:c r="G9" s="74" t="str">
+      <x:c r="G9" s="84" t="str">
         <x:v>Codex: wireframe, owner: review and approve</x:v>
       </x:c>
-      <x:c r="H9" s="75"/>
-      <x:c r="I9" s="75"/>
-      <x:c r="J9" s="74"/>
-      <x:c r="K9" s="74"/>
-      <x:c r="L9" s="74"/>
-      <x:c r="M9" s="74"/>
+      <x:c r="H9" s="85"/>
+      <x:c r="I9" s="85"/>
+      <x:c r="J9" s="84"/>
+      <x:c r="K9" s="84"/>
+      <x:c r="L9" s="84"/>
+      <x:c r="M9" s="84"/>
     </x:row>
     <x:row r="10" ht="310" customHeight="1">
-      <x:c r="A10" s="73" t="str">
+      <x:c r="A10" s="83" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B10" s="74" t="str">
+      <x:c r="B10" s="84" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C10" s="74" t="str">
+      <x:c r="C10" s="84" t="str">
         <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
-      <x:c r="D10" s="74" t="str">
+      <x:c r="D10" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="74" t="str">
+      <x:c r="E10" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="74" t="str">
+      <x:c r="F10" s="84" t="str">
         <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
-      <x:c r="G10" s="74" t="str">
+      <x:c r="G10" s="84" t="str">
         <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
       </x:c>
-      <x:c r="H10" s="75" t="d">
+      <x:c r="H10" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="75" t="d">
+      <x:c r="I10" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="74" t="str">
+      <x:c r="J10" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="74" t="str">
+      <x:c r="K10" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L10" s="74" t="str">
+      <x:c r="L10" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M10" s="74" t="str">
+      <x:c r="M10" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
 2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
 2026-10-09 Step 2: Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="73" t="str">
+      <x:c r="A11" s="83" t="str">
         <x:v>B17</x:v>
       </x:c>
-      <x:c r="B11" s="74" t="str">
+      <x:c r="B11" s="84" t="str">
         <x:v>Decision · Leads</x:v>
       </x:c>
-      <x:c r="C11" s="74" t="str">
+      <x:c r="C11" s="84" t="str">
         <x:v>Approve shared inbox versus listing agent enquiry destination</x:v>
       </x:c>
-      <x:c r="D11" s="74" t="str">
+      <x:c r="D11" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E11" s="74" t="str">
+      <x:c r="E11" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="74" t="str">
+      <x:c r="F11" s="84" t="str">
         <x:v>BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
-      <x:c r="G11" s="74" t="str">
+      <x:c r="G11" s="84" t="str">
         <x:v>Owner: select routing mode and mailbox</x:v>
       </x:c>
-      <x:c r="H11" s="75"/>
-      <x:c r="I11" s="75"/>
-      <x:c r="J11" s="74"/>
-      <x:c r="K11" s="74"/>
-      <x:c r="L11" s="74"/>
-      <x:c r="M11" s="74"/>
+      <x:c r="H11" s="85"/>
+      <x:c r="I11" s="85"/>
+      <x:c r="J11" s="84"/>
+      <x:c r="K11" s="84"/>
+      <x:c r="L11" s="84"/>
+      <x:c r="M11" s="84"/>
     </x:row>
     <x:row r="12" ht="250" customHeight="1">
-      <x:c r="A12" s="73" t="str">
+      <x:c r="A12" s="83" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B12" s="74" t="str">
+      <x:c r="B12" s="84" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C12" s="74" t="str">
+      <x:c r="C12" s="84" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D12" s="74" t="str">
+      <x:c r="D12" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E12" s="74" t="str">
+      <x:c r="E12" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="74" t="str">
+      <x:c r="F12" s="84" t="str">
         <x:v>Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending.</x:v>
       </x:c>
-      <x:c r="G12" s="74" t="str">
+      <x:c r="G12" s="84" t="str">
         <x:v>Owner: provide actual contacts/routing; Codex: integrate and review accessible contact actions later.</x:v>
       </x:c>
-      <x:c r="H12" s="75" t="d">
+      <x:c r="H12" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="75" t="d">
+      <x:c r="I12" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="74" t="str">
+      <x:c r="J12" s="84" t="str">
         <x:v>PASS: final production build and TypeScript. Before closure: 12/16 Playwright tests (8 shell + 4 API/routing) at 390/768/1024/1440; 4 preference/search failures. Origin/phone fixes compile, browser retest pending. PostgreSQL not configured. Port 3000 closed on owner request.</x:v>
       </x:c>
-      <x:c r="K12" s="74" t="str">
+      <x:c r="K12" s="84" t="str">
         <x:v>Preceding owner-decisions commit 3f56908 pushed. Foundation commit/push verified at finalization; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L12" s="74" t="str">
+      <x:c r="L12" s="84" t="str">
         <x:v>Baseline existing Git/live hashes matched. Intended foundation/docs/tracker safely synchronized and hash-checked at finalization; secrets/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M12" s="74" t="str">
+      <x:c r="M12" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #4 unresolved
 2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.
 2026-10-09 foundation: Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending. Owner requested localhost closure; do not reopen automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="73" t="str">
+      <x:c r="A13" s="83" t="str">
         <x:v>B23</x:v>
       </x:c>
-      <x:c r="B13" s="74" t="str">
+      <x:c r="B13" s="84" t="str">
         <x:v>Decision · Accounts</x:v>
       </x:c>
-      <x:c r="C13" s="74" t="str">
+      <x:c r="C13" s="84" t="str">
         <x:v>Approve LINE only or LINE+Google+email sign-in</x:v>
       </x:c>
-      <x:c r="D13" s="74" t="str">
+      <x:c r="D13" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E13" s="74" t="str">
+      <x:c r="E13" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F13" s="74" t="str">
+      <x:c r="F13" s="84" t="str">
         <x:v>BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
-      <x:c r="G13" s="74" t="str">
+      <x:c r="G13" s="84" t="str">
         <x:v>Owner: approve authentication providers</x:v>
       </x:c>
-      <x:c r="H13" s="75"/>
-      <x:c r="I13" s="75"/>
-      <x:c r="J13" s="74"/>
-      <x:c r="K13" s="74"/>
-      <x:c r="L13" s="74"/>
-      <x:c r="M13" s="74"/>
+      <x:c r="H13" s="85"/>
+      <x:c r="I13" s="85"/>
+      <x:c r="J13" s="84"/>
+      <x:c r="K13" s="84"/>
+      <x:c r="L13" s="84"/>
+      <x:c r="M13" s="84"/>
     </x:row>
     <x:row r="14" ht="200" customHeight="1">
-      <x:c r="A14" s="73" t="str">
+      <x:c r="A14" s="83" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B14" s="74" t="str">
+      <x:c r="B14" s="84" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C14" s="74" t="str">
+      <x:c r="C14" s="84" t="str">
         <x:v>Approve THB only versus optional approximate FX display</x:v>
       </x:c>
-      <x:c r="D14" s="74" t="str">
+      <x:c r="D14" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E14" s="74" t="str">
+      <x:c r="E14" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="74" t="str">
+      <x:c r="F14" s="84" t="str">
         <x:v>Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
-      <x:c r="G14" s="74" t="str">
+      <x:c r="G14" s="84" t="str">
         <x:v>Codex: implement USD/THB during authorized currency work; confirm rate source.</x:v>
       </x:c>
-      <x:c r="H14" s="75"/>
-      <x:c r="I14" s="75" t="d">
+      <x:c r="H14" s="85"/>
+      <x:c r="I14" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="74" t="str">
+      <x:c r="J14" s="84" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K14" s="74" t="str">
+      <x:c r="K14" s="84" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L14" s="74" t="str">
+      <x:c r="L14" s="84" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M14" s="74" t="str">
+      <x:c r="M14" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #6 unresolved
 2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="200" customHeight="1">
-      <x:c r="A15" s="73" t="str">
+      <x:c r="A15" s="83" t="str">
         <x:v>B29</x:v>
       </x:c>
-      <x:c r="B15" s="74" t="str">
+      <x:c r="B15" s="84" t="str">
         <x:v>Decision · Projects</x:v>
       </x:c>
-      <x:c r="C15" s="74" t="str">
+      <x:c r="C15" s="84" t="str">
         <x:v>Approve public project prices versus enquiry-only price list</x:v>
       </x:c>
-      <x:c r="D15" s="74" t="str">
+      <x:c r="D15" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E15" s="74" t="str">
+      <x:c r="E15" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F15" s="74" t="str">
+      <x:c r="F15" s="84" t="str">
         <x:v>Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
-      <x:c r="G15" s="74" t="str">
+      <x:c r="G15" s="84" t="str">
         <x:v>Codex: add per-record price visibility in authorized backend/admin work after admin wireframe approval.</x:v>
       </x:c>
-      <x:c r="H15" s="75"/>
-      <x:c r="I15" s="75" t="d">
+      <x:c r="H15" s="85"/>
+      <x:c r="I15" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J15" s="74" t="str">
+      <x:c r="J15" s="84" t="str">
         <x:v>Documentation-only update. Tracker/source-hash/mirror checks performed. No UI/backend code changed. Real-app/DB tests not run; components absent.</x:v>
       </x:c>
-      <x:c r="K15" s="74" t="str">
+      <x:c r="K15" s="84" t="str">
         <x:v>Preceding verification commit c600068 pushed. Decision update will be committed and verified; final report identifies its hash.</x:v>
       </x:c>
-      <x:c r="L15" s="74" t="str">
+      <x:c r="L15" s="84" t="str">
         <x:v>Git/live matched before update. Changed documentation and canonical workbook mirrored only after divergence checks; final SHA-256 comparison required.</x:v>
       </x:c>
-      <x:c r="M15" s="74" t="str">
+      <x:c r="M15" s="84" t="str">
         <x:v>Original planning evidence: BUILD-SPEC §12 #7 unresolved
 2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="310" customHeight="1">
-      <x:c r="A16" s="74" t="str">
+      <x:c r="A16" s="84" t="str">
         <x:v>R01</x:v>
       </x:c>
-      <x:c r="B16" s="74" t="str">
+      <x:c r="B16" s="84" t="str">
         <x:v>Step 0 · Preparation</x:v>
       </x:c>
-      <x:c r="C16" s="74" t="str">
+      <x:c r="C16" s="84" t="str">
         <x:v>Inspect project; establish permanent rules, documentation, Git/live mirror and tracker</x:v>
       </x:c>
-      <x:c r="D16" s="74" t="str">
+      <x:c r="D16" s="84" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E16" s="74" t="str">
+      <x:c r="E16" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F16" s="74" t="str">
+      <x:c r="F16" s="84" t="str">
         <x:v>Step 2 schema/seed/runtime tests pass. Preparation closeout remains separate: V5 Step 0 tracker-update utility is not in the project and original local prototype rendering is browser-policy blocked. No duplicate IDs or source changes. Servers stop under latest request.</x:v>
       </x:c>
-      <x:c r="G16" s="74" t="str">
+      <x:c r="G16" s="84" t="str">
         <x:v>Codex: close the separate Step 0 utility/reference-review requirements only when authorized; stop before Step 3.</x:v>
       </x:c>
-      <x:c r="H16" s="75" t="d">
+      <x:c r="H16" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I16" s="75" t="d">
+      <x:c r="I16" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J16" s="74" t="str">
+      <x:c r="J16" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K16" s="74" t="str">
+      <x:c r="K16" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L16" s="74" t="str">
+      <x:c r="L16" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M16" s="74" t="str">
+      <x:c r="M16" s="84" t="str">
         <x:v>2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
 2026-10-09 owner update: Owner choices documented and tracker updated. Foundation remains unbuilt; no app, PostgreSQL configuration or verified localhost URLs. Runtime gates remain pending.
@@ -33789,43 +34055,43 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="310" customHeight="1">
-      <x:c r="A17" s="74" t="str">
+      <x:c r="A17" s="84" t="str">
         <x:v>F01</x:v>
       </x:c>
-      <x:c r="B17" s="74" t="str">
+      <x:c r="B17" s="84" t="str">
         <x:v>Step 1 · Design</x:v>
       </x:c>
-      <x:c r="C17" s="74" t="str">
+      <x:c r="C17" s="84" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives</x:v>
       </x:c>
-      <x:c r="D17" s="74" t="str">
+      <x:c r="D17" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="74" t="str">
+      <x:c r="E17" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F17" s="74" t="str">
+      <x:c r="F17" s="84" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G17" s="74" t="str">
+      <x:c r="G17" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H17" s="75" t="d">
+      <x:c r="H17" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I17" s="75" t="d">
+      <x:c r="I17" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J17" s="74" t="str">
+      <x:c r="J17" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K17" s="74" t="str">
+      <x:c r="K17" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L17" s="74" t="str">
+      <x:c r="L17" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M17" s="74" t="str">
+      <x:c r="M17" s="84" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33833,43 +34099,43 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="310" customHeight="1">
-      <x:c r="A18" s="74" t="str">
+      <x:c r="A18" s="84" t="str">
         <x:v>F04</x:v>
       </x:c>
-      <x:c r="B18" s="74" t="str">
+      <x:c r="B18" s="84" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C18" s="74" t="str">
+      <x:c r="C18" s="84" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in</x:v>
       </x:c>
-      <x:c r="D18" s="74" t="str">
+      <x:c r="D18" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="74" t="str">
+      <x:c r="E18" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F18" s="74" t="str">
+      <x:c r="F18" s="84" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G18" s="74" t="str">
+      <x:c r="G18" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H18" s="75" t="d">
+      <x:c r="H18" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I18" s="75" t="d">
+      <x:c r="I18" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J18" s="74" t="str">
+      <x:c r="J18" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K18" s="74" t="str">
+      <x:c r="K18" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L18" s="74" t="str">
+      <x:c r="L18" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M18" s="74" t="str">
+      <x:c r="M18" s="84" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33877,43 +34143,43 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="310" customHeight="1">
-      <x:c r="A19" s="74" t="str">
+      <x:c r="A19" s="84" t="str">
         <x:v>F05</x:v>
       </x:c>
-      <x:c r="B19" s="74" t="str">
+      <x:c r="B19" s="84" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C19" s="74" t="str">
+      <x:c r="C19" s="84" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints</x:v>
       </x:c>
-      <x:c r="D19" s="74" t="str">
+      <x:c r="D19" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="74" t="str">
+      <x:c r="E19" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F19" s="74" t="str">
+      <x:c r="F19" s="84" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G19" s="74" t="str">
+      <x:c r="G19" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H19" s="75" t="d">
+      <x:c r="H19" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I19" s="75" t="d">
+      <x:c r="I19" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J19" s="74" t="str">
+      <x:c r="J19" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K19" s="74" t="str">
+      <x:c r="K19" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L19" s="74" t="str">
+      <x:c r="L19" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M19" s="74" t="str">
+      <x:c r="M19" s="84" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33921,43 +34187,43 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="310" customHeight="1">
-      <x:c r="A20" s="74" t="str">
+      <x:c r="A20" s="84" t="str">
         <x:v>F06</x:v>
       </x:c>
-      <x:c r="B20" s="74" t="str">
+      <x:c r="B20" s="84" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C20" s="74" t="str">
+      <x:c r="C20" s="84" t="str">
         <x:v>Light footer, company links, contact and PDPA link</x:v>
       </x:c>
-      <x:c r="D20" s="74" t="str">
+      <x:c r="D20" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="74" t="str">
+      <x:c r="E20" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F20" s="74" t="str">
+      <x:c r="F20" s="84" t="str">
         <x:v>Light footer, company links, contact and PDPA link: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G20" s="74" t="str">
+      <x:c r="G20" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H20" s="75" t="d">
+      <x:c r="H20" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I20" s="75" t="d">
+      <x:c r="I20" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J20" s="74" t="str">
+      <x:c r="J20" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K20" s="74" t="str">
+      <x:c r="K20" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L20" s="74" t="str">
+      <x:c r="L20" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M20" s="74" t="str">
+      <x:c r="M20" s="84" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -33965,63 +34231,89 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="310" customHeight="1">
-      <x:c r="A21" s="74" t="str">
+      <x:c r="A21" s="84" t="str">
         <x:v>F07</x:v>
       </x:c>
-      <x:c r="B21" s="74" t="str">
+      <x:c r="B21" s="84" t="str">
         <x:v>Step 1 · i18n</x:v>
       </x:c>
-      <x:c r="C21" s="74" t="str">
+      <x:c r="C21" s="84" t="str">
         <x:v>Thai/English routes, language switch and localized formatting</x:v>
       </x:c>
-      <x:c r="D21" s="74" t="str">
+      <x:c r="D21" s="84" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="74" t="str">
+      <x:c r="E21" s="84" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F21" s="74" t="str">
+      <x:c r="F21" s="84" t="str">
         <x:v>Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable.</x:v>
       </x:c>
-      <x:c r="G21" s="74" t="str">
+      <x:c r="G21" s="84" t="str">
         <x:v>Codex: preserve existing approved shell; any separate foundation closeout must use the latest passing evidence. Contact details remain owner-supplied.</x:v>
       </x:c>
-      <x:c r="H21" s="75" t="d">
+      <x:c r="H21" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I21" s="75" t="d">
+      <x:c r="I21" s="85" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J21" s="74" t="str">
+      <x:c r="J21" s="84" t="str">
         <x:v>PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K21" s="74" t="str">
+      <x:c r="K21" s="84" t="str">
         <x:v>Preceding V5 commit 6e3d7d9 pushed. This Step 2 commit/push is verified during finalization; exact hash is in final report. If final push/sync fails, B01-B04/B34 must revert to Pending.</x:v>
       </x:c>
-      <x:c r="L21" s="74" t="str">
+      <x:c r="L21" s="84" t="str">
         <x:v>44 baseline Git/live hashes matched before changes. Intended code/config/docs/tracker compared and synchronized; final SHA-256 check required before report. Credentials/runtime/deps/caches excluded.</x:v>
       </x:c>
-      <x:c r="M21" s="74" t="str">
+      <x:c r="M21" s="84" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
 2026-10-09 Step 2: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Latest evidence: all 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness verified. No Step 1 closeout or UI change is claimed in Step 2. Original prototype rendered comparison remains unverified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
 2026-10-09 Step 2: Thai/English routes, language switch and localized formatting: implemented in the foundation. All 16 browser/API checks now pass, including the previous preference/search failures; real PostgreSQL readiness is verified. Pending separate foundation closeout: original rendered-prototype comparison remains unverified. Step 2 changes no UI. Owner contact details remain unresolved where applicable. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="250" customHeight="1">
-      <x:c r="A22" s="44"/>
-      <x:c r="B22" s="44"/>
-      <x:c r="C22" s="44"/>
-      <x:c r="D22" s="44"/>
-      <x:c r="E22" s="44"/>
-      <x:c r="F22" s="44"/>
-      <x:c r="G22" s="44"/>
-      <x:c r="H22" s="45"/>
-      <x:c r="I22" s="45"/>
-      <x:c r="J22" s="44"/>
-      <x:c r="K22" s="44"/>
-      <x:c r="L22" s="44"/>
-      <x:c r="M22" s="44"/>
+    <x:row r="22" ht="400" customHeight="1">
+      <x:c r="A22" s="84" t="str">
+        <x:v>F25</x:v>
+      </x:c>
+      <x:c r="B22" s="84" t="str">
+        <x:v>Step 7 · Home</x:v>
+      </x:c>
+      <x:c r="C22" s="84" t="str">
+        <x:v>Small home listing rows; regional tiles with real listing counts (Steps 3B/7)</x:v>
+      </x:c>
+      <x:c r="D22" s="84" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E22" s="84" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F22" s="84" t="str">
+        <x:v>Step 3B implements approved topic rows, separate small cards, responsive rails, featured/newest safe queries, saves and honest local samples. Regional tiles/live location counts remain Step 7 and are not implemented. This broad task is therefore Pending; the scoped Step 3B work is R04 Done.</x:v>
+      </x:c>
+      <x:c r="G22" s="84" t="str">
+        <x:v>Codex: wait for Step 7 authorization to add regional tiles/live counts. Future admin row management requires its approved stage. Stop before Step 4 now.</x:v>
+      </x:c>
+      <x:c r="H22" s="85" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I22" s="85"/>
+      <x:c r="J22" s="84" t="str">
+        <x:v>PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
+      </x:c>
+      <x:c r="K22" s="84" t="str">
+        <x:v>Preceding 830e037 pushed. Current commit/push verified at finalization; exact hash in final report. Revert affected tasks to Pending if a final gate fails.</x:v>
+      </x:c>
+      <x:c r="L22" s="84" t="str">
+        <x:v>82-file live baseline rechecked before sync. Owner reference revisions adopted without rewriting their input hashes; 91 intended Git/live source/config/docs/tracker pairs verified at closeout. Secrets/dependencies/runtime/caches excluded.</x:v>
+      </x:c>
+      <x:c r="M22" s="84" t="str">
+        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
+2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.
+2026-10-10 R04: owner replaced the older big carousel with small topic rows and authorized this portion in Step 3B. Rows implemented/tested; regional tiles remain Step 7. Not started to Pending for partial scope; original history retained.</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="44"/>
@@ -41199,27 +41491,24 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="63" priority="1">
+    <x:cfRule type="expression" dxfId="81" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="64" priority="2">
+    <x:cfRule type="expression" dxfId="82" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="65" priority="3">
+    <x:cfRule type="expression" dxfId="83" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="E22">
-      <x:formula1>"Done,Pending,Not started"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="E6:E21">
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="E6:E22">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R865a040151a84c94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92795c9a315142a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41259,7 +41548,7 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>2026-10-10: R03 development-only Sample preview verified. 83 permanent IDs: 16 Done, 16 Pending, 51 Not started. F08/B06 history updated; other statuses preserved. Yellow Pending; light green Done; red Not started.</x:v>
+        <x:v>2026-10-10: Step 3B / R04 verified. 84 permanent IDs: 17 Done, 17 Pending, 50 Not started. F25 Pending for Step 7 regional tiles. Prior IDs/history retained. Yellow Pending; light green Done; red Not started.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -41274,21 +41563,21 @@
       </x:c>
       <x:c r="B3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)+COUNTA('Pending'!A6:A500)+COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F3" s="18" t="n">
         <x:f>COUNTA('Pending'!A6:A500)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
         <x:v>Not started</x:v>
@@ -41300,7 +41589,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -41345,1505 +41634,1480 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="250" customHeight="1">
-      <x:c r="A6" s="76" t="str">
+      <x:c r="A6" s="86" t="str">
         <x:v>F14</x:v>
       </x:c>
-      <x:c r="B6" s="77" t="str">
+      <x:c r="B6" s="87" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C6" s="77" t="str">
+      <x:c r="C6" s="87" t="str">
         <x:v>Desktop listing/map split and hover/focus pin synchronization</x:v>
       </x:c>
-      <x:c r="D6" s="77" t="str">
+      <x:c r="D6" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="77" t="str">
+      <x:c r="E6" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F6" s="77" t="str">
+      <x:c r="F6" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G6" s="77" t="str">
+      <x:c r="G6" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H6" s="78"/>
-      <x:c r="I6" s="78"/>
-      <x:c r="J6" s="77"/>
-      <x:c r="K6" s="77"/>
-      <x:c r="L6" s="77"/>
-      <x:c r="M6" s="77"/>
+      <x:c r="H6" s="88"/>
+      <x:c r="I6" s="88"/>
+      <x:c r="J6" s="87"/>
+      <x:c r="K6" s="87"/>
+      <x:c r="L6" s="87"/>
+      <x:c r="M6" s="87"/>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="76" t="str">
+      <x:c r="A7" s="86" t="str">
         <x:v>F15</x:v>
       </x:c>
-      <x:c r="B7" s="77" t="str">
+      <x:c r="B7" s="87" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C7" s="77" t="str">
+      <x:c r="C7" s="87" t="str">
         <x:v>Phone full-screen Map/List toggle</x:v>
       </x:c>
-      <x:c r="D7" s="77" t="str">
+      <x:c r="D7" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="77" t="str">
+      <x:c r="E7" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F7" s="77" t="str">
+      <x:c r="F7" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G7" s="77" t="str">
+      <x:c r="G7" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H7" s="78"/>
-      <x:c r="I7" s="78"/>
-      <x:c r="J7" s="77"/>
-      <x:c r="K7" s="77"/>
-      <x:c r="L7" s="77"/>
-      <x:c r="M7" s="77"/>
+      <x:c r="H7" s="88"/>
+      <x:c r="I7" s="88"/>
+      <x:c r="J7" s="87"/>
+      <x:c r="K7" s="87"/>
+      <x:c r="L7" s="87"/>
+      <x:c r="M7" s="87"/>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="76" t="str">
+      <x:c r="A8" s="86" t="str">
         <x:v>F16</x:v>
       </x:c>
-      <x:c r="B8" s="77" t="str">
+      <x:c r="B8" s="87" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C8" s="77" t="str">
+      <x:c r="C8" s="87" t="str">
         <x:v>Property detail photo grid and full-screen gallery</x:v>
       </x:c>
-      <x:c r="D8" s="77" t="str">
+      <x:c r="D8" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="77" t="str">
+      <x:c r="E8" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F8" s="77" t="str">
+      <x:c r="F8" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G8" s="77" t="str">
+      <x:c r="G8" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H8" s="78"/>
-      <x:c r="I8" s="78"/>
-      <x:c r="J8" s="77"/>
-      <x:c r="K8" s="77"/>
-      <x:c r="L8" s="77"/>
-      <x:c r="M8" s="77"/>
+      <x:c r="H8" s="88"/>
+      <x:c r="I8" s="88"/>
+      <x:c r="J8" s="87"/>
+      <x:c r="K8" s="87"/>
+      <x:c r="L8" s="87"/>
+      <x:c r="M8" s="87"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="76" t="str">
+      <x:c r="A9" s="86" t="str">
         <x:v>F17</x:v>
       </x:c>
-      <x:c r="B9" s="77" t="str">
+      <x:c r="B9" s="87" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C9" s="77" t="str">
+      <x:c r="C9" s="87" t="str">
         <x:v>Title, pricing, type-specific facts, long description and sticky tabs</x:v>
       </x:c>
-      <x:c r="D9" s="77" t="str">
+      <x:c r="D9" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="77" t="str">
+      <x:c r="E9" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F9" s="77" t="str">
+      <x:c r="F9" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G9" s="77" t="str">
+      <x:c r="G9" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H9" s="78"/>
-      <x:c r="I9" s="78"/>
-      <x:c r="J9" s="77"/>
-      <x:c r="K9" s="77"/>
-      <x:c r="L9" s="77"/>
-      <x:c r="M9" s="77"/>
+      <x:c r="H9" s="88"/>
+      <x:c r="I9" s="88"/>
+      <x:c r="J9" s="87"/>
+      <x:c r="K9" s="87"/>
+      <x:c r="L9" s="87"/>
+      <x:c r="M9" s="87"/>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="76" t="str">
+      <x:c r="A10" s="86" t="str">
         <x:v>F18</x:v>
       </x:c>
-      <x:c r="B10" s="77" t="str">
+      <x:c r="B10" s="87" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C10" s="77" t="str">
+      <x:c r="C10" s="87" t="str">
         <x:v>Floorplan/video/360 tabs, verified nearby information and map</x:v>
       </x:c>
-      <x:c r="D10" s="77" t="str">
+      <x:c r="D10" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E10" s="77" t="str">
+      <x:c r="E10" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F10" s="77" t="str">
+      <x:c r="F10" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G10" s="77" t="str">
+      <x:c r="G10" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H10" s="78"/>
-      <x:c r="I10" s="78"/>
-      <x:c r="J10" s="77"/>
-      <x:c r="K10" s="77"/>
-      <x:c r="L10" s="77"/>
-      <x:c r="M10" s="77"/>
+      <x:c r="H10" s="88"/>
+      <x:c r="I10" s="88"/>
+      <x:c r="J10" s="87"/>
+      <x:c r="K10" s="87"/>
+      <x:c r="L10" s="87"/>
+      <x:c r="M10" s="87"/>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="76" t="str">
+      <x:c r="A11" s="86" t="str">
         <x:v>F19</x:v>
       </x:c>
-      <x:c r="B11" s="77" t="str">
+      <x:c r="B11" s="87" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C11" s="77" t="str">
+      <x:c r="C11" s="87" t="str">
         <x:v>Mortgage calculator and area comparison when real data exists</x:v>
       </x:c>
-      <x:c r="D11" s="77" t="str">
+      <x:c r="D11" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E11" s="77" t="str">
+      <x:c r="E11" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F11" s="77" t="str">
+      <x:c r="F11" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G11" s="77" t="str">
+      <x:c r="G11" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H11" s="78"/>
-      <x:c r="I11" s="78"/>
-      <x:c r="J11" s="77"/>
-      <x:c r="K11" s="77"/>
-      <x:c r="L11" s="77"/>
-      <x:c r="M11" s="77"/>
+      <x:c r="H11" s="88"/>
+      <x:c r="I11" s="88"/>
+      <x:c r="J11" s="87"/>
+      <x:c r="K11" s="87"/>
+      <x:c r="L11" s="87"/>
+      <x:c r="M11" s="87"/>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="76" t="str">
+      <x:c r="A12" s="86" t="str">
         <x:v>F20</x:v>
       </x:c>
-      <x:c r="B12" s="77" t="str">
+      <x:c r="B12" s="87" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C12" s="77" t="str">
+      <x:c r="C12" s="87" t="str">
         <x:v>Same-project units and similar-property cards</x:v>
       </x:c>
-      <x:c r="D12" s="77" t="str">
+      <x:c r="D12" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E12" s="77" t="str">
+      <x:c r="E12" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F12" s="77" t="str">
+      <x:c r="F12" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G12" s="77" t="str">
+      <x:c r="G12" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H12" s="78"/>
-      <x:c r="I12" s="78"/>
-      <x:c r="J12" s="77"/>
-      <x:c r="K12" s="77"/>
-      <x:c r="L12" s="77"/>
-      <x:c r="M12" s="77"/>
+      <x:c r="H12" s="88"/>
+      <x:c r="I12" s="88"/>
+      <x:c r="J12" s="87"/>
+      <x:c r="K12" s="87"/>
+      <x:c r="L12" s="87"/>
+      <x:c r="M12" s="87"/>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="76" t="str">
+      <x:c r="A13" s="86" t="str">
         <x:v>F21</x:v>
       </x:c>
-      <x:c r="B13" s="77" t="str">
+      <x:c r="B13" s="87" t="str">
         <x:v>Step 6 · Contact</x:v>
       </x:c>
-      <x:c r="C13" s="77" t="str">
+      <x:c r="C13" s="87" t="str">
         <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
       </x:c>
-      <x:c r="D13" s="77" t="str">
+      <x:c r="D13" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E13" s="77" t="str">
+      <x:c r="E13" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="77" t="str">
+      <x:c r="F13" s="87" t="str">
         <x:v>V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
-      <x:c r="G13" s="77" t="str">
+      <x:c r="G13" s="87" t="str">
         <x:v>Owner: provide routing/contacts. Codex: implement only under Step 6 authorization.</x:v>
       </x:c>
-      <x:c r="H13" s="78"/>
-      <x:c r="I13" s="78" t="d">
+      <x:c r="H13" s="88"/>
+      <x:c r="I13" s="88" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J13" s="77" t="str">
+      <x:c r="J13" s="87" t="str">
         <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
       </x:c>
-      <x:c r="K13" s="77" t="str">
+      <x:c r="K13" s="87" t="str">
         <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
       </x:c>
-      <x:c r="L13" s="77" t="str">
+      <x:c r="L13" s="87" t="str">
         <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
       </x:c>
-      <x:c r="M13" s="77" t="str">
+      <x:c r="M13" s="87" t="str">
         <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="76" t="str">
+      <x:c r="A14" s="86" t="str">
         <x:v>F22</x:v>
       </x:c>
-      <x:c r="B14" s="77" t="str">
+      <x:c r="B14" s="87" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C14" s="77" t="str">
+      <x:c r="C14" s="87" t="str">
         <x:v>Single-image hero and compact photography-first layout</x:v>
       </x:c>
-      <x:c r="D14" s="77" t="str">
+      <x:c r="D14" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E14" s="77" t="str">
+      <x:c r="E14" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F14" s="77" t="str">
+      <x:c r="F14" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G14" s="77" t="str">
+      <x:c r="G14" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H14" s="78"/>
-      <x:c r="I14" s="78"/>
-      <x:c r="J14" s="77"/>
-      <x:c r="K14" s="77"/>
-      <x:c r="L14" s="77"/>
-      <x:c r="M14" s="77"/>
+      <x:c r="H14" s="88"/>
+      <x:c r="I14" s="88"/>
+      <x:c r="J14" s="87"/>
+      <x:c r="K14" s="87"/>
+      <x:c r="L14" s="87"/>
+      <x:c r="M14" s="87"/>
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="76" t="str">
+      <x:c r="A15" s="86" t="str">
         <x:v>F23</x:v>
       </x:c>
-      <x:c r="B15" s="77" t="str">
+      <x:c r="B15" s="87" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C15" s="77" t="str">
+      <x:c r="C15" s="87" t="str">
         <x:v>Shared search box with Buy/Rent/Projects/Investment tabs</x:v>
       </x:c>
-      <x:c r="D15" s="77" t="str">
+      <x:c r="D15" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="77" t="str">
+      <x:c r="E15" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="77" t="str">
+      <x:c r="F15" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G15" s="77" t="str">
+      <x:c r="G15" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H15" s="78"/>
-      <x:c r="I15" s="78"/>
-      <x:c r="J15" s="77"/>
-      <x:c r="K15" s="77"/>
-      <x:c r="L15" s="77"/>
-      <x:c r="M15" s="77"/>
+      <x:c r="H15" s="88"/>
+      <x:c r="I15" s="88"/>
+      <x:c r="J15" s="87"/>
+      <x:c r="K15" s="87"/>
+      <x:c r="L15" s="87"/>
+      <x:c r="M15" s="87"/>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="76" t="str">
+      <x:c r="A16" s="86" t="str">
         <x:v>F24</x:v>
       </x:c>
-      <x:c r="B16" s="77" t="str">
+      <x:c r="B16" s="87" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C16" s="77" t="str">
+      <x:c r="C16" s="87" t="str">
         <x:v>Categories, recent searches and location/station suggestions</x:v>
       </x:c>
-      <x:c r="D16" s="77" t="str">
+      <x:c r="D16" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E16" s="77" t="str">
+      <x:c r="E16" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="77" t="str">
+      <x:c r="F16" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G16" s="77" t="str">
+      <x:c r="G16" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H16" s="78"/>
-      <x:c r="I16" s="78"/>
-      <x:c r="J16" s="77"/>
-      <x:c r="K16" s="77"/>
-      <x:c r="L16" s="77"/>
-      <x:c r="M16" s="77"/>
+      <x:c r="H16" s="88"/>
+      <x:c r="I16" s="88"/>
+      <x:c r="J16" s="87"/>
+      <x:c r="K16" s="87"/>
+      <x:c r="L16" s="87"/>
+      <x:c r="M16" s="87"/>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="76" t="str">
-        <x:v>F25</x:v>
-      </x:c>
-      <x:c r="B17" s="77" t="str">
+      <x:c r="A17" s="86" t="str">
+        <x:v>F26</x:v>
+      </x:c>
+      <x:c r="B17" s="87" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C17" s="77" t="str">
-        <x:v>Homes for you carousel directly below search; regions with real listing counts</x:v>
-      </x:c>
-      <x:c r="D17" s="77" t="str">
+      <x:c r="C17" s="87" t="str">
+        <x:v>New projects, tools, services and owner lead CTAs</x:v>
+      </x:c>
+      <x:c r="D17" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="77" t="str">
+      <x:c r="E17" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="77" t="str">
-        <x:v>V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
-      </x:c>
-      <x:c r="G17" s="77" t="str">
-        <x:v>Codex: implement approved home-page.html only under Step 7 authorization.</x:v>
-      </x:c>
-      <x:c r="H17" s="78"/>
-      <x:c r="I17" s="78" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="J17" s="77" t="str">
-        <x:v>Documentation/planning update only. No application tests run at owner request. Existing runtime test results remain in prior history. Workbook/source/mirror checks performed.</x:v>
-      </x:c>
-      <x:c r="K17" s="77" t="str">
-        <x:v>Preceding foundation commit 604c62e pushed. V5 adoption commit/push verified at finalization; final report provides hash.</x:v>
-      </x:c>
-      <x:c r="L17" s="77" t="str">
-        <x:v>Baseline live files compared with Git before synchronization; revised guide/source/docs/tracker synchronized only after divergence checks.</x:v>
-      </x:c>
-      <x:c r="M17" s="77" t="str">
-        <x:v>Original planning evidence: Not yet implemented; follow approved V3 handoff.
-2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.</x:v>
-      </x:c>
+      <x:c r="F17" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G17" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H17" s="88"/>
+      <x:c r="I17" s="88"/>
+      <x:c r="J17" s="87"/>
+      <x:c r="K17" s="87"/>
+      <x:c r="L17" s="87"/>
+      <x:c r="M17" s="87"/>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="76" t="str">
-        <x:v>F26</x:v>
-      </x:c>
-      <x:c r="B18" s="77" t="str">
-        <x:v>Step 7 · Home</x:v>
-      </x:c>
-      <x:c r="C18" s="77" t="str">
-        <x:v>New projects, tools, services and owner lead CTAs</x:v>
-      </x:c>
-      <x:c r="D18" s="77" t="str">
+      <x:c r="A18" s="86" t="str">
+        <x:v>F27</x:v>
+      </x:c>
+      <x:c r="B18" s="87" t="str">
+        <x:v>Step 8 · Projects</x:v>
+      </x:c>
+      <x:c r="C18" s="87" t="str">
+        <x:v>Projects index and responsive project detail layouts</x:v>
+      </x:c>
+      <x:c r="D18" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="77" t="str">
+      <x:c r="E18" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F18" s="77" t="str">
+      <x:c r="F18" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G18" s="77" t="str">
+      <x:c r="G18" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H18" s="78"/>
-      <x:c r="I18" s="78"/>
-      <x:c r="J18" s="77"/>
-      <x:c r="K18" s="77"/>
-      <x:c r="L18" s="77"/>
-      <x:c r="M18" s="77"/>
+      <x:c r="H18" s="88"/>
+      <x:c r="I18" s="88"/>
+      <x:c r="J18" s="87"/>
+      <x:c r="K18" s="87"/>
+      <x:c r="L18" s="87"/>
+      <x:c r="M18" s="87"/>
     </x:row>
     <x:row r="19" ht="250" customHeight="1">
-      <x:c r="A19" s="76" t="str">
-        <x:v>F27</x:v>
-      </x:c>
-      <x:c r="B19" s="77" t="str">
+      <x:c r="A19" s="86" t="str">
+        <x:v>F28</x:v>
+      </x:c>
+      <x:c r="B19" s="87" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C19" s="77" t="str">
-        <x:v>Projects index and responsive project detail layouts</x:v>
-      </x:c>
-      <x:c r="D19" s="77" t="str">
+      <x:c r="C19" s="87" t="str">
+        <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
+      </x:c>
+      <x:c r="D19" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="77" t="str">
+      <x:c r="E19" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="77" t="str">
+      <x:c r="F19" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G19" s="77" t="str">
+      <x:c r="G19" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H19" s="78"/>
-      <x:c r="I19" s="78"/>
-      <x:c r="J19" s="77"/>
-      <x:c r="K19" s="77"/>
-      <x:c r="L19" s="77"/>
-      <x:c r="M19" s="77"/>
+      <x:c r="H19" s="88"/>
+      <x:c r="I19" s="88"/>
+      <x:c r="J19" s="87"/>
+      <x:c r="K19" s="87"/>
+      <x:c r="L19" s="87"/>
+      <x:c r="M19" s="87"/>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="76" t="str">
-        <x:v>F28</x:v>
-      </x:c>
-      <x:c r="B20" s="77" t="str">
+      <x:c r="A20" s="86" t="str">
+        <x:v>F29</x:v>
+      </x:c>
+      <x:c r="B20" s="87" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C20" s="77" t="str">
-        <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
-      </x:c>
-      <x:c r="D20" s="77" t="str">
+      <x:c r="C20" s="87" t="str">
+        <x:v>Data-driven clickable project SVG plot plan</x:v>
+      </x:c>
+      <x:c r="D20" s="87" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="77" t="str">
+      <x:c r="E20" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="77" t="str">
+      <x:c r="F20" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G20" s="77" t="str">
+      <x:c r="G20" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H20" s="78"/>
-      <x:c r="I20" s="78"/>
-      <x:c r="J20" s="77"/>
-      <x:c r="K20" s="77"/>
-      <x:c r="L20" s="77"/>
-      <x:c r="M20" s="77"/>
+      <x:c r="H20" s="88"/>
+      <x:c r="I20" s="88"/>
+      <x:c r="J20" s="87"/>
+      <x:c r="K20" s="87"/>
+      <x:c r="L20" s="87"/>
+      <x:c r="M20" s="87"/>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="76" t="str">
-        <x:v>F29</x:v>
-      </x:c>
-      <x:c r="B21" s="77" t="str">
+      <x:c r="A21" s="86" t="str">
+        <x:v>F30</x:v>
+      </x:c>
+      <x:c r="B21" s="87" t="str">
+        <x:v>Step 8 · Booking</x:v>
+      </x:c>
+      <x:c r="C21" s="87" t="str">
+        <x:v>Site visit 3-step form and confirmation screens</x:v>
+      </x:c>
+      <x:c r="D21" s="87" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E21" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F21" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G21" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H21" s="88"/>
+      <x:c r="I21" s="88"/>
+      <x:c r="J21" s="87"/>
+      <x:c r="K21" s="87"/>
+      <x:c r="L21" s="87"/>
+      <x:c r="M21" s="87"/>
+    </x:row>
+    <x:row r="22" ht="26" customHeight="1">
+      <x:c r="A22" s="86" t="str">
+        <x:v>F31</x:v>
+      </x:c>
+      <x:c r="B22" s="87" t="str">
+        <x:v>Step 9 · Saved</x:v>
+      </x:c>
+      <x:c r="C22" s="87" t="str">
+        <x:v>Homes, searches and viewings; local save without account</x:v>
+      </x:c>
+      <x:c r="D22" s="87" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E22" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F22" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G22" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H22" s="88"/>
+      <x:c r="I22" s="88"/>
+      <x:c r="J22" s="87"/>
+      <x:c r="K22" s="87"/>
+      <x:c r="L22" s="87"/>
+      <x:c r="M22" s="87"/>
+    </x:row>
+    <x:row r="23" ht="250" customHeight="1">
+      <x:c r="A23" s="86" t="str">
+        <x:v>F33</x:v>
+      </x:c>
+      <x:c r="B23" s="87" t="str">
+        <x:v>Step 10B · Accounts</x:v>
+      </x:c>
+      <x:c r="C23" s="87" t="str">
+        <x:v>Build approved auth and account screens only after approval</x:v>
+      </x:c>
+      <x:c r="D23" s="87" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E23" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F23" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G23" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H23" s="88"/>
+      <x:c r="I23" s="88"/>
+      <x:c r="J23" s="87"/>
+      <x:c r="K23" s="87"/>
+      <x:c r="L23" s="87"/>
+      <x:c r="M23" s="87"/>
+    </x:row>
+    <x:row r="24" ht="26" customHeight="1">
+      <x:c r="A24" s="86" t="str">
+        <x:v>F35</x:v>
+      </x:c>
+      <x:c r="B24" s="87" t="str">
+        <x:v>Step 11B · Admin</x:v>
+      </x:c>
+      <x:c r="C24" s="87" t="str">
+        <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
+      </x:c>
+      <x:c r="D24" s="87" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E24" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F24" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G24" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H24" s="88"/>
+      <x:c r="I24" s="88"/>
+      <x:c r="J24" s="87"/>
+      <x:c r="K24" s="87"/>
+      <x:c r="L24" s="87"/>
+      <x:c r="M24" s="87"/>
+    </x:row>
+    <x:row r="25" ht="26" customHeight="1">
+      <x:c r="A25" s="86" t="str">
+        <x:v>F36</x:v>
+      </x:c>
+      <x:c r="B25" s="87" t="str">
+        <x:v>Step 11B · Admin</x:v>
+      </x:c>
+      <x:c r="C25" s="87" t="str">
+        <x:v>Admin-managed searchable filter editor with type safety</x:v>
+      </x:c>
+      <x:c r="D25" s="87" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E25" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F25" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G25" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H25" s="88"/>
+      <x:c r="I25" s="88"/>
+      <x:c r="J25" s="87"/>
+      <x:c r="K25" s="87"/>
+      <x:c r="L25" s="87"/>
+      <x:c r="M25" s="87"/>
+    </x:row>
+    <x:row r="26" ht="26" customHeight="1">
+      <x:c r="A26" s="86" t="str">
+        <x:v>F37</x:v>
+      </x:c>
+      <x:c r="B26" s="87" t="str">
+        <x:v>Step 12 · Quality</x:v>
+      </x:c>
+      <x:c r="C26" s="87" t="str">
+        <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
+      </x:c>
+      <x:c r="D26" s="87" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E26" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F26" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G26" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H26" s="88"/>
+      <x:c r="I26" s="88"/>
+      <x:c r="J26" s="87"/>
+      <x:c r="K26" s="87"/>
+      <x:c r="L26" s="87"/>
+      <x:c r="M26" s="87"/>
+    </x:row>
+    <x:row r="27" ht="26" customHeight="1">
+      <x:c r="A27" s="86" t="str">
+        <x:v>F38</x:v>
+      </x:c>
+      <x:c r="B27" s="87" t="str">
+        <x:v>Step 12 · Quality</x:v>
+      </x:c>
+      <x:c r="C27" s="87" t="str">
+        <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
+      </x:c>
+      <x:c r="D27" s="87" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E27" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F27" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G27" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H27" s="88"/>
+      <x:c r="I27" s="88"/>
+      <x:c r="J27" s="87"/>
+      <x:c r="K27" s="87"/>
+      <x:c r="L27" s="87"/>
+      <x:c r="M27" s="87"/>
+    </x:row>
+    <x:row r="28" ht="26" customHeight="1">
+      <x:c r="A28" s="86" t="str">
+        <x:v>B08</x:v>
+      </x:c>
+      <x:c r="B28" s="87" t="str">
+        <x:v>Step 4 · Map</x:v>
+      </x:c>
+      <x:c r="C28" s="87" t="str">
+        <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
+      </x:c>
+      <x:c r="D28" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E28" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F28" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G28" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H28" s="88"/>
+      <x:c r="I28" s="88"/>
+      <x:c r="J28" s="87"/>
+      <x:c r="K28" s="87"/>
+      <x:c r="L28" s="87"/>
+      <x:c r="M28" s="87"/>
+    </x:row>
+    <x:row r="29" ht="26" customHeight="1">
+      <x:c r="A29" s="86" t="str">
+        <x:v>B10</x:v>
+      </x:c>
+      <x:c r="B29" s="87" t="str">
+        <x:v>Step 4 · Nearby</x:v>
+      </x:c>
+      <x:c r="C29" s="87" t="str">
+        <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
+      </x:c>
+      <x:c r="D29" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E29" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F29" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G29" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H29" s="88"/>
+      <x:c r="I29" s="88"/>
+      <x:c r="J29" s="87"/>
+      <x:c r="K29" s="87"/>
+      <x:c r="L29" s="87"/>
+      <x:c r="M29" s="87"/>
+    </x:row>
+    <x:row r="30" ht="26" customHeight="1">
+      <x:c r="A30" s="86" t="str">
+        <x:v>B11</x:v>
+      </x:c>
+      <x:c r="B30" s="87" t="str">
+        <x:v>Step 5 · Media</x:v>
+      </x:c>
+      <x:c r="C30" s="87" t="str">
+        <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
+      </x:c>
+      <x:c r="D30" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E30" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F30" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G30" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H30" s="88"/>
+      <x:c r="I30" s="88"/>
+      <x:c r="J30" s="87"/>
+      <x:c r="K30" s="87"/>
+      <x:c r="L30" s="87"/>
+      <x:c r="M30" s="87"/>
+    </x:row>
+    <x:row r="31" ht="26" customHeight="1">
+      <x:c r="A31" s="86" t="str">
+        <x:v>B12</x:v>
+      </x:c>
+      <x:c r="B31" s="87" t="str">
+        <x:v>Step 5 · Similar</x:v>
+      </x:c>
+      <x:c r="C31" s="87" t="str">
+        <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
+      </x:c>
+      <x:c r="D31" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E31" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F31" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G31" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H31" s="88"/>
+      <x:c r="I31" s="88"/>
+      <x:c r="J31" s="87"/>
+      <x:c r="K31" s="87"/>
+      <x:c r="L31" s="87"/>
+      <x:c r="M31" s="87"/>
+    </x:row>
+    <x:row r="32" ht="26" customHeight="1">
+      <x:c r="A32" s="86" t="str">
+        <x:v>B13</x:v>
+      </x:c>
+      <x:c r="B32" s="87" t="str">
+        <x:v>Step 5 · Metrics</x:v>
+      </x:c>
+      <x:c r="C32" s="87" t="str">
+        <x:v>Comparable pricing/yield gated by verified sample size</x:v>
+      </x:c>
+      <x:c r="D32" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E32" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F32" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G32" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H32" s="88"/>
+      <x:c r="I32" s="88"/>
+      <x:c r="J32" s="87"/>
+      <x:c r="K32" s="87"/>
+      <x:c r="L32" s="87"/>
+      <x:c r="M32" s="87"/>
+    </x:row>
+    <x:row r="33" ht="26" customHeight="1">
+      <x:c r="A33" s="86" t="str">
+        <x:v>B14</x:v>
+      </x:c>
+      <x:c r="B33" s="87" t="str">
+        <x:v>Step 6 · Leads</x:v>
+      </x:c>
+      <x:c r="C33" s="87" t="str">
+        <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
+      </x:c>
+      <x:c r="D33" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E33" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F33" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G33" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H33" s="88"/>
+      <x:c r="I33" s="88"/>
+      <x:c r="J33" s="87"/>
+      <x:c r="K33" s="87"/>
+      <x:c r="L33" s="87"/>
+      <x:c r="M33" s="87"/>
+    </x:row>
+    <x:row r="34" ht="26" customHeight="1">
+      <x:c r="A34" s="86" t="str">
+        <x:v>B15</x:v>
+      </x:c>
+      <x:c r="B34" s="87" t="str">
+        <x:v>Step 6 · Leads</x:v>
+      </x:c>
+      <x:c r="C34" s="87" t="str">
+        <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
+      </x:c>
+      <x:c r="D34" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E34" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F34" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G34" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H34" s="88"/>
+      <x:c r="I34" s="88"/>
+      <x:c r="J34" s="87"/>
+      <x:c r="K34" s="87"/>
+      <x:c r="L34" s="87"/>
+      <x:c r="M34" s="87"/>
+    </x:row>
+    <x:row r="35" ht="26" customHeight="1">
+      <x:c r="A35" s="86" t="str">
+        <x:v>B16</x:v>
+      </x:c>
+      <x:c r="B35" s="87" t="str">
+        <x:v>Step 6 · Security</x:v>
+      </x:c>
+      <x:c r="C35" s="87" t="str">
+        <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
+      </x:c>
+      <x:c r="D35" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E35" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F35" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G35" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H35" s="88"/>
+      <x:c r="I35" s="88"/>
+      <x:c r="J35" s="87"/>
+      <x:c r="K35" s="87"/>
+      <x:c r="L35" s="87"/>
+      <x:c r="M35" s="87"/>
+    </x:row>
+    <x:row r="36" ht="26" customHeight="1">
+      <x:c r="A36" s="86" t="str">
+        <x:v>B19</x:v>
+      </x:c>
+      <x:c r="B36" s="87" t="str">
+        <x:v>Step 6 · Chat</x:v>
+      </x:c>
+      <x:c r="C36" s="87" t="str">
+        <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
+      </x:c>
+      <x:c r="D36" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E36" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F36" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G36" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H36" s="88"/>
+      <x:c r="I36" s="88"/>
+      <x:c r="J36" s="87"/>
+      <x:c r="K36" s="87"/>
+      <x:c r="L36" s="87"/>
+      <x:c r="M36" s="87"/>
+    </x:row>
+    <x:row r="37" ht="26" customHeight="1">
+      <x:c r="A37" s="86" t="str">
+        <x:v>B20</x:v>
+      </x:c>
+      <x:c r="B37" s="87" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C21" s="77" t="str">
-        <x:v>Data-driven clickable project SVG plot plan</x:v>
-      </x:c>
-      <x:c r="D21" s="77" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E21" s="77" t="str">
+      <x:c r="C37" s="87" t="str">
+        <x:v>Project/unit/plot status logic and validation</x:v>
+      </x:c>
+      <x:c r="D37" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E37" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="77" t="str">
+      <x:c r="F37" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G21" s="77" t="str">
+      <x:c r="G37" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H21" s="78"/>
-      <x:c r="I21" s="78"/>
-      <x:c r="J21" s="77"/>
-      <x:c r="K21" s="77"/>
-      <x:c r="L21" s="77"/>
-      <x:c r="M21" s="77"/>
-    </x:row>
-    <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="76" t="str">
-        <x:v>F30</x:v>
-      </x:c>
-      <x:c r="B22" s="77" t="str">
+      <x:c r="H37" s="88"/>
+      <x:c r="I37" s="88"/>
+      <x:c r="J37" s="87"/>
+      <x:c r="K37" s="87"/>
+      <x:c r="L37" s="87"/>
+      <x:c r="M37" s="87"/>
+    </x:row>
+    <x:row r="38" ht="26" customHeight="1">
+      <x:c r="A38" s="86" t="str">
+        <x:v>B21</x:v>
+      </x:c>
+      <x:c r="B38" s="87" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C22" s="77" t="str">
-        <x:v>Site visit 3-step form and confirmation screens</x:v>
-      </x:c>
-      <x:c r="D22" s="77" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E22" s="77" t="str">
+      <x:c r="C38" s="87" t="str">
+        <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
+      </x:c>
+      <x:c r="D38" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E38" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="77" t="str">
+      <x:c r="F38" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G22" s="77" t="str">
+      <x:c r="G38" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H22" s="78"/>
-      <x:c r="I22" s="78"/>
-      <x:c r="J22" s="77"/>
-      <x:c r="K22" s="77"/>
-      <x:c r="L22" s="77"/>
-      <x:c r="M22" s="77"/>
-    </x:row>
-    <x:row r="23" ht="250" customHeight="1">
-      <x:c r="A23" s="76" t="str">
-        <x:v>F31</x:v>
-      </x:c>
-      <x:c r="B23" s="77" t="str">
+      <x:c r="H38" s="88"/>
+      <x:c r="I38" s="88"/>
+      <x:c r="J38" s="87"/>
+      <x:c r="K38" s="87"/>
+      <x:c r="L38" s="87"/>
+      <x:c r="M38" s="87"/>
+    </x:row>
+    <x:row r="39" ht="26" customHeight="1">
+      <x:c r="A39" s="86" t="str">
+        <x:v>B22</x:v>
+      </x:c>
+      <x:c r="B39" s="87" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C23" s="77" t="str">
-        <x:v>Homes, searches and viewings; local save without account</x:v>
-      </x:c>
-      <x:c r="D23" s="77" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E23" s="77" t="str">
+      <x:c r="C39" s="87" t="str">
+        <x:v>Saved listings/searches persistence, new-match calculations</x:v>
+      </x:c>
+      <x:c r="D39" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E39" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F23" s="77" t="str">
+      <x:c r="F39" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G23" s="77" t="str">
+      <x:c r="G39" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H23" s="78"/>
-      <x:c r="I23" s="78"/>
-      <x:c r="J23" s="77"/>
-      <x:c r="K23" s="77"/>
-      <x:c r="L23" s="77"/>
-      <x:c r="M23" s="77"/>
-    </x:row>
-    <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="76" t="str">
-        <x:v>F33</x:v>
-      </x:c>
-      <x:c r="B24" s="77" t="str">
-        <x:v>Step 10B · Accounts</x:v>
-      </x:c>
-      <x:c r="C24" s="77" t="str">
-        <x:v>Build approved auth and account screens only after approval</x:v>
-      </x:c>
-      <x:c r="D24" s="77" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E24" s="77" t="str">
+      <x:c r="H39" s="88"/>
+      <x:c r="I39" s="88"/>
+      <x:c r="J39" s="87"/>
+      <x:c r="K39" s="87"/>
+      <x:c r="L39" s="87"/>
+      <x:c r="M39" s="87"/>
+    </x:row>
+    <x:row r="40" ht="26" customHeight="1">
+      <x:c r="A40" s="86" t="str">
+        <x:v>B24</x:v>
+      </x:c>
+      <x:c r="B40" s="87" t="str">
+        <x:v>Step 10B · Auth</x:v>
+      </x:c>
+      <x:c r="C40" s="87" t="str">
+        <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
+      </x:c>
+      <x:c r="D40" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E40" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="77" t="str">
+      <x:c r="F40" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G24" s="77" t="str">
+      <x:c r="G40" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H24" s="78"/>
-      <x:c r="I24" s="78"/>
-      <x:c r="J24" s="77"/>
-      <x:c r="K24" s="77"/>
-      <x:c r="L24" s="77"/>
-      <x:c r="M24" s="77"/>
-    </x:row>
-    <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="76" t="str">
-        <x:v>F35</x:v>
-      </x:c>
-      <x:c r="B25" s="77" t="str">
+      <x:c r="H40" s="88"/>
+      <x:c r="I40" s="88"/>
+      <x:c r="J40" s="87"/>
+      <x:c r="K40" s="87"/>
+      <x:c r="L40" s="87"/>
+      <x:c r="M40" s="87"/>
+    </x:row>
+    <x:row r="41" ht="26" customHeight="1">
+      <x:c r="A41" s="86" t="str">
+        <x:v>B25</x:v>
+      </x:c>
+      <x:c r="B41" s="87" t="str">
+        <x:v>Step 10B · Auth</x:v>
+      </x:c>
+      <x:c r="C41" s="87" t="str">
+        <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
+      </x:c>
+      <x:c r="D41" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E41" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F41" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G41" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H41" s="88"/>
+      <x:c r="I41" s="88"/>
+      <x:c r="J41" s="87"/>
+      <x:c r="K41" s="87"/>
+      <x:c r="L41" s="87"/>
+      <x:c r="M41" s="87"/>
+    </x:row>
+    <x:row r="42" ht="26" customHeight="1">
+      <x:c r="A42" s="86" t="str">
+        <x:v>B26</x:v>
+      </x:c>
+      <x:c r="B42" s="87" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C25" s="77" t="str">
-        <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
-      </x:c>
-      <x:c r="D25" s="77" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E25" s="77" t="str">
+      <x:c r="C42" s="87" t="str">
+        <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
+      </x:c>
+      <x:c r="D42" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E42" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="77" t="str">
+      <x:c r="F42" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G25" s="77" t="str">
+      <x:c r="G42" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H25" s="78"/>
-      <x:c r="I25" s="78"/>
-      <x:c r="J25" s="77"/>
-      <x:c r="K25" s="77"/>
-      <x:c r="L25" s="77"/>
-      <x:c r="M25" s="77"/>
-    </x:row>
-    <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="76" t="str">
-        <x:v>F36</x:v>
-      </x:c>
-      <x:c r="B26" s="77" t="str">
+      <x:c r="H42" s="88"/>
+      <x:c r="I42" s="88"/>
+      <x:c r="J42" s="87"/>
+      <x:c r="K42" s="87"/>
+      <x:c r="L42" s="87"/>
+      <x:c r="M42" s="87"/>
+    </x:row>
+    <x:row r="43" ht="26" customHeight="1">
+      <x:c r="A43" s="86" t="str">
+        <x:v>B27</x:v>
+      </x:c>
+      <x:c r="B43" s="87" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C26" s="77" t="str">
-        <x:v>Admin-managed searchable filter editor with type safety</x:v>
-      </x:c>
-      <x:c r="D26" s="77" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E26" s="77" t="str">
+      <x:c r="C43" s="87" t="str">
+        <x:v>Admin user management, audit log and sensitive action authorization</x:v>
+      </x:c>
+      <x:c r="D43" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E43" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="77" t="str">
+      <x:c r="F43" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G26" s="77" t="str">
+      <x:c r="G43" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H26" s="78"/>
-      <x:c r="I26" s="78"/>
-      <x:c r="J26" s="77"/>
-      <x:c r="K26" s="77"/>
-      <x:c r="L26" s="77"/>
-      <x:c r="M26" s="77"/>
-    </x:row>
-    <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="76" t="str">
-        <x:v>F37</x:v>
-      </x:c>
-      <x:c r="B27" s="77" t="str">
+      <x:c r="H43" s="88"/>
+      <x:c r="I43" s="88"/>
+      <x:c r="J43" s="87"/>
+      <x:c r="K43" s="87"/>
+      <x:c r="L43" s="87"/>
+      <x:c r="M43" s="87"/>
+    </x:row>
+    <x:row r="44" ht="26" customHeight="1">
+      <x:c r="A44" s="86" t="str">
+        <x:v>B30</x:v>
+      </x:c>
+      <x:c r="B44" s="87" t="str">
+        <x:v>Step 12 · Deploy</x:v>
+      </x:c>
+      <x:c r="C44" s="87" t="str">
+        <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
+      </x:c>
+      <x:c r="D44" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E44" s="87" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F44" s="87" t="str">
+        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
+      </x:c>
+      <x:c r="G44" s="87" t="str">
+        <x:v>Codex: implement in assigned step</x:v>
+      </x:c>
+      <x:c r="H44" s="88"/>
+      <x:c r="I44" s="88"/>
+      <x:c r="J44" s="87"/>
+      <x:c r="K44" s="87"/>
+      <x:c r="L44" s="87"/>
+      <x:c r="M44" s="87"/>
+    </x:row>
+    <x:row r="45" ht="26" customHeight="1">
+      <x:c r="A45" s="86" t="str">
+        <x:v>B31</x:v>
+      </x:c>
+      <x:c r="B45" s="87" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C27" s="77" t="str">
-        <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
-      </x:c>
-      <x:c r="D27" s="77" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E27" s="77" t="str">
+      <x:c r="C45" s="87" t="str">
+        <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
+      </x:c>
+      <x:c r="D45" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E45" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="77" t="str">
+      <x:c r="F45" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G27" s="77" t="str">
+      <x:c r="G45" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H27" s="78"/>
-      <x:c r="I27" s="78"/>
-      <x:c r="J27" s="77"/>
-      <x:c r="K27" s="77"/>
-      <x:c r="L27" s="77"/>
-      <x:c r="M27" s="77"/>
-    </x:row>
-    <x:row r="28" ht="26" customHeight="1">
-      <x:c r="A28" s="76" t="str">
-        <x:v>F38</x:v>
-      </x:c>
-      <x:c r="B28" s="77" t="str">
-        <x:v>Step 12 · Quality</x:v>
-      </x:c>
-      <x:c r="C28" s="77" t="str">
-        <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
-      </x:c>
-      <x:c r="D28" s="77" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E28" s="77" t="str">
+      <x:c r="H45" s="88"/>
+      <x:c r="I45" s="88"/>
+      <x:c r="J45" s="87"/>
+      <x:c r="K45" s="87"/>
+      <x:c r="L45" s="87"/>
+      <x:c r="M45" s="87"/>
+    </x:row>
+    <x:row r="46" ht="26" customHeight="1">
+      <x:c r="A46" s="86" t="str">
+        <x:v>B32</x:v>
+      </x:c>
+      <x:c r="B46" s="87" t="str">
+        <x:v>Step 12 · Security</x:v>
+      </x:c>
+      <x:c r="C46" s="87" t="str">
+        <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
+      </x:c>
+      <x:c r="D46" s="87" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E46" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="77" t="str">
+      <x:c r="F46" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G28" s="77" t="str">
+      <x:c r="G46" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H28" s="78"/>
-      <x:c r="I28" s="78"/>
-      <x:c r="J28" s="77"/>
-      <x:c r="K28" s="77"/>
-      <x:c r="L28" s="77"/>
-      <x:c r="M28" s="77"/>
-    </x:row>
-    <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="76" t="str">
-        <x:v>B08</x:v>
-      </x:c>
-      <x:c r="B29" s="77" t="str">
-        <x:v>Step 4 · Map</x:v>
-      </x:c>
-      <x:c r="C29" s="77" t="str">
-        <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
-      </x:c>
-      <x:c r="D29" s="77" t="str">
+      <x:c r="H46" s="88"/>
+      <x:c r="I46" s="88"/>
+      <x:c r="J46" s="87"/>
+      <x:c r="K46" s="87"/>
+      <x:c r="L46" s="87"/>
+      <x:c r="M46" s="87"/>
+    </x:row>
+    <x:row r="47" ht="26" customHeight="1">
+      <x:c r="A47" s="86" t="str">
+        <x:v>B33</x:v>
+      </x:c>
+      <x:c r="B47" s="87" t="str">
+        <x:v>Step 7 · Owners</x:v>
+      </x:c>
+      <x:c r="C47" s="87" t="str">
+        <x:v>Home-value and service enquiry data handling</x:v>
+      </x:c>
+      <x:c r="D47" s="87" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E29" s="77" t="str">
+      <x:c r="E47" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="77" t="str">
+      <x:c r="F47" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G29" s="77" t="str">
+      <x:c r="G47" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H29" s="78"/>
-      <x:c r="I29" s="78"/>
-      <x:c r="J29" s="77"/>
-      <x:c r="K29" s="77"/>
-      <x:c r="L29" s="77"/>
-      <x:c r="M29" s="77"/>
-    </x:row>
-    <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="76" t="str">
-        <x:v>B10</x:v>
-      </x:c>
-      <x:c r="B30" s="77" t="str">
-        <x:v>Step 4 · Nearby</x:v>
-      </x:c>
-      <x:c r="C30" s="77" t="str">
-        <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
-      </x:c>
-      <x:c r="D30" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E30" s="77" t="str">
+      <x:c r="H47" s="88"/>
+      <x:c r="I47" s="88"/>
+      <x:c r="J47" s="87"/>
+      <x:c r="K47" s="87"/>
+      <x:c r="L47" s="87"/>
+      <x:c r="M47" s="87"/>
+    </x:row>
+    <x:row r="48" ht="26" customHeight="1">
+      <x:c r="A48" s="86" t="str">
+        <x:v>E01</x:v>
+      </x:c>
+      <x:c r="B48" s="87" t="str">
+        <x:v>Step 6 · Email</x:v>
+      </x:c>
+      <x:c r="C48" s="87" t="str">
+        <x:v>Enquiry notification with retryable queue/outbox</x:v>
+      </x:c>
+      <x:c r="D48" s="87" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E48" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="77" t="str">
+      <x:c r="F48" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G30" s="77" t="str">
+      <x:c r="G48" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H30" s="78"/>
-      <x:c r="I30" s="78"/>
-      <x:c r="J30" s="77"/>
-      <x:c r="K30" s="77"/>
-      <x:c r="L30" s="77"/>
-      <x:c r="M30" s="77"/>
-    </x:row>
-    <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="76" t="str">
-        <x:v>B11</x:v>
-      </x:c>
-      <x:c r="B31" s="77" t="str">
-        <x:v>Step 5 · Media</x:v>
-      </x:c>
-      <x:c r="C31" s="77" t="str">
-        <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
-      </x:c>
-      <x:c r="D31" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E31" s="77" t="str">
+      <x:c r="H48" s="88"/>
+      <x:c r="I48" s="88"/>
+      <x:c r="J48" s="87"/>
+      <x:c r="K48" s="87"/>
+      <x:c r="L48" s="87"/>
+      <x:c r="M48" s="87"/>
+    </x:row>
+    <x:row r="49" ht="26" customHeight="1">
+      <x:c r="A49" s="86" t="str">
+        <x:v>E02</x:v>
+      </x:c>
+      <x:c r="B49" s="87" t="str">
+        <x:v>Step 6 · Email</x:v>
+      </x:c>
+      <x:c r="C49" s="87" t="str">
+        <x:v>Thai and English buyer enquiry acknowledgments</x:v>
+      </x:c>
+      <x:c r="D49" s="87" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E49" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="77" t="str">
+      <x:c r="F49" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G31" s="77" t="str">
+      <x:c r="G49" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H31" s="78"/>
-      <x:c r="I31" s="78"/>
-      <x:c r="J31" s="77"/>
-      <x:c r="K31" s="77"/>
-      <x:c r="L31" s="77"/>
-      <x:c r="M31" s="77"/>
-    </x:row>
-    <x:row r="32" ht="26" customHeight="1">
-      <x:c r="A32" s="76" t="str">
-        <x:v>B12</x:v>
-      </x:c>
-      <x:c r="B32" s="77" t="str">
-        <x:v>Step 5 · Similar</x:v>
-      </x:c>
-      <x:c r="C32" s="77" t="str">
-        <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
-      </x:c>
-      <x:c r="D32" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E32" s="77" t="str">
+      <x:c r="H49" s="88"/>
+      <x:c r="I49" s="88"/>
+      <x:c r="J49" s="87"/>
+      <x:c r="K49" s="87"/>
+      <x:c r="L49" s="87"/>
+      <x:c r="M49" s="87"/>
+    </x:row>
+    <x:row r="50" ht="26" customHeight="1">
+      <x:c r="A50" s="86" t="str">
+        <x:v>E03</x:v>
+      </x:c>
+      <x:c r="B50" s="87" t="str">
+        <x:v>Step 8 · Email</x:v>
+      </x:c>
+      <x:c r="C50" s="87" t="str">
+        <x:v>Project brochure/price list email delivery</x:v>
+      </x:c>
+      <x:c r="D50" s="87" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E50" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="77" t="str">
+      <x:c r="F50" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G32" s="77" t="str">
+      <x:c r="G50" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H32" s="78"/>
-      <x:c r="I32" s="78"/>
-      <x:c r="J32" s="77"/>
-      <x:c r="K32" s="77"/>
-      <x:c r="L32" s="77"/>
-      <x:c r="M32" s="77"/>
-    </x:row>
-    <x:row r="33" ht="26" customHeight="1">
-      <x:c r="A33" s="76" t="str">
-        <x:v>B13</x:v>
-      </x:c>
-      <x:c r="B33" s="77" t="str">
-        <x:v>Step 5 · Metrics</x:v>
-      </x:c>
-      <x:c r="C33" s="77" t="str">
-        <x:v>Comparable pricing/yield gated by verified sample size</x:v>
-      </x:c>
-      <x:c r="D33" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E33" s="77" t="str">
+      <x:c r="H50" s="88"/>
+      <x:c r="I50" s="88"/>
+      <x:c r="J50" s="87"/>
+      <x:c r="K50" s="87"/>
+      <x:c r="L50" s="87"/>
+      <x:c r="M50" s="87"/>
+    </x:row>
+    <x:row r="51" ht="26" customHeight="1">
+      <x:c r="A51" s="86" t="str">
+        <x:v>E04</x:v>
+      </x:c>
+      <x:c r="B51" s="87" t="str">
+        <x:v>Step 8 · Email</x:v>
+      </x:c>
+      <x:c r="C51" s="87" t="str">
+        <x:v>Site visit request and confirmation notifications</x:v>
+      </x:c>
+      <x:c r="D51" s="87" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E51" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F33" s="77" t="str">
+      <x:c r="F51" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G33" s="77" t="str">
+      <x:c r="G51" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H33" s="78"/>
-      <x:c r="I33" s="78"/>
-      <x:c r="J33" s="77"/>
-      <x:c r="K33" s="77"/>
-      <x:c r="L33" s="77"/>
-      <x:c r="M33" s="77"/>
-    </x:row>
-    <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="76" t="str">
-        <x:v>B14</x:v>
-      </x:c>
-      <x:c r="B34" s="77" t="str">
-        <x:v>Step 6 · Leads</x:v>
-      </x:c>
-      <x:c r="C34" s="77" t="str">
-        <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
-      </x:c>
-      <x:c r="D34" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E34" s="77" t="str">
+      <x:c r="H51" s="88"/>
+      <x:c r="I51" s="88"/>
+      <x:c r="J51" s="87"/>
+      <x:c r="K51" s="87"/>
+      <x:c r="L51" s="87"/>
+      <x:c r="M51" s="87"/>
+    </x:row>
+    <x:row r="52" ht="26" customHeight="1">
+      <x:c r="A52" s="86" t="str">
+        <x:v>E05</x:v>
+      </x:c>
+      <x:c r="B52" s="87" t="str">
+        <x:v>Step 9 · Alerts</x:v>
+      </x:c>
+      <x:c r="C52" s="87" t="str">
+        <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
+      </x:c>
+      <x:c r="D52" s="87" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E52" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F34" s="77" t="str">
+      <x:c r="F52" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G34" s="77" t="str">
+      <x:c r="G52" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H34" s="78"/>
-      <x:c r="I34" s="78"/>
-      <x:c r="J34" s="77"/>
-      <x:c r="K34" s="77"/>
-      <x:c r="L34" s="77"/>
-      <x:c r="M34" s="77"/>
-    </x:row>
-    <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="76" t="str">
-        <x:v>B15</x:v>
-      </x:c>
-      <x:c r="B35" s="77" t="str">
-        <x:v>Step 6 · Leads</x:v>
-      </x:c>
-      <x:c r="C35" s="77" t="str">
-        <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
-      </x:c>
-      <x:c r="D35" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E35" s="77" t="str">
+      <x:c r="H52" s="88"/>
+      <x:c r="I52" s="88"/>
+      <x:c r="J52" s="87"/>
+      <x:c r="K52" s="87"/>
+      <x:c r="L52" s="87"/>
+      <x:c r="M52" s="87"/>
+    </x:row>
+    <x:row r="53" ht="26" customHeight="1">
+      <x:c r="A53" s="86" t="str">
+        <x:v>E06</x:v>
+      </x:c>
+      <x:c r="B53" s="87" t="str">
+        <x:v>Step 10B · Email</x:v>
+      </x:c>
+      <x:c r="C53" s="87" t="str">
+        <x:v>Account verification and recovery messages if email auth approved</x:v>
+      </x:c>
+      <x:c r="D53" s="87" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E53" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F35" s="77" t="str">
+      <x:c r="F53" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G35" s="77" t="str">
+      <x:c r="G53" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H35" s="78"/>
-      <x:c r="I35" s="78"/>
-      <x:c r="J35" s="77"/>
-      <x:c r="K35" s="77"/>
-      <x:c r="L35" s="77"/>
-      <x:c r="M35" s="77"/>
-    </x:row>
-    <x:row r="36" ht="26" customHeight="1">
-      <x:c r="A36" s="76" t="str">
-        <x:v>B16</x:v>
-      </x:c>
-      <x:c r="B36" s="77" t="str">
-        <x:v>Step 6 · Security</x:v>
-      </x:c>
-      <x:c r="C36" s="77" t="str">
-        <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
-      </x:c>
-      <x:c r="D36" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E36" s="77" t="str">
+      <x:c r="H53" s="88"/>
+      <x:c r="I53" s="88"/>
+      <x:c r="J53" s="87"/>
+      <x:c r="K53" s="87"/>
+      <x:c r="L53" s="87"/>
+      <x:c r="M53" s="87"/>
+    </x:row>
+    <x:row r="54" ht="26" customHeight="1">
+      <x:c r="A54" s="86" t="str">
+        <x:v>E07</x:v>
+      </x:c>
+      <x:c r="B54" s="87" t="str">
+        <x:v>Step 11B · Email</x:v>
+      </x:c>
+      <x:c r="C54" s="87" t="str">
+        <x:v>Agent notification/routing administration</x:v>
+      </x:c>
+      <x:c r="D54" s="87" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E54" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F36" s="77" t="str">
+      <x:c r="F54" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G36" s="77" t="str">
+      <x:c r="G54" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H36" s="78"/>
-      <x:c r="I36" s="78"/>
-      <x:c r="J36" s="77"/>
-      <x:c r="K36" s="77"/>
-      <x:c r="L36" s="77"/>
-      <x:c r="M36" s="77"/>
-    </x:row>
-    <x:row r="37" ht="26" customHeight="1">
-      <x:c r="A37" s="76" t="str">
-        <x:v>B19</x:v>
-      </x:c>
-      <x:c r="B37" s="77" t="str">
-        <x:v>Step 6 · Chat</x:v>
-      </x:c>
-      <x:c r="C37" s="77" t="str">
-        <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
-      </x:c>
-      <x:c r="D37" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E37" s="77" t="str">
+      <x:c r="H54" s="88"/>
+      <x:c r="I54" s="88"/>
+      <x:c r="J54" s="87"/>
+      <x:c r="K54" s="87"/>
+      <x:c r="L54" s="87"/>
+      <x:c r="M54" s="87"/>
+    </x:row>
+    <x:row r="55" ht="26" customHeight="1">
+      <x:c r="A55" s="86" t="str">
+        <x:v>E08</x:v>
+      </x:c>
+      <x:c r="B55" s="87" t="str">
+        <x:v>Step 7 · Email</x:v>
+      </x:c>
+      <x:c r="C55" s="87" t="str">
+        <x:v>Home valuation and service enquiry replies</x:v>
+      </x:c>
+      <x:c r="D55" s="87" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="E55" s="87" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F37" s="77" t="str">
+      <x:c r="F55" s="87" t="str">
         <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
-      <x:c r="G37" s="77" t="str">
+      <x:c r="G55" s="87" t="str">
         <x:v>Codex: implement in assigned step</x:v>
       </x:c>
-      <x:c r="H37" s="78"/>
-      <x:c r="I37" s="78"/>
-      <x:c r="J37" s="77"/>
-      <x:c r="K37" s="77"/>
-      <x:c r="L37" s="77"/>
-      <x:c r="M37" s="77"/>
-    </x:row>
-    <x:row r="38" ht="26" customHeight="1">
-      <x:c r="A38" s="76" t="str">
-        <x:v>B20</x:v>
-      </x:c>
-      <x:c r="B38" s="77" t="str">
-        <x:v>Step 8 · Projects</x:v>
-      </x:c>
-      <x:c r="C38" s="77" t="str">
-        <x:v>Project/unit/plot status logic and validation</x:v>
-      </x:c>
-      <x:c r="D38" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E38" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F38" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G38" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H38" s="78"/>
-      <x:c r="I38" s="78"/>
-      <x:c r="J38" s="77"/>
-      <x:c r="K38" s="77"/>
-      <x:c r="L38" s="77"/>
-      <x:c r="M38" s="77"/>
-    </x:row>
-    <x:row r="39" ht="26" customHeight="1">
-      <x:c r="A39" s="76" t="str">
-        <x:v>B21</x:v>
-      </x:c>
-      <x:c r="B39" s="77" t="str">
-        <x:v>Step 8 · Booking</x:v>
-      </x:c>
-      <x:c r="C39" s="77" t="str">
-        <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
-      </x:c>
-      <x:c r="D39" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E39" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F39" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G39" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H39" s="78"/>
-      <x:c r="I39" s="78"/>
-      <x:c r="J39" s="77"/>
-      <x:c r="K39" s="77"/>
-      <x:c r="L39" s="77"/>
-      <x:c r="M39" s="77"/>
-    </x:row>
-    <x:row r="40" ht="26" customHeight="1">
-      <x:c r="A40" s="76" t="str">
-        <x:v>B22</x:v>
-      </x:c>
-      <x:c r="B40" s="77" t="str">
-        <x:v>Step 9 · Saved</x:v>
-      </x:c>
-      <x:c r="C40" s="77" t="str">
-        <x:v>Saved listings/searches persistence, new-match calculations</x:v>
-      </x:c>
-      <x:c r="D40" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E40" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F40" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G40" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H40" s="78"/>
-      <x:c r="I40" s="78"/>
-      <x:c r="J40" s="77"/>
-      <x:c r="K40" s="77"/>
-      <x:c r="L40" s="77"/>
-      <x:c r="M40" s="77"/>
-    </x:row>
-    <x:row r="41" ht="26" customHeight="1">
-      <x:c r="A41" s="76" t="str">
-        <x:v>B24</x:v>
-      </x:c>
-      <x:c r="B41" s="77" t="str">
-        <x:v>Step 10B · Auth</x:v>
-      </x:c>
-      <x:c r="C41" s="77" t="str">
-        <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
-      </x:c>
-      <x:c r="D41" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E41" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F41" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G41" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H41" s="78"/>
-      <x:c r="I41" s="78"/>
-      <x:c r="J41" s="77"/>
-      <x:c r="K41" s="77"/>
-      <x:c r="L41" s="77"/>
-      <x:c r="M41" s="77"/>
-    </x:row>
-    <x:row r="42" ht="26" customHeight="1">
-      <x:c r="A42" s="76" t="str">
-        <x:v>B25</x:v>
-      </x:c>
-      <x:c r="B42" s="77" t="str">
-        <x:v>Step 10B · Auth</x:v>
-      </x:c>
-      <x:c r="C42" s="77" t="str">
-        <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
-      </x:c>
-      <x:c r="D42" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E42" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F42" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G42" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H42" s="78"/>
-      <x:c r="I42" s="78"/>
-      <x:c r="J42" s="77"/>
-      <x:c r="K42" s="77"/>
-      <x:c r="L42" s="77"/>
-      <x:c r="M42" s="77"/>
-    </x:row>
-    <x:row r="43" ht="26" customHeight="1">
-      <x:c r="A43" s="76" t="str">
-        <x:v>B26</x:v>
-      </x:c>
-      <x:c r="B43" s="77" t="str">
-        <x:v>Step 11B · Admin</x:v>
-      </x:c>
-      <x:c r="C43" s="77" t="str">
-        <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
-      </x:c>
-      <x:c r="D43" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E43" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F43" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G43" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H43" s="78"/>
-      <x:c r="I43" s="78"/>
-      <x:c r="J43" s="77"/>
-      <x:c r="K43" s="77"/>
-      <x:c r="L43" s="77"/>
-      <x:c r="M43" s="77"/>
-    </x:row>
-    <x:row r="44" ht="26" customHeight="1">
-      <x:c r="A44" s="76" t="str">
-        <x:v>B27</x:v>
-      </x:c>
-      <x:c r="B44" s="77" t="str">
-        <x:v>Step 11B · Admin</x:v>
-      </x:c>
-      <x:c r="C44" s="77" t="str">
-        <x:v>Admin user management, audit log and sensitive action authorization</x:v>
-      </x:c>
-      <x:c r="D44" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E44" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F44" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G44" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H44" s="78"/>
-      <x:c r="I44" s="78"/>
-      <x:c r="J44" s="77"/>
-      <x:c r="K44" s="77"/>
-      <x:c r="L44" s="77"/>
-      <x:c r="M44" s="77"/>
-    </x:row>
-    <x:row r="45" ht="26" customHeight="1">
-      <x:c r="A45" s="76" t="str">
-        <x:v>B30</x:v>
-      </x:c>
-      <x:c r="B45" s="77" t="str">
-        <x:v>Step 12 · Deploy</x:v>
-      </x:c>
-      <x:c r="C45" s="77" t="str">
-        <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
-      </x:c>
-      <x:c r="D45" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E45" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F45" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G45" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H45" s="78"/>
-      <x:c r="I45" s="78"/>
-      <x:c r="J45" s="77"/>
-      <x:c r="K45" s="77"/>
-      <x:c r="L45" s="77"/>
-      <x:c r="M45" s="77"/>
-    </x:row>
-    <x:row r="46" ht="26" customHeight="1">
-      <x:c r="A46" s="76" t="str">
-        <x:v>B31</x:v>
-      </x:c>
-      <x:c r="B46" s="77" t="str">
-        <x:v>Step 12 · Quality</x:v>
-      </x:c>
-      <x:c r="C46" s="77" t="str">
-        <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
-      </x:c>
-      <x:c r="D46" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E46" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F46" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G46" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H46" s="78"/>
-      <x:c r="I46" s="78"/>
-      <x:c r="J46" s="77"/>
-      <x:c r="K46" s="77"/>
-      <x:c r="L46" s="77"/>
-      <x:c r="M46" s="77"/>
-    </x:row>
-    <x:row r="47" ht="26" customHeight="1">
-      <x:c r="A47" s="76" t="str">
-        <x:v>B32</x:v>
-      </x:c>
-      <x:c r="B47" s="77" t="str">
-        <x:v>Step 12 · Security</x:v>
-      </x:c>
-      <x:c r="C47" s="77" t="str">
-        <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
-      </x:c>
-      <x:c r="D47" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E47" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F47" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G47" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H47" s="78"/>
-      <x:c r="I47" s="78"/>
-      <x:c r="J47" s="77"/>
-      <x:c r="K47" s="77"/>
-      <x:c r="L47" s="77"/>
-      <x:c r="M47" s="77"/>
-    </x:row>
-    <x:row r="48" ht="26" customHeight="1">
-      <x:c r="A48" s="76" t="str">
-        <x:v>B33</x:v>
-      </x:c>
-      <x:c r="B48" s="77" t="str">
-        <x:v>Step 7 · Owners</x:v>
-      </x:c>
-      <x:c r="C48" s="77" t="str">
-        <x:v>Home-value and service enquiry data handling</x:v>
-      </x:c>
-      <x:c r="D48" s="77" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-      <x:c r="E48" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F48" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G48" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H48" s="78"/>
-      <x:c r="I48" s="78"/>
-      <x:c r="J48" s="77"/>
-      <x:c r="K48" s="77"/>
-      <x:c r="L48" s="77"/>
-      <x:c r="M48" s="77"/>
-    </x:row>
-    <x:row r="49" ht="26" customHeight="1">
-      <x:c r="A49" s="76" t="str">
-        <x:v>E01</x:v>
-      </x:c>
-      <x:c r="B49" s="77" t="str">
-        <x:v>Step 6 · Email</x:v>
-      </x:c>
-      <x:c r="C49" s="77" t="str">
-        <x:v>Enquiry notification with retryable queue/outbox</x:v>
-      </x:c>
-      <x:c r="D49" s="77" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E49" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F49" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G49" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H49" s="78"/>
-      <x:c r="I49" s="78"/>
-      <x:c r="J49" s="77"/>
-      <x:c r="K49" s="77"/>
-      <x:c r="L49" s="77"/>
-      <x:c r="M49" s="77"/>
-    </x:row>
-    <x:row r="50" ht="26" customHeight="1">
-      <x:c r="A50" s="76" t="str">
-        <x:v>E02</x:v>
-      </x:c>
-      <x:c r="B50" s="77" t="str">
-        <x:v>Step 6 · Email</x:v>
-      </x:c>
-      <x:c r="C50" s="77" t="str">
-        <x:v>Thai and English buyer enquiry acknowledgments</x:v>
-      </x:c>
-      <x:c r="D50" s="77" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E50" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F50" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G50" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H50" s="78"/>
-      <x:c r="I50" s="78"/>
-      <x:c r="J50" s="77"/>
-      <x:c r="K50" s="77"/>
-      <x:c r="L50" s="77"/>
-      <x:c r="M50" s="77"/>
-    </x:row>
-    <x:row r="51" ht="26" customHeight="1">
-      <x:c r="A51" s="76" t="str">
-        <x:v>E03</x:v>
-      </x:c>
-      <x:c r="B51" s="77" t="str">
-        <x:v>Step 8 · Email</x:v>
-      </x:c>
-      <x:c r="C51" s="77" t="str">
-        <x:v>Project brochure/price list email delivery</x:v>
-      </x:c>
-      <x:c r="D51" s="77" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E51" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F51" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G51" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H51" s="78"/>
-      <x:c r="I51" s="78"/>
-      <x:c r="J51" s="77"/>
-      <x:c r="K51" s="77"/>
-      <x:c r="L51" s="77"/>
-      <x:c r="M51" s="77"/>
-    </x:row>
-    <x:row r="52" ht="26" customHeight="1">
-      <x:c r="A52" s="76" t="str">
-        <x:v>E04</x:v>
-      </x:c>
-      <x:c r="B52" s="77" t="str">
-        <x:v>Step 8 · Email</x:v>
-      </x:c>
-      <x:c r="C52" s="77" t="str">
-        <x:v>Site visit request and confirmation notifications</x:v>
-      </x:c>
-      <x:c r="D52" s="77" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E52" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F52" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G52" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H52" s="78"/>
-      <x:c r="I52" s="78"/>
-      <x:c r="J52" s="77"/>
-      <x:c r="K52" s="77"/>
-      <x:c r="L52" s="77"/>
-      <x:c r="M52" s="77"/>
-    </x:row>
-    <x:row r="53" ht="26" customHeight="1">
-      <x:c r="A53" s="76" t="str">
-        <x:v>E05</x:v>
-      </x:c>
-      <x:c r="B53" s="77" t="str">
-        <x:v>Step 9 · Alerts</x:v>
-      </x:c>
-      <x:c r="C53" s="77" t="str">
-        <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
-      </x:c>
-      <x:c r="D53" s="77" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E53" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F53" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G53" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H53" s="78"/>
-      <x:c r="I53" s="78"/>
-      <x:c r="J53" s="77"/>
-      <x:c r="K53" s="77"/>
-      <x:c r="L53" s="77"/>
-      <x:c r="M53" s="77"/>
-    </x:row>
-    <x:row r="54" ht="26" customHeight="1">
-      <x:c r="A54" s="76" t="str">
-        <x:v>E06</x:v>
-      </x:c>
-      <x:c r="B54" s="77" t="str">
-        <x:v>Step 10B · Email</x:v>
-      </x:c>
-      <x:c r="C54" s="77" t="str">
-        <x:v>Account verification and recovery messages if email auth approved</x:v>
-      </x:c>
-      <x:c r="D54" s="77" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E54" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F54" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G54" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H54" s="78"/>
-      <x:c r="I54" s="78"/>
-      <x:c r="J54" s="77"/>
-      <x:c r="K54" s="77"/>
-      <x:c r="L54" s="77"/>
-      <x:c r="M54" s="77"/>
-    </x:row>
-    <x:row r="55" ht="26" customHeight="1">
-      <x:c r="A55" s="76" t="str">
-        <x:v>E07</x:v>
-      </x:c>
-      <x:c r="B55" s="77" t="str">
-        <x:v>Step 11B · Email</x:v>
-      </x:c>
-      <x:c r="C55" s="77" t="str">
-        <x:v>Agent notification/routing administration</x:v>
-      </x:c>
-      <x:c r="D55" s="77" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E55" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F55" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G55" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H55" s="78"/>
-      <x:c r="I55" s="78"/>
-      <x:c r="J55" s="77"/>
-      <x:c r="K55" s="77"/>
-      <x:c r="L55" s="77"/>
-      <x:c r="M55" s="77"/>
+      <x:c r="H55" s="88"/>
+      <x:c r="I55" s="88"/>
+      <x:c r="J55" s="87"/>
+      <x:c r="K55" s="87"/>
+      <x:c r="L55" s="87"/>
+      <x:c r="M55" s="87"/>
     </x:row>
     <x:row r="56" ht="26" customHeight="1">
-      <x:c r="A56" s="76" t="str">
-        <x:v>E08</x:v>
-      </x:c>
-      <x:c r="B56" s="77" t="str">
-        <x:v>Step 7 · Email</x:v>
-      </x:c>
-      <x:c r="C56" s="77" t="str">
-        <x:v>Home valuation and service enquiry replies</x:v>
-      </x:c>
-      <x:c r="D56" s="77" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="E56" s="77" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F56" s="77" t="str">
-        <x:v>Not yet implemented; follow approved V3 handoff.</x:v>
-      </x:c>
-      <x:c r="G56" s="77" t="str">
-        <x:v>Codex: implement in assigned step</x:v>
-      </x:c>
-      <x:c r="H56" s="78"/>
-      <x:c r="I56" s="78"/>
-      <x:c r="J56" s="77"/>
-      <x:c r="K56" s="77"/>
-      <x:c r="L56" s="77"/>
-      <x:c r="M56" s="77"/>
+      <x:c r="A56" s="56"/>
+      <x:c r="B56" s="57"/>
+      <x:c r="C56" s="57"/>
+      <x:c r="D56" s="57"/>
+      <x:c r="E56" s="57"/>
+      <x:c r="F56" s="57"/>
+      <x:c r="G56" s="57"/>
+      <x:c r="H56" s="58"/>
+      <x:c r="I56" s="58"/>
+      <x:c r="J56" s="57"/>
+      <x:c r="K56" s="57"/>
+      <x:c r="L56" s="57"/>
+      <x:c r="M56" s="57"/>
     </x:row>
     <x:row r="57" ht="26" customHeight="1">
       <x:c r="A57" s="56"/>
@@ -49511,17 +49775,17 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A6:M500">
-    <x:cfRule type="expression" dxfId="66" priority="1">
+    <x:cfRule type="expression" dxfId="84" priority="1">
       <x:formula>$E6="Pending"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="67" priority="2">
+    <x:cfRule type="expression" dxfId="85" priority="2">
       <x:formula>$E6="Done"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="68" priority="3">
+    <x:cfRule type="expression" dxfId="86" priority="3">
       <x:formula>$E6="Not started"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="4">
+  <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="E70:E75">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
@@ -49531,13 +49795,16 @@
     <x:dataValidation type="list" sqref="E57:E65">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="E6:E56">
+    <x:dataValidation type="list" sqref="E56">
+      <x:formula1>"Done,Pending,Not started"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E6:E55">
       <x:formula1>"Done,Pending,Not started"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7cdf360283842d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R223f0757dbf8484e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Mstar-Property-Task-Tracker.xlsx
+++ b/Mstar-Property-Task-Tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R34b35e268f2b4f1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="Re73f2c9f97724a00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="R1f89a2f8bab04dd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="Red6df9cf769d418c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R3bc3172e7aab42c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="Rf564b7c6313c4dc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="1" r:id="R46f6bbe26a844bb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend" sheetId="2" r:id="R4be10149a8a34d2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emails" sheetId="3" r:id="Rd01e677d761c432a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Done" sheetId="4" r:id="R58d05a69f0a647ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="5" r:id="R46cfbb8644d04ea8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not started" sheetId="6" r:id="Rfe7b1cbfd0744284"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -82,7 +82,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="22">
+  <x:fills count="25">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -189,6 +189,21 @@
         <x:fgColor rgb="FFC6EFCE"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFF6666"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC6EFCE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="3">
     <x:border/>
@@ -211,7 +226,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="123">
+  <x:cellXfs count="143">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -533,6 +548,64 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="10" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1415,8 +1488,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:M37"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="MstarFrontendTasks" displayName="MstarFrontendTasks" ref="A5:M36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:M36"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1437,7 +1510,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="MstarBackendTasks" displayName="MstarBackendTasks" ref="A5:M31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A5:M31"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
@@ -1459,7 +1532,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="MstarEmailsTasks" displayName="MstarEmailsTasks" ref="A5:M13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A5:M13"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
@@ -1481,8 +1554,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="MstarDoneTasks" displayName="MstarDoneTasks" ref="A5:M25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:M25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="MstarDoneTasks" displayName="MstarDoneTasks" ref="A5:M26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:M26"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1503,7 +1576,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="62" name="MstarPendingTasks" displayName="MstarPendingTasks" ref="A5:M28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A5:M28"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
@@ -1525,8 +1598,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:M48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="63" name="MstarNotstartedTasks" displayName="MstarNotstartedTasks" ref="A5:M47" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:M47"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1772,7 +1845,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>Done = completed task scope with evidence. Pending = started/blocked with named remaining work. Not started = task implementation has not begun. History is dated past evidence.</x:v>
+        <x:v>2026-10-10 Step 3C: F39 Done. 86 permanent IDs: 21 Done, 23 Pending, 42 Not started. All prior IDs and dated history retained; independent remaining tasks unchanged.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -1794,7 +1867,7 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -1813,7 +1886,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -1858,43 +1931,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="112.5" hidden="0" customHeight="1">
-      <x:c r="A6" s="104" t="str">
+      <x:c r="A6" s="129" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B6" s="105" t="str">
+      <x:c r="B6" s="130" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="105" t="str">
+      <x:c r="C6" s="130" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D6" s="105" t="str">
+      <x:c r="D6" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="105" t="str">
+      <x:c r="E6" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="105" t="str">
+      <x:c r="F6" s="130" t="str">
         <x:v>Approved temporary crest extracted and implemented. Owner will provide final header logo later.</x:v>
       </x:c>
-      <x:c r="G6" s="105" t="str">
+      <x:c r="G6" s="130" t="str">
         <x:v>Owner: supply final asset/version later; Codex: replace only approved logo.</x:v>
       </x:c>
-      <x:c r="H6" s="106" t="d">
+      <x:c r="H6" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="106" t="d">
+      <x:c r="I6" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="105" t="str">
+      <x:c r="J6" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K6" s="105" t="str">
+      <x:c r="K6" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L6" s="105" t="str">
+      <x:c r="L6" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M6" s="105" t="str">
+      <x:c r="M6" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
 2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.
@@ -1903,123 +1976,123 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A7" s="110" t="str">
+      <x:c r="A7" s="132" t="str">
         <x:v>F32</x:v>
       </x:c>
-      <x:c r="B7" s="111" t="str">
+      <x:c r="B7" s="133" t="str">
         <x:v>Step 10A · Wireframe</x:v>
       </x:c>
-      <x:c r="C7" s="111" t="str">
+      <x:c r="C7" s="133" t="str">
         <x:v>Owner-approved login/register/account wireframe before coding</x:v>
       </x:c>
-      <x:c r="D7" s="111" t="str">
+      <x:c r="D7" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E7" s="111" t="str">
+      <x:c r="E7" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F7" s="111" t="str">
+      <x:c r="F7" s="133" t="str">
         <x:v>No production wireframe has been drafted for this task. Future design must precede owner approval; no draft is currently waiting for review.</x:v>
       </x:c>
-      <x:c r="G7" s="111" t="str">
+      <x:c r="G7" s="133" t="str">
         <x:v>Codex: draft only in the authorized account/admin design stage; owner reviews the actual draft afterward.</x:v>
       </x:c>
-      <x:c r="H7" s="112"/>
-      <x:c r="I7" s="112" t="d">
+      <x:c r="H7" s="134"/>
+      <x:c r="I7" s="134" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="111" t="str">
+      <x:c r="J7" s="133" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K7" s="111" t="str">
+      <x:c r="K7" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L7" s="111" t="str">
+      <x:c r="L7" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M7" s="111" t="str">
+      <x:c r="M7" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Pending changed to Not started. No production wireframe has been drafted for this task. Future design must precede owner approval; no draft is currently waiting for review.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A8" s="110" t="str">
+      <x:c r="A8" s="132" t="str">
         <x:v>F34</x:v>
       </x:c>
-      <x:c r="B8" s="111" t="str">
+      <x:c r="B8" s="133" t="str">
         <x:v>Step 11A · Wireframe</x:v>
       </x:c>
-      <x:c r="C8" s="111" t="str">
+      <x:c r="C8" s="133" t="str">
         <x:v>Owner-approved responsive admin dashboard wireframe</x:v>
       </x:c>
-      <x:c r="D8" s="111" t="str">
+      <x:c r="D8" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E8" s="111" t="str">
+      <x:c r="E8" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F8" s="111" t="str">
+      <x:c r="F8" s="133" t="str">
         <x:v>No production wireframe has been drafted for this task. Future design must precede owner approval; no draft is currently waiting for review.</x:v>
       </x:c>
-      <x:c r="G8" s="111" t="str">
+      <x:c r="G8" s="133" t="str">
         <x:v>Codex: draft only in the authorized account/admin design stage; owner reviews the actual draft afterward.</x:v>
       </x:c>
-      <x:c r="H8" s="112"/>
-      <x:c r="I8" s="112" t="d">
+      <x:c r="H8" s="134"/>
+      <x:c r="I8" s="134" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="111" t="str">
+      <x:c r="J8" s="133" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K8" s="111" t="str">
+      <x:c r="K8" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L8" s="111" t="str">
+      <x:c r="L8" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M8" s="111" t="str">
+      <x:c r="M8" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Pending changed to Not started. No production wireframe has been drafted for this task. Future design must precede owner approval; no draft is currently waiting for review.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="301.5" hidden="0" customHeight="1">
-      <x:c r="A9" s="104" t="str">
+      <x:c r="A9" s="129" t="str">
         <x:v>F01</x:v>
       </x:c>
-      <x:c r="B9" s="105" t="str">
+      <x:c r="B9" s="130" t="str">
         <x:v>Step 1 · Design</x:v>
       </x:c>
-      <x:c r="C9" s="105" t="str">
+      <x:c r="C9" s="130" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives</x:v>
       </x:c>
-      <x:c r="D9" s="105" t="str">
+      <x:c r="D9" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E9" s="105" t="str">
+      <x:c r="E9" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="105" t="str">
+      <x:c r="F9" s="130" t="str">
         <x:v>Implemented foundation and subsequent browser preference/search retests passed. Remaining separate closeout: approved-original rendered-reference comparison is unverified. No current browser/DB failure is inferred from old history.</x:v>
       </x:c>
-      <x:c r="G9" s="105" t="str">
+      <x:c r="G9" s="130" t="str">
         <x:v>Codex: resolve the separate rendered-reference closeout when authorized; preserve current passing implementation.</x:v>
       </x:c>
-      <x:c r="H9" s="106" t="d">
+      <x:c r="H9" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I9" s="106" t="d">
+      <x:c r="I9" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J9" s="105" t="str">
+      <x:c r="J9" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K9" s="105" t="str">
+      <x:c r="K9" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L9" s="105" t="str">
+      <x:c r="L9" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M9" s="105" t="str">
+      <x:c r="M9" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
@@ -2029,43 +2102,43 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="288" hidden="0" customHeight="1">
-      <x:c r="A10" s="104" t="str">
+      <x:c r="A10" s="129" t="str">
         <x:v>F04</x:v>
       </x:c>
-      <x:c r="B10" s="105" t="str">
+      <x:c r="B10" s="130" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C10" s="105" t="str">
+      <x:c r="C10" s="130" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in</x:v>
       </x:c>
-      <x:c r="D10" s="105" t="str">
+      <x:c r="D10" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E10" s="105" t="str">
+      <x:c r="E10" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="105" t="str">
+      <x:c r="F10" s="130" t="str">
         <x:v>Implemented foundation and subsequent browser preference/search retests passed. Remaining separate closeout: approved-original rendered-reference comparison is unverified. No current browser/DB failure is inferred from old history.</x:v>
       </x:c>
-      <x:c r="G10" s="105" t="str">
+      <x:c r="G10" s="130" t="str">
         <x:v>Codex: resolve the separate rendered-reference closeout when authorized; preserve current passing implementation.</x:v>
       </x:c>
-      <x:c r="H10" s="106" t="d">
+      <x:c r="H10" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="106" t="d">
+      <x:c r="I10" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="105" t="str">
+      <x:c r="J10" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="105" t="str">
+      <x:c r="K10" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L10" s="105" t="str">
+      <x:c r="L10" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M10" s="105" t="str">
+      <x:c r="M10" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
@@ -2075,43 +2148,43 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="288" hidden="0" customHeight="1">
-      <x:c r="A11" s="104" t="str">
+      <x:c r="A11" s="129" t="str">
         <x:v>F05</x:v>
       </x:c>
-      <x:c r="B11" s="105" t="str">
+      <x:c r="B11" s="130" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C11" s="105" t="str">
+      <x:c r="C11" s="130" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints</x:v>
       </x:c>
-      <x:c r="D11" s="105" t="str">
+      <x:c r="D11" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E11" s="105" t="str">
+      <x:c r="E11" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="105" t="str">
+      <x:c r="F11" s="130" t="str">
         <x:v>Implemented foundation and subsequent browser preference/search retests passed. Remaining separate closeout: approved-original rendered-reference comparison is unverified. No current browser/DB failure is inferred from old history.</x:v>
       </x:c>
-      <x:c r="G11" s="105" t="str">
+      <x:c r="G11" s="130" t="str">
         <x:v>Codex: resolve the separate rendered-reference closeout when authorized; preserve current passing implementation.</x:v>
       </x:c>
-      <x:c r="H11" s="106" t="d">
+      <x:c r="H11" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I11" s="106" t="d">
+      <x:c r="I11" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="105" t="str">
+      <x:c r="J11" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K11" s="105" t="str">
+      <x:c r="K11" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L11" s="105" t="str">
+      <x:c r="L11" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M11" s="105" t="str">
+      <x:c r="M11" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
@@ -2121,43 +2194,43 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="288" hidden="0" customHeight="1">
-      <x:c r="A12" s="104" t="str">
+      <x:c r="A12" s="129" t="str">
         <x:v>F06</x:v>
       </x:c>
-      <x:c r="B12" s="105" t="str">
+      <x:c r="B12" s="130" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C12" s="105" t="str">
+      <x:c r="C12" s="130" t="str">
         <x:v>Light footer, company links, contact and PDPA link</x:v>
       </x:c>
-      <x:c r="D12" s="105" t="str">
+      <x:c r="D12" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E12" s="105" t="str">
+      <x:c r="E12" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="105" t="str">
+      <x:c r="F12" s="130" t="str">
         <x:v>Implemented foundation and subsequent browser preference/search retests passed. Remaining separate closeout: approved-original rendered-reference comparison is unverified. No current browser/DB failure is inferred from old history.</x:v>
       </x:c>
-      <x:c r="G12" s="105" t="str">
+      <x:c r="G12" s="130" t="str">
         <x:v>Codex: resolve the separate rendered-reference closeout when authorized; preserve current passing implementation.</x:v>
       </x:c>
-      <x:c r="H12" s="106" t="d">
+      <x:c r="H12" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="106" t="d">
+      <x:c r="I12" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="105" t="str">
+      <x:c r="J12" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K12" s="105" t="str">
+      <x:c r="K12" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L12" s="105" t="str">
+      <x:c r="L12" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M12" s="105" t="str">
+      <x:c r="M12" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
@@ -2167,43 +2240,43 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="315" hidden="0" customHeight="1">
-      <x:c r="A13" s="104" t="str">
+      <x:c r="A13" s="129" t="str">
         <x:v>F07</x:v>
       </x:c>
-      <x:c r="B13" s="105" t="str">
+      <x:c r="B13" s="130" t="str">
         <x:v>Step 1 · i18n</x:v>
       </x:c>
-      <x:c r="C13" s="105" t="str">
+      <x:c r="C13" s="130" t="str">
         <x:v>Thai/English routes, language switch and localized formatting</x:v>
       </x:c>
-      <x:c r="D13" s="105" t="str">
+      <x:c r="D13" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E13" s="105" t="str">
+      <x:c r="E13" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F13" s="105" t="str">
+      <x:c r="F13" s="130" t="str">
         <x:v>Implemented foundation and subsequent browser preference/search retests passed. Remaining separate closeout: approved-original rendered-reference comparison is unverified. No current browser/DB failure is inferred from old history.</x:v>
       </x:c>
-      <x:c r="G13" s="105" t="str">
+      <x:c r="G13" s="130" t="str">
         <x:v>Codex: resolve the separate rendered-reference closeout when authorized; preserve current passing implementation.</x:v>
       </x:c>
-      <x:c r="H13" s="106" t="d">
+      <x:c r="H13" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I13" s="106" t="d">
+      <x:c r="I13" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J13" s="105" t="str">
+      <x:c r="J13" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K13" s="105" t="str">
+      <x:c r="K13" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L13" s="105" t="str">
+      <x:c r="L13" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M13" s="105" t="str">
+      <x:c r="M13" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
@@ -2213,43 +2286,43 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="139.5" hidden="0" customHeight="1">
-      <x:c r="A14" s="104" t="str">
+      <x:c r="A14" s="129" t="str">
         <x:v>F25</x:v>
       </x:c>
-      <x:c r="B14" s="105" t="str">
+      <x:c r="B14" s="130" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C14" s="105" t="str">
+      <x:c r="C14" s="130" t="str">
         <x:v>Small home listing rows; regional tiles with real listing counts (Steps 3B/7)</x:v>
       </x:c>
-      <x:c r="D14" s="105" t="str">
+      <x:c r="D14" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E14" s="105" t="str">
+      <x:c r="E14" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="105" t="str">
+      <x:c r="F14" s="130" t="str">
         <x:v>Step 3B implements approved topic rows, separate small cards, responsive rails, featured/newest safe queries, saves and honest local samples. Regional tiles/live location counts remain Step 7 and are not implemented. This broad task is therefore Pending; the scoped Step 3B work is R04 Done.</x:v>
       </x:c>
-      <x:c r="G14" s="105" t="str">
+      <x:c r="G14" s="130" t="str">
         <x:v>Codex: wait for Step 7 authorization to add regional tiles/live counts. Future admin row management requires its approved stage. Stop before Step 4 now.</x:v>
       </x:c>
-      <x:c r="H14" s="106" t="d">
+      <x:c r="H14" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I14" s="106" t="d">
+      <x:c r="I14" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="105" t="str">
+      <x:c r="J14" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K14" s="105" t="str">
+      <x:c r="K14" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L14" s="105" t="str">
+      <x:c r="L14" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M14" s="105" t="str">
+      <x:c r="M14" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.
@@ -2258,307 +2331,307 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A15" s="110" t="str">
+      <x:c r="A15" s="132" t="str">
         <x:v>F14</x:v>
       </x:c>
-      <x:c r="B15" s="111" t="str">
+      <x:c r="B15" s="133" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C15" s="111" t="str">
+      <x:c r="C15" s="133" t="str">
         <x:v>Desktop listing/map split and hover/focus pin synchronization</x:v>
       </x:c>
-      <x:c r="D15" s="111" t="str">
+      <x:c r="D15" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="111" t="str">
+      <x:c r="E15" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="111" t="str">
+      <x:c r="F15" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G15" s="111" t="str">
+      <x:c r="G15" s="133" t="str">
         <x:v>Codex: implement only in Step 4 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H15" s="112"/>
-      <x:c r="I15" s="112"/>
-      <x:c r="J15" s="111" t="str">
+      <x:c r="H15" s="134"/>
+      <x:c r="I15" s="134"/>
+      <x:c r="J15" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K15" s="111" t="str">
+      <x:c r="K15" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L15" s="111" t="str">
+      <x:c r="L15" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M15" s="111" t="str">
+      <x:c r="M15" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A16" s="110" t="str">
+      <x:c r="A16" s="132" t="str">
         <x:v>F15</x:v>
       </x:c>
-      <x:c r="B16" s="111" t="str">
+      <x:c r="B16" s="133" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C16" s="111" t="str">
+      <x:c r="C16" s="133" t="str">
         <x:v>Phone full-screen Map/List toggle</x:v>
       </x:c>
-      <x:c r="D16" s="111" t="str">
+      <x:c r="D16" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E16" s="111" t="str">
+      <x:c r="E16" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="111" t="str">
+      <x:c r="F16" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G16" s="111" t="str">
+      <x:c r="G16" s="133" t="str">
         <x:v>Codex: implement only in Step 4 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H16" s="112"/>
-      <x:c r="I16" s="112"/>
-      <x:c r="J16" s="111" t="str">
+      <x:c r="H16" s="134"/>
+      <x:c r="I16" s="134"/>
+      <x:c r="J16" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K16" s="111" t="str">
+      <x:c r="K16" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L16" s="111" t="str">
+      <x:c r="L16" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M16" s="111" t="str">
+      <x:c r="M16" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A17" s="110" t="str">
+      <x:c r="A17" s="132" t="str">
         <x:v>F16</x:v>
       </x:c>
-      <x:c r="B17" s="111" t="str">
+      <x:c r="B17" s="133" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C17" s="111" t="str">
+      <x:c r="C17" s="133" t="str">
         <x:v>Property detail photo grid and full-screen gallery</x:v>
       </x:c>
-      <x:c r="D17" s="111" t="str">
+      <x:c r="D17" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="111" t="str">
+      <x:c r="E17" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="111" t="str">
+      <x:c r="F17" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G17" s="111" t="str">
+      <x:c r="G17" s="133" t="str">
         <x:v>Codex: implement only in Step 5 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H17" s="112"/>
-      <x:c r="I17" s="112"/>
-      <x:c r="J17" s="111" t="str">
+      <x:c r="H17" s="134"/>
+      <x:c r="I17" s="134"/>
+      <x:c r="J17" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K17" s="111" t="str">
+      <x:c r="K17" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L17" s="111" t="str">
+      <x:c r="L17" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M17" s="111" t="str">
+      <x:c r="M17" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A18" s="110" t="str">
+      <x:c r="A18" s="132" t="str">
         <x:v>F17</x:v>
       </x:c>
-      <x:c r="B18" s="111" t="str">
+      <x:c r="B18" s="133" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C18" s="111" t="str">
+      <x:c r="C18" s="133" t="str">
         <x:v>Title, pricing, type-specific facts, long description and sticky tabs</x:v>
       </x:c>
-      <x:c r="D18" s="111" t="str">
+      <x:c r="D18" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="111" t="str">
+      <x:c r="E18" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F18" s="111" t="str">
+      <x:c r="F18" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G18" s="111" t="str">
+      <x:c r="G18" s="133" t="str">
         <x:v>Codex: implement only in Step 5 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H18" s="112"/>
-      <x:c r="I18" s="112"/>
-      <x:c r="J18" s="111" t="str">
+      <x:c r="H18" s="134"/>
+      <x:c r="I18" s="134"/>
+      <x:c r="J18" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K18" s="111" t="str">
+      <x:c r="K18" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L18" s="111" t="str">
+      <x:c r="L18" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M18" s="111" t="str">
+      <x:c r="M18" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A19" s="110" t="str">
+      <x:c r="A19" s="132" t="str">
         <x:v>F18</x:v>
       </x:c>
-      <x:c r="B19" s="111" t="str">
+      <x:c r="B19" s="133" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C19" s="111" t="str">
+      <x:c r="C19" s="133" t="str">
         <x:v>Floorplan/video/360 tabs, verified nearby information and map</x:v>
       </x:c>
-      <x:c r="D19" s="111" t="str">
+      <x:c r="D19" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="111" t="str">
+      <x:c r="E19" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="111" t="str">
+      <x:c r="F19" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G19" s="111" t="str">
+      <x:c r="G19" s="133" t="str">
         <x:v>Codex: implement only in Step 5 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H19" s="112"/>
-      <x:c r="I19" s="112"/>
-      <x:c r="J19" s="111" t="str">
+      <x:c r="H19" s="134"/>
+      <x:c r="I19" s="134"/>
+      <x:c r="J19" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K19" s="111" t="str">
+      <x:c r="K19" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L19" s="111" t="str">
+      <x:c r="L19" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M19" s="111" t="str">
+      <x:c r="M19" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A20" s="110" t="str">
+      <x:c r="A20" s="132" t="str">
         <x:v>F19</x:v>
       </x:c>
-      <x:c r="B20" s="111" t="str">
+      <x:c r="B20" s="133" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C20" s="111" t="str">
+      <x:c r="C20" s="133" t="str">
         <x:v>Mortgage calculator and area comparison when real data exists</x:v>
       </x:c>
-      <x:c r="D20" s="111" t="str">
+      <x:c r="D20" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="111" t="str">
+      <x:c r="E20" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="111" t="str">
+      <x:c r="F20" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G20" s="111" t="str">
+      <x:c r="G20" s="133" t="str">
         <x:v>Codex: implement only in Step 5 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H20" s="112"/>
-      <x:c r="I20" s="112"/>
-      <x:c r="J20" s="111" t="str">
+      <x:c r="H20" s="134"/>
+      <x:c r="I20" s="134"/>
+      <x:c r="J20" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K20" s="111" t="str">
+      <x:c r="K20" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L20" s="111" t="str">
+      <x:c r="L20" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M20" s="111" t="str">
+      <x:c r="M20" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A21" s="110" t="str">
+      <x:c r="A21" s="132" t="str">
         <x:v>F20</x:v>
       </x:c>
-      <x:c r="B21" s="111" t="str">
+      <x:c r="B21" s="133" t="str">
         <x:v>Step 5 · Property</x:v>
       </x:c>
-      <x:c r="C21" s="111" t="str">
+      <x:c r="C21" s="133" t="str">
         <x:v>Same-project units and similar-property cards</x:v>
       </x:c>
-      <x:c r="D21" s="111" t="str">
+      <x:c r="D21" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="111" t="str">
+      <x:c r="E21" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F21" s="111" t="str">
+      <x:c r="F21" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G21" s="111" t="str">
+      <x:c r="G21" s="133" t="str">
         <x:v>Codex: implement only in Step 5 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H21" s="112"/>
-      <x:c r="I21" s="112"/>
-      <x:c r="J21" s="111" t="str">
+      <x:c r="H21" s="134"/>
+      <x:c r="I21" s="134"/>
+      <x:c r="J21" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K21" s="111" t="str">
+      <x:c r="K21" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L21" s="111" t="str">
+      <x:c r="L21" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M21" s="111" t="str">
+      <x:c r="M21" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="99" hidden="0" customHeight="1">
-      <x:c r="A22" s="104" t="str">
+      <x:c r="A22" s="129" t="str">
         <x:v>F21</x:v>
       </x:c>
-      <x:c r="B22" s="105" t="str">
+      <x:c r="B22" s="130" t="str">
         <x:v>Step 6 · Contact</x:v>
       </x:c>
-      <x:c r="C22" s="105" t="str">
+      <x:c r="C22" s="130" t="str">
         <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
       </x:c>
-      <x:c r="D22" s="105" t="str">
+      <x:c r="D22" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E22" s="105" t="str">
+      <x:c r="E22" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F22" s="105" t="str">
+      <x:c r="F22" s="130" t="str">
         <x:v>Partly complete: Card contact dialog and listing-prefilled message exist. Shared submitting form, property contact box and phone bar are unfinished; enquiries cannot be sent.</x:v>
       </x:c>
-      <x:c r="G22" s="105" t="str">
+      <x:c r="G22" s="130" t="str">
         <x:v>Codex: Authorize Step 6, resolve B17/B18 contacts, then implement and test the shared form.</x:v>
       </x:c>
-      <x:c r="H22" s="106"/>
-      <x:c r="I22" s="106" t="d">
+      <x:c r="H22" s="131"/>
+      <x:c r="I22" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J22" s="105" t="str">
+      <x:c r="J22" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K22" s="105" t="str">
+      <x:c r="K22" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L22" s="105" t="str">
+      <x:c r="L22" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M22" s="105" t="str">
+      <x:c r="M22" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.
@@ -2566,583 +2639,557 @@
       </x:c>
     </x:row>
     <x:row r="23" ht="99" hidden="0" customHeight="1">
-      <x:c r="A23" s="104" t="str">
+      <x:c r="A23" s="129" t="str">
         <x:v>F22</x:v>
       </x:c>
-      <x:c r="B23" s="105" t="str">
+      <x:c r="B23" s="130" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C23" s="105" t="str">
+      <x:c r="C23" s="130" t="str">
         <x:v>Single-image hero and compact photography-first layout</x:v>
       </x:c>
-      <x:c r="D23" s="105" t="str">
+      <x:c r="D23" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E23" s="105" t="str">
+      <x:c r="E23" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F23" s="105" t="str">
+      <x:c r="F23" s="130" t="str">
         <x:v>Partly complete: Homepage hero heading, supporting text and foundation layout exist. Approved single-photo hero asset and completed photography layout are missing.</x:v>
       </x:c>
-      <x:c r="G23" s="105" t="str">
+      <x:c r="G23" s="130" t="str">
         <x:v>Codex: Complete approved photography hero in the authorized homepage stage; use an approved genuine asset.</x:v>
       </x:c>
-      <x:c r="H23" s="106"/>
-      <x:c r="I23" s="106" t="d">
+      <x:c r="H23" s="131"/>
+      <x:c r="I23" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J23" s="105" t="str">
+      <x:c r="J23" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K23" s="105" t="str">
+      <x:c r="K23" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L23" s="105" t="str">
+      <x:c r="L23" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M23" s="105" t="str">
+      <x:c r="M23" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Homepage hero heading, supporting text and foundation layout exist. Approved single-photo hero asset and completed photography layout are missing.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="99" hidden="0" customHeight="1">
-      <x:c r="A24" s="104" t="str">
+      <x:c r="A24" s="129" t="str">
         <x:v>F23</x:v>
       </x:c>
-      <x:c r="B24" s="105" t="str">
+      <x:c r="B24" s="130" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C24" s="105" t="str">
+      <x:c r="C24" s="130" t="str">
         <x:v>Shared search box with Buy/Rent/Projects/Investment tabs</x:v>
       </x:c>
-      <x:c r="D24" s="105" t="str">
+      <x:c r="D24" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E24" s="105" t="str">
+      <x:c r="E24" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F24" s="105" t="str">
+      <x:c r="F24" s="130" t="str">
         <x:v>Partly complete: Homepage Buy/Rent/Projects/Investment tabs, text location field, phone sheet and safe buy/rent/invest URL navigation exist. Type/price/beds fields are display-only; full search controls and project results are unfinished.</x:v>
       </x:c>
-      <x:c r="G24" s="105" t="str">
+      <x:c r="G24" s="130" t="str">
         <x:v>Codex: Complete functional shared fields and project search only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H24" s="106"/>
-      <x:c r="I24" s="106" t="d">
+      <x:c r="H24" s="131"/>
+      <x:c r="I24" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J24" s="105" t="str">
+      <x:c r="J24" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K24" s="105" t="str">
+      <x:c r="K24" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L24" s="105" t="str">
+      <x:c r="L24" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M24" s="105" t="str">
+      <x:c r="M24" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Homepage Buy/Rent/Projects/Investment tabs, text location field, phone sheet and safe buy/rent/invest URL navigation exist. Type/price/beds fields are display-only; full search controls and project results are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A25" s="110" t="str">
+      <x:c r="A25" s="132" t="str">
         <x:v>F24</x:v>
       </x:c>
-      <x:c r="B25" s="111" t="str">
+      <x:c r="B25" s="133" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C25" s="111" t="str">
+      <x:c r="C25" s="133" t="str">
         <x:v>Categories, recent searches and location/station suggestions</x:v>
       </x:c>
-      <x:c r="D25" s="111" t="str">
+      <x:c r="D25" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E25" s="111" t="str">
+      <x:c r="E25" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="111" t="str">
+      <x:c r="F25" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G25" s="111" t="str">
+      <x:c r="G25" s="133" t="str">
         <x:v>Codex: implement only in Step 7 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H25" s="112"/>
-      <x:c r="I25" s="112"/>
-      <x:c r="J25" s="111" t="str">
+      <x:c r="H25" s="134"/>
+      <x:c r="I25" s="134"/>
+      <x:c r="J25" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K25" s="111" t="str">
+      <x:c r="K25" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L25" s="111" t="str">
+      <x:c r="L25" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M25" s="111" t="str">
+      <x:c r="M25" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A26" s="110" t="str">
+      <x:c r="A26" s="132" t="str">
         <x:v>F26</x:v>
       </x:c>
-      <x:c r="B26" s="111" t="str">
+      <x:c r="B26" s="133" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C26" s="111" t="str">
+      <x:c r="C26" s="133" t="str">
         <x:v>New projects, tools, services and owner lead CTAs</x:v>
       </x:c>
-      <x:c r="D26" s="111" t="str">
+      <x:c r="D26" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E26" s="111" t="str">
+      <x:c r="E26" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="111" t="str">
+      <x:c r="F26" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G26" s="111" t="str">
+      <x:c r="G26" s="133" t="str">
         <x:v>Codex: implement only in Step 7 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H26" s="112"/>
-      <x:c r="I26" s="112"/>
-      <x:c r="J26" s="111" t="str">
+      <x:c r="H26" s="134"/>
+      <x:c r="I26" s="134"/>
+      <x:c r="J26" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K26" s="111" t="str">
+      <x:c r="K26" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L26" s="111" t="str">
+      <x:c r="L26" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M26" s="111" t="str">
+      <x:c r="M26" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A27" s="110" t="str">
+      <x:c r="A27" s="132" t="str">
         <x:v>F27</x:v>
       </x:c>
-      <x:c r="B27" s="111" t="str">
+      <x:c r="B27" s="133" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C27" s="111" t="str">
+      <x:c r="C27" s="133" t="str">
         <x:v>Projects index and responsive project detail layouts</x:v>
       </x:c>
-      <x:c r="D27" s="111" t="str">
+      <x:c r="D27" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E27" s="111" t="str">
+      <x:c r="E27" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="111" t="str">
+      <x:c r="F27" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G27" s="111" t="str">
+      <x:c r="G27" s="133" t="str">
         <x:v>Codex: implement only in Step 8 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H27" s="112"/>
-      <x:c r="I27" s="112"/>
-      <x:c r="J27" s="111" t="str">
+      <x:c r="H27" s="134"/>
+      <x:c r="I27" s="134"/>
+      <x:c r="J27" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K27" s="111" t="str">
+      <x:c r="K27" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L27" s="111" t="str">
+      <x:c r="L27" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M27" s="111" t="str">
+      <x:c r="M27" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A28" s="110" t="str">
+      <x:c r="A28" s="132" t="str">
         <x:v>F28</x:v>
       </x:c>
-      <x:c r="B28" s="111" t="str">
+      <x:c r="B28" s="133" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C28" s="111" t="str">
+      <x:c r="C28" s="133" t="str">
         <x:v>Unit types, availability, facility chips, progress and brochure</x:v>
       </x:c>
-      <x:c r="D28" s="111" t="str">
+      <x:c r="D28" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E28" s="111" t="str">
+      <x:c r="E28" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="111" t="str">
+      <x:c r="F28" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G28" s="111" t="str">
+      <x:c r="G28" s="133" t="str">
         <x:v>Codex: implement only in Step 8 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H28" s="112"/>
-      <x:c r="I28" s="112"/>
-      <x:c r="J28" s="111" t="str">
+      <x:c r="H28" s="134"/>
+      <x:c r="I28" s="134"/>
+      <x:c r="J28" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K28" s="111" t="str">
+      <x:c r="K28" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L28" s="111" t="str">
+      <x:c r="L28" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M28" s="111" t="str">
+      <x:c r="M28" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A29" s="110" t="str">
+      <x:c r="A29" s="132" t="str">
         <x:v>F29</x:v>
       </x:c>
-      <x:c r="B29" s="111" t="str">
+      <x:c r="B29" s="133" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C29" s="111" t="str">
+      <x:c r="C29" s="133" t="str">
         <x:v>Data-driven clickable project SVG plot plan</x:v>
       </x:c>
-      <x:c r="D29" s="111" t="str">
+      <x:c r="D29" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E29" s="111" t="str">
+      <x:c r="E29" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F29" s="111" t="str">
+      <x:c r="F29" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G29" s="111" t="str">
+      <x:c r="G29" s="133" t="str">
         <x:v>Codex: implement only in Step 8 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H29" s="112"/>
-      <x:c r="I29" s="112"/>
-      <x:c r="J29" s="111" t="str">
+      <x:c r="H29" s="134"/>
+      <x:c r="I29" s="134"/>
+      <x:c r="J29" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K29" s="111" t="str">
+      <x:c r="K29" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L29" s="111" t="str">
+      <x:c r="L29" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M29" s="111" t="str">
+      <x:c r="M29" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A30" s="110" t="str">
+      <x:c r="A30" s="132" t="str">
         <x:v>F30</x:v>
       </x:c>
-      <x:c r="B30" s="111" t="str">
+      <x:c r="B30" s="133" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C30" s="111" t="str">
+      <x:c r="C30" s="133" t="str">
         <x:v>Site visit 3-step form and confirmation screens</x:v>
       </x:c>
-      <x:c r="D30" s="111" t="str">
+      <x:c r="D30" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E30" s="111" t="str">
+      <x:c r="E30" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="111" t="str">
+      <x:c r="F30" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G30" s="111" t="str">
+      <x:c r="G30" s="133" t="str">
         <x:v>Codex: implement only in Step 8 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H30" s="112"/>
-      <x:c r="I30" s="112"/>
-      <x:c r="J30" s="111" t="str">
+      <x:c r="H30" s="134"/>
+      <x:c r="I30" s="134"/>
+      <x:c r="J30" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K30" s="111" t="str">
+      <x:c r="K30" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L30" s="111" t="str">
+      <x:c r="L30" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M30" s="111" t="str">
+      <x:c r="M30" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="99" hidden="0" customHeight="1">
-      <x:c r="A31" s="104" t="str">
+      <x:c r="A31" s="129" t="str">
         <x:v>F31</x:v>
       </x:c>
-      <x:c r="B31" s="105" t="str">
+      <x:c r="B31" s="130" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C31" s="105" t="str">
+      <x:c r="C31" s="130" t="str">
         <x:v>Homes, searches and viewings; local save without account</x:v>
       </x:c>
-      <x:c r="D31" s="105" t="str">
+      <x:c r="D31" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E31" s="105" t="str">
+      <x:c r="E31" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F31" s="105" t="str">
+      <x:c r="F31" s="130" t="str">
         <x:v>Partly complete: Device save hearts, reload persistence and shared storage across both card sizes exist. Saved page Homes/Searches/Viewings and local saved searches are unfinished.</x:v>
       </x:c>
-      <x:c r="G31" s="105" t="str">
+      <x:c r="G31" s="130" t="str">
         <x:v>Codex: Complete Saved page and remaining device workflows under Step 9 authorization.</x:v>
       </x:c>
-      <x:c r="H31" s="106"/>
-      <x:c r="I31" s="106" t="d">
+      <x:c r="H31" s="131"/>
+      <x:c r="I31" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J31" s="105" t="str">
+      <x:c r="J31" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K31" s="105" t="str">
+      <x:c r="K31" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L31" s="105" t="str">
+      <x:c r="L31" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M31" s="105" t="str">
+      <x:c r="M31" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Device save hearts, reload persistence and shared storage across both card sizes exist. Saved page Homes/Searches/Viewings and local saved searches are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A32" s="110" t="str">
+      <x:c r="A32" s="132" t="str">
         <x:v>F33</x:v>
       </x:c>
-      <x:c r="B32" s="111" t="str">
+      <x:c r="B32" s="133" t="str">
         <x:v>Step 10B · Accounts</x:v>
       </x:c>
-      <x:c r="C32" s="111" t="str">
+      <x:c r="C32" s="133" t="str">
         <x:v>Build approved auth and account screens only after approval</x:v>
       </x:c>
-      <x:c r="D32" s="111" t="str">
+      <x:c r="D32" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E32" s="111" t="str">
+      <x:c r="E32" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F32" s="111" t="str">
+      <x:c r="F32" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G32" s="111" t="str">
+      <x:c r="G32" s="133" t="str">
         <x:v>Codex: implement only in Step 10B after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H32" s="112"/>
-      <x:c r="I32" s="112"/>
-      <x:c r="J32" s="111" t="str">
+      <x:c r="H32" s="134"/>
+      <x:c r="I32" s="134"/>
+      <x:c r="J32" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K32" s="111" t="str">
+      <x:c r="K32" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L32" s="111" t="str">
+      <x:c r="L32" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M32" s="111" t="str">
+      <x:c r="M32" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A33" s="110" t="str">
+      <x:c r="A33" s="132" t="str">
         <x:v>F35</x:v>
       </x:c>
-      <x:c r="B33" s="111" t="str">
+      <x:c r="B33" s="133" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C33" s="111" t="str">
+      <x:c r="C33" s="133" t="str">
         <x:v>Admin listing, media, project, agent and enquiry interfaces</x:v>
       </x:c>
-      <x:c r="D33" s="111" t="str">
+      <x:c r="D33" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E33" s="111" t="str">
+      <x:c r="E33" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F33" s="111" t="str">
+      <x:c r="F33" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G33" s="111" t="str">
+      <x:c r="G33" s="133" t="str">
         <x:v>Codex: implement only in Step 11B after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H33" s="112"/>
-      <x:c r="I33" s="112"/>
-      <x:c r="J33" s="111" t="str">
+      <x:c r="H33" s="134"/>
+      <x:c r="I33" s="134"/>
+      <x:c r="J33" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K33" s="111" t="str">
+      <x:c r="K33" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L33" s="111" t="str">
+      <x:c r="L33" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M33" s="111" t="str">
+      <x:c r="M33" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A34" s="110" t="str">
+      <x:c r="A34" s="132" t="str">
         <x:v>F36</x:v>
       </x:c>
-      <x:c r="B34" s="111" t="str">
+      <x:c r="B34" s="133" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C34" s="111" t="str">
+      <x:c r="C34" s="133" t="str">
         <x:v>Admin-managed searchable filter editor with type safety</x:v>
       </x:c>
-      <x:c r="D34" s="111" t="str">
+      <x:c r="D34" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E34" s="111" t="str">
+      <x:c r="E34" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F34" s="111" t="str">
+      <x:c r="F34" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G34" s="111" t="str">
+      <x:c r="G34" s="133" t="str">
         <x:v>Codex: implement only in Step 11B after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H34" s="112"/>
-      <x:c r="I34" s="112"/>
-      <x:c r="J34" s="111" t="str">
+      <x:c r="H34" s="134"/>
+      <x:c r="I34" s="134"/>
+      <x:c r="J34" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K34" s="111" t="str">
+      <x:c r="K34" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L34" s="111" t="str">
+      <x:c r="L34" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M34" s="111" t="str">
+      <x:c r="M34" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A35" s="110" t="str">
+      <x:c r="A35" s="132" t="str">
         <x:v>F37</x:v>
       </x:c>
-      <x:c r="B35" s="111" t="str">
+      <x:c r="B35" s="133" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C35" s="111" t="str">
+      <x:c r="C35" s="133" t="str">
         <x:v>A11y/SEO/hreflang/structured data/mobile responsive audit</x:v>
       </x:c>
-      <x:c r="D35" s="111" t="str">
+      <x:c r="D35" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E35" s="111" t="str">
+      <x:c r="E35" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F35" s="111" t="str">
+      <x:c r="F35" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G35" s="111" t="str">
+      <x:c r="G35" s="133" t="str">
         <x:v>Codex: implement only in Step 12 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H35" s="112"/>
-      <x:c r="I35" s="112"/>
-      <x:c r="J35" s="111" t="str">
+      <x:c r="H35" s="134"/>
+      <x:c r="I35" s="134"/>
+      <x:c r="J35" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K35" s="111" t="str">
+      <x:c r="K35" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L35" s="111" t="str">
+      <x:c r="L35" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M35" s="111" t="str">
+      <x:c r="M35" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A36" s="110" t="str">
+      <x:c r="A36" s="132" t="str">
         <x:v>F38</x:v>
       </x:c>
-      <x:c r="B36" s="111" t="str">
+      <x:c r="B36" s="133" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C36" s="111" t="str">
+      <x:c r="C36" s="133" t="str">
         <x:v>LCP, INP, CLS, image and bundle optimization with measurements</x:v>
       </x:c>
-      <x:c r="D36" s="111" t="str">
+      <x:c r="D36" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E36" s="111" t="str">
+      <x:c r="E36" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F36" s="111" t="str">
+      <x:c r="F36" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G36" s="111" t="str">
+      <x:c r="G36" s="133" t="str">
         <x:v>Codex: implement only in Step 12 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H36" s="112"/>
-      <x:c r="I36" s="112"/>
-      <x:c r="J36" s="111" t="str">
+      <x:c r="H36" s="134"/>
+      <x:c r="I36" s="134"/>
+      <x:c r="J36" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K36" s="111" t="str">
+      <x:c r="K36" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L36" s="111" t="str">
+      <x:c r="L36" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M36" s="111" t="str">
+      <x:c r="M36" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A37" s="110" t="str">
-        <x:v>F39</x:v>
-      </x:c>
-      <x:c r="B37" s="111" t="str">
-        <x:v>Step 3C · Motion</x:v>
-      </x:c>
-      <x:c r="C37" s="111" t="str">
-        <x:v>Shared smooth motion for rows, card photos, dialogs, sheets and controls</x:v>
-      </x:c>
-      <x:c r="D37" s="111" t="str">
-        <x:v>Frontend</x:v>
-      </x:c>
-      <x:c r="E37" s="111" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F37" s="111" t="str">
-        <x:v>Owner revised V5/BUILD-SPEC to add Step 3C. No shared motion helper/tokens, card-edge animated row scrolling, photo slides or dialog/sheet transitions have been implemented. Existing reduced-motion reset alone does not complete this task.</x:v>
-      </x:c>
-      <x:c r="G37" s="111" t="str">
-        <x:v>Owner: authorize Step 3C. Codex: implement and test only after that prompt.</x:v>
-      </x:c>
-      <x:c r="H37" s="112" t="d">
-        <x:v>2026-10-10T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="I37" s="112" t="d">
-        <x:v>2026-10-10T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="J37" s="111" t="str">
-        <x:v>Not run: Step 3C implementation has not started.</x:v>
-      </x:c>
-      <x:c r="K37" s="111" t="str">
-        <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
-      </x:c>
-      <x:c r="L37" s="111" t="str">
-        <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
-      </x:c>
-      <x:c r="M37" s="111" t="str">
-        <x:v>2026-10-10 R05: recorded newly supplied Step 3C as unstarted; no implementation authorization is inferred from attached guide text.</x:v>
-      </x:c>
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+      <x:c r="H37"/>
+      <x:c r="I37"/>
+      <x:c r="J37"/>
+      <x:c r="K37"/>
+      <x:c r="L37"/>
+      <x:c r="M37"/>
     </x:row>
     <x:row r="38" ht="26" customHeight="1">
       <x:c r="A38"/>
@@ -10112,7 +10159,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra70697d851f1441e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rded70e99d6bc4fe9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10152,7 +10199,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>Done = completed task scope with evidence. Pending = started/blocked with named remaining work. Not started = task implementation has not begun. History is dated past evidence.</x:v>
+        <x:v>2026-10-10 Step 3C: F39 Done. 86 permanent IDs: 21 Done, 23 Pending, 42 Not started. All prior IDs and dated history retained; independent remaining tasks unchanged.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -10174,7 +10221,7 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -10193,7 +10240,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -10238,43 +10285,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="153" hidden="0" customHeight="1">
-      <x:c r="A6" s="104" t="str">
+      <x:c r="A6" s="129" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B6" s="105" t="str">
+      <x:c r="B6" s="130" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C6" s="105" t="str">
+      <x:c r="C6" s="130" t="str">
         <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
-      <x:c r="D6" s="105" t="str">
+      <x:c r="D6" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E6" s="105" t="str">
+      <x:c r="E6" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="105" t="str">
+      <x:c r="F6" s="130" t="str">
         <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
-      <x:c r="G6" s="105" t="str">
+      <x:c r="G6" s="130" t="str">
         <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
       </x:c>
-      <x:c r="H6" s="106" t="d">
+      <x:c r="H6" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="106" t="d">
+      <x:c r="I6" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="105" t="str">
+      <x:c r="J6" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K6" s="105" t="str">
+      <x:c r="K6" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L6" s="105" t="str">
+      <x:c r="L6" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M6" s="105" t="str">
+      <x:c r="M6" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
 2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
@@ -10283,83 +10330,83 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="99" hidden="0" customHeight="1">
-      <x:c r="A7" s="104" t="str">
+      <x:c r="A7" s="129" t="str">
         <x:v>B17</x:v>
       </x:c>
-      <x:c r="B7" s="105" t="str">
+      <x:c r="B7" s="130" t="str">
         <x:v>Decision · Leads</x:v>
       </x:c>
-      <x:c r="C7" s="105" t="str">
+      <x:c r="C7" s="130" t="str">
         <x:v>Approve shared inbox versus listing agent enquiry destination</x:v>
       </x:c>
-      <x:c r="D7" s="105" t="str">
+      <x:c r="D7" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E7" s="105" t="str">
+      <x:c r="E7" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="105" t="str">
+      <x:c r="F7" s="130" t="str">
         <x:v>BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
-      <x:c r="G7" s="105" t="str">
+      <x:c r="G7" s="130" t="str">
         <x:v>Owner: select routing mode and mailbox</x:v>
       </x:c>
-      <x:c r="H7" s="106"/>
-      <x:c r="I7" s="106" t="d">
+      <x:c r="H7" s="131"/>
+      <x:c r="I7" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="105" t="str">
+      <x:c r="J7" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K7" s="105" t="str">
+      <x:c r="K7" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L7" s="105" t="str">
+      <x:c r="L7" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M7" s="105" t="str">
+      <x:c r="M7" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="126" hidden="0" customHeight="1">
-      <x:c r="A8" s="104" t="str">
+      <x:c r="A8" s="129" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B8" s="105" t="str">
+      <x:c r="B8" s="130" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C8" s="105" t="str">
+      <x:c r="C8" s="130" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D8" s="105" t="str">
+      <x:c r="D8" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="105" t="str">
+      <x:c r="E8" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="105" t="str">
+      <x:c r="F8" s="130" t="str">
         <x:v>Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending.</x:v>
       </x:c>
-      <x:c r="G8" s="105" t="str">
+      <x:c r="G8" s="130" t="str">
         <x:v>Owner: provide actual contacts/routing; Codex: integrate and review accessible contact actions later.</x:v>
       </x:c>
-      <x:c r="H8" s="106" t="d">
+      <x:c r="H8" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I8" s="106" t="d">
+      <x:c r="I8" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="105" t="str">
+      <x:c r="J8" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K8" s="105" t="str">
+      <x:c r="K8" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L8" s="105" t="str">
+      <x:c r="L8" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M8" s="105" t="str">
+      <x:c r="M8" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: BUILD-SPEC §12 #4 unresolved
 2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.
@@ -10368,81 +10415,81 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="99" hidden="0" customHeight="1">
-      <x:c r="A9" s="104" t="str">
+      <x:c r="A9" s="129" t="str">
         <x:v>B23</x:v>
       </x:c>
-      <x:c r="B9" s="105" t="str">
+      <x:c r="B9" s="130" t="str">
         <x:v>Decision · Accounts</x:v>
       </x:c>
-      <x:c r="C9" s="105" t="str">
+      <x:c r="C9" s="130" t="str">
         <x:v>Approve LINE only or LINE+Google+email sign-in</x:v>
       </x:c>
-      <x:c r="D9" s="105" t="str">
+      <x:c r="D9" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E9" s="105" t="str">
+      <x:c r="E9" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="105" t="str">
+      <x:c r="F9" s="130" t="str">
         <x:v>BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
-      <x:c r="G9" s="105" t="str">
+      <x:c r="G9" s="130" t="str">
         <x:v>Owner: approve authentication providers</x:v>
       </x:c>
-      <x:c r="H9" s="106"/>
-      <x:c r="I9" s="106" t="d">
+      <x:c r="H9" s="131"/>
+      <x:c r="I9" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J9" s="105" t="str">
+      <x:c r="J9" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K9" s="105" t="str">
+      <x:c r="K9" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L9" s="105" t="str">
+      <x:c r="L9" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M9" s="105" t="str">
+      <x:c r="M9" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="99" hidden="0" customHeight="1">
-      <x:c r="A10" s="104" t="str">
+      <x:c r="A10" s="129" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B10" s="105" t="str">
+      <x:c r="B10" s="130" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C10" s="105" t="str">
+      <x:c r="C10" s="130" t="str">
         <x:v>USD/THB preference and approximate conversion with an approved rate source</x:v>
       </x:c>
-      <x:c r="D10" s="105" t="str">
+      <x:c r="D10" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="105" t="str">
+      <x:c r="E10" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="105" t="str">
+      <x:c r="F10" s="130" t="str">
         <x:v>Partly complete: owner approved USD and THB, THB storage and preference selection. Approximate USD conversion still needs an approved rate source and implementation.</x:v>
       </x:c>
-      <x:c r="G10" s="105" t="str">
+      <x:c r="G10" s="130" t="str">
         <x:v>Owner/Codex: choose rate source in authorized currency work, then implement and verify conversion.</x:v>
       </x:c>
-      <x:c r="H10" s="106"/>
-      <x:c r="I10" s="106" t="d">
+      <x:c r="H10" s="131"/>
+      <x:c r="I10" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="105" t="str">
+      <x:c r="J10" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K10" s="105" t="str">
+      <x:c r="K10" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L10" s="105" t="str">
+      <x:c r="L10" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M10" s="105" t="str">
+      <x:c r="M10" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: BUILD-SPEC §12 #6 unresolved
 2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.
@@ -10450,43 +10497,43 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="396" hidden="0" customHeight="1">
-      <x:c r="A11" s="104" t="str">
+      <x:c r="A11" s="129" t="str">
         <x:v>R01</x:v>
       </x:c>
-      <x:c r="B11" s="105" t="str">
+      <x:c r="B11" s="130" t="str">
         <x:v>Step 0 · Preparation</x:v>
       </x:c>
-      <x:c r="C11" s="105" t="str">
+      <x:c r="C11" s="130" t="str">
         <x:v>Inspect project; establish permanent rules, documentation, Git/live mirror and tracker</x:v>
       </x:c>
-      <x:c r="D11" s="105" t="str">
+      <x:c r="D11" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E11" s="105" t="str">
+      <x:c r="E11" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="105" t="str">
+      <x:c r="F11" s="130" t="str">
         <x:v>Preparation, rules, documentation, tracker and source mirror exist. A reusable in-project tracker-update utility and approved-original rendered-reference review remain unfinished. This one-off workbook correction does not complete those deliverables.</x:v>
       </x:c>
-      <x:c r="G11" s="105" t="str">
+      <x:c r="G11" s="130" t="str">
         <x:v>Codex: complete the separate utility/reference-review scope when authorized.</x:v>
       </x:c>
-      <x:c r="H11" s="106" t="d">
+      <x:c r="H11" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I11" s="106" t="d">
+      <x:c r="I11" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="105" t="str">
+      <x:c r="J11" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K11" s="105" t="str">
+      <x:c r="K11" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L11" s="105" t="str">
+      <x:c r="L11" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M11" s="105" t="str">
+      <x:c r="M11" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
@@ -10501,773 +10548,773 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="99" hidden="0" customHeight="1">
-      <x:c r="A12" s="104" t="str">
+      <x:c r="A12" s="129" t="str">
         <x:v>B08</x:v>
       </x:c>
-      <x:c r="B12" s="105" t="str">
+      <x:c r="B12" s="130" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C12" s="105" t="str">
+      <x:c r="C12" s="130" t="str">
         <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
       </x:c>
-      <x:c r="D12" s="105" t="str">
+      <x:c r="D12" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E12" s="105" t="str">
+      <x:c r="E12" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="105" t="str">
+      <x:c r="F12" s="130" t="str">
         <x:v>Partly complete: Bounding-coordinate index, validated bbox search and hidden-location exclusion exist in the schema/search layer. Map pins, geographic integration and full map-stage verification are unfinished.</x:v>
       </x:c>
-      <x:c r="G12" s="105" t="str">
+      <x:c r="G12" s="130" t="str">
         <x:v>Codex: Complete geospatial/map behavior under Step 4 after B09 choice; preserve hidden-location privacy.</x:v>
       </x:c>
-      <x:c r="H12" s="106"/>
-      <x:c r="I12" s="106" t="d">
+      <x:c r="H12" s="131"/>
+      <x:c r="I12" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="105" t="str">
+      <x:c r="J12" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K12" s="105" t="str">
+      <x:c r="K12" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L12" s="105" t="str">
+      <x:c r="L12" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M12" s="105" t="str">
+      <x:c r="M12" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Bounding-coordinate index, validated bbox search and hidden-location exclusion exist in the schema/search layer. Map pins, geographic integration and full map-stage verification are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A13" s="110" t="str">
+      <x:c r="A13" s="132" t="str">
         <x:v>B10</x:v>
       </x:c>
-      <x:c r="B13" s="111" t="str">
+      <x:c r="B13" s="133" t="str">
         <x:v>Step 4 · Nearby</x:v>
       </x:c>
-      <x:c r="C13" s="111" t="str">
+      <x:c r="C13" s="133" t="str">
         <x:v>Provider-backed nearby data ingest and 90-day refresh</x:v>
       </x:c>
-      <x:c r="D13" s="111" t="str">
+      <x:c r="D13" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E13" s="111" t="str">
+      <x:c r="E13" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="111" t="str">
+      <x:c r="F13" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G13" s="111" t="str">
+      <x:c r="G13" s="133" t="str">
         <x:v>Codex: implement only in Step 4 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H13" s="112"/>
-      <x:c r="I13" s="112"/>
-      <x:c r="J13" s="111" t="str">
+      <x:c r="H13" s="134"/>
+      <x:c r="I13" s="134"/>
+      <x:c r="J13" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K13" s="111" t="str">
+      <x:c r="K13" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L13" s="111" t="str">
+      <x:c r="L13" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M13" s="111" t="str">
+      <x:c r="M13" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="99" hidden="0" customHeight="1">
-      <x:c r="A14" s="104" t="str">
+      <x:c r="A14" s="129" t="str">
         <x:v>B11</x:v>
       </x:c>
-      <x:c r="B14" s="105" t="str">
+      <x:c r="B14" s="130" t="str">
         <x:v>Step 5 · Media</x:v>
       </x:c>
-      <x:c r="C14" s="105" t="str">
+      <x:c r="C14" s="130" t="str">
         <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
       </x:c>
-      <x:c r="D14" s="105" t="str">
+      <x:c r="D14" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E14" s="105" t="str">
+      <x:c r="E14" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="105" t="str">
+      <x:c r="F14" s="130" t="str">
         <x:v>Partly complete: Photo/floorplan/video/360 metadata, safe URL constraints and capped photo reads exist. Upload pipeline, file validation and production media handling are unfinished.</x:v>
       </x:c>
-      <x:c r="G14" s="105" t="str">
+      <x:c r="G14" s="130" t="str">
         <x:v>Codex: Complete and test safe media ingestion/upload in its authorized stage.</x:v>
       </x:c>
-      <x:c r="H14" s="106"/>
-      <x:c r="I14" s="106" t="d">
+      <x:c r="H14" s="131"/>
+      <x:c r="I14" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="105" t="str">
+      <x:c r="J14" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K14" s="105" t="str">
+      <x:c r="K14" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L14" s="105" t="str">
+      <x:c r="L14" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M14" s="105" t="str">
+      <x:c r="M14" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Photo/floorplan/video/360 metadata, safe URL constraints and capped photo reads exist. Upload pipeline, file validation and production media handling are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A15" s="110" t="str">
+      <x:c r="A15" s="132" t="str">
         <x:v>B12</x:v>
       </x:c>
-      <x:c r="B15" s="111" t="str">
+      <x:c r="B15" s="133" t="str">
         <x:v>Step 5 · Similar</x:v>
       </x:c>
-      <x:c r="C15" s="111" t="str">
+      <x:c r="C15" s="133" t="str">
         <x:v>Same-location/type/intent matching with ±25% price fallback</x:v>
       </x:c>
-      <x:c r="D15" s="111" t="str">
+      <x:c r="D15" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E15" s="111" t="str">
+      <x:c r="E15" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F15" s="111" t="str">
+      <x:c r="F15" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G15" s="111" t="str">
+      <x:c r="G15" s="133" t="str">
         <x:v>Codex: implement only in Step 5 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H15" s="112"/>
-      <x:c r="I15" s="112"/>
-      <x:c r="J15" s="111" t="str">
+      <x:c r="H15" s="134"/>
+      <x:c r="I15" s="134"/>
+      <x:c r="J15" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K15" s="111" t="str">
+      <x:c r="K15" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L15" s="111" t="str">
+      <x:c r="L15" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M15" s="111" t="str">
+      <x:c r="M15" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A16" s="110" t="str">
+      <x:c r="A16" s="132" t="str">
         <x:v>B13</x:v>
       </x:c>
-      <x:c r="B16" s="111" t="str">
+      <x:c r="B16" s="133" t="str">
         <x:v>Step 5 · Metrics</x:v>
       </x:c>
-      <x:c r="C16" s="111" t="str">
+      <x:c r="C16" s="133" t="str">
         <x:v>Comparable pricing/yield gated by verified sample size</x:v>
       </x:c>
-      <x:c r="D16" s="111" t="str">
+      <x:c r="D16" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E16" s="111" t="str">
+      <x:c r="E16" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F16" s="111" t="str">
+      <x:c r="F16" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G16" s="111" t="str">
+      <x:c r="G16" s="133" t="str">
         <x:v>Codex: implement only in Step 5 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H16" s="112"/>
-      <x:c r="I16" s="112"/>
-      <x:c r="J16" s="111" t="str">
+      <x:c r="H16" s="134"/>
+      <x:c r="I16" s="134"/>
+      <x:c r="J16" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K16" s="111" t="str">
+      <x:c r="K16" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L16" s="111" t="str">
+      <x:c r="L16" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M16" s="111" t="str">
+      <x:c r="M16" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A17" s="110" t="str">
+      <x:c r="A17" s="132" t="str">
         <x:v>B14</x:v>
       </x:c>
-      <x:c r="B17" s="111" t="str">
+      <x:c r="B17" s="133" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C17" s="111" t="str">
+      <x:c r="C17" s="133" t="str">
         <x:v>Enquiry API validation and DB-first persist-before-notify flow</x:v>
       </x:c>
-      <x:c r="D17" s="111" t="str">
+      <x:c r="D17" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E17" s="111" t="str">
+      <x:c r="E17" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F17" s="111" t="str">
+      <x:c r="F17" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G17" s="111" t="str">
+      <x:c r="G17" s="133" t="str">
         <x:v>Codex: implement only in Step 6 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H17" s="112"/>
-      <x:c r="I17" s="112"/>
-      <x:c r="J17" s="111" t="str">
+      <x:c r="H17" s="134"/>
+      <x:c r="I17" s="134"/>
+      <x:c r="J17" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K17" s="111" t="str">
+      <x:c r="K17" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L17" s="111" t="str">
+      <x:c r="L17" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M17" s="111" t="str">
+      <x:c r="M17" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="99" hidden="0" customHeight="1">
-      <x:c r="A18" s="104" t="str">
+      <x:c r="A18" s="129" t="str">
         <x:v>B15</x:v>
       </x:c>
-      <x:c r="B18" s="105" t="str">
+      <x:c r="B18" s="130" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C18" s="105" t="str">
+      <x:c r="C18" s="130" t="str">
         <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
       </x:c>
-      <x:c r="D18" s="105" t="str">
+      <x:c r="D18" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E18" s="105" t="str">
+      <x:c r="E18" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F18" s="105" t="str">
+      <x:c r="F18" s="130" t="str">
         <x:v>Partly complete: Enquiry schema stores versioned consent, consent timestamp, source URL, UTM, language and audit dates. Isolated DB fixture readback passed. Live form capture and request validation are unfinished.</x:v>
       </x:c>
-      <x:c r="G18" s="105" t="str">
+      <x:c r="G18" s="130" t="str">
         <x:v>Codex: Implement and verify real request-to-database metadata capture under Step 6.</x:v>
       </x:c>
-      <x:c r="H18" s="106"/>
-      <x:c r="I18" s="106" t="d">
+      <x:c r="H18" s="131"/>
+      <x:c r="I18" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J18" s="105" t="str">
+      <x:c r="J18" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K18" s="105" t="str">
+      <x:c r="K18" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L18" s="105" t="str">
+      <x:c r="L18" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M18" s="105" t="str">
+      <x:c r="M18" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Enquiry schema stores versioned consent, consent timestamp, source URL, UTM, language and audit dates. Isolated DB fixture readback passed. Live form capture and request validation are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A19" s="110" t="str">
+      <x:c r="A19" s="132" t="str">
         <x:v>B16</x:v>
       </x:c>
-      <x:c r="B19" s="111" t="str">
+      <x:c r="B19" s="133" t="str">
         <x:v>Step 6 · Security</x:v>
       </x:c>
-      <x:c r="C19" s="111" t="str">
+      <x:c r="C19" s="133" t="str">
         <x:v>Rate limits, honeypot and duplicate submission protection</x:v>
       </x:c>
-      <x:c r="D19" s="111" t="str">
+      <x:c r="D19" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E19" s="111" t="str">
+      <x:c r="E19" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F19" s="111" t="str">
+      <x:c r="F19" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G19" s="111" t="str">
+      <x:c r="G19" s="133" t="str">
         <x:v>Codex: implement only in Step 6 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H19" s="112"/>
-      <x:c r="I19" s="112"/>
-      <x:c r="J19" s="111" t="str">
+      <x:c r="H19" s="134"/>
+      <x:c r="I19" s="134"/>
+      <x:c r="J19" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K19" s="111" t="str">
+      <x:c r="K19" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L19" s="111" t="str">
+      <x:c r="L19" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M19" s="111" t="str">
+      <x:c r="M19" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A20" s="110" t="str">
+      <x:c r="A20" s="132" t="str">
         <x:v>B19</x:v>
       </x:c>
-      <x:c r="B20" s="111" t="str">
+      <x:c r="B20" s="133" t="str">
         <x:v>Step 6 · Chat</x:v>
       </x:c>
-      <x:c r="C20" s="111" t="str">
+      <x:c r="C20" s="133" t="str">
         <x:v>Validated LINE/WhatsApp URLs and click event tracking</x:v>
       </x:c>
-      <x:c r="D20" s="111" t="str">
+      <x:c r="D20" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E20" s="111" t="str">
+      <x:c r="E20" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F20" s="111" t="str">
+      <x:c r="F20" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G20" s="111" t="str">
+      <x:c r="G20" s="133" t="str">
         <x:v>Codex: implement only in Step 6 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H20" s="112"/>
-      <x:c r="I20" s="112"/>
-      <x:c r="J20" s="111" t="str">
+      <x:c r="H20" s="134"/>
+      <x:c r="I20" s="134"/>
+      <x:c r="J20" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K20" s="111" t="str">
+      <x:c r="K20" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L20" s="111" t="str">
+      <x:c r="L20" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M20" s="111" t="str">
+      <x:c r="M20" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="99" hidden="0" customHeight="1">
-      <x:c r="A21" s="104" t="str">
+      <x:c r="A21" s="129" t="str">
         <x:v>B20</x:v>
       </x:c>
-      <x:c r="B21" s="105" t="str">
+      <x:c r="B21" s="130" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C21" s="105" t="str">
+      <x:c r="C21" s="130" t="str">
         <x:v>Project/unit/plot status logic and validation</x:v>
       </x:c>
-      <x:c r="D21" s="105" t="str">
+      <x:c r="D21" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E21" s="105" t="str">
+      <x:c r="E21" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F21" s="105" t="str">
+      <x:c r="F21" s="130" t="str">
         <x:v>Partly complete: Project/unit/plot schema, status enums and parent/shape/value constraints exist; DB joins/constraint fixtures passed. Application status transitions and booking/business validation are unfinished.</x:v>
       </x:c>
-      <x:c r="G21" s="105" t="str">
+      <x:c r="G21" s="130" t="str">
         <x:v>Codex: Complete project/plot business behavior under Step 8 authorization.</x:v>
       </x:c>
-      <x:c r="H21" s="106"/>
-      <x:c r="I21" s="106" t="d">
+      <x:c r="H21" s="131"/>
+      <x:c r="I21" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J21" s="105" t="str">
+      <x:c r="J21" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K21" s="105" t="str">
+      <x:c r="K21" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L21" s="105" t="str">
+      <x:c r="L21" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M21" s="105" t="str">
+      <x:c r="M21" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Project/unit/plot schema, status enums and parent/shape/value constraints exist; DB joins/constraint fixtures passed. Application status transitions and booking/business validation are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A22" s="110" t="str">
+      <x:c r="A22" s="132" t="str">
         <x:v>B21</x:v>
       </x:c>
-      <x:c r="B22" s="111" t="str">
+      <x:c r="B22" s="133" t="str">
         <x:v>Step 8 · Booking</x:v>
       </x:c>
-      <x:c r="C22" s="111" t="str">
+      <x:c r="C22" s="133" t="str">
         <x:v>Site-visit availability and enquiry persistence, double-book protection</x:v>
       </x:c>
-      <x:c r="D22" s="111" t="str">
+      <x:c r="D22" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E22" s="111" t="str">
+      <x:c r="E22" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F22" s="111" t="str">
+      <x:c r="F22" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G22" s="111" t="str">
+      <x:c r="G22" s="133" t="str">
         <x:v>Codex: implement only in Step 8 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H22" s="112"/>
-      <x:c r="I22" s="112"/>
-      <x:c r="J22" s="111" t="str">
+      <x:c r="H22" s="134"/>
+      <x:c r="I22" s="134"/>
+      <x:c r="J22" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K22" s="111" t="str">
+      <x:c r="K22" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L22" s="111" t="str">
+      <x:c r="L22" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M22" s="111" t="str">
+      <x:c r="M22" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="99" hidden="0" customHeight="1">
-      <x:c r="A23" s="104" t="str">
+      <x:c r="A23" s="129" t="str">
         <x:v>B22</x:v>
       </x:c>
-      <x:c r="B23" s="105" t="str">
+      <x:c r="B23" s="130" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C23" s="105" t="str">
+      <x:c r="C23" s="130" t="str">
         <x:v>Saved listings/searches persistence, new-match calculations</x:v>
       </x:c>
-      <x:c r="D23" s="105" t="str">
+      <x:c r="D23" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E23" s="105" t="str">
+      <x:c r="E23" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F23" s="105" t="str">
+      <x:c r="F23" s="130" t="str">
         <x:v>Partly complete: Saved-listing/search tables and constraints exist; card hearts persist on this device. Authenticated save operations, saved-search workflows and new-match calculations are unfinished.</x:v>
       </x:c>
-      <x:c r="G23" s="105" t="str">
+      <x:c r="G23" s="130" t="str">
         <x:v>Codex: Complete persistence and new-match workflows under the authorized Saved/account stages.</x:v>
       </x:c>
-      <x:c r="H23" s="106"/>
-      <x:c r="I23" s="106" t="d">
+      <x:c r="H23" s="131"/>
+      <x:c r="I23" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J23" s="105" t="str">
+      <x:c r="J23" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K23" s="105" t="str">
+      <x:c r="K23" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L23" s="105" t="str">
+      <x:c r="L23" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M23" s="105" t="str">
+      <x:c r="M23" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Saved-listing/search tables and constraints exist; card hearts persist on this device. Authenticated save operations, saved-search workflows and new-match calculations are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A24" s="110" t="str">
+      <x:c r="A24" s="132" t="str">
         <x:v>B24</x:v>
       </x:c>
-      <x:c r="B24" s="111" t="str">
+      <x:c r="B24" s="133" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C24" s="111" t="str">
+      <x:c r="C24" s="133" t="str">
         <x:v>Secure sessions, approved sign-in integrations and auth tests</x:v>
       </x:c>
-      <x:c r="D24" s="111" t="str">
+      <x:c r="D24" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E24" s="111" t="str">
+      <x:c r="E24" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F24" s="111" t="str">
+      <x:c r="F24" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G24" s="111" t="str">
+      <x:c r="G24" s="133" t="str">
         <x:v>Codex: implement only in Step 10B after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H24" s="112"/>
-      <x:c r="I24" s="112"/>
-      <x:c r="J24" s="111" t="str">
+      <x:c r="H24" s="134"/>
+      <x:c r="I24" s="134"/>
+      <x:c r="J24" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K24" s="111" t="str">
+      <x:c r="K24" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L24" s="111" t="str">
+      <x:c r="L24" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M24" s="111" t="str">
+      <x:c r="M24" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A25" s="110" t="str">
+      <x:c r="A25" s="132" t="str">
         <x:v>B25</x:v>
       </x:c>
-      <x:c r="B25" s="111" t="str">
+      <x:c r="B25" s="133" t="str">
         <x:v>Step 10B · Auth</x:v>
       </x:c>
-      <x:c r="C25" s="111" t="str">
+      <x:c r="C25" s="133" t="str">
         <x:v>Account/localStorage saved-item merge and privacy isolation</x:v>
       </x:c>
-      <x:c r="D25" s="111" t="str">
+      <x:c r="D25" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E25" s="111" t="str">
+      <x:c r="E25" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F25" s="111" t="str">
+      <x:c r="F25" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G25" s="111" t="str">
+      <x:c r="G25" s="133" t="str">
         <x:v>Codex: implement only in Step 10B after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H25" s="112"/>
-      <x:c r="I25" s="112"/>
-      <x:c r="J25" s="111" t="str">
+      <x:c r="H25" s="134"/>
+      <x:c r="I25" s="134"/>
+      <x:c r="J25" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K25" s="111" t="str">
+      <x:c r="K25" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L25" s="111" t="str">
+      <x:c r="L25" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M25" s="111" t="str">
+      <x:c r="M25" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A26" s="110" t="str">
+      <x:c r="A26" s="132" t="str">
         <x:v>B26</x:v>
       </x:c>
-      <x:c r="B26" s="111" t="str">
+      <x:c r="B26" s="133" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C26" s="111" t="str">
+      <x:c r="C26" s="133" t="str">
         <x:v>Role-scoped CRUD for listings, images, projects, agents, filter config</x:v>
       </x:c>
-      <x:c r="D26" s="111" t="str">
+      <x:c r="D26" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E26" s="111" t="str">
+      <x:c r="E26" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F26" s="111" t="str">
+      <x:c r="F26" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G26" s="111" t="str">
+      <x:c r="G26" s="133" t="str">
         <x:v>Codex: implement only in Step 11B after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H26" s="112"/>
-      <x:c r="I26" s="112"/>
-      <x:c r="J26" s="111" t="str">
+      <x:c r="H26" s="134"/>
+      <x:c r="I26" s="134"/>
+      <x:c r="J26" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K26" s="111" t="str">
+      <x:c r="K26" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L26" s="111" t="str">
+      <x:c r="L26" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M26" s="111" t="str">
+      <x:c r="M26" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A27" s="110" t="str">
+      <x:c r="A27" s="132" t="str">
         <x:v>B27</x:v>
       </x:c>
-      <x:c r="B27" s="111" t="str">
+      <x:c r="B27" s="133" t="str">
         <x:v>Step 11B · Admin</x:v>
       </x:c>
-      <x:c r="C27" s="111" t="str">
+      <x:c r="C27" s="133" t="str">
         <x:v>Admin user management, audit log and sensitive action authorization</x:v>
       </x:c>
-      <x:c r="D27" s="111" t="str">
+      <x:c r="D27" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E27" s="111" t="str">
+      <x:c r="E27" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F27" s="111" t="str">
+      <x:c r="F27" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G27" s="111" t="str">
+      <x:c r="G27" s="133" t="str">
         <x:v>Codex: implement only in Step 11B after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H27" s="112"/>
-      <x:c r="I27" s="112"/>
-      <x:c r="J27" s="111" t="str">
+      <x:c r="H27" s="134"/>
+      <x:c r="I27" s="134"/>
+      <x:c r="J27" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K27" s="111" t="str">
+      <x:c r="K27" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L27" s="111" t="str">
+      <x:c r="L27" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M27" s="111" t="str">
+      <x:c r="M27" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A28" s="110" t="str">
+      <x:c r="A28" s="132" t="str">
         <x:v>B30</x:v>
       </x:c>
-      <x:c r="B28" s="111" t="str">
+      <x:c r="B28" s="133" t="str">
         <x:v>Step 12 · Deploy</x:v>
       </x:c>
-      <x:c r="C28" s="111" t="str">
+      <x:c r="C28" s="133" t="str">
         <x:v>Single VPS deployment, TLS, backups and migration runbook</x:v>
       </x:c>
-      <x:c r="D28" s="111" t="str">
+      <x:c r="D28" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E28" s="111" t="str">
+      <x:c r="E28" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F28" s="111" t="str">
+      <x:c r="F28" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G28" s="111" t="str">
+      <x:c r="G28" s="133" t="str">
         <x:v>Codex: implement only in Step 12 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H28" s="112"/>
-      <x:c r="I28" s="112"/>
-      <x:c r="J28" s="111" t="str">
+      <x:c r="H28" s="134"/>
+      <x:c r="I28" s="134"/>
+      <x:c r="J28" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K28" s="111" t="str">
+      <x:c r="K28" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L28" s="111" t="str">
+      <x:c r="L28" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M28" s="111" t="str">
+      <x:c r="M28" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="99" hidden="0" customHeight="1">
-      <x:c r="A29" s="104" t="str">
+      <x:c r="A29" s="129" t="str">
         <x:v>B31</x:v>
       </x:c>
-      <x:c r="B29" s="105" t="str">
+      <x:c r="B29" s="130" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C29" s="105" t="str">
+      <x:c r="C29" s="130" t="str">
         <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
       </x:c>
-      <x:c r="D29" s="105" t="str">
+      <x:c r="D29" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E29" s="105" t="str">
+      <x:c r="E29" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F29" s="105" t="str">
+      <x:c r="F29" s="130" t="str">
         <x:v>Partly complete: Real PostgreSQL regression and application/Playwright suites exist and prior results passed. Final whole-project QA and realistic-volume EXPLAIN ANALYZE are unfinished.</x:v>
       </x:c>
-      <x:c r="G29" s="105" t="str">
+      <x:c r="G29" s="130" t="str">
         <x:v>Codex: Run complete scope and performance evidence in the final authorized quality stage.</x:v>
       </x:c>
-      <x:c r="H29" s="106"/>
-      <x:c r="I29" s="106" t="d">
+      <x:c r="H29" s="131"/>
+      <x:c r="I29" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J29" s="105" t="str">
+      <x:c r="J29" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K29" s="105" t="str">
+      <x:c r="K29" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L29" s="105" t="str">
+      <x:c r="L29" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M29" s="105" t="str">
+      <x:c r="M29" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Real PostgreSQL regression and application/Playwright suites exist and prior results passed. Final whole-project QA and realistic-volume EXPLAIN ANALYZE are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A30" s="110" t="str">
+      <x:c r="A30" s="132" t="str">
         <x:v>B32</x:v>
       </x:c>
-      <x:c r="B30" s="111" t="str">
+      <x:c r="B30" s="133" t="str">
         <x:v>Step 12 · Security</x:v>
       </x:c>
-      <x:c r="C30" s="111" t="str">
+      <x:c r="C30" s="133" t="str">
         <x:v>Access control, PDPA, headers, secrets and rate-limit audit</x:v>
       </x:c>
-      <x:c r="D30" s="111" t="str">
+      <x:c r="D30" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E30" s="111" t="str">
+      <x:c r="E30" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F30" s="111" t="str">
+      <x:c r="F30" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G30" s="111" t="str">
+      <x:c r="G30" s="133" t="str">
         <x:v>Codex: implement only in Step 12 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H30" s="112"/>
-      <x:c r="I30" s="112"/>
-      <x:c r="J30" s="111" t="str">
+      <x:c r="H30" s="134"/>
+      <x:c r="I30" s="134"/>
+      <x:c r="J30" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K30" s="111" t="str">
+      <x:c r="K30" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L30" s="111" t="str">
+      <x:c r="L30" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M30" s="111" t="str">
+      <x:c r="M30" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A31" s="110" t="str">
+      <x:c r="A31" s="132" t="str">
         <x:v>B33</x:v>
       </x:c>
-      <x:c r="B31" s="111" t="str">
+      <x:c r="B31" s="133" t="str">
         <x:v>Step 7 · Owners</x:v>
       </x:c>
-      <x:c r="C31" s="111" t="str">
+      <x:c r="C31" s="133" t="str">
         <x:v>Home-value and service enquiry data handling</x:v>
       </x:c>
-      <x:c r="D31" s="111" t="str">
+      <x:c r="D31" s="133" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E31" s="111" t="str">
+      <x:c r="E31" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F31" s="111" t="str">
+      <x:c r="F31" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G31" s="111" t="str">
+      <x:c r="G31" s="133" t="str">
         <x:v>Codex: implement only in Step 7 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H31" s="112"/>
-      <x:c r="I31" s="112"/>
-      <x:c r="J31" s="111" t="str">
+      <x:c r="H31" s="134"/>
+      <x:c r="I31" s="134"/>
+      <x:c r="J31" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K31" s="111" t="str">
+      <x:c r="K31" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L31" s="111" t="str">
+      <x:c r="L31" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M31" s="111" t="str">
+      <x:c r="M31" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
@@ -18330,7 +18377,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R531ba5996d1c42b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe7a72fe09144bba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18370,7 +18417,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>Done = completed task scope with evidence. Pending = started/blocked with named remaining work. Not started = task implementation has not begun. History is dated past evidence.</x:v>
+        <x:v>2026-10-10 Step 3C: F39 Done. 86 permanent IDs: 21 Done, 23 Pending, 42 Not started. All prior IDs and dated history retained; independent remaining tasks unchanged.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -18392,7 +18439,7 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -18411,7 +18458,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -18456,305 +18503,305 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A6" s="110" t="str">
+      <x:c r="A6" s="132" t="str">
         <x:v>E01</x:v>
       </x:c>
-      <x:c r="B6" s="111" t="str">
+      <x:c r="B6" s="133" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C6" s="111" t="str">
+      <x:c r="C6" s="133" t="str">
         <x:v>Enquiry notification with retryable queue/outbox</x:v>
       </x:c>
-      <x:c r="D6" s="111" t="str">
+      <x:c r="D6" s="133" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E6" s="111" t="str">
+      <x:c r="E6" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F6" s="111" t="str">
+      <x:c r="F6" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G6" s="111" t="str">
+      <x:c r="G6" s="133" t="str">
         <x:v>Codex: implement only in Step 6 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H6" s="112"/>
-      <x:c r="I6" s="112"/>
-      <x:c r="J6" s="111" t="str">
+      <x:c r="H6" s="134"/>
+      <x:c r="I6" s="134"/>
+      <x:c r="J6" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K6" s="111" t="str">
+      <x:c r="K6" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L6" s="111" t="str">
+      <x:c r="L6" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M6" s="111" t="str">
+      <x:c r="M6" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A7" s="110" t="str">
+      <x:c r="A7" s="132" t="str">
         <x:v>E02</x:v>
       </x:c>
-      <x:c r="B7" s="111" t="str">
+      <x:c r="B7" s="133" t="str">
         <x:v>Step 6 · Email</x:v>
       </x:c>
-      <x:c r="C7" s="111" t="str">
+      <x:c r="C7" s="133" t="str">
         <x:v>Thai and English buyer enquiry acknowledgments</x:v>
       </x:c>
-      <x:c r="D7" s="111" t="str">
+      <x:c r="D7" s="133" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E7" s="111" t="str">
+      <x:c r="E7" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F7" s="111" t="str">
+      <x:c r="F7" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G7" s="111" t="str">
+      <x:c r="G7" s="133" t="str">
         <x:v>Codex: implement only in Step 6 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H7" s="112"/>
-      <x:c r="I7" s="112"/>
-      <x:c r="J7" s="111" t="str">
+      <x:c r="H7" s="134"/>
+      <x:c r="I7" s="134"/>
+      <x:c r="J7" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K7" s="111" t="str">
+      <x:c r="K7" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L7" s="111" t="str">
+      <x:c r="L7" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M7" s="111" t="str">
+      <x:c r="M7" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A8" s="110" t="str">
+      <x:c r="A8" s="132" t="str">
         <x:v>E03</x:v>
       </x:c>
-      <x:c r="B8" s="111" t="str">
+      <x:c r="B8" s="133" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C8" s="111" t="str">
+      <x:c r="C8" s="133" t="str">
         <x:v>Project brochure/price list email delivery</x:v>
       </x:c>
-      <x:c r="D8" s="111" t="str">
+      <x:c r="D8" s="133" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E8" s="111" t="str">
+      <x:c r="E8" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F8" s="111" t="str">
+      <x:c r="F8" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G8" s="111" t="str">
+      <x:c r="G8" s="133" t="str">
         <x:v>Codex: implement only in Step 8 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H8" s="112"/>
-      <x:c r="I8" s="112"/>
-      <x:c r="J8" s="111" t="str">
+      <x:c r="H8" s="134"/>
+      <x:c r="I8" s="134"/>
+      <x:c r="J8" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K8" s="111" t="str">
+      <x:c r="K8" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L8" s="111" t="str">
+      <x:c r="L8" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M8" s="111" t="str">
+      <x:c r="M8" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A9" s="110" t="str">
+      <x:c r="A9" s="132" t="str">
         <x:v>E04</x:v>
       </x:c>
-      <x:c r="B9" s="111" t="str">
+      <x:c r="B9" s="133" t="str">
         <x:v>Step 8 · Email</x:v>
       </x:c>
-      <x:c r="C9" s="111" t="str">
+      <x:c r="C9" s="133" t="str">
         <x:v>Site visit request and confirmation notifications</x:v>
       </x:c>
-      <x:c r="D9" s="111" t="str">
+      <x:c r="D9" s="133" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E9" s="111" t="str">
+      <x:c r="E9" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F9" s="111" t="str">
+      <x:c r="F9" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G9" s="111" t="str">
+      <x:c r="G9" s="133" t="str">
         <x:v>Codex: implement only in Step 8 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H9" s="112"/>
-      <x:c r="I9" s="112"/>
-      <x:c r="J9" s="111" t="str">
+      <x:c r="H9" s="134"/>
+      <x:c r="I9" s="134"/>
+      <x:c r="J9" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K9" s="111" t="str">
+      <x:c r="K9" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L9" s="111" t="str">
+      <x:c r="L9" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M9" s="111" t="str">
+      <x:c r="M9" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A10" s="110" t="str">
+      <x:c r="A10" s="132" t="str">
         <x:v>E05</x:v>
       </x:c>
-      <x:c r="B10" s="111" t="str">
+      <x:c r="B10" s="133" t="str">
         <x:v>Step 9 · Alerts</x:v>
       </x:c>
-      <x:c r="C10" s="111" t="str">
+      <x:c r="C10" s="133" t="str">
         <x:v>Instant/daily saved search email alerts for signed-in users</x:v>
       </x:c>
-      <x:c r="D10" s="111" t="str">
+      <x:c r="D10" s="133" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E10" s="111" t="str">
+      <x:c r="E10" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F10" s="111" t="str">
+      <x:c r="F10" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G10" s="111" t="str">
+      <x:c r="G10" s="133" t="str">
         <x:v>Codex: implement only in Step 9 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H10" s="112"/>
-      <x:c r="I10" s="112"/>
-      <x:c r="J10" s="111" t="str">
+      <x:c r="H10" s="134"/>
+      <x:c r="I10" s="134"/>
+      <x:c r="J10" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K10" s="111" t="str">
+      <x:c r="K10" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L10" s="111" t="str">
+      <x:c r="L10" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M10" s="111" t="str">
+      <x:c r="M10" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A11" s="110" t="str">
+      <x:c r="A11" s="132" t="str">
         <x:v>E06</x:v>
       </x:c>
-      <x:c r="B11" s="111" t="str">
+      <x:c r="B11" s="133" t="str">
         <x:v>Step 10B · Email</x:v>
       </x:c>
-      <x:c r="C11" s="111" t="str">
+      <x:c r="C11" s="133" t="str">
         <x:v>Account verification and recovery messages if email auth approved</x:v>
       </x:c>
-      <x:c r="D11" s="111" t="str">
+      <x:c r="D11" s="133" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E11" s="111" t="str">
+      <x:c r="E11" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F11" s="111" t="str">
+      <x:c r="F11" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G11" s="111" t="str">
+      <x:c r="G11" s="133" t="str">
         <x:v>Codex: implement only in Step 10B after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H11" s="112"/>
-      <x:c r="I11" s="112"/>
-      <x:c r="J11" s="111" t="str">
+      <x:c r="H11" s="134"/>
+      <x:c r="I11" s="134"/>
+      <x:c r="J11" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K11" s="111" t="str">
+      <x:c r="K11" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L11" s="111" t="str">
+      <x:c r="L11" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M11" s="111" t="str">
+      <x:c r="M11" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A12" s="110" t="str">
+      <x:c r="A12" s="132" t="str">
         <x:v>E07</x:v>
       </x:c>
-      <x:c r="B12" s="111" t="str">
+      <x:c r="B12" s="133" t="str">
         <x:v>Step 11B · Email</x:v>
       </x:c>
-      <x:c r="C12" s="111" t="str">
+      <x:c r="C12" s="133" t="str">
         <x:v>Agent notification/routing administration</x:v>
       </x:c>
-      <x:c r="D12" s="111" t="str">
+      <x:c r="D12" s="133" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E12" s="111" t="str">
+      <x:c r="E12" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F12" s="111" t="str">
+      <x:c r="F12" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G12" s="111" t="str">
+      <x:c r="G12" s="133" t="str">
         <x:v>Codex: implement only in Step 11B after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H12" s="112"/>
-      <x:c r="I12" s="112"/>
-      <x:c r="J12" s="111" t="str">
+      <x:c r="H12" s="134"/>
+      <x:c r="I12" s="134"/>
+      <x:c r="J12" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K12" s="111" t="str">
+      <x:c r="K12" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L12" s="111" t="str">
+      <x:c r="L12" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M12" s="111" t="str">
+      <x:c r="M12" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A13" s="110" t="str">
+      <x:c r="A13" s="132" t="str">
         <x:v>E08</x:v>
       </x:c>
-      <x:c r="B13" s="111" t="str">
+      <x:c r="B13" s="133" t="str">
         <x:v>Step 7 · Email</x:v>
       </x:c>
-      <x:c r="C13" s="111" t="str">
+      <x:c r="C13" s="133" t="str">
         <x:v>Home valuation and service enquiry replies</x:v>
       </x:c>
-      <x:c r="D13" s="111" t="str">
+      <x:c r="D13" s="133" t="str">
         <x:v>Email</x:v>
       </x:c>
-      <x:c r="E13" s="111" t="str">
+      <x:c r="E13" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F13" s="111" t="str">
+      <x:c r="F13" s="133" t="str">
         <x:v>Not started: no implementation of this task feature/workflow exists. Shared schema or foundation prerequisites are tracked separately.</x:v>
       </x:c>
-      <x:c r="G13" s="111" t="str">
+      <x:c r="G13" s="133" t="str">
         <x:v>Codex: implement only in Step 7 after explicit stage authorization.</x:v>
       </x:c>
-      <x:c r="H13" s="112"/>
-      <x:c r="I13" s="112"/>
-      <x:c r="J13" s="111" t="str">
+      <x:c r="H13" s="134"/>
+      <x:c r="I13" s="134"/>
+      <x:c r="J13" s="133" t="str">
         <x:v>Not run: this task implementation has not started.</x:v>
       </x:c>
-      <x:c r="K13" s="111" t="str">
+      <x:c r="K13" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L13" s="111" t="str">
+      <x:c r="L13" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M13" s="111" t="str">
+      <x:c r="M13" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not yet implemented; follow approved V3 handoff.</x:v>
       </x:c>
@@ -26087,7 +26134,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e834c43a6084a54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45e61ea27886475f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26127,7 +26174,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>Done = completed task scope with evidence. Pending = started/blocked with named remaining work. Not started = task implementation has not begun. History is dated past evidence.</x:v>
+        <x:v>2026-10-10 Step 3C: F39 Done. 86 permanent IDs: 21 Done, 23 Pending, 42 Not started. All prior IDs and dated history retained; independent remaining tasks unchanged.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -26149,7 +26196,7 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -26168,7 +26215,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -26213,43 +26260,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="180" hidden="0" customHeight="1">
-      <x:c r="A6" s="121" t="str">
+      <x:c r="A6" s="141" t="str">
         <x:v>B34</x:v>
       </x:c>
-      <x:c r="B6" s="121" t="str">
+      <x:c r="B6" s="141" t="str">
         <x:v>Step 1 · Health</x:v>
       </x:c>
-      <x:c r="C6" s="121" t="str">
+      <x:c r="C6" s="141" t="str">
         <x:v>Basic /api/health endpoint with accurate application and database status</x:v>
       </x:c>
-      <x:c r="D6" s="121" t="str">
+      <x:c r="D6" s="141" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E6" s="121" t="str">
+      <x:c r="E6" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F6" s="121" t="str">
+      <x:c r="F6" s="141" t="str">
         <x:v>Completed: health probes the migrated public view and station schema. Prior real tests prove HTTP 200/ready, stopped-database 503 and recovery.</x:v>
       </x:c>
-      <x:c r="G6" s="121" t="str">
+      <x:c r="G6" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H6" s="122" t="d">
+      <x:c r="H6" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="122" t="d">
+      <x:c r="I6" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="121" t="str">
+      <x:c r="J6" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K6" s="121" t="str">
+      <x:c r="K6" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L6" s="121" t="str">
+      <x:c r="L6" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M6" s="121" t="str">
+      <x:c r="M6" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-09: Health API planned. No implementation in Step 0.
 2026-10-09 foundation: Real health API implemented: HTTP 200 app ok, database not_configured, ready false before closure. Configured PostgreSQL is probed with Drizzle select 1; failure returns 503. No real database configuration exists. Owner requested localhost closure; do not reopen automatically.
@@ -26258,43 +26305,43 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="153" hidden="0" customHeight="1">
-      <x:c r="A7" s="121" t="str">
+      <x:c r="A7" s="141" t="str">
         <x:v>B01</x:v>
       </x:c>
-      <x:c r="B7" s="121" t="str">
+      <x:c r="B7" s="141" t="str">
         <x:v>Step 2 · Database</x:v>
       </x:c>
-      <x:c r="C7" s="121" t="str">
+      <x:c r="C7" s="141" t="str">
         <x:v>PostgreSQL/Drizzle schema for listings, projects, agents and users</x:v>
       </x:c>
-      <x:c r="D7" s="121" t="str">
+      <x:c r="D7" s="141" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E7" s="121" t="str">
+      <x:c r="E7" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F7" s="121" t="str">
+      <x:c r="F7" s="141" t="str">
         <x:v>Completed: 18-table Drizzle schema, bilingual/type-specific constraints and isolated PostgreSQL development/test roles. Runtime access is server-only and read-only.</x:v>
       </x:c>
-      <x:c r="G7" s="121" t="str">
+      <x:c r="G7" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H7" s="122" t="d">
+      <x:c r="H7" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="122" t="d">
+      <x:c r="I7" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="121" t="str">
+      <x:c r="J7" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K7" s="121" t="str">
+      <x:c r="K7" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L7" s="121" t="str">
+      <x:c r="L7" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M7" s="121" t="str">
+      <x:c r="M7" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: 18-table Drizzle schema implemented with bilingual fields, seven property types, sale/rent rules, explicit price visibility and separate non-superuser migration/read-only app roles. Isolated local development/test PostgreSQL configured; no shared service modified. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -26302,43 +26349,43 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="153" hidden="0" customHeight="1">
-      <x:c r="A8" s="121" t="str">
+      <x:c r="A8" s="141" t="str">
         <x:v>B02</x:v>
       </x:c>
-      <x:c r="B8" s="121" t="str">
+      <x:c r="B8" s="141" t="str">
         <x:v>Step 2 · Database</x:v>
       </x:c>
-      <x:c r="C8" s="121" t="str">
+      <x:c r="C8" s="141" t="str">
         <x:v>Migrations, foreign keys, constraints and rollback procedure</x:v>
       </x:c>
-      <x:c r="D8" s="121" t="str">
+      <x:c r="D8" s="141" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="121" t="str">
+      <x:c r="E8" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F8" s="121" t="str">
+      <x:c r="F8" s="141" t="str">
         <x:v>Completed: three committed migrations, constraints, keys, triggers, snapshots/journal and guarded rollback procedure. Real dump/rollback/restore/rerun tests passed.</x:v>
       </x:c>
-      <x:c r="G8" s="121" t="str">
+      <x:c r="G8" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H8" s="122" t="d">
+      <x:c r="H8" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I8" s="122" t="d">
+      <x:c r="I8" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="121" t="str">
+      <x:c r="J8" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K8" s="121" t="str">
+      <x:c r="K8" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L8" s="121" t="str">
+      <x:c r="L8" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M8" s="121" t="str">
+      <x:c r="M8" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Generated foundation and custom relational migrations, journal/snapshots, constraints/FKs/triggers and guarded test-only initial rollback implemented. Real pg_dump/committed rollback/pg_restore/rerun pass. No production migration performed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -26346,43 +26393,43 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="153" hidden="0" customHeight="1">
-      <x:c r="A9" s="121" t="str">
+      <x:c r="A9" s="141" t="str">
         <x:v>B03</x:v>
       </x:c>
-      <x:c r="B9" s="121" t="str">
+      <x:c r="B9" s="141" t="str">
         <x:v>Step 2 · Demo</x:v>
       </x:c>
-      <x:c r="C9" s="121" t="str">
+      <x:c r="C9" s="141" t="str">
         <x:v>Clearly fictional seed listings, projects and agents</x:v>
       </x:c>
-      <x:c r="D9" s="121" t="str">
+      <x:c r="D9" s="141" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E9" s="121" t="str">
+      <x:c r="E9" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F9" s="121" t="str">
+      <x:c r="F9" s="141" t="str">
         <x:v>Completed: repeatable fictional seeds for the named local databases. Regression seed has 14 listings; search preview has 16. Public inventory excludes fictional records.</x:v>
       </x:c>
-      <x:c r="G9" s="121" t="str">
+      <x:c r="G9" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H9" s="122" t="d">
+      <x:c r="H9" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I9" s="122" t="d">
+      <x:c r="I9" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J9" s="121" t="str">
+      <x:c r="J9" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K9" s="121" t="str">
+      <x:c r="K9" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L9" s="121" t="str">
+      <x:c r="L9" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M9" s="121" t="str">
+      <x:c r="M9" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Repeatable local-only seed: 14 explicitly fictional listings, seven types/both intents and related demo records. Invalid domains, disabled users/agents, closed enquiries and off alerts. Public projection excludes demo inventory; no real prices/agents advertised. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -26390,43 +26437,43 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="153" hidden="0" customHeight="1">
-      <x:c r="A10" s="121" t="str">
+      <x:c r="A10" s="141" t="str">
         <x:v>B04</x:v>
       </x:c>
-      <x:c r="B10" s="121" t="str">
+      <x:c r="B10" s="141" t="str">
         <x:v>Step 2 · Search</x:v>
       </x:c>
-      <x:c r="C10" s="121" t="str">
+      <x:c r="C10" s="141" t="str">
         <x:v>Indexes for status, intent, type, price, location and title</x:v>
       </x:c>
-      <x:c r="D10" s="121" t="str">
+      <x:c r="D10" s="141" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="121" t="str">
+      <x:c r="E10" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F10" s="121" t="str">
+      <x:c r="F10" s="141" t="str">
         <x:v>Completed: status/intent/type/price/location/bounds/feed/text indexes. Catalog and EXPLAIN checks passed. Production-scale profiling belongs to B31.</x:v>
       </x:c>
-      <x:c r="G10" s="121" t="str">
+      <x:c r="G10" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H10" s="122" t="d">
+      <x:c r="H10" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="122" t="d">
+      <x:c r="I10" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="121" t="str">
+      <x:c r="J10" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K10" s="121" t="str">
+      <x:c r="K10" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L10" s="121" t="str">
+      <x:c r="L10" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M10" s="121" t="str">
+      <x:c r="M10" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 2: Intent/type/status/price, location/status, bounding coordinates, publication/feed and bilingual simple-text indexes implemented. Catalog and EXPLAIN use checks pass. Tiny-seed plans prove indexes are usable, not production speed. PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.
@@ -26434,43 +26481,43 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="261" hidden="0" customHeight="1">
-      <x:c r="A11" s="121" t="str">
+      <x:c r="A11" s="141" t="str">
         <x:v>F08</x:v>
       </x:c>
-      <x:c r="B11" s="121" t="str">
+      <x:c r="B11" s="141" t="str">
         <x:v>Step 3 · Cards</x:v>
       </x:c>
-      <x:c r="C11" s="121" t="str">
+      <x:c r="C11" s="141" t="str">
         <x:v>Realtor-style 3:2 listing cards, photo controls, bottom-right save heart, facts/address and Contact agent dialog trigger</x:v>
       </x:c>
-      <x:c r="D11" s="121" t="str">
+      <x:c r="D11" s="141" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E11" s="121" t="str">
+      <x:c r="E11" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F11" s="121" t="str">
+      <x:c r="F11" s="141" t="str">
         <x:v>Completed Step 3/3B card scope: 3:2 photos, controls/swipe, badges, shared device hearts, type facts, gated prices, protected address and contact-dialog trigger. Real submission is tracked separately in F21/B14; new Step 3C motion is F39.</x:v>
       </x:c>
-      <x:c r="G11" s="121" t="str">
+      <x:c r="G11" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H11" s="122" t="d">
+      <x:c r="H11" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I11" s="122" t="d">
+      <x:c r="I11" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="121" t="str">
+      <x:c r="J11" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
       </x:c>
-      <x:c r="K11" s="121" t="str">
+      <x:c r="K11" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L11" s="121" t="str">
+      <x:c r="L11" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M11" s="121" t="str">
+      <x:c r="M11" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 3 and revised BUILD-SPEC 4.3 replace the older 4:3 card plan. One reusable card across homepage/results/Saved. Not implemented; requires Step 2 Done.
@@ -26481,43 +26528,43 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="247.5" hidden="0" customHeight="1">
-      <x:c r="A12" s="121" t="str">
+      <x:c r="A12" s="141" t="str">
         <x:v>F09</x:v>
       </x:c>
-      <x:c r="B12" s="121" t="str">
+      <x:c r="B12" s="141" t="str">
         <x:v>Step 3 · Results</x:v>
       </x:c>
-      <x:c r="C12" s="121" t="str">
+      <x:c r="C12" s="141" t="str">
         <x:v>Responsive /buy, /rent and /invest results layouts</x:v>
       </x:c>
-      <x:c r="D12" s="121" t="str">
+      <x:c r="D12" s="141" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E12" s="121" t="str">
+      <x:c r="E12" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F12" s="121" t="str">
+      <x:c r="F12" s="141" t="str">
         <x:v>Completed: Thai/English buy/rent/invest results use full-width 3/2/1 equal columns and cumulative 12-home batches. Empty states and browser history passed. Map work is F14/F15/B08.</x:v>
       </x:c>
-      <x:c r="G12" s="121" t="str">
+      <x:c r="G12" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H12" s="122" t="d">
+      <x:c r="H12" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="122" t="d">
+      <x:c r="I12" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="121" t="str">
+      <x:c r="J12" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
       </x:c>
-      <x:c r="K12" s="121" t="str">
+      <x:c r="K12" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L12" s="121" t="str">
+      <x:c r="L12" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M12" s="121" t="str">
+      <x:c r="M12" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Server-rendered /th and /en buy/rent/invest routes. Two desktop card columns, one phone column; empty state, readable heading and cumulative Show more homes. Reserved blank desktop map column; no fake map. Property link reaches an explicit unfinished detail route, not an implemented Step 5 page. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
@@ -26526,43 +26573,43 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="247.5" hidden="0" customHeight="1">
-      <x:c r="A13" s="121" t="str">
+      <x:c r="A13" s="141" t="str">
         <x:v>F10</x:v>
       </x:c>
-      <x:c r="B13" s="121" t="str">
+      <x:c r="B13" s="141" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C13" s="121" t="str">
+      <x:c r="C13" s="141" t="str">
         <x:v>Shared URL filters, active chips, sorting and navigation history</x:v>
       </x:c>
-      <x:c r="D13" s="121" t="str">
+      <x:c r="D13" s="141" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E13" s="121" t="str">
+      <x:c r="E13" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F13" s="121" t="str">
+      <x:c r="F13" s="141" t="str">
         <x:v>Completed: shared validated URL filters, active chips, Clear, sorting, 12-home page state and router.push history. Popup drafts stay local. Refresh/back/forward passed.</x:v>
       </x:c>
-      <x:c r="G13" s="121" t="str">
+      <x:c r="G13" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H13" s="122" t="d">
+      <x:c r="H13" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I13" s="122" t="d">
+      <x:c r="I13" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J13" s="121" t="str">
+      <x:c r="J13" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
       </x:c>
-      <x:c r="K13" s="121" t="str">
+      <x:c r="K13" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L13" s="121" t="str">
+      <x:c r="L13" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M13" s="121" t="str">
+      <x:c r="M13" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Shared validated URL state for homepage/results; active chips, Clear all, sorting and cumulative page state. Applied changes use Next router.push without full reload to preserve meaningful back/forward history; uncommitted popup drafts do not change URLs. Refresh/back/forward tested. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
@@ -26571,43 +26618,43 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="180" hidden="0" customHeight="1">
-      <x:c r="A14" s="121" t="str">
+      <x:c r="A14" s="141" t="str">
         <x:v>F11</x:v>
       </x:c>
-      <x:c r="B14" s="121" t="str">
+      <x:c r="B14" s="141" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C14" s="121" t="str">
+      <x:c r="C14" s="141" t="str">
         <x:v>Desktop popovers for price, beds, type and advanced filters</x:v>
       </x:c>
-      <x:c r="D14" s="121" t="str">
+      <x:c r="D14" s="141" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E14" s="121" t="str">
+      <x:c r="E14" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F14" s="121" t="str">
+      <x:c r="F14" s="141" t="str">
         <x:v>Completed Step 3 filter behavior: desktop dialogs for location, intent, price, beds, types and typed advanced metadata. Apply, live counts, focus and Escape passed. Step 3C animation is F39.</x:v>
       </x:c>
-      <x:c r="G14" s="121" t="str">
+      <x:c r="G14" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H14" s="122" t="d">
+      <x:c r="H14" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I14" s="122" t="d">
+      <x:c r="I14" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="121" t="str">
+      <x:c r="J14" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K14" s="121" t="str">
+      <x:c r="K14" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L14" s="121" t="str">
+      <x:c r="L14" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M14" s="121" t="str">
+      <x:c r="M14" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Accessible native-dialog desktop popovers for location, intent, price, beds, property types and advanced/DB-defined typed filters. Actual metadata options and live price count tested; Escape, focus trapping and focus restoration verified. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
@@ -26615,43 +26662,43 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="180" hidden="0" customHeight="1">
-      <x:c r="A15" s="121" t="str">
+      <x:c r="A15" s="141" t="str">
         <x:v>F12</x:v>
       </x:c>
-      <x:c r="B15" s="121" t="str">
+      <x:c r="B15" s="141" t="str">
         <x:v>Step 3 · Filters</x:v>
       </x:c>
-      <x:c r="C15" s="121" t="str">
+      <x:c r="C15" s="141" t="str">
         <x:v>Phone full-screen filter sheet, Apply and Clear</x:v>
       </x:c>
-      <x:c r="D15" s="121" t="str">
+      <x:c r="D15" s="141" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="121" t="str">
+      <x:c r="E15" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F15" s="121" t="str">
+      <x:c r="F15" s="141" t="str">
         <x:v>Completed Step 3 phone filter behavior: full-screen sheets, Apply/Clear, labels, focus and overflow checks in both languages. Step 3C animation is F39.</x:v>
       </x:c>
-      <x:c r="G15" s="121" t="str">
+      <x:c r="G15" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H15" s="122" t="d">
+      <x:c r="H15" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I15" s="122" t="d">
+      <x:c r="I15" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J15" s="121" t="str">
+      <x:c r="J15" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K15" s="121" t="str">
+      <x:c r="K15" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L15" s="121" t="str">
+      <x:c r="L15" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M15" s="121" t="str">
+      <x:c r="M15" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Phone full-screen filter sheets with Apply/Clear, labels, focus controls and no page overflow. Native Chromium phone input proves card swipe; UI checked at 390/768/1024/1440 in Thai/English. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
@@ -26659,43 +26706,43 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="180" hidden="0" customHeight="1">
-      <x:c r="A16" s="121" t="str">
+      <x:c r="A16" s="141" t="str">
         <x:v>F13</x:v>
       </x:c>
-      <x:c r="B16" s="121" t="str">
+      <x:c r="B16" s="141" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C16" s="121" t="str">
+      <x:c r="C16" s="141" t="str">
         <x:v>Database-derived price histogram and live result count</x:v>
       </x:c>
-      <x:c r="D16" s="121" t="str">
+      <x:c r="D16" s="141" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E16" s="121" t="str">
+      <x:c r="E16" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F16" s="121" t="str">
+      <x:c r="F16" s="141" t="str">
         <x:v>Completed: histogram derives from matching public-price records; gated values are excluded. Debounced real result counts and deterministic bounded queries passed.</x:v>
       </x:c>
-      <x:c r="G16" s="121" t="str">
+      <x:c r="G16" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H16" s="122" t="d">
+      <x:c r="H16" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I16" s="122" t="d">
+      <x:c r="I16" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J16" s="121" t="str">
+      <x:c r="J16" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K16" s="121" t="str">
+      <x:c r="K16" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L16" s="121" t="str">
+      <x:c r="L16" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M16" s="121" t="str">
+      <x:c r="M16" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Histogram uses actual matching PUBLIC-price rows, excluding only current min/max range. Gated prices are excluded from price predicates, price ordering and histogram. Debounced actual API count and bounded deterministic queries implemented. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
@@ -26703,43 +26750,43 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="180" hidden="0" customHeight="1">
-      <x:c r="A17" s="121" t="str">
+      <x:c r="A17" s="141" t="str">
         <x:v>B05</x:v>
       </x:c>
-      <x:c r="B17" s="121" t="str">
+      <x:c r="B17" s="141" t="str">
         <x:v>Step 2 · Filters</x:v>
       </x:c>
-      <x:c r="C17" s="121" t="str">
+      <x:c r="C17" s="141" t="str">
         <x:v>Configurable filter-definition/option tables with safe allowed query fields</x:v>
       </x:c>
-      <x:c r="D17" s="121" t="str">
+      <x:c r="D17" s="141" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E17" s="121" t="str">
+      <x:c r="E17" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F17" s="121" t="str">
+      <x:c r="F17" s="141" t="str">
         <x:v>Completed: typed definition/option/value tables and validated active search metadata. Allowed options, property scopes and parameterized query handling passed. Admin editor is F36/B26.</x:v>
       </x:c>
-      <x:c r="G17" s="121" t="str">
+      <x:c r="G17" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H17" s="122" t="d">
+      <x:c r="H17" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I17" s="122" t="d">
+      <x:c r="I17" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J17" s="121" t="str">
+      <x:c r="J17" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K17" s="121" t="str">
+      <x:c r="K17" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L17" s="121" t="str">
+      <x:c r="L17" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M17" s="121" t="str">
+      <x:c r="M17" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Existing typed filter definition/option/value tables are consumed safely by results. Only active metadata in the selected genuine/demo partition is exposed. Single/multi/number/boolean kinds, allowed options and property scope validated with parameterized SQL. Production admin CRUD remains Step 11. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
@@ -26747,43 +26794,43 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="247.5" hidden="0" customHeight="1">
-      <x:c r="A18" s="121" t="str">
+      <x:c r="A18" s="141" t="str">
         <x:v>B06</x:v>
       </x:c>
-      <x:c r="B18" s="121" t="str">
+      <x:c r="B18" s="141" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C18" s="121" t="str">
+      <x:c r="C18" s="141" t="str">
         <x:v>Typed validated listing/search data access and pagination</x:v>
       </x:c>
-      <x:c r="D18" s="121" t="str">
+      <x:c r="D18" s="141" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E18" s="121" t="str">
+      <x:c r="E18" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F18" s="121" t="str">
+      <x:c r="F18" s="141" t="str">
         <x:v>Completed: server-only validated listing API/search, sorting and 12-home pagination. DTOs protect gated prices, hidden exact location and contacts. Samples require all local-development guards.</x:v>
       </x:c>
-      <x:c r="G18" s="121" t="str">
+      <x:c r="G18" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H18" s="122" t="d">
+      <x:c r="H18" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I18" s="122" t="d">
+      <x:c r="I18" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J18" s="121" t="str">
+      <x:c r="J18" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
       </x:c>
-      <x:c r="K18" s="121" t="str">
+      <x:c r="K18" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L18" s="121" t="str">
+      <x:c r="L18" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M18" s="121" t="str">
+      <x:c r="M18" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Server-only bounded, parameterized listing queries and GET /api/listings: sale/rent/invest, location hierarchy/station slugs, beds/baths/size/land/year/amenities/project, sorting/pagination. No contacts, exact hidden location or gated prices in result DTOs. Local demo requires explicit flag and named local DB/trusted Host. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
@@ -26793,43 +26840,43 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="180" hidden="0" customHeight="1">
-      <x:c r="A19" s="121" t="str">
+      <x:c r="A19" s="141" t="str">
         <x:v>B07</x:v>
       </x:c>
-      <x:c r="B19" s="121" t="str">
+      <x:c r="B19" s="141" t="str">
         <x:v>Step 3 · Search</x:v>
       </x:c>
-      <x:c r="C19" s="121" t="str">
+      <x:c r="C19" s="141" t="str">
         <x:v>Filter parsing, result counts, sort and histogram queries</x:v>
       </x:c>
-      <x:c r="D19" s="121" t="str">
+      <x:c r="D19" s="141" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E19" s="121" t="str">
+      <x:c r="E19" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F19" s="121" t="str">
+      <x:c r="F19" s="141" t="str">
         <x:v>Completed: shared parser, actual count/sort/histogram queries and unique station slugs. Three-migration rerun, seed idempotency and isolated rollback/restore passed.</x:v>
       </x:c>
-      <x:c r="G19" s="121" t="str">
+      <x:c r="G19" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H19" s="122" t="d">
+      <x:c r="H19" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I19" s="122" t="d">
+      <x:c r="I19" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J19" s="121" t="str">
+      <x:c r="J19" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K19" s="121" t="str">
+      <x:c r="K19" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L19" s="121" t="str">
+      <x:c r="L19" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M19" s="121" t="str">
+      <x:c r="M19" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 Step 3: Validated shared URL parser, actual counts/sort/histogram and DB metadata filters. Additive 0002_station_search_slug migration provides unique non-null station slugs. Real pre-migration development backup, three-migration rerun and isolated dump/rollback/restore regression passed. Demo search seed rerun is idempotent. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
@@ -26837,43 +26884,43 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="180" hidden="0" customHeight="1">
-      <x:c r="A20" s="121" t="str">
+      <x:c r="A20" s="141" t="str">
         <x:v>R02</x:v>
       </x:c>
-      <x:c r="B20" s="121" t="str">
+      <x:c r="B20" s="141" t="str">
         <x:v>Step 3 · Accessibility</x:v>
       </x:c>
-      <x:c r="C20" s="121" t="str">
+      <x:c r="C20" s="141" t="str">
         <x:v>Fix contact autofocus and swipe/keyboard link handling (F01/F08)</x:v>
       </x:c>
-      <x:c r="D20" s="121" t="str">
+      <x:c r="D20" s="141" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="121" t="str">
+      <x:c r="E20" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F20" s="121" t="str">
+      <x:c r="F20" s="141" t="str">
         <x:v>Completed: contact autofocus/focus restoration and swipe/keyboard handling fixes. Affected browser regressions passed.</x:v>
       </x:c>
-      <x:c r="G20" s="121" t="str">
+      <x:c r="G20" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H20" s="122" t="d">
+      <x:c r="H20" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I20" s="122" t="d">
+      <x:c r="I20" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J20" s="121" t="str">
+      <x:c r="J20" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.</x:v>
       </x:c>
-      <x:c r="K20" s="121" t="str">
+      <x:c r="K20" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L20" s="121" t="str">
+      <x:c r="L20" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M20" s="121" t="str">
+      <x:c r="M20" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-09 discovered during Step 3 real browser testing: contact input lacked focus; swipe suppression blocked the next keyboard activation. Linked to F01/F08.
 2026-10-09 Step 3: Fix linked to F01/F08: dialog autofocus now occurs after native showModal and preserves the trigger for restoration. Swipe cancels only the immediate synthetic pointer click, allowing subsequent keyboard Enter. Streaming-page keyboard test waits for visible focused links. All affected regressions pass. PASS: final build/TypeScript; 36/36 real Chromium tests at 390/768/1024/1440, Thai/English; native phone swipe, save/reload, photo controls, dialog focus/Tab/Escape, metadata option Apply, URL/refresh/back/forward, empty state, sale/rent/invest and screenshots. PASS: 12/12 real app/PostgreSQL search groups and 12/12 database regression groups, three-migration apply/rerun, unique station slug rejection, actual counts/joins, public/gated privacy, parameterization, seed rerun, dump/rollback/restore. Frontend, listings API and health HTTP 200/ready true verified; no submission/admin exists. Test servers stopped afterward.
@@ -26881,129 +26928,129 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="234" hidden="0" customHeight="1">
-      <x:c r="A21" s="121" t="str">
+      <x:c r="A21" s="141" t="str">
         <x:v>R03</x:v>
       </x:c>
-      <x:c r="B21" s="121" t="str">
+      <x:c r="B21" s="141" t="str">
         <x:v>Step 3 · Sample safety</x:v>
       </x:c>
-      <x:c r="C21" s="121" t="str">
+      <x:c r="C21" s="141" t="str">
         <x:v>Restrict fictional sample preview to local development; label each card Sample (F08/B06)</x:v>
       </x:c>
-      <x:c r="D21" s="121" t="str">
+      <x:c r="D21" s="141" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E21" s="121" t="str">
+      <x:c r="E21" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F21" s="121" t="str">
+      <x:c r="F21" s="141" t="str">
         <x:v>Completed: development-only sample guards at request and query/metadata boundaries, visible sample labels and fictional notice. Production and public-site exclusion passed.</x:v>
       </x:c>
-      <x:c r="G21" s="121" t="str">
+      <x:c r="G21" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H21" s="122" t="d">
+      <x:c r="H21" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I21" s="122" t="d">
+      <x:c r="I21" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J21" s="121" t="str">
+      <x:c r="J21" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: all 44 development Chromium checks covered (42 initially passed; two homepage cold-load timeouts passed in a focused 2/2 warm rerun), Thai/English at 390/768/1024/1440; Sample badge on each buy/rent/invest card and no overflow. PASS: eight production browser checks on actual next build/next start with sample flag still 1; no sample cards, notice, DTOs or metadata; query override and public Host cannot enable samples. PASS: five development and six production actual app/PostgreSQL checks prove 16 published fictional rows remain seeded, production counts match genuine inventory, forced internal sample queries/metadata are denied and configured public SITE_URL rejects samples. PASS: 12 development search groups, TypeScript and production build. Servers stopped afterward; no admin/form submission.</x:v>
       </x:c>
-      <x:c r="K21" s="121" t="str">
+      <x:c r="K21" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L21" s="121" t="str">
+      <x:c r="L21" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M21" s="121" t="str">
+      <x:c r="M21" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R03 created from owner clarification: prior preview lacked a NODE_ENV guard and could appear under next start. Linked F08/B06. Owner requested local development samples with a visible Sample badge. NODE_ENV must equal development; explicit flag, loopback Host/SITE_URL and named local DB are also required. Request and query/metadata boundaries ignore samples in production even when MSTAR_DEMO_MODE=1. Public hosts are denied. Existing fictional notice and privacy constraints remain. PASS: all 44 development Chromium checks covered (42 initially passed; two homepage cold-load timeouts passed in a focused 2/2 warm rerun), Thai/English at 390/768/1024/1440; Sample badge on each buy/rent/invest card and no overflow. PASS: eight production browser checks on actual next build/next start with sample flag still 1; no sample cards, notice, DTOs or metadata; query override and public Host cannot enable samples. PASS: five development and six production actual app/PostgreSQL checks prove 16 published fictional rows remain seeded, production counts match genuine inventory, forced internal sample queries/metadata are denied and configured public SITE_URL rejects samples. PASS: 12 development search groups, TypeScript and production build. Servers stopped afterward; no admin/form submission.
 2026-10-10 R05 audit: Completed: development-only sample guards at request and query/metadata boundaries, visible sample labels and fictional notice. Production and public-site exclusion passed.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="247.5" hidden="0" customHeight="1">
-      <x:c r="A22" s="121" t="str">
+      <x:c r="A22" s="141" t="str">
         <x:v>R04</x:v>
       </x:c>
-      <x:c r="B22" s="121" t="str">
+      <x:c r="B22" s="141" t="str">
         <x:v>Step 3B</x:v>
       </x:c>
-      <x:c r="C22" s="121" t="str">
+      <x:c r="C22" s="141" t="str">
         <x:v>Full-width results, card corrections and small home topic rows (F08/F09/F10/B06/F25)</x:v>
       </x:c>
-      <x:c r="D22" s="121" t="str">
+      <x:c r="D22" s="141" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E22" s="121" t="str">
+      <x:c r="E22" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F22" s="121" t="str">
+      <x:c r="F22" s="141" t="str">
         <x:v>Completed authorized Step 3B only: full-width results, 12-home batches, whole land units, actual transit lines, Thai sample labels and small topic rows. New Step 3C motion is a separate unstarted F39; regional tiles remain F25.</x:v>
       </x:c>
-      <x:c r="G22" s="121" t="str">
+      <x:c r="G22" s="141" t="str">
         <x:v>No remaining work within this completed task scope. Preserve tested behavior; use separate IDs for later stages.</x:v>
       </x:c>
-      <x:c r="H22" s="122" t="d">
+      <x:c r="H22" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I22" s="122" t="d">
+      <x:c r="I22" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J22" s="121" t="str">
+      <x:c r="J22" s="141" t="str">
         <x:v>Verified in prior authorized tests; evidence retained in dated history and testing.md. PASS: 66 existing development browser checks; 24 new checks plus one breakpoint-boundary check pass after visibility/focus waits corrected initial test timing. Final visual run: 25 passed, five redundant boundary runs skipped. Thai/English at 390/768/1024/1280/1440/1600, 3/2/1 results, 7/6/5/4 home widths, about 2.3 phone cards, native swipe/arrows, correct query links, heart persistence across both card sizes, keyboard and land/hotel facts. PASS: 18 real-DB fixture browser checks, 12/24/28 pagination with history, MRT/ARL labels. Eight actual Step 3B DB groups prove featured order, cap/privacy and cleanup; original listing hashes unchanged, permanent seed still 16. PASS: 12 existing search groups, five development/six production sample checks, 12 production browser checks with flag=1; no samples/home rows/metadata. Build/TypeScript passed. Screenshots reviewed. Ports 3000/5432 stopped; admin/forms absent.</x:v>
       </x:c>
-      <x:c r="K22" s="121" t="str">
+      <x:c r="K22" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L22" s="121" t="str">
+      <x:c r="L22" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M22" s="121" t="str">
+      <x:c r="M22" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R04 created for the owner-approved Step 3B change. Linked F08/F09/F10/B06/F25. Implemented grid/card/home-row scope only. Initial new browser checks needed streamed-content visibility/focus waits; final checks pass. 91 development checks covered, 18 fixture checks and 12 production checks pass; real PostgreSQL ranking/pagination/cleanup and sample denial verified. No permanent seed/schema changes. Original histories are retained. Stop before Step 4.
 2026-10-10 R05 audit: Completed authorized Step 3B only: full-width results, 12-home batches, whole land units, actual transit lines, Thai sample labels and small topic rows. New Step 3C motion is a separate unstarted F39; regional tiles remain F25.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="315" hidden="0" customHeight="1">
-      <x:c r="A23" s="121" t="str">
+      <x:c r="A23" s="141" t="str">
         <x:v>F02</x:v>
       </x:c>
-      <x:c r="B23" s="121" t="str">
+      <x:c r="B23" s="141" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C23" s="121" t="str">
+      <x:c r="C23" s="141" t="str">
         <x:v>Owner approves gold / blue / teal / coral accent</x:v>
       </x:c>
-      <x:c r="D23" s="121" t="str">
+      <x:c r="D23" s="141" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E23" s="121" t="str">
+      <x:c r="E23" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F23" s="121" t="str">
+      <x:c r="F23" s="141" t="str">
         <x:v>Completed owner decision: approved wireframe colours/default gold. Exact gold tokens are present in app/globals.css. Final logo is a separate F03 dependency.</x:v>
       </x:c>
-      <x:c r="G23" s="121" t="str">
+      <x:c r="G23" s="141" t="str">
         <x:v>No remaining colour-choice action. Preserve approved gold.</x:v>
       </x:c>
-      <x:c r="H23" s="122" t="d">
+      <x:c r="H23" s="142" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I23" s="122" t="d">
+      <x:c r="I23" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J23" s="121" t="str">
+      <x:c r="J23" s="141" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K23" s="121" t="str">
+      <x:c r="K23" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L23" s="121" t="str">
+      <x:c r="L23" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M23" s="121" t="str">
+      <x:c r="M23" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: BUILD-SPEC §12 #1: accent not finalized
 2026-10-09 owner update: Owner selected approved wireframe colours: default gold #f2a91a and associated V3 tokens. Choice recorded; implementation/runtime completion gates remain pending.
@@ -27014,41 +27061,41 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="99" hidden="0" customHeight="1">
-      <x:c r="A24" s="121" t="str">
+      <x:c r="A24" s="141" t="str">
         <x:v>B29</x:v>
       </x:c>
-      <x:c r="B24" s="121" t="str">
+      <x:c r="B24" s="141" t="str">
         <x:v>Decision · Projects</x:v>
       </x:c>
-      <x:c r="C24" s="121" t="str">
+      <x:c r="C24" s="141" t="str">
         <x:v>Approve public project prices versus enquiry-only price list</x:v>
       </x:c>
-      <x:c r="D24" s="121" t="str">
+      <x:c r="D24" s="141" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E24" s="121" t="str">
+      <x:c r="E24" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F24" s="121" t="str">
+      <x:c r="F24" s="141" t="str">
         <x:v>Completed owner decision: admin chooses public or contact-gated prices per listing/project. Explicit visibility columns, public projection and privacy tests already enforce the data contract. Admin UI is F35/B26.</x:v>
       </x:c>
-      <x:c r="G24" s="121" t="str">
+      <x:c r="G24" s="141" t="str">
         <x:v>No remaining price-policy decision. Implement admin controls only under F35/B26 authorization.</x:v>
       </x:c>
-      <x:c r="H24" s="122"/>
-      <x:c r="I24" s="122" t="d">
+      <x:c r="H24" s="142"/>
+      <x:c r="I24" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J24" s="121" t="str">
+      <x:c r="J24" s="141" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K24" s="121" t="str">
+      <x:c r="K24" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L24" s="121" t="str">
+      <x:c r="L24" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M24" s="121" t="str">
+      <x:c r="M24" s="141" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: BUILD-SPEC §12 #7 unresolved
 2026-10-09 owner update: Owner selected both public and contact-gated pricing, chosen by admin per listing/product or project. Choice recorded; implementation pending.
@@ -27056,60 +27103,87 @@
       </x:c>
     </x:row>
     <x:row r="25" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A25" s="121" t="str">
+      <x:c r="A25" s="141" t="str">
         <x:v>R05</x:v>
       </x:c>
-      <x:c r="B25" s="121" t="str">
+      <x:c r="B25" s="141" t="str">
         <x:v>Tracker correction</x:v>
       </x:c>
-      <x:c r="C25" s="121" t="str">
+      <x:c r="C25" s="141" t="str">
         <x:v>Audit true completion status and restore visible spreadsheet grid</x:v>
       </x:c>
-      <x:c r="D25" s="121" t="str">
+      <x:c r="D25" s="141" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E25" s="121" t="str">
+      <x:c r="E25" s="141" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="F25" s="121" t="str">
+      <x:c r="F25" s="141" t="str">
         <x:v>Completed workbook-only correction: audited full scope, corrected classifications, refreshed current evidence, preserved historical text and all prior IDs, regenerated six views, and added borders/gridlines.</x:v>
       </x:c>
-      <x:c r="G25" s="121" t="str">
+      <x:c r="G25" s="141" t="str">
         <x:v>No remaining tracker-correction action after export, six-sheet validation, mirror and commit/push gates.</x:v>
       </x:c>
-      <x:c r="H25" s="122" t="d">
+      <x:c r="H25" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I25" s="122" t="d">
+      <x:c r="I25" s="142" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J25" s="121" t="str">
+      <x:c r="J25" s="141" t="str">
         <x:v>PASS: exported workbook integrity, exact ID/status/category reconciliation, histories, formulas/caches, tables, validation, colours/borders/gridlines and six-sheet visual review. Application/DB retests are not applicable to this workbook-only edit.</x:v>
       </x:c>
-      <x:c r="K25" s="121" t="str">
+      <x:c r="K25" s="141" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L25" s="121" t="str">
+      <x:c r="L25" s="141" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M25" s="121" t="str">
+      <x:c r="M25" s="141" t="str">
         <x:v>2026-10-10 R05: owner requested truthful Done/Pending/Not started classifications and a visible grid. Scope is workbook/document correction only.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26"/>
-      <x:c r="B26"/>
-      <x:c r="C26"/>
-      <x:c r="D26"/>
-      <x:c r="E26"/>
-      <x:c r="F26"/>
-      <x:c r="G26"/>
-      <x:c r="H26"/>
-      <x:c r="I26"/>
-      <x:c r="J26"/>
-      <x:c r="K26"/>
-      <x:c r="L26"/>
-      <x:c r="M26"/>
+    <x:row r="26" ht="360" customHeight="1">
+      <x:c r="A26" s="141" t="str">
+        <x:v>F39</x:v>
+      </x:c>
+      <x:c r="B26" s="141" t="str">
+        <x:v>Step 3C · Motion</x:v>
+      </x:c>
+      <x:c r="C26" s="141" t="str">
+        <x:v>Shared smooth motion for rows, card photos, dialogs, sheets and controls</x:v>
+      </x:c>
+      <x:c r="D26" s="141" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E26" s="141" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F26" s="141" t="str">
+        <x:v>Shared motion is implemented across existing home rails, big-card photos, both card hovers, dialogs/popovers/phone sheets and all controls. Card-edge requestAnimationFrame scrolling, interrupted/repeated clicks, native gestures and Left/Right keys use lib/motion.ts. CSS tokens match the approved Motion section; reduced motion finishes immediately. Dialog content and background layout remain stable through exit; focus restores after closure. No Step 4 or later UI is added.</x:v>
+      </x:c>
+      <x:c r="G26" s="141" t="str">
+        <x:v>Codex: stop before Step 4. Future map/gallery/project/Saved stages must reuse lib/motion.ts and shared CSS tokens. Existing unrelated partial tasks retain their own next actions.</x:v>
+      </x:c>
+      <x:c r="H26" s="142" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I26" s="142" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J26" s="141" t="str">
+        <x:v>Final verification: 36/36 motion browser checks and 91 existing development regression checks passed; five redundant boundary runs were intentionally skipped. Twelve production browser checks passed with samples hidden despite MSTAR_DEMO_MODE=1. Real application/PostgreSQL checks passed: 12 search groups, five development sample groups and six production sample groups. Production build and TypeScript passed. Both languages and 390/768/1024/1280/1440/1600px were covered; screenshots were visually reviewed on phone and desktop. An exit test originally checked after a protocol delay longer than the sheet animation; first-frame browser inspection now verifies inert retained content, duration and eventual removal deterministically. Admin and real enquiry submission remain absent. Verified HTTP 200 during actual testing: http://127.0.0.1:3000/en, /th, /en/buy, /th/buy, /en/rent, /en/invest, /api/listings?route=buy&amp;lang=en and /api/health (database ready). Test servers on ports 3000 and 5432 are stopped afterward; these links are not currently running. No admin URL exists. Preview remains owner-controlled; an explicitly authorized preview uses the existing local-postgres.ps1 start command and npm run dev. No deployment or migration is performed. Evidence logs: D:/dev/tmp/mstar-step3c/final-motion.log, regression.log, production-browser.log, search.log, samples-dev.log and production-db.log. Six repeated wheel checks also passed.</x:v>
+      </x:c>
+      <x:c r="K26" s="141" t="str">
+        <x:v>Preceding 44f405a tracker correction preserved. Current Step 3C commit/origin/main push verified at closeout; exact hash in final report. No force-push. If any gate fails, F39 becomes Pending.</x:v>
+      </x:c>
+      <x:c r="L26" s="141" t="str">
+        <x:v>91-file current live baseline compared before synchronization; approved input/migration hashes preserved. Intended code/config/docs/workbook SHA-256 pairs verified at closeout. Secrets, dependencies, database runtime and caches excluded.</x:v>
+      </x:c>
+      <x:c r="M26" s="141" t="str">
+        <x:v>2026-10-10 R05: recorded newly supplied Step 3C as unstarted; no implementation authorization is inferred from attached guide text.
+2026-10-10 Step 3C: F39 implemented and verified across both languages and six widths. Shared requestAnimationFrame/WAAPI motion, card-edge scrolling, photo direction, modal exit/focus and reduced motion validated against the real app/PostgreSQL. Prior history retained. No later stage started.</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27"/>
@@ -34244,7 +34318,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd987da4139f240cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25862bcfd5a5450e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -34284,7 +34358,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>Done = completed task scope with evidence. Pending = started/blocked with named remaining work. Not started = task implementation has not begun. History is dated past evidence.</x:v>
+        <x:v>2026-10-10 Step 3C: F39 Done. 86 permanent IDs: 21 Done, 23 Pending, 42 Not started. All prior IDs and dated history retained; independent remaining tasks unchanged.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -34306,7 +34380,7 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -34325,7 +34399,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -34370,43 +34444,43 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="112.5" hidden="0" customHeight="1">
-      <x:c r="A6" s="104" t="str">
+      <x:c r="A6" s="129" t="str">
         <x:v>F03</x:v>
       </x:c>
-      <x:c r="B6" s="105" t="str">
+      <x:c r="B6" s="130" t="str">
         <x:v>Decision · Branding</x:v>
       </x:c>
-      <x:c r="C6" s="105" t="str">
+      <x:c r="C6" s="130" t="str">
         <x:v>Provide final crest or horizontal logo for white header</x:v>
       </x:c>
-      <x:c r="D6" s="105" t="str">
+      <x:c r="D6" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="105" t="str">
+      <x:c r="E6" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F6" s="105" t="str">
+      <x:c r="F6" s="130" t="str">
         <x:v>Approved temporary crest extracted and implemented. Owner will provide final header logo later.</x:v>
       </x:c>
-      <x:c r="G6" s="105" t="str">
+      <x:c r="G6" s="130" t="str">
         <x:v>Owner: supply final asset/version later; Codex: replace only approved logo.</x:v>
       </x:c>
-      <x:c r="H6" s="106" t="d">
+      <x:c r="H6" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="106" t="d">
+      <x:c r="I6" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="105" t="str">
+      <x:c r="J6" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K6" s="105" t="str">
+      <x:c r="K6" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L6" s="105" t="str">
+      <x:c r="L6" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M6" s="105" t="str">
+      <x:c r="M6" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: BUILD-SPEC §12 #2 and §11: logo source needed
 2026-10-09 owner update: Owner will add header logo later. Final asset/version deferred. Temporary approved crest can be used during foundation work.
@@ -34415,43 +34489,43 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="153" hidden="0" customHeight="1">
-      <x:c r="A7" s="104" t="str">
+      <x:c r="A7" s="129" t="str">
         <x:v>B09</x:v>
       </x:c>
-      <x:c r="B7" s="105" t="str">
+      <x:c r="B7" s="130" t="str">
         <x:v>Decision · Map</x:v>
       </x:c>
-      <x:c r="C7" s="105" t="str">
+      <x:c r="C7" s="130" t="str">
         <x:v>Select free open-source map library, tile/nearby provider and usage policy</x:v>
       </x:c>
-      <x:c r="D7" s="105" t="str">
+      <x:c r="D7" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E7" s="105" t="str">
+      <x:c r="E7" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F7" s="105" t="str">
+      <x:c r="F7" s="130" t="str">
         <x:v>Owner/V5 require free open-source mapping. Concrete provider/library/policy remain unresolved; Step 2 makes no choice.</x:v>
       </x:c>
-      <x:c r="G7" s="105" t="str">
+      <x:c r="G7" s="130" t="str">
         <x:v>Codex: present free options and wait for owner choice under Step 4 authorization.</x:v>
       </x:c>
-      <x:c r="H7" s="106" t="d">
+      <x:c r="H7" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="106" t="d">
+      <x:c r="I7" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J7" s="105" t="str">
+      <x:c r="J7" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K7" s="105" t="str">
+      <x:c r="K7" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L7" s="105" t="str">
+      <x:c r="L7" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M7" s="105" t="str">
+      <x:c r="M7" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: BUILD-SPEC §12 #8: map provider not selected
 2026-10-09 owner update: Owner requests free open-source mapping for now. Specific library and tile/nearby provider remain undecided.
@@ -34460,83 +34534,83 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="99" hidden="0" customHeight="1">
-      <x:c r="A8" s="104" t="str">
+      <x:c r="A8" s="129" t="str">
         <x:v>B17</x:v>
       </x:c>
-      <x:c r="B8" s="105" t="str">
+      <x:c r="B8" s="130" t="str">
         <x:v>Decision · Leads</x:v>
       </x:c>
-      <x:c r="C8" s="105" t="str">
+      <x:c r="C8" s="130" t="str">
         <x:v>Approve shared inbox versus listing agent enquiry destination</x:v>
       </x:c>
-      <x:c r="D8" s="105" t="str">
+      <x:c r="D8" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E8" s="105" t="str">
+      <x:c r="E8" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F8" s="105" t="str">
+      <x:c r="F8" s="130" t="str">
         <x:v>BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
-      <x:c r="G8" s="105" t="str">
+      <x:c r="G8" s="130" t="str">
         <x:v>Owner: select routing mode and mailbox</x:v>
       </x:c>
-      <x:c r="H8" s="106"/>
-      <x:c r="I8" s="106" t="d">
+      <x:c r="H8" s="131"/>
+      <x:c r="I8" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J8" s="105" t="str">
+      <x:c r="J8" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K8" s="105" t="str">
+      <x:c r="K8" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L8" s="105" t="str">
+      <x:c r="L8" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M8" s="105" t="str">
+      <x:c r="M8" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: BUILD-SPEC §12 #3 unresolved</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="126" hidden="0" customHeight="1">
-      <x:c r="A9" s="104" t="str">
+      <x:c r="A9" s="129" t="str">
         <x:v>B18</x:v>
       </x:c>
-      <x:c r="B9" s="105" t="str">
+      <x:c r="B9" s="130" t="str">
         <x:v>Decision · Chat</x:v>
       </x:c>
-      <x:c r="C9" s="105" t="str">
+      <x:c r="C9" s="130" t="str">
         <x:v>Approve company-wide versus per-agent LINE/WhatsApp IDs</x:v>
       </x:c>
-      <x:c r="D9" s="105" t="str">
+      <x:c r="D9" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E9" s="105" t="str">
+      <x:c r="E9" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F9" s="105" t="str">
+      <x:c r="F9" s="130" t="str">
         <x:v>Approved LINE/WhatsApp buttons implemented, disabled until real destinations exist. No contact invented. Routing, contacts and active green/white contrast review remain pending.</x:v>
       </x:c>
-      <x:c r="G9" s="105" t="str">
+      <x:c r="G9" s="130" t="str">
         <x:v>Owner: provide actual contacts/routing; Codex: integrate and review accessible contact actions later.</x:v>
       </x:c>
-      <x:c r="H9" s="106" t="d">
+      <x:c r="H9" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I9" s="106" t="d">
+      <x:c r="I9" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J9" s="105" t="str">
+      <x:c r="J9" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K9" s="105" t="str">
+      <x:c r="K9" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L9" s="105" t="str">
+      <x:c r="L9" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M9" s="105" t="str">
+      <x:c r="M9" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: BUILD-SPEC §12 #4 unresolved
 2026-10-09 owner update: Owner requests LINE and WhatsApp buttons first. Actual contacts and company versus per-agent routing remain unresolved.
@@ -34545,81 +34619,81 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="99" hidden="0" customHeight="1">
-      <x:c r="A10" s="104" t="str">
+      <x:c r="A10" s="129" t="str">
         <x:v>B23</x:v>
       </x:c>
-      <x:c r="B10" s="105" t="str">
+      <x:c r="B10" s="130" t="str">
         <x:v>Decision · Accounts</x:v>
       </x:c>
-      <x:c r="C10" s="105" t="str">
+      <x:c r="C10" s="130" t="str">
         <x:v>Approve LINE only or LINE+Google+email sign-in</x:v>
       </x:c>
-      <x:c r="D10" s="105" t="str">
+      <x:c r="D10" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E10" s="105" t="str">
+      <x:c r="E10" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F10" s="105" t="str">
+      <x:c r="F10" s="130" t="str">
         <x:v>BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
-      <x:c r="G10" s="105" t="str">
+      <x:c r="G10" s="130" t="str">
         <x:v>Owner: approve authentication providers</x:v>
       </x:c>
-      <x:c r="H10" s="106"/>
-      <x:c r="I10" s="106" t="d">
+      <x:c r="H10" s="131"/>
+      <x:c r="I10" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J10" s="105" t="str">
+      <x:c r="J10" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K10" s="105" t="str">
+      <x:c r="K10" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L10" s="105" t="str">
+      <x:c r="L10" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M10" s="105" t="str">
+      <x:c r="M10" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: BUILD-SPEC §12 #5 unresolved</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="99" hidden="0" customHeight="1">
-      <x:c r="A11" s="104" t="str">
+      <x:c r="A11" s="129" t="str">
         <x:v>B28</x:v>
       </x:c>
-      <x:c r="B11" s="105" t="str">
+      <x:c r="B11" s="130" t="str">
         <x:v>Decision · Currency</x:v>
       </x:c>
-      <x:c r="C11" s="105" t="str">
+      <x:c r="C11" s="130" t="str">
         <x:v>USD/THB preference and approximate conversion with an approved rate source</x:v>
       </x:c>
-      <x:c r="D11" s="105" t="str">
+      <x:c r="D11" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E11" s="105" t="str">
+      <x:c r="E11" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F11" s="105" t="str">
+      <x:c r="F11" s="130" t="str">
         <x:v>Partly complete: owner approved USD and THB, THB storage and preference selection. Approximate USD conversion still needs an approved rate source and implementation.</x:v>
       </x:c>
-      <x:c r="G11" s="105" t="str">
+      <x:c r="G11" s="130" t="str">
         <x:v>Owner/Codex: choose rate source in authorized currency work, then implement and verify conversion.</x:v>
       </x:c>
-      <x:c r="H11" s="106"/>
-      <x:c r="I11" s="106" t="d">
+      <x:c r="H11" s="131"/>
+      <x:c r="I11" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J11" s="105" t="str">
+      <x:c r="J11" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K11" s="105" t="str">
+      <x:c r="K11" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L11" s="105" t="str">
+      <x:c r="L11" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M11" s="105" t="str">
+      <x:c r="M11" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: BUILD-SPEC §12 #6 unresolved
 2026-10-09 owner update: Owner selected USD (US dollars) and THB. Store THB base; display approximate USD using daily rates. Rate source not selected; code not built.
@@ -34627,43 +34701,43 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="396" hidden="0" customHeight="1">
-      <x:c r="A12" s="104" t="str">
+      <x:c r="A12" s="129" t="str">
         <x:v>R01</x:v>
       </x:c>
-      <x:c r="B12" s="105" t="str">
+      <x:c r="B12" s="130" t="str">
         <x:v>Step 0 · Preparation</x:v>
       </x:c>
-      <x:c r="C12" s="105" t="str">
+      <x:c r="C12" s="130" t="str">
         <x:v>Inspect project; establish permanent rules, documentation, Git/live mirror and tracker</x:v>
       </x:c>
-      <x:c r="D12" s="105" t="str">
+      <x:c r="D12" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E12" s="105" t="str">
+      <x:c r="E12" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F12" s="105" t="str">
+      <x:c r="F12" s="130" t="str">
         <x:v>Preparation, rules, documentation, tracker and source mirror exist. A reusable in-project tracker-update utility and approved-original rendered-reference review remain unfinished. This one-off workbook correction does not complete those deliverables.</x:v>
       </x:c>
-      <x:c r="G12" s="105" t="str">
+      <x:c r="G12" s="130" t="str">
         <x:v>Codex: complete the separate utility/reference-review scope when authorized.</x:v>
       </x:c>
-      <x:c r="H12" s="106" t="d">
+      <x:c r="H12" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="106" t="d">
+      <x:c r="I12" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J12" s="105" t="str">
+      <x:c r="J12" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K12" s="105" t="str">
+      <x:c r="K12" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L12" s="105" t="str">
+      <x:c r="L12" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M12" s="105" t="str">
+      <x:c r="M12" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-09: Preparation recorded. Pending real-app/DB tests and localhost verification. Preserve this ID for subsequent updates.
 2026-10-09: cd897da pushed. Six sheets rendered; 81 IDs verified; 79 original IDs preserved. Preparation mirror hashes pass. R01 remains Pending for real-app/DB tests and localhost verification.
@@ -34678,43 +34752,43 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="301.5" hidden="0" customHeight="1">
-      <x:c r="A13" s="104" t="str">
+      <x:c r="A13" s="129" t="str">
         <x:v>F01</x:v>
       </x:c>
-      <x:c r="B13" s="105" t="str">
+      <x:c r="B13" s="130" t="str">
         <x:v>Step 1 · Design</x:v>
       </x:c>
-      <x:c r="C13" s="105" t="str">
+      <x:c r="C13" s="130" t="str">
         <x:v>Approved V3 CSS tokens, Prompt/Noto Sans Thai fonts, shared UI primitives</x:v>
       </x:c>
-      <x:c r="D13" s="105" t="str">
+      <x:c r="D13" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E13" s="105" t="str">
+      <x:c r="E13" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F13" s="105" t="str">
+      <x:c r="F13" s="130" t="str">
         <x:v>Implemented foundation and subsequent browser preference/search retests passed. Remaining separate closeout: approved-original rendered-reference comparison is unverified. No current browser/DB failure is inferred from old history.</x:v>
       </x:c>
-      <x:c r="G13" s="105" t="str">
+      <x:c r="G13" s="130" t="str">
         <x:v>Codex: resolve the separate rendered-reference closeout when authorized; preserve current passing implementation.</x:v>
       </x:c>
-      <x:c r="H13" s="106" t="d">
+      <x:c r="H13" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I13" s="106" t="d">
+      <x:c r="I13" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J13" s="105" t="str">
+      <x:c r="J13" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K13" s="105" t="str">
+      <x:c r="K13" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L13" s="105" t="str">
+      <x:c r="L13" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M13" s="105" t="str">
+      <x:c r="M13" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Exact tokens, self-hosted fonts and reusable buttons/inputs/chips/tabs/dialogs/skeletons/search fields implemented. Final browser retests and real PostgreSQL completion gate remain pending. Owner requested localhost closure; do not reopen automatically.
@@ -34724,43 +34798,43 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="288" hidden="0" customHeight="1">
-      <x:c r="A14" s="104" t="str">
+      <x:c r="A14" s="129" t="str">
         <x:v>F04</x:v>
       </x:c>
-      <x:c r="B14" s="105" t="str">
+      <x:c r="B14" s="130" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C14" s="105" t="str">
+      <x:c r="C14" s="130" t="str">
         <x:v>Sticky desktop header with one-line navigation and rectangular Sign in</x:v>
       </x:c>
-      <x:c r="D14" s="105" t="str">
+      <x:c r="D14" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E14" s="105" t="str">
+      <x:c r="E14" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F14" s="105" t="str">
+      <x:c r="F14" s="130" t="str">
         <x:v>Implemented foundation and subsequent browser preference/search retests passed. Remaining separate closeout: approved-original rendered-reference comparison is unverified. No current browser/DB failure is inferred from old history.</x:v>
       </x:c>
-      <x:c r="G14" s="105" t="str">
+      <x:c r="G14" s="130" t="str">
         <x:v>Codex: resolve the separate rendered-reference closeout when authorized; preserve current passing implementation.</x:v>
       </x:c>
-      <x:c r="H14" s="106" t="d">
+      <x:c r="H14" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I14" s="106" t="d">
+      <x:c r="I14" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J14" s="105" t="str">
+      <x:c r="J14" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K14" s="105" t="str">
+      <x:c r="K14" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L14" s="105" t="str">
+      <x:c r="L14" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M14" s="105" t="str">
+      <x:c r="M14" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Sticky 64px header, five desktop links, language/currency selector, Saved and rectangular Sign in implemented. All eight shell tests passed. Preference save fix needs retesting. Owner requested localhost closure; do not reopen automatically.
@@ -34770,43 +34844,43 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="288" hidden="0" customHeight="1">
-      <x:c r="A15" s="104" t="str">
+      <x:c r="A15" s="129" t="str">
         <x:v>F05</x:v>
       </x:c>
-      <x:c r="B15" s="105" t="str">
+      <x:c r="B15" s="130" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C15" s="105" t="str">
+      <x:c r="C15" s="130" t="str">
         <x:v>Phone header, bottom tabs and responsive breakpoints</x:v>
       </x:c>
-      <x:c r="D15" s="105" t="str">
+      <x:c r="D15" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E15" s="105" t="str">
+      <x:c r="E15" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F15" s="105" t="str">
+      <x:c r="F15" s="130" t="str">
         <x:v>Implemented foundation and subsequent browser preference/search retests passed. Remaining separate closeout: approved-original rendered-reference comparison is unverified. No current browser/DB failure is inferred from old history.</x:v>
       </x:c>
-      <x:c r="G15" s="105" t="str">
+      <x:c r="G15" s="130" t="str">
         <x:v>Codex: resolve the separate rendered-reference closeout when authorized; preserve current passing implementation.</x:v>
       </x:c>
-      <x:c r="H15" s="106" t="d">
+      <x:c r="H15" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I15" s="106" t="d">
+      <x:c r="I15" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J15" s="105" t="str">
+      <x:c r="J15" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K15" s="105" t="str">
+      <x:c r="K15" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L15" s="105" t="str">
+      <x:c r="L15" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M15" s="105" t="str">
+      <x:c r="M15" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Responsive phone header and five safe-area bottom tabs implemented. 390px Thai/English shell tests passed. Final phone search containment change needs retesting. Owner requested localhost closure; do not reopen automatically.
@@ -34816,43 +34890,43 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="288" hidden="0" customHeight="1">
-      <x:c r="A16" s="105" t="str">
+      <x:c r="A16" s="130" t="str">
         <x:v>F06</x:v>
       </x:c>
-      <x:c r="B16" s="105" t="str">
+      <x:c r="B16" s="130" t="str">
         <x:v>Step 1 · Layout</x:v>
       </x:c>
-      <x:c r="C16" s="105" t="str">
+      <x:c r="C16" s="130" t="str">
         <x:v>Light footer, company links, contact and PDPA link</x:v>
       </x:c>
-      <x:c r="D16" s="105" t="str">
+      <x:c r="D16" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E16" s="105" t="str">
+      <x:c r="E16" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F16" s="105" t="str">
+      <x:c r="F16" s="130" t="str">
         <x:v>Implemented foundation and subsequent browser preference/search retests passed. Remaining separate closeout: approved-original rendered-reference comparison is unverified. No current browser/DB failure is inferred from old history.</x:v>
       </x:c>
-      <x:c r="G16" s="105" t="str">
+      <x:c r="G16" s="130" t="str">
         <x:v>Codex: resolve the separate rendered-reference closeout when authorized; preserve current passing implementation.</x:v>
       </x:c>
-      <x:c r="H16" s="106" t="d">
+      <x:c r="H16" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I16" s="106" t="d">
+      <x:c r="I16" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J16" s="105" t="str">
+      <x:c r="J16" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K16" s="105" t="str">
+      <x:c r="K16" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L16" s="105" t="str">
+      <x:c r="L16" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M16" s="105" t="str">
+      <x:c r="M16" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Approved soft-background footer with bilingual company/area/help links implemented. Actual LINE ID omitted until provided. Shell tests passed. Owner requested localhost closure; do not reopen automatically.
@@ -34862,43 +34936,43 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="315" hidden="0" customHeight="1">
-      <x:c r="A17" s="105" t="str">
+      <x:c r="A17" s="130" t="str">
         <x:v>F07</x:v>
       </x:c>
-      <x:c r="B17" s="105" t="str">
+      <x:c r="B17" s="130" t="str">
         <x:v>Step 1 · i18n</x:v>
       </x:c>
-      <x:c r="C17" s="105" t="str">
+      <x:c r="C17" s="130" t="str">
         <x:v>Thai/English routes, language switch and localized formatting</x:v>
       </x:c>
-      <x:c r="D17" s="105" t="str">
+      <x:c r="D17" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E17" s="105" t="str">
+      <x:c r="E17" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F17" s="105" t="str">
+      <x:c r="F17" s="130" t="str">
         <x:v>Implemented foundation and subsequent browser preference/search retests passed. Remaining separate closeout: approved-original rendered-reference comparison is unverified. No current browser/DB failure is inferred from old history.</x:v>
       </x:c>
-      <x:c r="G17" s="105" t="str">
+      <x:c r="G17" s="130" t="str">
         <x:v>Codex: resolve the separate rendered-reference closeout when authorized; preserve current passing implementation.</x:v>
       </x:c>
-      <x:c r="H17" s="106" t="d">
+      <x:c r="H17" s="131" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I17" s="106" t="d">
+      <x:c r="I17" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J17" s="105" t="str">
+      <x:c r="J17" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: PASS: real PostgreSQL 18.6, 12/12 DB groups (migrations/rerun, fictional seed/rerun, insert/readback, joins, constraints/FKs, filter scope, indexes/EXPLAIN, privacy/permissions, pg_dump, committed rollback/restore). PASS: build/TypeScript, 16/16 Playwright at 390/768/1024/1440 in TH/EN. Real health 200/ready true, stopped DB 503, recovered 200. No implemented forms/admin; no form-delivery claim. Servers stop after task. Full npm audit: zero findings.</x:v>
       </x:c>
-      <x:c r="K17" s="105" t="str">
+      <x:c r="K17" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L17" s="105" t="str">
+      <x:c r="L17" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M17" s="105" t="str">
+      <x:c r="M17" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 foundation: Thai/English routes, Accept-Language and explicit preference cookies implemented. Redirect checks passed. Four browser preference/search flows failed before closure; Host-based origin fix compiles but remains untested in browser. Owner requested localhost closure; do not reopen automatically.
@@ -34908,43 +34982,43 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="139.5" hidden="0" customHeight="1">
-      <x:c r="A18" s="105" t="str">
+      <x:c r="A18" s="130" t="str">
         <x:v>F25</x:v>
       </x:c>
-      <x:c r="B18" s="105" t="str">
+      <x:c r="B18" s="130" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C18" s="105" t="str">
+      <x:c r="C18" s="130" t="str">
         <x:v>Small home listing rows; regional tiles with real listing counts (Steps 3B/7)</x:v>
       </x:c>
-      <x:c r="D18" s="105" t="str">
+      <x:c r="D18" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E18" s="105" t="str">
+      <x:c r="E18" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F18" s="105" t="str">
+      <x:c r="F18" s="130" t="str">
         <x:v>Step 3B implements approved topic rows, separate small cards, responsive rails, featured/newest safe queries, saves and honest local samples. Regional tiles/live location counts remain Step 7 and are not implemented. This broad task is therefore Pending; the scoped Step 3B work is R04 Done.</x:v>
       </x:c>
-      <x:c r="G18" s="105" t="str">
+      <x:c r="G18" s="130" t="str">
         <x:v>Codex: wait for Step 7 authorization to add regional tiles/live counts. Future admin row management requires its approved stage. Stop before Step 4 now.</x:v>
       </x:c>
-      <x:c r="H18" s="106" t="d">
+      <x:c r="H18" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I18" s="106" t="d">
+      <x:c r="I18" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J18" s="105" t="str">
+      <x:c r="J18" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K18" s="105" t="str">
+      <x:c r="K18" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L18" s="105" t="str">
+      <x:c r="L18" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M18" s="105" t="str">
+      <x:c r="M18" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 7 uses Step 3 cards: five tabs, arrows, See all, 3/2/1.1 visible cards, swipe/scroll-snap, featured first then newest, up to 12 per tab. Not implemented.
@@ -34953,41 +35027,41 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="99" hidden="0" customHeight="1">
-      <x:c r="A19" s="105" t="str">
+      <x:c r="A19" s="130" t="str">
         <x:v>F21</x:v>
       </x:c>
-      <x:c r="B19" s="105" t="str">
+      <x:c r="B19" s="130" t="str">
         <x:v>Step 6 · Contact</x:v>
       </x:c>
-      <x:c r="C19" s="105" t="str">
+      <x:c r="C19" s="130" t="str">
         <x:v>Shared agent enquiry form, card Contact agent dialog, desktop sticky box and phone contact bar</x:v>
       </x:c>
-      <x:c r="D19" s="105" t="str">
+      <x:c r="D19" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E19" s="105" t="str">
+      <x:c r="E19" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F19" s="105" t="str">
+      <x:c r="F19" s="130" t="str">
         <x:v>Partly complete: Card contact dialog and listing-prefilled message exist. Shared submitting form, property contact box and phone bar are unfinished; enquiries cannot be sent.</x:v>
       </x:c>
-      <x:c r="G19" s="105" t="str">
+      <x:c r="G19" s="130" t="str">
         <x:v>Codex: Authorize Step 6, resolve B17/B18 contacts, then implement and test the shared form.</x:v>
       </x:c>
-      <x:c r="H19" s="106"/>
-      <x:c r="I19" s="106" t="d">
+      <x:c r="H19" s="131"/>
+      <x:c r="I19" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J19" s="105" t="str">
+      <x:c r="J19" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K19" s="105" t="str">
+      <x:c r="K19" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L19" s="105" t="str">
+      <x:c r="L19" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M19" s="105" t="str">
+      <x:c r="M19" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 Original planning evidence: Not yet implemented; follow approved V3 handoff.
 2026-10-09 V5 adoption: V5 Step 6 wires the card dialog and property form through one component/action. No implementation started; destinations still unresolved.
@@ -34995,361 +35069,361 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="99" hidden="0" customHeight="1">
-      <x:c r="A20" s="105" t="str">
+      <x:c r="A20" s="130" t="str">
         <x:v>F22</x:v>
       </x:c>
-      <x:c r="B20" s="105" t="str">
+      <x:c r="B20" s="130" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C20" s="105" t="str">
+      <x:c r="C20" s="130" t="str">
         <x:v>Single-image hero and compact photography-first layout</x:v>
       </x:c>
-      <x:c r="D20" s="105" t="str">
+      <x:c r="D20" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E20" s="105" t="str">
+      <x:c r="E20" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F20" s="105" t="str">
+      <x:c r="F20" s="130" t="str">
         <x:v>Partly complete: Homepage hero heading, supporting text and foundation layout exist. Approved single-photo hero asset and completed photography layout are missing.</x:v>
       </x:c>
-      <x:c r="G20" s="105" t="str">
+      <x:c r="G20" s="130" t="str">
         <x:v>Codex: Complete approved photography hero in the authorized homepage stage; use an approved genuine asset.</x:v>
       </x:c>
-      <x:c r="H20" s="106"/>
-      <x:c r="I20" s="106" t="d">
+      <x:c r="H20" s="131"/>
+      <x:c r="I20" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J20" s="105" t="str">
+      <x:c r="J20" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K20" s="105" t="str">
+      <x:c r="K20" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L20" s="105" t="str">
+      <x:c r="L20" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M20" s="105" t="str">
+      <x:c r="M20" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Homepage hero heading, supporting text and foundation layout exist. Approved single-photo hero asset and completed photography layout are missing.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="99" hidden="0" customHeight="1">
-      <x:c r="A21" s="105" t="str">
+      <x:c r="A21" s="130" t="str">
         <x:v>F23</x:v>
       </x:c>
-      <x:c r="B21" s="105" t="str">
+      <x:c r="B21" s="130" t="str">
         <x:v>Step 7 · Home</x:v>
       </x:c>
-      <x:c r="C21" s="105" t="str">
+      <x:c r="C21" s="130" t="str">
         <x:v>Shared search box with Buy/Rent/Projects/Investment tabs</x:v>
       </x:c>
-      <x:c r="D21" s="105" t="str">
+      <x:c r="D21" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E21" s="105" t="str">
+      <x:c r="E21" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F21" s="105" t="str">
+      <x:c r="F21" s="130" t="str">
         <x:v>Partly complete: Homepage Buy/Rent/Projects/Investment tabs, text location field, phone sheet and safe buy/rent/invest URL navigation exist. Type/price/beds fields are display-only; full search controls and project results are unfinished.</x:v>
       </x:c>
-      <x:c r="G21" s="105" t="str">
+      <x:c r="G21" s="130" t="str">
         <x:v>Codex: Complete functional shared fields and project search only in their authorized stages.</x:v>
       </x:c>
-      <x:c r="H21" s="106"/>
-      <x:c r="I21" s="106" t="d">
+      <x:c r="H21" s="131"/>
+      <x:c r="I21" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J21" s="105" t="str">
+      <x:c r="J21" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K21" s="105" t="str">
+      <x:c r="K21" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L21" s="105" t="str">
+      <x:c r="L21" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M21" s="105" t="str">
+      <x:c r="M21" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Homepage Buy/Rent/Projects/Investment tabs, text location field, phone sheet and safe buy/rent/invest URL navigation exist. Type/price/beds fields are display-only; full search controls and project results are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="99" hidden="0" customHeight="1">
-      <x:c r="A22" s="105" t="str">
+      <x:c r="A22" s="130" t="str">
         <x:v>F31</x:v>
       </x:c>
-      <x:c r="B22" s="105" t="str">
+      <x:c r="B22" s="130" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C22" s="105" t="str">
+      <x:c r="C22" s="130" t="str">
         <x:v>Homes, searches and viewings; local save without account</x:v>
       </x:c>
-      <x:c r="D22" s="105" t="str">
+      <x:c r="D22" s="130" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E22" s="105" t="str">
+      <x:c r="E22" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F22" s="105" t="str">
+      <x:c r="F22" s="130" t="str">
         <x:v>Partly complete: Device save hearts, reload persistence and shared storage across both card sizes exist. Saved page Homes/Searches/Viewings and local saved searches are unfinished.</x:v>
       </x:c>
-      <x:c r="G22" s="105" t="str">
+      <x:c r="G22" s="130" t="str">
         <x:v>Codex: Complete Saved page and remaining device workflows under Step 9 authorization.</x:v>
       </x:c>
-      <x:c r="H22" s="106"/>
-      <x:c r="I22" s="106" t="d">
+      <x:c r="H22" s="131"/>
+      <x:c r="I22" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J22" s="105" t="str">
+      <x:c r="J22" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K22" s="105" t="str">
+      <x:c r="K22" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L22" s="105" t="str">
+      <x:c r="L22" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M22" s="105" t="str">
+      <x:c r="M22" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Device save hearts, reload persistence and shared storage across both card sizes exist. Saved page Homes/Searches/Viewings and local saved searches are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="99" hidden="0" customHeight="1">
-      <x:c r="A23" s="105" t="str">
+      <x:c r="A23" s="130" t="str">
         <x:v>B08</x:v>
       </x:c>
-      <x:c r="B23" s="105" t="str">
+      <x:c r="B23" s="130" t="str">
         <x:v>Step 4 · Map</x:v>
       </x:c>
-      <x:c r="C23" s="105" t="str">
+      <x:c r="C23" s="130" t="str">
         <x:v>Geospatial index, bounding-box search and hidden-pin privacy</x:v>
       </x:c>
-      <x:c r="D23" s="105" t="str">
+      <x:c r="D23" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E23" s="105" t="str">
+      <x:c r="E23" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F23" s="105" t="str">
+      <x:c r="F23" s="130" t="str">
         <x:v>Partly complete: Bounding-coordinate index, validated bbox search and hidden-location exclusion exist in the schema/search layer. Map pins, geographic integration and full map-stage verification are unfinished.</x:v>
       </x:c>
-      <x:c r="G23" s="105" t="str">
+      <x:c r="G23" s="130" t="str">
         <x:v>Codex: Complete geospatial/map behavior under Step 4 after B09 choice; preserve hidden-location privacy.</x:v>
       </x:c>
-      <x:c r="H23" s="106"/>
-      <x:c r="I23" s="106" t="d">
+      <x:c r="H23" s="131"/>
+      <x:c r="I23" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J23" s="105" t="str">
+      <x:c r="J23" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K23" s="105" t="str">
+      <x:c r="K23" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L23" s="105" t="str">
+      <x:c r="L23" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M23" s="105" t="str">
+      <x:c r="M23" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Bounding-coordinate index, validated bbox search and hidden-location exclusion exist in the schema/search layer. Map pins, geographic integration and full map-stage verification are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="99" hidden="0" customHeight="1">
-      <x:c r="A24" s="105" t="str">
+      <x:c r="A24" s="130" t="str">
         <x:v>B11</x:v>
       </x:c>
-      <x:c r="B24" s="105" t="str">
+      <x:c r="B24" s="130" t="str">
         <x:v>Step 5 · Media</x:v>
       </x:c>
-      <x:c r="C24" s="105" t="str">
+      <x:c r="C24" s="130" t="str">
         <x:v>Photo/floorplan/video metadata and safe image upload pipeline</x:v>
       </x:c>
-      <x:c r="D24" s="105" t="str">
+      <x:c r="D24" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E24" s="105" t="str">
+      <x:c r="E24" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F24" s="105" t="str">
+      <x:c r="F24" s="130" t="str">
         <x:v>Partly complete: Photo/floorplan/video/360 metadata, safe URL constraints and capped photo reads exist. Upload pipeline, file validation and production media handling are unfinished.</x:v>
       </x:c>
-      <x:c r="G24" s="105" t="str">
+      <x:c r="G24" s="130" t="str">
         <x:v>Codex: Complete and test safe media ingestion/upload in its authorized stage.</x:v>
       </x:c>
-      <x:c r="H24" s="106"/>
-      <x:c r="I24" s="106" t="d">
+      <x:c r="H24" s="131"/>
+      <x:c r="I24" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J24" s="105" t="str">
+      <x:c r="J24" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K24" s="105" t="str">
+      <x:c r="K24" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L24" s="105" t="str">
+      <x:c r="L24" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M24" s="105" t="str">
+      <x:c r="M24" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Photo/floorplan/video/360 metadata, safe URL constraints and capped photo reads exist. Upload pipeline, file validation and production media handling are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="99" hidden="0" customHeight="1">
-      <x:c r="A25" s="105" t="str">
+      <x:c r="A25" s="130" t="str">
         <x:v>B15</x:v>
       </x:c>
-      <x:c r="B25" s="105" t="str">
+      <x:c r="B25" s="130" t="str">
         <x:v>Step 6 · Leads</x:v>
       </x:c>
-      <x:c r="C25" s="105" t="str">
+      <x:c r="C25" s="130" t="str">
         <x:v>PDPA consent version, UTM/source, language and audit metadata</x:v>
       </x:c>
-      <x:c r="D25" s="105" t="str">
+      <x:c r="D25" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E25" s="105" t="str">
+      <x:c r="E25" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F25" s="105" t="str">
+      <x:c r="F25" s="130" t="str">
         <x:v>Partly complete: Enquiry schema stores versioned consent, consent timestamp, source URL, UTM, language and audit dates. Isolated DB fixture readback passed. Live form capture and request validation are unfinished.</x:v>
       </x:c>
-      <x:c r="G25" s="105" t="str">
+      <x:c r="G25" s="130" t="str">
         <x:v>Codex: Implement and verify real request-to-database metadata capture under Step 6.</x:v>
       </x:c>
-      <x:c r="H25" s="106"/>
-      <x:c r="I25" s="106" t="d">
+      <x:c r="H25" s="131"/>
+      <x:c r="I25" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J25" s="105" t="str">
+      <x:c r="J25" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K25" s="105" t="str">
+      <x:c r="K25" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L25" s="105" t="str">
+      <x:c r="L25" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M25" s="105" t="str">
+      <x:c r="M25" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Enquiry schema stores versioned consent, consent timestamp, source URL, UTM, language and audit dates. Isolated DB fixture readback passed. Live form capture and request validation are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="99" hidden="0" customHeight="1">
-      <x:c r="A26" s="105" t="str">
+      <x:c r="A26" s="130" t="str">
         <x:v>B20</x:v>
       </x:c>
-      <x:c r="B26" s="105" t="str">
+      <x:c r="B26" s="130" t="str">
         <x:v>Step 8 · Projects</x:v>
       </x:c>
-      <x:c r="C26" s="105" t="str">
+      <x:c r="C26" s="130" t="str">
         <x:v>Project/unit/plot status logic and validation</x:v>
       </x:c>
-      <x:c r="D26" s="105" t="str">
+      <x:c r="D26" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E26" s="105" t="str">
+      <x:c r="E26" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F26" s="105" t="str">
+      <x:c r="F26" s="130" t="str">
         <x:v>Partly complete: Project/unit/plot schema, status enums and parent/shape/value constraints exist; DB joins/constraint fixtures passed. Application status transitions and booking/business validation are unfinished.</x:v>
       </x:c>
-      <x:c r="G26" s="105" t="str">
+      <x:c r="G26" s="130" t="str">
         <x:v>Codex: Complete project/plot business behavior under Step 8 authorization.</x:v>
       </x:c>
-      <x:c r="H26" s="106"/>
-      <x:c r="I26" s="106" t="d">
+      <x:c r="H26" s="131"/>
+      <x:c r="I26" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J26" s="105" t="str">
+      <x:c r="J26" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K26" s="105" t="str">
+      <x:c r="K26" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L26" s="105" t="str">
+      <x:c r="L26" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M26" s="105" t="str">
+      <x:c r="M26" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Project/unit/plot schema, status enums and parent/shape/value constraints exist; DB joins/constraint fixtures passed. Application status transitions and booking/business validation are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="99" hidden="0" customHeight="1">
-      <x:c r="A27" s="105" t="str">
+      <x:c r="A27" s="130" t="str">
         <x:v>B22</x:v>
       </x:c>
-      <x:c r="B27" s="105" t="str">
+      <x:c r="B27" s="130" t="str">
         <x:v>Step 9 · Saved</x:v>
       </x:c>
-      <x:c r="C27" s="105" t="str">
+      <x:c r="C27" s="130" t="str">
         <x:v>Saved listings/searches persistence, new-match calculations</x:v>
       </x:c>
-      <x:c r="D27" s="105" t="str">
+      <x:c r="D27" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E27" s="105" t="str">
+      <x:c r="E27" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F27" s="105" t="str">
+      <x:c r="F27" s="130" t="str">
         <x:v>Partly complete: Saved-listing/search tables and constraints exist; card hearts persist on this device. Authenticated save operations, saved-search workflows and new-match calculations are unfinished.</x:v>
       </x:c>
-      <x:c r="G27" s="105" t="str">
+      <x:c r="G27" s="130" t="str">
         <x:v>Codex: Complete persistence and new-match workflows under the authorized Saved/account stages.</x:v>
       </x:c>
-      <x:c r="H27" s="106"/>
-      <x:c r="I27" s="106" t="d">
+      <x:c r="H27" s="131"/>
+      <x:c r="I27" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J27" s="105" t="str">
+      <x:c r="J27" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K27" s="105" t="str">
+      <x:c r="K27" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L27" s="105" t="str">
+      <x:c r="L27" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M27" s="105" t="str">
+      <x:c r="M27" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Saved-listing/search tables and constraints exist; card hearts persist on this device. Authenticated save operations, saved-search workflows and new-match calculations are unfinished.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="99" hidden="0" customHeight="1">
-      <x:c r="A28" s="105" t="str">
+      <x:c r="A28" s="130" t="str">
         <x:v>B31</x:v>
       </x:c>
-      <x:c r="B28" s="105" t="str">
+      <x:c r="B28" s="130" t="str">
         <x:v>Step 12 · Quality</x:v>
       </x:c>
-      <x:c r="C28" s="105" t="str">
+      <x:c r="C28" s="130" t="str">
         <x:v>Real PostgreSQL integration/Playwright tests and EXPLAIN ANALYZE</x:v>
       </x:c>
-      <x:c r="D28" s="105" t="str">
+      <x:c r="D28" s="130" t="str">
         <x:v>Backend</x:v>
       </x:c>
-      <x:c r="E28" s="105" t="str">
+      <x:c r="E28" s="130" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="F28" s="105" t="str">
+      <x:c r="F28" s="130" t="str">
         <x:v>Partly complete: Real PostgreSQL regression and application/Playwright suites exist and prior results passed. Final whole-project QA and realistic-volume EXPLAIN ANALYZE are unfinished.</x:v>
       </x:c>
-      <x:c r="G28" s="105" t="str">
+      <x:c r="G28" s="130" t="str">
         <x:v>Codex: Run complete scope and performance evidence in the final authorized quality stage.</x:v>
       </x:c>
-      <x:c r="H28" s="106"/>
-      <x:c r="I28" s="106" t="d">
+      <x:c r="H28" s="131"/>
+      <x:c r="I28" s="131" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J28" s="105" t="str">
+      <x:c r="J28" s="130" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction. Earlier evidence: 2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K28" s="105" t="str">
+      <x:c r="K28" s="130" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L28" s="105" t="str">
+      <x:c r="L28" s="130" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M28" s="105" t="str">
+      <x:c r="M28" s="130" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe their dated stage; use Status and Current state for today's result.
 2026-10-10 R05 audit: Not started changed to Pending. Partly complete: Real PostgreSQL regression and application/Playwright suites exist and prior results passed. Final whole-project QA and realistic-volume EXPLAIN ANALYZE are unfinished.</x:v>
       </x:c>
@@ -42457,7 +42531,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c03d13268eb4bb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5db7738e25304594"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42497,7 +42571,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>Done = completed task scope with evidence. Pending = started/blocked with named remaining work. Not started = task implementation has not begun. History is dated past evidence.</x:v>
+        <x:v>2026-10-10 Step 3C: F39 Done. 86 permanent IDs: 21 Done, 23 Pending, 42 Not started. All prior IDs and dated history retained; independent remaining tasks unchanged.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -42519,7 +42593,7 @@
       </x:c>
       <x:c r="D3" s="18" t="n">
         <x:f>COUNTA('Done'!A6:A500)</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>Pending</x:v>
@@ -42538,7 +42612,7 @@
       </x:c>
       <x:c r="G4" s="22" t="n">
         <x:f>COUNTA('Not started'!A6:A500)</x:f>
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -42583,1645 +42657,1619 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="85.5" hidden="0" customHeight="1">
-      <x:c r="A6" s="110" t="str">
+      <x:c r="A6" s="132" t="str">
         <x:v>F32</x:v>
       </x:c>
-      <x:c r="B6" s="111" t="str">
+      <x:c r="B6" s="133" t="str">
         <x:v>Step 10A · Wireframe</x:v>
       </x:c>
-      <x:c r="C6" s="111" t="str">
+      <x:c r="C6" s="133" t="str">
         <x:v>Owner-approved login/register/account wireframe before coding</x:v>
       </x:c>
-      <x:c r="D6" s="111" t="str">
+      <x:c r="D6" s="133" t="str">
         <x:v>Frontend</x:v>
       </x:c>
-      <x:c r="E6" s="111" t="str">
+      <x:c r="E6" s="133" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="F6" s="111" t="str">
+      <x:c r="F6" s="133" t="str">
         <x:v>No production wireframe has been drafted for this task. Future design must precede owner approval; no draft is currently waiting for review.</x:v>
       </x:c>
-      <x:c r="G6" s="111" t="str">
+      <x:c r="G6" s="133" t="str">
         <x:v>Codex: draft only in the authorized account/admin design stage; owner reviews the actual draft afterward.</x:v>
       </x:c>
-      <x:c r="H6" s="112"/>
-      <x:c r="I6" s="112" t="d">
+      <x:c r="H6" s="134"/>
+      <x:c r="I6" s="134" t="d">
         <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="J6" s="111" t="str">
+      <x:c r="J6" s="133" t="str">
         <x:v>2026-10-10 tracker audit: reviewed current source and dated testing.md evidence. No new application/browser/PostgreSQL run for this workbook-only correction.</x:v>
       </x:c>
-      <x:c r="K6" s="111" t="str">
+      <x:c r="K6" s="133" t="str">
         <x:v>Workbook/document correction committed and pushed during closeout; exact hash appears in final report. Other uncommitted owner files are excluded.</x:v>
       </x:c>
-      <x:c r="L6" s="111" t="str">
+      <x:c r="L6" s="133" t="str">
         <x:v>Intended workbook and nine documents synchronized by SHA-256 after baseline checks. Pre-existing divergent handoff revisions are preserved.</x:v>
       </x:c>
-      <x:c r="M6" s="111" t="str">
+      <x:c r="M6" s="133" t="str">
         <x:v>HISTORICAL RECORD — earlier statements below describe the